--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BD98D9F-1127-4A1C-B696-1253C8D227AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61230B95-132B-463E-9B4E-DDD8FBE3E3B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_foe_v8" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="掉落" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_foe_v8!$A$2:$AF$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_foe_v8!$A$2:$AF$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="204">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -744,7 +744,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -809,6 +809,13 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -904,7 +911,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2">
@@ -948,6 +955,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1244,7 +1254,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG51"/>
+  <dimension ref="A1:AG65"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.125" style="4" bestFit="1" customWidth="1"/>
@@ -4430,58 +4440,58 @@
     </row>
     <row r="33" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A33" s="7">
-        <v>121101</v>
+        <v>110201</v>
       </c>
       <c r="B33" s="7">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="F33" s="7">
-        <v>1000102</v>
-      </c>
-      <c r="G33" s="7">
-        <v>12</v>
-      </c>
-      <c r="H33" s="7">
-        <v>1</v>
-      </c>
-      <c r="I33" s="7" t="s">
+      <c r="F33" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G33" s="15">
+        <v>1</v>
+      </c>
+      <c r="H33" s="15">
+        <v>2</v>
+      </c>
+      <c r="I33" s="15" t="s">
         <v>18</v>
       </c>
       <c r="J33" s="7">
         <v>0</v>
       </c>
-      <c r="K33" s="7" t="s">
-        <v>184</v>
+      <c r="K33" s="7">
+        <v>800001021</v>
       </c>
       <c r="L33" s="7">
-        <v>800001011</v>
+        <v>800001021</v>
       </c>
       <c r="M33" s="7">
-        <v>12</v>
-      </c>
-      <c r="N33" s="7">
-        <v>70</v>
+        <v>1</v>
+      </c>
+      <c r="N33" s="17">
+        <v>120</v>
       </c>
       <c r="O33" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P33" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q33" s="7">
         <v>0</v>
       </c>
       <c r="R33" s="7">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="S33" s="7">
         <v>-3000</v>
@@ -4493,16 +4503,16 @@
         <v>0</v>
       </c>
       <c r="V33" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="W33" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="X33" s="7" t="s">
-        <v>201</v>
+        <v>143</v>
       </c>
       <c r="Y33" s="14">
-        <v>201001011</v>
+        <v>20010001</v>
       </c>
       <c r="Z33" s="14">
         <v>0</v>
@@ -4511,7 +4521,7 @@
         <v>1</v>
       </c>
       <c r="AB33" s="4" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="AC33" s="7">
         <v>10000</v>
@@ -4520,69 +4530,69 @@
         <v>10000</v>
       </c>
       <c r="AE33" s="7">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF33" s="4">
         <v>40</v>
       </c>
       <c r="AG33" s="4">
-        <v>10000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A34" s="7">
-        <v>121102</v>
+        <v>110301</v>
       </c>
       <c r="B34" s="7">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>67</v>
+        <v>22</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="F34" s="7">
-        <v>1000102</v>
-      </c>
-      <c r="G34" s="7">
-        <v>12</v>
-      </c>
-      <c r="H34" s="7">
-        <v>1</v>
-      </c>
-      <c r="I34" s="7" t="s">
+      <c r="F34" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G34" s="15">
+        <v>1</v>
+      </c>
+      <c r="H34" s="15">
+        <v>2</v>
+      </c>
+      <c r="I34" s="15" t="s">
         <v>18</v>
       </c>
       <c r="J34" s="7">
         <v>0</v>
       </c>
-      <c r="K34" s="7" t="s">
-        <v>185</v>
+      <c r="K34" s="7">
+        <v>800001021</v>
       </c>
       <c r="L34" s="7">
         <v>800001021</v>
       </c>
       <c r="M34" s="7">
-        <v>12</v>
-      </c>
-      <c r="N34" s="7">
-        <v>200</v>
+        <v>1</v>
+      </c>
+      <c r="N34" s="17">
+        <v>310</v>
       </c>
       <c r="O34" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P34" s="7">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="Q34" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R34" s="7">
-        <v>216</v>
+        <v>25</v>
       </c>
       <c r="S34" s="7">
         <v>-3000</v>
@@ -4591,19 +4601,19 @@
         <v>1</v>
       </c>
       <c r="U34" s="7">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="V34" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="W34" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="X34" s="7" t="s">
-        <v>201</v>
+        <v>143</v>
       </c>
       <c r="Y34" s="14">
-        <v>201002011</v>
+        <v>20010001</v>
       </c>
       <c r="Z34" s="14">
         <v>0</v>
@@ -4612,7 +4622,7 @@
         <v>1</v>
       </c>
       <c r="AB34" s="4" t="s">
-        <v>197</v>
+        <v>157</v>
       </c>
       <c r="AC34" s="7">
         <v>10000</v>
@@ -4621,108 +4631,108 @@
         <v>10000</v>
       </c>
       <c r="AE34" s="7">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF34" s="4">
         <v>40</v>
       </c>
       <c r="AG34" s="4">
-        <v>10000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A35" s="12">
-        <v>121103</v>
-      </c>
-      <c r="B35" s="12">
-        <v>12</v>
-      </c>
-      <c r="C35" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="D35" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="E35" s="6" t="s">
+      <c r="A35" s="7">
+        <v>110302</v>
+      </c>
+      <c r="B35" s="7">
+        <v>1</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E35" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="F35" s="12">
-        <v>1000102</v>
-      </c>
-      <c r="G35" s="12">
-        <v>12</v>
-      </c>
-      <c r="H35" s="12">
-        <v>1</v>
-      </c>
-      <c r="I35" s="12" t="s">
+      <c r="F35" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G35" s="15">
+        <v>1</v>
+      </c>
+      <c r="H35" s="15">
+        <v>2</v>
+      </c>
+      <c r="I35" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="J35" s="12">
-        <v>0</v>
-      </c>
-      <c r="K35" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="L35" s="12">
+      <c r="J35" s="7">
+        <v>0</v>
+      </c>
+      <c r="K35" s="7">
         <v>800001021</v>
       </c>
-      <c r="M35" s="12">
-        <v>12</v>
-      </c>
-      <c r="N35" s="12">
-        <v>70</v>
-      </c>
-      <c r="O35" s="12">
-        <v>0</v>
-      </c>
-      <c r="P35" s="12">
-        <v>15</v>
-      </c>
-      <c r="Q35" s="12">
-        <v>1</v>
-      </c>
-      <c r="R35" s="12">
-        <v>300</v>
-      </c>
-      <c r="S35" s="12">
+      <c r="L35" s="7">
+        <v>800001021</v>
+      </c>
+      <c r="M35" s="7">
+        <v>1</v>
+      </c>
+      <c r="N35" s="17">
+        <v>700</v>
+      </c>
+      <c r="O35" s="7">
+        <v>2</v>
+      </c>
+      <c r="P35" s="7">
+        <v>8</v>
+      </c>
+      <c r="Q35" s="7">
+        <v>0</v>
+      </c>
+      <c r="R35" s="7">
+        <v>25</v>
+      </c>
+      <c r="S35" s="7">
         <v>-3000</v>
       </c>
-      <c r="T35" s="12">
-        <v>1</v>
-      </c>
-      <c r="U35" s="12">
-        <v>250</v>
-      </c>
-      <c r="V35" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="W35" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="X35" s="12" t="s">
-        <v>201</v>
-      </c>
-      <c r="Y35" s="13">
+      <c r="T35" s="7">
+        <v>1</v>
+      </c>
+      <c r="U35" s="7">
+        <v>0</v>
+      </c>
+      <c r="V35" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="W35" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="X35" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="Y35" s="14">
         <v>20010001</v>
       </c>
-      <c r="Z35" s="13">
-        <v>0</v>
-      </c>
-      <c r="AA35" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB35" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="AC35" s="12">
-        <v>10000</v>
-      </c>
-      <c r="AD35" s="12">
-        <v>10000</v>
-      </c>
-      <c r="AE35" s="12">
-        <v>25010001</v>
+      <c r="Z35" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB35" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC35" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AD35" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AE35" s="7">
+        <v>0</v>
       </c>
       <c r="AF35" s="4">
         <v>40</v>
@@ -4733,58 +4743,58 @@
     </row>
     <row r="36" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A36" s="7">
-        <v>121104</v>
+        <v>110303</v>
       </c>
       <c r="B36" s="7">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>68</v>
+        <v>101</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="F36" s="7">
-        <v>1000010</v>
-      </c>
-      <c r="G36" s="7">
-        <v>12</v>
-      </c>
-      <c r="H36" s="7">
-        <v>1</v>
-      </c>
-      <c r="I36" s="7" t="s">
+      <c r="F36" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G36" s="15">
+        <v>1</v>
+      </c>
+      <c r="H36" s="15">
+        <v>2</v>
+      </c>
+      <c r="I36" s="15" t="s">
         <v>18</v>
       </c>
       <c r="J36" s="7">
         <v>0</v>
       </c>
-      <c r="K36" s="7" t="s">
-        <v>187</v>
+      <c r="K36" s="7">
+        <v>800001021</v>
       </c>
       <c r="L36" s="7">
-        <v>800001041</v>
+        <v>800001021</v>
       </c>
       <c r="M36" s="7">
-        <v>12</v>
-      </c>
-      <c r="N36" s="7">
-        <v>70</v>
+        <v>1</v>
+      </c>
+      <c r="N36" s="17">
+        <v>2150</v>
       </c>
       <c r="O36" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P36" s="7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q36" s="7">
         <v>0</v>
       </c>
       <c r="R36" s="7">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="S36" s="7">
         <v>-3000</v>
@@ -4796,16 +4806,16 @@
         <v>0</v>
       </c>
       <c r="V36" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="W36" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="X36" s="7" t="s">
-        <v>201</v>
+        <v>143</v>
       </c>
       <c r="Y36" s="14">
-        <v>201004011</v>
+        <v>20010001</v>
       </c>
       <c r="Z36" s="14">
         <v>0</v>
@@ -4814,7 +4824,7 @@
         <v>1</v>
       </c>
       <c r="AB36" s="4" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="AC36" s="7">
         <v>10000</v>
@@ -4823,69 +4833,69 @@
         <v>10000</v>
       </c>
       <c r="AE36" s="7">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF36" s="4">
         <v>40</v>
       </c>
       <c r="AG36" s="4">
-        <v>10000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A37" s="7">
-        <v>121105</v>
+        <v>110304</v>
       </c>
       <c r="B37" s="7">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="E37" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="F37" s="7">
-        <v>1000010</v>
-      </c>
-      <c r="G37" s="7">
-        <v>12</v>
-      </c>
-      <c r="H37" s="7">
-        <v>1</v>
-      </c>
-      <c r="I37" s="7" t="s">
+      <c r="F37" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G37" s="15">
+        <v>1</v>
+      </c>
+      <c r="H37" s="15">
+        <v>2</v>
+      </c>
+      <c r="I37" s="15" t="s">
         <v>18</v>
       </c>
       <c r="J37" s="7">
         <v>0</v>
       </c>
-      <c r="K37" s="7" t="s">
-        <v>188</v>
+      <c r="K37" s="7">
+        <v>800001021</v>
       </c>
       <c r="L37" s="7">
-        <v>800014011</v>
+        <v>800001021</v>
       </c>
       <c r="M37" s="7">
-        <v>12</v>
-      </c>
-      <c r="N37" s="7">
-        <v>125</v>
+        <v>1</v>
+      </c>
+      <c r="N37" s="17">
+        <v>6000</v>
       </c>
       <c r="O37" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P37" s="7">
         <v>8</v>
       </c>
       <c r="Q37" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R37" s="7">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="S37" s="7">
         <v>-3000</v>
@@ -4897,16 +4907,16 @@
         <v>0</v>
       </c>
       <c r="V37" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="W37" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="X37" s="7" t="s">
-        <v>201</v>
+        <v>143</v>
       </c>
       <c r="Y37" s="14">
-        <v>214001011</v>
+        <v>20010001</v>
       </c>
       <c r="Z37" s="14">
         <v>0</v>
@@ -4915,7 +4925,7 @@
         <v>1</v>
       </c>
       <c r="AB37" s="4" t="s">
-        <v>198</v>
+        <v>157</v>
       </c>
       <c r="AC37" s="7">
         <v>10000</v>
@@ -4924,108 +4934,108 @@
         <v>10000</v>
       </c>
       <c r="AE37" s="7">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF37" s="4">
         <v>40</v>
       </c>
       <c r="AG37" s="4">
-        <v>10000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A38" s="12">
-        <v>121106</v>
-      </c>
-      <c r="B38" s="12">
-        <v>12</v>
-      </c>
-      <c r="C38" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="D38" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="E38" s="6" t="s">
+      <c r="A38" s="7">
+        <v>110305</v>
+      </c>
+      <c r="B38" s="7">
+        <v>1</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E38" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="F38" s="12">
-        <v>1000010</v>
-      </c>
-      <c r="G38" s="12">
-        <v>12</v>
-      </c>
-      <c r="H38" s="12">
-        <v>1</v>
-      </c>
-      <c r="I38" s="12" t="s">
+      <c r="F38" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G38" s="15">
+        <v>1</v>
+      </c>
+      <c r="H38" s="15">
+        <v>2</v>
+      </c>
+      <c r="I38" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="J38" s="12">
-        <v>0</v>
-      </c>
-      <c r="K38" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="L38" s="12">
-        <v>1000010</v>
-      </c>
-      <c r="M38" s="12">
-        <v>12</v>
-      </c>
-      <c r="N38" s="12">
-        <v>100</v>
-      </c>
-      <c r="O38" s="12">
-        <v>0</v>
-      </c>
-      <c r="P38" s="12">
-        <v>15</v>
-      </c>
-      <c r="Q38" s="12">
-        <v>0</v>
-      </c>
-      <c r="R38" s="12">
-        <v>36</v>
-      </c>
-      <c r="S38" s="12">
+      <c r="J38" s="7">
+        <v>0</v>
+      </c>
+      <c r="K38" s="7">
+        <v>800001021</v>
+      </c>
+      <c r="L38" s="7">
+        <v>800001021</v>
+      </c>
+      <c r="M38" s="7">
+        <v>1</v>
+      </c>
+      <c r="N38" s="17">
+        <v>13200</v>
+      </c>
+      <c r="O38" s="7">
+        <v>2</v>
+      </c>
+      <c r="P38" s="7">
+        <v>8</v>
+      </c>
+      <c r="Q38" s="7">
+        <v>0</v>
+      </c>
+      <c r="R38" s="7">
+        <v>25</v>
+      </c>
+      <c r="S38" s="7">
         <v>-3000</v>
       </c>
-      <c r="T38" s="12">
-        <v>1</v>
-      </c>
-      <c r="U38" s="12">
-        <v>0</v>
-      </c>
-      <c r="V38" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="W38" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="X38" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="Y38" s="13">
-        <v>20040001</v>
-      </c>
-      <c r="Z38" s="13">
-        <v>0</v>
-      </c>
-      <c r="AA38" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB38" s="6" t="s">
+      <c r="T38" s="7">
+        <v>1</v>
+      </c>
+      <c r="U38" s="7">
+        <v>0</v>
+      </c>
+      <c r="V38" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="W38" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="X38" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="Y38" s="14">
+        <v>20010001</v>
+      </c>
+      <c r="Z38" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA38" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB38" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="AC38" s="12">
-        <v>10000</v>
-      </c>
-      <c r="AD38" s="12">
-        <v>10000</v>
-      </c>
-      <c r="AE38" s="12">
-        <v>25010001</v>
+      <c r="AC38" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AD38" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AE38" s="7">
+        <v>0</v>
       </c>
       <c r="AF38" s="4">
         <v>40</v>
@@ -5035,98 +5045,98 @@
       </c>
     </row>
     <row r="39" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A39" s="12">
-        <v>121107</v>
-      </c>
-      <c r="B39" s="12">
-        <v>12</v>
-      </c>
-      <c r="C39" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="D39" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="E39" s="6" t="s">
+      <c r="A39" s="7">
+        <v>110306</v>
+      </c>
+      <c r="B39" s="7">
+        <v>1</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E39" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="F39" s="12">
-        <v>1000006</v>
-      </c>
-      <c r="G39" s="12">
-        <v>12</v>
-      </c>
-      <c r="H39" s="12">
-        <v>1</v>
-      </c>
-      <c r="I39" s="12" t="s">
+      <c r="F39" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G39" s="15">
+        <v>1</v>
+      </c>
+      <c r="H39" s="15">
+        <v>2</v>
+      </c>
+      <c r="I39" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="J39" s="12">
-        <v>0</v>
-      </c>
-      <c r="K39" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="L39" s="12">
-        <v>1000006</v>
-      </c>
-      <c r="M39" s="12">
-        <v>12</v>
-      </c>
-      <c r="N39" s="12">
-        <v>100</v>
-      </c>
-      <c r="O39" s="12">
-        <v>0</v>
-      </c>
-      <c r="P39" s="12">
-        <v>15</v>
-      </c>
-      <c r="Q39" s="12">
-        <v>0</v>
-      </c>
-      <c r="R39" s="12">
-        <v>36</v>
-      </c>
-      <c r="S39" s="12">
+      <c r="J39" s="7">
+        <v>0</v>
+      </c>
+      <c r="K39" s="7">
+        <v>800001021</v>
+      </c>
+      <c r="L39" s="7">
+        <v>800001021</v>
+      </c>
+      <c r="M39" s="7">
+        <v>1</v>
+      </c>
+      <c r="N39" s="17">
+        <v>34700</v>
+      </c>
+      <c r="O39" s="7">
+        <v>2</v>
+      </c>
+      <c r="P39" s="7">
+        <v>8</v>
+      </c>
+      <c r="Q39" s="7">
+        <v>0</v>
+      </c>
+      <c r="R39" s="7">
+        <v>25</v>
+      </c>
+      <c r="S39" s="7">
         <v>-3000</v>
       </c>
-      <c r="T39" s="12">
-        <v>1</v>
-      </c>
-      <c r="U39" s="12">
-        <v>0</v>
-      </c>
-      <c r="V39" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="W39" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="X39" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="Y39" s="13">
-        <v>20030001</v>
-      </c>
-      <c r="Z39" s="13">
-        <v>0</v>
-      </c>
-      <c r="AA39" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB39" s="6" t="s">
+      <c r="T39" s="7">
+        <v>1</v>
+      </c>
+      <c r="U39" s="7">
+        <v>0</v>
+      </c>
+      <c r="V39" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="W39" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="X39" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="Y39" s="14">
+        <v>20010001</v>
+      </c>
+      <c r="Z39" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB39" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="AC39" s="12">
-        <v>10000</v>
-      </c>
-      <c r="AD39" s="12">
-        <v>10000</v>
-      </c>
-      <c r="AE39" s="12">
-        <v>25010001</v>
+      <c r="AC39" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AD39" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AE39" s="7">
+        <v>0</v>
       </c>
       <c r="AF39" s="4">
         <v>40</v>
@@ -5136,98 +5146,98 @@
       </c>
     </row>
     <row r="40" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A40" s="12">
-        <v>121108</v>
-      </c>
-      <c r="B40" s="12">
-        <v>12</v>
-      </c>
-      <c r="C40" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="D40" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="E40" s="6" t="s">
+      <c r="A40" s="7">
+        <v>110307</v>
+      </c>
+      <c r="B40" s="7">
+        <v>1</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E40" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="F40" s="12">
-        <v>1000006</v>
-      </c>
-      <c r="G40" s="12">
-        <v>12</v>
-      </c>
-      <c r="H40" s="12">
-        <v>1</v>
-      </c>
-      <c r="I40" s="12" t="s">
+      <c r="F40" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G40" s="15">
+        <v>1</v>
+      </c>
+      <c r="H40" s="15">
+        <v>2</v>
+      </c>
+      <c r="I40" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="J40" s="12">
-        <v>0</v>
-      </c>
-      <c r="K40" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="L40" s="12">
-        <v>1000006</v>
-      </c>
-      <c r="M40" s="12">
-        <v>12</v>
-      </c>
-      <c r="N40" s="12">
-        <v>100</v>
-      </c>
-      <c r="O40" s="12">
-        <v>0</v>
-      </c>
-      <c r="P40" s="12">
-        <v>15</v>
-      </c>
-      <c r="Q40" s="12">
-        <v>0</v>
-      </c>
-      <c r="R40" s="12">
-        <v>36</v>
-      </c>
-      <c r="S40" s="12">
+      <c r="J40" s="7">
+        <v>0</v>
+      </c>
+      <c r="K40" s="7">
+        <v>800001021</v>
+      </c>
+      <c r="L40" s="7">
+        <v>800001021</v>
+      </c>
+      <c r="M40" s="7">
+        <v>1</v>
+      </c>
+      <c r="N40" s="17">
+        <v>76500</v>
+      </c>
+      <c r="O40" s="7">
+        <v>2</v>
+      </c>
+      <c r="P40" s="7">
+        <v>8</v>
+      </c>
+      <c r="Q40" s="7">
+        <v>0</v>
+      </c>
+      <c r="R40" s="7">
+        <v>25</v>
+      </c>
+      <c r="S40" s="7">
         <v>-3000</v>
       </c>
-      <c r="T40" s="12">
-        <v>1</v>
-      </c>
-      <c r="U40" s="12">
-        <v>0</v>
-      </c>
-      <c r="V40" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="W40" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="X40" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="Y40" s="13">
-        <v>20030001</v>
-      </c>
-      <c r="Z40" s="13">
-        <v>0</v>
-      </c>
-      <c r="AA40" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB40" s="6" t="s">
+      <c r="T40" s="7">
+        <v>1</v>
+      </c>
+      <c r="U40" s="7">
+        <v>0</v>
+      </c>
+      <c r="V40" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="W40" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="X40" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="Y40" s="14">
+        <v>20010001</v>
+      </c>
+      <c r="Z40" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA40" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB40" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="AC40" s="12">
-        <v>10000</v>
-      </c>
-      <c r="AD40" s="12">
-        <v>10000</v>
-      </c>
-      <c r="AE40" s="12">
-        <v>25010001</v>
+      <c r="AC40" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AD40" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AE40" s="7">
+        <v>0</v>
       </c>
       <c r="AF40" s="4">
         <v>40</v>
@@ -5237,98 +5247,98 @@
       </c>
     </row>
     <row r="41" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A41" s="12">
-        <v>121109</v>
-      </c>
-      <c r="B41" s="12">
-        <v>12</v>
-      </c>
-      <c r="C41" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="D41" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E41" s="6" t="s">
+      <c r="A41" s="7">
+        <v>110308</v>
+      </c>
+      <c r="B41" s="7">
+        <v>1</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E41" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="F41" s="12">
-        <v>1000006</v>
-      </c>
-      <c r="G41" s="12">
-        <v>12</v>
-      </c>
-      <c r="H41" s="12">
-        <v>1</v>
-      </c>
-      <c r="I41" s="12" t="s">
+      <c r="F41" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G41" s="15">
+        <v>1</v>
+      </c>
+      <c r="H41" s="15">
+        <v>2</v>
+      </c>
+      <c r="I41" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="J41" s="12">
-        <v>0</v>
-      </c>
-      <c r="K41" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="L41" s="12">
-        <v>1000006</v>
-      </c>
-      <c r="M41" s="12">
-        <v>12</v>
-      </c>
-      <c r="N41" s="12">
-        <v>100</v>
-      </c>
-      <c r="O41" s="12">
-        <v>0</v>
-      </c>
-      <c r="P41" s="12">
-        <v>15</v>
-      </c>
-      <c r="Q41" s="12">
-        <v>0</v>
-      </c>
-      <c r="R41" s="12">
-        <v>36</v>
-      </c>
-      <c r="S41" s="12">
+      <c r="J41" s="7">
+        <v>0</v>
+      </c>
+      <c r="K41" s="7">
+        <v>800001021</v>
+      </c>
+      <c r="L41" s="7">
+        <v>800001021</v>
+      </c>
+      <c r="M41" s="7">
+        <v>1</v>
+      </c>
+      <c r="N41" s="17">
+        <v>172000</v>
+      </c>
+      <c r="O41" s="7">
+        <v>2</v>
+      </c>
+      <c r="P41" s="7">
+        <v>8</v>
+      </c>
+      <c r="Q41" s="7">
+        <v>0</v>
+      </c>
+      <c r="R41" s="7">
+        <v>25</v>
+      </c>
+      <c r="S41" s="7">
         <v>-3000</v>
       </c>
-      <c r="T41" s="12">
-        <v>1</v>
-      </c>
-      <c r="U41" s="12">
-        <v>0</v>
-      </c>
-      <c r="V41" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="W41" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="X41" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="Y41" s="13">
-        <v>20030001</v>
-      </c>
-      <c r="Z41" s="13">
-        <v>0</v>
-      </c>
-      <c r="AA41" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB41" s="6" t="s">
+      <c r="T41" s="7">
+        <v>1</v>
+      </c>
+      <c r="U41" s="7">
+        <v>0</v>
+      </c>
+      <c r="V41" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="W41" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="X41" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="Y41" s="14">
+        <v>20010001</v>
+      </c>
+      <c r="Z41" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB41" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="AC41" s="12">
-        <v>10000</v>
-      </c>
-      <c r="AD41" s="12">
-        <v>10000</v>
-      </c>
-      <c r="AE41" s="12">
-        <v>25010001</v>
+      <c r="AC41" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AD41" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AE41" s="7">
+        <v>0</v>
       </c>
       <c r="AF41" s="4">
         <v>40</v>
@@ -5338,98 +5348,98 @@
       </c>
     </row>
     <row r="42" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A42" s="12">
-        <v>121110</v>
-      </c>
-      <c r="B42" s="12">
-        <v>12</v>
-      </c>
-      <c r="C42" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="D42" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="E42" s="6" t="s">
+      <c r="A42" s="7">
+        <v>110309</v>
+      </c>
+      <c r="B42" s="7">
+        <v>1</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E42" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="F42" s="12">
-        <v>1000103</v>
-      </c>
-      <c r="G42" s="12">
-        <v>12</v>
-      </c>
-      <c r="H42" s="12">
-        <v>1</v>
-      </c>
-      <c r="I42" s="12" t="s">
+      <c r="F42" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G42" s="15">
+        <v>1</v>
+      </c>
+      <c r="H42" s="15">
+        <v>2</v>
+      </c>
+      <c r="I42" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="J42" s="12">
-        <v>0</v>
-      </c>
-      <c r="K42" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="L42" s="12">
-        <v>1000103</v>
-      </c>
-      <c r="M42" s="12">
-        <v>12</v>
-      </c>
-      <c r="N42" s="12">
+      <c r="J42" s="7">
+        <v>0</v>
+      </c>
+      <c r="K42" s="7">
+        <v>800001021</v>
+      </c>
+      <c r="L42" s="7">
+        <v>800001021</v>
+      </c>
+      <c r="M42" s="7">
+        <v>1</v>
+      </c>
+      <c r="N42" s="7">
         <v>100</v>
       </c>
-      <c r="O42" s="12">
-        <v>0</v>
-      </c>
-      <c r="P42" s="12">
-        <v>15</v>
-      </c>
-      <c r="Q42" s="12">
-        <v>0</v>
-      </c>
-      <c r="R42" s="12">
-        <v>36</v>
-      </c>
-      <c r="S42" s="12">
+      <c r="O42" s="7">
+        <v>2</v>
+      </c>
+      <c r="P42" s="7">
+        <v>8</v>
+      </c>
+      <c r="Q42" s="7">
+        <v>0</v>
+      </c>
+      <c r="R42" s="7">
+        <v>25</v>
+      </c>
+      <c r="S42" s="7">
         <v>-3000</v>
       </c>
-      <c r="T42" s="12">
-        <v>1</v>
-      </c>
-      <c r="U42" s="12">
-        <v>0</v>
-      </c>
-      <c r="V42" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="W42" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="X42" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="Y42" s="13">
-        <v>20020001</v>
-      </c>
-      <c r="Z42" s="13">
-        <v>0</v>
-      </c>
-      <c r="AA42" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB42" s="6" t="s">
+      <c r="T42" s="7">
+        <v>1</v>
+      </c>
+      <c r="U42" s="7">
+        <v>0</v>
+      </c>
+      <c r="V42" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="W42" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="X42" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="Y42" s="14">
+        <v>20010001</v>
+      </c>
+      <c r="Z42" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB42" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="AC42" s="12">
-        <v>10000</v>
-      </c>
-      <c r="AD42" s="12">
-        <v>10000</v>
-      </c>
-      <c r="AE42" s="12">
-        <v>25010001</v>
+      <c r="AC42" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AD42" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AE42" s="7">
+        <v>0</v>
       </c>
       <c r="AF42" s="4">
         <v>40</v>
@@ -5439,98 +5449,98 @@
       </c>
     </row>
     <row r="43" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A43" s="12">
-        <v>121111</v>
-      </c>
-      <c r="B43" s="12">
-        <v>12</v>
-      </c>
-      <c r="C43" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="D43" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="E43" s="6" t="s">
+      <c r="A43" s="7">
+        <v>110310</v>
+      </c>
+      <c r="B43" s="7">
+        <v>1</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E43" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="F43" s="12">
-        <v>1000103</v>
-      </c>
-      <c r="G43" s="12">
-        <v>12</v>
-      </c>
-      <c r="H43" s="12">
-        <v>1</v>
-      </c>
-      <c r="I43" s="12" t="s">
+      <c r="F43" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G43" s="15">
+        <v>1</v>
+      </c>
+      <c r="H43" s="15">
+        <v>2</v>
+      </c>
+      <c r="I43" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="J43" s="12">
-        <v>0</v>
-      </c>
-      <c r="K43" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="L43" s="12">
-        <v>1000103</v>
-      </c>
-      <c r="M43" s="12">
-        <v>12</v>
-      </c>
-      <c r="N43" s="12">
+      <c r="J43" s="7">
+        <v>0</v>
+      </c>
+      <c r="K43" s="7">
+        <v>800001021</v>
+      </c>
+      <c r="L43" s="7">
+        <v>800001021</v>
+      </c>
+      <c r="M43" s="7">
+        <v>1</v>
+      </c>
+      <c r="N43" s="7">
         <v>100</v>
       </c>
-      <c r="O43" s="12">
-        <v>0</v>
-      </c>
-      <c r="P43" s="12">
-        <v>15</v>
-      </c>
-      <c r="Q43" s="12">
-        <v>0</v>
-      </c>
-      <c r="R43" s="12">
-        <v>36</v>
-      </c>
-      <c r="S43" s="12">
+      <c r="O43" s="7">
+        <v>2</v>
+      </c>
+      <c r="P43" s="7">
+        <v>8</v>
+      </c>
+      <c r="Q43" s="7">
+        <v>0</v>
+      </c>
+      <c r="R43" s="7">
+        <v>25</v>
+      </c>
+      <c r="S43" s="7">
         <v>-3000</v>
       </c>
-      <c r="T43" s="12">
-        <v>1</v>
-      </c>
-      <c r="U43" s="12">
-        <v>0</v>
-      </c>
-      <c r="V43" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="W43" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="X43" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="Y43" s="13">
-        <v>20020001</v>
-      </c>
-      <c r="Z43" s="13">
-        <v>0</v>
-      </c>
-      <c r="AA43" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB43" s="6" t="s">
+      <c r="T43" s="7">
+        <v>1</v>
+      </c>
+      <c r="U43" s="7">
+        <v>0</v>
+      </c>
+      <c r="V43" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="W43" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="X43" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="Y43" s="14">
+        <v>20010001</v>
+      </c>
+      <c r="Z43" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB43" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="AC43" s="12">
-        <v>10000</v>
-      </c>
-      <c r="AD43" s="12">
-        <v>10000</v>
-      </c>
-      <c r="AE43" s="12">
-        <v>25010001</v>
+      <c r="AC43" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AD43" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AE43" s="7">
+        <v>0</v>
       </c>
       <c r="AF43" s="4">
         <v>40</v>
@@ -5540,98 +5550,98 @@
       </c>
     </row>
     <row r="44" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A44" s="12">
-        <v>121112</v>
-      </c>
-      <c r="B44" s="12">
-        <v>12</v>
-      </c>
-      <c r="C44" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="D44" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="E44" s="6" t="s">
+      <c r="A44" s="7">
+        <v>110401</v>
+      </c>
+      <c r="B44" s="7">
+        <v>1</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E44" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="F44" s="12">
-        <v>1000103</v>
-      </c>
-      <c r="G44" s="12">
-        <v>12</v>
-      </c>
-      <c r="H44" s="12">
-        <v>1</v>
-      </c>
-      <c r="I44" s="12" t="s">
+      <c r="F44" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G44" s="15">
+        <v>1</v>
+      </c>
+      <c r="H44" s="15">
+        <v>2</v>
+      </c>
+      <c r="I44" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="J44" s="12">
-        <v>0</v>
-      </c>
-      <c r="K44" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="L44" s="12">
-        <v>1000103</v>
-      </c>
-      <c r="M44" s="12">
-        <v>12</v>
-      </c>
-      <c r="N44" s="12">
+      <c r="J44" s="7">
+        <v>0</v>
+      </c>
+      <c r="K44" s="7">
+        <v>800001021</v>
+      </c>
+      <c r="L44" s="7">
+        <v>800001021</v>
+      </c>
+      <c r="M44" s="7">
+        <v>1</v>
+      </c>
+      <c r="N44" s="7">
         <v>100</v>
       </c>
-      <c r="O44" s="12">
-        <v>0</v>
-      </c>
-      <c r="P44" s="12">
-        <v>15</v>
-      </c>
-      <c r="Q44" s="12">
-        <v>0</v>
-      </c>
-      <c r="R44" s="12">
-        <v>36</v>
-      </c>
-      <c r="S44" s="12">
+      <c r="O44" s="7">
+        <v>2</v>
+      </c>
+      <c r="P44" s="7">
+        <v>8</v>
+      </c>
+      <c r="Q44" s="7">
+        <v>0</v>
+      </c>
+      <c r="R44" s="7">
+        <v>25</v>
+      </c>
+      <c r="S44" s="7">
         <v>-3000</v>
       </c>
-      <c r="T44" s="12">
-        <v>1</v>
-      </c>
-      <c r="U44" s="12">
-        <v>0</v>
-      </c>
-      <c r="V44" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="W44" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="X44" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="Y44" s="13">
-        <v>20020001</v>
-      </c>
-      <c r="Z44" s="13">
-        <v>0</v>
-      </c>
-      <c r="AA44" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB44" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="AC44" s="12">
-        <v>10000</v>
-      </c>
-      <c r="AD44" s="12">
-        <v>10000</v>
-      </c>
-      <c r="AE44" s="12">
-        <v>25010001</v>
+      <c r="T44" s="7">
+        <v>1</v>
+      </c>
+      <c r="U44" s="7">
+        <v>0</v>
+      </c>
+      <c r="V44" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="W44" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="X44" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="Y44" s="14">
+        <v>20010001</v>
+      </c>
+      <c r="Z44" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB44" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="AC44" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AD44" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AE44" s="7">
+        <v>0</v>
       </c>
       <c r="AF44" s="4">
         <v>40</v>
@@ -5640,60 +5650,60 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:33" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A45" s="7">
-        <v>121113</v>
+        <v>110402</v>
       </c>
       <c r="B45" s="7">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="F45" s="7">
-        <v>1000011</v>
-      </c>
-      <c r="G45" s="7">
-        <v>12</v>
-      </c>
-      <c r="H45" s="7">
-        <v>1</v>
-      </c>
-      <c r="I45" s="7" t="s">
+      <c r="F45" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G45" s="15">
+        <v>1</v>
+      </c>
+      <c r="H45" s="15">
+        <v>2</v>
+      </c>
+      <c r="I45" s="15" t="s">
         <v>18</v>
       </c>
       <c r="J45" s="7">
         <v>0</v>
       </c>
-      <c r="K45" s="7" t="s">
-        <v>191</v>
+      <c r="K45" s="7">
+        <v>800001021</v>
       </c>
       <c r="L45" s="7">
-        <v>800003021</v>
+        <v>800001021</v>
       </c>
       <c r="M45" s="7">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N45" s="7">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="O45" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P45" s="7">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="Q45" s="7">
-        <v>4</v>
-      </c>
-      <c r="R45" s="16">
-        <v>1760</v>
+        <v>0</v>
+      </c>
+      <c r="R45" s="7">
+        <v>25</v>
       </c>
       <c r="S45" s="7">
         <v>-3000</v>
@@ -5702,19 +5712,19 @@
         <v>1</v>
       </c>
       <c r="U45" s="7">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="V45" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="W45" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="X45" s="7" t="s">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="Y45" s="14">
-        <v>203002011</v>
+        <v>20010001</v>
       </c>
       <c r="Z45" s="14">
         <v>0</v>
@@ -5723,7 +5733,7 @@
         <v>1</v>
       </c>
       <c r="AB45" s="4" t="s">
-        <v>199</v>
+        <v>156</v>
       </c>
       <c r="AC45" s="7">
         <v>10000</v>
@@ -5732,7 +5742,7 @@
         <v>10000</v>
       </c>
       <c r="AE45" s="7">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF45" s="4">
         <v>40</v>
@@ -5742,97 +5752,97 @@
       </c>
     </row>
     <row r="46" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A46" s="12">
-        <v>121114</v>
-      </c>
-      <c r="B46" s="12">
-        <v>12</v>
-      </c>
-      <c r="C46" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D46" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="E46" s="6" t="s">
+      <c r="A46" s="7">
+        <v>110403</v>
+      </c>
+      <c r="B46" s="7">
+        <v>1</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E46" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="F46" s="12">
-        <v>1000011</v>
-      </c>
-      <c r="G46" s="12">
-        <v>12</v>
-      </c>
-      <c r="H46" s="12">
-        <v>1</v>
-      </c>
-      <c r="I46" s="12" t="s">
+      <c r="F46" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G46" s="15">
+        <v>1</v>
+      </c>
+      <c r="H46" s="15">
+        <v>2</v>
+      </c>
+      <c r="I46" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="J46" s="12">
-        <v>0</v>
-      </c>
-      <c r="K46" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="L46" s="12">
-        <v>1000011</v>
-      </c>
-      <c r="M46" s="12">
-        <v>12</v>
-      </c>
-      <c r="N46" s="12">
+      <c r="J46" s="7">
+        <v>0</v>
+      </c>
+      <c r="K46" s="7">
+        <v>800001021</v>
+      </c>
+      <c r="L46" s="7">
+        <v>800001021</v>
+      </c>
+      <c r="M46" s="7">
+        <v>1</v>
+      </c>
+      <c r="N46" s="7">
         <v>100</v>
       </c>
-      <c r="O46" s="12">
-        <v>0</v>
-      </c>
-      <c r="P46" s="12">
-        <v>15</v>
-      </c>
-      <c r="Q46" s="12">
-        <v>0</v>
-      </c>
-      <c r="R46" s="12">
-        <v>36</v>
-      </c>
-      <c r="S46" s="12">
+      <c r="O46" s="7">
+        <v>2</v>
+      </c>
+      <c r="P46" s="7">
+        <v>8</v>
+      </c>
+      <c r="Q46" s="7">
+        <v>0</v>
+      </c>
+      <c r="R46" s="7">
+        <v>25</v>
+      </c>
+      <c r="S46" s="7">
         <v>-3000</v>
       </c>
-      <c r="T46" s="12">
-        <v>1</v>
-      </c>
-      <c r="U46" s="12">
-        <v>0</v>
-      </c>
-      <c r="V46" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="W46" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="X46" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="Y46" s="13">
-        <v>20050001</v>
-      </c>
-      <c r="Z46" s="13">
-        <v>0</v>
-      </c>
-      <c r="AA46" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB46" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="AC46" s="12">
-        <v>10000</v>
-      </c>
-      <c r="AD46" s="12">
-        <v>10000</v>
-      </c>
-      <c r="AE46" s="12">
+      <c r="T46" s="7">
+        <v>1</v>
+      </c>
+      <c r="U46" s="7">
+        <v>0</v>
+      </c>
+      <c r="V46" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="W46" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="X46" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="Y46" s="14">
+        <v>20010001</v>
+      </c>
+      <c r="Z46" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA46" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB46" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="AC46" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AD46" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AE46" s="7">
         <v>0</v>
       </c>
       <c r="AF46" s="4">
@@ -5843,125 +5853,127 @@
       </c>
     </row>
     <row r="47" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A47" s="12">
-        <v>121115</v>
-      </c>
-      <c r="B47" s="12">
+      <c r="A47" s="7">
+        <v>121101</v>
+      </c>
+      <c r="B47" s="7">
         <v>12</v>
       </c>
-      <c r="C47" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="D47" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="E47" s="6" t="s">
+      <c r="C47" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E47" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="F47" s="12">
-        <v>1000011</v>
-      </c>
-      <c r="G47" s="12">
+      <c r="F47" s="7">
+        <v>1000102</v>
+      </c>
+      <c r="G47" s="7">
         <v>12</v>
       </c>
-      <c r="H47" s="12">
-        <v>1</v>
-      </c>
-      <c r="I47" s="12" t="s">
+      <c r="H47" s="7">
+        <v>1</v>
+      </c>
+      <c r="I47" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="J47" s="12">
-        <v>0</v>
-      </c>
-      <c r="K47" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="L47" s="12">
-        <v>1000011</v>
-      </c>
-      <c r="M47" s="12">
+      <c r="J47" s="7">
+        <v>0</v>
+      </c>
+      <c r="K47" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="L47" s="7">
+        <v>800001011</v>
+      </c>
+      <c r="M47" s="7">
         <v>12</v>
       </c>
-      <c r="N47" s="12">
-        <v>100</v>
-      </c>
-      <c r="O47" s="12">
-        <v>0</v>
-      </c>
-      <c r="P47" s="12">
-        <v>15</v>
-      </c>
-      <c r="Q47" s="12">
-        <v>0</v>
-      </c>
-      <c r="R47" s="12">
-        <v>36</v>
-      </c>
-      <c r="S47" s="12">
+      <c r="N47" s="7">
+        <v>70</v>
+      </c>
+      <c r="O47" s="7">
+        <v>0</v>
+      </c>
+      <c r="P47" s="7">
+        <v>7</v>
+      </c>
+      <c r="Q47" s="7">
+        <v>0</v>
+      </c>
+      <c r="R47" s="7">
+        <v>18</v>
+      </c>
+      <c r="S47" s="7">
         <v>-3000</v>
       </c>
-      <c r="T47" s="12">
-        <v>1</v>
-      </c>
-      <c r="U47" s="12">
-        <v>0</v>
-      </c>
-      <c r="V47" s="12" t="s">
+      <c r="T47" s="7">
+        <v>1</v>
+      </c>
+      <c r="U47" s="7">
+        <v>0</v>
+      </c>
+      <c r="V47" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="W47" s="12" t="s">
+      <c r="W47" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="X47" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="Y47" s="13">
-        <v>20050001</v>
-      </c>
-      <c r="Z47" s="13">
-        <v>0</v>
-      </c>
-      <c r="AA47" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB47" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="AC47" s="12">
-        <v>10000</v>
-      </c>
-      <c r="AD47" s="12">
-        <v>10000</v>
-      </c>
-      <c r="AE47" s="12">
-        <v>0</v>
+      <c r="X47" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="Y47" s="14">
+        <v>201001011</v>
+      </c>
+      <c r="Z47" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB47" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="AC47" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AD47" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AE47" s="7">
+        <v>25010001</v>
       </c>
       <c r="AF47" s="4">
         <v>40</v>
       </c>
       <c r="AG47" s="4">
-        <v>0</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="48" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A48" s="7">
-        <v>999001</v>
+        <v>121102</v>
       </c>
       <c r="B48" s="7">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="D48" s="7"/>
+        <v>49</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>67</v>
+      </c>
       <c r="E48" s="4" t="s">
         <v>153</v>
       </c>
       <c r="F48" s="7">
-        <v>1000010</v>
+        <v>1000102</v>
       </c>
       <c r="G48" s="7">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H48" s="7">
         <v>1</v>
@@ -5973,28 +5985,28 @@
         <v>0</v>
       </c>
       <c r="K48" s="7" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="L48" s="7">
-        <v>800001041</v>
+        <v>800001021</v>
       </c>
       <c r="M48" s="7">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="N48" s="7">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O48" s="7">
         <v>0</v>
       </c>
       <c r="P48" s="7">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="Q48" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R48" s="7">
-        <v>10000</v>
+        <v>216</v>
       </c>
       <c r="S48" s="7">
         <v>-3000</v>
@@ -6003,7 +6015,7 @@
         <v>1</v>
       </c>
       <c r="U48" s="7">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="V48" s="7" t="s">
         <v>145</v>
@@ -6012,10 +6024,10 @@
         <v>144</v>
       </c>
       <c r="X48" s="7" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="Y48" s="14">
-        <v>201004011</v>
+        <v>201002011</v>
       </c>
       <c r="Z48" s="14">
         <v>0</v>
@@ -6024,7 +6036,7 @@
         <v>1</v>
       </c>
       <c r="AB48" s="4" t="s">
-        <v>157</v>
+        <v>197</v>
       </c>
       <c r="AC48" s="7">
         <v>10000</v>
@@ -6033,133 +6045,137 @@
         <v>10000</v>
       </c>
       <c r="AE48" s="7">
-        <v>0</v>
+        <v>25010001</v>
       </c>
       <c r="AF48" s="4">
         <v>40</v>
       </c>
       <c r="AG48" s="4">
-        <v>3000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="49" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A49" s="7">
-        <v>999002</v>
-      </c>
-      <c r="B49" s="7">
-        <v>1</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="D49" s="7"/>
-      <c r="E49" s="4" t="s">
+      <c r="A49" s="12">
+        <v>121103</v>
+      </c>
+      <c r="B49" s="12">
+        <v>12</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D49" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E49" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="F49" s="7">
+      <c r="F49" s="12">
         <v>1000102</v>
       </c>
-      <c r="G49" s="7">
-        <v>1</v>
-      </c>
-      <c r="H49" s="7">
-        <v>1</v>
-      </c>
-      <c r="I49" s="7" t="s">
+      <c r="G49" s="12">
+        <v>12</v>
+      </c>
+      <c r="H49" s="12">
+        <v>1</v>
+      </c>
+      <c r="I49" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="J49" s="7">
-        <v>0</v>
-      </c>
-      <c r="K49" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="L49" s="7">
+      <c r="J49" s="12">
+        <v>0</v>
+      </c>
+      <c r="K49" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="L49" s="12">
         <v>800001021</v>
       </c>
-      <c r="M49" s="7">
-        <v>1</v>
-      </c>
-      <c r="N49" s="7">
-        <v>100</v>
-      </c>
-      <c r="O49" s="7">
-        <v>0</v>
-      </c>
-      <c r="P49" s="7">
-        <v>5</v>
-      </c>
-      <c r="Q49" s="7">
-        <v>0</v>
-      </c>
-      <c r="R49" s="7">
-        <v>10000</v>
-      </c>
-      <c r="S49" s="7">
+      <c r="M49" s="12">
+        <v>12</v>
+      </c>
+      <c r="N49" s="12">
+        <v>70</v>
+      </c>
+      <c r="O49" s="12">
+        <v>0</v>
+      </c>
+      <c r="P49" s="12">
+        <v>15</v>
+      </c>
+      <c r="Q49" s="12">
+        <v>1</v>
+      </c>
+      <c r="R49" s="12">
+        <v>300</v>
+      </c>
+      <c r="S49" s="12">
         <v>-3000</v>
       </c>
-      <c r="T49" s="7">
-        <v>1</v>
-      </c>
-      <c r="U49" s="7">
-        <v>100</v>
-      </c>
-      <c r="V49" s="7" t="s">
+      <c r="T49" s="12">
+        <v>1</v>
+      </c>
+      <c r="U49" s="12">
+        <v>250</v>
+      </c>
+      <c r="V49" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="W49" s="7" t="s">
+      <c r="W49" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="X49" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="Y49" s="14">
-        <v>201002011</v>
-      </c>
-      <c r="Z49" s="14">
-        <v>0</v>
-      </c>
-      <c r="AA49" s="7">
-        <v>1</v>
-      </c>
-      <c r="AB49" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="AC49" s="7">
-        <v>10000</v>
-      </c>
-      <c r="AD49" s="7">
-        <v>10000</v>
-      </c>
-      <c r="AE49" s="7">
-        <v>0</v>
+      <c r="X49" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="Y49" s="13">
+        <v>20010001</v>
+      </c>
+      <c r="Z49" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA49" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB49" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="AC49" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AD49" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AE49" s="12">
+        <v>25010001</v>
       </c>
       <c r="AF49" s="4">
         <v>40</v>
       </c>
       <c r="AG49" s="4">
-        <v>3000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A50" s="7">
-        <v>999003</v>
+        <v>121104</v>
       </c>
       <c r="B50" s="7">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="D50" s="7"/>
+        <v>51</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>68</v>
+      </c>
       <c r="E50" s="4" t="s">
         <v>153</v>
       </c>
       <c r="F50" s="7">
-        <v>1000102</v>
+        <v>1000010</v>
       </c>
       <c r="G50" s="7">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H50" s="7">
         <v>1</v>
@@ -6177,22 +6193,22 @@
         <v>800001041</v>
       </c>
       <c r="M50" s="7">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="N50" s="7">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="O50" s="7">
         <v>0</v>
       </c>
       <c r="P50" s="7">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Q50" s="7">
         <v>0</v>
       </c>
       <c r="R50" s="7">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="S50" s="7">
         <v>-3000</v>
@@ -6201,7 +6217,7 @@
         <v>1</v>
       </c>
       <c r="U50" s="7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V50" s="7" t="s">
         <v>145</v>
@@ -6210,10 +6226,10 @@
         <v>144</v>
       </c>
       <c r="X50" s="7" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="Y50" s="14">
-        <v>201002011</v>
+        <v>201004011</v>
       </c>
       <c r="Z50" s="14">
         <v>0</v>
@@ -6222,7 +6238,7 @@
         <v>1</v>
       </c>
       <c r="AB50" s="4" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="AC50" s="7">
         <v>10000</v>
@@ -6231,34 +6247,36 @@
         <v>10000</v>
       </c>
       <c r="AE50" s="7">
-        <v>0</v>
+        <v>25010001</v>
       </c>
       <c r="AF50" s="4">
         <v>40</v>
       </c>
       <c r="AG50" s="4">
-        <v>3000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="51" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A51" s="7">
-        <v>999004</v>
+        <v>121105</v>
       </c>
       <c r="B51" s="7">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="D51" s="7"/>
+        <v>52</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>69</v>
+      </c>
       <c r="E51" s="4" t="s">
         <v>153</v>
       </c>
       <c r="F51" s="7">
-        <v>1000102</v>
+        <v>1000010</v>
       </c>
       <c r="G51" s="7">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H51" s="7">
         <v>1</v>
@@ -6270,28 +6288,28 @@
         <v>0</v>
       </c>
       <c r="K51" s="7" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="L51" s="7">
-        <v>800001021</v>
+        <v>800014011</v>
       </c>
       <c r="M51" s="7">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="N51" s="7">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="O51" s="7">
         <v>0</v>
       </c>
       <c r="P51" s="7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q51" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R51" s="7">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="S51" s="7">
         <v>-3000</v>
@@ -6300,7 +6318,7 @@
         <v>1</v>
       </c>
       <c r="U51" s="7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V51" s="7" t="s">
         <v>145</v>
@@ -6309,10 +6327,10 @@
         <v>144</v>
       </c>
       <c r="X51" s="7" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="Y51" s="14">
-        <v>201002011</v>
+        <v>214001011</v>
       </c>
       <c r="Z51" s="14">
         <v>0</v>
@@ -6321,7 +6339,7 @@
         <v>1</v>
       </c>
       <c r="AB51" s="4" t="s">
-        <v>157</v>
+        <v>198</v>
       </c>
       <c r="AC51" s="7">
         <v>10000</v>
@@ -6330,18 +6348,1424 @@
         <v>10000</v>
       </c>
       <c r="AE51" s="7">
-        <v>0</v>
+        <v>25010001</v>
       </c>
       <c r="AF51" s="4">
         <v>40</v>
       </c>
       <c r="AG51" s="4">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A52" s="12">
+        <v>121106</v>
+      </c>
+      <c r="B52" s="12">
+        <v>12</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="D52" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F52" s="12">
+        <v>1000010</v>
+      </c>
+      <c r="G52" s="12">
+        <v>12</v>
+      </c>
+      <c r="H52" s="12">
+        <v>1</v>
+      </c>
+      <c r="I52" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J52" s="12">
+        <v>0</v>
+      </c>
+      <c r="K52" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="L52" s="12">
+        <v>1000010</v>
+      </c>
+      <c r="M52" s="12">
+        <v>12</v>
+      </c>
+      <c r="N52" s="12">
+        <v>100</v>
+      </c>
+      <c r="O52" s="12">
+        <v>0</v>
+      </c>
+      <c r="P52" s="12">
+        <v>15</v>
+      </c>
+      <c r="Q52" s="12">
+        <v>0</v>
+      </c>
+      <c r="R52" s="12">
+        <v>36</v>
+      </c>
+      <c r="S52" s="12">
+        <v>-3000</v>
+      </c>
+      <c r="T52" s="12">
+        <v>1</v>
+      </c>
+      <c r="U52" s="12">
+        <v>0</v>
+      </c>
+      <c r="V52" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="W52" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="X52" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y52" s="13">
+        <v>20040001</v>
+      </c>
+      <c r="Z52" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB52" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC52" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AD52" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AE52" s="12">
+        <v>25010001</v>
+      </c>
+      <c r="AF52" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG52" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A53" s="12">
+        <v>121107</v>
+      </c>
+      <c r="B53" s="12">
+        <v>12</v>
+      </c>
+      <c r="C53" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="D53" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F53" s="12">
+        <v>1000006</v>
+      </c>
+      <c r="G53" s="12">
+        <v>12</v>
+      </c>
+      <c r="H53" s="12">
+        <v>1</v>
+      </c>
+      <c r="I53" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J53" s="12">
+        <v>0</v>
+      </c>
+      <c r="K53" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="L53" s="12">
+        <v>1000006</v>
+      </c>
+      <c r="M53" s="12">
+        <v>12</v>
+      </c>
+      <c r="N53" s="12">
+        <v>100</v>
+      </c>
+      <c r="O53" s="12">
+        <v>0</v>
+      </c>
+      <c r="P53" s="12">
+        <v>15</v>
+      </c>
+      <c r="Q53" s="12">
+        <v>0</v>
+      </c>
+      <c r="R53" s="12">
+        <v>36</v>
+      </c>
+      <c r="S53" s="12">
+        <v>-3000</v>
+      </c>
+      <c r="T53" s="12">
+        <v>1</v>
+      </c>
+      <c r="U53" s="12">
+        <v>0</v>
+      </c>
+      <c r="V53" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="W53" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="X53" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y53" s="13">
+        <v>20030001</v>
+      </c>
+      <c r="Z53" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB53" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC53" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AD53" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AE53" s="12">
+        <v>25010001</v>
+      </c>
+      <c r="AF53" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG53" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A54" s="12">
+        <v>121108</v>
+      </c>
+      <c r="B54" s="12">
+        <v>12</v>
+      </c>
+      <c r="C54" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="D54" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F54" s="12">
+        <v>1000006</v>
+      </c>
+      <c r="G54" s="12">
+        <v>12</v>
+      </c>
+      <c r="H54" s="12">
+        <v>1</v>
+      </c>
+      <c r="I54" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J54" s="12">
+        <v>0</v>
+      </c>
+      <c r="K54" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="L54" s="12">
+        <v>1000006</v>
+      </c>
+      <c r="M54" s="12">
+        <v>12</v>
+      </c>
+      <c r="N54" s="12">
+        <v>100</v>
+      </c>
+      <c r="O54" s="12">
+        <v>0</v>
+      </c>
+      <c r="P54" s="12">
+        <v>15</v>
+      </c>
+      <c r="Q54" s="12">
+        <v>0</v>
+      </c>
+      <c r="R54" s="12">
+        <v>36</v>
+      </c>
+      <c r="S54" s="12">
+        <v>-3000</v>
+      </c>
+      <c r="T54" s="12">
+        <v>1</v>
+      </c>
+      <c r="U54" s="12">
+        <v>0</v>
+      </c>
+      <c r="V54" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="W54" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="X54" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y54" s="13">
+        <v>20030001</v>
+      </c>
+      <c r="Z54" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA54" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB54" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC54" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AD54" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AE54" s="12">
+        <v>25010001</v>
+      </c>
+      <c r="AF54" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG54" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A55" s="12">
+        <v>121109</v>
+      </c>
+      <c r="B55" s="12">
+        <v>12</v>
+      </c>
+      <c r="C55" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D55" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F55" s="12">
+        <v>1000006</v>
+      </c>
+      <c r="G55" s="12">
+        <v>12</v>
+      </c>
+      <c r="H55" s="12">
+        <v>1</v>
+      </c>
+      <c r="I55" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J55" s="12">
+        <v>0</v>
+      </c>
+      <c r="K55" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="L55" s="12">
+        <v>1000006</v>
+      </c>
+      <c r="M55" s="12">
+        <v>12</v>
+      </c>
+      <c r="N55" s="12">
+        <v>100</v>
+      </c>
+      <c r="O55" s="12">
+        <v>0</v>
+      </c>
+      <c r="P55" s="12">
+        <v>15</v>
+      </c>
+      <c r="Q55" s="12">
+        <v>0</v>
+      </c>
+      <c r="R55" s="12">
+        <v>36</v>
+      </c>
+      <c r="S55" s="12">
+        <v>-3000</v>
+      </c>
+      <c r="T55" s="12">
+        <v>1</v>
+      </c>
+      <c r="U55" s="12">
+        <v>0</v>
+      </c>
+      <c r="V55" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="W55" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="X55" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y55" s="13">
+        <v>20030001</v>
+      </c>
+      <c r="Z55" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA55" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB55" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC55" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AD55" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AE55" s="12">
+        <v>25010001</v>
+      </c>
+      <c r="AF55" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG55" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A56" s="12">
+        <v>121110</v>
+      </c>
+      <c r="B56" s="12">
+        <v>12</v>
+      </c>
+      <c r="C56" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="D56" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F56" s="12">
+        <v>1000103</v>
+      </c>
+      <c r="G56" s="12">
+        <v>12</v>
+      </c>
+      <c r="H56" s="12">
+        <v>1</v>
+      </c>
+      <c r="I56" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J56" s="12">
+        <v>0</v>
+      </c>
+      <c r="K56" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="L56" s="12">
+        <v>1000103</v>
+      </c>
+      <c r="M56" s="12">
+        <v>12</v>
+      </c>
+      <c r="N56" s="12">
+        <v>100</v>
+      </c>
+      <c r="O56" s="12">
+        <v>0</v>
+      </c>
+      <c r="P56" s="12">
+        <v>15</v>
+      </c>
+      <c r="Q56" s="12">
+        <v>0</v>
+      </c>
+      <c r="R56" s="12">
+        <v>36</v>
+      </c>
+      <c r="S56" s="12">
+        <v>-3000</v>
+      </c>
+      <c r="T56" s="12">
+        <v>1</v>
+      </c>
+      <c r="U56" s="12">
+        <v>0</v>
+      </c>
+      <c r="V56" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="W56" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="X56" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y56" s="13">
+        <v>20020001</v>
+      </c>
+      <c r="Z56" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA56" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB56" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC56" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AD56" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AE56" s="12">
+        <v>25010001</v>
+      </c>
+      <c r="AF56" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG56" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A57" s="12">
+        <v>121111</v>
+      </c>
+      <c r="B57" s="12">
+        <v>12</v>
+      </c>
+      <c r="C57" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="D57" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F57" s="12">
+        <v>1000103</v>
+      </c>
+      <c r="G57" s="12">
+        <v>12</v>
+      </c>
+      <c r="H57" s="12">
+        <v>1</v>
+      </c>
+      <c r="I57" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J57" s="12">
+        <v>0</v>
+      </c>
+      <c r="K57" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="L57" s="12">
+        <v>1000103</v>
+      </c>
+      <c r="M57" s="12">
+        <v>12</v>
+      </c>
+      <c r="N57" s="12">
+        <v>100</v>
+      </c>
+      <c r="O57" s="12">
+        <v>0</v>
+      </c>
+      <c r="P57" s="12">
+        <v>15</v>
+      </c>
+      <c r="Q57" s="12">
+        <v>0</v>
+      </c>
+      <c r="R57" s="12">
+        <v>36</v>
+      </c>
+      <c r="S57" s="12">
+        <v>-3000</v>
+      </c>
+      <c r="T57" s="12">
+        <v>1</v>
+      </c>
+      <c r="U57" s="12">
+        <v>0</v>
+      </c>
+      <c r="V57" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="W57" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="X57" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y57" s="13">
+        <v>20020001</v>
+      </c>
+      <c r="Z57" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA57" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB57" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC57" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AD57" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AE57" s="12">
+        <v>25010001</v>
+      </c>
+      <c r="AF57" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG57" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A58" s="12">
+        <v>121112</v>
+      </c>
+      <c r="B58" s="12">
+        <v>12</v>
+      </c>
+      <c r="C58" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F58" s="12">
+        <v>1000103</v>
+      </c>
+      <c r="G58" s="12">
+        <v>12</v>
+      </c>
+      <c r="H58" s="12">
+        <v>1</v>
+      </c>
+      <c r="I58" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J58" s="12">
+        <v>0</v>
+      </c>
+      <c r="K58" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="L58" s="12">
+        <v>1000103</v>
+      </c>
+      <c r="M58" s="12">
+        <v>12</v>
+      </c>
+      <c r="N58" s="12">
+        <v>100</v>
+      </c>
+      <c r="O58" s="12">
+        <v>0</v>
+      </c>
+      <c r="P58" s="12">
+        <v>15</v>
+      </c>
+      <c r="Q58" s="12">
+        <v>0</v>
+      </c>
+      <c r="R58" s="12">
+        <v>36</v>
+      </c>
+      <c r="S58" s="12">
+        <v>-3000</v>
+      </c>
+      <c r="T58" s="12">
+        <v>1</v>
+      </c>
+      <c r="U58" s="12">
+        <v>0</v>
+      </c>
+      <c r="V58" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="W58" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="X58" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y58" s="13">
+        <v>20020001</v>
+      </c>
+      <c r="Z58" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB58" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC58" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AD58" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AE58" s="12">
+        <v>25010001</v>
+      </c>
+      <c r="AF58" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG58" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:33" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A59" s="7">
+        <v>121113</v>
+      </c>
+      <c r="B59" s="7">
+        <v>12</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F59" s="7">
+        <v>1000011</v>
+      </c>
+      <c r="G59" s="7">
+        <v>12</v>
+      </c>
+      <c r="H59" s="7">
+        <v>1</v>
+      </c>
+      <c r="I59" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J59" s="7">
+        <v>0</v>
+      </c>
+      <c r="K59" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="L59" s="7">
+        <v>800003021</v>
+      </c>
+      <c r="M59" s="7">
+        <v>12</v>
+      </c>
+      <c r="N59" s="7">
+        <v>500</v>
+      </c>
+      <c r="O59" s="7">
+        <v>0</v>
+      </c>
+      <c r="P59" s="7">
+        <v>30</v>
+      </c>
+      <c r="Q59" s="7">
+        <v>4</v>
+      </c>
+      <c r="R59" s="16">
+        <v>1760</v>
+      </c>
+      <c r="S59" s="7">
+        <v>-3000</v>
+      </c>
+      <c r="T59" s="7">
+        <v>1</v>
+      </c>
+      <c r="U59" s="7">
+        <v>30000</v>
+      </c>
+      <c r="V59" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="W59" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="X59" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="Y59" s="14">
+        <v>203002011</v>
+      </c>
+      <c r="Z59" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA59" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB59" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="AC59" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AD59" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AE59" s="7">
+        <v>25010001</v>
+      </c>
+      <c r="AF59" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG59" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A60" s="12">
+        <v>121114</v>
+      </c>
+      <c r="B60" s="12">
+        <v>12</v>
+      </c>
+      <c r="C60" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D60" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F60" s="12">
+        <v>1000011</v>
+      </c>
+      <c r="G60" s="12">
+        <v>12</v>
+      </c>
+      <c r="H60" s="12">
+        <v>1</v>
+      </c>
+      <c r="I60" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J60" s="12">
+        <v>0</v>
+      </c>
+      <c r="K60" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="L60" s="12">
+        <v>1000011</v>
+      </c>
+      <c r="M60" s="12">
+        <v>12</v>
+      </c>
+      <c r="N60" s="12">
+        <v>100</v>
+      </c>
+      <c r="O60" s="12">
+        <v>0</v>
+      </c>
+      <c r="P60" s="12">
+        <v>15</v>
+      </c>
+      <c r="Q60" s="12">
+        <v>0</v>
+      </c>
+      <c r="R60" s="12">
+        <v>36</v>
+      </c>
+      <c r="S60" s="12">
+        <v>-3000</v>
+      </c>
+      <c r="T60" s="12">
+        <v>1</v>
+      </c>
+      <c r="U60" s="12">
+        <v>0</v>
+      </c>
+      <c r="V60" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="W60" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="X60" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y60" s="13">
+        <v>20050001</v>
+      </c>
+      <c r="Z60" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA60" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB60" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC60" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AD60" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AE60" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF60" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG60" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A61" s="12">
+        <v>121115</v>
+      </c>
+      <c r="B61" s="12">
+        <v>12</v>
+      </c>
+      <c r="C61" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="D61" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F61" s="12">
+        <v>1000011</v>
+      </c>
+      <c r="G61" s="12">
+        <v>12</v>
+      </c>
+      <c r="H61" s="12">
+        <v>1</v>
+      </c>
+      <c r="I61" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J61" s="12">
+        <v>0</v>
+      </c>
+      <c r="K61" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="L61" s="12">
+        <v>1000011</v>
+      </c>
+      <c r="M61" s="12">
+        <v>12</v>
+      </c>
+      <c r="N61" s="12">
+        <v>100</v>
+      </c>
+      <c r="O61" s="12">
+        <v>0</v>
+      </c>
+      <c r="P61" s="12">
+        <v>15</v>
+      </c>
+      <c r="Q61" s="12">
+        <v>0</v>
+      </c>
+      <c r="R61" s="12">
+        <v>36</v>
+      </c>
+      <c r="S61" s="12">
+        <v>-3000</v>
+      </c>
+      <c r="T61" s="12">
+        <v>1</v>
+      </c>
+      <c r="U61" s="12">
+        <v>0</v>
+      </c>
+      <c r="V61" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="W61" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="X61" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y61" s="13">
+        <v>20050001</v>
+      </c>
+      <c r="Z61" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB61" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC61" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AD61" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AE61" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG61" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A62" s="7">
+        <v>999001</v>
+      </c>
+      <c r="B62" s="7">
+        <v>1</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="D62" s="7"/>
+      <c r="E62" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F62" s="7">
+        <v>1000010</v>
+      </c>
+      <c r="G62" s="7">
+        <v>1</v>
+      </c>
+      <c r="H62" s="7">
+        <v>1</v>
+      </c>
+      <c r="I62" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J62" s="7">
+        <v>0</v>
+      </c>
+      <c r="K62" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="L62" s="7">
+        <v>800001041</v>
+      </c>
+      <c r="M62" s="7">
+        <v>1</v>
+      </c>
+      <c r="N62" s="7">
+        <v>100</v>
+      </c>
+      <c r="O62" s="7">
+        <v>0</v>
+      </c>
+      <c r="P62" s="7">
+        <v>5</v>
+      </c>
+      <c r="Q62" s="7">
+        <v>0</v>
+      </c>
+      <c r="R62" s="7">
+        <v>10000</v>
+      </c>
+      <c r="S62" s="7">
+        <v>-3000</v>
+      </c>
+      <c r="T62" s="7">
+        <v>1</v>
+      </c>
+      <c r="U62" s="7">
+        <v>100</v>
+      </c>
+      <c r="V62" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="W62" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="X62" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="Y62" s="14">
+        <v>201004011</v>
+      </c>
+      <c r="Z62" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB62" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC62" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AD62" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AE62" s="7">
+        <v>0</v>
+      </c>
+      <c r="AF62" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG62" s="4">
         <v>3000</v>
       </c>
     </row>
+    <row r="63" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A63" s="7">
+        <v>999002</v>
+      </c>
+      <c r="B63" s="7">
+        <v>1</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="D63" s="7"/>
+      <c r="E63" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F63" s="7">
+        <v>1000102</v>
+      </c>
+      <c r="G63" s="7">
+        <v>1</v>
+      </c>
+      <c r="H63" s="7">
+        <v>1</v>
+      </c>
+      <c r="I63" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J63" s="7">
+        <v>0</v>
+      </c>
+      <c r="K63" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="L63" s="7">
+        <v>800001021</v>
+      </c>
+      <c r="M63" s="7">
+        <v>1</v>
+      </c>
+      <c r="N63" s="7">
+        <v>100</v>
+      </c>
+      <c r="O63" s="7">
+        <v>0</v>
+      </c>
+      <c r="P63" s="7">
+        <v>5</v>
+      </c>
+      <c r="Q63" s="7">
+        <v>0</v>
+      </c>
+      <c r="R63" s="7">
+        <v>10000</v>
+      </c>
+      <c r="S63" s="7">
+        <v>-3000</v>
+      </c>
+      <c r="T63" s="7">
+        <v>1</v>
+      </c>
+      <c r="U63" s="7">
+        <v>100</v>
+      </c>
+      <c r="V63" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="W63" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="X63" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="Y63" s="14">
+        <v>201002011</v>
+      </c>
+      <c r="Z63" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA63" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB63" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC63" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AD63" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AE63" s="7">
+        <v>0</v>
+      </c>
+      <c r="AF63" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG63" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="64" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A64" s="7">
+        <v>999003</v>
+      </c>
+      <c r="B64" s="7">
+        <v>1</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="D64" s="7"/>
+      <c r="E64" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F64" s="7">
+        <v>1000102</v>
+      </c>
+      <c r="G64" s="7">
+        <v>1</v>
+      </c>
+      <c r="H64" s="7">
+        <v>1</v>
+      </c>
+      <c r="I64" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J64" s="7">
+        <v>0</v>
+      </c>
+      <c r="K64" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="L64" s="7">
+        <v>800001041</v>
+      </c>
+      <c r="M64" s="7">
+        <v>1</v>
+      </c>
+      <c r="N64" s="7">
+        <v>100</v>
+      </c>
+      <c r="O64" s="7">
+        <v>0</v>
+      </c>
+      <c r="P64" s="7">
+        <v>5</v>
+      </c>
+      <c r="Q64" s="7">
+        <v>0</v>
+      </c>
+      <c r="R64" s="7">
+        <v>10</v>
+      </c>
+      <c r="S64" s="7">
+        <v>-3000</v>
+      </c>
+      <c r="T64" s="7">
+        <v>1</v>
+      </c>
+      <c r="U64" s="7">
+        <v>100</v>
+      </c>
+      <c r="V64" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="W64" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="X64" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="Y64" s="14">
+        <v>201002011</v>
+      </c>
+      <c r="Z64" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA64" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB64" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC64" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AD64" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AE64" s="7">
+        <v>0</v>
+      </c>
+      <c r="AF64" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG64" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="65" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A65" s="7">
+        <v>999004</v>
+      </c>
+      <c r="B65" s="7">
+        <v>1</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="D65" s="7"/>
+      <c r="E65" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F65" s="7">
+        <v>1000102</v>
+      </c>
+      <c r="G65" s="7">
+        <v>1</v>
+      </c>
+      <c r="H65" s="7">
+        <v>1</v>
+      </c>
+      <c r="I65" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J65" s="7">
+        <v>0</v>
+      </c>
+      <c r="K65" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="L65" s="7">
+        <v>800001021</v>
+      </c>
+      <c r="M65" s="7">
+        <v>1</v>
+      </c>
+      <c r="N65" s="7">
+        <v>100</v>
+      </c>
+      <c r="O65" s="7">
+        <v>0</v>
+      </c>
+      <c r="P65" s="7">
+        <v>5</v>
+      </c>
+      <c r="Q65" s="7">
+        <v>0</v>
+      </c>
+      <c r="R65" s="7">
+        <v>10</v>
+      </c>
+      <c r="S65" s="7">
+        <v>-3000</v>
+      </c>
+      <c r="T65" s="7">
+        <v>1</v>
+      </c>
+      <c r="U65" s="7">
+        <v>100</v>
+      </c>
+      <c r="V65" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="W65" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="X65" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="Y65" s="14">
+        <v>201002011</v>
+      </c>
+      <c r="Z65" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA65" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB65" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC65" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AD65" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AE65" s="7">
+        <v>0</v>
+      </c>
+      <c r="AF65" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG65" s="4">
+        <v>3000</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:AD47">
-    <sortCondition ref="A5:A47"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:AD61">
+    <sortCondition ref="A5:A61"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61230B95-132B-463E-9B4E-DDD8FBE3E3B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A78385E2-CB76-4FAC-971A-921DB1DEBD8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="210">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -737,6 +737,30 @@
   </si>
   <si>
     <t>测试怪远程2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>attacked_back_range_after</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>被击退距离系数（破除韧性后）（万分比）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>threat_value</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>arrow_threat_value</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>威胁值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>远程威胁值</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1254,7 +1278,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG65"/>
+  <dimension ref="A1:AJ65"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.125" style="4" bestFit="1" customWidth="1"/>
@@ -1272,10 +1296,13 @@
     <col min="29" max="29" width="44.625" style="4" bestFit="1" customWidth="1"/>
     <col min="30" max="31" width="53" style="4" bestFit="1" customWidth="1"/>
     <col min="32" max="33" width="27.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9" style="4"/>
+    <col min="34" max="34" width="40.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="20.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -1307,7 +1334,7 @@
       <c r="AD1" s="7"/>
       <c r="AE1" s="7"/>
     </row>
-    <row r="2" spans="1:33" ht="14.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:36" ht="14.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
@@ -1407,8 +1434,17 @@
       <c r="AG2" s="10" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="3" spans="1:33" ht="14.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="AH2" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="AI2" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="AJ2" s="10" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="3" spans="1:36" ht="14.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
@@ -1508,8 +1544,17 @@
       <c r="AG3" s="5" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="4" spans="1:33" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="AH3" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="AI3" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="AJ3" s="4" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="4" spans="1:36" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>7</v>
       </c>
@@ -1609,8 +1654,17 @@
       <c r="AG4" s="5" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH4" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="AI4" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="AJ4" s="4" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="7">
         <v>10201</v>
       </c>
@@ -1710,8 +1764,17 @@
       <c r="AG5" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH5" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>10301</v>
       </c>
@@ -1811,8 +1874,17 @@
       <c r="AG6" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A7" s="7">
         <v>10302</v>
       </c>
@@ -1912,8 +1984,17 @@
       <c r="AG7" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
         <v>10303</v>
       </c>
@@ -2013,8 +2094,17 @@
       <c r="AG8" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A9" s="7">
         <v>10304</v>
       </c>
@@ -2114,8 +2204,17 @@
       <c r="AG9" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A10" s="7">
         <v>10305</v>
       </c>
@@ -2215,8 +2314,17 @@
       <c r="AG10" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A11" s="7">
         <v>10306</v>
       </c>
@@ -2316,8 +2424,17 @@
       <c r="AG11" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A12" s="7">
         <v>10307</v>
       </c>
@@ -2417,8 +2534,17 @@
       <c r="AG12" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A13" s="7">
         <v>10308</v>
       </c>
@@ -2518,8 +2644,17 @@
       <c r="AG13" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A14" s="7">
         <v>10309</v>
       </c>
@@ -2619,8 +2754,17 @@
       <c r="AG14" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A15" s="7">
         <v>10310</v>
       </c>
@@ -2720,8 +2864,17 @@
       <c r="AG15" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A16" s="7">
         <v>10401</v>
       </c>
@@ -2821,8 +2974,17 @@
       <c r="AG16" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ16" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A17" s="7">
         <v>10402</v>
       </c>
@@ -2922,8 +3084,17 @@
       <c r="AG17" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH17" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI17" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A18" s="7">
         <v>10403</v>
       </c>
@@ -3023,8 +3194,17 @@
       <c r="AG18" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH18" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI18" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ18" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A19" s="7">
         <v>20201</v>
       </c>
@@ -3124,8 +3304,17 @@
       <c r="AG19" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI19" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ19" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A20" s="7">
         <v>20301</v>
       </c>
@@ -3225,8 +3414,17 @@
       <c r="AG20" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A21" s="7">
         <v>20302</v>
       </c>
@@ -3326,8 +3524,17 @@
       <c r="AG21" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI21" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ21" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A22" s="7">
         <v>20303</v>
       </c>
@@ -3427,8 +3634,17 @@
       <c r="AG22" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A23" s="7">
         <v>20304</v>
       </c>
@@ -3528,8 +3744,17 @@
       <c r="AG23" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH23" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI23" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ23" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A24" s="7">
         <v>20305</v>
       </c>
@@ -3629,8 +3854,17 @@
       <c r="AG24" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ24" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A25" s="7">
         <v>20306</v>
       </c>
@@ -3730,8 +3964,17 @@
       <c r="AG25" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ25" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A26" s="7">
         <v>20307</v>
       </c>
@@ -3831,8 +4074,17 @@
       <c r="AG26" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH26" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI26" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ26" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A27" s="7">
         <v>20308</v>
       </c>
@@ -3932,8 +4184,17 @@
       <c r="AG27" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH27" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI27" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ27" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A28" s="7">
         <v>20309</v>
       </c>
@@ -4033,8 +4294,17 @@
       <c r="AG28" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ28" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A29" s="7">
         <v>20310</v>
       </c>
@@ -4134,8 +4404,17 @@
       <c r="AG29" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A30" s="7">
         <v>20401</v>
       </c>
@@ -4235,8 +4514,17 @@
       <c r="AG30" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ30" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A31" s="7">
         <v>20402</v>
       </c>
@@ -4336,8 +4624,17 @@
       <c r="AG31" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ31" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A32" s="7">
         <v>20403</v>
       </c>
@@ -4437,8 +4734,17 @@
       <c r="AG32" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A33" s="7">
         <v>110201</v>
       </c>
@@ -4538,8 +4844,17 @@
       <c r="AG33" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH33" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI33" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ33" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A34" s="7">
         <v>110301</v>
       </c>
@@ -4639,8 +4954,17 @@
       <c r="AG34" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ34" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A35" s="7">
         <v>110302</v>
       </c>
@@ -4740,8 +5064,17 @@
       <c r="AG35" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH35" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI35" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ35" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A36" s="7">
         <v>110303</v>
       </c>
@@ -4841,8 +5174,17 @@
       <c r="AG36" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH36" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI36" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ36" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A37" s="7">
         <v>110304</v>
       </c>
@@ -4942,8 +5284,17 @@
       <c r="AG37" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH37" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI37" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ37" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A38" s="7">
         <v>110305</v>
       </c>
@@ -5043,8 +5394,17 @@
       <c r="AG38" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH38" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI38" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ38" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A39" s="7">
         <v>110306</v>
       </c>
@@ -5144,8 +5504,17 @@
       <c r="AG39" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI39" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ39" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A40" s="7">
         <v>110307</v>
       </c>
@@ -5245,8 +5614,17 @@
       <c r="AG40" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI40" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ40" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A41" s="7">
         <v>110308</v>
       </c>
@@ -5346,8 +5724,17 @@
       <c r="AG41" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH41" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI41" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ41" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A42" s="7">
         <v>110309</v>
       </c>
@@ -5447,8 +5834,17 @@
       <c r="AG42" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A43" s="7">
         <v>110310</v>
       </c>
@@ -5548,8 +5944,17 @@
       <c r="AG43" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI43" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ43" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A44" s="7">
         <v>110401</v>
       </c>
@@ -5649,8 +6054,17 @@
       <c r="AG44" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI44" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ44" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A45" s="7">
         <v>110402</v>
       </c>
@@ -5750,8 +6164,17 @@
       <c r="AG45" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI45" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ45" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A46" s="7">
         <v>110403</v>
       </c>
@@ -5851,8 +6274,17 @@
       <c r="AG46" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI46" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ46" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A47" s="7">
         <v>121101</v>
       </c>
@@ -5952,8 +6384,17 @@
       <c r="AG47" s="4">
         <v>10000</v>
       </c>
-    </row>
-    <row r="48" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="4">
+        <v>10000</v>
+      </c>
+      <c r="AI47" s="4">
+        <v>50</v>
+      </c>
+      <c r="AJ47" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A48" s="7">
         <v>121102</v>
       </c>
@@ -6051,10 +6492,19 @@
         <v>40</v>
       </c>
       <c r="AG48" s="4">
+        <v>3000</v>
+      </c>
+      <c r="AH48" s="4">
         <v>10000</v>
       </c>
-    </row>
-    <row r="49" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AI48" s="4">
+        <v>10</v>
+      </c>
+      <c r="AJ48" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A49" s="12">
         <v>121103</v>
       </c>
@@ -6154,8 +6604,17 @@
       <c r="AG49" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI49" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ49" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A50" s="7">
         <v>121104</v>
       </c>
@@ -6255,8 +6714,17 @@
       <c r="AG50" s="4">
         <v>10000</v>
       </c>
-    </row>
-    <row r="51" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="4">
+        <v>10000</v>
+      </c>
+      <c r="AI50" s="4">
+        <v>80</v>
+      </c>
+      <c r="AJ50" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A51" s="7">
         <v>121105</v>
       </c>
@@ -6356,8 +6824,17 @@
       <c r="AG51" s="4">
         <v>10000</v>
       </c>
-    </row>
-    <row r="52" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="4">
+        <v>10000</v>
+      </c>
+      <c r="AI51" s="4">
+        <v>40</v>
+      </c>
+      <c r="AJ51" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A52" s="12">
         <v>121106</v>
       </c>
@@ -6457,8 +6934,17 @@
       <c r="AG52" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI52" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ52" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A53" s="12">
         <v>121107</v>
       </c>
@@ -6558,8 +7044,17 @@
       <c r="AG53" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI53" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ53" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A54" s="12">
         <v>121108</v>
       </c>
@@ -6659,8 +7154,17 @@
       <c r="AG54" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH54" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI54" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ54" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A55" s="12">
         <v>121109</v>
       </c>
@@ -6760,8 +7264,17 @@
       <c r="AG55" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI55" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ55" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A56" s="12">
         <v>121110</v>
       </c>
@@ -6861,8 +7374,17 @@
       <c r="AG56" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI56" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ56" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A57" s="12">
         <v>121111</v>
       </c>
@@ -6962,8 +7484,17 @@
       <c r="AG57" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI57" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ57" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A58" s="12">
         <v>121112</v>
       </c>
@@ -7063,8 +7594,17 @@
       <c r="AG58" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:33" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="AH58" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI58" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A59" s="7">
         <v>121113</v>
       </c>
@@ -7162,10 +7702,19 @@
         <v>40</v>
       </c>
       <c r="AG59" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:33" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="AH59" s="4">
+        <v>5000</v>
+      </c>
+      <c r="AI59" s="4">
+        <v>2</v>
+      </c>
+      <c r="AJ59" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A60" s="12">
         <v>121114</v>
       </c>
@@ -7265,8 +7814,17 @@
       <c r="AG60" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI60" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ60" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A61" s="12">
         <v>121115</v>
       </c>
@@ -7366,8 +7924,17 @@
       <c r="AG61" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI61" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ61" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A62" s="7">
         <v>999001</v>
       </c>
@@ -7465,8 +8032,17 @@
       <c r="AG62" s="4">
         <v>3000</v>
       </c>
-    </row>
-    <row r="63" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="4">
+        <v>6000</v>
+      </c>
+      <c r="AI62" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ62" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A63" s="7">
         <v>999002</v>
       </c>
@@ -7564,8 +8140,17 @@
       <c r="AG63" s="4">
         <v>3000</v>
       </c>
-    </row>
-    <row r="64" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="4">
+        <v>6000</v>
+      </c>
+      <c r="AI63" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ63" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A64" s="7">
         <v>999003</v>
       </c>
@@ -7663,8 +8248,17 @@
       <c r="AG64" s="4">
         <v>3000</v>
       </c>
-    </row>
-    <row r="65" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="4">
+        <v>6000</v>
+      </c>
+      <c r="AI64" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ64" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A65" s="7">
         <v>999004</v>
       </c>
@@ -7761,6 +8355,15 @@
       </c>
       <c r="AG65" s="4">
         <v>3000</v>
+      </c>
+      <c r="AH65" s="4">
+        <v>6000</v>
+      </c>
+      <c r="AI65" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ65" s="4">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D546A328-D3D7-49E3-990A-7BEC2B8D3A35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{176C1BAA-DD41-4076-BA23-EBA07AC09006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6420,7 +6420,7 @@
         <v>0</v>
       </c>
       <c r="P47" s="7">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="Q47" s="7">
         <v>0</v>
@@ -6530,13 +6530,13 @@
         <v>0</v>
       </c>
       <c r="P48" s="7">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="Q48" s="7">
         <v>2</v>
       </c>
       <c r="R48" s="7">
-        <v>216</v>
+        <v>292</v>
       </c>
       <c r="S48" s="7">
         <v>-3000</v>
@@ -6750,7 +6750,7 @@
         <v>0</v>
       </c>
       <c r="P50" s="7">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="Q50" s="7">
         <v>0</v>
@@ -6860,7 +6860,7 @@
         <v>0</v>
       </c>
       <c r="P51" s="7">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="Q51" s="7">
         <v>1</v>
@@ -7740,13 +7740,13 @@
         <v>0</v>
       </c>
       <c r="P59" s="7">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="Q59" s="7">
         <v>4</v>
       </c>
       <c r="R59" s="16">
-        <v>1760</v>
+        <v>2200</v>
       </c>
       <c r="S59" s="7">
         <v>-3000</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{176C1BAA-DD41-4076-BA23-EBA07AC09006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7CB6792-9851-4A08-8912-C8402A7F5E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6420,7 +6420,7 @@
         <v>0</v>
       </c>
       <c r="P47" s="7">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q47" s="7">
         <v>0</v>
@@ -6530,13 +6530,13 @@
         <v>0</v>
       </c>
       <c r="P48" s="7">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Q48" s="7">
         <v>2</v>
       </c>
       <c r="R48" s="7">
-        <v>292</v>
+        <v>230</v>
       </c>
       <c r="S48" s="7">
         <v>-3000</v>
@@ -6750,7 +6750,7 @@
         <v>0</v>
       </c>
       <c r="P50" s="7">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q50" s="7">
         <v>0</v>
@@ -6860,7 +6860,7 @@
         <v>0</v>
       </c>
       <c r="P51" s="7">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q51" s="7">
         <v>1</v>
@@ -7740,7 +7740,7 @@
         <v>0</v>
       </c>
       <c r="P59" s="7">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Q59" s="7">
         <v>4</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7CB6792-9851-4A08-8912-C8402A7F5E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7E4F3D4-CA30-4B9F-AC97-FAEC4ADE7325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6420,7 +6420,7 @@
         <v>0</v>
       </c>
       <c r="P47" s="7">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Q47" s="7">
         <v>0</v>
@@ -6530,7 +6530,7 @@
         <v>0</v>
       </c>
       <c r="P48" s="7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q48" s="7">
         <v>2</v>
@@ -6545,7 +6545,7 @@
         <v>1</v>
       </c>
       <c r="U48" s="7">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="V48" s="7" t="s">
         <v>145</v>
@@ -6750,7 +6750,7 @@
         <v>0</v>
       </c>
       <c r="P50" s="7">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Q50" s="7">
         <v>0</v>
@@ -6860,7 +6860,7 @@
         <v>0</v>
       </c>
       <c r="P51" s="7">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q51" s="7">
         <v>1</v>
@@ -7743,10 +7743,10 @@
         <v>38</v>
       </c>
       <c r="Q59" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R59" s="16">
-        <v>2200</v>
+        <v>1964</v>
       </c>
       <c r="S59" s="7">
         <v>-3000</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7E4F3D4-CA30-4B9F-AC97-FAEC4ADE7325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6BFB544-2383-4C70-AA9A-E1A2552070F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6420,7 +6420,7 @@
         <v>0</v>
       </c>
       <c r="P47" s="7">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q47" s="7">
         <v>0</v>
@@ -6530,7 +6530,7 @@
         <v>0</v>
       </c>
       <c r="P48" s="7">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="Q48" s="7">
         <v>2</v>
@@ -6750,7 +6750,7 @@
         <v>0</v>
       </c>
       <c r="P50" s="7">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="Q50" s="7">
         <v>0</v>
@@ -6860,7 +6860,7 @@
         <v>0</v>
       </c>
       <c r="P51" s="7">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Q51" s="7">
         <v>1</v>
@@ -7740,13 +7740,13 @@
         <v>0</v>
       </c>
       <c r="P59" s="7">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="Q59" s="7">
         <v>3</v>
       </c>
       <c r="R59" s="16">
-        <v>1964</v>
+        <v>1683</v>
       </c>
       <c r="S59" s="7">
         <v>-3000</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6BFB544-2383-4C70-AA9A-E1A2552070F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E625C186-7C60-4393-B268-05C65DCA3EA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7746,7 +7746,7 @@
         <v>3</v>
       </c>
       <c r="R59" s="16">
-        <v>1683</v>
+        <v>1496</v>
       </c>
       <c r="S59" s="7">
         <v>-3000</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E625C186-7C60-4393-B268-05C65DCA3EA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{718D7FBB-C4B0-4AE1-A01D-C99C02242017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6420,7 +6420,7 @@
         <v>0</v>
       </c>
       <c r="P47" s="7">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q47" s="7">
         <v>0</v>
@@ -6530,7 +6530,7 @@
         <v>0</v>
       </c>
       <c r="P48" s="7">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="Q48" s="7">
         <v>2</v>
@@ -6750,7 +6750,7 @@
         <v>0</v>
       </c>
       <c r="P50" s="7">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Q50" s="7">
         <v>0</v>
@@ -6860,7 +6860,7 @@
         <v>0</v>
       </c>
       <c r="P51" s="7">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Q51" s="7">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{718D7FBB-C4B0-4AE1-A01D-C99C02242017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16ADACB1-C2A9-45C2-B8E1-331D5A996404}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1209" uniqueCount="221">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1367,7 +1367,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AJ70"/>
+  <dimension ref="A1:AJ115"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.125" style="4" bestFit="1" customWidth="1"/>
@@ -9002,6 +9002,4956 @@
         <v>2</v>
       </c>
       <c r="AJ70" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A71" s="7">
+        <v>301101</v>
+      </c>
+      <c r="B71" s="7">
+        <v>30</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F71" s="7">
+        <v>1000102</v>
+      </c>
+      <c r="G71" s="7">
+        <v>12</v>
+      </c>
+      <c r="H71" s="7">
+        <v>1</v>
+      </c>
+      <c r="I71" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J71" s="7">
+        <v>0</v>
+      </c>
+      <c r="K71" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="L71" s="7">
+        <v>800001011</v>
+      </c>
+      <c r="M71" s="7">
+        <v>12</v>
+      </c>
+      <c r="N71" s="7">
+        <v>70</v>
+      </c>
+      <c r="O71" s="7">
+        <v>0</v>
+      </c>
+      <c r="P71" s="7">
+        <v>16</v>
+      </c>
+      <c r="Q71" s="7">
+        <v>0</v>
+      </c>
+      <c r="R71" s="7">
+        <v>18</v>
+      </c>
+      <c r="S71" s="7">
+        <v>-3000</v>
+      </c>
+      <c r="T71" s="7">
+        <v>1</v>
+      </c>
+      <c r="U71" s="7">
+        <v>0</v>
+      </c>
+      <c r="V71" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="W71" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="X71" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="Y71" s="14">
+        <v>201001011</v>
+      </c>
+      <c r="Z71" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB71" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="AC71" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AD71" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AE71" s="7">
+        <v>25010001</v>
+      </c>
+      <c r="AF71" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG71" s="4">
+        <v>10000</v>
+      </c>
+      <c r="AH71" s="4">
+        <v>10000</v>
+      </c>
+      <c r="AI71" s="4">
+        <v>50</v>
+      </c>
+      <c r="AJ71" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A72" s="7">
+        <v>301102</v>
+      </c>
+      <c r="B72" s="7">
+        <v>30</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F72" s="7">
+        <v>1000102</v>
+      </c>
+      <c r="G72" s="7">
+        <v>12</v>
+      </c>
+      <c r="H72" s="7">
+        <v>1</v>
+      </c>
+      <c r="I72" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J72" s="7">
+        <v>0</v>
+      </c>
+      <c r="K72" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="L72" s="7">
+        <v>800001021</v>
+      </c>
+      <c r="M72" s="7">
+        <v>12</v>
+      </c>
+      <c r="N72" s="7">
+        <v>200</v>
+      </c>
+      <c r="O72" s="7">
+        <v>0</v>
+      </c>
+      <c r="P72" s="7">
+        <v>30</v>
+      </c>
+      <c r="Q72" s="7">
+        <v>2</v>
+      </c>
+      <c r="R72" s="7">
+        <v>230</v>
+      </c>
+      <c r="S72" s="7">
+        <v>-3000</v>
+      </c>
+      <c r="T72" s="7">
+        <v>1</v>
+      </c>
+      <c r="U72" s="7">
+        <v>0</v>
+      </c>
+      <c r="V72" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="W72" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="X72" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="Y72" s="14">
+        <v>201002011</v>
+      </c>
+      <c r="Z72" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA72" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB72" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="AC72" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AD72" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AE72" s="7">
+        <v>25010001</v>
+      </c>
+      <c r="AF72" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG72" s="4">
+        <v>3000</v>
+      </c>
+      <c r="AH72" s="4">
+        <v>10000</v>
+      </c>
+      <c r="AI72" s="4">
+        <v>10</v>
+      </c>
+      <c r="AJ72" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A73" s="12">
+        <v>301103</v>
+      </c>
+      <c r="B73" s="12">
+        <v>30</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D73" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F73" s="12">
+        <v>1000102</v>
+      </c>
+      <c r="G73" s="12">
+        <v>12</v>
+      </c>
+      <c r="H73" s="12">
+        <v>1</v>
+      </c>
+      <c r="I73" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J73" s="12">
+        <v>0</v>
+      </c>
+      <c r="K73" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="L73" s="12">
+        <v>800001021</v>
+      </c>
+      <c r="M73" s="12">
+        <v>12</v>
+      </c>
+      <c r="N73" s="12">
+        <v>70</v>
+      </c>
+      <c r="O73" s="12">
+        <v>0</v>
+      </c>
+      <c r="P73" s="12">
+        <v>15</v>
+      </c>
+      <c r="Q73" s="12">
+        <v>1</v>
+      </c>
+      <c r="R73" s="12">
+        <v>300</v>
+      </c>
+      <c r="S73" s="12">
+        <v>-3000</v>
+      </c>
+      <c r="T73" s="12">
+        <v>1</v>
+      </c>
+      <c r="U73" s="12">
+        <v>250</v>
+      </c>
+      <c r="V73" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="W73" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="X73" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="Y73" s="13">
+        <v>20010001</v>
+      </c>
+      <c r="Z73" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA73" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB73" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="AC73" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AD73" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AE73" s="12">
+        <v>25010001</v>
+      </c>
+      <c r="AF73" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG73" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI73" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ73" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A74" s="7">
+        <v>301104</v>
+      </c>
+      <c r="B74" s="7">
+        <v>30</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F74" s="7">
+        <v>1000010</v>
+      </c>
+      <c r="G74" s="7">
+        <v>12</v>
+      </c>
+      <c r="H74" s="7">
+        <v>1</v>
+      </c>
+      <c r="I74" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J74" s="7">
+        <v>0</v>
+      </c>
+      <c r="K74" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="L74" s="7">
+        <v>800001041</v>
+      </c>
+      <c r="M74" s="7">
+        <v>12</v>
+      </c>
+      <c r="N74" s="7">
+        <v>70</v>
+      </c>
+      <c r="O74" s="7">
+        <v>0</v>
+      </c>
+      <c r="P74" s="7">
+        <v>19</v>
+      </c>
+      <c r="Q74" s="7">
+        <v>0</v>
+      </c>
+      <c r="R74" s="7">
+        <v>15</v>
+      </c>
+      <c r="S74" s="7">
+        <v>-3000</v>
+      </c>
+      <c r="T74" s="7">
+        <v>1</v>
+      </c>
+      <c r="U74" s="7">
+        <v>0</v>
+      </c>
+      <c r="V74" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="W74" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="X74" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="Y74" s="14">
+        <v>201004011</v>
+      </c>
+      <c r="Z74" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA74" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB74" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="AC74" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AD74" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AE74" s="7">
+        <v>25010001</v>
+      </c>
+      <c r="AF74" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG74" s="4">
+        <v>10000</v>
+      </c>
+      <c r="AH74" s="4">
+        <v>10000</v>
+      </c>
+      <c r="AI74" s="4">
+        <v>80</v>
+      </c>
+      <c r="AJ74" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="75" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A75" s="7">
+        <v>301105</v>
+      </c>
+      <c r="B75" s="7">
+        <v>30</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F75" s="7">
+        <v>1000010</v>
+      </c>
+      <c r="G75" s="7">
+        <v>12</v>
+      </c>
+      <c r="H75" s="7">
+        <v>1</v>
+      </c>
+      <c r="I75" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J75" s="7">
+        <v>0</v>
+      </c>
+      <c r="K75" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="L75" s="7">
+        <v>800014011</v>
+      </c>
+      <c r="M75" s="7">
+        <v>12</v>
+      </c>
+      <c r="N75" s="7">
+        <v>125</v>
+      </c>
+      <c r="O75" s="7">
+        <v>0</v>
+      </c>
+      <c r="P75" s="7">
+        <v>18</v>
+      </c>
+      <c r="Q75" s="7">
+        <v>1</v>
+      </c>
+      <c r="R75" s="7">
+        <v>48</v>
+      </c>
+      <c r="S75" s="7">
+        <v>-3000</v>
+      </c>
+      <c r="T75" s="7">
+        <v>1</v>
+      </c>
+      <c r="U75" s="7">
+        <v>0</v>
+      </c>
+      <c r="V75" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="W75" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="X75" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="Y75" s="14">
+        <v>214001011</v>
+      </c>
+      <c r="Z75" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB75" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="AC75" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AD75" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AE75" s="7">
+        <v>25010001</v>
+      </c>
+      <c r="AF75" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG75" s="4">
+        <v>10000</v>
+      </c>
+      <c r="AH75" s="4">
+        <v>10000</v>
+      </c>
+      <c r="AI75" s="4">
+        <v>40</v>
+      </c>
+      <c r="AJ75" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A76" s="12">
+        <v>301106</v>
+      </c>
+      <c r="B76" s="12">
+        <v>30</v>
+      </c>
+      <c r="C76" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="D76" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E76" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F76" s="12">
+        <v>1000010</v>
+      </c>
+      <c r="G76" s="12">
+        <v>12</v>
+      </c>
+      <c r="H76" s="12">
+        <v>1</v>
+      </c>
+      <c r="I76" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J76" s="12">
+        <v>0</v>
+      </c>
+      <c r="K76" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="L76" s="12">
+        <v>1000010</v>
+      </c>
+      <c r="M76" s="12">
+        <v>12</v>
+      </c>
+      <c r="N76" s="12">
+        <v>100</v>
+      </c>
+      <c r="O76" s="12">
+        <v>0</v>
+      </c>
+      <c r="P76" s="12">
+        <v>15</v>
+      </c>
+      <c r="Q76" s="12">
+        <v>0</v>
+      </c>
+      <c r="R76" s="12">
+        <v>36</v>
+      </c>
+      <c r="S76" s="12">
+        <v>-3000</v>
+      </c>
+      <c r="T76" s="12">
+        <v>1</v>
+      </c>
+      <c r="U76" s="12">
+        <v>0</v>
+      </c>
+      <c r="V76" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="W76" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="X76" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y76" s="13">
+        <v>20040001</v>
+      </c>
+      <c r="Z76" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB76" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC76" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AD76" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AE76" s="12">
+        <v>25010001</v>
+      </c>
+      <c r="AF76" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG76" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH76" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI76" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ76" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A77" s="12">
+        <v>301107</v>
+      </c>
+      <c r="B77" s="12">
+        <v>30</v>
+      </c>
+      <c r="C77" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="D77" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E77" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F77" s="12">
+        <v>1000006</v>
+      </c>
+      <c r="G77" s="12">
+        <v>12</v>
+      </c>
+      <c r="H77" s="12">
+        <v>1</v>
+      </c>
+      <c r="I77" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J77" s="12">
+        <v>0</v>
+      </c>
+      <c r="K77" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="L77" s="12">
+        <v>1000006</v>
+      </c>
+      <c r="M77" s="12">
+        <v>12</v>
+      </c>
+      <c r="N77" s="12">
+        <v>100</v>
+      </c>
+      <c r="O77" s="12">
+        <v>0</v>
+      </c>
+      <c r="P77" s="12">
+        <v>15</v>
+      </c>
+      <c r="Q77" s="12">
+        <v>0</v>
+      </c>
+      <c r="R77" s="12">
+        <v>36</v>
+      </c>
+      <c r="S77" s="12">
+        <v>-3000</v>
+      </c>
+      <c r="T77" s="12">
+        <v>1</v>
+      </c>
+      <c r="U77" s="12">
+        <v>0</v>
+      </c>
+      <c r="V77" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="W77" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="X77" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y77" s="13">
+        <v>20030001</v>
+      </c>
+      <c r="Z77" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB77" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC77" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AD77" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AE77" s="12">
+        <v>25010001</v>
+      </c>
+      <c r="AF77" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG77" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI77" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ77" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A78" s="12">
+        <v>301108</v>
+      </c>
+      <c r="B78" s="12">
+        <v>30</v>
+      </c>
+      <c r="C78" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="D78" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="E78" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F78" s="12">
+        <v>1000006</v>
+      </c>
+      <c r="G78" s="12">
+        <v>12</v>
+      </c>
+      <c r="H78" s="12">
+        <v>1</v>
+      </c>
+      <c r="I78" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J78" s="12">
+        <v>0</v>
+      </c>
+      <c r="K78" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="L78" s="12">
+        <v>1000006</v>
+      </c>
+      <c r="M78" s="12">
+        <v>12</v>
+      </c>
+      <c r="N78" s="12">
+        <v>100</v>
+      </c>
+      <c r="O78" s="12">
+        <v>0</v>
+      </c>
+      <c r="P78" s="12">
+        <v>15</v>
+      </c>
+      <c r="Q78" s="12">
+        <v>0</v>
+      </c>
+      <c r="R78" s="12">
+        <v>36</v>
+      </c>
+      <c r="S78" s="12">
+        <v>-3000</v>
+      </c>
+      <c r="T78" s="12">
+        <v>1</v>
+      </c>
+      <c r="U78" s="12">
+        <v>0</v>
+      </c>
+      <c r="V78" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="W78" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="X78" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y78" s="13">
+        <v>20030001</v>
+      </c>
+      <c r="Z78" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA78" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB78" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC78" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AD78" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AE78" s="12">
+        <v>25010001</v>
+      </c>
+      <c r="AF78" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG78" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH78" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI78" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ78" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A79" s="12">
+        <v>301109</v>
+      </c>
+      <c r="B79" s="12">
+        <v>30</v>
+      </c>
+      <c r="C79" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D79" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E79" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F79" s="12">
+        <v>1000006</v>
+      </c>
+      <c r="G79" s="12">
+        <v>12</v>
+      </c>
+      <c r="H79" s="12">
+        <v>1</v>
+      </c>
+      <c r="I79" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J79" s="12">
+        <v>0</v>
+      </c>
+      <c r="K79" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="L79" s="12">
+        <v>1000006</v>
+      </c>
+      <c r="M79" s="12">
+        <v>12</v>
+      </c>
+      <c r="N79" s="12">
+        <v>100</v>
+      </c>
+      <c r="O79" s="12">
+        <v>0</v>
+      </c>
+      <c r="P79" s="12">
+        <v>15</v>
+      </c>
+      <c r="Q79" s="12">
+        <v>0</v>
+      </c>
+      <c r="R79" s="12">
+        <v>36</v>
+      </c>
+      <c r="S79" s="12">
+        <v>-3000</v>
+      </c>
+      <c r="T79" s="12">
+        <v>1</v>
+      </c>
+      <c r="U79" s="12">
+        <v>0</v>
+      </c>
+      <c r="V79" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="W79" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="X79" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y79" s="13">
+        <v>20030001</v>
+      </c>
+      <c r="Z79" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA79" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB79" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC79" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AD79" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AE79" s="12">
+        <v>25010001</v>
+      </c>
+      <c r="AF79" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG79" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH79" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI79" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ79" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A80" s="12">
+        <v>301110</v>
+      </c>
+      <c r="B80" s="12">
+        <v>30</v>
+      </c>
+      <c r="C80" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="D80" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="E80" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F80" s="12">
+        <v>1000103</v>
+      </c>
+      <c r="G80" s="12">
+        <v>12</v>
+      </c>
+      <c r="H80" s="12">
+        <v>1</v>
+      </c>
+      <c r="I80" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J80" s="12">
+        <v>0</v>
+      </c>
+      <c r="K80" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="L80" s="12">
+        <v>1000103</v>
+      </c>
+      <c r="M80" s="12">
+        <v>12</v>
+      </c>
+      <c r="N80" s="12">
+        <v>100</v>
+      </c>
+      <c r="O80" s="12">
+        <v>0</v>
+      </c>
+      <c r="P80" s="12">
+        <v>15</v>
+      </c>
+      <c r="Q80" s="12">
+        <v>0</v>
+      </c>
+      <c r="R80" s="12">
+        <v>36</v>
+      </c>
+      <c r="S80" s="12">
+        <v>-3000</v>
+      </c>
+      <c r="T80" s="12">
+        <v>1</v>
+      </c>
+      <c r="U80" s="12">
+        <v>0</v>
+      </c>
+      <c r="V80" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="W80" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="X80" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y80" s="13">
+        <v>20020001</v>
+      </c>
+      <c r="Z80" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA80" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB80" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC80" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AD80" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AE80" s="12">
+        <v>25010001</v>
+      </c>
+      <c r="AF80" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG80" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH80" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI80" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ80" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A81" s="12">
+        <v>301111</v>
+      </c>
+      <c r="B81" s="12">
+        <v>30</v>
+      </c>
+      <c r="C81" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="D81" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E81" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F81" s="12">
+        <v>1000103</v>
+      </c>
+      <c r="G81" s="12">
+        <v>12</v>
+      </c>
+      <c r="H81" s="12">
+        <v>1</v>
+      </c>
+      <c r="I81" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J81" s="12">
+        <v>0</v>
+      </c>
+      <c r="K81" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="L81" s="12">
+        <v>1000103</v>
+      </c>
+      <c r="M81" s="12">
+        <v>12</v>
+      </c>
+      <c r="N81" s="12">
+        <v>100</v>
+      </c>
+      <c r="O81" s="12">
+        <v>0</v>
+      </c>
+      <c r="P81" s="12">
+        <v>15</v>
+      </c>
+      <c r="Q81" s="12">
+        <v>0</v>
+      </c>
+      <c r="R81" s="12">
+        <v>36</v>
+      </c>
+      <c r="S81" s="12">
+        <v>-3000</v>
+      </c>
+      <c r="T81" s="12">
+        <v>1</v>
+      </c>
+      <c r="U81" s="12">
+        <v>0</v>
+      </c>
+      <c r="V81" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="W81" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="X81" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y81" s="13">
+        <v>20020001</v>
+      </c>
+      <c r="Z81" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA81" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB81" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC81" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AD81" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AE81" s="12">
+        <v>25010001</v>
+      </c>
+      <c r="AF81" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG81" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH81" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI81" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ81" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A82" s="12">
+        <v>301112</v>
+      </c>
+      <c r="B82" s="12">
+        <v>30</v>
+      </c>
+      <c r="C82" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="D82" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="E82" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F82" s="12">
+        <v>1000103</v>
+      </c>
+      <c r="G82" s="12">
+        <v>12</v>
+      </c>
+      <c r="H82" s="12">
+        <v>1</v>
+      </c>
+      <c r="I82" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J82" s="12">
+        <v>0</v>
+      </c>
+      <c r="K82" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="L82" s="12">
+        <v>1000103</v>
+      </c>
+      <c r="M82" s="12">
+        <v>12</v>
+      </c>
+      <c r="N82" s="12">
+        <v>100</v>
+      </c>
+      <c r="O82" s="12">
+        <v>0</v>
+      </c>
+      <c r="P82" s="12">
+        <v>15</v>
+      </c>
+      <c r="Q82" s="12">
+        <v>0</v>
+      </c>
+      <c r="R82" s="12">
+        <v>36</v>
+      </c>
+      <c r="S82" s="12">
+        <v>-3000</v>
+      </c>
+      <c r="T82" s="12">
+        <v>1</v>
+      </c>
+      <c r="U82" s="12">
+        <v>0</v>
+      </c>
+      <c r="V82" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="W82" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="X82" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y82" s="13">
+        <v>20020001</v>
+      </c>
+      <c r="Z82" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA82" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB82" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC82" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AD82" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AE82" s="12">
+        <v>25010001</v>
+      </c>
+      <c r="AF82" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG82" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH82" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI82" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ82" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A83" s="7">
+        <v>301113</v>
+      </c>
+      <c r="B83" s="7">
+        <v>30</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D83" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F83" s="7">
+        <v>1000011</v>
+      </c>
+      <c r="G83" s="7">
+        <v>12</v>
+      </c>
+      <c r="H83" s="7">
+        <v>1</v>
+      </c>
+      <c r="I83" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J83" s="7">
+        <v>0</v>
+      </c>
+      <c r="K83" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="L83" s="7">
+        <v>800003021</v>
+      </c>
+      <c r="M83" s="7">
+        <v>12</v>
+      </c>
+      <c r="N83" s="7">
+        <v>500</v>
+      </c>
+      <c r="O83" s="7">
+        <v>0</v>
+      </c>
+      <c r="P83" s="7">
+        <v>42</v>
+      </c>
+      <c r="Q83" s="7">
+        <v>3</v>
+      </c>
+      <c r="R83" s="16">
+        <v>1496</v>
+      </c>
+      <c r="S83" s="7">
+        <v>-3000</v>
+      </c>
+      <c r="T83" s="7">
+        <v>1</v>
+      </c>
+      <c r="U83" s="7">
+        <v>30000</v>
+      </c>
+      <c r="V83" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="W83" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="X83" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="Y83" s="14">
+        <v>203002011</v>
+      </c>
+      <c r="Z83" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA83" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB83" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="AC83" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AD83" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AE83" s="7">
+        <v>25010001</v>
+      </c>
+      <c r="AF83" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG83" s="4">
+        <v>1000</v>
+      </c>
+      <c r="AH83" s="4">
+        <v>5000</v>
+      </c>
+      <c r="AI83" s="4">
+        <v>2</v>
+      </c>
+      <c r="AJ83" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A84" s="12">
+        <v>301114</v>
+      </c>
+      <c r="B84" s="12">
+        <v>30</v>
+      </c>
+      <c r="C84" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D84" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="E84" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F84" s="12">
+        <v>1000011</v>
+      </c>
+      <c r="G84" s="12">
+        <v>12</v>
+      </c>
+      <c r="H84" s="12">
+        <v>1</v>
+      </c>
+      <c r="I84" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J84" s="12">
+        <v>0</v>
+      </c>
+      <c r="K84" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="L84" s="12">
+        <v>1000011</v>
+      </c>
+      <c r="M84" s="12">
+        <v>12</v>
+      </c>
+      <c r="N84" s="12">
+        <v>100</v>
+      </c>
+      <c r="O84" s="12">
+        <v>0</v>
+      </c>
+      <c r="P84" s="12">
+        <v>15</v>
+      </c>
+      <c r="Q84" s="12">
+        <v>0</v>
+      </c>
+      <c r="R84" s="12">
+        <v>36</v>
+      </c>
+      <c r="S84" s="12">
+        <v>-3000</v>
+      </c>
+      <c r="T84" s="12">
+        <v>1</v>
+      </c>
+      <c r="U84" s="12">
+        <v>0</v>
+      </c>
+      <c r="V84" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="W84" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="X84" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y84" s="13">
+        <v>20050001</v>
+      </c>
+      <c r="Z84" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA84" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB84" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC84" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AD84" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AE84" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF84" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG84" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI84" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ84" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A85" s="12">
+        <v>301115</v>
+      </c>
+      <c r="B85" s="12">
+        <v>30</v>
+      </c>
+      <c r="C85" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="D85" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="E85" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F85" s="12">
+        <v>1000011</v>
+      </c>
+      <c r="G85" s="12">
+        <v>12</v>
+      </c>
+      <c r="H85" s="12">
+        <v>1</v>
+      </c>
+      <c r="I85" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J85" s="12">
+        <v>0</v>
+      </c>
+      <c r="K85" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="L85" s="12">
+        <v>1000011</v>
+      </c>
+      <c r="M85" s="12">
+        <v>12</v>
+      </c>
+      <c r="N85" s="12">
+        <v>100</v>
+      </c>
+      <c r="O85" s="12">
+        <v>0</v>
+      </c>
+      <c r="P85" s="12">
+        <v>15</v>
+      </c>
+      <c r="Q85" s="12">
+        <v>0</v>
+      </c>
+      <c r="R85" s="12">
+        <v>36</v>
+      </c>
+      <c r="S85" s="12">
+        <v>-3000</v>
+      </c>
+      <c r="T85" s="12">
+        <v>1</v>
+      </c>
+      <c r="U85" s="12">
+        <v>0</v>
+      </c>
+      <c r="V85" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="W85" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="X85" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y85" s="13">
+        <v>20050001</v>
+      </c>
+      <c r="Z85" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA85" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB85" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC85" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AD85" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AE85" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF85" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG85" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI85" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ85" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A86" s="7">
+        <v>301201</v>
+      </c>
+      <c r="B86" s="7">
+        <v>30</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F86" s="7">
+        <v>1000102</v>
+      </c>
+      <c r="G86" s="7">
+        <v>12</v>
+      </c>
+      <c r="H86" s="7">
+        <v>1</v>
+      </c>
+      <c r="I86" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J86" s="7">
+        <v>0</v>
+      </c>
+      <c r="K86" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="L86" s="7">
+        <v>800001011</v>
+      </c>
+      <c r="M86" s="7">
+        <v>12</v>
+      </c>
+      <c r="N86" s="7">
+        <v>70</v>
+      </c>
+      <c r="O86" s="7">
+        <v>0</v>
+      </c>
+      <c r="P86" s="7">
+        <v>16</v>
+      </c>
+      <c r="Q86" s="7">
+        <v>0</v>
+      </c>
+      <c r="R86" s="7">
+        <v>18</v>
+      </c>
+      <c r="S86" s="7">
+        <v>-3000</v>
+      </c>
+      <c r="T86" s="7">
+        <v>1</v>
+      </c>
+      <c r="U86" s="7">
+        <v>0</v>
+      </c>
+      <c r="V86" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="W86" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="X86" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="Y86" s="14">
+        <v>201001011</v>
+      </c>
+      <c r="Z86" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA86" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB86" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="AC86" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AD86" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AE86" s="7">
+        <v>25010001</v>
+      </c>
+      <c r="AF86" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG86" s="4">
+        <v>10000</v>
+      </c>
+      <c r="AH86" s="4">
+        <v>10000</v>
+      </c>
+      <c r="AI86" s="4">
+        <v>50</v>
+      </c>
+      <c r="AJ86" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A87" s="7">
+        <v>301202</v>
+      </c>
+      <c r="B87" s="7">
+        <v>30</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F87" s="7">
+        <v>1000102</v>
+      </c>
+      <c r="G87" s="7">
+        <v>12</v>
+      </c>
+      <c r="H87" s="7">
+        <v>1</v>
+      </c>
+      <c r="I87" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J87" s="7">
+        <v>0</v>
+      </c>
+      <c r="K87" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="L87" s="7">
+        <v>800001021</v>
+      </c>
+      <c r="M87" s="7">
+        <v>12</v>
+      </c>
+      <c r="N87" s="7">
+        <v>200</v>
+      </c>
+      <c r="O87" s="7">
+        <v>0</v>
+      </c>
+      <c r="P87" s="7">
+        <v>30</v>
+      </c>
+      <c r="Q87" s="7">
+        <v>2</v>
+      </c>
+      <c r="R87" s="7">
+        <v>230</v>
+      </c>
+      <c r="S87" s="7">
+        <v>-3000</v>
+      </c>
+      <c r="T87" s="7">
+        <v>1</v>
+      </c>
+      <c r="U87" s="7">
+        <v>0</v>
+      </c>
+      <c r="V87" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="W87" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="X87" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="Y87" s="14">
+        <v>201002011</v>
+      </c>
+      <c r="Z87" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA87" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB87" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="AC87" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AD87" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AE87" s="7">
+        <v>25010001</v>
+      </c>
+      <c r="AF87" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG87" s="4">
+        <v>3000</v>
+      </c>
+      <c r="AH87" s="4">
+        <v>10000</v>
+      </c>
+      <c r="AI87" s="4">
+        <v>10</v>
+      </c>
+      <c r="AJ87" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A88" s="12">
+        <v>301203</v>
+      </c>
+      <c r="B88" s="12">
+        <v>30</v>
+      </c>
+      <c r="C88" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D88" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E88" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F88" s="12">
+        <v>1000102</v>
+      </c>
+      <c r="G88" s="12">
+        <v>12</v>
+      </c>
+      <c r="H88" s="12">
+        <v>1</v>
+      </c>
+      <c r="I88" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J88" s="12">
+        <v>0</v>
+      </c>
+      <c r="K88" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="L88" s="12">
+        <v>800001021</v>
+      </c>
+      <c r="M88" s="12">
+        <v>12</v>
+      </c>
+      <c r="N88" s="12">
+        <v>70</v>
+      </c>
+      <c r="O88" s="12">
+        <v>0</v>
+      </c>
+      <c r="P88" s="12">
+        <v>15</v>
+      </c>
+      <c r="Q88" s="12">
+        <v>1</v>
+      </c>
+      <c r="R88" s="12">
+        <v>300</v>
+      </c>
+      <c r="S88" s="12">
+        <v>-3000</v>
+      </c>
+      <c r="T88" s="12">
+        <v>1</v>
+      </c>
+      <c r="U88" s="12">
+        <v>250</v>
+      </c>
+      <c r="V88" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="W88" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="X88" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="Y88" s="13">
+        <v>20010001</v>
+      </c>
+      <c r="Z88" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA88" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB88" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="AC88" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AD88" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AE88" s="12">
+        <v>25010001</v>
+      </c>
+      <c r="AF88" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG88" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI88" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ88" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A89" s="7">
+        <v>301204</v>
+      </c>
+      <c r="B89" s="7">
+        <v>30</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="E89" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F89" s="7">
+        <v>1000010</v>
+      </c>
+      <c r="G89" s="7">
+        <v>12</v>
+      </c>
+      <c r="H89" s="7">
+        <v>1</v>
+      </c>
+      <c r="I89" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J89" s="7">
+        <v>0</v>
+      </c>
+      <c r="K89" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="L89" s="7">
+        <v>800001041</v>
+      </c>
+      <c r="M89" s="7">
+        <v>12</v>
+      </c>
+      <c r="N89" s="7">
+        <v>70</v>
+      </c>
+      <c r="O89" s="7">
+        <v>0</v>
+      </c>
+      <c r="P89" s="7">
+        <v>19</v>
+      </c>
+      <c r="Q89" s="7">
+        <v>0</v>
+      </c>
+      <c r="R89" s="7">
+        <v>15</v>
+      </c>
+      <c r="S89" s="7">
+        <v>-3000</v>
+      </c>
+      <c r="T89" s="7">
+        <v>1</v>
+      </c>
+      <c r="U89" s="7">
+        <v>0</v>
+      </c>
+      <c r="V89" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="W89" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="X89" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="Y89" s="14">
+        <v>201004011</v>
+      </c>
+      <c r="Z89" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB89" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="AC89" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AD89" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AE89" s="7">
+        <v>25010001</v>
+      </c>
+      <c r="AF89" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG89" s="4">
+        <v>10000</v>
+      </c>
+      <c r="AH89" s="4">
+        <v>10000</v>
+      </c>
+      <c r="AI89" s="4">
+        <v>80</v>
+      </c>
+      <c r="AJ89" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A90" s="7">
+        <v>301205</v>
+      </c>
+      <c r="B90" s="7">
+        <v>30</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D90" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F90" s="7">
+        <v>1000010</v>
+      </c>
+      <c r="G90" s="7">
+        <v>12</v>
+      </c>
+      <c r="H90" s="7">
+        <v>1</v>
+      </c>
+      <c r="I90" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J90" s="7">
+        <v>0</v>
+      </c>
+      <c r="K90" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="L90" s="7">
+        <v>800014011</v>
+      </c>
+      <c r="M90" s="7">
+        <v>12</v>
+      </c>
+      <c r="N90" s="7">
+        <v>125</v>
+      </c>
+      <c r="O90" s="7">
+        <v>0</v>
+      </c>
+      <c r="P90" s="7">
+        <v>18</v>
+      </c>
+      <c r="Q90" s="7">
+        <v>1</v>
+      </c>
+      <c r="R90" s="7">
+        <v>48</v>
+      </c>
+      <c r="S90" s="7">
+        <v>-3000</v>
+      </c>
+      <c r="T90" s="7">
+        <v>1</v>
+      </c>
+      <c r="U90" s="7">
+        <v>0</v>
+      </c>
+      <c r="V90" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="W90" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="X90" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="Y90" s="14">
+        <v>214001011</v>
+      </c>
+      <c r="Z90" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA90" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB90" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="AC90" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AD90" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AE90" s="7">
+        <v>25010001</v>
+      </c>
+      <c r="AF90" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG90" s="4">
+        <v>10000</v>
+      </c>
+      <c r="AH90" s="4">
+        <v>10000</v>
+      </c>
+      <c r="AI90" s="4">
+        <v>40</v>
+      </c>
+      <c r="AJ90" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A91" s="12">
+        <v>301206</v>
+      </c>
+      <c r="B91" s="12">
+        <v>30</v>
+      </c>
+      <c r="C91" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="D91" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E91" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F91" s="12">
+        <v>1000010</v>
+      </c>
+      <c r="G91" s="12">
+        <v>12</v>
+      </c>
+      <c r="H91" s="12">
+        <v>1</v>
+      </c>
+      <c r="I91" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J91" s="12">
+        <v>0</v>
+      </c>
+      <c r="K91" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="L91" s="12">
+        <v>1000010</v>
+      </c>
+      <c r="M91" s="12">
+        <v>12</v>
+      </c>
+      <c r="N91" s="12">
+        <v>100</v>
+      </c>
+      <c r="O91" s="12">
+        <v>0</v>
+      </c>
+      <c r="P91" s="12">
+        <v>15</v>
+      </c>
+      <c r="Q91" s="12">
+        <v>0</v>
+      </c>
+      <c r="R91" s="12">
+        <v>36</v>
+      </c>
+      <c r="S91" s="12">
+        <v>-3000</v>
+      </c>
+      <c r="T91" s="12">
+        <v>1</v>
+      </c>
+      <c r="U91" s="12">
+        <v>0</v>
+      </c>
+      <c r="V91" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="W91" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="X91" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y91" s="13">
+        <v>20040001</v>
+      </c>
+      <c r="Z91" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB91" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC91" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AD91" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AE91" s="12">
+        <v>25010001</v>
+      </c>
+      <c r="AF91" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG91" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI91" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ91" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A92" s="12">
+        <v>301207</v>
+      </c>
+      <c r="B92" s="12">
+        <v>30</v>
+      </c>
+      <c r="C92" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="D92" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E92" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F92" s="12">
+        <v>1000006</v>
+      </c>
+      <c r="G92" s="12">
+        <v>12</v>
+      </c>
+      <c r="H92" s="12">
+        <v>1</v>
+      </c>
+      <c r="I92" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J92" s="12">
+        <v>0</v>
+      </c>
+      <c r="K92" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="L92" s="12">
+        <v>1000006</v>
+      </c>
+      <c r="M92" s="12">
+        <v>12</v>
+      </c>
+      <c r="N92" s="12">
+        <v>100</v>
+      </c>
+      <c r="O92" s="12">
+        <v>0</v>
+      </c>
+      <c r="P92" s="12">
+        <v>15</v>
+      </c>
+      <c r="Q92" s="12">
+        <v>0</v>
+      </c>
+      <c r="R92" s="12">
+        <v>36</v>
+      </c>
+      <c r="S92" s="12">
+        <v>-3000</v>
+      </c>
+      <c r="T92" s="12">
+        <v>1</v>
+      </c>
+      <c r="U92" s="12">
+        <v>0</v>
+      </c>
+      <c r="V92" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="W92" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="X92" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y92" s="13">
+        <v>20030001</v>
+      </c>
+      <c r="Z92" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA92" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB92" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC92" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AD92" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AE92" s="12">
+        <v>25010001</v>
+      </c>
+      <c r="AF92" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG92" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI92" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ92" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A93" s="12">
+        <v>301208</v>
+      </c>
+      <c r="B93" s="12">
+        <v>30</v>
+      </c>
+      <c r="C93" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="D93" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="E93" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F93" s="12">
+        <v>1000006</v>
+      </c>
+      <c r="G93" s="12">
+        <v>12</v>
+      </c>
+      <c r="H93" s="12">
+        <v>1</v>
+      </c>
+      <c r="I93" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J93" s="12">
+        <v>0</v>
+      </c>
+      <c r="K93" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="L93" s="12">
+        <v>1000006</v>
+      </c>
+      <c r="M93" s="12">
+        <v>12</v>
+      </c>
+      <c r="N93" s="12">
+        <v>100</v>
+      </c>
+      <c r="O93" s="12">
+        <v>0</v>
+      </c>
+      <c r="P93" s="12">
+        <v>15</v>
+      </c>
+      <c r="Q93" s="12">
+        <v>0</v>
+      </c>
+      <c r="R93" s="12">
+        <v>36</v>
+      </c>
+      <c r="S93" s="12">
+        <v>-3000</v>
+      </c>
+      <c r="T93" s="12">
+        <v>1</v>
+      </c>
+      <c r="U93" s="12">
+        <v>0</v>
+      </c>
+      <c r="V93" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="W93" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="X93" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y93" s="13">
+        <v>20030001</v>
+      </c>
+      <c r="Z93" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA93" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB93" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC93" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AD93" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AE93" s="12">
+        <v>25010001</v>
+      </c>
+      <c r="AF93" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG93" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI93" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ93" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A94" s="12">
+        <v>301209</v>
+      </c>
+      <c r="B94" s="12">
+        <v>30</v>
+      </c>
+      <c r="C94" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D94" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E94" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F94" s="12">
+        <v>1000006</v>
+      </c>
+      <c r="G94" s="12">
+        <v>12</v>
+      </c>
+      <c r="H94" s="12">
+        <v>1</v>
+      </c>
+      <c r="I94" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J94" s="12">
+        <v>0</v>
+      </c>
+      <c r="K94" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="L94" s="12">
+        <v>1000006</v>
+      </c>
+      <c r="M94" s="12">
+        <v>12</v>
+      </c>
+      <c r="N94" s="12">
+        <v>100</v>
+      </c>
+      <c r="O94" s="12">
+        <v>0</v>
+      </c>
+      <c r="P94" s="12">
+        <v>15</v>
+      </c>
+      <c r="Q94" s="12">
+        <v>0</v>
+      </c>
+      <c r="R94" s="12">
+        <v>36</v>
+      </c>
+      <c r="S94" s="12">
+        <v>-3000</v>
+      </c>
+      <c r="T94" s="12">
+        <v>1</v>
+      </c>
+      <c r="U94" s="12">
+        <v>0</v>
+      </c>
+      <c r="V94" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="W94" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="X94" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y94" s="13">
+        <v>20030001</v>
+      </c>
+      <c r="Z94" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB94" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC94" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AD94" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AE94" s="12">
+        <v>25010001</v>
+      </c>
+      <c r="AF94" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG94" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI94" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ94" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A95" s="12">
+        <v>301210</v>
+      </c>
+      <c r="B95" s="12">
+        <v>30</v>
+      </c>
+      <c r="C95" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="D95" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="E95" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F95" s="12">
+        <v>1000103</v>
+      </c>
+      <c r="G95" s="12">
+        <v>12</v>
+      </c>
+      <c r="H95" s="12">
+        <v>1</v>
+      </c>
+      <c r="I95" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J95" s="12">
+        <v>0</v>
+      </c>
+      <c r="K95" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="L95" s="12">
+        <v>1000103</v>
+      </c>
+      <c r="M95" s="12">
+        <v>12</v>
+      </c>
+      <c r="N95" s="12">
+        <v>100</v>
+      </c>
+      <c r="O95" s="12">
+        <v>0</v>
+      </c>
+      <c r="P95" s="12">
+        <v>15</v>
+      </c>
+      <c r="Q95" s="12">
+        <v>0</v>
+      </c>
+      <c r="R95" s="12">
+        <v>36</v>
+      </c>
+      <c r="S95" s="12">
+        <v>-3000</v>
+      </c>
+      <c r="T95" s="12">
+        <v>1</v>
+      </c>
+      <c r="U95" s="12">
+        <v>0</v>
+      </c>
+      <c r="V95" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="W95" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="X95" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y95" s="13">
+        <v>20020001</v>
+      </c>
+      <c r="Z95" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA95" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB95" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC95" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AD95" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AE95" s="12">
+        <v>25010001</v>
+      </c>
+      <c r="AF95" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG95" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH95" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI95" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ95" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A96" s="12">
+        <v>301211</v>
+      </c>
+      <c r="B96" s="12">
+        <v>30</v>
+      </c>
+      <c r="C96" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="D96" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E96" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F96" s="12">
+        <v>1000103</v>
+      </c>
+      <c r="G96" s="12">
+        <v>12</v>
+      </c>
+      <c r="H96" s="12">
+        <v>1</v>
+      </c>
+      <c r="I96" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J96" s="12">
+        <v>0</v>
+      </c>
+      <c r="K96" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="L96" s="12">
+        <v>1000103</v>
+      </c>
+      <c r="M96" s="12">
+        <v>12</v>
+      </c>
+      <c r="N96" s="12">
+        <v>100</v>
+      </c>
+      <c r="O96" s="12">
+        <v>0</v>
+      </c>
+      <c r="P96" s="12">
+        <v>15</v>
+      </c>
+      <c r="Q96" s="12">
+        <v>0</v>
+      </c>
+      <c r="R96" s="12">
+        <v>36</v>
+      </c>
+      <c r="S96" s="12">
+        <v>-3000</v>
+      </c>
+      <c r="T96" s="12">
+        <v>1</v>
+      </c>
+      <c r="U96" s="12">
+        <v>0</v>
+      </c>
+      <c r="V96" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="W96" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="X96" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y96" s="13">
+        <v>20020001</v>
+      </c>
+      <c r="Z96" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB96" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC96" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AD96" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AE96" s="12">
+        <v>25010001</v>
+      </c>
+      <c r="AF96" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG96" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A97" s="12">
+        <v>301212</v>
+      </c>
+      <c r="B97" s="12">
+        <v>30</v>
+      </c>
+      <c r="C97" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="D97" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="E97" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F97" s="12">
+        <v>1000103</v>
+      </c>
+      <c r="G97" s="12">
+        <v>12</v>
+      </c>
+      <c r="H97" s="12">
+        <v>1</v>
+      </c>
+      <c r="I97" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J97" s="12">
+        <v>0</v>
+      </c>
+      <c r="K97" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="L97" s="12">
+        <v>1000103</v>
+      </c>
+      <c r="M97" s="12">
+        <v>12</v>
+      </c>
+      <c r="N97" s="12">
+        <v>100</v>
+      </c>
+      <c r="O97" s="12">
+        <v>0</v>
+      </c>
+      <c r="P97" s="12">
+        <v>15</v>
+      </c>
+      <c r="Q97" s="12">
+        <v>0</v>
+      </c>
+      <c r="R97" s="12">
+        <v>36</v>
+      </c>
+      <c r="S97" s="12">
+        <v>-3000</v>
+      </c>
+      <c r="T97" s="12">
+        <v>1</v>
+      </c>
+      <c r="U97" s="12">
+        <v>0</v>
+      </c>
+      <c r="V97" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="W97" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="X97" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y97" s="13">
+        <v>20020001</v>
+      </c>
+      <c r="Z97" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA97" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB97" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC97" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AD97" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AE97" s="12">
+        <v>25010001</v>
+      </c>
+      <c r="AF97" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG97" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI97" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ97" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A98" s="7">
+        <v>301213</v>
+      </c>
+      <c r="B98" s="7">
+        <v>30</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D98" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="E98" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F98" s="7">
+        <v>1000011</v>
+      </c>
+      <c r="G98" s="7">
+        <v>12</v>
+      </c>
+      <c r="H98" s="7">
+        <v>1</v>
+      </c>
+      <c r="I98" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J98" s="7">
+        <v>0</v>
+      </c>
+      <c r="K98" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="L98" s="7">
+        <v>800003021</v>
+      </c>
+      <c r="M98" s="7">
+        <v>12</v>
+      </c>
+      <c r="N98" s="7">
+        <v>500</v>
+      </c>
+      <c r="O98" s="7">
+        <v>0</v>
+      </c>
+      <c r="P98" s="7">
+        <v>42</v>
+      </c>
+      <c r="Q98" s="7">
+        <v>3</v>
+      </c>
+      <c r="R98" s="16">
+        <v>1496</v>
+      </c>
+      <c r="S98" s="7">
+        <v>-3000</v>
+      </c>
+      <c r="T98" s="7">
+        <v>1</v>
+      </c>
+      <c r="U98" s="7">
+        <v>30000</v>
+      </c>
+      <c r="V98" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="W98" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="X98" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="Y98" s="14">
+        <v>203002011</v>
+      </c>
+      <c r="Z98" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA98" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB98" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="AC98" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AD98" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AE98" s="7">
+        <v>25010001</v>
+      </c>
+      <c r="AF98" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG98" s="4">
+        <v>1000</v>
+      </c>
+      <c r="AH98" s="4">
+        <v>5000</v>
+      </c>
+      <c r="AI98" s="4">
+        <v>2</v>
+      </c>
+      <c r="AJ98" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A99" s="12">
+        <v>301214</v>
+      </c>
+      <c r="B99" s="12">
+        <v>30</v>
+      </c>
+      <c r="C99" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D99" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="E99" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F99" s="12">
+        <v>1000011</v>
+      </c>
+      <c r="G99" s="12">
+        <v>12</v>
+      </c>
+      <c r="H99" s="12">
+        <v>1</v>
+      </c>
+      <c r="I99" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J99" s="12">
+        <v>0</v>
+      </c>
+      <c r="K99" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="L99" s="12">
+        <v>1000011</v>
+      </c>
+      <c r="M99" s="12">
+        <v>12</v>
+      </c>
+      <c r="N99" s="12">
+        <v>100</v>
+      </c>
+      <c r="O99" s="12">
+        <v>0</v>
+      </c>
+      <c r="P99" s="12">
+        <v>15</v>
+      </c>
+      <c r="Q99" s="12">
+        <v>0</v>
+      </c>
+      <c r="R99" s="12">
+        <v>36</v>
+      </c>
+      <c r="S99" s="12">
+        <v>-3000</v>
+      </c>
+      <c r="T99" s="12">
+        <v>1</v>
+      </c>
+      <c r="U99" s="12">
+        <v>0</v>
+      </c>
+      <c r="V99" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="W99" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="X99" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y99" s="13">
+        <v>20050001</v>
+      </c>
+      <c r="Z99" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA99" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB99" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC99" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AD99" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AE99" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF99" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG99" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI99" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ99" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A100" s="12">
+        <v>301215</v>
+      </c>
+      <c r="B100" s="12">
+        <v>30</v>
+      </c>
+      <c r="C100" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="D100" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="E100" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F100" s="12">
+        <v>1000011</v>
+      </c>
+      <c r="G100" s="12">
+        <v>12</v>
+      </c>
+      <c r="H100" s="12">
+        <v>1</v>
+      </c>
+      <c r="I100" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J100" s="12">
+        <v>0</v>
+      </c>
+      <c r="K100" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="L100" s="12">
+        <v>1000011</v>
+      </c>
+      <c r="M100" s="12">
+        <v>12</v>
+      </c>
+      <c r="N100" s="12">
+        <v>100</v>
+      </c>
+      <c r="O100" s="12">
+        <v>0</v>
+      </c>
+      <c r="P100" s="12">
+        <v>15</v>
+      </c>
+      <c r="Q100" s="12">
+        <v>0</v>
+      </c>
+      <c r="R100" s="12">
+        <v>36</v>
+      </c>
+      <c r="S100" s="12">
+        <v>-3000</v>
+      </c>
+      <c r="T100" s="12">
+        <v>1</v>
+      </c>
+      <c r="U100" s="12">
+        <v>0</v>
+      </c>
+      <c r="V100" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="W100" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="X100" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y100" s="13">
+        <v>20050001</v>
+      </c>
+      <c r="Z100" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB100" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC100" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AD100" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AE100" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG100" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI100" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ100" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A101" s="7">
+        <v>301301</v>
+      </c>
+      <c r="B101" s="7">
+        <v>30</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D101" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E101" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F101" s="7">
+        <v>1000102</v>
+      </c>
+      <c r="G101" s="7">
+        <v>12</v>
+      </c>
+      <c r="H101" s="7">
+        <v>1</v>
+      </c>
+      <c r="I101" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J101" s="7">
+        <v>0</v>
+      </c>
+      <c r="K101" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="L101" s="7">
+        <v>800001011</v>
+      </c>
+      <c r="M101" s="7">
+        <v>12</v>
+      </c>
+      <c r="N101" s="7">
+        <v>70</v>
+      </c>
+      <c r="O101" s="7">
+        <v>0</v>
+      </c>
+      <c r="P101" s="7">
+        <v>16</v>
+      </c>
+      <c r="Q101" s="7">
+        <v>0</v>
+      </c>
+      <c r="R101" s="7">
+        <v>18</v>
+      </c>
+      <c r="S101" s="7">
+        <v>-3000</v>
+      </c>
+      <c r="T101" s="7">
+        <v>1</v>
+      </c>
+      <c r="U101" s="7">
+        <v>0</v>
+      </c>
+      <c r="V101" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="W101" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="X101" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="Y101" s="14">
+        <v>201001011</v>
+      </c>
+      <c r="Z101" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB101" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="AC101" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AD101" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AE101" s="7">
+        <v>25010001</v>
+      </c>
+      <c r="AF101" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG101" s="4">
+        <v>10000</v>
+      </c>
+      <c r="AH101" s="4">
+        <v>10000</v>
+      </c>
+      <c r="AI101" s="4">
+        <v>50</v>
+      </c>
+      <c r="AJ101" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A102" s="7">
+        <v>301302</v>
+      </c>
+      <c r="B102" s="7">
+        <v>30</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D102" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E102" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F102" s="7">
+        <v>1000102</v>
+      </c>
+      <c r="G102" s="7">
+        <v>12</v>
+      </c>
+      <c r="H102" s="7">
+        <v>1</v>
+      </c>
+      <c r="I102" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J102" s="7">
+        <v>0</v>
+      </c>
+      <c r="K102" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="L102" s="7">
+        <v>800001021</v>
+      </c>
+      <c r="M102" s="7">
+        <v>12</v>
+      </c>
+      <c r="N102" s="7">
+        <v>200</v>
+      </c>
+      <c r="O102" s="7">
+        <v>0</v>
+      </c>
+      <c r="P102" s="7">
+        <v>30</v>
+      </c>
+      <c r="Q102" s="7">
+        <v>2</v>
+      </c>
+      <c r="R102" s="7">
+        <v>230</v>
+      </c>
+      <c r="S102" s="7">
+        <v>-3000</v>
+      </c>
+      <c r="T102" s="7">
+        <v>1</v>
+      </c>
+      <c r="U102" s="7">
+        <v>0</v>
+      </c>
+      <c r="V102" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="W102" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="X102" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="Y102" s="14">
+        <v>201002011</v>
+      </c>
+      <c r="Z102" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB102" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="AC102" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AD102" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AE102" s="7">
+        <v>25010001</v>
+      </c>
+      <c r="AF102" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG102" s="4">
+        <v>3000</v>
+      </c>
+      <c r="AH102" s="4">
+        <v>10000</v>
+      </c>
+      <c r="AI102" s="4">
+        <v>10</v>
+      </c>
+      <c r="AJ102" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A103" s="12">
+        <v>301303</v>
+      </c>
+      <c r="B103" s="12">
+        <v>30</v>
+      </c>
+      <c r="C103" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D103" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E103" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F103" s="12">
+        <v>1000102</v>
+      </c>
+      <c r="G103" s="12">
+        <v>12</v>
+      </c>
+      <c r="H103" s="12">
+        <v>1</v>
+      </c>
+      <c r="I103" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J103" s="12">
+        <v>0</v>
+      </c>
+      <c r="K103" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="L103" s="12">
+        <v>800001021</v>
+      </c>
+      <c r="M103" s="12">
+        <v>12</v>
+      </c>
+      <c r="N103" s="12">
+        <v>70</v>
+      </c>
+      <c r="O103" s="12">
+        <v>0</v>
+      </c>
+      <c r="P103" s="12">
+        <v>15</v>
+      </c>
+      <c r="Q103" s="12">
+        <v>1</v>
+      </c>
+      <c r="R103" s="12">
+        <v>300</v>
+      </c>
+      <c r="S103" s="12">
+        <v>-3000</v>
+      </c>
+      <c r="T103" s="12">
+        <v>1</v>
+      </c>
+      <c r="U103" s="12">
+        <v>250</v>
+      </c>
+      <c r="V103" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="W103" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="X103" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="Y103" s="13">
+        <v>20010001</v>
+      </c>
+      <c r="Z103" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA103" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB103" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="AC103" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AD103" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AE103" s="12">
+        <v>25010001</v>
+      </c>
+      <c r="AF103" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG103" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH103" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI103" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ103" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A104" s="7">
+        <v>301304</v>
+      </c>
+      <c r="B104" s="7">
+        <v>30</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D104" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="E104" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F104" s="7">
+        <v>1000010</v>
+      </c>
+      <c r="G104" s="7">
+        <v>12</v>
+      </c>
+      <c r="H104" s="7">
+        <v>1</v>
+      </c>
+      <c r="I104" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J104" s="7">
+        <v>0</v>
+      </c>
+      <c r="K104" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="L104" s="7">
+        <v>800001041</v>
+      </c>
+      <c r="M104" s="7">
+        <v>12</v>
+      </c>
+      <c r="N104" s="7">
+        <v>70</v>
+      </c>
+      <c r="O104" s="7">
+        <v>0</v>
+      </c>
+      <c r="P104" s="7">
+        <v>19</v>
+      </c>
+      <c r="Q104" s="7">
+        <v>0</v>
+      </c>
+      <c r="R104" s="7">
+        <v>15</v>
+      </c>
+      <c r="S104" s="7">
+        <v>-3000</v>
+      </c>
+      <c r="T104" s="7">
+        <v>1</v>
+      </c>
+      <c r="U104" s="7">
+        <v>0</v>
+      </c>
+      <c r="V104" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="W104" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="X104" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="Y104" s="14">
+        <v>201004011</v>
+      </c>
+      <c r="Z104" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA104" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB104" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="AC104" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AD104" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AE104" s="7">
+        <v>25010001</v>
+      </c>
+      <c r="AF104" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG104" s="4">
+        <v>10000</v>
+      </c>
+      <c r="AH104" s="4">
+        <v>10000</v>
+      </c>
+      <c r="AI104" s="4">
+        <v>80</v>
+      </c>
+      <c r="AJ104" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="105" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A105" s="7">
+        <v>301305</v>
+      </c>
+      <c r="B105" s="7">
+        <v>30</v>
+      </c>
+      <c r="C105" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D105" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E105" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F105" s="7">
+        <v>1000010</v>
+      </c>
+      <c r="G105" s="7">
+        <v>12</v>
+      </c>
+      <c r="H105" s="7">
+        <v>1</v>
+      </c>
+      <c r="I105" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J105" s="7">
+        <v>0</v>
+      </c>
+      <c r="K105" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="L105" s="7">
+        <v>800014011</v>
+      </c>
+      <c r="M105" s="7">
+        <v>12</v>
+      </c>
+      <c r="N105" s="7">
+        <v>125</v>
+      </c>
+      <c r="O105" s="7">
+        <v>0</v>
+      </c>
+      <c r="P105" s="7">
+        <v>18</v>
+      </c>
+      <c r="Q105" s="7">
+        <v>1</v>
+      </c>
+      <c r="R105" s="7">
+        <v>48</v>
+      </c>
+      <c r="S105" s="7">
+        <v>-3000</v>
+      </c>
+      <c r="T105" s="7">
+        <v>1</v>
+      </c>
+      <c r="U105" s="7">
+        <v>0</v>
+      </c>
+      <c r="V105" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="W105" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="X105" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="Y105" s="14">
+        <v>214001011</v>
+      </c>
+      <c r="Z105" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA105" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB105" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="AC105" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AD105" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AE105" s="7">
+        <v>25010001</v>
+      </c>
+      <c r="AF105" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG105" s="4">
+        <v>10000</v>
+      </c>
+      <c r="AH105" s="4">
+        <v>10000</v>
+      </c>
+      <c r="AI105" s="4">
+        <v>40</v>
+      </c>
+      <c r="AJ105" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A106" s="12">
+        <v>301306</v>
+      </c>
+      <c r="B106" s="12">
+        <v>30</v>
+      </c>
+      <c r="C106" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="D106" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E106" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F106" s="12">
+        <v>1000010</v>
+      </c>
+      <c r="G106" s="12">
+        <v>12</v>
+      </c>
+      <c r="H106" s="12">
+        <v>1</v>
+      </c>
+      <c r="I106" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J106" s="12">
+        <v>0</v>
+      </c>
+      <c r="K106" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="L106" s="12">
+        <v>1000010</v>
+      </c>
+      <c r="M106" s="12">
+        <v>12</v>
+      </c>
+      <c r="N106" s="12">
+        <v>100</v>
+      </c>
+      <c r="O106" s="12">
+        <v>0</v>
+      </c>
+      <c r="P106" s="12">
+        <v>15</v>
+      </c>
+      <c r="Q106" s="12">
+        <v>0</v>
+      </c>
+      <c r="R106" s="12">
+        <v>36</v>
+      </c>
+      <c r="S106" s="12">
+        <v>-3000</v>
+      </c>
+      <c r="T106" s="12">
+        <v>1</v>
+      </c>
+      <c r="U106" s="12">
+        <v>0</v>
+      </c>
+      <c r="V106" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="W106" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="X106" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y106" s="13">
+        <v>20040001</v>
+      </c>
+      <c r="Z106" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA106" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB106" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC106" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AD106" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AE106" s="12">
+        <v>25010001</v>
+      </c>
+      <c r="AF106" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG106" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH106" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI106" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ106" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A107" s="12">
+        <v>301307</v>
+      </c>
+      <c r="B107" s="12">
+        <v>30</v>
+      </c>
+      <c r="C107" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="D107" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E107" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F107" s="12">
+        <v>1000006</v>
+      </c>
+      <c r="G107" s="12">
+        <v>12</v>
+      </c>
+      <c r="H107" s="12">
+        <v>1</v>
+      </c>
+      <c r="I107" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J107" s="12">
+        <v>0</v>
+      </c>
+      <c r="K107" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="L107" s="12">
+        <v>1000006</v>
+      </c>
+      <c r="M107" s="12">
+        <v>12</v>
+      </c>
+      <c r="N107" s="12">
+        <v>100</v>
+      </c>
+      <c r="O107" s="12">
+        <v>0</v>
+      </c>
+      <c r="P107" s="12">
+        <v>15</v>
+      </c>
+      <c r="Q107" s="12">
+        <v>0</v>
+      </c>
+      <c r="R107" s="12">
+        <v>36</v>
+      </c>
+      <c r="S107" s="12">
+        <v>-3000</v>
+      </c>
+      <c r="T107" s="12">
+        <v>1</v>
+      </c>
+      <c r="U107" s="12">
+        <v>0</v>
+      </c>
+      <c r="V107" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="W107" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="X107" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y107" s="13">
+        <v>20030001</v>
+      </c>
+      <c r="Z107" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA107" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB107" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC107" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AD107" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AE107" s="12">
+        <v>25010001</v>
+      </c>
+      <c r="AF107" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG107" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH107" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI107" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ107" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A108" s="12">
+        <v>301308</v>
+      </c>
+      <c r="B108" s="12">
+        <v>30</v>
+      </c>
+      <c r="C108" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="D108" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="E108" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F108" s="12">
+        <v>1000006</v>
+      </c>
+      <c r="G108" s="12">
+        <v>12</v>
+      </c>
+      <c r="H108" s="12">
+        <v>1</v>
+      </c>
+      <c r="I108" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J108" s="12">
+        <v>0</v>
+      </c>
+      <c r="K108" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="L108" s="12">
+        <v>1000006</v>
+      </c>
+      <c r="M108" s="12">
+        <v>12</v>
+      </c>
+      <c r="N108" s="12">
+        <v>100</v>
+      </c>
+      <c r="O108" s="12">
+        <v>0</v>
+      </c>
+      <c r="P108" s="12">
+        <v>15</v>
+      </c>
+      <c r="Q108" s="12">
+        <v>0</v>
+      </c>
+      <c r="R108" s="12">
+        <v>36</v>
+      </c>
+      <c r="S108" s="12">
+        <v>-3000</v>
+      </c>
+      <c r="T108" s="12">
+        <v>1</v>
+      </c>
+      <c r="U108" s="12">
+        <v>0</v>
+      </c>
+      <c r="V108" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="W108" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="X108" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y108" s="13">
+        <v>20030001</v>
+      </c>
+      <c r="Z108" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA108" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB108" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC108" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AD108" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AE108" s="12">
+        <v>25010001</v>
+      </c>
+      <c r="AF108" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG108" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH108" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI108" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ108" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A109" s="12">
+        <v>301309</v>
+      </c>
+      <c r="B109" s="12">
+        <v>30</v>
+      </c>
+      <c r="C109" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D109" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E109" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F109" s="12">
+        <v>1000006</v>
+      </c>
+      <c r="G109" s="12">
+        <v>12</v>
+      </c>
+      <c r="H109" s="12">
+        <v>1</v>
+      </c>
+      <c r="I109" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J109" s="12">
+        <v>0</v>
+      </c>
+      <c r="K109" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="L109" s="12">
+        <v>1000006</v>
+      </c>
+      <c r="M109" s="12">
+        <v>12</v>
+      </c>
+      <c r="N109" s="12">
+        <v>100</v>
+      </c>
+      <c r="O109" s="12">
+        <v>0</v>
+      </c>
+      <c r="P109" s="12">
+        <v>15</v>
+      </c>
+      <c r="Q109" s="12">
+        <v>0</v>
+      </c>
+      <c r="R109" s="12">
+        <v>36</v>
+      </c>
+      <c r="S109" s="12">
+        <v>-3000</v>
+      </c>
+      <c r="T109" s="12">
+        <v>1</v>
+      </c>
+      <c r="U109" s="12">
+        <v>0</v>
+      </c>
+      <c r="V109" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="W109" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="X109" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y109" s="13">
+        <v>20030001</v>
+      </c>
+      <c r="Z109" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA109" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB109" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC109" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AD109" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AE109" s="12">
+        <v>25010001</v>
+      </c>
+      <c r="AF109" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG109" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH109" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI109" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ109" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A110" s="12">
+        <v>301310</v>
+      </c>
+      <c r="B110" s="12">
+        <v>30</v>
+      </c>
+      <c r="C110" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="D110" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="E110" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F110" s="12">
+        <v>1000103</v>
+      </c>
+      <c r="G110" s="12">
+        <v>12</v>
+      </c>
+      <c r="H110" s="12">
+        <v>1</v>
+      </c>
+      <c r="I110" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J110" s="12">
+        <v>0</v>
+      </c>
+      <c r="K110" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="L110" s="12">
+        <v>1000103</v>
+      </c>
+      <c r="M110" s="12">
+        <v>12</v>
+      </c>
+      <c r="N110" s="12">
+        <v>100</v>
+      </c>
+      <c r="O110" s="12">
+        <v>0</v>
+      </c>
+      <c r="P110" s="12">
+        <v>15</v>
+      </c>
+      <c r="Q110" s="12">
+        <v>0</v>
+      </c>
+      <c r="R110" s="12">
+        <v>36</v>
+      </c>
+      <c r="S110" s="12">
+        <v>-3000</v>
+      </c>
+      <c r="T110" s="12">
+        <v>1</v>
+      </c>
+      <c r="U110" s="12">
+        <v>0</v>
+      </c>
+      <c r="V110" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="W110" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="X110" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y110" s="13">
+        <v>20020001</v>
+      </c>
+      <c r="Z110" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA110" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB110" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC110" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AD110" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AE110" s="12">
+        <v>25010001</v>
+      </c>
+      <c r="AF110" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG110" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH110" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI110" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ110" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A111" s="12">
+        <v>301311</v>
+      </c>
+      <c r="B111" s="12">
+        <v>30</v>
+      </c>
+      <c r="C111" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="D111" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E111" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F111" s="12">
+        <v>1000103</v>
+      </c>
+      <c r="G111" s="12">
+        <v>12</v>
+      </c>
+      <c r="H111" s="12">
+        <v>1</v>
+      </c>
+      <c r="I111" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J111" s="12">
+        <v>0</v>
+      </c>
+      <c r="K111" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="L111" s="12">
+        <v>1000103</v>
+      </c>
+      <c r="M111" s="12">
+        <v>12</v>
+      </c>
+      <c r="N111" s="12">
+        <v>100</v>
+      </c>
+      <c r="O111" s="12">
+        <v>0</v>
+      </c>
+      <c r="P111" s="12">
+        <v>15</v>
+      </c>
+      <c r="Q111" s="12">
+        <v>0</v>
+      </c>
+      <c r="R111" s="12">
+        <v>36</v>
+      </c>
+      <c r="S111" s="12">
+        <v>-3000</v>
+      </c>
+      <c r="T111" s="12">
+        <v>1</v>
+      </c>
+      <c r="U111" s="12">
+        <v>0</v>
+      </c>
+      <c r="V111" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="W111" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="X111" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y111" s="13">
+        <v>20020001</v>
+      </c>
+      <c r="Z111" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA111" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB111" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC111" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AD111" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AE111" s="12">
+        <v>25010001</v>
+      </c>
+      <c r="AF111" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG111" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH111" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI111" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ111" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A112" s="12">
+        <v>301312</v>
+      </c>
+      <c r="B112" s="12">
+        <v>30</v>
+      </c>
+      <c r="C112" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="D112" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="E112" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F112" s="12">
+        <v>1000103</v>
+      </c>
+      <c r="G112" s="12">
+        <v>12</v>
+      </c>
+      <c r="H112" s="12">
+        <v>1</v>
+      </c>
+      <c r="I112" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J112" s="12">
+        <v>0</v>
+      </c>
+      <c r="K112" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="L112" s="12">
+        <v>1000103</v>
+      </c>
+      <c r="M112" s="12">
+        <v>12</v>
+      </c>
+      <c r="N112" s="12">
+        <v>100</v>
+      </c>
+      <c r="O112" s="12">
+        <v>0</v>
+      </c>
+      <c r="P112" s="12">
+        <v>15</v>
+      </c>
+      <c r="Q112" s="12">
+        <v>0</v>
+      </c>
+      <c r="R112" s="12">
+        <v>36</v>
+      </c>
+      <c r="S112" s="12">
+        <v>-3000</v>
+      </c>
+      <c r="T112" s="12">
+        <v>1</v>
+      </c>
+      <c r="U112" s="12">
+        <v>0</v>
+      </c>
+      <c r="V112" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="W112" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="X112" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y112" s="13">
+        <v>20020001</v>
+      </c>
+      <c r="Z112" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA112" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB112" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC112" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AD112" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AE112" s="12">
+        <v>25010001</v>
+      </c>
+      <c r="AF112" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG112" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH112" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI112" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ112" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A113" s="7">
+        <v>301313</v>
+      </c>
+      <c r="B113" s="7">
+        <v>30</v>
+      </c>
+      <c r="C113" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D113" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="E113" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F113" s="7">
+        <v>1000011</v>
+      </c>
+      <c r="G113" s="7">
+        <v>12</v>
+      </c>
+      <c r="H113" s="7">
+        <v>1</v>
+      </c>
+      <c r="I113" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J113" s="7">
+        <v>0</v>
+      </c>
+      <c r="K113" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="L113" s="7">
+        <v>800003021</v>
+      </c>
+      <c r="M113" s="7">
+        <v>12</v>
+      </c>
+      <c r="N113" s="7">
+        <v>500</v>
+      </c>
+      <c r="O113" s="7">
+        <v>0</v>
+      </c>
+      <c r="P113" s="7">
+        <v>42</v>
+      </c>
+      <c r="Q113" s="7">
+        <v>3</v>
+      </c>
+      <c r="R113" s="16">
+        <v>1496</v>
+      </c>
+      <c r="S113" s="7">
+        <v>-3000</v>
+      </c>
+      <c r="T113" s="7">
+        <v>1</v>
+      </c>
+      <c r="U113" s="7">
+        <v>30000</v>
+      </c>
+      <c r="V113" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="W113" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="X113" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="Y113" s="14">
+        <v>203002011</v>
+      </c>
+      <c r="Z113" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA113" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB113" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="AC113" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AD113" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AE113" s="7">
+        <v>25010001</v>
+      </c>
+      <c r="AF113" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG113" s="4">
+        <v>1000</v>
+      </c>
+      <c r="AH113" s="4">
+        <v>5000</v>
+      </c>
+      <c r="AI113" s="4">
+        <v>2</v>
+      </c>
+      <c r="AJ113" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A114" s="12">
+        <v>301314</v>
+      </c>
+      <c r="B114" s="12">
+        <v>30</v>
+      </c>
+      <c r="C114" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D114" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="E114" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F114" s="12">
+        <v>1000011</v>
+      </c>
+      <c r="G114" s="12">
+        <v>12</v>
+      </c>
+      <c r="H114" s="12">
+        <v>1</v>
+      </c>
+      <c r="I114" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J114" s="12">
+        <v>0</v>
+      </c>
+      <c r="K114" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="L114" s="12">
+        <v>1000011</v>
+      </c>
+      <c r="M114" s="12">
+        <v>12</v>
+      </c>
+      <c r="N114" s="12">
+        <v>100</v>
+      </c>
+      <c r="O114" s="12">
+        <v>0</v>
+      </c>
+      <c r="P114" s="12">
+        <v>15</v>
+      </c>
+      <c r="Q114" s="12">
+        <v>0</v>
+      </c>
+      <c r="R114" s="12">
+        <v>36</v>
+      </c>
+      <c r="S114" s="12">
+        <v>-3000</v>
+      </c>
+      <c r="T114" s="12">
+        <v>1</v>
+      </c>
+      <c r="U114" s="12">
+        <v>0</v>
+      </c>
+      <c r="V114" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="W114" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="X114" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y114" s="13">
+        <v>20050001</v>
+      </c>
+      <c r="Z114" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA114" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB114" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC114" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AD114" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AE114" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF114" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG114" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH114" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI114" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ114" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A115" s="12">
+        <v>301315</v>
+      </c>
+      <c r="B115" s="12">
+        <v>30</v>
+      </c>
+      <c r="C115" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="D115" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="E115" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F115" s="12">
+        <v>1000011</v>
+      </c>
+      <c r="G115" s="12">
+        <v>12</v>
+      </c>
+      <c r="H115" s="12">
+        <v>1</v>
+      </c>
+      <c r="I115" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J115" s="12">
+        <v>0</v>
+      </c>
+      <c r="K115" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="L115" s="12">
+        <v>1000011</v>
+      </c>
+      <c r="M115" s="12">
+        <v>12</v>
+      </c>
+      <c r="N115" s="12">
+        <v>100</v>
+      </c>
+      <c r="O115" s="12">
+        <v>0</v>
+      </c>
+      <c r="P115" s="12">
+        <v>15</v>
+      </c>
+      <c r="Q115" s="12">
+        <v>0</v>
+      </c>
+      <c r="R115" s="12">
+        <v>36</v>
+      </c>
+      <c r="S115" s="12">
+        <v>-3000</v>
+      </c>
+      <c r="T115" s="12">
+        <v>1</v>
+      </c>
+      <c r="U115" s="12">
+        <v>0</v>
+      </c>
+      <c r="V115" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="W115" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="X115" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y115" s="13">
+        <v>20050001</v>
+      </c>
+      <c r="Z115" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA115" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB115" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC115" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AD115" s="12">
+        <v>10000</v>
+      </c>
+      <c r="AE115" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF115" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG115" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH115" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI115" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ115" s="4">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D1F34B4-2A8E-4FF3-BD53-61F3881E7F1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D27597C-2246-4B15-AEC4-3B9FF40EDC1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1209" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="197">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -128,9 +128,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>野猪怪</t>
-  </si>
-  <si>
     <t>乌龟怪1</t>
   </si>
   <si>
@@ -187,18 +184,6 @@
     <t>寄居蟹4</t>
   </si>
   <si>
-    <t>拳头怪3</t>
-  </si>
-  <si>
-    <t>斯巴达勇士2</t>
-  </si>
-  <si>
-    <t>爆裂悍匪2</t>
-  </si>
-  <si>
-    <t>毒气猛士3</t>
-  </si>
-  <si>
     <t>蜥蜴怪1</t>
   </si>
   <si>
@@ -262,79 +247,28 @@
     <t>守卫？3</t>
   </si>
   <si>
-    <t>寄居蟹-红</t>
-  </si>
-  <si>
-    <t>寄居蟹-蓝</t>
-  </si>
-  <si>
-    <t>寄居蟹-绿</t>
-  </si>
-  <si>
-    <t>乌龟怪-红</t>
-  </si>
-  <si>
-    <t>乌龟怪-绿</t>
-  </si>
-  <si>
-    <t>乌龟怪-蓝</t>
-  </si>
-  <si>
-    <t>野狼怪-红</t>
-  </si>
-  <si>
     <t>小怪8</t>
   </si>
   <si>
-    <t>野狼怪-绿</t>
-  </si>
-  <si>
     <t>小怪9</t>
   </si>
   <si>
-    <t>野狼怪-蓝</t>
-  </si>
-  <si>
     <t>小怪10</t>
   </si>
   <si>
-    <t>青蛙怪-红</t>
-  </si>
-  <si>
     <t>小怪11</t>
   </si>
   <si>
-    <t>青蛙怪-绿</t>
-  </si>
-  <si>
     <t>小怪12</t>
   </si>
   <si>
-    <t>青蛙怪-黄</t>
-  </si>
-  <si>
     <t>小怪13</t>
   </si>
   <si>
-    <t>蜥蜴怪-紫</t>
-  </si>
-  <si>
     <t>小怪14</t>
   </si>
   <si>
-    <t>蜥蜴怪-绿</t>
-  </si>
-  <si>
     <t>小怪15</t>
-  </si>
-  <si>
-    <t>蜥蜴怪-蓝</t>
-  </si>
-  <si>
-    <t>雷霆魔头3</t>
-  </si>
-  <si>
-    <t>喷火恶龙2</t>
   </si>
   <si>
     <t>守卫8</t>
@@ -371,10 +305,6 @@
     <t>喷火恶龙</t>
   </si>
   <si>
-    <t>爆裂悍匪2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>爆裂悍匪</t>
   </si>
   <si>
@@ -443,10 +373,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>怪物类型（1-小怪 2-守关boss 3-巡逻守卫</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>speed</t>
   </si>
   <si>
@@ -560,9 +486,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>未使用</t>
-  </si>
-  <si>
     <t>受击回复动作播放速度系数（&gt;10000加速 ,&lt;10000减速</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -638,9 +561,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>客户端资源组</t>
-  </si>
-  <si>
     <t>tough_deplete</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -693,10 +613,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>僵尸精英</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>战甲斑狼</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -795,6 +711,18 @@
   </si>
   <si>
     <t>守卫11</t>
+  </si>
+  <si>
+    <t>怪物类型（1-小怪 2-守关boss 3-巡逻守卫 4-精英怪</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>僵尸等级2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>石像鬼精英</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1012,7 +940,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2">
@@ -1059,9 +987,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1373,7 +1298,9 @@
     <col min="1" max="1" width="20.125" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.625" style="4" customWidth="1"/>
     <col min="3" max="3" width="12.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="10.625" style="4" customWidth="1"/>
+    <col min="4" max="7" width="10.625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="40.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.625" style="4" customWidth="1"/>
     <col min="10" max="10" width="19.375" style="4" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.125" style="4" bestFit="1" customWidth="1"/>
     <col min="12" max="20" width="10.625" style="4" customWidth="1"/>
@@ -1443,94 +1370,94 @@
         <v>3</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="K2" s="10" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="L2" s="10" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="M2" s="10" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="N2" s="10" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="O2" s="10" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="P2" s="10" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="Q2" s="10" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="R2" s="10" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="S2" s="10" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="T2" s="10" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="U2" s="10" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="V2" s="10" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="W2" s="10" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="X2" s="10" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="Y2" s="10" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="Z2" s="10" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="AA2" s="10" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="AB2" s="10" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="AC2" s="10" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="AD2" s="10" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="AE2" s="10" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="AF2" s="10" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="AG2" s="10" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="AH2" s="10" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="AI2" s="10" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="AJ2" s="10" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:36" ht="14.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -1547,22 +1474,22 @@
         <v>5</v>
       </c>
       <c r="E3" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="11" t="s">
-        <v>34</v>
-      </c>
       <c r="G3" s="5" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>11</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>181</v>
+        <v>155</v>
       </c>
       <c r="K3" s="5" t="s">
         <v>14</v>
@@ -1571,7 +1498,7 @@
         <v>13</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="N3" s="5" t="s">
         <v>6</v>
@@ -1580,67 +1507,67 @@
         <v>20</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="R3" s="5" t="s">
         <v>19</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="T3" s="5" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="U3" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="V3" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="W3" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="X3" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y3" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z3" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA3" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="AB3" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="V3" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="W3" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="X3" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="Y3" s="5" t="s">
+      <c r="AC3" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="Z3" s="5" t="s">
+      <c r="AD3" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="AA3" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="AB3" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="AC3" s="5" t="s">
+      <c r="AE3" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="AD3" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="AE3" s="5" t="s">
+      <c r="AF3" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="AG3" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="AH3" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="AF3" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="AG3" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="AH3" s="5" t="s">
-        <v>204</v>
-      </c>
       <c r="AI3" s="4" t="s">
-        <v>206</v>
+        <v>179</v>
       </c>
       <c r="AJ3" s="4" t="s">
-        <v>207</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" spans="1:36" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -1657,31 +1584,31 @@
         <v>9</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>120</v>
+        <v>194</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>12</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>180</v>
+        <v>154</v>
       </c>
       <c r="K4" s="5" t="s">
         <v>15</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="N4" s="5" t="s">
         <v>10</v>
@@ -1690,67 +1617,67 @@
         <v>21</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>141</v>
+        <v>117</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="R4" s="5" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="S4" s="5" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="T4" s="5" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="U4" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="V4" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="W4" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="X4" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y4" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="Z4" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="AA4" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="AB4" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="V4" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="W4" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="X4" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="Y4" s="5" t="s">
+      <c r="AC4" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="AD4" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="Z4" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="AA4" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="AB4" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="AC4" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="AD4" s="5" t="s">
-        <v>154</v>
-      </c>
       <c r="AE4" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="AF4" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="AG4" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="AH4" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="AF4" s="5" t="s">
+      <c r="AI4" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="AJ4" s="4" t="s">
         <v>182</v>
-      </c>
-      <c r="AG4" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="AH4" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="AI4" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="AJ4" s="4" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.2">
@@ -1761,17 +1688,10 @@
         <v>1</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>176</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="D5" s="7"/>
+      <c r="F5" s="7"/>
       <c r="G5" s="15">
         <v>1</v>
       </c>
@@ -1793,7 +1713,7 @@
       <c r="M5" s="7">
         <v>1</v>
       </c>
-      <c r="N5" s="20">
+      <c r="N5" s="19">
         <v>1</v>
       </c>
       <c r="O5" s="7">
@@ -1809,7 +1729,7 @@
         <v>25</v>
       </c>
       <c r="S5" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T5" s="7">
         <v>1</v>
@@ -1818,13 +1738,13 @@
         <v>0</v>
       </c>
       <c r="V5" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="W5" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="X5" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="Y5" s="14">
         <v>20010001</v>
@@ -1836,7 +1756,7 @@
         <v>1</v>
       </c>
       <c r="AB5" s="4" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC5" s="7">
         <v>10000</v>
@@ -1871,17 +1791,10 @@
         <v>1</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>176</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="D6" s="7"/>
+      <c r="F6" s="7"/>
       <c r="G6" s="15">
         <v>1</v>
       </c>
@@ -1903,7 +1816,7 @@
       <c r="M6" s="7">
         <v>1</v>
       </c>
-      <c r="N6" s="20">
+      <c r="N6" s="19">
         <v>2</v>
       </c>
       <c r="O6" s="7">
@@ -1919,7 +1832,7 @@
         <v>25</v>
       </c>
       <c r="S6" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T6" s="7">
         <v>1</v>
@@ -1928,13 +1841,13 @@
         <v>0</v>
       </c>
       <c r="V6" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="W6" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="X6" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="Y6" s="14">
         <v>20010001</v>
@@ -1946,7 +1859,7 @@
         <v>1</v>
       </c>
       <c r="AB6" s="4" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC6" s="7">
         <v>10000</v>
@@ -1981,17 +1894,10 @@
         <v>1</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>176</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="D7" s="7"/>
+      <c r="F7" s="7"/>
       <c r="G7" s="15">
         <v>1</v>
       </c>
@@ -2013,7 +1919,7 @@
       <c r="M7" s="7">
         <v>1</v>
       </c>
-      <c r="N7" s="20">
+      <c r="N7" s="19">
         <v>3</v>
       </c>
       <c r="O7" s="7">
@@ -2029,7 +1935,7 @@
         <v>25</v>
       </c>
       <c r="S7" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T7" s="7">
         <v>1</v>
@@ -2038,13 +1944,13 @@
         <v>0</v>
       </c>
       <c r="V7" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="W7" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="X7" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="Y7" s="14">
         <v>20010001</v>
@@ -2056,7 +1962,7 @@
         <v>1</v>
       </c>
       <c r="AB7" s="4" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC7" s="7">
         <v>10000</v>
@@ -2091,17 +1997,10 @@
         <v>1</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>176</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="D8" s="7"/>
+      <c r="F8" s="7"/>
       <c r="G8" s="15">
         <v>1</v>
       </c>
@@ -2123,7 +2022,7 @@
       <c r="M8" s="7">
         <v>1</v>
       </c>
-      <c r="N8" s="20">
+      <c r="N8" s="19">
         <v>4</v>
       </c>
       <c r="O8" s="7">
@@ -2139,7 +2038,7 @@
         <v>25</v>
       </c>
       <c r="S8" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T8" s="7">
         <v>1</v>
@@ -2148,13 +2047,13 @@
         <v>0</v>
       </c>
       <c r="V8" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="W8" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="X8" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="Y8" s="14">
         <v>20010001</v>
@@ -2166,7 +2065,7 @@
         <v>1</v>
       </c>
       <c r="AB8" s="4" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC8" s="7">
         <v>10000</v>
@@ -2201,17 +2100,10 @@
         <v>1</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>176</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="D9" s="7"/>
+      <c r="F9" s="7"/>
       <c r="G9" s="15">
         <v>1</v>
       </c>
@@ -2233,7 +2125,7 @@
       <c r="M9" s="7">
         <v>1</v>
       </c>
-      <c r="N9" s="20">
+      <c r="N9" s="19">
         <v>4</v>
       </c>
       <c r="O9" s="7">
@@ -2249,7 +2141,7 @@
         <v>25</v>
       </c>
       <c r="S9" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T9" s="7">
         <v>1</v>
@@ -2258,13 +2150,13 @@
         <v>0</v>
       </c>
       <c r="V9" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="W9" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="X9" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="Y9" s="14">
         <v>20010001</v>
@@ -2276,7 +2168,7 @@
         <v>1</v>
       </c>
       <c r="AB9" s="4" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC9" s="7">
         <v>10000</v>
@@ -2311,17 +2203,10 @@
         <v>1</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>176</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="D10" s="7"/>
+      <c r="F10" s="7"/>
       <c r="G10" s="15">
         <v>1</v>
       </c>
@@ -2343,7 +2228,7 @@
       <c r="M10" s="7">
         <v>1</v>
       </c>
-      <c r="N10" s="20">
+      <c r="N10" s="19">
         <v>13</v>
       </c>
       <c r="O10" s="7">
@@ -2359,7 +2244,7 @@
         <v>25</v>
       </c>
       <c r="S10" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T10" s="7">
         <v>1</v>
@@ -2368,13 +2253,13 @@
         <v>0</v>
       </c>
       <c r="V10" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="W10" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="X10" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="Y10" s="14">
         <v>20010001</v>
@@ -2386,7 +2271,7 @@
         <v>1</v>
       </c>
       <c r="AB10" s="4" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC10" s="7">
         <v>10000</v>
@@ -2421,17 +2306,10 @@
         <v>1</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>176</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D11" s="7"/>
+      <c r="F11" s="7"/>
       <c r="G11" s="15">
         <v>1</v>
       </c>
@@ -2453,7 +2331,7 @@
       <c r="M11" s="7">
         <v>1</v>
       </c>
-      <c r="N11" s="20">
+      <c r="N11" s="19">
         <v>15</v>
       </c>
       <c r="O11" s="7">
@@ -2469,7 +2347,7 @@
         <v>25</v>
       </c>
       <c r="S11" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T11" s="7">
         <v>1</v>
@@ -2478,13 +2356,13 @@
         <v>0</v>
       </c>
       <c r="V11" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="W11" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="X11" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="Y11" s="14">
         <v>20010001</v>
@@ -2496,7 +2374,7 @@
         <v>1</v>
       </c>
       <c r="AB11" s="4" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC11" s="7">
         <v>10000</v>
@@ -2531,17 +2409,10 @@
         <v>1</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>176</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="D12" s="7"/>
+      <c r="F12" s="7"/>
       <c r="G12" s="15">
         <v>1</v>
       </c>
@@ -2563,7 +2434,7 @@
       <c r="M12" s="7">
         <v>1</v>
       </c>
-      <c r="N12" s="20">
+      <c r="N12" s="19">
         <v>35</v>
       </c>
       <c r="O12" s="7">
@@ -2579,7 +2450,7 @@
         <v>25</v>
       </c>
       <c r="S12" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T12" s="7">
         <v>1</v>
@@ -2588,13 +2459,13 @@
         <v>0</v>
       </c>
       <c r="V12" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="W12" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="X12" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="Y12" s="14">
         <v>20010001</v>
@@ -2606,7 +2477,7 @@
         <v>1</v>
       </c>
       <c r="AB12" s="4" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC12" s="7">
         <v>10000</v>
@@ -2641,17 +2512,10 @@
         <v>1</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>176</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="D13" s="7"/>
+      <c r="F13" s="7"/>
       <c r="G13" s="15">
         <v>1</v>
       </c>
@@ -2673,7 +2537,7 @@
       <c r="M13" s="7">
         <v>1</v>
       </c>
-      <c r="N13" s="20">
+      <c r="N13" s="19">
         <v>40</v>
       </c>
       <c r="O13" s="7">
@@ -2689,7 +2553,7 @@
         <v>25</v>
       </c>
       <c r="S13" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T13" s="7">
         <v>1</v>
@@ -2698,13 +2562,13 @@
         <v>0</v>
       </c>
       <c r="V13" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="W13" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="X13" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="Y13" s="14">
         <v>20010001</v>
@@ -2716,7 +2580,7 @@
         <v>1</v>
       </c>
       <c r="AB13" s="4" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC13" s="7">
         <v>10000</v>
@@ -2751,17 +2615,10 @@
         <v>1</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>176</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="D14" s="7"/>
+      <c r="F14" s="7"/>
       <c r="G14" s="15">
         <v>1</v>
       </c>
@@ -2783,7 +2640,7 @@
       <c r="M14" s="7">
         <v>1</v>
       </c>
-      <c r="N14" s="20">
+      <c r="N14" s="19">
         <v>90</v>
       </c>
       <c r="O14" s="7">
@@ -2799,7 +2656,7 @@
         <v>25</v>
       </c>
       <c r="S14" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T14" s="7">
         <v>1</v>
@@ -2808,13 +2665,13 @@
         <v>0</v>
       </c>
       <c r="V14" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="W14" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="X14" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="Y14" s="14">
         <v>20010001</v>
@@ -2826,7 +2683,7 @@
         <v>1</v>
       </c>
       <c r="AB14" s="4" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC14" s="7">
         <v>10000</v>
@@ -2861,17 +2718,10 @@
         <v>1</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>176</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="D15" s="7"/>
+      <c r="F15" s="7"/>
       <c r="G15" s="15">
         <v>1</v>
       </c>
@@ -2893,7 +2743,7 @@
       <c r="M15" s="7">
         <v>1</v>
       </c>
-      <c r="N15" s="20">
+      <c r="N15" s="19">
         <v>100</v>
       </c>
       <c r="O15" s="7">
@@ -2909,7 +2759,7 @@
         <v>25</v>
       </c>
       <c r="S15" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T15" s="7">
         <v>1</v>
@@ -2918,13 +2768,13 @@
         <v>0</v>
       </c>
       <c r="V15" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="W15" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="X15" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="Y15" s="14">
         <v>20010001</v>
@@ -2936,7 +2786,7 @@
         <v>1</v>
       </c>
       <c r="AB15" s="4" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC15" s="7">
         <v>10000</v>
@@ -2971,17 +2821,10 @@
         <v>1</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>176</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="D16" s="7"/>
+      <c r="F16" s="7"/>
       <c r="G16" s="15">
         <v>1</v>
       </c>
@@ -3019,7 +2862,7 @@
         <v>25</v>
       </c>
       <c r="S16" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T16" s="7">
         <v>1</v>
@@ -3028,13 +2871,13 @@
         <v>0</v>
       </c>
       <c r="V16" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="W16" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="X16" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="Y16" s="14">
         <v>20010001</v>
@@ -3046,7 +2889,7 @@
         <v>1</v>
       </c>
       <c r="AB16" s="4" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="AC16" s="7">
         <v>10000</v>
@@ -3081,17 +2924,10 @@
         <v>1</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>176</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="D17" s="7"/>
+      <c r="F17" s="7"/>
       <c r="G17" s="15">
         <v>1</v>
       </c>
@@ -3129,7 +2965,7 @@
         <v>25</v>
       </c>
       <c r="S17" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T17" s="7">
         <v>1</v>
@@ -3138,13 +2974,13 @@
         <v>0</v>
       </c>
       <c r="V17" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="W17" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="X17" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="Y17" s="14">
         <v>20010001</v>
@@ -3156,7 +2992,7 @@
         <v>1</v>
       </c>
       <c r="AB17" s="4" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="AC17" s="7">
         <v>10000</v>
@@ -3191,17 +3027,10 @@
         <v>1</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>176</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="D18" s="7"/>
+      <c r="F18" s="7"/>
       <c r="G18" s="15">
         <v>1</v>
       </c>
@@ -3239,7 +3068,7 @@
         <v>25</v>
       </c>
       <c r="S18" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T18" s="7">
         <v>1</v>
@@ -3248,13 +3077,13 @@
         <v>0</v>
       </c>
       <c r="V18" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="W18" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="X18" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="Y18" s="14">
         <v>20010001</v>
@@ -3266,7 +3095,7 @@
         <v>1</v>
       </c>
       <c r="AB18" s="4" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="AC18" s="7">
         <v>10000</v>
@@ -3301,17 +3130,10 @@
         <v>2</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>176</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="D19" s="7"/>
+      <c r="F19" s="7"/>
       <c r="G19" s="15">
         <v>2</v>
       </c>
@@ -3325,7 +3147,7 @@
         <v>0</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="L19" s="7">
         <v>800001021</v>
@@ -3333,7 +3155,7 @@
       <c r="M19" s="7">
         <v>2</v>
       </c>
-      <c r="N19" s="20">
+      <c r="N19" s="19">
         <v>240</v>
       </c>
       <c r="O19" s="7">
@@ -3349,7 +3171,7 @@
         <v>36</v>
       </c>
       <c r="S19" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T19" s="7">
         <v>1</v>
@@ -3358,13 +3180,13 @@
         <v>80</v>
       </c>
       <c r="V19" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="W19" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="X19" s="7" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="Y19" s="14">
         <v>20010001</v>
@@ -3376,7 +3198,7 @@
         <v>1</v>
       </c>
       <c r="AB19" s="4" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC19" s="7">
         <v>10000</v>
@@ -3411,17 +3233,10 @@
         <v>2</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>176</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="D20" s="7"/>
+      <c r="F20" s="7"/>
       <c r="G20" s="15">
         <v>2</v>
       </c>
@@ -3435,7 +3250,7 @@
         <v>0</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="L20" s="7">
         <v>800001021</v>
@@ -3443,7 +3258,7 @@
       <c r="M20" s="7">
         <v>2</v>
       </c>
-      <c r="N20" s="20">
+      <c r="N20" s="19">
         <v>300</v>
       </c>
       <c r="O20" s="7">
@@ -3459,7 +3274,7 @@
         <v>40</v>
       </c>
       <c r="S20" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T20" s="7">
         <v>1</v>
@@ -3468,13 +3283,13 @@
         <v>80</v>
       </c>
       <c r="V20" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="W20" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="X20" s="7" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="Y20" s="14">
         <v>20010001</v>
@@ -3486,7 +3301,7 @@
         <v>1</v>
       </c>
       <c r="AB20" s="4" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC20" s="7">
         <v>10000</v>
@@ -3521,17 +3336,10 @@
         <v>2</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>176</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="D21" s="7"/>
+      <c r="F21" s="7"/>
       <c r="G21" s="15">
         <v>2</v>
       </c>
@@ -3545,7 +3353,7 @@
         <v>0</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="L21" s="7">
         <v>800001021</v>
@@ -3553,7 +3361,7 @@
       <c r="M21" s="7">
         <v>2</v>
       </c>
-      <c r="N21" s="20">
+      <c r="N21" s="19">
         <v>700</v>
       </c>
       <c r="O21" s="7">
@@ -3569,7 +3377,7 @@
         <v>44</v>
       </c>
       <c r="S21" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T21" s="7">
         <v>1</v>
@@ -3578,13 +3386,13 @@
         <v>80</v>
       </c>
       <c r="V21" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="W21" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="X21" s="7" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="Y21" s="14">
         <v>20010001</v>
@@ -3596,7 +3404,7 @@
         <v>1</v>
       </c>
       <c r="AB21" s="4" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC21" s="7">
         <v>10000</v>
@@ -3631,17 +3439,10 @@
         <v>2</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>176</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="D22" s="7"/>
+      <c r="F22" s="7"/>
       <c r="G22" s="15">
         <v>2</v>
       </c>
@@ -3655,7 +3456,7 @@
         <v>0</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="L22" s="7">
         <v>800001021</v>
@@ -3663,7 +3464,7 @@
       <c r="M22" s="7">
         <v>2</v>
       </c>
-      <c r="N22" s="20">
+      <c r="N22" s="19">
         <v>800</v>
       </c>
       <c r="O22" s="7">
@@ -3679,7 +3480,7 @@
         <v>45</v>
       </c>
       <c r="S22" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T22" s="7">
         <v>1</v>
@@ -3688,13 +3489,13 @@
         <v>100</v>
       </c>
       <c r="V22" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="W22" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="X22" s="7" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="Y22" s="14">
         <v>20010001</v>
@@ -3706,7 +3507,7 @@
         <v>1</v>
       </c>
       <c r="AB22" s="4" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC22" s="7">
         <v>10000</v>
@@ -3741,17 +3542,10 @@
         <v>2</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>176</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="D23" s="7"/>
+      <c r="F23" s="7"/>
       <c r="G23" s="15">
         <v>2</v>
       </c>
@@ -3765,7 +3559,7 @@
         <v>0</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="L23" s="7">
         <v>800001021</v>
@@ -3773,7 +3567,7 @@
       <c r="M23" s="7">
         <v>2</v>
       </c>
-      <c r="N23" s="20">
+      <c r="N23" s="19">
         <v>1500</v>
       </c>
       <c r="O23" s="7">
@@ -3789,7 +3583,7 @@
         <v>50</v>
       </c>
       <c r="S23" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T23" s="7">
         <v>1</v>
@@ -3798,13 +3592,13 @@
         <v>100</v>
       </c>
       <c r="V23" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="W23" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="X23" s="7" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="Y23" s="14">
         <v>20010001</v>
@@ -3816,7 +3610,7 @@
         <v>1</v>
       </c>
       <c r="AB23" s="4" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC23" s="7">
         <v>10000</v>
@@ -3851,17 +3645,10 @@
         <v>2</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>176</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="D24" s="7"/>
+      <c r="F24" s="7"/>
       <c r="G24" s="15">
         <v>2</v>
       </c>
@@ -3875,7 +3662,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="L24" s="7">
         <v>800001021</v>
@@ -3883,7 +3670,7 @@
       <c r="M24" s="7">
         <v>2</v>
       </c>
-      <c r="N24" s="20">
+      <c r="N24" s="19">
         <v>3000</v>
       </c>
       <c r="O24" s="7">
@@ -3899,7 +3686,7 @@
         <v>55</v>
       </c>
       <c r="S24" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T24" s="7">
         <v>1</v>
@@ -3908,13 +3695,13 @@
         <v>100</v>
       </c>
       <c r="V24" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="W24" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="X24" s="7" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="Y24" s="14">
         <v>20010001</v>
@@ -3926,7 +3713,7 @@
         <v>1</v>
       </c>
       <c r="AB24" s="4" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC24" s="7">
         <v>10000</v>
@@ -3961,17 +3748,10 @@
         <v>2</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>176</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D25" s="7"/>
+      <c r="F25" s="7"/>
       <c r="G25" s="15">
         <v>2</v>
       </c>
@@ -3985,7 +3765,7 @@
         <v>0</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="L25" s="7">
         <v>800001021</v>
@@ -3993,7 +3773,7 @@
       <c r="M25" s="7">
         <v>2</v>
       </c>
-      <c r="N25" s="20">
+      <c r="N25" s="19">
         <v>4800</v>
       </c>
       <c r="O25" s="7">
@@ -4009,7 +3789,7 @@
         <v>160</v>
       </c>
       <c r="S25" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T25" s="7">
         <v>1</v>
@@ -4018,13 +3798,13 @@
         <v>500</v>
       </c>
       <c r="V25" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="W25" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="X25" s="7" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="Y25" s="14">
         <v>20010001</v>
@@ -4036,7 +3816,7 @@
         <v>1</v>
       </c>
       <c r="AB25" s="4" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC25" s="7">
         <v>10000</v>
@@ -4071,17 +3851,10 @@
         <v>2</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>176</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="D26" s="7"/>
+      <c r="F26" s="7"/>
       <c r="G26" s="15">
         <v>2</v>
       </c>
@@ -4103,7 +3876,7 @@
       <c r="M26" s="7">
         <v>2</v>
       </c>
-      <c r="N26" s="20">
+      <c r="N26" s="19">
         <v>8000</v>
       </c>
       <c r="O26" s="7">
@@ -4119,7 +3892,7 @@
         <v>200</v>
       </c>
       <c r="S26" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T26" s="7">
         <v>1</v>
@@ -4128,13 +3901,13 @@
         <v>500</v>
       </c>
       <c r="V26" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="W26" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="X26" s="7" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="Y26" s="14">
         <v>20010001</v>
@@ -4146,7 +3919,7 @@
         <v>1</v>
       </c>
       <c r="AB26" s="4" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC26" s="7">
         <v>10000</v>
@@ -4181,17 +3954,10 @@
         <v>2</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>176</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="D27" s="7"/>
+      <c r="F27" s="7"/>
       <c r="G27" s="15">
         <v>2</v>
       </c>
@@ -4229,7 +3995,7 @@
         <v>240</v>
       </c>
       <c r="S27" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T27" s="7">
         <v>1</v>
@@ -4238,13 +4004,13 @@
         <v>500</v>
       </c>
       <c r="V27" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="W27" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="X27" s="7" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="Y27" s="14">
         <v>20010001</v>
@@ -4256,7 +4022,7 @@
         <v>1</v>
       </c>
       <c r="AB27" s="4" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC27" s="7">
         <v>10000</v>
@@ -4291,17 +4057,10 @@
         <v>2</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>176</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="D28" s="7"/>
+      <c r="F28" s="7"/>
       <c r="G28" s="15">
         <v>2</v>
       </c>
@@ -4339,7 +4098,7 @@
         <v>720</v>
       </c>
       <c r="S28" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T28" s="7">
         <v>1</v>
@@ -4348,13 +4107,13 @@
         <v>1200</v>
       </c>
       <c r="V28" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="W28" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="X28" s="7" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="Y28" s="14">
         <v>20010001</v>
@@ -4366,7 +4125,7 @@
         <v>1</v>
       </c>
       <c r="AB28" s="4" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC28" s="7">
         <v>10000</v>
@@ -4401,17 +4160,10 @@
         <v>2</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>176</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="D29" s="7"/>
+      <c r="F29" s="7"/>
       <c r="G29" s="15">
         <v>2</v>
       </c>
@@ -4449,7 +4201,7 @@
         <v>800</v>
       </c>
       <c r="S29" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T29" s="7">
         <v>1</v>
@@ -4458,13 +4210,13 @@
         <v>1200</v>
       </c>
       <c r="V29" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="W29" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="X29" s="7" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="Y29" s="14">
         <v>20010001</v>
@@ -4476,7 +4228,7 @@
         <v>1</v>
       </c>
       <c r="AB29" s="4" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC29" s="7">
         <v>10000</v>
@@ -4511,17 +4263,10 @@
         <v>2</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F30" s="7" t="s">
-        <v>176</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="D30" s="7"/>
+      <c r="F30" s="7"/>
       <c r="G30" s="15">
         <v>2</v>
       </c>
@@ -4535,7 +4280,7 @@
         <v>0</v>
       </c>
       <c r="K30" s="7" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="L30" s="7">
         <v>800001021</v>
@@ -4559,7 +4304,7 @@
         <v>880</v>
       </c>
       <c r="S30" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T30" s="7">
         <v>1</v>
@@ -4568,13 +4313,13 @@
         <v>1200</v>
       </c>
       <c r="V30" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="W30" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="X30" s="7" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="Y30" s="14">
         <v>20010001</v>
@@ -4586,7 +4331,7 @@
         <v>1</v>
       </c>
       <c r="AB30" s="4" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC30" s="7">
         <v>10000</v>
@@ -4621,17 +4366,10 @@
         <v>2</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>176</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="D31" s="7"/>
+      <c r="F31" s="7"/>
       <c r="G31" s="15">
         <v>2</v>
       </c>
@@ -4645,7 +4383,7 @@
         <v>0</v>
       </c>
       <c r="K31" s="7" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="L31" s="7">
         <v>800001021</v>
@@ -4669,7 +4407,7 @@
         <v>25</v>
       </c>
       <c r="S31" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T31" s="7">
         <v>1</v>
@@ -4678,13 +4416,13 @@
         <v>0</v>
       </c>
       <c r="V31" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="W31" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="X31" s="7" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="Y31" s="14">
         <v>20010001</v>
@@ -4696,7 +4434,7 @@
         <v>1</v>
       </c>
       <c r="AB31" s="4" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC31" s="7">
         <v>10000</v>
@@ -4731,17 +4469,10 @@
         <v>2</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F32" s="7" t="s">
-        <v>176</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="D32" s="7"/>
+      <c r="F32" s="7"/>
       <c r="G32" s="15">
         <v>2</v>
       </c>
@@ -4755,7 +4486,7 @@
         <v>0</v>
       </c>
       <c r="K32" s="7" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="L32" s="7">
         <v>800001021</v>
@@ -4779,7 +4510,7 @@
         <v>25</v>
       </c>
       <c r="S32" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T32" s="7">
         <v>1</v>
@@ -4788,13 +4519,13 @@
         <v>0</v>
       </c>
       <c r="V32" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="W32" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="X32" s="7" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="Y32" s="14">
         <v>20010001</v>
@@ -4806,7 +4537,7 @@
         <v>1</v>
       </c>
       <c r="AB32" s="4" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC32" s="7">
         <v>10000</v>
@@ -4841,17 +4572,10 @@
         <v>1</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>176</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="D33" s="7"/>
+      <c r="F33" s="7"/>
       <c r="G33" s="15">
         <v>1</v>
       </c>
@@ -4873,7 +4597,7 @@
       <c r="M33" s="7">
         <v>1</v>
       </c>
-      <c r="N33" s="21">
+      <c r="N33" s="20">
         <v>120</v>
       </c>
       <c r="O33" s="7">
@@ -4889,7 +4613,7 @@
         <v>25</v>
       </c>
       <c r="S33" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T33" s="7">
         <v>1</v>
@@ -4898,13 +4622,13 @@
         <v>0</v>
       </c>
       <c r="V33" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="W33" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="X33" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="Y33" s="14">
         <v>20010001</v>
@@ -4916,7 +4640,7 @@
         <v>1</v>
       </c>
       <c r="AB33" s="4" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC33" s="7">
         <v>10000</v>
@@ -4951,17 +4675,10 @@
         <v>1</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>176</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="D34" s="7"/>
+      <c r="F34" s="7"/>
       <c r="G34" s="15">
         <v>1</v>
       </c>
@@ -4983,7 +4700,7 @@
       <c r="M34" s="7">
         <v>1</v>
       </c>
-      <c r="N34" s="21">
+      <c r="N34" s="20">
         <v>310</v>
       </c>
       <c r="O34" s="7">
@@ -4999,7 +4716,7 @@
         <v>25</v>
       </c>
       <c r="S34" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T34" s="7">
         <v>1</v>
@@ -5008,13 +4725,13 @@
         <v>0</v>
       </c>
       <c r="V34" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="W34" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="X34" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="Y34" s="14">
         <v>20010001</v>
@@ -5026,7 +4743,7 @@
         <v>1</v>
       </c>
       <c r="AB34" s="4" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC34" s="7">
         <v>10000</v>
@@ -5061,17 +4778,10 @@
         <v>1</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>176</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="D35" s="7"/>
+      <c r="F35" s="7"/>
       <c r="G35" s="15">
         <v>1</v>
       </c>
@@ -5093,7 +4803,7 @@
       <c r="M35" s="7">
         <v>1</v>
       </c>
-      <c r="N35" s="21">
+      <c r="N35" s="20">
         <v>700</v>
       </c>
       <c r="O35" s="7">
@@ -5109,7 +4819,7 @@
         <v>25</v>
       </c>
       <c r="S35" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T35" s="7">
         <v>1</v>
@@ -5118,13 +4828,13 @@
         <v>0</v>
       </c>
       <c r="V35" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="W35" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="X35" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="Y35" s="14">
         <v>20010001</v>
@@ -5136,7 +4846,7 @@
         <v>1</v>
       </c>
       <c r="AB35" s="4" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC35" s="7">
         <v>10000</v>
@@ -5171,17 +4881,10 @@
         <v>1</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>176</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="D36" s="7"/>
+      <c r="F36" s="7"/>
       <c r="G36" s="15">
         <v>1</v>
       </c>
@@ -5203,7 +4906,7 @@
       <c r="M36" s="7">
         <v>1</v>
       </c>
-      <c r="N36" s="21">
+      <c r="N36" s="20">
         <v>2150</v>
       </c>
       <c r="O36" s="7">
@@ -5219,7 +4922,7 @@
         <v>25</v>
       </c>
       <c r="S36" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T36" s="7">
         <v>1</v>
@@ -5228,13 +4931,13 @@
         <v>0</v>
       </c>
       <c r="V36" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="W36" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="X36" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="Y36" s="14">
         <v>20010001</v>
@@ -5246,7 +4949,7 @@
         <v>1</v>
       </c>
       <c r="AB36" s="4" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC36" s="7">
         <v>10000</v>
@@ -5281,17 +4984,10 @@
         <v>1</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>176</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="D37" s="7"/>
+      <c r="F37" s="7"/>
       <c r="G37" s="15">
         <v>1</v>
       </c>
@@ -5313,7 +5009,7 @@
       <c r="M37" s="7">
         <v>1</v>
       </c>
-      <c r="N37" s="21">
+      <c r="N37" s="20">
         <v>6000</v>
       </c>
       <c r="O37" s="7">
@@ -5329,7 +5025,7 @@
         <v>25</v>
       </c>
       <c r="S37" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T37" s="7">
         <v>1</v>
@@ -5338,13 +5034,13 @@
         <v>0</v>
       </c>
       <c r="V37" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="W37" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="X37" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="Y37" s="14">
         <v>20010001</v>
@@ -5356,7 +5052,7 @@
         <v>1</v>
       </c>
       <c r="AB37" s="4" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC37" s="7">
         <v>10000</v>
@@ -5391,17 +5087,10 @@
         <v>1</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="E38" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>176</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="D38" s="7"/>
+      <c r="F38" s="7"/>
       <c r="G38" s="15">
         <v>1</v>
       </c>
@@ -5423,7 +5112,7 @@
       <c r="M38" s="7">
         <v>1</v>
       </c>
-      <c r="N38" s="21">
+      <c r="N38" s="20">
         <v>13200</v>
       </c>
       <c r="O38" s="7">
@@ -5439,7 +5128,7 @@
         <v>25</v>
       </c>
       <c r="S38" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T38" s="7">
         <v>1</v>
@@ -5448,13 +5137,13 @@
         <v>0</v>
       </c>
       <c r="V38" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="W38" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="X38" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="Y38" s="14">
         <v>20010001</v>
@@ -5466,7 +5155,7 @@
         <v>1</v>
       </c>
       <c r="AB38" s="4" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC38" s="7">
         <v>10000</v>
@@ -5501,17 +5190,10 @@
         <v>1</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>176</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D39" s="7"/>
+      <c r="F39" s="7"/>
       <c r="G39" s="15">
         <v>1</v>
       </c>
@@ -5533,7 +5215,7 @@
       <c r="M39" s="7">
         <v>1</v>
       </c>
-      <c r="N39" s="21">
+      <c r="N39" s="20">
         <v>34700</v>
       </c>
       <c r="O39" s="7">
@@ -5549,7 +5231,7 @@
         <v>25</v>
       </c>
       <c r="S39" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T39" s="7">
         <v>1</v>
@@ -5558,13 +5240,13 @@
         <v>0</v>
       </c>
       <c r="V39" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="W39" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="X39" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="Y39" s="14">
         <v>20010001</v>
@@ -5576,7 +5258,7 @@
         <v>1</v>
       </c>
       <c r="AB39" s="4" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC39" s="7">
         <v>10000</v>
@@ -5611,17 +5293,10 @@
         <v>1</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>176</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="D40" s="7"/>
+      <c r="F40" s="7"/>
       <c r="G40" s="15">
         <v>1</v>
       </c>
@@ -5643,7 +5318,7 @@
       <c r="M40" s="7">
         <v>1</v>
       </c>
-      <c r="N40" s="21">
+      <c r="N40" s="20">
         <v>76500</v>
       </c>
       <c r="O40" s="7">
@@ -5659,7 +5334,7 @@
         <v>25</v>
       </c>
       <c r="S40" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T40" s="7">
         <v>1</v>
@@ -5668,13 +5343,13 @@
         <v>0</v>
       </c>
       <c r="V40" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="W40" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="X40" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="Y40" s="14">
         <v>20010001</v>
@@ -5686,7 +5361,7 @@
         <v>1</v>
       </c>
       <c r="AB40" s="4" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC40" s="7">
         <v>10000</v>
@@ -5721,17 +5396,10 @@
         <v>1</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>176</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="D41" s="7"/>
+      <c r="F41" s="7"/>
       <c r="G41" s="15">
         <v>1</v>
       </c>
@@ -5753,7 +5421,7 @@
       <c r="M41" s="7">
         <v>1</v>
       </c>
-      <c r="N41" s="21">
+      <c r="N41" s="20">
         <v>172000</v>
       </c>
       <c r="O41" s="7">
@@ -5769,7 +5437,7 @@
         <v>25</v>
       </c>
       <c r="S41" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T41" s="7">
         <v>1</v>
@@ -5778,13 +5446,13 @@
         <v>0</v>
       </c>
       <c r="V41" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="W41" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="X41" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="Y41" s="14">
         <v>20010001</v>
@@ -5796,7 +5464,7 @@
         <v>1</v>
       </c>
       <c r="AB41" s="4" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC41" s="7">
         <v>10000</v>
@@ -5831,17 +5499,10 @@
         <v>1</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>176</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D42" s="7"/>
+      <c r="F42" s="7"/>
       <c r="G42" s="15">
         <v>1</v>
       </c>
@@ -5879,7 +5540,7 @@
         <v>25</v>
       </c>
       <c r="S42" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T42" s="7">
         <v>1</v>
@@ -5888,13 +5549,13 @@
         <v>0</v>
       </c>
       <c r="V42" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="W42" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="X42" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="Y42" s="14">
         <v>20010001</v>
@@ -5906,7 +5567,7 @@
         <v>1</v>
       </c>
       <c r="AB42" s="4" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC42" s="7">
         <v>10000</v>
@@ -5941,17 +5602,10 @@
         <v>1</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>176</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="D43" s="7"/>
+      <c r="F43" s="7"/>
       <c r="G43" s="15">
         <v>1</v>
       </c>
@@ -5989,7 +5643,7 @@
         <v>25</v>
       </c>
       <c r="S43" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T43" s="7">
         <v>1</v>
@@ -5998,13 +5652,13 @@
         <v>0</v>
       </c>
       <c r="V43" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="W43" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="X43" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="Y43" s="14">
         <v>20010001</v>
@@ -6016,7 +5670,7 @@
         <v>1</v>
       </c>
       <c r="AB43" s="4" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC43" s="7">
         <v>10000</v>
@@ -6051,17 +5705,10 @@
         <v>1</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F44" s="7" t="s">
-        <v>176</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="D44" s="7"/>
+      <c r="F44" s="7"/>
       <c r="G44" s="15">
         <v>1</v>
       </c>
@@ -6099,7 +5746,7 @@
         <v>25</v>
       </c>
       <c r="S44" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T44" s="7">
         <v>1</v>
@@ -6108,13 +5755,13 @@
         <v>0</v>
       </c>
       <c r="V44" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="W44" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="X44" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="Y44" s="14">
         <v>20010001</v>
@@ -6126,7 +5773,7 @@
         <v>1</v>
       </c>
       <c r="AB44" s="4" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="AC44" s="7">
         <v>10000</v>
@@ -6161,17 +5808,10 @@
         <v>1</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>176</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="D45" s="7"/>
+      <c r="F45" s="7"/>
       <c r="G45" s="15">
         <v>1</v>
       </c>
@@ -6209,7 +5849,7 @@
         <v>25</v>
       </c>
       <c r="S45" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T45" s="7">
         <v>1</v>
@@ -6218,13 +5858,13 @@
         <v>0</v>
       </c>
       <c r="V45" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="W45" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="X45" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="Y45" s="14">
         <v>20010001</v>
@@ -6236,7 +5876,7 @@
         <v>1</v>
       </c>
       <c r="AB45" s="4" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="AC45" s="7">
         <v>10000</v>
@@ -6271,17 +5911,10 @@
         <v>1</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F46" s="7" t="s">
-        <v>176</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="D46" s="7"/>
+      <c r="F46" s="7"/>
       <c r="G46" s="15">
         <v>1</v>
       </c>
@@ -6319,7 +5952,7 @@
         <v>25</v>
       </c>
       <c r="S46" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T46" s="7">
         <v>1</v>
@@ -6328,13 +5961,13 @@
         <v>0</v>
       </c>
       <c r="V46" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="W46" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="X46" s="7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="Y46" s="14">
         <v>20010001</v>
@@ -6346,7 +5979,7 @@
         <v>1</v>
       </c>
       <c r="AB46" s="4" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="AC46" s="7">
         <v>10000</v>
@@ -6381,17 +6014,10 @@
         <v>12</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D47" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F47" s="7">
-        <v>1000102</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="D47" s="7"/>
+      <c r="F47" s="7"/>
       <c r="G47" s="7">
         <v>12</v>
       </c>
@@ -6405,13 +6031,13 @@
         <v>0</v>
       </c>
       <c r="K47" s="7" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="L47" s="7">
         <v>800001011</v>
       </c>
       <c r="M47" s="7">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N47" s="7">
         <v>70</v>
@@ -6429,7 +6055,7 @@
         <v>18</v>
       </c>
       <c r="S47" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T47" s="7">
         <v>1</v>
@@ -6438,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="V47" s="7" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W47" s="7" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X47" s="7" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="Y47" s="14">
         <v>201001011</v>
@@ -6456,7 +6082,7 @@
         <v>1</v>
       </c>
       <c r="AB47" s="4" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
       <c r="AC47" s="7">
         <v>10000</v>
@@ -6491,17 +6117,10 @@
         <v>12</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F48" s="7">
-        <v>1000102</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="D48" s="7"/>
+      <c r="F48" s="7"/>
       <c r="G48" s="7">
         <v>12</v>
       </c>
@@ -6515,13 +6134,13 @@
         <v>0</v>
       </c>
       <c r="K48" s="7" t="s">
-        <v>185</v>
+        <v>159</v>
       </c>
       <c r="L48" s="7">
         <v>800001021</v>
       </c>
       <c r="M48" s="7">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N48" s="7">
         <v>200</v>
@@ -6539,7 +6158,7 @@
         <v>230</v>
       </c>
       <c r="S48" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T48" s="7">
         <v>1</v>
@@ -6548,13 +6167,13 @@
         <v>0</v>
       </c>
       <c r="V48" s="7" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W48" s="7" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X48" s="7" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="Y48" s="14">
         <v>201002011</v>
@@ -6566,7 +6185,7 @@
         <v>1</v>
       </c>
       <c r="AB48" s="4" t="s">
-        <v>197</v>
+        <v>170</v>
       </c>
       <c r="AC48" s="7">
         <v>10000</v>
@@ -6601,17 +6220,11 @@
         <v>12</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="D49" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="E49" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F49" s="12">
-        <v>1000102</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="D49" s="12"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="12"/>
       <c r="G49" s="12">
         <v>12</v>
       </c>
@@ -6625,13 +6238,13 @@
         <v>0</v>
       </c>
       <c r="K49" s="12" t="s">
-        <v>186</v>
+        <v>160</v>
       </c>
       <c r="L49" s="12">
         <v>800001021</v>
       </c>
       <c r="M49" s="12">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N49" s="12">
         <v>70</v>
@@ -6649,7 +6262,7 @@
         <v>300</v>
       </c>
       <c r="S49" s="12">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T49" s="12">
         <v>1</v>
@@ -6658,13 +6271,13 @@
         <v>250</v>
       </c>
       <c r="V49" s="12" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W49" s="12" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X49" s="12" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="Y49" s="13">
         <v>20010001</v>
@@ -6676,7 +6289,7 @@
         <v>1</v>
       </c>
       <c r="AB49" s="6" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
       <c r="AC49" s="12">
         <v>10000</v>
@@ -6711,17 +6324,10 @@
         <v>12</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F50" s="7">
-        <v>1000010</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="D50" s="7"/>
+      <c r="F50" s="7"/>
       <c r="G50" s="7">
         <v>12</v>
       </c>
@@ -6735,13 +6341,13 @@
         <v>0</v>
       </c>
       <c r="K50" s="7" t="s">
-        <v>187</v>
+        <v>161</v>
       </c>
       <c r="L50" s="7">
         <v>800001041</v>
       </c>
       <c r="M50" s="7">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N50" s="7">
         <v>70</v>
@@ -6759,7 +6365,7 @@
         <v>15</v>
       </c>
       <c r="S50" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T50" s="7">
         <v>1</v>
@@ -6768,13 +6374,13 @@
         <v>0</v>
       </c>
       <c r="V50" s="7" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W50" s="7" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X50" s="7" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="Y50" s="14">
         <v>201004011</v>
@@ -6786,7 +6392,7 @@
         <v>1</v>
       </c>
       <c r="AB50" s="4" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
       <c r="AC50" s="7">
         <v>10000</v>
@@ -6821,17 +6427,10 @@
         <v>12</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F51" s="7">
-        <v>1000010</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="D51" s="7"/>
+      <c r="F51" s="7"/>
       <c r="G51" s="7">
         <v>12</v>
       </c>
@@ -6845,13 +6444,13 @@
         <v>0</v>
       </c>
       <c r="K51" s="7" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="L51" s="7">
         <v>800014011</v>
       </c>
       <c r="M51" s="7">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N51" s="7">
         <v>125</v>
@@ -6869,7 +6468,7 @@
         <v>48</v>
       </c>
       <c r="S51" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T51" s="7">
         <v>1</v>
@@ -6878,13 +6477,13 @@
         <v>0</v>
       </c>
       <c r="V51" s="7" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W51" s="7" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X51" s="7" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="Y51" s="14">
         <v>214001011</v>
@@ -6896,7 +6495,7 @@
         <v>1</v>
       </c>
       <c r="AB51" s="4" t="s">
-        <v>198</v>
+        <v>171</v>
       </c>
       <c r="AC51" s="7">
         <v>10000</v>
@@ -6931,17 +6530,11 @@
         <v>12</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="D52" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F52" s="12">
-        <v>1000010</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="D52" s="12"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="12"/>
       <c r="G52" s="12">
         <v>12</v>
       </c>
@@ -6955,13 +6548,13 @@
         <v>0</v>
       </c>
       <c r="K52" s="12" t="s">
-        <v>192</v>
+        <v>165</v>
       </c>
       <c r="L52" s="12">
         <v>1000010</v>
       </c>
       <c r="M52" s="12">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N52" s="12">
         <v>100</v>
@@ -6979,7 +6572,7 @@
         <v>36</v>
       </c>
       <c r="S52" s="12">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T52" s="12">
         <v>1</v>
@@ -6988,13 +6581,13 @@
         <v>0</v>
       </c>
       <c r="V52" s="12" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W52" s="12" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X52" s="12" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="Y52" s="13">
         <v>20040001</v>
@@ -7006,7 +6599,7 @@
         <v>1</v>
       </c>
       <c r="AB52" s="6" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC52" s="12">
         <v>10000</v>
@@ -7041,17 +6634,11 @@
         <v>12</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="D53" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="E53" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F53" s="12">
-        <v>1000006</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="D53" s="12"/>
+      <c r="E53" s="6"/>
+      <c r="F53" s="12"/>
       <c r="G53" s="12">
         <v>12</v>
       </c>
@@ -7065,13 +6652,13 @@
         <v>0</v>
       </c>
       <c r="K53" s="12" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="L53" s="12">
         <v>1000006</v>
       </c>
       <c r="M53" s="12">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N53" s="12">
         <v>100</v>
@@ -7089,7 +6676,7 @@
         <v>36</v>
       </c>
       <c r="S53" s="12">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T53" s="12">
         <v>1</v>
@@ -7098,13 +6685,13 @@
         <v>0</v>
       </c>
       <c r="V53" s="12" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W53" s="12" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X53" s="12" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="Y53" s="13">
         <v>20030001</v>
@@ -7116,7 +6703,7 @@
         <v>1</v>
       </c>
       <c r="AB53" s="6" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC53" s="12">
         <v>10000</v>
@@ -7151,17 +6738,11 @@
         <v>12</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="D54" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="E54" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F54" s="12">
-        <v>1000006</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="D54" s="12"/>
+      <c r="E54" s="6"/>
+      <c r="F54" s="12"/>
       <c r="G54" s="12">
         <v>12</v>
       </c>
@@ -7175,13 +6756,13 @@
         <v>0</v>
       </c>
       <c r="K54" s="12" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="L54" s="12">
         <v>1000006</v>
       </c>
       <c r="M54" s="12">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N54" s="12">
         <v>100</v>
@@ -7199,7 +6780,7 @@
         <v>36</v>
       </c>
       <c r="S54" s="12">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T54" s="12">
         <v>1</v>
@@ -7208,13 +6789,13 @@
         <v>0</v>
       </c>
       <c r="V54" s="12" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W54" s="12" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X54" s="12" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="Y54" s="13">
         <v>20030001</v>
@@ -7226,7 +6807,7 @@
         <v>1</v>
       </c>
       <c r="AB54" s="6" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC54" s="12">
         <v>10000</v>
@@ -7261,17 +6842,11 @@
         <v>12</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="D55" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E55" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F55" s="12">
-        <v>1000006</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="D55" s="12"/>
+      <c r="E55" s="6"/>
+      <c r="F55" s="12"/>
       <c r="G55" s="12">
         <v>12</v>
       </c>
@@ -7285,13 +6860,13 @@
         <v>0</v>
       </c>
       <c r="K55" s="12" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="L55" s="12">
         <v>1000006</v>
       </c>
       <c r="M55" s="12">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N55" s="12">
         <v>100</v>
@@ -7309,7 +6884,7 @@
         <v>36</v>
       </c>
       <c r="S55" s="12">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T55" s="12">
         <v>1</v>
@@ -7318,13 +6893,13 @@
         <v>0</v>
       </c>
       <c r="V55" s="12" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W55" s="12" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X55" s="12" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="Y55" s="13">
         <v>20030001</v>
@@ -7336,7 +6911,7 @@
         <v>1</v>
       </c>
       <c r="AB55" s="6" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC55" s="12">
         <v>10000</v>
@@ -7371,17 +6946,11 @@
         <v>12</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="D56" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="E56" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F56" s="12">
-        <v>1000103</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="D56" s="12"/>
+      <c r="E56" s="6"/>
+      <c r="F56" s="12"/>
       <c r="G56" s="12">
         <v>12</v>
       </c>
@@ -7395,13 +6964,13 @@
         <v>0</v>
       </c>
       <c r="K56" s="12" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="L56" s="12">
         <v>1000103</v>
       </c>
       <c r="M56" s="12">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N56" s="12">
         <v>100</v>
@@ -7419,7 +6988,7 @@
         <v>36</v>
       </c>
       <c r="S56" s="12">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T56" s="12">
         <v>1</v>
@@ -7428,13 +6997,13 @@
         <v>0</v>
       </c>
       <c r="V56" s="12" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W56" s="12" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X56" s="12" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="Y56" s="13">
         <v>20020001</v>
@@ -7446,7 +7015,7 @@
         <v>1</v>
       </c>
       <c r="AB56" s="6" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC56" s="12">
         <v>10000</v>
@@ -7481,17 +7050,11 @@
         <v>12</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="D57" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="E57" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F57" s="12">
-        <v>1000103</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="D57" s="12"/>
+      <c r="E57" s="6"/>
+      <c r="F57" s="12"/>
       <c r="G57" s="12">
         <v>12</v>
       </c>
@@ -7505,13 +7068,13 @@
         <v>0</v>
       </c>
       <c r="K57" s="12" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="L57" s="12">
         <v>1000103</v>
       </c>
       <c r="M57" s="12">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N57" s="12">
         <v>100</v>
@@ -7529,7 +7092,7 @@
         <v>36</v>
       </c>
       <c r="S57" s="12">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T57" s="12">
         <v>1</v>
@@ -7538,13 +7101,13 @@
         <v>0</v>
       </c>
       <c r="V57" s="12" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W57" s="12" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X57" s="12" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="Y57" s="13">
         <v>20020001</v>
@@ -7556,7 +7119,7 @@
         <v>1</v>
       </c>
       <c r="AB57" s="6" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC57" s="12">
         <v>10000</v>
@@ -7591,17 +7154,11 @@
         <v>12</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="D58" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="E58" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F58" s="12">
-        <v>1000103</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="D58" s="12"/>
+      <c r="E58" s="6"/>
+      <c r="F58" s="12"/>
       <c r="G58" s="12">
         <v>12</v>
       </c>
@@ -7615,13 +7172,13 @@
         <v>0</v>
       </c>
       <c r="K58" s="12" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="L58" s="12">
         <v>1000103</v>
       </c>
       <c r="M58" s="12">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N58" s="12">
         <v>100</v>
@@ -7639,7 +7196,7 @@
         <v>36</v>
       </c>
       <c r="S58" s="12">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T58" s="12">
         <v>1</v>
@@ -7648,13 +7205,13 @@
         <v>0</v>
       </c>
       <c r="V58" s="12" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W58" s="12" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X58" s="12" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="Y58" s="13">
         <v>20020001</v>
@@ -7666,7 +7223,7 @@
         <v>1</v>
       </c>
       <c r="AB58" s="6" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC58" s="12">
         <v>10000</v>
@@ -7701,22 +7258,15 @@
         <v>12</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="E59" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F59" s="7">
-        <v>1000011</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="D59" s="7"/>
+      <c r="F59" s="7"/>
       <c r="G59" s="7">
         <v>12</v>
       </c>
       <c r="H59" s="7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I59" s="7" t="s">
         <v>18</v>
@@ -7725,13 +7275,13 @@
         <v>0</v>
       </c>
       <c r="K59" s="7" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="L59" s="7">
         <v>800003021</v>
       </c>
       <c r="M59" s="7">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N59" s="7">
         <v>500</v>
@@ -7749,7 +7299,7 @@
         <v>1496</v>
       </c>
       <c r="S59" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T59" s="7">
         <v>1</v>
@@ -7758,13 +7308,13 @@
         <v>30000</v>
       </c>
       <c r="V59" s="7" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W59" s="7" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X59" s="7" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="Y59" s="14">
         <v>203002011</v>
@@ -7776,7 +7326,7 @@
         <v>1</v>
       </c>
       <c r="AB59" s="4" t="s">
-        <v>199</v>
+        <v>172</v>
       </c>
       <c r="AC59" s="7">
         <v>10000</v>
@@ -7811,17 +7361,11 @@
         <v>12</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D60" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="E60" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F60" s="12">
-        <v>1000011</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="D60" s="12"/>
+      <c r="E60" s="6"/>
+      <c r="F60" s="12"/>
       <c r="G60" s="12">
         <v>12</v>
       </c>
@@ -7835,13 +7379,13 @@
         <v>0</v>
       </c>
       <c r="K60" s="12" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="L60" s="12">
         <v>1000011</v>
       </c>
       <c r="M60" s="12">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N60" s="12">
         <v>100</v>
@@ -7859,7 +7403,7 @@
         <v>36</v>
       </c>
       <c r="S60" s="12">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T60" s="12">
         <v>1</v>
@@ -7868,13 +7412,13 @@
         <v>0</v>
       </c>
       <c r="V60" s="12" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W60" s="12" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X60" s="12" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="Y60" s="13">
         <v>20050001</v>
@@ -7886,7 +7430,7 @@
         <v>1</v>
       </c>
       <c r="AB60" s="6" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC60" s="12">
         <v>10000</v>
@@ -7921,17 +7465,11 @@
         <v>12</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="D61" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="E61" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F61" s="12">
-        <v>1000011</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="D61" s="12"/>
+      <c r="E61" s="6"/>
+      <c r="F61" s="12"/>
       <c r="G61" s="12">
         <v>12</v>
       </c>
@@ -7945,13 +7483,13 @@
         <v>0</v>
       </c>
       <c r="K61" s="12" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="L61" s="12">
         <v>1000011</v>
       </c>
       <c r="M61" s="12">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N61" s="12">
         <v>100</v>
@@ -7969,7 +7507,7 @@
         <v>36</v>
       </c>
       <c r="S61" s="12">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T61" s="12">
         <v>1</v>
@@ -7978,13 +7516,13 @@
         <v>0</v>
       </c>
       <c r="V61" s="12" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W61" s="12" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X61" s="12" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="Y61" s="13">
         <v>20050001</v>
@@ -7996,7 +7534,7 @@
         <v>1</v>
       </c>
       <c r="AB61" s="6" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC61" s="12">
         <v>10000</v>
@@ -8031,15 +7569,10 @@
         <v>1</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>193</v>
+        <v>166</v>
       </c>
       <c r="D62" s="7"/>
-      <c r="E62" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F62" s="7">
-        <v>1000010</v>
-      </c>
+      <c r="F62" s="7"/>
       <c r="G62" s="7">
         <v>1</v>
       </c>
@@ -8053,7 +7586,7 @@
         <v>0</v>
       </c>
       <c r="K62" s="7" t="s">
-        <v>187</v>
+        <v>161</v>
       </c>
       <c r="L62" s="7">
         <v>800001041</v>
@@ -8077,7 +7610,7 @@
         <v>10000</v>
       </c>
       <c r="S62" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T62" s="7">
         <v>1</v>
@@ -8086,13 +7619,13 @@
         <v>100</v>
       </c>
       <c r="V62" s="7" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W62" s="7" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X62" s="7" t="s">
-        <v>189</v>
+        <v>163</v>
       </c>
       <c r="Y62" s="14">
         <v>201004011</v>
@@ -8104,7 +7637,7 @@
         <v>1</v>
       </c>
       <c r="AB62" s="4" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC62" s="7">
         <v>10000</v>
@@ -8139,15 +7672,10 @@
         <v>1</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>194</v>
+        <v>167</v>
       </c>
       <c r="D63" s="7"/>
-      <c r="E63" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F63" s="7">
-        <v>1000102</v>
-      </c>
+      <c r="F63" s="7"/>
       <c r="G63" s="7">
         <v>1</v>
       </c>
@@ -8161,7 +7689,7 @@
         <v>0</v>
       </c>
       <c r="K63" s="7" t="s">
-        <v>185</v>
+        <v>159</v>
       </c>
       <c r="L63" s="7">
         <v>800001021</v>
@@ -8185,7 +7713,7 @@
         <v>10000</v>
       </c>
       <c r="S63" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T63" s="7">
         <v>1</v>
@@ -8194,13 +7722,13 @@
         <v>100</v>
       </c>
       <c r="V63" s="7" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W63" s="7" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X63" s="7" t="s">
-        <v>189</v>
+        <v>163</v>
       </c>
       <c r="Y63" s="14">
         <v>201002011</v>
@@ -8212,7 +7740,7 @@
         <v>1</v>
       </c>
       <c r="AB63" s="4" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC63" s="7">
         <v>10000</v>
@@ -8247,15 +7775,10 @@
         <v>1</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>203</v>
+        <v>176</v>
       </c>
       <c r="D64" s="7"/>
-      <c r="E64" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F64" s="7">
-        <v>1000102</v>
-      </c>
+      <c r="F64" s="7"/>
       <c r="G64" s="7">
         <v>1</v>
       </c>
@@ -8269,7 +7792,7 @@
         <v>0</v>
       </c>
       <c r="K64" s="7" t="s">
-        <v>187</v>
+        <v>161</v>
       </c>
       <c r="L64" s="7">
         <v>800001041</v>
@@ -8293,7 +7816,7 @@
         <v>10</v>
       </c>
       <c r="S64" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T64" s="7">
         <v>1</v>
@@ -8302,13 +7825,13 @@
         <v>100</v>
       </c>
       <c r="V64" s="7" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W64" s="7" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X64" s="7" t="s">
-        <v>189</v>
+        <v>163</v>
       </c>
       <c r="Y64" s="14">
         <v>201002011</v>
@@ -8320,7 +7843,7 @@
         <v>1</v>
       </c>
       <c r="AB64" s="4" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC64" s="7">
         <v>10000</v>
@@ -8355,15 +7878,10 @@
         <v>1</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>202</v>
+        <v>175</v>
       </c>
       <c r="D65" s="7"/>
-      <c r="E65" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F65" s="7">
-        <v>1000102</v>
-      </c>
+      <c r="F65" s="7"/>
       <c r="G65" s="7">
         <v>1</v>
       </c>
@@ -8377,7 +7895,7 @@
         <v>0</v>
       </c>
       <c r="K65" s="7" t="s">
-        <v>185</v>
+        <v>159</v>
       </c>
       <c r="L65" s="7">
         <v>800001021</v>
@@ -8401,7 +7919,7 @@
         <v>10</v>
       </c>
       <c r="S65" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T65" s="7">
         <v>1</v>
@@ -8410,13 +7928,13 @@
         <v>100</v>
       </c>
       <c r="V65" s="7" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W65" s="7" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X65" s="7" t="s">
-        <v>189</v>
+        <v>163</v>
       </c>
       <c r="Y65" s="14">
         <v>201002011</v>
@@ -8428,7 +7946,7 @@
         <v>1</v>
       </c>
       <c r="AB65" s="4" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC65" s="7">
         <v>10000</v>
@@ -8463,37 +7981,31 @@
         <v>21</v>
       </c>
       <c r="C66" s="17" t="s">
-        <v>210</v>
-      </c>
-      <c r="D66" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="E66" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="F66" s="17">
-        <v>1000102</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="D66" s="17"/>
+      <c r="E66" s="17"/>
+      <c r="F66" s="17"/>
       <c r="G66" s="17">
         <v>12</v>
       </c>
-      <c r="H66" s="17">
-        <v>1</v>
-      </c>
-      <c r="I66" s="18">
-        <v>0</v>
+      <c r="H66" s="7">
+        <v>1</v>
+      </c>
+      <c r="I66" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="J66" s="17">
         <v>0</v>
       </c>
       <c r="K66" s="17" t="s">
-        <v>211</v>
+        <v>184</v>
       </c>
       <c r="L66" s="17">
         <v>800001011</v>
       </c>
       <c r="M66" s="17">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N66" s="17">
         <v>70</v>
@@ -8511,7 +8023,7 @@
         <v>300</v>
       </c>
       <c r="S66" s="17">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T66" s="17">
         <v>1</v>
@@ -8520,25 +8032,25 @@
         <v>0</v>
       </c>
       <c r="V66" s="17" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W66" s="17" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X66" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="Y66" s="19">
+        <v>174</v>
+      </c>
+      <c r="Y66" s="18">
         <v>201001011</v>
       </c>
-      <c r="Z66" s="19">
+      <c r="Z66" s="18">
         <v>0</v>
       </c>
       <c r="AA66" s="17">
         <v>1</v>
       </c>
       <c r="AB66" s="17" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
       <c r="AC66" s="17">
         <v>10000</v>
@@ -8573,37 +8085,31 @@
         <v>21</v>
       </c>
       <c r="C67" s="17" t="s">
-        <v>212</v>
-      </c>
-      <c r="D67" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="E67" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="F67" s="17">
-        <v>1000102</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="D67" s="17"/>
+      <c r="E67" s="17"/>
+      <c r="F67" s="17"/>
       <c r="G67" s="17">
         <v>12</v>
       </c>
-      <c r="H67" s="17">
-        <v>1</v>
-      </c>
-      <c r="I67" s="18">
-        <v>0</v>
+      <c r="H67" s="7">
+        <v>1</v>
+      </c>
+      <c r="I67" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="J67" s="17">
         <v>0</v>
       </c>
       <c r="K67" s="17" t="s">
-        <v>185</v>
+        <v>159</v>
       </c>
       <c r="L67" s="17">
         <v>800001021</v>
       </c>
       <c r="M67" s="17">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N67" s="17">
         <v>200</v>
@@ -8621,7 +8127,7 @@
         <v>300</v>
       </c>
       <c r="S67" s="17">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T67" s="17">
         <v>1</v>
@@ -8630,25 +8136,25 @@
         <v>250</v>
       </c>
       <c r="V67" s="17" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W67" s="17" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X67" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="Y67" s="19">
+        <v>174</v>
+      </c>
+      <c r="Y67" s="18">
         <v>201002011</v>
       </c>
-      <c r="Z67" s="19">
+      <c r="Z67" s="18">
         <v>0</v>
       </c>
       <c r="AA67" s="17">
         <v>1</v>
       </c>
       <c r="AB67" s="17" t="s">
-        <v>197</v>
+        <v>170</v>
       </c>
       <c r="AC67" s="17">
         <v>10000</v>
@@ -8683,37 +8189,31 @@
         <v>21</v>
       </c>
       <c r="C68" s="17" t="s">
-        <v>213</v>
-      </c>
-      <c r="D68" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="E68" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="F68" s="17">
-        <v>1000010</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="D68" s="17"/>
+      <c r="E68" s="17"/>
+      <c r="F68" s="17"/>
       <c r="G68" s="17">
         <v>12</v>
       </c>
-      <c r="H68" s="17">
-        <v>1</v>
-      </c>
-      <c r="I68" s="18">
-        <v>0</v>
+      <c r="H68" s="7">
+        <v>1</v>
+      </c>
+      <c r="I68" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="J68" s="17">
         <v>0</v>
       </c>
       <c r="K68" s="17" t="s">
-        <v>214</v>
+        <v>187</v>
       </c>
       <c r="L68" s="17">
         <v>800001041</v>
       </c>
       <c r="M68" s="17">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N68" s="17">
         <v>70</v>
@@ -8731,7 +8231,7 @@
         <v>300</v>
       </c>
       <c r="S68" s="17">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T68" s="17">
         <v>1</v>
@@ -8740,25 +8240,25 @@
         <v>0</v>
       </c>
       <c r="V68" s="17" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W68" s="17" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X68" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="Y68" s="19">
+        <v>174</v>
+      </c>
+      <c r="Y68" s="18">
         <v>201004011</v>
       </c>
-      <c r="Z68" s="19">
+      <c r="Z68" s="18">
         <v>0</v>
       </c>
       <c r="AA68" s="17">
         <v>1</v>
       </c>
       <c r="AB68" s="17" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
       <c r="AC68" s="17">
         <v>10000</v>
@@ -8793,37 +8293,31 @@
         <v>21</v>
       </c>
       <c r="C69" s="17" t="s">
-        <v>215</v>
-      </c>
-      <c r="D69" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="E69" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="F69" s="17">
-        <v>1000010</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="D69" s="17"/>
+      <c r="E69" s="17"/>
+      <c r="F69" s="17"/>
       <c r="G69" s="17">
         <v>12</v>
       </c>
-      <c r="H69" s="17">
-        <v>1</v>
-      </c>
-      <c r="I69" s="18">
-        <v>0</v>
+      <c r="H69" s="7">
+        <v>1</v>
+      </c>
+      <c r="I69" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="J69" s="17">
         <v>0</v>
       </c>
       <c r="K69" s="17" t="s">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="L69" s="17">
         <v>800014011</v>
       </c>
       <c r="M69" s="17">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N69" s="17">
         <v>125</v>
@@ -8841,7 +8335,7 @@
         <v>300</v>
       </c>
       <c r="S69" s="17">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T69" s="17">
         <v>1</v>
@@ -8850,25 +8344,25 @@
         <v>0</v>
       </c>
       <c r="V69" s="17" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W69" s="17" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X69" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="Y69" s="19">
+        <v>174</v>
+      </c>
+      <c r="Y69" s="18">
         <v>214001011</v>
       </c>
-      <c r="Z69" s="19">
+      <c r="Z69" s="18">
         <v>0</v>
       </c>
       <c r="AA69" s="17">
         <v>1</v>
       </c>
       <c r="AB69" s="17" t="s">
-        <v>198</v>
+        <v>171</v>
       </c>
       <c r="AC69" s="17">
         <v>10000</v>
@@ -8903,37 +8397,31 @@
         <v>21</v>
       </c>
       <c r="C70" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="D70" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="E70" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="F70" s="17">
-        <v>1000011</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="D70" s="17"/>
+      <c r="E70" s="17"/>
+      <c r="F70" s="17"/>
       <c r="G70" s="17">
         <v>12</v>
       </c>
-      <c r="H70" s="17">
-        <v>1</v>
-      </c>
-      <c r="I70" s="18">
-        <v>0</v>
+      <c r="H70" s="7">
+        <v>1</v>
+      </c>
+      <c r="I70" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="J70" s="17">
         <v>0</v>
       </c>
       <c r="K70" s="17" t="s">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="L70" s="17">
         <v>800003021</v>
       </c>
       <c r="M70" s="17">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N70" s="17">
         <v>500</v>
@@ -8951,7 +8439,7 @@
         <v>1760</v>
       </c>
       <c r="S70" s="17">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T70" s="17">
         <v>1</v>
@@ -8960,25 +8448,25 @@
         <v>30000</v>
       </c>
       <c r="V70" s="17" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W70" s="17" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X70" s="17" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y70" s="19">
+        <v>173</v>
+      </c>
+      <c r="Y70" s="18">
         <v>203002011</v>
       </c>
-      <c r="Z70" s="19">
+      <c r="Z70" s="18">
         <v>0</v>
       </c>
       <c r="AA70" s="17">
         <v>1</v>
       </c>
       <c r="AB70" s="17" t="s">
-        <v>199</v>
+        <v>172</v>
       </c>
       <c r="AC70" s="17">
         <v>10000</v>
@@ -9013,17 +8501,10 @@
         <v>30</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D71" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E71" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F71" s="7">
-        <v>1000102</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="D71" s="7"/>
+      <c r="F71" s="7"/>
       <c r="G71" s="7">
         <v>12</v>
       </c>
@@ -9037,13 +8518,13 @@
         <v>0</v>
       </c>
       <c r="K71" s="7" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="L71" s="7">
         <v>800001011</v>
       </c>
       <c r="M71" s="7">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N71" s="7">
         <v>70</v>
@@ -9061,7 +8542,7 @@
         <v>18</v>
       </c>
       <c r="S71" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T71" s="7">
         <v>1</v>
@@ -9070,13 +8551,13 @@
         <v>0</v>
       </c>
       <c r="V71" s="7" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W71" s="7" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X71" s="7" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="Y71" s="14">
         <v>201001011</v>
@@ -9088,7 +8569,7 @@
         <v>1</v>
       </c>
       <c r="AB71" s="4" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
       <c r="AC71" s="7">
         <v>10000</v>
@@ -9123,17 +8604,10 @@
         <v>30</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D72" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="E72" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F72" s="7">
-        <v>1000102</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="D72" s="7"/>
+      <c r="F72" s="7"/>
       <c r="G72" s="7">
         <v>12</v>
       </c>
@@ -9147,13 +8621,13 @@
         <v>0</v>
       </c>
       <c r="K72" s="7" t="s">
-        <v>185</v>
+        <v>159</v>
       </c>
       <c r="L72" s="7">
         <v>800001021</v>
       </c>
       <c r="M72" s="7">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N72" s="7">
         <v>200</v>
@@ -9171,7 +8645,7 @@
         <v>230</v>
       </c>
       <c r="S72" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T72" s="7">
         <v>1</v>
@@ -9180,13 +8654,13 @@
         <v>0</v>
       </c>
       <c r="V72" s="7" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W72" s="7" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X72" s="7" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="Y72" s="14">
         <v>201002011</v>
@@ -9198,7 +8672,7 @@
         <v>1</v>
       </c>
       <c r="AB72" s="4" t="s">
-        <v>197</v>
+        <v>170</v>
       </c>
       <c r="AC72" s="7">
         <v>10000</v>
@@ -9233,17 +8707,11 @@
         <v>30</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="D73" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="E73" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F73" s="12">
-        <v>1000102</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="D73" s="12"/>
+      <c r="E73" s="6"/>
+      <c r="F73" s="12"/>
       <c r="G73" s="12">
         <v>12</v>
       </c>
@@ -9257,13 +8725,13 @@
         <v>0</v>
       </c>
       <c r="K73" s="12" t="s">
-        <v>186</v>
+        <v>160</v>
       </c>
       <c r="L73" s="12">
         <v>800001021</v>
       </c>
       <c r="M73" s="12">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N73" s="12">
         <v>70</v>
@@ -9281,7 +8749,7 @@
         <v>300</v>
       </c>
       <c r="S73" s="12">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T73" s="12">
         <v>1</v>
@@ -9290,13 +8758,13 @@
         <v>250</v>
       </c>
       <c r="V73" s="12" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W73" s="12" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X73" s="12" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="Y73" s="13">
         <v>20010001</v>
@@ -9308,7 +8776,7 @@
         <v>1</v>
       </c>
       <c r="AB73" s="6" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
       <c r="AC73" s="12">
         <v>10000</v>
@@ -9343,17 +8811,10 @@
         <v>30</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D74" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="E74" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F74" s="7">
-        <v>1000010</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="D74" s="7"/>
+      <c r="F74" s="7"/>
       <c r="G74" s="7">
         <v>12</v>
       </c>
@@ -9367,13 +8828,13 @@
         <v>0</v>
       </c>
       <c r="K74" s="7" t="s">
-        <v>187</v>
+        <v>161</v>
       </c>
       <c r="L74" s="7">
         <v>800001041</v>
       </c>
       <c r="M74" s="7">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N74" s="7">
         <v>70</v>
@@ -9391,7 +8852,7 @@
         <v>15</v>
       </c>
       <c r="S74" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T74" s="7">
         <v>1</v>
@@ -9400,13 +8861,13 @@
         <v>0</v>
       </c>
       <c r="V74" s="7" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W74" s="7" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X74" s="7" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="Y74" s="14">
         <v>201004011</v>
@@ -9418,7 +8879,7 @@
         <v>1</v>
       </c>
       <c r="AB74" s="4" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
       <c r="AC74" s="7">
         <v>10000</v>
@@ -9453,17 +8914,10 @@
         <v>30</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="D75" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="E75" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F75" s="7">
-        <v>1000010</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="D75" s="7"/>
+      <c r="F75" s="7"/>
       <c r="G75" s="7">
         <v>12</v>
       </c>
@@ -9477,13 +8931,13 @@
         <v>0</v>
       </c>
       <c r="K75" s="7" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="L75" s="7">
         <v>800014011</v>
       </c>
       <c r="M75" s="7">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N75" s="7">
         <v>125</v>
@@ -9501,7 +8955,7 @@
         <v>48</v>
       </c>
       <c r="S75" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T75" s="7">
         <v>1</v>
@@ -9510,13 +8964,13 @@
         <v>0</v>
       </c>
       <c r="V75" s="7" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W75" s="7" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X75" s="7" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="Y75" s="14">
         <v>214001011</v>
@@ -9528,7 +8982,7 @@
         <v>1</v>
       </c>
       <c r="AB75" s="4" t="s">
-        <v>198</v>
+        <v>171</v>
       </c>
       <c r="AC75" s="7">
         <v>10000</v>
@@ -9563,17 +9017,11 @@
         <v>30</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="D76" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="E76" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F76" s="12">
-        <v>1000010</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="D76" s="12"/>
+      <c r="E76" s="6"/>
+      <c r="F76" s="12"/>
       <c r="G76" s="12">
         <v>12</v>
       </c>
@@ -9587,13 +9035,13 @@
         <v>0</v>
       </c>
       <c r="K76" s="12" t="s">
-        <v>192</v>
+        <v>165</v>
       </c>
       <c r="L76" s="12">
         <v>1000010</v>
       </c>
       <c r="M76" s="12">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N76" s="12">
         <v>100</v>
@@ -9611,7 +9059,7 @@
         <v>36</v>
       </c>
       <c r="S76" s="12">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T76" s="12">
         <v>1</v>
@@ -9620,13 +9068,13 @@
         <v>0</v>
       </c>
       <c r="V76" s="12" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W76" s="12" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X76" s="12" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="Y76" s="13">
         <v>20040001</v>
@@ -9638,7 +9086,7 @@
         <v>1</v>
       </c>
       <c r="AB76" s="6" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC76" s="12">
         <v>10000</v>
@@ -9673,17 +9121,11 @@
         <v>30</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="D77" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="E77" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F77" s="12">
-        <v>1000006</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="D77" s="12"/>
+      <c r="E77" s="6"/>
+      <c r="F77" s="12"/>
       <c r="G77" s="12">
         <v>12</v>
       </c>
@@ -9697,13 +9139,13 @@
         <v>0</v>
       </c>
       <c r="K77" s="12" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="L77" s="12">
         <v>1000006</v>
       </c>
       <c r="M77" s="12">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N77" s="12">
         <v>100</v>
@@ -9721,7 +9163,7 @@
         <v>36</v>
       </c>
       <c r="S77" s="12">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T77" s="12">
         <v>1</v>
@@ -9730,13 +9172,13 @@
         <v>0</v>
       </c>
       <c r="V77" s="12" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W77" s="12" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X77" s="12" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="Y77" s="13">
         <v>20030001</v>
@@ -9748,7 +9190,7 @@
         <v>1</v>
       </c>
       <c r="AB77" s="6" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC77" s="12">
         <v>10000</v>
@@ -9783,17 +9225,11 @@
         <v>30</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="D78" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="E78" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F78" s="12">
-        <v>1000006</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="D78" s="12"/>
+      <c r="E78" s="6"/>
+      <c r="F78" s="12"/>
       <c r="G78" s="12">
         <v>12</v>
       </c>
@@ -9807,13 +9243,13 @@
         <v>0</v>
       </c>
       <c r="K78" s="12" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="L78" s="12">
         <v>1000006</v>
       </c>
       <c r="M78" s="12">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N78" s="12">
         <v>100</v>
@@ -9831,7 +9267,7 @@
         <v>36</v>
       </c>
       <c r="S78" s="12">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T78" s="12">
         <v>1</v>
@@ -9840,13 +9276,13 @@
         <v>0</v>
       </c>
       <c r="V78" s="12" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W78" s="12" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X78" s="12" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="Y78" s="13">
         <v>20030001</v>
@@ -9858,7 +9294,7 @@
         <v>1</v>
       </c>
       <c r="AB78" s="6" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC78" s="12">
         <v>10000</v>
@@ -9893,17 +9329,11 @@
         <v>30</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="D79" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E79" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F79" s="12">
-        <v>1000006</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="D79" s="12"/>
+      <c r="E79" s="6"/>
+      <c r="F79" s="12"/>
       <c r="G79" s="12">
         <v>12</v>
       </c>
@@ -9917,13 +9347,13 @@
         <v>0</v>
       </c>
       <c r="K79" s="12" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="L79" s="12">
         <v>1000006</v>
       </c>
       <c r="M79" s="12">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N79" s="12">
         <v>100</v>
@@ -9941,7 +9371,7 @@
         <v>36</v>
       </c>
       <c r="S79" s="12">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T79" s="12">
         <v>1</v>
@@ -9950,13 +9380,13 @@
         <v>0</v>
       </c>
       <c r="V79" s="12" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W79" s="12" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X79" s="12" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="Y79" s="13">
         <v>20030001</v>
@@ -9968,7 +9398,7 @@
         <v>1</v>
       </c>
       <c r="AB79" s="6" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC79" s="12">
         <v>10000</v>
@@ -10003,17 +9433,11 @@
         <v>30</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="D80" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="E80" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F80" s="12">
-        <v>1000103</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="D80" s="12"/>
+      <c r="E80" s="6"/>
+      <c r="F80" s="12"/>
       <c r="G80" s="12">
         <v>12</v>
       </c>
@@ -10027,13 +9451,13 @@
         <v>0</v>
       </c>
       <c r="K80" s="12" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="L80" s="12">
         <v>1000103</v>
       </c>
       <c r="M80" s="12">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N80" s="12">
         <v>100</v>
@@ -10051,7 +9475,7 @@
         <v>36</v>
       </c>
       <c r="S80" s="12">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T80" s="12">
         <v>1</v>
@@ -10060,13 +9484,13 @@
         <v>0</v>
       </c>
       <c r="V80" s="12" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W80" s="12" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X80" s="12" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="Y80" s="13">
         <v>20020001</v>
@@ -10078,7 +9502,7 @@
         <v>1</v>
       </c>
       <c r="AB80" s="6" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC80" s="12">
         <v>10000</v>
@@ -10113,17 +9537,11 @@
         <v>30</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="D81" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="E81" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F81" s="12">
-        <v>1000103</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="D81" s="12"/>
+      <c r="E81" s="6"/>
+      <c r="F81" s="12"/>
       <c r="G81" s="12">
         <v>12</v>
       </c>
@@ -10137,13 +9555,13 @@
         <v>0</v>
       </c>
       <c r="K81" s="12" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="L81" s="12">
         <v>1000103</v>
       </c>
       <c r="M81" s="12">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N81" s="12">
         <v>100</v>
@@ -10161,7 +9579,7 @@
         <v>36</v>
       </c>
       <c r="S81" s="12">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T81" s="12">
         <v>1</v>
@@ -10170,13 +9588,13 @@
         <v>0</v>
       </c>
       <c r="V81" s="12" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W81" s="12" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X81" s="12" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="Y81" s="13">
         <v>20020001</v>
@@ -10188,7 +9606,7 @@
         <v>1</v>
       </c>
       <c r="AB81" s="6" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC81" s="12">
         <v>10000</v>
@@ -10223,17 +9641,11 @@
         <v>30</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="D82" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="E82" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F82" s="12">
-        <v>1000103</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="D82" s="12"/>
+      <c r="E82" s="6"/>
+      <c r="F82" s="12"/>
       <c r="G82" s="12">
         <v>12</v>
       </c>
@@ -10247,13 +9659,13 @@
         <v>0</v>
       </c>
       <c r="K82" s="12" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="L82" s="12">
         <v>1000103</v>
       </c>
       <c r="M82" s="12">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N82" s="12">
         <v>100</v>
@@ -10271,7 +9683,7 @@
         <v>36</v>
       </c>
       <c r="S82" s="12">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T82" s="12">
         <v>1</v>
@@ -10280,13 +9692,13 @@
         <v>0</v>
       </c>
       <c r="V82" s="12" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W82" s="12" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X82" s="12" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="Y82" s="13">
         <v>20020001</v>
@@ -10298,7 +9710,7 @@
         <v>1</v>
       </c>
       <c r="AB82" s="6" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC82" s="12">
         <v>10000</v>
@@ -10333,17 +9745,10 @@
         <v>30</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D83" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="E83" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F83" s="7">
-        <v>1000011</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="D83" s="7"/>
+      <c r="F83" s="7"/>
       <c r="G83" s="7">
         <v>12</v>
       </c>
@@ -10357,13 +9762,13 @@
         <v>0</v>
       </c>
       <c r="K83" s="7" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="L83" s="7">
         <v>800003021</v>
       </c>
       <c r="M83" s="7">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N83" s="7">
         <v>500</v>
@@ -10381,7 +9786,7 @@
         <v>1496</v>
       </c>
       <c r="S83" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T83" s="7">
         <v>1</v>
@@ -10390,13 +9795,13 @@
         <v>30000</v>
       </c>
       <c r="V83" s="7" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W83" s="7" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X83" s="7" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="Y83" s="14">
         <v>203002011</v>
@@ -10408,7 +9813,7 @@
         <v>1</v>
       </c>
       <c r="AB83" s="4" t="s">
-        <v>199</v>
+        <v>172</v>
       </c>
       <c r="AC83" s="7">
         <v>10000</v>
@@ -10429,7 +9834,7 @@
         <v>5000</v>
       </c>
       <c r="AI83" s="4">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="AJ83" s="4">
         <v>0</v>
@@ -10443,17 +9848,11 @@
         <v>30</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D84" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="E84" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F84" s="12">
-        <v>1000011</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="D84" s="12"/>
+      <c r="E84" s="6"/>
+      <c r="F84" s="12"/>
       <c r="G84" s="12">
         <v>12</v>
       </c>
@@ -10467,13 +9866,13 @@
         <v>0</v>
       </c>
       <c r="K84" s="12" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="L84" s="12">
         <v>1000011</v>
       </c>
       <c r="M84" s="12">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N84" s="12">
         <v>100</v>
@@ -10491,7 +9890,7 @@
         <v>36</v>
       </c>
       <c r="S84" s="12">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T84" s="12">
         <v>1</v>
@@ -10500,13 +9899,13 @@
         <v>0</v>
       </c>
       <c r="V84" s="12" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W84" s="12" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X84" s="12" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="Y84" s="13">
         <v>20050001</v>
@@ -10518,7 +9917,7 @@
         <v>1</v>
       </c>
       <c r="AB84" s="6" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC84" s="12">
         <v>10000</v>
@@ -10553,17 +9952,11 @@
         <v>30</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="D85" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="E85" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F85" s="12">
-        <v>1000011</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="D85" s="12"/>
+      <c r="E85" s="6"/>
+      <c r="F85" s="12"/>
       <c r="G85" s="12">
         <v>12</v>
       </c>
@@ -10577,13 +9970,13 @@
         <v>0</v>
       </c>
       <c r="K85" s="12" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="L85" s="12">
         <v>1000011</v>
       </c>
       <c r="M85" s="12">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N85" s="12">
         <v>100</v>
@@ -10601,7 +9994,7 @@
         <v>36</v>
       </c>
       <c r="S85" s="12">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T85" s="12">
         <v>1</v>
@@ -10610,13 +10003,13 @@
         <v>0</v>
       </c>
       <c r="V85" s="12" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W85" s="12" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X85" s="12" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="Y85" s="13">
         <v>20050001</v>
@@ -10628,7 +10021,7 @@
         <v>1</v>
       </c>
       <c r="AB85" s="6" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC85" s="12">
         <v>10000</v>
@@ -10663,17 +10056,10 @@
         <v>30</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D86" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E86" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F86" s="7">
-        <v>1000102</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="D86" s="7"/>
+      <c r="F86" s="7"/>
       <c r="G86" s="7">
         <v>12</v>
       </c>
@@ -10687,13 +10073,13 @@
         <v>0</v>
       </c>
       <c r="K86" s="7" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="L86" s="7">
         <v>800001011</v>
       </c>
       <c r="M86" s="7">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N86" s="7">
         <v>70</v>
@@ -10711,7 +10097,7 @@
         <v>18</v>
       </c>
       <c r="S86" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T86" s="7">
         <v>1</v>
@@ -10720,13 +10106,13 @@
         <v>0</v>
       </c>
       <c r="V86" s="7" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W86" s="7" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X86" s="7" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="Y86" s="14">
         <v>201001011</v>
@@ -10738,7 +10124,7 @@
         <v>1</v>
       </c>
       <c r="AB86" s="4" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
       <c r="AC86" s="7">
         <v>10000</v>
@@ -10773,17 +10159,10 @@
         <v>30</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D87" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="E87" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F87" s="7">
-        <v>1000102</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="D87" s="7"/>
+      <c r="F87" s="7"/>
       <c r="G87" s="7">
         <v>12</v>
       </c>
@@ -10797,13 +10176,13 @@
         <v>0</v>
       </c>
       <c r="K87" s="7" t="s">
-        <v>185</v>
+        <v>159</v>
       </c>
       <c r="L87" s="7">
         <v>800001021</v>
       </c>
       <c r="M87" s="7">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N87" s="7">
         <v>200</v>
@@ -10821,7 +10200,7 @@
         <v>230</v>
       </c>
       <c r="S87" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T87" s="7">
         <v>1</v>
@@ -10830,13 +10209,13 @@
         <v>0</v>
       </c>
       <c r="V87" s="7" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W87" s="7" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X87" s="7" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="Y87" s="14">
         <v>201002011</v>
@@ -10848,7 +10227,7 @@
         <v>1</v>
       </c>
       <c r="AB87" s="4" t="s">
-        <v>197</v>
+        <v>170</v>
       </c>
       <c r="AC87" s="7">
         <v>10000</v>
@@ -10883,17 +10262,11 @@
         <v>30</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="D88" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="E88" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F88" s="12">
-        <v>1000102</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="D88" s="12"/>
+      <c r="E88" s="6"/>
+      <c r="F88" s="12"/>
       <c r="G88" s="12">
         <v>12</v>
       </c>
@@ -10907,13 +10280,13 @@
         <v>0</v>
       </c>
       <c r="K88" s="12" t="s">
-        <v>186</v>
+        <v>160</v>
       </c>
       <c r="L88" s="12">
         <v>800001021</v>
       </c>
       <c r="M88" s="12">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N88" s="12">
         <v>70</v>
@@ -10931,7 +10304,7 @@
         <v>300</v>
       </c>
       <c r="S88" s="12">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T88" s="12">
         <v>1</v>
@@ -10940,13 +10313,13 @@
         <v>250</v>
       </c>
       <c r="V88" s="12" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W88" s="12" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X88" s="12" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="Y88" s="13">
         <v>20010001</v>
@@ -10958,7 +10331,7 @@
         <v>1</v>
       </c>
       <c r="AB88" s="6" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
       <c r="AC88" s="12">
         <v>10000</v>
@@ -10993,17 +10366,10 @@
         <v>30</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D89" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="E89" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F89" s="7">
-        <v>1000010</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="D89" s="7"/>
+      <c r="F89" s="7"/>
       <c r="G89" s="7">
         <v>12</v>
       </c>
@@ -11017,13 +10383,13 @@
         <v>0</v>
       </c>
       <c r="K89" s="7" t="s">
-        <v>187</v>
+        <v>161</v>
       </c>
       <c r="L89" s="7">
         <v>800001041</v>
       </c>
       <c r="M89" s="7">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N89" s="7">
         <v>70</v>
@@ -11041,7 +10407,7 @@
         <v>15</v>
       </c>
       <c r="S89" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T89" s="7">
         <v>1</v>
@@ -11050,13 +10416,13 @@
         <v>0</v>
       </c>
       <c r="V89" s="7" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W89" s="7" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X89" s="7" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="Y89" s="14">
         <v>201004011</v>
@@ -11068,7 +10434,7 @@
         <v>1</v>
       </c>
       <c r="AB89" s="4" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
       <c r="AC89" s="7">
         <v>10000</v>
@@ -11103,17 +10469,10 @@
         <v>30</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="D90" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="E90" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F90" s="7">
-        <v>1000010</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="D90" s="7"/>
+      <c r="F90" s="7"/>
       <c r="G90" s="7">
         <v>12</v>
       </c>
@@ -11127,13 +10486,13 @@
         <v>0</v>
       </c>
       <c r="K90" s="7" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="L90" s="7">
         <v>800014011</v>
       </c>
       <c r="M90" s="7">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N90" s="7">
         <v>125</v>
@@ -11151,7 +10510,7 @@
         <v>48</v>
       </c>
       <c r="S90" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T90" s="7">
         <v>1</v>
@@ -11160,13 +10519,13 @@
         <v>0</v>
       </c>
       <c r="V90" s="7" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W90" s="7" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X90" s="7" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="Y90" s="14">
         <v>214001011</v>
@@ -11178,7 +10537,7 @@
         <v>1</v>
       </c>
       <c r="AB90" s="4" t="s">
-        <v>198</v>
+        <v>171</v>
       </c>
       <c r="AC90" s="7">
         <v>10000</v>
@@ -11213,17 +10572,11 @@
         <v>30</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="D91" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="E91" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F91" s="12">
-        <v>1000010</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="D91" s="12"/>
+      <c r="E91" s="6"/>
+      <c r="F91" s="12"/>
       <c r="G91" s="12">
         <v>12</v>
       </c>
@@ -11237,13 +10590,13 @@
         <v>0</v>
       </c>
       <c r="K91" s="12" t="s">
-        <v>192</v>
+        <v>165</v>
       </c>
       <c r="L91" s="12">
         <v>1000010</v>
       </c>
       <c r="M91" s="12">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N91" s="12">
         <v>100</v>
@@ -11261,7 +10614,7 @@
         <v>36</v>
       </c>
       <c r="S91" s="12">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T91" s="12">
         <v>1</v>
@@ -11270,13 +10623,13 @@
         <v>0</v>
       </c>
       <c r="V91" s="12" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W91" s="12" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X91" s="12" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="Y91" s="13">
         <v>20040001</v>
@@ -11288,7 +10641,7 @@
         <v>1</v>
       </c>
       <c r="AB91" s="6" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC91" s="12">
         <v>10000</v>
@@ -11323,17 +10676,11 @@
         <v>30</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="D92" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="E92" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F92" s="12">
-        <v>1000006</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="D92" s="12"/>
+      <c r="E92" s="6"/>
+      <c r="F92" s="12"/>
       <c r="G92" s="12">
         <v>12</v>
       </c>
@@ -11347,13 +10694,13 @@
         <v>0</v>
       </c>
       <c r="K92" s="12" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="L92" s="12">
         <v>1000006</v>
       </c>
       <c r="M92" s="12">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N92" s="12">
         <v>100</v>
@@ -11371,7 +10718,7 @@
         <v>36</v>
       </c>
       <c r="S92" s="12">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T92" s="12">
         <v>1</v>
@@ -11380,13 +10727,13 @@
         <v>0</v>
       </c>
       <c r="V92" s="12" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W92" s="12" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X92" s="12" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="Y92" s="13">
         <v>20030001</v>
@@ -11398,7 +10745,7 @@
         <v>1</v>
       </c>
       <c r="AB92" s="6" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC92" s="12">
         <v>10000</v>
@@ -11433,17 +10780,11 @@
         <v>30</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="D93" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="E93" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F93" s="12">
-        <v>1000006</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="D93" s="12"/>
+      <c r="E93" s="6"/>
+      <c r="F93" s="12"/>
       <c r="G93" s="12">
         <v>12</v>
       </c>
@@ -11457,13 +10798,13 @@
         <v>0</v>
       </c>
       <c r="K93" s="12" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="L93" s="12">
         <v>1000006</v>
       </c>
       <c r="M93" s="12">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N93" s="12">
         <v>100</v>
@@ -11481,7 +10822,7 @@
         <v>36</v>
       </c>
       <c r="S93" s="12">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T93" s="12">
         <v>1</v>
@@ -11490,13 +10831,13 @@
         <v>0</v>
       </c>
       <c r="V93" s="12" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W93" s="12" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X93" s="12" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="Y93" s="13">
         <v>20030001</v>
@@ -11508,7 +10849,7 @@
         <v>1</v>
       </c>
       <c r="AB93" s="6" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC93" s="12">
         <v>10000</v>
@@ -11543,17 +10884,11 @@
         <v>30</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="D94" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E94" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F94" s="12">
-        <v>1000006</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="D94" s="12"/>
+      <c r="E94" s="6"/>
+      <c r="F94" s="12"/>
       <c r="G94" s="12">
         <v>12</v>
       </c>
@@ -11567,13 +10902,13 @@
         <v>0</v>
       </c>
       <c r="K94" s="12" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="L94" s="12">
         <v>1000006</v>
       </c>
       <c r="M94" s="12">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N94" s="12">
         <v>100</v>
@@ -11591,7 +10926,7 @@
         <v>36</v>
       </c>
       <c r="S94" s="12">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T94" s="12">
         <v>1</v>
@@ -11600,13 +10935,13 @@
         <v>0</v>
       </c>
       <c r="V94" s="12" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W94" s="12" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X94" s="12" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="Y94" s="13">
         <v>20030001</v>
@@ -11618,7 +10953,7 @@
         <v>1</v>
       </c>
       <c r="AB94" s="6" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC94" s="12">
         <v>10000</v>
@@ -11653,17 +10988,11 @@
         <v>30</v>
       </c>
       <c r="C95" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="D95" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="E95" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F95" s="12">
-        <v>1000103</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="D95" s="12"/>
+      <c r="E95" s="6"/>
+      <c r="F95" s="12"/>
       <c r="G95" s="12">
         <v>12</v>
       </c>
@@ -11677,13 +11006,13 @@
         <v>0</v>
       </c>
       <c r="K95" s="12" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="L95" s="12">
         <v>1000103</v>
       </c>
       <c r="M95" s="12">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N95" s="12">
         <v>100</v>
@@ -11701,7 +11030,7 @@
         <v>36</v>
       </c>
       <c r="S95" s="12">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T95" s="12">
         <v>1</v>
@@ -11710,13 +11039,13 @@
         <v>0</v>
       </c>
       <c r="V95" s="12" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W95" s="12" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X95" s="12" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="Y95" s="13">
         <v>20020001</v>
@@ -11728,7 +11057,7 @@
         <v>1</v>
       </c>
       <c r="AB95" s="6" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC95" s="12">
         <v>10000</v>
@@ -11763,17 +11092,11 @@
         <v>30</v>
       </c>
       <c r="C96" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="D96" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="E96" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F96" s="12">
-        <v>1000103</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="D96" s="12"/>
+      <c r="E96" s="6"/>
+      <c r="F96" s="12"/>
       <c r="G96" s="12">
         <v>12</v>
       </c>
@@ -11787,13 +11110,13 @@
         <v>0</v>
       </c>
       <c r="K96" s="12" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="L96" s="12">
         <v>1000103</v>
       </c>
       <c r="M96" s="12">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N96" s="12">
         <v>100</v>
@@ -11811,7 +11134,7 @@
         <v>36</v>
       </c>
       <c r="S96" s="12">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T96" s="12">
         <v>1</v>
@@ -11820,13 +11143,13 @@
         <v>0</v>
       </c>
       <c r="V96" s="12" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W96" s="12" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X96" s="12" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="Y96" s="13">
         <v>20020001</v>
@@ -11838,7 +11161,7 @@
         <v>1</v>
       </c>
       <c r="AB96" s="6" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC96" s="12">
         <v>10000</v>
@@ -11873,17 +11196,11 @@
         <v>30</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="D97" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="E97" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F97" s="12">
-        <v>1000103</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="D97" s="12"/>
+      <c r="E97" s="6"/>
+      <c r="F97" s="12"/>
       <c r="G97" s="12">
         <v>12</v>
       </c>
@@ -11897,13 +11214,13 @@
         <v>0</v>
       </c>
       <c r="K97" s="12" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="L97" s="12">
         <v>1000103</v>
       </c>
       <c r="M97" s="12">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N97" s="12">
         <v>100</v>
@@ -11921,7 +11238,7 @@
         <v>36</v>
       </c>
       <c r="S97" s="12">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T97" s="12">
         <v>1</v>
@@ -11930,13 +11247,13 @@
         <v>0</v>
       </c>
       <c r="V97" s="12" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W97" s="12" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X97" s="12" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="Y97" s="13">
         <v>20020001</v>
@@ -11948,7 +11265,7 @@
         <v>1</v>
       </c>
       <c r="AB97" s="6" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC97" s="12">
         <v>10000</v>
@@ -11983,17 +11300,10 @@
         <v>30</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D98" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="E98" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F98" s="7">
-        <v>1000011</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="D98" s="7"/>
+      <c r="F98" s="7"/>
       <c r="G98" s="7">
         <v>12</v>
       </c>
@@ -12007,13 +11317,13 @@
         <v>0</v>
       </c>
       <c r="K98" s="7" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="L98" s="7">
         <v>800003021</v>
       </c>
       <c r="M98" s="7">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N98" s="7">
         <v>500</v>
@@ -12031,7 +11341,7 @@
         <v>1496</v>
       </c>
       <c r="S98" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T98" s="7">
         <v>1</v>
@@ -12040,13 +11350,13 @@
         <v>30000</v>
       </c>
       <c r="V98" s="7" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W98" s="7" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X98" s="7" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="Y98" s="14">
         <v>203002011</v>
@@ -12058,7 +11368,7 @@
         <v>1</v>
       </c>
       <c r="AB98" s="4" t="s">
-        <v>199</v>
+        <v>172</v>
       </c>
       <c r="AC98" s="7">
         <v>10000</v>
@@ -12079,7 +11389,7 @@
         <v>5000</v>
       </c>
       <c r="AI98" s="4">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="AJ98" s="4">
         <v>0</v>
@@ -12093,17 +11403,11 @@
         <v>30</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D99" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="E99" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F99" s="12">
-        <v>1000011</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="D99" s="12"/>
+      <c r="E99" s="6"/>
+      <c r="F99" s="12"/>
       <c r="G99" s="12">
         <v>12</v>
       </c>
@@ -12117,13 +11421,13 @@
         <v>0</v>
       </c>
       <c r="K99" s="12" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="L99" s="12">
         <v>1000011</v>
       </c>
       <c r="M99" s="12">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N99" s="12">
         <v>100</v>
@@ -12141,7 +11445,7 @@
         <v>36</v>
       </c>
       <c r="S99" s="12">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T99" s="12">
         <v>1</v>
@@ -12150,13 +11454,13 @@
         <v>0</v>
       </c>
       <c r="V99" s="12" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W99" s="12" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X99" s="12" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="Y99" s="13">
         <v>20050001</v>
@@ -12168,7 +11472,7 @@
         <v>1</v>
       </c>
       <c r="AB99" s="6" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC99" s="12">
         <v>10000</v>
@@ -12203,17 +11507,11 @@
         <v>30</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="D100" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="E100" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F100" s="12">
-        <v>1000011</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="D100" s="12"/>
+      <c r="E100" s="6"/>
+      <c r="F100" s="12"/>
       <c r="G100" s="12">
         <v>12</v>
       </c>
@@ -12227,13 +11525,13 @@
         <v>0</v>
       </c>
       <c r="K100" s="12" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="L100" s="12">
         <v>1000011</v>
       </c>
       <c r="M100" s="12">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N100" s="12">
         <v>100</v>
@@ -12251,7 +11549,7 @@
         <v>36</v>
       </c>
       <c r="S100" s="12">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T100" s="12">
         <v>1</v>
@@ -12260,13 +11558,13 @@
         <v>0</v>
       </c>
       <c r="V100" s="12" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W100" s="12" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X100" s="12" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="Y100" s="13">
         <v>20050001</v>
@@ -12278,7 +11576,7 @@
         <v>1</v>
       </c>
       <c r="AB100" s="6" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC100" s="12">
         <v>10000</v>
@@ -12313,17 +11611,10 @@
         <v>30</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D101" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E101" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F101" s="7">
-        <v>1000102</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="D101" s="7"/>
+      <c r="F101" s="7"/>
       <c r="G101" s="7">
         <v>12</v>
       </c>
@@ -12337,13 +11628,13 @@
         <v>0</v>
       </c>
       <c r="K101" s="7" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="L101" s="7">
         <v>800001011</v>
       </c>
       <c r="M101" s="7">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N101" s="7">
         <v>70</v>
@@ -12361,7 +11652,7 @@
         <v>18</v>
       </c>
       <c r="S101" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T101" s="7">
         <v>1</v>
@@ -12370,13 +11661,13 @@
         <v>0</v>
       </c>
       <c r="V101" s="7" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W101" s="7" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X101" s="7" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="Y101" s="14">
         <v>201001011</v>
@@ -12388,7 +11679,7 @@
         <v>1</v>
       </c>
       <c r="AB101" s="4" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
       <c r="AC101" s="7">
         <v>10000</v>
@@ -12423,17 +11714,10 @@
         <v>30</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D102" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="E102" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F102" s="7">
-        <v>1000102</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="D102" s="7"/>
+      <c r="F102" s="7"/>
       <c r="G102" s="7">
         <v>12</v>
       </c>
@@ -12447,13 +11731,13 @@
         <v>0</v>
       </c>
       <c r="K102" s="7" t="s">
-        <v>185</v>
+        <v>159</v>
       </c>
       <c r="L102" s="7">
         <v>800001021</v>
       </c>
       <c r="M102" s="7">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N102" s="7">
         <v>200</v>
@@ -12471,7 +11755,7 @@
         <v>230</v>
       </c>
       <c r="S102" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T102" s="7">
         <v>1</v>
@@ -12480,13 +11764,13 @@
         <v>0</v>
       </c>
       <c r="V102" s="7" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W102" s="7" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X102" s="7" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="Y102" s="14">
         <v>201002011</v>
@@ -12498,7 +11782,7 @@
         <v>1</v>
       </c>
       <c r="AB102" s="4" t="s">
-        <v>197</v>
+        <v>170</v>
       </c>
       <c r="AC102" s="7">
         <v>10000</v>
@@ -12533,17 +11817,11 @@
         <v>30</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="D103" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="E103" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F103" s="12">
-        <v>1000102</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="D103" s="12"/>
+      <c r="E103" s="6"/>
+      <c r="F103" s="12"/>
       <c r="G103" s="12">
         <v>12</v>
       </c>
@@ -12557,13 +11835,13 @@
         <v>0</v>
       </c>
       <c r="K103" s="12" t="s">
-        <v>186</v>
+        <v>160</v>
       </c>
       <c r="L103" s="12">
         <v>800001021</v>
       </c>
       <c r="M103" s="12">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N103" s="12">
         <v>70</v>
@@ -12581,7 +11859,7 @@
         <v>300</v>
       </c>
       <c r="S103" s="12">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T103" s="12">
         <v>1</v>
@@ -12590,13 +11868,13 @@
         <v>250</v>
       </c>
       <c r="V103" s="12" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W103" s="12" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X103" s="12" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="Y103" s="13">
         <v>20010001</v>
@@ -12608,7 +11886,7 @@
         <v>1</v>
       </c>
       <c r="AB103" s="6" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
       <c r="AC103" s="12">
         <v>10000</v>
@@ -12643,17 +11921,10 @@
         <v>30</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D104" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="E104" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F104" s="7">
-        <v>1000010</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="D104" s="7"/>
+      <c r="F104" s="7"/>
       <c r="G104" s="7">
         <v>12</v>
       </c>
@@ -12667,13 +11938,13 @@
         <v>0</v>
       </c>
       <c r="K104" s="7" t="s">
-        <v>187</v>
+        <v>161</v>
       </c>
       <c r="L104" s="7">
         <v>800001041</v>
       </c>
       <c r="M104" s="7">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N104" s="7">
         <v>70</v>
@@ -12691,7 +11962,7 @@
         <v>15</v>
       </c>
       <c r="S104" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T104" s="7">
         <v>1</v>
@@ -12700,13 +11971,13 @@
         <v>0</v>
       </c>
       <c r="V104" s="7" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W104" s="7" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X104" s="7" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="Y104" s="14">
         <v>201004011</v>
@@ -12718,7 +11989,7 @@
         <v>1</v>
       </c>
       <c r="AB104" s="4" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
       <c r="AC104" s="7">
         <v>10000</v>
@@ -12753,17 +12024,10 @@
         <v>30</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="D105" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="E105" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F105" s="7">
-        <v>1000010</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="D105" s="7"/>
+      <c r="F105" s="7"/>
       <c r="G105" s="7">
         <v>12</v>
       </c>
@@ -12777,13 +12041,13 @@
         <v>0</v>
       </c>
       <c r="K105" s="7" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="L105" s="7">
         <v>800014011</v>
       </c>
       <c r="M105" s="7">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N105" s="7">
         <v>125</v>
@@ -12801,7 +12065,7 @@
         <v>48</v>
       </c>
       <c r="S105" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T105" s="7">
         <v>1</v>
@@ -12810,13 +12074,13 @@
         <v>0</v>
       </c>
       <c r="V105" s="7" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W105" s="7" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X105" s="7" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="Y105" s="14">
         <v>214001011</v>
@@ -12828,7 +12092,7 @@
         <v>1</v>
       </c>
       <c r="AB105" s="4" t="s">
-        <v>198</v>
+        <v>171</v>
       </c>
       <c r="AC105" s="7">
         <v>10000</v>
@@ -12863,17 +12127,11 @@
         <v>30</v>
       </c>
       <c r="C106" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="D106" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="E106" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F106" s="12">
-        <v>1000010</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="D106" s="12"/>
+      <c r="E106" s="6"/>
+      <c r="F106" s="12"/>
       <c r="G106" s="12">
         <v>12</v>
       </c>
@@ -12887,13 +12145,13 @@
         <v>0</v>
       </c>
       <c r="K106" s="12" t="s">
-        <v>192</v>
+        <v>165</v>
       </c>
       <c r="L106" s="12">
         <v>1000010</v>
       </c>
       <c r="M106" s="12">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N106" s="12">
         <v>100</v>
@@ -12911,7 +12169,7 @@
         <v>36</v>
       </c>
       <c r="S106" s="12">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T106" s="12">
         <v>1</v>
@@ -12920,13 +12178,13 @@
         <v>0</v>
       </c>
       <c r="V106" s="12" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W106" s="12" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X106" s="12" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="Y106" s="13">
         <v>20040001</v>
@@ -12938,7 +12196,7 @@
         <v>1</v>
       </c>
       <c r="AB106" s="6" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC106" s="12">
         <v>10000</v>
@@ -12973,17 +12231,11 @@
         <v>30</v>
       </c>
       <c r="C107" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="D107" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="E107" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F107" s="12">
-        <v>1000006</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="D107" s="12"/>
+      <c r="E107" s="6"/>
+      <c r="F107" s="12"/>
       <c r="G107" s="12">
         <v>12</v>
       </c>
@@ -12997,13 +12249,13 @@
         <v>0</v>
       </c>
       <c r="K107" s="12" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="L107" s="12">
         <v>1000006</v>
       </c>
       <c r="M107" s="12">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N107" s="12">
         <v>100</v>
@@ -13021,7 +12273,7 @@
         <v>36</v>
       </c>
       <c r="S107" s="12">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T107" s="12">
         <v>1</v>
@@ -13030,13 +12282,13 @@
         <v>0</v>
       </c>
       <c r="V107" s="12" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W107" s="12" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X107" s="12" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="Y107" s="13">
         <v>20030001</v>
@@ -13048,7 +12300,7 @@
         <v>1</v>
       </c>
       <c r="AB107" s="6" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC107" s="12">
         <v>10000</v>
@@ -13083,17 +12335,11 @@
         <v>30</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="D108" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="E108" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F108" s="12">
-        <v>1000006</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="D108" s="12"/>
+      <c r="E108" s="6"/>
+      <c r="F108" s="12"/>
       <c r="G108" s="12">
         <v>12</v>
       </c>
@@ -13107,13 +12353,13 @@
         <v>0</v>
       </c>
       <c r="K108" s="12" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="L108" s="12">
         <v>1000006</v>
       </c>
       <c r="M108" s="12">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N108" s="12">
         <v>100</v>
@@ -13131,7 +12377,7 @@
         <v>36</v>
       </c>
       <c r="S108" s="12">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T108" s="12">
         <v>1</v>
@@ -13140,13 +12386,13 @@
         <v>0</v>
       </c>
       <c r="V108" s="12" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W108" s="12" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X108" s="12" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="Y108" s="13">
         <v>20030001</v>
@@ -13158,7 +12404,7 @@
         <v>1</v>
       </c>
       <c r="AB108" s="6" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC108" s="12">
         <v>10000</v>
@@ -13193,17 +12439,11 @@
         <v>30</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="D109" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E109" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F109" s="12">
-        <v>1000006</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="D109" s="12"/>
+      <c r="E109" s="6"/>
+      <c r="F109" s="12"/>
       <c r="G109" s="12">
         <v>12</v>
       </c>
@@ -13217,13 +12457,13 @@
         <v>0</v>
       </c>
       <c r="K109" s="12" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="L109" s="12">
         <v>1000006</v>
       </c>
       <c r="M109" s="12">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N109" s="12">
         <v>100</v>
@@ -13241,7 +12481,7 @@
         <v>36</v>
       </c>
       <c r="S109" s="12">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T109" s="12">
         <v>1</v>
@@ -13250,13 +12490,13 @@
         <v>0</v>
       </c>
       <c r="V109" s="12" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W109" s="12" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X109" s="12" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="Y109" s="13">
         <v>20030001</v>
@@ -13268,7 +12508,7 @@
         <v>1</v>
       </c>
       <c r="AB109" s="6" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC109" s="12">
         <v>10000</v>
@@ -13303,17 +12543,11 @@
         <v>30</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="D110" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="E110" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F110" s="12">
-        <v>1000103</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="D110" s="12"/>
+      <c r="E110" s="6"/>
+      <c r="F110" s="12"/>
       <c r="G110" s="12">
         <v>12</v>
       </c>
@@ -13327,13 +12561,13 @@
         <v>0</v>
       </c>
       <c r="K110" s="12" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="L110" s="12">
         <v>1000103</v>
       </c>
       <c r="M110" s="12">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N110" s="12">
         <v>100</v>
@@ -13351,7 +12585,7 @@
         <v>36</v>
       </c>
       <c r="S110" s="12">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T110" s="12">
         <v>1</v>
@@ -13360,13 +12594,13 @@
         <v>0</v>
       </c>
       <c r="V110" s="12" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W110" s="12" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X110" s="12" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="Y110" s="13">
         <v>20020001</v>
@@ -13378,7 +12612,7 @@
         <v>1</v>
       </c>
       <c r="AB110" s="6" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC110" s="12">
         <v>10000</v>
@@ -13413,17 +12647,11 @@
         <v>30</v>
       </c>
       <c r="C111" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="D111" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="E111" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F111" s="12">
-        <v>1000103</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="D111" s="12"/>
+      <c r="E111" s="6"/>
+      <c r="F111" s="12"/>
       <c r="G111" s="12">
         <v>12</v>
       </c>
@@ -13437,13 +12665,13 @@
         <v>0</v>
       </c>
       <c r="K111" s="12" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="L111" s="12">
         <v>1000103</v>
       </c>
       <c r="M111" s="12">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N111" s="12">
         <v>100</v>
@@ -13461,7 +12689,7 @@
         <v>36</v>
       </c>
       <c r="S111" s="12">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T111" s="12">
         <v>1</v>
@@ -13470,13 +12698,13 @@
         <v>0</v>
       </c>
       <c r="V111" s="12" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W111" s="12" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X111" s="12" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="Y111" s="13">
         <v>20020001</v>
@@ -13488,7 +12716,7 @@
         <v>1</v>
       </c>
       <c r="AB111" s="6" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC111" s="12">
         <v>10000</v>
@@ -13523,17 +12751,11 @@
         <v>30</v>
       </c>
       <c r="C112" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="D112" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="E112" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F112" s="12">
-        <v>1000103</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="D112" s="12"/>
+      <c r="E112" s="6"/>
+      <c r="F112" s="12"/>
       <c r="G112" s="12">
         <v>12</v>
       </c>
@@ -13547,13 +12769,13 @@
         <v>0</v>
       </c>
       <c r="K112" s="12" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="L112" s="12">
         <v>1000103</v>
       </c>
       <c r="M112" s="12">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N112" s="12">
         <v>100</v>
@@ -13571,7 +12793,7 @@
         <v>36</v>
       </c>
       <c r="S112" s="12">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T112" s="12">
         <v>1</v>
@@ -13580,13 +12802,13 @@
         <v>0</v>
       </c>
       <c r="V112" s="12" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W112" s="12" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X112" s="12" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="Y112" s="13">
         <v>20020001</v>
@@ -13598,7 +12820,7 @@
         <v>1</v>
       </c>
       <c r="AB112" s="6" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC112" s="12">
         <v>10000</v>
@@ -13633,17 +12855,10 @@
         <v>30</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D113" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="E113" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F113" s="7">
-        <v>1000011</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="D113" s="7"/>
+      <c r="F113" s="7"/>
       <c r="G113" s="7">
         <v>12</v>
       </c>
@@ -13657,13 +12872,13 @@
         <v>0</v>
       </c>
       <c r="K113" s="7" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="L113" s="7">
         <v>800003021</v>
       </c>
       <c r="M113" s="7">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N113" s="7">
         <v>500</v>
@@ -13681,22 +12896,22 @@
         <v>1496</v>
       </c>
       <c r="S113" s="7">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T113" s="7">
         <v>1</v>
       </c>
       <c r="U113" s="7">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="V113" s="7" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W113" s="7" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X113" s="7" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="Y113" s="14">
         <v>203002011</v>
@@ -13708,7 +12923,7 @@
         <v>1</v>
       </c>
       <c r="AB113" s="4" t="s">
-        <v>199</v>
+        <v>153</v>
       </c>
       <c r="AC113" s="7">
         <v>10000</v>
@@ -13723,13 +12938,13 @@
         <v>40</v>
       </c>
       <c r="AG113" s="4">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="AH113" s="4">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="AI113" s="4">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="AJ113" s="4">
         <v>0</v>
@@ -13743,17 +12958,11 @@
         <v>30</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D114" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="E114" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F114" s="12">
-        <v>1000011</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="D114" s="12"/>
+      <c r="E114" s="6"/>
+      <c r="F114" s="12"/>
       <c r="G114" s="12">
         <v>12</v>
       </c>
@@ -13767,13 +12976,13 @@
         <v>0</v>
       </c>
       <c r="K114" s="12" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="L114" s="12">
         <v>1000011</v>
       </c>
       <c r="M114" s="12">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N114" s="12">
         <v>100</v>
@@ -13791,7 +13000,7 @@
         <v>36</v>
       </c>
       <c r="S114" s="12">
-        <v>-3000</v>
+        <v>-5000</v>
       </c>
       <c r="T114" s="12">
         <v>1</v>
@@ -13800,13 +13009,13 @@
         <v>0</v>
       </c>
       <c r="V114" s="12" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="W114" s="12" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="X114" s="12" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="Y114" s="13">
         <v>20050001</v>
@@ -13818,7 +13027,7 @@
         <v>1</v>
       </c>
       <c r="AB114" s="6" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="AC114" s="12">
         <v>10000</v>
@@ -13845,111 +13054,104 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A115" s="12">
+    <row r="115" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A115" s="7">
         <v>303115</v>
       </c>
-      <c r="B115" s="12">
+      <c r="B115" s="7">
         <v>30</v>
       </c>
-      <c r="C115" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="D115" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="E115" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F115" s="12">
-        <v>1000011</v>
-      </c>
-      <c r="G115" s="12">
+      <c r="C115" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D115" s="7"/>
+      <c r="F115" s="7"/>
+      <c r="G115" s="7">
         <v>12</v>
       </c>
-      <c r="H115" s="12">
-        <v>1</v>
-      </c>
-      <c r="I115" s="12" t="s">
+      <c r="H115" s="7">
+        <v>4</v>
+      </c>
+      <c r="I115" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="J115" s="12">
-        <v>0</v>
-      </c>
-      <c r="K115" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="L115" s="12">
-        <v>1000011</v>
-      </c>
-      <c r="M115" s="12">
-        <v>12</v>
-      </c>
-      <c r="N115" s="12">
+      <c r="J115" s="7">
+        <v>0</v>
+      </c>
+      <c r="K115" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="L115" s="7">
+        <v>800016011</v>
+      </c>
+      <c r="M115" s="7">
+        <v>1</v>
+      </c>
+      <c r="N115" s="7">
         <v>100</v>
       </c>
-      <c r="O115" s="12">
-        <v>0</v>
-      </c>
-      <c r="P115" s="12">
+      <c r="O115" s="7">
+        <v>0</v>
+      </c>
+      <c r="P115" s="7">
         <v>15</v>
       </c>
-      <c r="Q115" s="12">
-        <v>0</v>
-      </c>
-      <c r="R115" s="12">
+      <c r="Q115" s="7">
+        <v>0</v>
+      </c>
+      <c r="R115" s="16">
         <v>36</v>
       </c>
-      <c r="S115" s="12">
-        <v>-3000</v>
-      </c>
-      <c r="T115" s="12">
-        <v>1</v>
-      </c>
-      <c r="U115" s="12">
-        <v>0</v>
-      </c>
-      <c r="V115" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="W115" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="X115" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="Y115" s="13">
-        <v>20050001</v>
-      </c>
-      <c r="Z115" s="13">
-        <v>0</v>
-      </c>
-      <c r="AA115" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB115" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="AC115" s="12">
-        <v>10000</v>
-      </c>
-      <c r="AD115" s="12">
-        <v>10000</v>
-      </c>
-      <c r="AE115" s="12">
-        <v>0</v>
+      <c r="S115" s="7">
+        <v>-5000</v>
+      </c>
+      <c r="T115" s="7">
+        <v>1</v>
+      </c>
+      <c r="U115" s="7">
+        <v>30000</v>
+      </c>
+      <c r="V115" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="W115" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="X115" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="Y115" s="14">
+        <v>216001001</v>
+      </c>
+      <c r="Z115" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA115" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB115" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="AC115" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AD115" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AE115" s="7">
+        <v>25010001</v>
       </c>
       <c r="AF115" s="4">
         <v>40</v>
       </c>
       <c r="AG115" s="4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH115" s="4">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="AI115" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ115" s="4">
         <v>0</v>
@@ -14714,30 +13916,30 @@
   <sheetData>
     <row r="6" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="C6" t="s">
-        <v>172</v>
+        <v>147</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
       <c r="F6"/>
       <c r="G6" t="s">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="J6" t="s">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="K6"/>
       <c r="L6"/>
       <c r="M6"/>
       <c r="N6" s="1" t="s">
-        <v>175</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="B7">
         <v>1000003</v>
@@ -14747,7 +13949,7 @@
         <v>20030001</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E7" t="str">
         <f t="shared" ref="E7:E14" si="0">LEFT(D7,3)</f>
@@ -14758,16 +13960,16 @@
         <v>3</v>
       </c>
       <c r="G7" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="J7">
         <v>990101</v>
       </c>
       <c r="K7" t="s">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="L7" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="M7">
         <v>1</v>
@@ -14776,12 +13978,12 @@
         <v>20010001</v>
       </c>
       <c r="O7" s="9" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A8" s="12" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="B8">
         <v>1000004</v>
@@ -14791,7 +13993,7 @@
         <v>20030001</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E8" t="str">
         <f t="shared" si="0"/>
@@ -14802,16 +14004,16 @@
         <v>3</v>
       </c>
       <c r="G8" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="J8">
         <v>990102</v>
       </c>
       <c r="K8" t="s">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="L8" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="M8">
         <v>1</v>
@@ -14820,12 +14022,12 @@
         <v>20010002</v>
       </c>
       <c r="O8" s="9" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="B9">
         <v>1000005</v>
@@ -14835,7 +14037,7 @@
         <v>20030001</v>
       </c>
       <c r="D9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E9" t="str">
         <f t="shared" si="0"/>
@@ -14846,16 +14048,16 @@
         <v>3</v>
       </c>
       <c r="G9" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="J9">
         <v>990201</v>
       </c>
       <c r="K9" t="s">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="L9" t="s">
-        <v>168</v>
+        <v>143</v>
       </c>
       <c r="M9">
         <v>2</v>
@@ -14864,12 +14066,12 @@
         <v>20020001</v>
       </c>
       <c r="O9" s="9" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A10" s="12" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="B10">
         <v>1000006</v>
@@ -14879,7 +14081,7 @@
         <v>20030001</v>
       </c>
       <c r="D10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E10" t="str">
         <f t="shared" si="0"/>
@@ -14890,16 +14092,16 @@
         <v>3</v>
       </c>
       <c r="G10" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="J10">
         <v>990202</v>
       </c>
       <c r="K10" t="s">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="L10" t="s">
-        <v>168</v>
+        <v>143</v>
       </c>
       <c r="M10">
         <v>2</v>
@@ -14908,12 +14110,12 @@
         <v>20020002</v>
       </c>
       <c r="O10" s="9" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="B11">
         <v>1000007</v>
@@ -14923,7 +14125,7 @@
         <v>20040001</v>
       </c>
       <c r="D11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E11" t="str">
         <f t="shared" si="0"/>
@@ -14934,16 +14136,16 @@
         <v>4</v>
       </c>
       <c r="G11" t="s">
-        <v>162</v>
+        <v>137</v>
       </c>
       <c r="J11">
         <v>990301</v>
       </c>
       <c r="K11" t="s">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="L11" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="M11">
         <v>3</v>
@@ -14952,12 +14154,12 @@
         <v>20030001</v>
       </c>
       <c r="O11" s="9" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="B12">
         <v>1000008</v>
@@ -14967,7 +14169,7 @@
         <v>20040001</v>
       </c>
       <c r="D12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E12" t="str">
         <f t="shared" si="0"/>
@@ -14978,16 +14180,16 @@
         <v>4</v>
       </c>
       <c r="G12" t="s">
-        <v>162</v>
+        <v>137</v>
       </c>
       <c r="J12">
         <v>990302</v>
       </c>
       <c r="K12" t="s">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="L12" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="M12">
         <v>3</v>
@@ -14996,12 +14198,12 @@
         <v>20030002</v>
       </c>
       <c r="O12" s="9" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="B13">
         <v>1000009</v>
@@ -15011,7 +14213,7 @@
         <v>20040001</v>
       </c>
       <c r="D13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E13" t="str">
         <f t="shared" si="0"/>
@@ -15022,16 +14224,16 @@
         <v>4</v>
       </c>
       <c r="G13" t="s">
-        <v>162</v>
+        <v>137</v>
       </c>
       <c r="J13">
         <v>990401</v>
       </c>
       <c r="K13" t="s">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="L13" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="M13">
         <v>4</v>
@@ -15040,12 +14242,12 @@
         <v>20040001</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>174</v>
+        <v>149</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="B14">
         <v>1000010</v>
@@ -15055,7 +14257,7 @@
         <v>20040001</v>
       </c>
       <c r="D14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E14" t="str">
         <f t="shared" si="0"/>
@@ -15066,16 +14268,16 @@
         <v>4</v>
       </c>
       <c r="G14" t="s">
-        <v>162</v>
+        <v>137</v>
       </c>
       <c r="J14">
         <v>990402</v>
       </c>
       <c r="K14" t="s">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="L14" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="M14">
         <v>4</v>
@@ -15084,12 +14286,12 @@
         <v>20040002</v>
       </c>
       <c r="O14" s="9" t="s">
-        <v>174</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="B15">
         <v>1000011</v>
@@ -15099,26 +14301,26 @@
         <v>20050001</v>
       </c>
       <c r="D15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E15" t="s">
-        <v>161</v>
+        <v>136</v>
       </c>
       <c r="F15">
         <f>VLOOKUP(E15,备注资源组与动作id!$L$7:$M$16,2,FALSE)</f>
         <v>5</v>
       </c>
       <c r="G15" t="s">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="J15">
         <v>990501</v>
       </c>
       <c r="K15" t="s">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="L15" t="s">
-        <v>161</v>
+        <v>136</v>
       </c>
       <c r="M15">
         <v>5</v>
@@ -15127,12 +14329,12 @@
         <v>20050001</v>
       </c>
       <c r="O15" s="9" t="s">
-        <v>161</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A16" s="12" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="B16">
         <v>1000012</v>
@@ -15142,26 +14344,26 @@
         <v>20050001</v>
       </c>
       <c r="D16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E16" t="s">
-        <v>161</v>
+        <v>136</v>
       </c>
       <c r="F16">
         <f>VLOOKUP(E16,备注资源组与动作id!$L$7:$M$16,2,FALSE)</f>
         <v>5</v>
       </c>
       <c r="G16" t="s">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="J16">
         <v>990502</v>
       </c>
       <c r="K16" t="s">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="L16" t="s">
-        <v>161</v>
+        <v>136</v>
       </c>
       <c r="M16">
         <v>5</v>
@@ -15170,12 +14372,12 @@
         <v>20050002</v>
       </c>
       <c r="O16" s="9" t="s">
-        <v>161</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="B17">
         <v>1000013</v>
@@ -15185,22 +14387,22 @@
         <v>20050001</v>
       </c>
       <c r="D17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E17" t="s">
-        <v>161</v>
+        <v>136</v>
       </c>
       <c r="F17">
         <f>VLOOKUP(E17,备注资源组与动作id!$L$7:$M$16,2,FALSE)</f>
         <v>5</v>
       </c>
       <c r="G17" t="s">
-        <v>160</v>
+        <v>135</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A18" s="12" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="B18">
         <v>1000014</v>
@@ -15210,22 +14412,22 @@
         <v>20050001</v>
       </c>
       <c r="D18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E18" t="s">
-        <v>161</v>
+        <v>136</v>
       </c>
       <c r="F18">
         <f>VLOOKUP(E18,备注资源组与动作id!$L$7:$M$16,2,FALSE)</f>
         <v>5</v>
       </c>
       <c r="G18" t="s">
-        <v>160</v>
+        <v>135</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="B19">
         <v>1000101</v>
@@ -15235,7 +14437,7 @@
         <v>20010001</v>
       </c>
       <c r="D19" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E19" t="str">
         <f>LEFT(D19,3)</f>
@@ -15246,12 +14448,12 @@
         <v>1</v>
       </c>
       <c r="G19" t="s">
-        <v>159</v>
+        <v>134</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A20" s="12" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="B20">
         <v>1000102</v>
@@ -15261,7 +14463,7 @@
         <v>20010001</v>
       </c>
       <c r="D20" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E20" t="str">
         <f>LEFT(D20,3)</f>
@@ -15272,12 +14474,12 @@
         <v>1</v>
       </c>
       <c r="G20" t="s">
-        <v>159</v>
+        <v>134</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="B21">
         <v>1000103</v>
@@ -15287,7 +14489,7 @@
         <v>20020001</v>
       </c>
       <c r="D21" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E21" t="str">
         <f>LEFT(D21,3)</f>
@@ -15298,12 +14500,12 @@
         <v>2</v>
       </c>
       <c r="G21" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A22" s="12" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="B22">
         <v>1000104</v>
@@ -15313,7 +14515,7 @@
         <v>20020001</v>
       </c>
       <c r="D22" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E22" t="str">
         <f>LEFT(D22,3)</f>
@@ -15324,7 +14526,7 @@
         <v>2</v>
       </c>
       <c r="G22" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -15341,31 +14543,31 @@
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C2" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="F2" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="G2" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="H2" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="I2" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="J2" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="K2" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.2">

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D27597C-2246-4B15-AEC4-3B9FF40EDC1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42C8A7C2-5515-408D-9719-04E6C3A2F583}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="198">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -723,6 +723,9 @@
   <si>
     <t>石像鬼精英</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:22_2:22_3:22_4:22_5:22_6:22_7:22_8:22_9:22_10:22_11:22_12:22_13:22_14:22_15:22_16:22_17:22_18:22_19:22_20:22_21:22_22:22_23:22_24:22_25:22_26:22_27:22_28:22_29:22_30:22_31:22_32:22_33:22_34:22_35:22_36:22_37:22_38:22_39:22_40:22_41:22_42:22_43:22_44:22_45:22_46:22_47:22_48:22_49:22_50:22_51:22_52:22_53:22_54:22_55:22_56:22_57:22_58:22_59:22_60:22_61:22_62:22_63:22_64:22_65:22_66:22_67:22_68:22_69:22_70:22_71:22_72:22_73:22_74:22_75:22_76:22_77:22_78:22_79:22_80:22_81:22_82:22_83:22_84:22_85:22_86:22_87:22_88:22_89:22_90:22_91:22_92:22_93:22_94:22_95:22_96:22_97:22_98:22_99:22_100:22_101:22_102:22_103:22_104:22_105:22_106:22_107:22_108:22_109:22_110:22_111:22_112:22_113:22_114:22_115:22_116:22_117:22_118:22_119:22_120:22_121:22_122:22_123:22_124:22_125:22_126:22_127:22_128:22_129:22_130:22_131:22_132:22_133:22_134:22_135:22_136:22_137:22_138:22_139:22_140:22_141:22_142:22_143:22_144:22_145:22_146:22_147:22_148:22_149:22_150:22_151:22_152:22_153:22_154:22_155:22_156:22_157:22_158:22_159:22_160:22</t>
   </si>
 </sst>
 </file>
@@ -8533,13 +8536,13 @@
         <v>0</v>
       </c>
       <c r="P71" s="7">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="Q71" s="7">
         <v>0</v>
       </c>
       <c r="R71" s="7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="S71" s="7">
         <v>-5000</v>
@@ -8557,7 +8560,7 @@
         <v>120</v>
       </c>
       <c r="X71" s="7" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="Y71" s="14">
         <v>201001011</v>
@@ -8636,13 +8639,13 @@
         <v>0</v>
       </c>
       <c r="P72" s="7">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="Q72" s="7">
         <v>2</v>
       </c>
       <c r="R72" s="7">
-        <v>230</v>
+        <v>281</v>
       </c>
       <c r="S72" s="7">
         <v>-5000</v>
@@ -8660,7 +8663,7 @@
         <v>120</v>
       </c>
       <c r="X72" s="7" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="Y72" s="14">
         <v>201002011</v>
@@ -8764,7 +8767,7 @@
         <v>120</v>
       </c>
       <c r="X73" s="12" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="Y73" s="13">
         <v>20010001</v>
@@ -8843,13 +8846,13 @@
         <v>0</v>
       </c>
       <c r="P74" s="7">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="Q74" s="7">
         <v>0</v>
       </c>
       <c r="R74" s="7">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="S74" s="7">
         <v>-5000</v>
@@ -8867,7 +8870,7 @@
         <v>120</v>
       </c>
       <c r="X74" s="7" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="Y74" s="14">
         <v>201004011</v>
@@ -8946,13 +8949,13 @@
         <v>0</v>
       </c>
       <c r="P75" s="7">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Q75" s="7">
         <v>1</v>
       </c>
       <c r="R75" s="7">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="S75" s="7">
         <v>-5000</v>
@@ -8970,7 +8973,7 @@
         <v>120</v>
       </c>
       <c r="X75" s="7" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="Y75" s="14">
         <v>214001011</v>
@@ -10088,13 +10091,13 @@
         <v>0</v>
       </c>
       <c r="P86" s="7">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="Q86" s="7">
         <v>0</v>
       </c>
       <c r="R86" s="7">
-        <v>18</v>
+        <v>251</v>
       </c>
       <c r="S86" s="7">
         <v>-5000</v>
@@ -10112,7 +10115,7 @@
         <v>120</v>
       </c>
       <c r="X86" s="7" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="Y86" s="14">
         <v>201001011</v>
@@ -10191,13 +10194,13 @@
         <v>0</v>
       </c>
       <c r="P87" s="7">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="Q87" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R87" s="7">
-        <v>230</v>
+        <v>1343</v>
       </c>
       <c r="S87" s="7">
         <v>-5000</v>
@@ -10215,7 +10218,7 @@
         <v>120</v>
       </c>
       <c r="X87" s="7" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="Y87" s="14">
         <v>201002011</v>
@@ -10319,7 +10322,7 @@
         <v>120</v>
       </c>
       <c r="X88" s="12" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="Y88" s="13">
         <v>20010001</v>
@@ -10398,13 +10401,13 @@
         <v>0</v>
       </c>
       <c r="P89" s="7">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="Q89" s="7">
         <v>0</v>
       </c>
       <c r="R89" s="7">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="S89" s="7">
         <v>-5000</v>
@@ -10422,7 +10425,7 @@
         <v>120</v>
       </c>
       <c r="X89" s="7" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="Y89" s="14">
         <v>201004011</v>
@@ -10501,13 +10504,13 @@
         <v>0</v>
       </c>
       <c r="P90" s="7">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="Q90" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R90" s="7">
-        <v>48</v>
+        <v>354</v>
       </c>
       <c r="S90" s="7">
         <v>-5000</v>
@@ -10525,7 +10528,7 @@
         <v>120</v>
       </c>
       <c r="X90" s="7" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="Y90" s="14">
         <v>214001011</v>
@@ -11643,13 +11646,13 @@
         <v>0</v>
       </c>
       <c r="P101" s="7">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="Q101" s="7">
         <v>0</v>
       </c>
       <c r="R101" s="7">
-        <v>18</v>
+        <v>623</v>
       </c>
       <c r="S101" s="7">
         <v>-5000</v>
@@ -11667,7 +11670,7 @@
         <v>120</v>
       </c>
       <c r="X101" s="7" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="Y101" s="14">
         <v>201001011</v>
@@ -11746,13 +11749,13 @@
         <v>0</v>
       </c>
       <c r="P102" s="7">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="Q102" s="7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R102" s="7">
-        <v>230</v>
+        <v>2647</v>
       </c>
       <c r="S102" s="7">
         <v>-5000</v>
@@ -11770,7 +11773,7 @@
         <v>120</v>
       </c>
       <c r="X102" s="7" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="Y102" s="14">
         <v>201002011</v>
@@ -11874,7 +11877,7 @@
         <v>120</v>
       </c>
       <c r="X103" s="12" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="Y103" s="13">
         <v>20010001</v>
@@ -11953,13 +11956,13 @@
         <v>0</v>
       </c>
       <c r="P104" s="7">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="Q104" s="7">
         <v>0</v>
       </c>
       <c r="R104" s="7">
-        <v>15</v>
+        <v>519</v>
       </c>
       <c r="S104" s="7">
         <v>-5000</v>
@@ -11977,7 +11980,7 @@
         <v>120</v>
       </c>
       <c r="X104" s="7" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="Y104" s="14">
         <v>201004011</v>
@@ -12056,13 +12059,13 @@
         <v>0</v>
       </c>
       <c r="P105" s="7">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="Q105" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R105" s="7">
-        <v>48</v>
+        <v>822</v>
       </c>
       <c r="S105" s="7">
         <v>-5000</v>
@@ -12080,7 +12083,7 @@
         <v>120</v>
       </c>
       <c r="X105" s="7" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="Y105" s="14">
         <v>214001011</v>
@@ -13094,13 +13097,13 @@
         <v>0</v>
       </c>
       <c r="P115" s="7">
-        <v>15</v>
+        <v>86</v>
       </c>
       <c r="Q115" s="7">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R115" s="16">
-        <v>36</v>
+        <v>11989</v>
       </c>
       <c r="S115" s="7">
         <v>-5000</v>
@@ -13118,7 +13121,7 @@
         <v>120</v>
       </c>
       <c r="X115" s="7" t="s">
-        <v>123</v>
+        <v>173</v>
       </c>
       <c r="Y115" s="14">
         <v>216001001</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42C8A7C2-5515-408D-9719-04E6C3A2F583}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AFB2EF4-36A0-4212-9B31-638A93B4438C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8545,7 +8545,7 @@
         <v>20</v>
       </c>
       <c r="S71" s="7">
-        <v>-5000</v>
+        <v>-7000</v>
       </c>
       <c r="T71" s="7">
         <v>1</v>
@@ -8648,7 +8648,7 @@
         <v>281</v>
       </c>
       <c r="S72" s="7">
-        <v>-5000</v>
+        <v>-7000</v>
       </c>
       <c r="T72" s="7">
         <v>1</v>
@@ -8752,7 +8752,7 @@
         <v>300</v>
       </c>
       <c r="S73" s="12">
-        <v>-5000</v>
+        <v>-7000</v>
       </c>
       <c r="T73" s="12">
         <v>1</v>
@@ -8855,7 +8855,7 @@
         <v>17</v>
       </c>
       <c r="S74" s="7">
-        <v>-5000</v>
+        <v>-7000</v>
       </c>
       <c r="T74" s="7">
         <v>1</v>
@@ -8958,7 +8958,7 @@
         <v>53</v>
       </c>
       <c r="S75" s="7">
-        <v>-5000</v>
+        <v>-7000</v>
       </c>
       <c r="T75" s="7">
         <v>1</v>
@@ -9062,7 +9062,7 @@
         <v>36</v>
       </c>
       <c r="S76" s="12">
-        <v>-5000</v>
+        <v>-7000</v>
       </c>
       <c r="T76" s="12">
         <v>1</v>
@@ -9166,7 +9166,7 @@
         <v>36</v>
       </c>
       <c r="S77" s="12">
-        <v>-5000</v>
+        <v>-7000</v>
       </c>
       <c r="T77" s="12">
         <v>1</v>
@@ -9270,7 +9270,7 @@
         <v>36</v>
       </c>
       <c r="S78" s="12">
-        <v>-5000</v>
+        <v>-7000</v>
       </c>
       <c r="T78" s="12">
         <v>1</v>
@@ -9374,7 +9374,7 @@
         <v>36</v>
       </c>
       <c r="S79" s="12">
-        <v>-5000</v>
+        <v>-7000</v>
       </c>
       <c r="T79" s="12">
         <v>1</v>
@@ -9478,7 +9478,7 @@
         <v>36</v>
       </c>
       <c r="S80" s="12">
-        <v>-5000</v>
+        <v>-7000</v>
       </c>
       <c r="T80" s="12">
         <v>1</v>
@@ -9582,7 +9582,7 @@
         <v>36</v>
       </c>
       <c r="S81" s="12">
-        <v>-5000</v>
+        <v>-7000</v>
       </c>
       <c r="T81" s="12">
         <v>1</v>
@@ -9686,7 +9686,7 @@
         <v>36</v>
       </c>
       <c r="S82" s="12">
-        <v>-5000</v>
+        <v>-7000</v>
       </c>
       <c r="T82" s="12">
         <v>1</v>
@@ -9789,7 +9789,7 @@
         <v>1496</v>
       </c>
       <c r="S83" s="7">
-        <v>-5000</v>
+        <v>-7000</v>
       </c>
       <c r="T83" s="7">
         <v>1</v>
@@ -9893,7 +9893,7 @@
         <v>36</v>
       </c>
       <c r="S84" s="12">
-        <v>-5000</v>
+        <v>-7000</v>
       </c>
       <c r="T84" s="12">
         <v>1</v>
@@ -9997,7 +9997,7 @@
         <v>36</v>
       </c>
       <c r="S85" s="12">
-        <v>-5000</v>
+        <v>-7000</v>
       </c>
       <c r="T85" s="12">
         <v>1</v>
@@ -10100,7 +10100,7 @@
         <v>251</v>
       </c>
       <c r="S86" s="7">
-        <v>-5000</v>
+        <v>-7000</v>
       </c>
       <c r="T86" s="7">
         <v>1</v>
@@ -10203,7 +10203,7 @@
         <v>1343</v>
       </c>
       <c r="S87" s="7">
-        <v>-5000</v>
+        <v>-7000</v>
       </c>
       <c r="T87" s="7">
         <v>1</v>
@@ -10307,7 +10307,7 @@
         <v>300</v>
       </c>
       <c r="S88" s="12">
-        <v>-5000</v>
+        <v>-7000</v>
       </c>
       <c r="T88" s="12">
         <v>1</v>
@@ -10410,7 +10410,7 @@
         <v>23</v>
       </c>
       <c r="S89" s="7">
-        <v>-5000</v>
+        <v>-7000</v>
       </c>
       <c r="T89" s="7">
         <v>1</v>
@@ -10513,7 +10513,7 @@
         <v>354</v>
       </c>
       <c r="S90" s="7">
-        <v>-5000</v>
+        <v>-7000</v>
       </c>
       <c r="T90" s="7">
         <v>1</v>
@@ -10617,7 +10617,7 @@
         <v>36</v>
       </c>
       <c r="S91" s="12">
-        <v>-5000</v>
+        <v>-7000</v>
       </c>
       <c r="T91" s="12">
         <v>1</v>
@@ -10721,7 +10721,7 @@
         <v>36</v>
       </c>
       <c r="S92" s="12">
-        <v>-5000</v>
+        <v>-7000</v>
       </c>
       <c r="T92" s="12">
         <v>1</v>
@@ -10825,7 +10825,7 @@
         <v>36</v>
       </c>
       <c r="S93" s="12">
-        <v>-5000</v>
+        <v>-7000</v>
       </c>
       <c r="T93" s="12">
         <v>1</v>
@@ -10929,7 +10929,7 @@
         <v>36</v>
       </c>
       <c r="S94" s="12">
-        <v>-5000</v>
+        <v>-7000</v>
       </c>
       <c r="T94" s="12">
         <v>1</v>
@@ -11033,7 +11033,7 @@
         <v>36</v>
       </c>
       <c r="S95" s="12">
-        <v>-5000</v>
+        <v>-7000</v>
       </c>
       <c r="T95" s="12">
         <v>1</v>
@@ -11137,7 +11137,7 @@
         <v>36</v>
       </c>
       <c r="S96" s="12">
-        <v>-5000</v>
+        <v>-7000</v>
       </c>
       <c r="T96" s="12">
         <v>1</v>
@@ -11241,7 +11241,7 @@
         <v>36</v>
       </c>
       <c r="S97" s="12">
-        <v>-5000</v>
+        <v>-7000</v>
       </c>
       <c r="T97" s="12">
         <v>1</v>
@@ -11344,7 +11344,7 @@
         <v>1496</v>
       </c>
       <c r="S98" s="7">
-        <v>-5000</v>
+        <v>-7000</v>
       </c>
       <c r="T98" s="7">
         <v>1</v>
@@ -11448,7 +11448,7 @@
         <v>36</v>
       </c>
       <c r="S99" s="12">
-        <v>-5000</v>
+        <v>-7000</v>
       </c>
       <c r="T99" s="12">
         <v>1</v>
@@ -11552,7 +11552,7 @@
         <v>36</v>
       </c>
       <c r="S100" s="12">
-        <v>-5000</v>
+        <v>-7000</v>
       </c>
       <c r="T100" s="12">
         <v>1</v>
@@ -11655,7 +11655,7 @@
         <v>623</v>
       </c>
       <c r="S101" s="7">
-        <v>-5000</v>
+        <v>-7000</v>
       </c>
       <c r="T101" s="7">
         <v>1</v>
@@ -11758,7 +11758,7 @@
         <v>2647</v>
       </c>
       <c r="S102" s="7">
-        <v>-5000</v>
+        <v>-7000</v>
       </c>
       <c r="T102" s="7">
         <v>1</v>
@@ -11862,7 +11862,7 @@
         <v>300</v>
       </c>
       <c r="S103" s="12">
-        <v>-5000</v>
+        <v>-7000</v>
       </c>
       <c r="T103" s="12">
         <v>1</v>
@@ -11965,7 +11965,7 @@
         <v>519</v>
       </c>
       <c r="S104" s="7">
-        <v>-5000</v>
+        <v>-7000</v>
       </c>
       <c r="T104" s="7">
         <v>1</v>
@@ -12068,7 +12068,7 @@
         <v>822</v>
       </c>
       <c r="S105" s="7">
-        <v>-5000</v>
+        <v>-7000</v>
       </c>
       <c r="T105" s="7">
         <v>1</v>
@@ -12172,7 +12172,7 @@
         <v>36</v>
       </c>
       <c r="S106" s="12">
-        <v>-5000</v>
+        <v>-7000</v>
       </c>
       <c r="T106" s="12">
         <v>1</v>
@@ -12276,7 +12276,7 @@
         <v>36</v>
       </c>
       <c r="S107" s="12">
-        <v>-5000</v>
+        <v>-7000</v>
       </c>
       <c r="T107" s="12">
         <v>1</v>
@@ -12380,7 +12380,7 @@
         <v>36</v>
       </c>
       <c r="S108" s="12">
-        <v>-5000</v>
+        <v>-7000</v>
       </c>
       <c r="T108" s="12">
         <v>1</v>
@@ -12484,7 +12484,7 @@
         <v>36</v>
       </c>
       <c r="S109" s="12">
-        <v>-5000</v>
+        <v>-7000</v>
       </c>
       <c r="T109" s="12">
         <v>1</v>
@@ -12588,7 +12588,7 @@
         <v>36</v>
       </c>
       <c r="S110" s="12">
-        <v>-5000</v>
+        <v>-7000</v>
       </c>
       <c r="T110" s="12">
         <v>1</v>
@@ -12692,7 +12692,7 @@
         <v>36</v>
       </c>
       <c r="S111" s="12">
-        <v>-5000</v>
+        <v>-7000</v>
       </c>
       <c r="T111" s="12">
         <v>1</v>
@@ -12796,7 +12796,7 @@
         <v>36</v>
       </c>
       <c r="S112" s="12">
-        <v>-5000</v>
+        <v>-7000</v>
       </c>
       <c r="T112" s="12">
         <v>1</v>
@@ -12899,7 +12899,7 @@
         <v>1496</v>
       </c>
       <c r="S113" s="7">
-        <v>-5000</v>
+        <v>-7000</v>
       </c>
       <c r="T113" s="7">
         <v>1</v>
@@ -13003,7 +13003,7 @@
         <v>36</v>
       </c>
       <c r="S114" s="12">
-        <v>-5000</v>
+        <v>-7000</v>
       </c>
       <c r="T114" s="12">
         <v>1</v>
@@ -13106,7 +13106,7 @@
         <v>11989</v>
       </c>
       <c r="S115" s="7">
-        <v>-5000</v>
+        <v>-7000</v>
       </c>
       <c r="T115" s="7">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AFB2EF4-36A0-4212-9B31-638A93B4438C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C2EDCE0-B938-4978-B605-75C5D28E9EA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_foe_v8" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="204">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -726,6 +726,30 @@
   </si>
   <si>
     <t>1:22_2:22_3:22_4:22_5:22_6:22_7:22_8:22_9:22_10:22_11:22_12:22_13:22_14:22_15:22_16:22_17:22_18:22_19:22_20:22_21:22_22:22_23:22_24:22_25:22_26:22_27:22_28:22_29:22_30:22_31:22_32:22_33:22_34:22_35:22_36:22_37:22_38:22_39:22_40:22_41:22_42:22_43:22_44:22_45:22_46:22_47:22_48:22_49:22_50:22_51:22_52:22_53:22_54:22_55:22_56:22_57:22_58:22_59:22_60:22_61:22_62:22_63:22_64:22_65:22_66:22_67:22_68:22_69:22_70:22_71:22_72:22_73:22_74:22_75:22_76:22_77:22_78:22_79:22_80:22_81:22_82:22_83:22_84:22_85:22_86:22_87:22_88:22_89:22_90:22_91:22_92:22_93:22_94:22_95:22_96:22_97:22_98:22_99:22_100:22_101:22_102:22_103:22_104:22_105:22_106:22_107:22_108:22_109:22_110:22_111:22_112:22_113:22_114:22_115:22_116:22_117:22_118:22_119:22_120:22_121:22_122:22_123:22_124:22_125:22_126:22_127:22_128:22_129:22_130:22_131:22_132:22_133:22_134:22_135:22_136:22_137:22_138:22_139:22_140:22_141:22_142:22_143:22_144:22_145:22_146:22_147:22_148:22_149:22_150:22_151:22_152:22_153:22_154:22_155:22_156:22_157:22_158:22_159:22_160:22</t>
+  </si>
+  <si>
+    <t>僵尸等级1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>僵尸等级3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>狼等级1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>狼等级2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>沉沦魔等级1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>沉沦魔等级2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -6283,7 +6307,7 @@
         <v>174</v>
       </c>
       <c r="Y49" s="13">
-        <v>20010001</v>
+        <v>201001011</v>
       </c>
       <c r="Z49" s="13">
         <v>0</v>
@@ -6593,7 +6617,7 @@
         <v>123</v>
       </c>
       <c r="Y52" s="13">
-        <v>20040001</v>
+        <v>201001011</v>
       </c>
       <c r="Z52" s="13">
         <v>0</v>
@@ -6697,7 +6721,7 @@
         <v>123</v>
       </c>
       <c r="Y53" s="13">
-        <v>20030001</v>
+        <v>201001011</v>
       </c>
       <c r="Z53" s="13">
         <v>0</v>
@@ -6801,7 +6825,7 @@
         <v>123</v>
       </c>
       <c r="Y54" s="13">
-        <v>20030001</v>
+        <v>201001011</v>
       </c>
       <c r="Z54" s="13">
         <v>0</v>
@@ -6905,7 +6929,7 @@
         <v>123</v>
       </c>
       <c r="Y55" s="13">
-        <v>20030001</v>
+        <v>201001011</v>
       </c>
       <c r="Z55" s="13">
         <v>0</v>
@@ -7009,7 +7033,7 @@
         <v>123</v>
       </c>
       <c r="Y56" s="13">
-        <v>20020001</v>
+        <v>201001011</v>
       </c>
       <c r="Z56" s="13">
         <v>0</v>
@@ -7113,7 +7137,7 @@
         <v>123</v>
       </c>
       <c r="Y57" s="13">
-        <v>20020001</v>
+        <v>201001011</v>
       </c>
       <c r="Z57" s="13">
         <v>0</v>
@@ -7217,7 +7241,7 @@
         <v>123</v>
       </c>
       <c r="Y58" s="13">
-        <v>20020001</v>
+        <v>201001011</v>
       </c>
       <c r="Z58" s="13">
         <v>0</v>
@@ -7424,7 +7448,7 @@
         <v>123</v>
       </c>
       <c r="Y60" s="13">
-        <v>20050001</v>
+        <v>201001011</v>
       </c>
       <c r="Z60" s="13">
         <v>0</v>
@@ -7528,7 +7552,7 @@
         <v>123</v>
       </c>
       <c r="Y61" s="13">
-        <v>20050001</v>
+        <v>201001011</v>
       </c>
       <c r="Z61" s="13">
         <v>0</v>
@@ -8727,9 +8751,7 @@
       <c r="J73" s="12">
         <v>0</v>
       </c>
-      <c r="K73" s="12" t="s">
-        <v>160</v>
-      </c>
+      <c r="K73" s="12"/>
       <c r="L73" s="12">
         <v>800001021</v>
       </c>
@@ -8770,7 +8792,7 @@
         <v>197</v>
       </c>
       <c r="Y73" s="13">
-        <v>20010001</v>
+        <v>201001011</v>
       </c>
       <c r="Z73" s="13">
         <v>0</v>
@@ -9037,9 +9059,7 @@
       <c r="J76" s="12">
         <v>0</v>
       </c>
-      <c r="K76" s="12" t="s">
-        <v>165</v>
-      </c>
+      <c r="K76" s="12"/>
       <c r="L76" s="12">
         <v>1000010</v>
       </c>
@@ -9079,8 +9099,8 @@
       <c r="X76" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="Y76" s="13">
-        <v>20040001</v>
+      <c r="Y76" s="12">
+        <v>201002011</v>
       </c>
       <c r="Z76" s="13">
         <v>0</v>
@@ -9141,9 +9161,7 @@
       <c r="J77" s="12">
         <v>0</v>
       </c>
-      <c r="K77" s="12" t="s">
-        <v>72</v>
-      </c>
+      <c r="K77" s="12"/>
       <c r="L77" s="12">
         <v>1000006</v>
       </c>
@@ -9183,8 +9201,8 @@
       <c r="X77" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="Y77" s="13">
-        <v>20030001</v>
+      <c r="Y77" s="12">
+        <v>201002011</v>
       </c>
       <c r="Z77" s="13">
         <v>0</v>
@@ -9220,92 +9238,91 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A78" s="12">
+    <row r="78" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A78" s="7">
         <v>301108</v>
       </c>
-      <c r="B78" s="12">
+      <c r="B78" s="7">
         <v>30</v>
       </c>
-      <c r="C78" s="12" t="s">
+      <c r="C78" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="D78" s="12"/>
-      <c r="E78" s="6"/>
-      <c r="F78" s="12"/>
-      <c r="G78" s="12">
+      <c r="D78" s="7"/>
+      <c r="F78" s="7"/>
+      <c r="G78" s="7">
         <v>12</v>
       </c>
-      <c r="H78" s="12">
-        <v>1</v>
-      </c>
-      <c r="I78" s="12" t="s">
+      <c r="H78" s="7">
+        <v>1</v>
+      </c>
+      <c r="I78" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="J78" s="12">
-        <v>0</v>
-      </c>
-      <c r="K78" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="L78" s="12">
-        <v>1000006</v>
-      </c>
-      <c r="M78" s="12">
-        <v>1</v>
-      </c>
-      <c r="N78" s="12">
+      <c r="J78" s="7">
+        <v>0</v>
+      </c>
+      <c r="K78" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="L78" s="7">
+        <v>800004011</v>
+      </c>
+      <c r="M78" s="7">
+        <v>1</v>
+      </c>
+      <c r="N78" s="7">
         <v>100</v>
       </c>
-      <c r="O78" s="12">
-        <v>0</v>
-      </c>
-      <c r="P78" s="12">
+      <c r="O78" s="7">
+        <v>0</v>
+      </c>
+      <c r="P78" s="7">
         <v>15</v>
       </c>
-      <c r="Q78" s="12">
-        <v>0</v>
-      </c>
-      <c r="R78" s="12">
+      <c r="Q78" s="7">
+        <v>0</v>
+      </c>
+      <c r="R78" s="16">
         <v>36</v>
       </c>
-      <c r="S78" s="12">
+      <c r="S78" s="7">
         <v>-7000</v>
       </c>
-      <c r="T78" s="12">
-        <v>1</v>
-      </c>
-      <c r="U78" s="12">
-        <v>0</v>
-      </c>
-      <c r="V78" s="12" t="s">
+      <c r="T78" s="7">
+        <v>1</v>
+      </c>
+      <c r="U78" s="7">
+        <v>0</v>
+      </c>
+      <c r="V78" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="W78" s="12" t="s">
+      <c r="W78" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="X78" s="12" t="s">
+      <c r="X78" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="Y78" s="13">
-        <v>20030001</v>
-      </c>
-      <c r="Z78" s="13">
-        <v>0</v>
-      </c>
-      <c r="AA78" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB78" s="6" t="s">
+      <c r="Y78" s="14">
+        <v>204001001</v>
+      </c>
+      <c r="Z78" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA78" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB78" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="AC78" s="12">
-        <v>10000</v>
-      </c>
-      <c r="AD78" s="12">
-        <v>10000</v>
-      </c>
-      <c r="AE78" s="12">
+      <c r="AC78" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AD78" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AE78" s="7">
         <v>25010001</v>
       </c>
       <c r="AF78" s="4">
@@ -9324,92 +9341,91 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A79" s="12">
+    <row r="79" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A79" s="7">
         <v>301109</v>
       </c>
-      <c r="B79" s="12">
+      <c r="B79" s="7">
         <v>30</v>
       </c>
-      <c r="C79" s="12" t="s">
+      <c r="C79" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="D79" s="12"/>
-      <c r="E79" s="6"/>
-      <c r="F79" s="12"/>
-      <c r="G79" s="12">
+      <c r="D79" s="7"/>
+      <c r="F79" s="7"/>
+      <c r="G79" s="7">
         <v>12</v>
       </c>
-      <c r="H79" s="12">
-        <v>1</v>
-      </c>
-      <c r="I79" s="12" t="s">
+      <c r="H79" s="7">
+        <v>1</v>
+      </c>
+      <c r="I79" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="J79" s="12">
-        <v>0</v>
-      </c>
-      <c r="K79" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="L79" s="12">
-        <v>1000006</v>
-      </c>
-      <c r="M79" s="12">
-        <v>1</v>
-      </c>
-      <c r="N79" s="12">
+      <c r="J79" s="7">
+        <v>0</v>
+      </c>
+      <c r="K79" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="L79" s="7">
+        <v>800004021</v>
+      </c>
+      <c r="M79" s="7">
+        <v>1</v>
+      </c>
+      <c r="N79" s="7">
         <v>100</v>
       </c>
-      <c r="O79" s="12">
-        <v>0</v>
-      </c>
-      <c r="P79" s="12">
+      <c r="O79" s="7">
+        <v>0</v>
+      </c>
+      <c r="P79" s="7">
         <v>15</v>
       </c>
-      <c r="Q79" s="12">
-        <v>0</v>
-      </c>
-      <c r="R79" s="12">
+      <c r="Q79" s="7">
+        <v>0</v>
+      </c>
+      <c r="R79" s="16">
         <v>36</v>
       </c>
-      <c r="S79" s="12">
+      <c r="S79" s="7">
         <v>-7000</v>
       </c>
-      <c r="T79" s="12">
-        <v>1</v>
-      </c>
-      <c r="U79" s="12">
-        <v>0</v>
-      </c>
-      <c r="V79" s="12" t="s">
+      <c r="T79" s="7">
+        <v>1</v>
+      </c>
+      <c r="U79" s="7">
+        <v>0</v>
+      </c>
+      <c r="V79" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="W79" s="12" t="s">
+      <c r="W79" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="X79" s="12" t="s">
+      <c r="X79" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="Y79" s="13">
-        <v>20030001</v>
-      </c>
-      <c r="Z79" s="13">
-        <v>0</v>
-      </c>
-      <c r="AA79" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB79" s="6" t="s">
+      <c r="Y79" s="14">
+        <v>204002001</v>
+      </c>
+      <c r="Z79" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA79" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB79" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="AC79" s="12">
-        <v>10000</v>
-      </c>
-      <c r="AD79" s="12">
-        <v>10000</v>
-      </c>
-      <c r="AE79" s="12">
+      <c r="AC79" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AD79" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AE79" s="7">
         <v>25010001</v>
       </c>
       <c r="AF79" s="4">
@@ -9428,92 +9444,91 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A80" s="12">
+    <row r="80" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A80" s="7">
         <v>301110</v>
       </c>
-      <c r="B80" s="12">
+      <c r="B80" s="7">
         <v>30</v>
       </c>
-      <c r="C80" s="12" t="s">
+      <c r="C80" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="D80" s="12"/>
-      <c r="E80" s="6"/>
-      <c r="F80" s="12"/>
-      <c r="G80" s="12">
+      <c r="D80" s="7"/>
+      <c r="F80" s="7"/>
+      <c r="G80" s="7">
         <v>12</v>
       </c>
-      <c r="H80" s="12">
-        <v>1</v>
-      </c>
-      <c r="I80" s="12" t="s">
+      <c r="H80" s="7">
+        <v>1</v>
+      </c>
+      <c r="I80" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="J80" s="12">
-        <v>0</v>
-      </c>
-      <c r="K80" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="L80" s="12">
-        <v>1000103</v>
-      </c>
-      <c r="M80" s="12">
-        <v>1</v>
-      </c>
-      <c r="N80" s="12">
+      <c r="J80" s="7">
+        <v>0</v>
+      </c>
+      <c r="K80" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="L80" s="7">
+        <v>800011011</v>
+      </c>
+      <c r="M80" s="7">
+        <v>1</v>
+      </c>
+      <c r="N80" s="7">
         <v>100</v>
       </c>
-      <c r="O80" s="12">
-        <v>0</v>
-      </c>
-      <c r="P80" s="12">
+      <c r="O80" s="7">
+        <v>0</v>
+      </c>
+      <c r="P80" s="7">
         <v>15</v>
       </c>
-      <c r="Q80" s="12">
-        <v>0</v>
-      </c>
-      <c r="R80" s="12">
+      <c r="Q80" s="7">
+        <v>0</v>
+      </c>
+      <c r="R80" s="16">
         <v>36</v>
       </c>
-      <c r="S80" s="12">
+      <c r="S80" s="7">
         <v>-7000</v>
       </c>
-      <c r="T80" s="12">
-        <v>1</v>
-      </c>
-      <c r="U80" s="12">
-        <v>0</v>
-      </c>
-      <c r="V80" s="12" t="s">
+      <c r="T80" s="7">
+        <v>1</v>
+      </c>
+      <c r="U80" s="7">
+        <v>0</v>
+      </c>
+      <c r="V80" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="W80" s="12" t="s">
+      <c r="W80" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="X80" s="12" t="s">
+      <c r="X80" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="Y80" s="13">
-        <v>20020001</v>
-      </c>
-      <c r="Z80" s="13">
-        <v>0</v>
-      </c>
-      <c r="AA80" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB80" s="6" t="s">
+      <c r="Y80" s="14">
+        <v>211001001</v>
+      </c>
+      <c r="Z80" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA80" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB80" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="AC80" s="12">
-        <v>10000</v>
-      </c>
-      <c r="AD80" s="12">
-        <v>10000</v>
-      </c>
-      <c r="AE80" s="12">
+      <c r="AC80" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AD80" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AE80" s="7">
         <v>25010001</v>
       </c>
       <c r="AF80" s="4">
@@ -9532,92 +9547,91 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A81" s="12">
+    <row r="81" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A81" s="7">
         <v>301111</v>
       </c>
-      <c r="B81" s="12">
+      <c r="B81" s="7">
         <v>30</v>
       </c>
-      <c r="C81" s="12" t="s">
+      <c r="C81" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="D81" s="12"/>
-      <c r="E81" s="6"/>
-      <c r="F81" s="12"/>
-      <c r="G81" s="12">
+      <c r="D81" s="7"/>
+      <c r="F81" s="7"/>
+      <c r="G81" s="7">
         <v>12</v>
       </c>
-      <c r="H81" s="12">
-        <v>1</v>
-      </c>
-      <c r="I81" s="12" t="s">
+      <c r="H81" s="7">
+        <v>1</v>
+      </c>
+      <c r="I81" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="J81" s="12">
-        <v>0</v>
-      </c>
-      <c r="K81" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="L81" s="12">
-        <v>1000103</v>
-      </c>
-      <c r="M81" s="12">
-        <v>1</v>
-      </c>
-      <c r="N81" s="12">
+      <c r="J81" s="7">
+        <v>0</v>
+      </c>
+      <c r="K81" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="L81" s="7">
+        <v>800011021</v>
+      </c>
+      <c r="M81" s="7">
+        <v>1</v>
+      </c>
+      <c r="N81" s="7">
         <v>100</v>
       </c>
-      <c r="O81" s="12">
-        <v>0</v>
-      </c>
-      <c r="P81" s="12">
+      <c r="O81" s="7">
+        <v>0</v>
+      </c>
+      <c r="P81" s="7">
         <v>15</v>
       </c>
-      <c r="Q81" s="12">
-        <v>0</v>
-      </c>
-      <c r="R81" s="12">
+      <c r="Q81" s="7">
+        <v>0</v>
+      </c>
+      <c r="R81" s="16">
         <v>36</v>
       </c>
-      <c r="S81" s="12">
+      <c r="S81" s="7">
         <v>-7000</v>
       </c>
-      <c r="T81" s="12">
-        <v>1</v>
-      </c>
-      <c r="U81" s="12">
-        <v>0</v>
-      </c>
-      <c r="V81" s="12" t="s">
+      <c r="T81" s="7">
+        <v>1</v>
+      </c>
+      <c r="U81" s="7">
+        <v>0</v>
+      </c>
+      <c r="V81" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="W81" s="12" t="s">
+      <c r="W81" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="X81" s="12" t="s">
+      <c r="X81" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="Y81" s="13">
-        <v>20020001</v>
-      </c>
-      <c r="Z81" s="13">
-        <v>0</v>
-      </c>
-      <c r="AA81" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB81" s="6" t="s">
+      <c r="Y81" s="14">
+        <v>211002001</v>
+      </c>
+      <c r="Z81" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA81" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB81" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="AC81" s="12">
-        <v>10000</v>
-      </c>
-      <c r="AD81" s="12">
-        <v>10000</v>
-      </c>
-      <c r="AE81" s="12">
+      <c r="AC81" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AD81" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AE81" s="7">
         <v>25010001</v>
       </c>
       <c r="AF81" s="4">
@@ -9636,92 +9650,91 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A82" s="12">
+    <row r="82" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A82" s="7">
         <v>301112</v>
       </c>
-      <c r="B82" s="12">
+      <c r="B82" s="7">
         <v>30</v>
       </c>
-      <c r="C82" s="12" t="s">
+      <c r="C82" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="D82" s="12"/>
-      <c r="E82" s="6"/>
-      <c r="F82" s="12"/>
-      <c r="G82" s="12">
+      <c r="D82" s="7"/>
+      <c r="F82" s="7"/>
+      <c r="G82" s="7">
         <v>12</v>
       </c>
-      <c r="H82" s="12">
-        <v>1</v>
-      </c>
-      <c r="I82" s="12" t="s">
+      <c r="H82" s="7">
+        <v>1</v>
+      </c>
+      <c r="I82" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="J82" s="12">
-        <v>0</v>
-      </c>
-      <c r="K82" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="L82" s="12">
-        <v>1000103</v>
-      </c>
-      <c r="M82" s="12">
-        <v>1</v>
-      </c>
-      <c r="N82" s="12">
+      <c r="J82" s="7">
+        <v>0</v>
+      </c>
+      <c r="K82" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="L82" s="7">
+        <v>800003011</v>
+      </c>
+      <c r="M82" s="7">
+        <v>1</v>
+      </c>
+      <c r="N82" s="7">
         <v>100</v>
       </c>
-      <c r="O82" s="12">
-        <v>0</v>
-      </c>
-      <c r="P82" s="12">
+      <c r="O82" s="7">
+        <v>0</v>
+      </c>
+      <c r="P82" s="7">
         <v>15</v>
       </c>
-      <c r="Q82" s="12">
-        <v>0</v>
-      </c>
-      <c r="R82" s="12">
+      <c r="Q82" s="7">
+        <v>0</v>
+      </c>
+      <c r="R82" s="16">
         <v>36</v>
       </c>
-      <c r="S82" s="12">
+      <c r="S82" s="7">
         <v>-7000</v>
       </c>
-      <c r="T82" s="12">
-        <v>1</v>
-      </c>
-      <c r="U82" s="12">
-        <v>0</v>
-      </c>
-      <c r="V82" s="12" t="s">
+      <c r="T82" s="7">
+        <v>1</v>
+      </c>
+      <c r="U82" s="7">
+        <v>0</v>
+      </c>
+      <c r="V82" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="W82" s="12" t="s">
+      <c r="W82" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="X82" s="12" t="s">
+      <c r="X82" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="Y82" s="13">
-        <v>20020001</v>
-      </c>
-      <c r="Z82" s="13">
-        <v>0</v>
-      </c>
-      <c r="AA82" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB82" s="6" t="s">
+      <c r="Y82" s="14">
+        <v>203001001</v>
+      </c>
+      <c r="Z82" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA82" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB82" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="AC82" s="12">
-        <v>10000</v>
-      </c>
-      <c r="AD82" s="12">
-        <v>10000</v>
-      </c>
-      <c r="AE82" s="12">
+      <c r="AC82" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AD82" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AE82" s="7">
         <v>25010001</v>
       </c>
       <c r="AF82" s="4">
@@ -9843,92 +9856,91 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A84" s="12">
+    <row r="84" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A84" s="7">
         <v>301114</v>
       </c>
-      <c r="B84" s="12">
+      <c r="B84" s="7">
         <v>30</v>
       </c>
-      <c r="C84" s="12" t="s">
+      <c r="C84" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="D84" s="12"/>
-      <c r="E84" s="6"/>
-      <c r="F84" s="12"/>
-      <c r="G84" s="12">
+      <c r="D84" s="7"/>
+      <c r="F84" s="7"/>
+      <c r="G84" s="7">
         <v>12</v>
       </c>
-      <c r="H84" s="12">
-        <v>1</v>
-      </c>
-      <c r="I84" s="12" t="s">
+      <c r="H84" s="7">
+        <v>1</v>
+      </c>
+      <c r="I84" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="J84" s="12">
-        <v>0</v>
-      </c>
-      <c r="K84" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="L84" s="12">
-        <v>1000011</v>
-      </c>
-      <c r="M84" s="12">
-        <v>1</v>
-      </c>
-      <c r="N84" s="12">
+      <c r="J84" s="7">
+        <v>0</v>
+      </c>
+      <c r="K84" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="L84" s="7">
+        <v>800003031</v>
+      </c>
+      <c r="M84" s="7">
+        <v>1</v>
+      </c>
+      <c r="N84" s="7">
         <v>100</v>
       </c>
-      <c r="O84" s="12">
-        <v>0</v>
-      </c>
-      <c r="P84" s="12">
+      <c r="O84" s="7">
+        <v>0</v>
+      </c>
+      <c r="P84" s="7">
         <v>15</v>
       </c>
-      <c r="Q84" s="12">
-        <v>0</v>
-      </c>
-      <c r="R84" s="12">
+      <c r="Q84" s="7">
+        <v>0</v>
+      </c>
+      <c r="R84" s="16">
         <v>36</v>
       </c>
-      <c r="S84" s="12">
+      <c r="S84" s="7">
         <v>-7000</v>
       </c>
-      <c r="T84" s="12">
-        <v>1</v>
-      </c>
-      <c r="U84" s="12">
-        <v>0</v>
-      </c>
-      <c r="V84" s="12" t="s">
+      <c r="T84" s="7">
+        <v>1</v>
+      </c>
+      <c r="U84" s="7">
+        <v>0</v>
+      </c>
+      <c r="V84" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="W84" s="12" t="s">
+      <c r="W84" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="X84" s="12" t="s">
+      <c r="X84" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="Y84" s="13">
-        <v>20050001</v>
-      </c>
-      <c r="Z84" s="13">
-        <v>0</v>
-      </c>
-      <c r="AA84" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB84" s="6" t="s">
+      <c r="Y84" s="14">
+        <v>203003001</v>
+      </c>
+      <c r="Z84" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA84" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB84" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="AC84" s="12">
-        <v>10000</v>
-      </c>
-      <c r="AD84" s="12">
-        <v>10000</v>
-      </c>
-      <c r="AE84" s="12">
+      <c r="AC84" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AD84" s="7">
+        <v>10000</v>
+      </c>
+      <c r="AE84" s="7">
         <v>0</v>
       </c>
       <c r="AF84" s="4">
@@ -9972,9 +9984,7 @@
       <c r="J85" s="12">
         <v>0</v>
       </c>
-      <c r="K85" s="12" t="s">
-        <v>71</v>
-      </c>
+      <c r="K85" s="12"/>
       <c r="L85" s="12">
         <v>1000011</v>
       </c>
@@ -10015,7 +10025,7 @@
         <v>123</v>
       </c>
       <c r="Y85" s="13">
-        <v>20050001</v>
+        <v>201002011</v>
       </c>
       <c r="Z85" s="13">
         <v>0</v>
@@ -10325,7 +10335,7 @@
         <v>197</v>
       </c>
       <c r="Y88" s="13">
-        <v>20010001</v>
+        <v>201002011</v>
       </c>
       <c r="Z88" s="13">
         <v>0</v>
@@ -10635,7 +10645,7 @@
         <v>123</v>
       </c>
       <c r="Y91" s="13">
-        <v>20040001</v>
+        <v>201002011</v>
       </c>
       <c r="Z91" s="13">
         <v>0</v>
@@ -10739,7 +10749,7 @@
         <v>123</v>
       </c>
       <c r="Y92" s="13">
-        <v>20030001</v>
+        <v>201002011</v>
       </c>
       <c r="Z92" s="13">
         <v>0</v>
@@ -10843,7 +10853,7 @@
         <v>123</v>
       </c>
       <c r="Y93" s="13">
-        <v>20030001</v>
+        <v>201002011</v>
       </c>
       <c r="Z93" s="13">
         <v>0</v>
@@ -10947,7 +10957,7 @@
         <v>123</v>
       </c>
       <c r="Y94" s="13">
-        <v>20030001</v>
+        <v>201002011</v>
       </c>
       <c r="Z94" s="13">
         <v>0</v>
@@ -11051,7 +11061,7 @@
         <v>123</v>
       </c>
       <c r="Y95" s="13">
-        <v>20020001</v>
+        <v>201002011</v>
       </c>
       <c r="Z95" s="13">
         <v>0</v>
@@ -11155,7 +11165,7 @@
         <v>123</v>
       </c>
       <c r="Y96" s="13">
-        <v>20020001</v>
+        <v>201002011</v>
       </c>
       <c r="Z96" s="13">
         <v>0</v>
@@ -11259,7 +11269,7 @@
         <v>123</v>
       </c>
       <c r="Y97" s="13">
-        <v>20020001</v>
+        <v>201002011</v>
       </c>
       <c r="Z97" s="13">
         <v>0</v>
@@ -11466,7 +11476,7 @@
         <v>123</v>
       </c>
       <c r="Y99" s="13">
-        <v>20050001</v>
+        <v>201002011</v>
       </c>
       <c r="Z99" s="13">
         <v>0</v>
@@ -11570,7 +11580,7 @@
         <v>123</v>
       </c>
       <c r="Y100" s="13">
-        <v>20050001</v>
+        <v>201002011</v>
       </c>
       <c r="Z100" s="13">
         <v>0</v>
@@ -11880,7 +11890,7 @@
         <v>197</v>
       </c>
       <c r="Y103" s="13">
-        <v>20010001</v>
+        <v>201002011</v>
       </c>
       <c r="Z103" s="13">
         <v>0</v>
@@ -12190,7 +12200,7 @@
         <v>123</v>
       </c>
       <c r="Y106" s="13">
-        <v>20040001</v>
+        <v>201002011</v>
       </c>
       <c r="Z106" s="13">
         <v>0</v>
@@ -12294,7 +12304,7 @@
         <v>123</v>
       </c>
       <c r="Y107" s="13">
-        <v>20030001</v>
+        <v>201002011</v>
       </c>
       <c r="Z107" s="13">
         <v>0</v>
@@ -12398,7 +12408,7 @@
         <v>123</v>
       </c>
       <c r="Y108" s="13">
-        <v>20030001</v>
+        <v>201002011</v>
       </c>
       <c r="Z108" s="13">
         <v>0</v>
@@ -12502,7 +12512,7 @@
         <v>123</v>
       </c>
       <c r="Y109" s="13">
-        <v>20030001</v>
+        <v>201002011</v>
       </c>
       <c r="Z109" s="13">
         <v>0</v>
@@ -12606,7 +12616,7 @@
         <v>123</v>
       </c>
       <c r="Y110" s="13">
-        <v>20020001</v>
+        <v>201002011</v>
       </c>
       <c r="Z110" s="13">
         <v>0</v>
@@ -12710,7 +12720,7 @@
         <v>123</v>
       </c>
       <c r="Y111" s="13">
-        <v>20020001</v>
+        <v>201002011</v>
       </c>
       <c r="Z111" s="13">
         <v>0</v>
@@ -12814,7 +12824,7 @@
         <v>123</v>
       </c>
       <c r="Y112" s="13">
-        <v>20020001</v>
+        <v>201002011</v>
       </c>
       <c r="Z112" s="13">
         <v>0</v>
@@ -13021,7 +13031,7 @@
         <v>123</v>
       </c>
       <c r="Y114" s="13">
-        <v>20050001</v>
+        <v>201002011</v>
       </c>
       <c r="Z114" s="13">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C2EDCE0-B938-4978-B605-75C5D28E9EA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A912DA5-E5FF-4BC6-A403-0C34890BE0AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_foe_v8" sheetId="1" r:id="rId1"/>
@@ -8560,7 +8560,7 @@
         <v>0</v>
       </c>
       <c r="P71" s="7">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="Q71" s="7">
         <v>0</v>
@@ -8599,7 +8599,7 @@
         <v>153</v>
       </c>
       <c r="AC71" s="7">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AD71" s="7">
         <v>10000</v>
@@ -8663,13 +8663,13 @@
         <v>0</v>
       </c>
       <c r="P72" s="7">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="Q72" s="7">
         <v>2</v>
       </c>
       <c r="R72" s="7">
-        <v>281</v>
+        <v>124</v>
       </c>
       <c r="S72" s="7">
         <v>-7000</v>
@@ -8702,7 +8702,7 @@
         <v>170</v>
       </c>
       <c r="AC72" s="7">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AD72" s="7">
         <v>10000</v>
@@ -8804,7 +8804,7 @@
         <v>153</v>
       </c>
       <c r="AC73" s="12">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AD73" s="12">
         <v>10000</v>
@@ -8868,7 +8868,7 @@
         <v>0</v>
       </c>
       <c r="P74" s="7">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="Q74" s="7">
         <v>0</v>
@@ -8907,7 +8907,7 @@
         <v>153</v>
       </c>
       <c r="AC74" s="7">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AD74" s="7">
         <v>10000</v>
@@ -8971,13 +8971,13 @@
         <v>0</v>
       </c>
       <c r="P75" s="7">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="Q75" s="7">
         <v>1</v>
       </c>
       <c r="R75" s="7">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="S75" s="7">
         <v>-7000</v>
@@ -9010,7 +9010,7 @@
         <v>171</v>
       </c>
       <c r="AC75" s="7">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AD75" s="7">
         <v>10000</v>
@@ -9112,7 +9112,7 @@
         <v>132</v>
       </c>
       <c r="AC76" s="12">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AD76" s="12">
         <v>10000</v>
@@ -9214,7 +9214,7 @@
         <v>132</v>
       </c>
       <c r="AC77" s="12">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AD77" s="12">
         <v>10000</v>
@@ -9317,7 +9317,7 @@
         <v>132</v>
       </c>
       <c r="AC78" s="7">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AD78" s="7">
         <v>10000</v>
@@ -9420,7 +9420,7 @@
         <v>132</v>
       </c>
       <c r="AC79" s="7">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AD79" s="7">
         <v>10000</v>
@@ -9523,7 +9523,7 @@
         <v>132</v>
       </c>
       <c r="AC80" s="7">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AD80" s="7">
         <v>10000</v>
@@ -9626,7 +9626,7 @@
         <v>132</v>
       </c>
       <c r="AC81" s="7">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AD81" s="7">
         <v>10000</v>
@@ -9729,7 +9729,7 @@
         <v>132</v>
       </c>
       <c r="AC82" s="7">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AD82" s="7">
         <v>10000</v>
@@ -9832,7 +9832,7 @@
         <v>172</v>
       </c>
       <c r="AC83" s="7">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AD83" s="7">
         <v>10000</v>
@@ -9935,7 +9935,7 @@
         <v>132</v>
       </c>
       <c r="AC84" s="7">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AD84" s="7">
         <v>10000</v>
@@ -10037,7 +10037,7 @@
         <v>132</v>
       </c>
       <c r="AC85" s="12">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AD85" s="12">
         <v>10000</v>
@@ -10140,7 +10140,7 @@
         <v>153</v>
       </c>
       <c r="AC86" s="7">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AD86" s="7">
         <v>10000</v>
@@ -10243,7 +10243,7 @@
         <v>170</v>
       </c>
       <c r="AC87" s="7">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AD87" s="7">
         <v>10000</v>
@@ -10347,7 +10347,7 @@
         <v>153</v>
       </c>
       <c r="AC88" s="12">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AD88" s="12">
         <v>10000</v>
@@ -10450,7 +10450,7 @@
         <v>153</v>
       </c>
       <c r="AC89" s="7">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AD89" s="7">
         <v>10000</v>
@@ -10553,7 +10553,7 @@
         <v>171</v>
       </c>
       <c r="AC90" s="7">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AD90" s="7">
         <v>10000</v>
@@ -10657,7 +10657,7 @@
         <v>132</v>
       </c>
       <c r="AC91" s="12">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AD91" s="12">
         <v>10000</v>
@@ -10761,7 +10761,7 @@
         <v>132</v>
       </c>
       <c r="AC92" s="12">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AD92" s="12">
         <v>10000</v>
@@ -10865,7 +10865,7 @@
         <v>132</v>
       </c>
       <c r="AC93" s="12">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AD93" s="12">
         <v>10000</v>
@@ -10969,7 +10969,7 @@
         <v>132</v>
       </c>
       <c r="AC94" s="12">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AD94" s="12">
         <v>10000</v>
@@ -11073,7 +11073,7 @@
         <v>132</v>
       </c>
       <c r="AC95" s="12">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AD95" s="12">
         <v>10000</v>
@@ -11177,7 +11177,7 @@
         <v>132</v>
       </c>
       <c r="AC96" s="12">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AD96" s="12">
         <v>10000</v>
@@ -11281,7 +11281,7 @@
         <v>132</v>
       </c>
       <c r="AC97" s="12">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AD97" s="12">
         <v>10000</v>
@@ -11384,7 +11384,7 @@
         <v>172</v>
       </c>
       <c r="AC98" s="7">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AD98" s="7">
         <v>10000</v>
@@ -11488,7 +11488,7 @@
         <v>132</v>
       </c>
       <c r="AC99" s="12">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AD99" s="12">
         <v>10000</v>
@@ -11592,7 +11592,7 @@
         <v>132</v>
       </c>
       <c r="AC100" s="12">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AD100" s="12">
         <v>10000</v>
@@ -11695,7 +11695,7 @@
         <v>153</v>
       </c>
       <c r="AC101" s="7">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AD101" s="7">
         <v>10000</v>
@@ -11798,7 +11798,7 @@
         <v>170</v>
       </c>
       <c r="AC102" s="7">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AD102" s="7">
         <v>10000</v>
@@ -11902,7 +11902,7 @@
         <v>153</v>
       </c>
       <c r="AC103" s="12">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AD103" s="12">
         <v>10000</v>
@@ -12005,7 +12005,7 @@
         <v>153</v>
       </c>
       <c r="AC104" s="7">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AD104" s="7">
         <v>10000</v>
@@ -12108,7 +12108,7 @@
         <v>171</v>
       </c>
       <c r="AC105" s="7">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AD105" s="7">
         <v>10000</v>
@@ -12212,7 +12212,7 @@
         <v>132</v>
       </c>
       <c r="AC106" s="12">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AD106" s="12">
         <v>10000</v>
@@ -12316,7 +12316,7 @@
         <v>132</v>
       </c>
       <c r="AC107" s="12">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AD107" s="12">
         <v>10000</v>
@@ -12420,7 +12420,7 @@
         <v>132</v>
       </c>
       <c r="AC108" s="12">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AD108" s="12">
         <v>10000</v>
@@ -12524,7 +12524,7 @@
         <v>132</v>
       </c>
       <c r="AC109" s="12">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AD109" s="12">
         <v>10000</v>
@@ -12628,7 +12628,7 @@
         <v>132</v>
       </c>
       <c r="AC110" s="12">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AD110" s="12">
         <v>10000</v>
@@ -12732,7 +12732,7 @@
         <v>132</v>
       </c>
       <c r="AC111" s="12">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AD111" s="12">
         <v>10000</v>
@@ -12836,7 +12836,7 @@
         <v>132</v>
       </c>
       <c r="AC112" s="12">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AD112" s="12">
         <v>10000</v>
@@ -12939,7 +12939,7 @@
         <v>153</v>
       </c>
       <c r="AC113" s="7">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AD113" s="7">
         <v>10000</v>
@@ -13043,7 +13043,7 @@
         <v>132</v>
       </c>
       <c r="AC114" s="12">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AD114" s="12">
         <v>10000</v>
@@ -13146,7 +13146,7 @@
         <v>172</v>
       </c>
       <c r="AC115" s="7">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AD115" s="7">
         <v>10000</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A912DA5-E5FF-4BC6-A403-0C34890BE0AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B83A57F6-ACF1-48C0-AEB7-8D1C2248B28B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="204">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -8956,10 +8956,10 @@
         <v>0</v>
       </c>
       <c r="K75" s="7" t="s">
-        <v>162</v>
+        <v>198</v>
       </c>
       <c r="L75" s="7">
-        <v>800014011</v>
+        <v>800003011</v>
       </c>
       <c r="M75" s="7">
         <v>1</v>
@@ -8998,7 +8998,7 @@
         <v>197</v>
       </c>
       <c r="Y75" s="14">
-        <v>214001011</v>
+        <v>203001001</v>
       </c>
       <c r="Z75" s="14">
         <v>0</v>
@@ -9161,9 +9161,11 @@
       <c r="J77" s="12">
         <v>0</v>
       </c>
-      <c r="K77" s="12"/>
+      <c r="K77" s="12" t="s">
+        <v>162</v>
+      </c>
       <c r="L77" s="12">
-        <v>1000006</v>
+        <v>800014011</v>
       </c>
       <c r="M77" s="12">
         <v>1</v>
@@ -9202,7 +9204,7 @@
         <v>123</v>
       </c>
       <c r="Y77" s="12">
-        <v>201002011</v>
+        <v>214001011</v>
       </c>
       <c r="Z77" s="13">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B83A57F6-ACF1-48C0-AEB7-8D1C2248B28B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3556FAD9-6DC8-431F-83C1-DA4470C4E335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8569,7 +8569,7 @@
         <v>20</v>
       </c>
       <c r="S71" s="7">
-        <v>-7000</v>
+        <v>-5500</v>
       </c>
       <c r="T71" s="7">
         <v>1</v>
@@ -8672,7 +8672,7 @@
         <v>124</v>
       </c>
       <c r="S72" s="7">
-        <v>-7000</v>
+        <v>-5500</v>
       </c>
       <c r="T72" s="7">
         <v>1</v>
@@ -8774,7 +8774,7 @@
         <v>300</v>
       </c>
       <c r="S73" s="12">
-        <v>-7000</v>
+        <v>-5500</v>
       </c>
       <c r="T73" s="12">
         <v>1</v>
@@ -8877,7 +8877,7 @@
         <v>17</v>
       </c>
       <c r="S74" s="7">
-        <v>-7000</v>
+        <v>-5500</v>
       </c>
       <c r="T74" s="7">
         <v>1</v>
@@ -8956,10 +8956,10 @@
         <v>0</v>
       </c>
       <c r="K75" s="7" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="L75" s="7">
-        <v>800003011</v>
+        <v>800014011</v>
       </c>
       <c r="M75" s="7">
         <v>1</v>
@@ -8980,7 +8980,7 @@
         <v>49</v>
       </c>
       <c r="S75" s="7">
-        <v>-7000</v>
+        <v>-5500</v>
       </c>
       <c r="T75" s="7">
         <v>1</v>
@@ -8998,7 +8998,7 @@
         <v>197</v>
       </c>
       <c r="Y75" s="14">
-        <v>203001001</v>
+        <v>214001011</v>
       </c>
       <c r="Z75" s="14">
         <v>0</v>
@@ -9082,7 +9082,7 @@
         <v>36</v>
       </c>
       <c r="S76" s="12">
-        <v>-7000</v>
+        <v>-5500</v>
       </c>
       <c r="T76" s="12">
         <v>1</v>
@@ -9186,7 +9186,7 @@
         <v>36</v>
       </c>
       <c r="S77" s="12">
-        <v>-7000</v>
+        <v>-5500</v>
       </c>
       <c r="T77" s="12">
         <v>1</v>
@@ -9289,7 +9289,7 @@
         <v>36</v>
       </c>
       <c r="S78" s="7">
-        <v>-7000</v>
+        <v>-5500</v>
       </c>
       <c r="T78" s="7">
         <v>1</v>
@@ -9392,7 +9392,7 @@
         <v>36</v>
       </c>
       <c r="S79" s="7">
-        <v>-7000</v>
+        <v>-5500</v>
       </c>
       <c r="T79" s="7">
         <v>1</v>
@@ -9495,7 +9495,7 @@
         <v>36</v>
       </c>
       <c r="S80" s="7">
-        <v>-7000</v>
+        <v>-5500</v>
       </c>
       <c r="T80" s="7">
         <v>1</v>
@@ -9598,7 +9598,7 @@
         <v>36</v>
       </c>
       <c r="S81" s="7">
-        <v>-7000</v>
+        <v>-5500</v>
       </c>
       <c r="T81" s="7">
         <v>1</v>
@@ -9701,7 +9701,7 @@
         <v>36</v>
       </c>
       <c r="S82" s="7">
-        <v>-7000</v>
+        <v>-5500</v>
       </c>
       <c r="T82" s="7">
         <v>1</v>
@@ -9804,7 +9804,7 @@
         <v>1496</v>
       </c>
       <c r="S83" s="7">
-        <v>-7000</v>
+        <v>-5500</v>
       </c>
       <c r="T83" s="7">
         <v>1</v>
@@ -9907,7 +9907,7 @@
         <v>36</v>
       </c>
       <c r="S84" s="7">
-        <v>-7000</v>
+        <v>-5500</v>
       </c>
       <c r="T84" s="7">
         <v>1</v>
@@ -10009,7 +10009,7 @@
         <v>36</v>
       </c>
       <c r="S85" s="12">
-        <v>-7000</v>
+        <v>-5500</v>
       </c>
       <c r="T85" s="12">
         <v>1</v>
@@ -10112,7 +10112,7 @@
         <v>251</v>
       </c>
       <c r="S86" s="7">
-        <v>-7000</v>
+        <v>-5500</v>
       </c>
       <c r="T86" s="7">
         <v>1</v>
@@ -10215,7 +10215,7 @@
         <v>1343</v>
       </c>
       <c r="S87" s="7">
-        <v>-7000</v>
+        <v>-5500</v>
       </c>
       <c r="T87" s="7">
         <v>1</v>
@@ -10319,7 +10319,7 @@
         <v>300</v>
       </c>
       <c r="S88" s="12">
-        <v>-7000</v>
+        <v>-5500</v>
       </c>
       <c r="T88" s="12">
         <v>1</v>
@@ -10422,7 +10422,7 @@
         <v>23</v>
       </c>
       <c r="S89" s="7">
-        <v>-7000</v>
+        <v>-5500</v>
       </c>
       <c r="T89" s="7">
         <v>1</v>
@@ -10525,7 +10525,7 @@
         <v>354</v>
       </c>
       <c r="S90" s="7">
-        <v>-7000</v>
+        <v>-5500</v>
       </c>
       <c r="T90" s="7">
         <v>1</v>
@@ -10629,7 +10629,7 @@
         <v>36</v>
       </c>
       <c r="S91" s="12">
-        <v>-7000</v>
+        <v>-5500</v>
       </c>
       <c r="T91" s="12">
         <v>1</v>
@@ -10733,7 +10733,7 @@
         <v>36</v>
       </c>
       <c r="S92" s="12">
-        <v>-7000</v>
+        <v>-5500</v>
       </c>
       <c r="T92" s="12">
         <v>1</v>
@@ -10837,7 +10837,7 @@
         <v>36</v>
       </c>
       <c r="S93" s="12">
-        <v>-7000</v>
+        <v>-5500</v>
       </c>
       <c r="T93" s="12">
         <v>1</v>
@@ -10941,7 +10941,7 @@
         <v>36</v>
       </c>
       <c r="S94" s="12">
-        <v>-7000</v>
+        <v>-5500</v>
       </c>
       <c r="T94" s="12">
         <v>1</v>
@@ -11045,7 +11045,7 @@
         <v>36</v>
       </c>
       <c r="S95" s="12">
-        <v>-7000</v>
+        <v>-5500</v>
       </c>
       <c r="T95" s="12">
         <v>1</v>
@@ -11149,7 +11149,7 @@
         <v>36</v>
       </c>
       <c r="S96" s="12">
-        <v>-7000</v>
+        <v>-5500</v>
       </c>
       <c r="T96" s="12">
         <v>1</v>
@@ -11253,7 +11253,7 @@
         <v>36</v>
       </c>
       <c r="S97" s="12">
-        <v>-7000</v>
+        <v>-5500</v>
       </c>
       <c r="T97" s="12">
         <v>1</v>
@@ -11356,7 +11356,7 @@
         <v>1496</v>
       </c>
       <c r="S98" s="7">
-        <v>-7000</v>
+        <v>-5500</v>
       </c>
       <c r="T98" s="7">
         <v>1</v>
@@ -11460,7 +11460,7 @@
         <v>36</v>
       </c>
       <c r="S99" s="12">
-        <v>-7000</v>
+        <v>-5500</v>
       </c>
       <c r="T99" s="12">
         <v>1</v>
@@ -11564,7 +11564,7 @@
         <v>36</v>
       </c>
       <c r="S100" s="12">
-        <v>-7000</v>
+        <v>-5500</v>
       </c>
       <c r="T100" s="12">
         <v>1</v>
@@ -11667,7 +11667,7 @@
         <v>623</v>
       </c>
       <c r="S101" s="7">
-        <v>-7000</v>
+        <v>-5500</v>
       </c>
       <c r="T101" s="7">
         <v>1</v>
@@ -11770,7 +11770,7 @@
         <v>2647</v>
       </c>
       <c r="S102" s="7">
-        <v>-7000</v>
+        <v>-5500</v>
       </c>
       <c r="T102" s="7">
         <v>1</v>
@@ -11874,7 +11874,7 @@
         <v>300</v>
       </c>
       <c r="S103" s="12">
-        <v>-7000</v>
+        <v>-5500</v>
       </c>
       <c r="T103" s="12">
         <v>1</v>
@@ -11977,7 +11977,7 @@
         <v>519</v>
       </c>
       <c r="S104" s="7">
-        <v>-7000</v>
+        <v>-5500</v>
       </c>
       <c r="T104" s="7">
         <v>1</v>
@@ -12080,7 +12080,7 @@
         <v>822</v>
       </c>
       <c r="S105" s="7">
-        <v>-7000</v>
+        <v>-5500</v>
       </c>
       <c r="T105" s="7">
         <v>1</v>
@@ -12184,7 +12184,7 @@
         <v>36</v>
       </c>
       <c r="S106" s="12">
-        <v>-7000</v>
+        <v>-5500</v>
       </c>
       <c r="T106" s="12">
         <v>1</v>
@@ -12288,7 +12288,7 @@
         <v>36</v>
       </c>
       <c r="S107" s="12">
-        <v>-7000</v>
+        <v>-5500</v>
       </c>
       <c r="T107" s="12">
         <v>1</v>
@@ -12392,7 +12392,7 @@
         <v>36</v>
       </c>
       <c r="S108" s="12">
-        <v>-7000</v>
+        <v>-5500</v>
       </c>
       <c r="T108" s="12">
         <v>1</v>
@@ -12496,7 +12496,7 @@
         <v>36</v>
       </c>
       <c r="S109" s="12">
-        <v>-7000</v>
+        <v>-5500</v>
       </c>
       <c r="T109" s="12">
         <v>1</v>
@@ -12600,7 +12600,7 @@
         <v>36</v>
       </c>
       <c r="S110" s="12">
-        <v>-7000</v>
+        <v>-5500</v>
       </c>
       <c r="T110" s="12">
         <v>1</v>
@@ -12704,7 +12704,7 @@
         <v>36</v>
       </c>
       <c r="S111" s="12">
-        <v>-7000</v>
+        <v>-5500</v>
       </c>
       <c r="T111" s="12">
         <v>1</v>
@@ -12808,7 +12808,7 @@
         <v>36</v>
       </c>
       <c r="S112" s="12">
-        <v>-7000</v>
+        <v>-5500</v>
       </c>
       <c r="T112" s="12">
         <v>1</v>
@@ -12911,7 +12911,7 @@
         <v>1496</v>
       </c>
       <c r="S113" s="7">
-        <v>-7000</v>
+        <v>-5500</v>
       </c>
       <c r="T113" s="7">
         <v>1</v>
@@ -13015,7 +13015,7 @@
         <v>36</v>
       </c>
       <c r="S114" s="12">
-        <v>-7000</v>
+        <v>-5500</v>
       </c>
       <c r="T114" s="12">
         <v>1</v>
@@ -13118,7 +13118,7 @@
         <v>11989</v>
       </c>
       <c r="S115" s="7">
-        <v>-7000</v>
+        <v>-5500</v>
       </c>
       <c r="T115" s="7">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3556FAD9-6DC8-431F-83C1-DA4470C4E335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0632BAA5-3FBC-4BB7-B950-DA9EE6ED1795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10103,13 +10103,13 @@
         <v>0</v>
       </c>
       <c r="P86" s="7">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="Q86" s="7">
         <v>0</v>
       </c>
       <c r="R86" s="7">
-        <v>251</v>
+        <v>131</v>
       </c>
       <c r="S86" s="7">
         <v>-5500</v>
@@ -10206,13 +10206,13 @@
         <v>0</v>
       </c>
       <c r="P87" s="7">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="Q87" s="7">
         <v>3</v>
       </c>
       <c r="R87" s="7">
-        <v>1343</v>
+        <v>406</v>
       </c>
       <c r="S87" s="7">
         <v>-5500</v>
@@ -10413,13 +10413,13 @@
         <v>0</v>
       </c>
       <c r="P89" s="7">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="Q89" s="7">
         <v>0</v>
       </c>
       <c r="R89" s="7">
-        <v>23</v>
+        <v>109</v>
       </c>
       <c r="S89" s="7">
         <v>-5500</v>
@@ -10516,13 +10516,13 @@
         <v>0</v>
       </c>
       <c r="P90" s="7">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="Q90" s="7">
         <v>2</v>
       </c>
       <c r="R90" s="7">
-        <v>354</v>
+        <v>184</v>
       </c>
       <c r="S90" s="7">
         <v>-5500</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0632BAA5-3FBC-4BB7-B950-DA9EE6ED1795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90C24533-6557-467D-8ED2-78F8F1CE7C31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8560,7 +8560,7 @@
         <v>0</v>
       </c>
       <c r="P71" s="7">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="Q71" s="7">
         <v>0</v>
@@ -8720,7 +8720,7 @@
         <v>10000</v>
       </c>
       <c r="AI72" s="4">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AJ72" s="4">
         <v>0</v>
@@ -8971,7 +8971,7 @@
         <v>0</v>
       </c>
       <c r="P75" s="7">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Q75" s="7">
         <v>1</v>
@@ -10103,7 +10103,7 @@
         <v>0</v>
       </c>
       <c r="P86" s="7">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q86" s="7">
         <v>0</v>
@@ -10206,7 +10206,7 @@
         <v>0</v>
       </c>
       <c r="P87" s="7">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="Q87" s="7">
         <v>3</v>
@@ -10263,7 +10263,7 @@
         <v>10000</v>
       </c>
       <c r="AI87" s="4">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AJ87" s="4">
         <v>0</v>
@@ -10413,7 +10413,7 @@
         <v>0</v>
       </c>
       <c r="P89" s="7">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="Q89" s="7">
         <v>0</v>
@@ -10516,7 +10516,7 @@
         <v>0</v>
       </c>
       <c r="P90" s="7">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Q90" s="7">
         <v>2</v>
@@ -11664,7 +11664,7 @@
         <v>0</v>
       </c>
       <c r="R101" s="7">
-        <v>623</v>
+        <v>313</v>
       </c>
       <c r="S101" s="7">
         <v>-5500</v>
@@ -11761,13 +11761,13 @@
         <v>0</v>
       </c>
       <c r="P102" s="7">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q102" s="7">
         <v>4</v>
       </c>
       <c r="R102" s="7">
-        <v>2647</v>
+        <v>783</v>
       </c>
       <c r="S102" s="7">
         <v>-5500</v>
@@ -11818,7 +11818,7 @@
         <v>10000</v>
       </c>
       <c r="AI102" s="4">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AJ102" s="4">
         <v>0</v>
@@ -11968,13 +11968,13 @@
         <v>0</v>
       </c>
       <c r="P104" s="7">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="Q104" s="7">
         <v>0</v>
       </c>
       <c r="R104" s="7">
-        <v>519</v>
+        <v>261</v>
       </c>
       <c r="S104" s="7">
         <v>-5500</v>
@@ -12071,13 +12071,13 @@
         <v>0</v>
       </c>
       <c r="P105" s="7">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="Q105" s="7">
         <v>2</v>
       </c>
       <c r="R105" s="7">
-        <v>822</v>
+        <v>413</v>
       </c>
       <c r="S105" s="7">
         <v>-5500</v>
@@ -13109,13 +13109,13 @@
         <v>0</v>
       </c>
       <c r="P115" s="7">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="Q115" s="7">
         <v>7</v>
       </c>
       <c r="R115" s="16">
-        <v>11989</v>
+        <v>5745</v>
       </c>
       <c r="S115" s="7">
         <v>-5500</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90C24533-6557-467D-8ED2-78F8F1CE7C31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CBC618B-6C0B-4647-B933-91B3EB6B715D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8868,7 +8868,7 @@
         <v>0</v>
       </c>
       <c r="P74" s="7">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Q74" s="7">
         <v>0</v>
@@ -8971,7 +8971,7 @@
         <v>0</v>
       </c>
       <c r="P75" s="7">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="Q75" s="7">
         <v>1</v>
@@ -10103,7 +10103,7 @@
         <v>0</v>
       </c>
       <c r="P86" s="7">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="Q86" s="7">
         <v>0</v>
@@ -10413,7 +10413,7 @@
         <v>0</v>
       </c>
       <c r="P89" s="7">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Q89" s="7">
         <v>0</v>
@@ -10516,7 +10516,7 @@
         <v>0</v>
       </c>
       <c r="P90" s="7">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Q90" s="7">
         <v>2</v>
@@ -11658,7 +11658,7 @@
         <v>0</v>
       </c>
       <c r="P101" s="7">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="Q101" s="7">
         <v>0</v>
@@ -11968,7 +11968,7 @@
         <v>0</v>
       </c>
       <c r="P104" s="7">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="Q104" s="7">
         <v>0</v>
@@ -12071,7 +12071,7 @@
         <v>0</v>
       </c>
       <c r="P105" s="7">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="Q105" s="7">
         <v>2</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CBC618B-6C0B-4647-B933-91B3EB6B715D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BFDA3F6-4DD6-4808-9988-0A6415A8FE47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8868,7 +8868,7 @@
         <v>0</v>
       </c>
       <c r="P74" s="7">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="Q74" s="7">
         <v>0</v>
@@ -10103,7 +10103,7 @@
         <v>0</v>
       </c>
       <c r="P86" s="7">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Q86" s="7">
         <v>0</v>
@@ -10413,7 +10413,7 @@
         <v>0</v>
       </c>
       <c r="P89" s="7">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="Q89" s="7">
         <v>0</v>
@@ -10516,7 +10516,7 @@
         <v>0</v>
       </c>
       <c r="P90" s="7">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="Q90" s="7">
         <v>2</v>
@@ -11658,7 +11658,7 @@
         <v>0</v>
       </c>
       <c r="P101" s="7">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="Q101" s="7">
         <v>0</v>
@@ -11968,7 +11968,7 @@
         <v>0</v>
       </c>
       <c r="P104" s="7">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="Q104" s="7">
         <v>0</v>
@@ -12071,7 +12071,7 @@
         <v>0</v>
       </c>
       <c r="P105" s="7">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Q105" s="7">
         <v>2</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BFDA3F6-4DD6-4808-9988-0A6415A8FE47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA7FA3C2-E449-4A72-96DD-0D09BA2FD351}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8560,7 +8560,7 @@
         <v>0</v>
       </c>
       <c r="P71" s="7">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Q71" s="7">
         <v>0</v>
@@ -8663,7 +8663,7 @@
         <v>0</v>
       </c>
       <c r="P72" s="7">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="Q72" s="7">
         <v>2</v>
@@ -8868,7 +8868,7 @@
         <v>0</v>
       </c>
       <c r="P74" s="7">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q74" s="7">
         <v>0</v>
@@ -8971,7 +8971,7 @@
         <v>0</v>
       </c>
       <c r="P75" s="7">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="Q75" s="7">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA7FA3C2-E449-4A72-96DD-0D09BA2FD351}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A52E68E-79D3-48D0-BB9E-5A55F23F93BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11658,7 +11658,7 @@
         <v>0</v>
       </c>
       <c r="P101" s="7">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Q101" s="7">
         <v>0</v>
@@ -11761,7 +11761,7 @@
         <v>0</v>
       </c>
       <c r="P102" s="7">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="Q102" s="7">
         <v>4</v>
@@ -11968,7 +11968,7 @@
         <v>0</v>
       </c>
       <c r="P104" s="7">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="Q104" s="7">
         <v>0</v>
@@ -12071,7 +12071,7 @@
         <v>0</v>
       </c>
       <c r="P105" s="7">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="Q105" s="7">
         <v>2</v>
@@ -13109,10 +13109,10 @@
         <v>0</v>
       </c>
       <c r="P115" s="7">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="Q115" s="7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R115" s="16">
         <v>5745</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A52E68E-79D3-48D0-BB9E-5A55F23F93BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A7DD542-F8E9-4E75-9736-6390E2378C24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8560,7 +8560,7 @@
         <v>0</v>
       </c>
       <c r="P71" s="7">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q71" s="7">
         <v>0</v>
@@ -8663,13 +8663,13 @@
         <v>0</v>
       </c>
       <c r="P72" s="7">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Q72" s="7">
         <v>2</v>
       </c>
       <c r="R72" s="7">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="S72" s="7">
         <v>-5500</v>
@@ -8868,7 +8868,7 @@
         <v>0</v>
       </c>
       <c r="P74" s="7">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q74" s="7">
         <v>0</v>
@@ -8971,13 +8971,13 @@
         <v>0</v>
       </c>
       <c r="P75" s="7">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Q75" s="7">
         <v>1</v>
       </c>
       <c r="R75" s="7">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="S75" s="7">
         <v>-5500</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA1DD0F0-B34C-4A07-A185-4898704FF8B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C1F61DF-1E98-4A90-8E60-1562C9FC7605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_foe_v8" sheetId="1" r:id="rId1"/>
@@ -30,8 +30,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -10082,13 +10080,13 @@
         <v>0</v>
       </c>
       <c r="P86" s="3">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Q86" s="3">
         <v>0</v>
       </c>
       <c r="R86" s="3">
-        <v>131</v>
+        <v>104</v>
       </c>
       <c r="S86" s="3">
         <v>-5500</v>
@@ -10185,13 +10183,13 @@
         <v>0</v>
       </c>
       <c r="P87" s="3">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="Q87" s="3">
         <v>3</v>
       </c>
       <c r="R87" s="3">
-        <v>406</v>
+        <v>324</v>
       </c>
       <c r="S87" s="3">
         <v>-5500</v>
@@ -10392,13 +10390,13 @@
         <v>0</v>
       </c>
       <c r="P89" s="3">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="Q89" s="3">
         <v>0</v>
       </c>
       <c r="R89" s="3">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="S89" s="3">
         <v>-5500</v>
@@ -10495,13 +10493,13 @@
         <v>0</v>
       </c>
       <c r="P90" s="3">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="Q90" s="3">
         <v>2</v>
       </c>
       <c r="R90" s="3">
-        <v>184</v>
+        <v>146</v>
       </c>
       <c r="S90" s="3">
         <v>-5500</v>
@@ -11637,13 +11635,13 @@
         <v>0</v>
       </c>
       <c r="P101" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
       </c>
       <c r="R101" s="3">
-        <v>313</v>
+        <v>253</v>
       </c>
       <c r="S101" s="3">
         <v>-5500</v>
@@ -11740,13 +11738,13 @@
         <v>0</v>
       </c>
       <c r="P102" s="3">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="Q102" s="3">
         <v>4</v>
       </c>
       <c r="R102" s="3">
-        <v>783</v>
+        <v>634</v>
       </c>
       <c r="S102" s="3">
         <v>-5500</v>
@@ -11947,13 +11945,13 @@
         <v>0</v>
       </c>
       <c r="P104" s="3">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="Q104" s="3">
         <v>0</v>
       </c>
       <c r="R104" s="3">
-        <v>261</v>
+        <v>211</v>
       </c>
       <c r="S104" s="3">
         <v>-5500</v>
@@ -12056,7 +12054,7 @@
         <v>2</v>
       </c>
       <c r="R105" s="3">
-        <v>413</v>
+        <v>334</v>
       </c>
       <c r="S105" s="3">
         <v>-5500</v>
@@ -13088,13 +13086,13 @@
         <v>0</v>
       </c>
       <c r="P115" s="3">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="Q115" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R115" s="15">
-        <v>5745</v>
+        <v>4646</v>
       </c>
       <c r="S115" s="3">
         <v>-5500</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C1F61DF-1E98-4A90-8E60-1562C9FC7605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF2B72D1-26B8-4E8D-AEEE-79C0B8E4F73A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8948,7 +8948,7 @@
         <v>0</v>
       </c>
       <c r="P75" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q75" s="3">
         <v>1</v>
@@ -10080,13 +10080,13 @@
         <v>0</v>
       </c>
       <c r="P86" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Q86" s="3">
         <v>0</v>
       </c>
       <c r="R86" s="3">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="S86" s="3">
         <v>-5500</v>
@@ -10183,13 +10183,13 @@
         <v>0</v>
       </c>
       <c r="P87" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q87" s="3">
         <v>3</v>
       </c>
       <c r="R87" s="3">
-        <v>324</v>
+        <v>292</v>
       </c>
       <c r="S87" s="3">
         <v>-5500</v>
@@ -10390,13 +10390,13 @@
         <v>0</v>
       </c>
       <c r="P89" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q89" s="3">
         <v>0</v>
       </c>
       <c r="R89" s="3">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="S89" s="3">
         <v>-5500</v>
@@ -10493,13 +10493,13 @@
         <v>0</v>
       </c>
       <c r="P90" s="3">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Q90" s="3">
         <v>2</v>
       </c>
       <c r="R90" s="3">
-        <v>146</v>
+        <v>116</v>
       </c>
       <c r="S90" s="3">
         <v>-5500</v>
@@ -11635,13 +11635,13 @@
         <v>0</v>
       </c>
       <c r="P101" s="3">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
       </c>
       <c r="R101" s="3">
-        <v>253</v>
+        <v>211</v>
       </c>
       <c r="S101" s="3">
         <v>-5500</v>
@@ -11744,7 +11744,7 @@
         <v>4</v>
       </c>
       <c r="R102" s="3">
-        <v>634</v>
+        <v>570</v>
       </c>
       <c r="S102" s="3">
         <v>-5500</v>
@@ -11945,13 +11945,13 @@
         <v>0</v>
       </c>
       <c r="P104" s="3">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="Q104" s="3">
         <v>0</v>
       </c>
       <c r="R104" s="3">
-        <v>211</v>
+        <v>169</v>
       </c>
       <c r="S104" s="3">
         <v>-5500</v>
@@ -12048,13 +12048,13 @@
         <v>0</v>
       </c>
       <c r="P105" s="3">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="Q105" s="3">
         <v>2</v>
       </c>
       <c r="R105" s="3">
-        <v>334</v>
+        <v>268</v>
       </c>
       <c r="S105" s="3">
         <v>-5500</v>
@@ -12879,13 +12879,13 @@
         <v>0</v>
       </c>
       <c r="P113" s="3">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="Q113" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R113" s="15">
-        <v>1496</v>
+        <v>570</v>
       </c>
       <c r="S113" s="3">
         <v>-5500</v>
@@ -13086,13 +13086,13 @@
         <v>0</v>
       </c>
       <c r="P115" s="3">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="Q115" s="3">
         <v>7</v>
       </c>
       <c r="R115" s="15">
-        <v>4646</v>
+        <v>4356</v>
       </c>
       <c r="S115" s="3">
         <v>-5500</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF2B72D1-26B8-4E8D-AEEE-79C0B8E4F73A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="maze_foe_v8" sheetId="1" r:id="rId1"/>
@@ -30,6 +24,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -519,6 +515,57 @@
     <t>石像鬼精英</t>
   </si>
   <si>
+    <t>2-守卫1</t>
+  </si>
+  <si>
+    <t>3-守卫1</t>
+  </si>
+  <si>
+    <t>3-守卫2</t>
+  </si>
+  <si>
+    <t>4-守卫1</t>
+  </si>
+  <si>
+    <t>4-守卫2</t>
+  </si>
+  <si>
+    <t>5-守卫1</t>
+  </si>
+  <si>
+    <t>5-守卫2</t>
+  </si>
+  <si>
+    <t>5-守卫3</t>
+  </si>
+  <si>
+    <t>5-守卫4</t>
+  </si>
+  <si>
+    <t>6-守卫1</t>
+  </si>
+  <si>
+    <t>6-守卫2</t>
+  </si>
+  <si>
+    <t>6-守卫3</t>
+  </si>
+  <si>
+    <t>6-守卫4</t>
+  </si>
+  <si>
+    <t>6-守卫5</t>
+  </si>
+  <si>
+    <t>6-守卫6</t>
+  </si>
+  <si>
+    <t>6-守卫7</t>
+  </si>
+  <si>
+    <t>6-守卫8</t>
+  </si>
+  <si>
     <t>攻击技能</t>
   </si>
   <si>
@@ -629,63 +676,71 @@
   <si>
     <t>装备分数</t>
   </si>
-  <si>
-    <t>2-守卫1</t>
-  </si>
-  <si>
-    <t>3-守卫1</t>
-  </si>
-  <si>
-    <t>3-守卫2</t>
-  </si>
-  <si>
-    <t>4-守卫1</t>
-  </si>
-  <si>
-    <t>4-守卫2</t>
-  </si>
-  <si>
-    <t>5-守卫1</t>
-  </si>
-  <si>
-    <t>5-守卫2</t>
-  </si>
-  <si>
-    <t>5-守卫3</t>
-  </si>
-  <si>
-    <t>5-守卫4</t>
-  </si>
-  <si>
-    <t>6-守卫1</t>
-  </si>
-  <si>
-    <t>6-守卫2</t>
-  </si>
-  <si>
-    <t>6-守卫3</t>
-  </si>
-  <si>
-    <t>6-守卫4</t>
-  </si>
-  <si>
-    <t>6-守卫5</t>
-  </si>
-  <si>
-    <t>6-守卫6</t>
-  </si>
-  <si>
-    <t>6-守卫7</t>
-  </si>
-  <si>
-    <t>6-守卫8</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="32">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="5" tint="0.799951170384838"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFEE0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -697,75 +752,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="5" tint="0.79995117038483843"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFEE0000"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -773,40 +759,160 @@
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -815,13 +921,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <fgColor theme="0" tint="-0.349986266670736"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79976805932798245"/>
+        <fgColor theme="5" tint="0.799768059327982"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -845,17 +951,192 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -913,105 +1194,376 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="6">
+  <cellStyleXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="16" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="16" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="51"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="52" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="53">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
-    <cellStyle name="常规 2 2" xfId="5" xr:uid="{7D443560-E36C-4DC8-83DE-3D699464C87A}"/>
-    <cellStyle name="常规 3" xfId="3" xr:uid="{763D98E0-5C7D-4AE2-8906-6D59461EC424}"/>
-    <cellStyle name="输入" xfId="1" builtinId="20"/>
-    <cellStyle name="输入 2" xfId="4" xr:uid="{03AB5DB4-8245-4025-B75C-A087E59607CF}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 2" xfId="49"/>
+    <cellStyle name="常规 2 2" xfId="50"/>
+    <cellStyle name="常规 3" xfId="51"/>
+    <cellStyle name="输入 2" xfId="52"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -1029,9 +1581,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1289,15 +1838,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:AJ132"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="20.125" style="8" customWidth="1"/>
     <col min="2" max="2" width="10.625" style="8" customWidth="1"/>
@@ -1322,7 +1870,7 @@
     <col min="37" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:31">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1354,7 +1902,7 @@
       <c r="AD1" s="3"/>
       <c r="AE1" s="3"/>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="2" ht="14.25" spans="1:36">
       <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
@@ -1464,7 +2012,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="3" ht="14.25" spans="1:36">
       <c r="A3" s="11" t="s">
         <v>9</v>
       </c>
@@ -1574,7 +2122,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:36" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" ht="25.5" customHeight="1" spans="1:36">
       <c r="A4" s="11" t="s">
         <v>45</v>
       </c>
@@ -1684,7 +2232,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36">
       <c r="A5" s="3">
         <v>10201</v>
       </c>
@@ -1702,7 +2250,7 @@
       <c r="H5" s="3">
         <v>2</v>
       </c>
-      <c r="I5" s="20" t="s">
+      <c r="I5" s="25" t="s">
         <v>81</v>
       </c>
       <c r="J5" s="3">
@@ -1787,7 +2335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36">
       <c r="A6" s="3">
         <v>10301</v>
       </c>
@@ -1805,7 +2353,7 @@
       <c r="H6" s="3">
         <v>2</v>
       </c>
-      <c r="I6" s="20" t="s">
+      <c r="I6" s="25" t="s">
         <v>81</v>
       </c>
       <c r="J6" s="3">
@@ -1890,7 +2438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36">
       <c r="A7" s="3">
         <v>10302</v>
       </c>
@@ -1908,7 +2456,7 @@
       <c r="H7" s="3">
         <v>2</v>
       </c>
-      <c r="I7" s="20" t="s">
+      <c r="I7" s="25" t="s">
         <v>81</v>
       </c>
       <c r="J7" s="3">
@@ -1993,7 +2541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36">
       <c r="A8" s="3">
         <v>10303</v>
       </c>
@@ -2011,7 +2559,7 @@
       <c r="H8" s="3">
         <v>2</v>
       </c>
-      <c r="I8" s="20" t="s">
+      <c r="I8" s="25" t="s">
         <v>81</v>
       </c>
       <c r="J8" s="3">
@@ -2096,7 +2644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36">
       <c r="A9" s="3">
         <v>10304</v>
       </c>
@@ -2114,7 +2662,7 @@
       <c r="H9" s="3">
         <v>2</v>
       </c>
-      <c r="I9" s="20" t="s">
+      <c r="I9" s="25" t="s">
         <v>81</v>
       </c>
       <c r="J9" s="3">
@@ -2199,7 +2747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36">
       <c r="A10" s="3">
         <v>10305</v>
       </c>
@@ -2217,7 +2765,7 @@
       <c r="H10" s="3">
         <v>2</v>
       </c>
-      <c r="I10" s="20" t="s">
+      <c r="I10" s="25" t="s">
         <v>81</v>
       </c>
       <c r="J10" s="3">
@@ -2302,7 +2850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36">
       <c r="A11" s="3">
         <v>10306</v>
       </c>
@@ -2320,7 +2868,7 @@
       <c r="H11" s="3">
         <v>2</v>
       </c>
-      <c r="I11" s="20" t="s">
+      <c r="I11" s="25" t="s">
         <v>81</v>
       </c>
       <c r="J11" s="3">
@@ -2405,7 +2953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36">
       <c r="A12" s="3">
         <v>10307</v>
       </c>
@@ -2423,7 +2971,7 @@
       <c r="H12" s="3">
         <v>2</v>
       </c>
-      <c r="I12" s="20" t="s">
+      <c r="I12" s="25" t="s">
         <v>81</v>
       </c>
       <c r="J12" s="3">
@@ -2508,7 +3056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36">
       <c r="A13" s="3">
         <v>10308</v>
       </c>
@@ -2526,7 +3074,7 @@
       <c r="H13" s="3">
         <v>2</v>
       </c>
-      <c r="I13" s="20" t="s">
+      <c r="I13" s="25" t="s">
         <v>81</v>
       </c>
       <c r="J13" s="3">
@@ -2611,7 +3159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36">
       <c r="A14" s="3">
         <v>10309</v>
       </c>
@@ -2629,7 +3177,7 @@
       <c r="H14" s="3">
         <v>2</v>
       </c>
-      <c r="I14" s="20" t="s">
+      <c r="I14" s="25" t="s">
         <v>81</v>
       </c>
       <c r="J14" s="3">
@@ -2714,7 +3262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36">
       <c r="A15" s="3">
         <v>10310</v>
       </c>
@@ -2732,7 +3280,7 @@
       <c r="H15" s="3">
         <v>2</v>
       </c>
-      <c r="I15" s="20" t="s">
+      <c r="I15" s="25" t="s">
         <v>81</v>
       </c>
       <c r="J15" s="3">
@@ -2817,7 +3365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36">
       <c r="A16" s="3">
         <v>10401</v>
       </c>
@@ -2835,7 +3383,7 @@
       <c r="H16" s="3">
         <v>2</v>
       </c>
-      <c r="I16" s="20" t="s">
+      <c r="I16" s="25" t="s">
         <v>81</v>
       </c>
       <c r="J16" s="3">
@@ -2920,7 +3468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:36">
       <c r="A17" s="3">
         <v>10402</v>
       </c>
@@ -2938,7 +3486,7 @@
       <c r="H17" s="3">
         <v>2</v>
       </c>
-      <c r="I17" s="20" t="s">
+      <c r="I17" s="25" t="s">
         <v>81</v>
       </c>
       <c r="J17" s="3">
@@ -3023,7 +3571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:36">
       <c r="A18" s="3">
         <v>10403</v>
       </c>
@@ -3041,7 +3589,7 @@
       <c r="H18" s="3">
         <v>2</v>
       </c>
-      <c r="I18" s="20" t="s">
+      <c r="I18" s="25" t="s">
         <v>81</v>
       </c>
       <c r="J18" s="3">
@@ -3126,7 +3674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:36">
       <c r="A19" s="3">
         <v>20201</v>
       </c>
@@ -3144,7 +3692,7 @@
       <c r="H19" s="3">
         <v>2</v>
       </c>
-      <c r="I19" s="20" t="s">
+      <c r="I19" s="25" t="s">
         <v>81</v>
       </c>
       <c r="J19" s="3">
@@ -3229,7 +3777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:36">
       <c r="A20" s="3">
         <v>20301</v>
       </c>
@@ -3247,7 +3795,7 @@
       <c r="H20" s="3">
         <v>2</v>
       </c>
-      <c r="I20" s="20" t="s">
+      <c r="I20" s="25" t="s">
         <v>81</v>
       </c>
       <c r="J20" s="3">
@@ -3332,7 +3880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:36">
       <c r="A21" s="3">
         <v>20302</v>
       </c>
@@ -3350,7 +3898,7 @@
       <c r="H21" s="3">
         <v>2</v>
       </c>
-      <c r="I21" s="20" t="s">
+      <c r="I21" s="25" t="s">
         <v>81</v>
       </c>
       <c r="J21" s="3">
@@ -3435,7 +3983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:36">
       <c r="A22" s="3">
         <v>20303</v>
       </c>
@@ -3453,7 +4001,7 @@
       <c r="H22" s="3">
         <v>2</v>
       </c>
-      <c r="I22" s="20" t="s">
+      <c r="I22" s="25" t="s">
         <v>81</v>
       </c>
       <c r="J22" s="3">
@@ -3538,7 +4086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:36">
       <c r="A23" s="3">
         <v>20304</v>
       </c>
@@ -3556,7 +4104,7 @@
       <c r="H23" s="3">
         <v>2</v>
       </c>
-      <c r="I23" s="20" t="s">
+      <c r="I23" s="25" t="s">
         <v>81</v>
       </c>
       <c r="J23" s="3">
@@ -3641,7 +4189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:36">
       <c r="A24" s="3">
         <v>20305</v>
       </c>
@@ -3659,7 +4207,7 @@
       <c r="H24" s="3">
         <v>2</v>
       </c>
-      <c r="I24" s="20" t="s">
+      <c r="I24" s="25" t="s">
         <v>81</v>
       </c>
       <c r="J24" s="3">
@@ -3744,7 +4292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:36">
       <c r="A25" s="3">
         <v>20306</v>
       </c>
@@ -3762,7 +4310,7 @@
       <c r="H25" s="3">
         <v>2</v>
       </c>
-      <c r="I25" s="20" t="s">
+      <c r="I25" s="25" t="s">
         <v>81</v>
       </c>
       <c r="J25" s="3">
@@ -3847,7 +4395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:36">
       <c r="A26" s="3">
         <v>20307</v>
       </c>
@@ -3865,7 +4413,7 @@
       <c r="H26" s="3">
         <v>2</v>
       </c>
-      <c r="I26" s="20" t="s">
+      <c r="I26" s="25" t="s">
         <v>81</v>
       </c>
       <c r="J26" s="3">
@@ -3950,7 +4498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:36">
       <c r="A27" s="3">
         <v>20308</v>
       </c>
@@ -3968,7 +4516,7 @@
       <c r="H27" s="3">
         <v>2</v>
       </c>
-      <c r="I27" s="20" t="s">
+      <c r="I27" s="25" t="s">
         <v>81</v>
       </c>
       <c r="J27" s="3">
@@ -4053,7 +4601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:36">
       <c r="A28" s="3">
         <v>20309</v>
       </c>
@@ -4071,7 +4619,7 @@
       <c r="H28" s="3">
         <v>2</v>
       </c>
-      <c r="I28" s="20" t="s">
+      <c r="I28" s="25" t="s">
         <v>81</v>
       </c>
       <c r="J28" s="3">
@@ -4156,7 +4704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:36">
       <c r="A29" s="3">
         <v>20310</v>
       </c>
@@ -4174,7 +4722,7 @@
       <c r="H29" s="3">
         <v>2</v>
       </c>
-      <c r="I29" s="20" t="s">
+      <c r="I29" s="25" t="s">
         <v>81</v>
       </c>
       <c r="J29" s="3">
@@ -4259,7 +4807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:36">
       <c r="A30" s="3">
         <v>20401</v>
       </c>
@@ -4277,7 +4825,7 @@
       <c r="H30" s="3">
         <v>2</v>
       </c>
-      <c r="I30" s="20" t="s">
+      <c r="I30" s="25" t="s">
         <v>81</v>
       </c>
       <c r="J30" s="3">
@@ -4362,7 +4910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:36">
       <c r="A31" s="3">
         <v>20402</v>
       </c>
@@ -4380,7 +4928,7 @@
       <c r="H31" s="3">
         <v>2</v>
       </c>
-      <c r="I31" s="20" t="s">
+      <c r="I31" s="25" t="s">
         <v>81</v>
       </c>
       <c r="J31" s="3">
@@ -4465,7 +5013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:36">
       <c r="A32" s="3">
         <v>20403</v>
       </c>
@@ -4483,7 +5031,7 @@
       <c r="H32" s="3">
         <v>2</v>
       </c>
-      <c r="I32" s="20" t="s">
+      <c r="I32" s="25" t="s">
         <v>81</v>
       </c>
       <c r="J32" s="3">
@@ -4568,7 +5116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:36">
       <c r="A33" s="3">
         <v>110201</v>
       </c>
@@ -4586,7 +5134,7 @@
       <c r="H33" s="3">
         <v>2</v>
       </c>
-      <c r="I33" s="20" t="s">
+      <c r="I33" s="25" t="s">
         <v>81</v>
       </c>
       <c r="J33" s="3">
@@ -4671,7 +5219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:36">
       <c r="A34" s="3">
         <v>110301</v>
       </c>
@@ -4689,7 +5237,7 @@
       <c r="H34" s="3">
         <v>2</v>
       </c>
-      <c r="I34" s="20" t="s">
+      <c r="I34" s="25" t="s">
         <v>81</v>
       </c>
       <c r="J34" s="3">
@@ -4774,7 +5322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:36">
       <c r="A35" s="3">
         <v>110302</v>
       </c>
@@ -4792,7 +5340,7 @@
       <c r="H35" s="3">
         <v>2</v>
       </c>
-      <c r="I35" s="20" t="s">
+      <c r="I35" s="25" t="s">
         <v>81</v>
       </c>
       <c r="J35" s="3">
@@ -4877,7 +5425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:36">
       <c r="A36" s="3">
         <v>110303</v>
       </c>
@@ -4895,7 +5443,7 @@
       <c r="H36" s="3">
         <v>2</v>
       </c>
-      <c r="I36" s="20" t="s">
+      <c r="I36" s="25" t="s">
         <v>81</v>
       </c>
       <c r="J36" s="3">
@@ -4980,7 +5528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:36">
       <c r="A37" s="3">
         <v>110304</v>
       </c>
@@ -4998,7 +5546,7 @@
       <c r="H37" s="3">
         <v>2</v>
       </c>
-      <c r="I37" s="20" t="s">
+      <c r="I37" s="25" t="s">
         <v>81</v>
       </c>
       <c r="J37" s="3">
@@ -5083,7 +5631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:36">
       <c r="A38" s="3">
         <v>110305</v>
       </c>
@@ -5101,7 +5649,7 @@
       <c r="H38" s="3">
         <v>2</v>
       </c>
-      <c r="I38" s="20" t="s">
+      <c r="I38" s="25" t="s">
         <v>81</v>
       </c>
       <c r="J38" s="3">
@@ -5186,7 +5734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:36">
       <c r="A39" s="3">
         <v>110306</v>
       </c>
@@ -5204,7 +5752,7 @@
       <c r="H39" s="3">
         <v>2</v>
       </c>
-      <c r="I39" s="20" t="s">
+      <c r="I39" s="25" t="s">
         <v>81</v>
       </c>
       <c r="J39" s="3">
@@ -5289,7 +5837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:36">
       <c r="A40" s="3">
         <v>110307</v>
       </c>
@@ -5307,7 +5855,7 @@
       <c r="H40" s="3">
         <v>2</v>
       </c>
-      <c r="I40" s="20" t="s">
+      <c r="I40" s="25" t="s">
         <v>81</v>
       </c>
       <c r="J40" s="3">
@@ -5392,7 +5940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:36">
       <c r="A41" s="3">
         <v>110308</v>
       </c>
@@ -5410,7 +5958,7 @@
       <c r="H41" s="3">
         <v>2</v>
       </c>
-      <c r="I41" s="20" t="s">
+      <c r="I41" s="25" t="s">
         <v>81</v>
       </c>
       <c r="J41" s="3">
@@ -5495,7 +6043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:36">
       <c r="A42" s="3">
         <v>110309</v>
       </c>
@@ -5513,7 +6061,7 @@
       <c r="H42" s="3">
         <v>2</v>
       </c>
-      <c r="I42" s="20" t="s">
+      <c r="I42" s="25" t="s">
         <v>81</v>
       </c>
       <c r="J42" s="3">
@@ -5598,7 +6146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:36">
       <c r="A43" s="3">
         <v>110310</v>
       </c>
@@ -5616,7 +6164,7 @@
       <c r="H43" s="3">
         <v>2</v>
       </c>
-      <c r="I43" s="20" t="s">
+      <c r="I43" s="25" t="s">
         <v>81</v>
       </c>
       <c r="J43" s="3">
@@ -5701,7 +6249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:36">
       <c r="A44" s="3">
         <v>110401</v>
       </c>
@@ -5719,7 +6267,7 @@
       <c r="H44" s="3">
         <v>2</v>
       </c>
-      <c r="I44" s="20" t="s">
+      <c r="I44" s="25" t="s">
         <v>81</v>
       </c>
       <c r="J44" s="3">
@@ -5804,7 +6352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:36">
       <c r="A45" s="3">
         <v>110402</v>
       </c>
@@ -5822,7 +6370,7 @@
       <c r="H45" s="3">
         <v>2</v>
       </c>
-      <c r="I45" s="20" t="s">
+      <c r="I45" s="25" t="s">
         <v>81</v>
       </c>
       <c r="J45" s="3">
@@ -5907,7 +6455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:36">
       <c r="A46" s="3">
         <v>110403</v>
       </c>
@@ -5925,7 +6473,7 @@
       <c r="H46" s="3">
         <v>2</v>
       </c>
-      <c r="I46" s="20" t="s">
+      <c r="I46" s="25" t="s">
         <v>81</v>
       </c>
       <c r="J46" s="3">
@@ -6010,7 +6558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:36">
       <c r="A47" s="3">
         <v>121101</v>
       </c>
@@ -6056,7 +6604,7 @@
         <v>1</v>
       </c>
       <c r="R47" s="3">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="S47" s="3">
         <v>-6500</v>
@@ -6113,7 +6661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:36">
       <c r="A48" s="3">
         <v>121102</v>
       </c>
@@ -6159,7 +6707,7 @@
         <v>4</v>
       </c>
       <c r="R48" s="3">
-        <v>651</v>
+        <v>93</v>
       </c>
       <c r="S48" s="3">
         <v>-4750</v>
@@ -6216,7 +6764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:36">
       <c r="A49" s="2">
         <v>121103</v>
       </c>
@@ -6320,7 +6868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:36">
       <c r="A50" s="3">
         <v>121104</v>
       </c>
@@ -6366,7 +6914,7 @@
         <v>1</v>
       </c>
       <c r="R50" s="3">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="S50" s="3">
         <v>-6500</v>
@@ -6423,7 +6971,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="51" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:36">
       <c r="A51" s="3">
         <v>121105</v>
       </c>
@@ -6469,7 +7017,7 @@
         <v>1</v>
       </c>
       <c r="R51" s="3">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="S51" s="3">
         <v>-6500</v>
@@ -6526,7 +7074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:36">
       <c r="A52" s="2">
         <v>121106</v>
       </c>
@@ -6630,7 +7178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:36">
       <c r="A53" s="2">
         <v>121107</v>
       </c>
@@ -6734,7 +7282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:36">
       <c r="A54" s="2">
         <v>121108</v>
       </c>
@@ -6838,7 +7386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:36">
       <c r="A55" s="2">
         <v>121109</v>
       </c>
@@ -6942,7 +7490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:36">
       <c r="A56" s="2">
         <v>121110</v>
       </c>
@@ -7046,7 +7594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:36">
       <c r="A57" s="2">
         <v>121111</v>
       </c>
@@ -7150,7 +7698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:36">
       <c r="A58" s="2">
         <v>121112</v>
       </c>
@@ -7254,7 +7802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="59" ht="14.25" spans="1:36">
       <c r="A59" s="3">
         <v>121113</v>
       </c>
@@ -7300,7 +7848,7 @@
         <v>6</v>
       </c>
       <c r="R59" s="15">
-        <v>4023</v>
+        <v>552</v>
       </c>
       <c r="S59" s="3">
         <v>-1600</v>
@@ -7357,7 +7905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:36">
       <c r="A60" s="2">
         <v>121114</v>
       </c>
@@ -7461,7 +8009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:36">
       <c r="A61" s="2">
         <v>121115</v>
       </c>
@@ -7565,7 +8113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:36">
       <c r="A62" s="3">
         <v>999001</v>
       </c>
@@ -7668,7 +8216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:36">
       <c r="A63" s="3">
         <v>999002</v>
       </c>
@@ -7771,7 +8319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:36">
       <c r="A64" s="3">
         <v>999003</v>
       </c>
@@ -7874,7 +8422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:36">
       <c r="A65" s="3">
         <v>999004</v>
       </c>
@@ -7977,7 +8525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="66" ht="14.25" spans="1:36">
       <c r="A66" s="18">
         <v>9999001</v>
       </c>
@@ -8044,10 +8592,10 @@
       <c r="X66" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="Y66" s="19">
+      <c r="Y66" s="22">
         <v>201001011</v>
       </c>
-      <c r="Z66" s="19">
+      <c r="Z66" s="22">
         <v>0</v>
       </c>
       <c r="AA66" s="18">
@@ -8081,7 +8629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="67" ht="14.25" spans="1:36">
       <c r="A67" s="18">
         <v>9999002</v>
       </c>
@@ -8148,10 +8696,10 @@
       <c r="X67" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="Y67" s="19">
+      <c r="Y67" s="22">
         <v>201002011</v>
       </c>
-      <c r="Z67" s="19">
+      <c r="Z67" s="22">
         <v>0</v>
       </c>
       <c r="AA67" s="18">
@@ -8185,7 +8733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="68" ht="14.25" spans="1:36">
       <c r="A68" s="18">
         <v>9999004</v>
       </c>
@@ -8252,10 +8800,10 @@
       <c r="X68" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="Y68" s="19">
+      <c r="Y68" s="22">
         <v>201004011</v>
       </c>
-      <c r="Z68" s="19">
+      <c r="Z68" s="22">
         <v>0</v>
       </c>
       <c r="AA68" s="18">
@@ -8289,7 +8837,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="69" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="69" ht="14.25" spans="1:36">
       <c r="A69" s="18">
         <v>9999005</v>
       </c>
@@ -8356,10 +8904,10 @@
       <c r="X69" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="Y69" s="19">
+      <c r="Y69" s="22">
         <v>214001011</v>
       </c>
-      <c r="Z69" s="19">
+      <c r="Z69" s="22">
         <v>0</v>
       </c>
       <c r="AA69" s="18">
@@ -8393,7 +8941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="70" ht="14.25" spans="1:36">
       <c r="A70" s="18">
         <v>9999013</v>
       </c>
@@ -8460,10 +9008,10 @@
       <c r="X70" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="Y70" s="19">
+      <c r="Y70" s="22">
         <v>203002011</v>
       </c>
-      <c r="Z70" s="19">
+      <c r="Z70" s="22">
         <v>0</v>
       </c>
       <c r="AA70" s="18">
@@ -8497,7 +9045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:36">
       <c r="A71" s="3">
         <v>301101</v>
       </c>
@@ -8600,7 +9148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:36">
       <c r="A72" s="3">
         <v>301102</v>
       </c>
@@ -8703,7 +9251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:36">
       <c r="A73" s="2">
         <v>301103</v>
       </c>
@@ -8805,7 +9353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:36">
       <c r="A74" s="3">
         <v>301104</v>
       </c>
@@ -8908,7 +9456,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="75" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:36">
       <c r="A75" s="3">
         <v>301105</v>
       </c>
@@ -9011,7 +9559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:36">
       <c r="A76" s="2">
         <v>301106</v>
       </c>
@@ -9113,7 +9661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:36">
       <c r="A77" s="2">
         <v>301107</v>
       </c>
@@ -9217,7 +9765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="78" ht="14.25" spans="1:36">
       <c r="A78" s="3">
         <v>301108</v>
       </c>
@@ -9320,7 +9868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="79" ht="14.25" spans="1:36">
       <c r="A79" s="3">
         <v>301109</v>
       </c>
@@ -9423,7 +9971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="80" ht="14.25" spans="1:36">
       <c r="A80" s="3">
         <v>301110</v>
       </c>
@@ -9526,7 +10074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="81" ht="14.25" spans="1:36">
       <c r="A81" s="3">
         <v>301111</v>
       </c>
@@ -9629,7 +10177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="82" ht="14.25" spans="1:36">
       <c r="A82" s="3">
         <v>301112</v>
       </c>
@@ -9732,7 +10280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="83" ht="14.25" spans="1:36">
       <c r="A83" s="3">
         <v>301113</v>
       </c>
@@ -9835,7 +10383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="84" ht="14.25" spans="1:36">
       <c r="A84" s="3">
         <v>301114</v>
       </c>
@@ -9938,7 +10486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:36">
       <c r="A85" s="2">
         <v>301115</v>
       </c>
@@ -10040,7 +10588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:36">
       <c r="A86" s="3">
         <v>302101</v>
       </c>
@@ -10143,7 +10691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:36">
       <c r="A87" s="3">
         <v>302102</v>
       </c>
@@ -10246,7 +10794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:36">
       <c r="A88" s="2">
         <v>302103</v>
       </c>
@@ -10350,7 +10898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:36">
       <c r="A89" s="3">
         <v>302104</v>
       </c>
@@ -10453,7 +11001,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:36">
       <c r="A90" s="3">
         <v>302105</v>
       </c>
@@ -10556,7 +11104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:36">
       <c r="A91" s="2">
         <v>302106</v>
       </c>
@@ -10660,7 +11208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:36">
       <c r="A92" s="2">
         <v>302107</v>
       </c>
@@ -10764,7 +11312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:36">
       <c r="A93" s="2">
         <v>302108</v>
       </c>
@@ -10868,7 +11416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:36">
       <c r="A94" s="2">
         <v>302109</v>
       </c>
@@ -10972,7 +11520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:36">
       <c r="A95" s="2">
         <v>302110</v>
       </c>
@@ -11076,7 +11624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:36">
       <c r="A96" s="2">
         <v>302111</v>
       </c>
@@ -11180,7 +11728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:36">
       <c r="A97" s="2">
         <v>302112</v>
       </c>
@@ -11284,7 +11832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="98" ht="14.25" spans="1:36">
       <c r="A98" s="3">
         <v>302113</v>
       </c>
@@ -11387,7 +11935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:36">
       <c r="A99" s="2">
         <v>302114</v>
       </c>
@@ -11491,7 +12039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:36">
       <c r="A100" s="2">
         <v>302115</v>
       </c>
@@ -11595,7 +12143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:36">
       <c r="A101" s="3">
         <v>303101</v>
       </c>
@@ -11698,7 +12246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:36">
       <c r="A102" s="3">
         <v>303102</v>
       </c>
@@ -11801,7 +12349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:36">
       <c r="A103" s="2">
         <v>303103</v>
       </c>
@@ -11905,7 +12453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:36">
       <c r="A104" s="3">
         <v>303104</v>
       </c>
@@ -12008,7 +12556,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="105" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:36">
       <c r="A105" s="3">
         <v>303105</v>
       </c>
@@ -12111,7 +12659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:36">
       <c r="A106" s="2">
         <v>303106</v>
       </c>
@@ -12215,7 +12763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:36">
       <c r="A107" s="2">
         <v>303107</v>
       </c>
@@ -12319,7 +12867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:36">
       <c r="A108" s="2">
         <v>303108</v>
       </c>
@@ -12423,7 +12971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:36">
       <c r="A109" s="2">
         <v>303109</v>
       </c>
@@ -12527,7 +13075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:36">
       <c r="A110" s="2">
         <v>303110</v>
       </c>
@@ -12631,7 +13179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:36">
       <c r="A111" s="2">
         <v>303111</v>
       </c>
@@ -12735,7 +13283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:36">
       <c r="A112" s="2">
         <v>303112</v>
       </c>
@@ -12839,7 +13387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="113" ht="14.25" spans="1:36">
       <c r="A113" s="3">
         <v>303113</v>
       </c>
@@ -12942,7 +13490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:36">
       <c r="A114" s="2">
         <v>303114</v>
       </c>
@@ -13046,7 +13594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="115" ht="14.25" spans="1:36">
       <c r="A115" s="3">
         <v>303115</v>
       </c>
@@ -13149,1797 +13697,1797 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A116" s="23">
+    <row r="116" ht="14.25" spans="1:36">
+      <c r="A116" s="19">
         <v>90000201</v>
       </c>
-      <c r="B116" s="23">
+      <c r="B116" s="19">
         <v>2</v>
       </c>
-      <c r="C116" s="23" t="s">
-        <v>197</v>
-      </c>
-      <c r="D116" s="23"/>
-      <c r="E116" s="21"/>
-      <c r="F116" s="23"/>
-      <c r="G116" s="25">
-        <v>1</v>
-      </c>
-      <c r="H116" s="25">
+      <c r="C116" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="D116" s="19"/>
+      <c r="E116" s="20"/>
+      <c r="F116" s="19"/>
+      <c r="G116" s="19">
+        <v>1</v>
+      </c>
+      <c r="H116" s="19">
         <v>2</v>
       </c>
-      <c r="I116" s="25" t="s">
+      <c r="I116" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="J116" s="23">
-        <v>0</v>
-      </c>
-      <c r="K116" s="23" t="s">
+      <c r="J116" s="19">
+        <v>0</v>
+      </c>
+      <c r="K116" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="L116" s="23">
+      <c r="L116" s="19">
         <v>800001011</v>
       </c>
-      <c r="M116" s="23">
-        <v>1</v>
-      </c>
-      <c r="N116" s="26">
-        <v>1</v>
-      </c>
-      <c r="O116" s="23">
-        <v>1</v>
-      </c>
-      <c r="P116" s="23">
+      <c r="M116" s="19">
+        <v>1</v>
+      </c>
+      <c r="N116" s="21">
+        <v>1</v>
+      </c>
+      <c r="O116" s="19">
+        <v>1</v>
+      </c>
+      <c r="P116" s="19">
         <v>8</v>
       </c>
-      <c r="Q116" s="23">
-        <v>0</v>
-      </c>
-      <c r="R116" s="23">
+      <c r="Q116" s="19">
+        <v>0</v>
+      </c>
+      <c r="R116" s="19">
         <v>25</v>
       </c>
-      <c r="S116" s="23">
+      <c r="S116" s="19">
         <v>-5000</v>
       </c>
-      <c r="T116" s="23">
-        <v>1</v>
-      </c>
-      <c r="U116" s="23">
-        <v>0</v>
-      </c>
-      <c r="V116" s="23" t="s">
+      <c r="T116" s="19">
+        <v>1</v>
+      </c>
+      <c r="U116" s="19">
+        <v>0</v>
+      </c>
+      <c r="V116" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="W116" s="23" t="s">
+      <c r="W116" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="X116" s="23" t="s">
+      <c r="X116" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="Y116" s="24">
+      <c r="Y116" s="23">
         <v>20010001</v>
       </c>
-      <c r="Z116" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA116" s="23">
-        <v>1</v>
-      </c>
-      <c r="AB116" s="22" t="s">
+      <c r="Z116" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA116" s="19">
+        <v>1</v>
+      </c>
+      <c r="AB116" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="AC116" s="23">
-        <v>10000</v>
-      </c>
-      <c r="AD116" s="23">
-        <v>10000</v>
-      </c>
-      <c r="AE116" s="23">
-        <v>0</v>
-      </c>
-      <c r="AF116" s="22">
+      <c r="AC116" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AD116" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AE116" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF116" s="24">
         <v>40</v>
       </c>
-      <c r="AG116" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH116" s="22">
-        <v>0</v>
-      </c>
-      <c r="AI116" s="22">
-        <v>0</v>
-      </c>
-      <c r="AJ116" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A117" s="23">
+      <c r="AG116" s="24">
+        <v>0</v>
+      </c>
+      <c r="AH116" s="24">
+        <v>0</v>
+      </c>
+      <c r="AI116" s="24">
+        <v>0</v>
+      </c>
+      <c r="AJ116" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" ht="14.25" spans="1:36">
+      <c r="A117" s="19">
         <v>90000301</v>
       </c>
-      <c r="B117" s="23">
+      <c r="B117" s="19">
         <v>3</v>
       </c>
-      <c r="C117" s="23" t="s">
-        <v>198</v>
-      </c>
-      <c r="D117" s="23"/>
-      <c r="E117" s="21"/>
-      <c r="F117" s="23"/>
-      <c r="G117" s="25">
-        <v>1</v>
-      </c>
-      <c r="H117" s="25">
+      <c r="C117" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="D117" s="19"/>
+      <c r="E117" s="20"/>
+      <c r="F117" s="19"/>
+      <c r="G117" s="19">
+        <v>1</v>
+      </c>
+      <c r="H117" s="19">
         <v>2</v>
       </c>
-      <c r="I117" s="25" t="s">
+      <c r="I117" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="J117" s="23">
-        <v>0</v>
-      </c>
-      <c r="K117" s="23" t="s">
+      <c r="J117" s="19">
+        <v>0</v>
+      </c>
+      <c r="K117" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="L117" s="23">
+      <c r="L117" s="19">
         <v>800001011</v>
       </c>
-      <c r="M117" s="23">
-        <v>1</v>
-      </c>
-      <c r="N117" s="26">
-        <v>1</v>
-      </c>
-      <c r="O117" s="23">
-        <v>1</v>
-      </c>
-      <c r="P117" s="23">
+      <c r="M117" s="19">
+        <v>1</v>
+      </c>
+      <c r="N117" s="21">
+        <v>1</v>
+      </c>
+      <c r="O117" s="19">
+        <v>1</v>
+      </c>
+      <c r="P117" s="19">
         <v>8</v>
       </c>
-      <c r="Q117" s="23">
-        <v>0</v>
-      </c>
-      <c r="R117" s="23">
+      <c r="Q117" s="19">
+        <v>0</v>
+      </c>
+      <c r="R117" s="19">
         <v>25</v>
       </c>
-      <c r="S117" s="23">
+      <c r="S117" s="19">
         <v>-5000</v>
       </c>
-      <c r="T117" s="23">
-        <v>1</v>
-      </c>
-      <c r="U117" s="23">
-        <v>0</v>
-      </c>
-      <c r="V117" s="23" t="s">
+      <c r="T117" s="19">
+        <v>1</v>
+      </c>
+      <c r="U117" s="19">
+        <v>0</v>
+      </c>
+      <c r="V117" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="W117" s="23" t="s">
+      <c r="W117" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="X117" s="23" t="s">
+      <c r="X117" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="Y117" s="24">
+      <c r="Y117" s="23">
         <v>20010001</v>
       </c>
-      <c r="Z117" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA117" s="23">
-        <v>1</v>
-      </c>
-      <c r="AB117" s="22" t="s">
+      <c r="Z117" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA117" s="19">
+        <v>1</v>
+      </c>
+      <c r="AB117" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="AC117" s="23">
-        <v>10000</v>
-      </c>
-      <c r="AD117" s="23">
-        <v>10000</v>
-      </c>
-      <c r="AE117" s="23">
-        <v>0</v>
-      </c>
-      <c r="AF117" s="22">
+      <c r="AC117" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AD117" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AE117" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF117" s="24">
         <v>40</v>
       </c>
-      <c r="AG117" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH117" s="22">
-        <v>0</v>
-      </c>
-      <c r="AI117" s="22">
-        <v>0</v>
-      </c>
-      <c r="AJ117" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A118" s="23">
+      <c r="AG117" s="24">
+        <v>0</v>
+      </c>
+      <c r="AH117" s="24">
+        <v>0</v>
+      </c>
+      <c r="AI117" s="24">
+        <v>0</v>
+      </c>
+      <c r="AJ117" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" ht="14.25" spans="1:36">
+      <c r="A118" s="19">
         <v>90000302</v>
       </c>
-      <c r="B118" s="23">
+      <c r="B118" s="19">
         <v>3</v>
       </c>
-      <c r="C118" s="23" t="s">
-        <v>199</v>
-      </c>
-      <c r="D118" s="23"/>
-      <c r="E118" s="21"/>
-      <c r="F118" s="23"/>
-      <c r="G118" s="25">
-        <v>1</v>
-      </c>
-      <c r="H118" s="25">
+      <c r="C118" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="D118" s="19"/>
+      <c r="E118" s="20"/>
+      <c r="F118" s="19"/>
+      <c r="G118" s="19">
+        <v>1</v>
+      </c>
+      <c r="H118" s="19">
         <v>2</v>
       </c>
-      <c r="I118" s="25" t="s">
+      <c r="I118" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="J118" s="23">
-        <v>0</v>
-      </c>
-      <c r="K118" s="23" t="s">
+      <c r="J118" s="19">
+        <v>0</v>
+      </c>
+      <c r="K118" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="L118" s="23">
+      <c r="L118" s="19">
         <v>800001011</v>
       </c>
-      <c r="M118" s="23">
-        <v>1</v>
-      </c>
-      <c r="N118" s="26">
+      <c r="M118" s="19">
+        <v>1</v>
+      </c>
+      <c r="N118" s="21">
         <v>2</v>
       </c>
-      <c r="O118" s="23">
-        <v>1</v>
-      </c>
-      <c r="P118" s="23">
+      <c r="O118" s="19">
+        <v>1</v>
+      </c>
+      <c r="P118" s="19">
         <v>8</v>
       </c>
-      <c r="Q118" s="23">
-        <v>0</v>
-      </c>
-      <c r="R118" s="23">
+      <c r="Q118" s="19">
+        <v>0</v>
+      </c>
+      <c r="R118" s="19">
         <v>25</v>
       </c>
-      <c r="S118" s="23">
+      <c r="S118" s="19">
         <v>-5000</v>
       </c>
-      <c r="T118" s="23">
-        <v>1</v>
-      </c>
-      <c r="U118" s="23">
-        <v>0</v>
-      </c>
-      <c r="V118" s="23" t="s">
+      <c r="T118" s="19">
+        <v>1</v>
+      </c>
+      <c r="U118" s="19">
+        <v>0</v>
+      </c>
+      <c r="V118" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="W118" s="23" t="s">
+      <c r="W118" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="X118" s="23" t="s">
+      <c r="X118" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="Y118" s="24">
+      <c r="Y118" s="23">
         <v>20010001</v>
       </c>
-      <c r="Z118" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA118" s="23">
-        <v>1</v>
-      </c>
-      <c r="AB118" s="22" t="s">
+      <c r="Z118" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA118" s="19">
+        <v>1</v>
+      </c>
+      <c r="AB118" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="AC118" s="23">
-        <v>10000</v>
-      </c>
-      <c r="AD118" s="23">
-        <v>10000</v>
-      </c>
-      <c r="AE118" s="23">
-        <v>0</v>
-      </c>
-      <c r="AF118" s="22">
+      <c r="AC118" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AD118" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AE118" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF118" s="24">
         <v>40</v>
       </c>
-      <c r="AG118" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH118" s="22">
-        <v>0</v>
-      </c>
-      <c r="AI118" s="22">
-        <v>0</v>
-      </c>
-      <c r="AJ118" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A119" s="23">
+      <c r="AG118" s="24">
+        <v>0</v>
+      </c>
+      <c r="AH118" s="24">
+        <v>0</v>
+      </c>
+      <c r="AI118" s="24">
+        <v>0</v>
+      </c>
+      <c r="AJ118" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" ht="14.25" spans="1:36">
+      <c r="A119" s="19">
         <v>90000401</v>
       </c>
-      <c r="B119" s="23">
+      <c r="B119" s="19">
         <v>3</v>
       </c>
-      <c r="C119" s="23" t="s">
-        <v>200</v>
-      </c>
-      <c r="D119" s="23"/>
-      <c r="E119" s="21"/>
-      <c r="F119" s="23"/>
-      <c r="G119" s="25">
-        <v>1</v>
-      </c>
-      <c r="H119" s="25">
+      <c r="C119" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="D119" s="19"/>
+      <c r="E119" s="20"/>
+      <c r="F119" s="19"/>
+      <c r="G119" s="19">
+        <v>1</v>
+      </c>
+      <c r="H119" s="19">
         <v>2</v>
       </c>
-      <c r="I119" s="25" t="s">
+      <c r="I119" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="J119" s="23">
-        <v>0</v>
-      </c>
-      <c r="K119" s="23" t="s">
+      <c r="J119" s="19">
+        <v>0</v>
+      </c>
+      <c r="K119" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="L119" s="23">
+      <c r="L119" s="19">
         <v>800001011</v>
       </c>
-      <c r="M119" s="23">
-        <v>1</v>
-      </c>
-      <c r="N119" s="26">
-        <v>1</v>
-      </c>
-      <c r="O119" s="23">
-        <v>1</v>
-      </c>
-      <c r="P119" s="23">
+      <c r="M119" s="19">
+        <v>1</v>
+      </c>
+      <c r="N119" s="21">
+        <v>1</v>
+      </c>
+      <c r="O119" s="19">
+        <v>1</v>
+      </c>
+      <c r="P119" s="19">
         <v>8</v>
       </c>
-      <c r="Q119" s="23">
-        <v>0</v>
-      </c>
-      <c r="R119" s="23">
+      <c r="Q119" s="19">
+        <v>0</v>
+      </c>
+      <c r="R119" s="19">
         <v>25</v>
       </c>
-      <c r="S119" s="23">
+      <c r="S119" s="19">
         <v>-5000</v>
       </c>
-      <c r="T119" s="23">
-        <v>1</v>
-      </c>
-      <c r="U119" s="23">
-        <v>0</v>
-      </c>
-      <c r="V119" s="23" t="s">
+      <c r="T119" s="19">
+        <v>1</v>
+      </c>
+      <c r="U119" s="19">
+        <v>0</v>
+      </c>
+      <c r="V119" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="W119" s="23" t="s">
+      <c r="W119" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="X119" s="23" t="s">
+      <c r="X119" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="Y119" s="24">
+      <c r="Y119" s="23">
         <v>20010001</v>
       </c>
-      <c r="Z119" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA119" s="23">
-        <v>1</v>
-      </c>
-      <c r="AB119" s="22" t="s">
+      <c r="Z119" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA119" s="19">
+        <v>1</v>
+      </c>
+      <c r="AB119" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="AC119" s="23">
-        <v>10000</v>
-      </c>
-      <c r="AD119" s="23">
-        <v>10000</v>
-      </c>
-      <c r="AE119" s="23">
-        <v>0</v>
-      </c>
-      <c r="AF119" s="22">
+      <c r="AC119" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AD119" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AE119" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF119" s="24">
         <v>40</v>
       </c>
-      <c r="AG119" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH119" s="22">
-        <v>0</v>
-      </c>
-      <c r="AI119" s="22">
-        <v>0</v>
-      </c>
-      <c r="AJ119" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A120" s="23">
+      <c r="AG119" s="24">
+        <v>0</v>
+      </c>
+      <c r="AH119" s="24">
+        <v>0</v>
+      </c>
+      <c r="AI119" s="24">
+        <v>0</v>
+      </c>
+      <c r="AJ119" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" ht="14.25" spans="1:36">
+      <c r="A120" s="19">
         <v>90000402</v>
       </c>
-      <c r="B120" s="23">
+      <c r="B120" s="19">
         <v>3</v>
       </c>
-      <c r="C120" s="23" t="s">
-        <v>201</v>
-      </c>
-      <c r="D120" s="23"/>
-      <c r="E120" s="21"/>
-      <c r="F120" s="23"/>
-      <c r="G120" s="25">
-        <v>1</v>
-      </c>
-      <c r="H120" s="25">
+      <c r="C120" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="D120" s="19"/>
+      <c r="E120" s="20"/>
+      <c r="F120" s="19"/>
+      <c r="G120" s="19">
+        <v>1</v>
+      </c>
+      <c r="H120" s="19">
         <v>2</v>
       </c>
-      <c r="I120" s="25" t="s">
+      <c r="I120" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="J120" s="23">
-        <v>0</v>
-      </c>
-      <c r="K120" s="23" t="s">
+      <c r="J120" s="19">
+        <v>0</v>
+      </c>
+      <c r="K120" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="L120" s="23">
+      <c r="L120" s="19">
         <v>800001011</v>
       </c>
-      <c r="M120" s="23">
-        <v>1</v>
-      </c>
-      <c r="N120" s="26">
+      <c r="M120" s="19">
+        <v>1</v>
+      </c>
+      <c r="N120" s="21">
         <v>2</v>
       </c>
-      <c r="O120" s="23">
-        <v>1</v>
-      </c>
-      <c r="P120" s="23">
+      <c r="O120" s="19">
+        <v>1</v>
+      </c>
+      <c r="P120" s="19">
         <v>8</v>
       </c>
-      <c r="Q120" s="23">
-        <v>0</v>
-      </c>
-      <c r="R120" s="23">
+      <c r="Q120" s="19">
+        <v>0</v>
+      </c>
+      <c r="R120" s="19">
         <v>25</v>
       </c>
-      <c r="S120" s="23">
+      <c r="S120" s="19">
         <v>-5000</v>
       </c>
-      <c r="T120" s="23">
-        <v>1</v>
-      </c>
-      <c r="U120" s="23">
-        <v>0</v>
-      </c>
-      <c r="V120" s="23" t="s">
+      <c r="T120" s="19">
+        <v>1</v>
+      </c>
+      <c r="U120" s="19">
+        <v>0</v>
+      </c>
+      <c r="V120" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="W120" s="23" t="s">
+      <c r="W120" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="X120" s="23" t="s">
+      <c r="X120" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="Y120" s="24">
+      <c r="Y120" s="23">
         <v>20010001</v>
       </c>
-      <c r="Z120" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA120" s="23">
-        <v>1</v>
-      </c>
-      <c r="AB120" s="22" t="s">
+      <c r="Z120" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA120" s="19">
+        <v>1</v>
+      </c>
+      <c r="AB120" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="AC120" s="23">
-        <v>10000</v>
-      </c>
-      <c r="AD120" s="23">
-        <v>10000</v>
-      </c>
-      <c r="AE120" s="23">
-        <v>0</v>
-      </c>
-      <c r="AF120" s="22">
+      <c r="AC120" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AD120" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AE120" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF120" s="24">
         <v>40</v>
       </c>
-      <c r="AG120" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH120" s="22">
-        <v>0</v>
-      </c>
-      <c r="AI120" s="22">
-        <v>0</v>
-      </c>
-      <c r="AJ120" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A121" s="23">
+      <c r="AG120" s="24">
+        <v>0</v>
+      </c>
+      <c r="AH120" s="24">
+        <v>0</v>
+      </c>
+      <c r="AI120" s="24">
+        <v>0</v>
+      </c>
+      <c r="AJ120" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" ht="14.25" spans="1:36">
+      <c r="A121" s="19">
         <v>90000501</v>
       </c>
-      <c r="B121" s="23">
+      <c r="B121" s="19">
         <v>3</v>
       </c>
-      <c r="C121" s="23" t="s">
-        <v>202</v>
-      </c>
-      <c r="D121" s="23"/>
-      <c r="E121" s="21"/>
-      <c r="F121" s="23"/>
-      <c r="G121" s="25">
-        <v>1</v>
-      </c>
-      <c r="H121" s="25">
+      <c r="C121" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="D121" s="19"/>
+      <c r="E121" s="20"/>
+      <c r="F121" s="19"/>
+      <c r="G121" s="19">
+        <v>1</v>
+      </c>
+      <c r="H121" s="19">
         <v>2</v>
       </c>
-      <c r="I121" s="25" t="s">
+      <c r="I121" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="J121" s="23">
-        <v>0</v>
-      </c>
-      <c r="K121" s="23" t="s">
+      <c r="J121" s="19">
+        <v>0</v>
+      </c>
+      <c r="K121" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="L121" s="23">
+      <c r="L121" s="19">
         <v>800001011</v>
       </c>
-      <c r="M121" s="23">
-        <v>1</v>
-      </c>
-      <c r="N121" s="26">
-        <v>1</v>
-      </c>
-      <c r="O121" s="23">
-        <v>1</v>
-      </c>
-      <c r="P121" s="23">
+      <c r="M121" s="19">
+        <v>1</v>
+      </c>
+      <c r="N121" s="21">
+        <v>1</v>
+      </c>
+      <c r="O121" s="19">
+        <v>1</v>
+      </c>
+      <c r="P121" s="19">
         <v>8</v>
       </c>
-      <c r="Q121" s="23">
-        <v>0</v>
-      </c>
-      <c r="R121" s="23">
+      <c r="Q121" s="19">
+        <v>0</v>
+      </c>
+      <c r="R121" s="19">
         <v>25</v>
       </c>
-      <c r="S121" s="23">
+      <c r="S121" s="19">
         <v>-5000</v>
       </c>
-      <c r="T121" s="23">
-        <v>1</v>
-      </c>
-      <c r="U121" s="23">
-        <v>0</v>
-      </c>
-      <c r="V121" s="23" t="s">
+      <c r="T121" s="19">
+        <v>1</v>
+      </c>
+      <c r="U121" s="19">
+        <v>0</v>
+      </c>
+      <c r="V121" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="W121" s="23" t="s">
+      <c r="W121" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="X121" s="23" t="s">
+      <c r="X121" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="Y121" s="24">
+      <c r="Y121" s="23">
         <v>20010001</v>
       </c>
-      <c r="Z121" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA121" s="23">
-        <v>1</v>
-      </c>
-      <c r="AB121" s="22" t="s">
+      <c r="Z121" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA121" s="19">
+        <v>1</v>
+      </c>
+      <c r="AB121" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="AC121" s="23">
-        <v>10000</v>
-      </c>
-      <c r="AD121" s="23">
-        <v>10000</v>
-      </c>
-      <c r="AE121" s="23">
-        <v>0</v>
-      </c>
-      <c r="AF121" s="22">
+      <c r="AC121" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AD121" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AE121" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF121" s="24">
         <v>40</v>
       </c>
-      <c r="AG121" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH121" s="22">
-        <v>0</v>
-      </c>
-      <c r="AI121" s="22">
-        <v>0</v>
-      </c>
-      <c r="AJ121" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A122" s="23">
+      <c r="AG121" s="24">
+        <v>0</v>
+      </c>
+      <c r="AH121" s="24">
+        <v>0</v>
+      </c>
+      <c r="AI121" s="24">
+        <v>0</v>
+      </c>
+      <c r="AJ121" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" ht="14.25" spans="1:36">
+      <c r="A122" s="19">
         <v>90000502</v>
       </c>
-      <c r="B122" s="23">
+      <c r="B122" s="19">
         <v>3</v>
       </c>
-      <c r="C122" s="23" t="s">
-        <v>203</v>
-      </c>
-      <c r="D122" s="23"/>
-      <c r="E122" s="21"/>
-      <c r="F122" s="23"/>
-      <c r="G122" s="25">
-        <v>1</v>
-      </c>
-      <c r="H122" s="25">
+      <c r="C122" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="D122" s="19"/>
+      <c r="E122" s="20"/>
+      <c r="F122" s="19"/>
+      <c r="G122" s="19">
+        <v>1</v>
+      </c>
+      <c r="H122" s="19">
         <v>2</v>
       </c>
-      <c r="I122" s="25" t="s">
+      <c r="I122" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="J122" s="23">
-        <v>0</v>
-      </c>
-      <c r="K122" s="23" t="s">
+      <c r="J122" s="19">
+        <v>0</v>
+      </c>
+      <c r="K122" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="L122" s="23">
+      <c r="L122" s="19">
         <v>800001011</v>
       </c>
-      <c r="M122" s="23">
-        <v>1</v>
-      </c>
-      <c r="N122" s="26">
+      <c r="M122" s="19">
+        <v>1</v>
+      </c>
+      <c r="N122" s="21">
         <v>2</v>
       </c>
-      <c r="O122" s="23">
-        <v>1</v>
-      </c>
-      <c r="P122" s="23">
+      <c r="O122" s="19">
+        <v>1</v>
+      </c>
+      <c r="P122" s="19">
         <v>8</v>
       </c>
-      <c r="Q122" s="23">
-        <v>0</v>
-      </c>
-      <c r="R122" s="23">
+      <c r="Q122" s="19">
+        <v>0</v>
+      </c>
+      <c r="R122" s="19">
         <v>25</v>
       </c>
-      <c r="S122" s="23">
+      <c r="S122" s="19">
         <v>-5000</v>
       </c>
-      <c r="T122" s="23">
-        <v>1</v>
-      </c>
-      <c r="U122" s="23">
-        <v>0</v>
-      </c>
-      <c r="V122" s="23" t="s">
+      <c r="T122" s="19">
+        <v>1</v>
+      </c>
+      <c r="U122" s="19">
+        <v>0</v>
+      </c>
+      <c r="V122" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="W122" s="23" t="s">
+      <c r="W122" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="X122" s="23" t="s">
+      <c r="X122" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="Y122" s="24">
+      <c r="Y122" s="23">
         <v>20010001</v>
       </c>
-      <c r="Z122" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA122" s="23">
-        <v>1</v>
-      </c>
-      <c r="AB122" s="22" t="s">
+      <c r="Z122" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA122" s="19">
+        <v>1</v>
+      </c>
+      <c r="AB122" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="AC122" s="23">
-        <v>10000</v>
-      </c>
-      <c r="AD122" s="23">
-        <v>10000</v>
-      </c>
-      <c r="AE122" s="23">
-        <v>0</v>
-      </c>
-      <c r="AF122" s="22">
+      <c r="AC122" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AD122" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AE122" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF122" s="24">
         <v>40</v>
       </c>
-      <c r="AG122" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH122" s="22">
-        <v>0</v>
-      </c>
-      <c r="AI122" s="22">
-        <v>0</v>
-      </c>
-      <c r="AJ122" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A123" s="23">
+      <c r="AG122" s="24">
+        <v>0</v>
+      </c>
+      <c r="AH122" s="24">
+        <v>0</v>
+      </c>
+      <c r="AI122" s="24">
+        <v>0</v>
+      </c>
+      <c r="AJ122" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" ht="14.25" spans="1:36">
+      <c r="A123" s="19">
         <v>90000503</v>
       </c>
-      <c r="B123" s="23">
+      <c r="B123" s="19">
         <v>3</v>
       </c>
-      <c r="C123" s="23" t="s">
-        <v>204</v>
-      </c>
-      <c r="D123" s="23"/>
-      <c r="E123" s="21"/>
-      <c r="F123" s="23"/>
-      <c r="G123" s="25">
-        <v>1</v>
-      </c>
-      <c r="H123" s="25">
+      <c r="C123" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="D123" s="19"/>
+      <c r="E123" s="20"/>
+      <c r="F123" s="19"/>
+      <c r="G123" s="19">
+        <v>1</v>
+      </c>
+      <c r="H123" s="19">
         <v>2</v>
       </c>
-      <c r="I123" s="25" t="s">
+      <c r="I123" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="J123" s="23">
-        <v>0</v>
-      </c>
-      <c r="K123" s="23" t="s">
+      <c r="J123" s="19">
+        <v>0</v>
+      </c>
+      <c r="K123" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="L123" s="23">
+      <c r="L123" s="19">
         <v>800001021</v>
       </c>
-      <c r="M123" s="23">
-        <v>1</v>
-      </c>
-      <c r="N123" s="26">
+      <c r="M123" s="19">
+        <v>1</v>
+      </c>
+      <c r="N123" s="21">
         <v>3</v>
       </c>
-      <c r="O123" s="23">
-        <v>1</v>
-      </c>
-      <c r="P123" s="23">
+      <c r="O123" s="19">
+        <v>1</v>
+      </c>
+      <c r="P123" s="19">
         <v>8</v>
       </c>
-      <c r="Q123" s="23">
-        <v>0</v>
-      </c>
-      <c r="R123" s="23">
+      <c r="Q123" s="19">
+        <v>0</v>
+      </c>
+      <c r="R123" s="19">
         <v>25</v>
       </c>
-      <c r="S123" s="23">
+      <c r="S123" s="19">
         <v>-5000</v>
       </c>
-      <c r="T123" s="23">
-        <v>1</v>
-      </c>
-      <c r="U123" s="23">
-        <v>0</v>
-      </c>
-      <c r="V123" s="23" t="s">
+      <c r="T123" s="19">
+        <v>1</v>
+      </c>
+      <c r="U123" s="19">
+        <v>0</v>
+      </c>
+      <c r="V123" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="W123" s="23" t="s">
+      <c r="W123" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="X123" s="23" t="s">
+      <c r="X123" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="Y123" s="24">
+      <c r="Y123" s="23">
         <v>20010001</v>
       </c>
-      <c r="Z123" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA123" s="23">
-        <v>1</v>
-      </c>
-      <c r="AB123" s="22" t="s">
+      <c r="Z123" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA123" s="19">
+        <v>1</v>
+      </c>
+      <c r="AB123" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="AC123" s="23">
-        <v>10000</v>
-      </c>
-      <c r="AD123" s="23">
-        <v>10000</v>
-      </c>
-      <c r="AE123" s="23">
-        <v>0</v>
-      </c>
-      <c r="AF123" s="22">
+      <c r="AC123" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AD123" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AE123" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF123" s="24">
         <v>40</v>
       </c>
-      <c r="AG123" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH123" s="22">
-        <v>0</v>
-      </c>
-      <c r="AI123" s="22">
-        <v>0</v>
-      </c>
-      <c r="AJ123" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A124" s="23">
+      <c r="AG123" s="24">
+        <v>0</v>
+      </c>
+      <c r="AH123" s="24">
+        <v>0</v>
+      </c>
+      <c r="AI123" s="24">
+        <v>0</v>
+      </c>
+      <c r="AJ123" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" ht="14.25" spans="1:36">
+      <c r="A124" s="19">
         <v>90000504</v>
       </c>
-      <c r="B124" s="23">
+      <c r="B124" s="19">
         <v>3</v>
       </c>
-      <c r="C124" s="23" t="s">
-        <v>205</v>
-      </c>
-      <c r="D124" s="23"/>
-      <c r="E124" s="21"/>
-      <c r="F124" s="23"/>
-      <c r="G124" s="25">
-        <v>1</v>
-      </c>
-      <c r="H124" s="25">
+      <c r="C124" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="D124" s="19"/>
+      <c r="E124" s="20"/>
+      <c r="F124" s="19"/>
+      <c r="G124" s="19">
+        <v>1</v>
+      </c>
+      <c r="H124" s="19">
         <v>2</v>
       </c>
-      <c r="I124" s="25" t="s">
+      <c r="I124" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="J124" s="23">
-        <v>0</v>
-      </c>
-      <c r="K124" s="23" t="s">
+      <c r="J124" s="19">
+        <v>0</v>
+      </c>
+      <c r="K124" s="19" t="s">
         <v>155</v>
       </c>
-      <c r="L124" s="23">
+      <c r="L124" s="19">
         <v>800011011</v>
       </c>
-      <c r="M124" s="23">
-        <v>1</v>
-      </c>
-      <c r="N124" s="26">
+      <c r="M124" s="19">
+        <v>1</v>
+      </c>
+      <c r="N124" s="21">
         <v>6</v>
       </c>
-      <c r="O124" s="23">
-        <v>1</v>
-      </c>
-      <c r="P124" s="23">
+      <c r="O124" s="19">
+        <v>1</v>
+      </c>
+      <c r="P124" s="19">
         <v>8</v>
       </c>
-      <c r="Q124" s="23">
-        <v>0</v>
-      </c>
-      <c r="R124" s="23">
+      <c r="Q124" s="19">
+        <v>0</v>
+      </c>
+      <c r="R124" s="19">
         <v>25</v>
       </c>
-      <c r="S124" s="23">
+      <c r="S124" s="19">
         <v>-5000</v>
       </c>
-      <c r="T124" s="23">
-        <v>1</v>
-      </c>
-      <c r="U124" s="23">
-        <v>0</v>
-      </c>
-      <c r="V124" s="23" t="s">
+      <c r="T124" s="19">
+        <v>1</v>
+      </c>
+      <c r="U124" s="19">
+        <v>0</v>
+      </c>
+      <c r="V124" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="W124" s="23" t="s">
+      <c r="W124" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="X124" s="23" t="s">
+      <c r="X124" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="Y124" s="24">
+      <c r="Y124" s="23">
         <v>20010001</v>
       </c>
-      <c r="Z124" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA124" s="23">
-        <v>1</v>
-      </c>
-      <c r="AB124" s="22" t="s">
+      <c r="Z124" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA124" s="19">
+        <v>1</v>
+      </c>
+      <c r="AB124" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="AC124" s="23">
-        <v>10000</v>
-      </c>
-      <c r="AD124" s="23">
-        <v>10000</v>
-      </c>
-      <c r="AE124" s="23">
-        <v>0</v>
-      </c>
-      <c r="AF124" s="22">
+      <c r="AC124" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AD124" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AE124" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF124" s="24">
         <v>40</v>
       </c>
-      <c r="AG124" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH124" s="22">
-        <v>0</v>
-      </c>
-      <c r="AI124" s="22">
-        <v>0</v>
-      </c>
-      <c r="AJ124" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A125" s="23">
+      <c r="AG124" s="24">
+        <v>0</v>
+      </c>
+      <c r="AH124" s="24">
+        <v>0</v>
+      </c>
+      <c r="AI124" s="24">
+        <v>0</v>
+      </c>
+      <c r="AJ124" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" ht="14.25" spans="1:36">
+      <c r="A125" s="19">
         <v>90000601</v>
       </c>
-      <c r="B125" s="23">
+      <c r="B125" s="19">
         <v>3</v>
       </c>
-      <c r="C125" s="23" t="s">
-        <v>206</v>
-      </c>
-      <c r="D125" s="23"/>
-      <c r="E125" s="21"/>
-      <c r="F125" s="23"/>
-      <c r="G125" s="25">
-        <v>1</v>
-      </c>
-      <c r="H125" s="25">
+      <c r="C125" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="D125" s="19"/>
+      <c r="E125" s="20"/>
+      <c r="F125" s="19"/>
+      <c r="G125" s="19">
+        <v>1</v>
+      </c>
+      <c r="H125" s="19">
         <v>2</v>
       </c>
-      <c r="I125" s="25" t="s">
+      <c r="I125" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="J125" s="23">
-        <v>0</v>
-      </c>
-      <c r="K125" s="23" t="s">
+      <c r="J125" s="19">
+        <v>0</v>
+      </c>
+      <c r="K125" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="L125" s="23">
+      <c r="L125" s="19">
         <v>800001011</v>
       </c>
-      <c r="M125" s="23">
-        <v>1</v>
-      </c>
-      <c r="N125" s="26">
-        <v>1</v>
-      </c>
-      <c r="O125" s="23">
-        <v>1</v>
-      </c>
-      <c r="P125" s="23">
+      <c r="M125" s="19">
+        <v>1</v>
+      </c>
+      <c r="N125" s="21">
+        <v>1</v>
+      </c>
+      <c r="O125" s="19">
+        <v>1</v>
+      </c>
+      <c r="P125" s="19">
         <v>8</v>
       </c>
-      <c r="Q125" s="23">
-        <v>0</v>
-      </c>
-      <c r="R125" s="23">
+      <c r="Q125" s="19">
+        <v>0</v>
+      </c>
+      <c r="R125" s="19">
         <v>25</v>
       </c>
-      <c r="S125" s="23">
+      <c r="S125" s="19">
         <v>-5000</v>
       </c>
-      <c r="T125" s="23">
-        <v>1</v>
-      </c>
-      <c r="U125" s="23">
-        <v>0</v>
-      </c>
-      <c r="V125" s="23" t="s">
+      <c r="T125" s="19">
+        <v>1</v>
+      </c>
+      <c r="U125" s="19">
+        <v>0</v>
+      </c>
+      <c r="V125" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="W125" s="23" t="s">
+      <c r="W125" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="X125" s="23" t="s">
+      <c r="X125" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="Y125" s="24">
+      <c r="Y125" s="23">
         <v>20010001</v>
       </c>
-      <c r="Z125" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA125" s="23">
-        <v>1</v>
-      </c>
-      <c r="AB125" s="22" t="s">
+      <c r="Z125" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA125" s="19">
+        <v>1</v>
+      </c>
+      <c r="AB125" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="AC125" s="23">
-        <v>10000</v>
-      </c>
-      <c r="AD125" s="23">
-        <v>10000</v>
-      </c>
-      <c r="AE125" s="23">
-        <v>0</v>
-      </c>
-      <c r="AF125" s="22">
+      <c r="AC125" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AD125" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AE125" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF125" s="24">
         <v>40</v>
       </c>
-      <c r="AG125" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH125" s="22">
-        <v>0</v>
-      </c>
-      <c r="AI125" s="22">
-        <v>0</v>
-      </c>
-      <c r="AJ125" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A126" s="23">
+      <c r="AG125" s="24">
+        <v>0</v>
+      </c>
+      <c r="AH125" s="24">
+        <v>0</v>
+      </c>
+      <c r="AI125" s="24">
+        <v>0</v>
+      </c>
+      <c r="AJ125" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" ht="14.25" spans="1:36">
+      <c r="A126" s="19">
         <v>90000602</v>
       </c>
-      <c r="B126" s="23">
+      <c r="B126" s="19">
         <v>3</v>
       </c>
-      <c r="C126" s="23" t="s">
-        <v>207</v>
-      </c>
-      <c r="D126" s="23"/>
-      <c r="E126" s="21"/>
-      <c r="F126" s="23"/>
-      <c r="G126" s="25">
-        <v>1</v>
-      </c>
-      <c r="H126" s="25">
+      <c r="C126" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="D126" s="19"/>
+      <c r="E126" s="20"/>
+      <c r="F126" s="19"/>
+      <c r="G126" s="19">
+        <v>1</v>
+      </c>
+      <c r="H126" s="19">
         <v>2</v>
       </c>
-      <c r="I126" s="25" t="s">
+      <c r="I126" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="J126" s="23">
-        <v>0</v>
-      </c>
-      <c r="K126" s="23" t="s">
+      <c r="J126" s="19">
+        <v>0</v>
+      </c>
+      <c r="K126" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="L126" s="23">
+      <c r="L126" s="19">
         <v>800001011</v>
       </c>
-      <c r="M126" s="23">
-        <v>1</v>
-      </c>
-      <c r="N126" s="26">
+      <c r="M126" s="19">
+        <v>1</v>
+      </c>
+      <c r="N126" s="21">
         <v>2</v>
       </c>
-      <c r="O126" s="23">
-        <v>1</v>
-      </c>
-      <c r="P126" s="23">
+      <c r="O126" s="19">
+        <v>1</v>
+      </c>
+      <c r="P126" s="19">
         <v>8</v>
       </c>
-      <c r="Q126" s="23">
-        <v>0</v>
-      </c>
-      <c r="R126" s="23">
+      <c r="Q126" s="19">
+        <v>0</v>
+      </c>
+      <c r="R126" s="19">
         <v>25</v>
       </c>
-      <c r="S126" s="23">
+      <c r="S126" s="19">
         <v>-5000</v>
       </c>
-      <c r="T126" s="23">
-        <v>1</v>
-      </c>
-      <c r="U126" s="23">
-        <v>0</v>
-      </c>
-      <c r="V126" s="23" t="s">
+      <c r="T126" s="19">
+        <v>1</v>
+      </c>
+      <c r="U126" s="19">
+        <v>0</v>
+      </c>
+      <c r="V126" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="W126" s="23" t="s">
+      <c r="W126" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="X126" s="23" t="s">
+      <c r="X126" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="Y126" s="24">
+      <c r="Y126" s="23">
         <v>20010001</v>
       </c>
-      <c r="Z126" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA126" s="23">
-        <v>1</v>
-      </c>
-      <c r="AB126" s="22" t="s">
+      <c r="Z126" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA126" s="19">
+        <v>1</v>
+      </c>
+      <c r="AB126" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="AC126" s="23">
-        <v>10000</v>
-      </c>
-      <c r="AD126" s="23">
-        <v>10000</v>
-      </c>
-      <c r="AE126" s="23">
-        <v>0</v>
-      </c>
-      <c r="AF126" s="22">
+      <c r="AC126" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AD126" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AE126" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF126" s="24">
         <v>40</v>
       </c>
-      <c r="AG126" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH126" s="22">
-        <v>0</v>
-      </c>
-      <c r="AI126" s="22">
-        <v>0</v>
-      </c>
-      <c r="AJ126" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A127" s="23">
+      <c r="AG126" s="24">
+        <v>0</v>
+      </c>
+      <c r="AH126" s="24">
+        <v>0</v>
+      </c>
+      <c r="AI126" s="24">
+        <v>0</v>
+      </c>
+      <c r="AJ126" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" ht="14.25" spans="1:36">
+      <c r="A127" s="19">
         <v>90000603</v>
       </c>
-      <c r="B127" s="23">
+      <c r="B127" s="19">
         <v>3</v>
       </c>
-      <c r="C127" s="23" t="s">
-        <v>208</v>
-      </c>
-      <c r="D127" s="23"/>
-      <c r="E127" s="21"/>
-      <c r="F127" s="23"/>
-      <c r="G127" s="25">
-        <v>1</v>
-      </c>
-      <c r="H127" s="25">
+      <c r="C127" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="D127" s="19"/>
+      <c r="E127" s="20"/>
+      <c r="F127" s="19"/>
+      <c r="G127" s="19">
+        <v>1</v>
+      </c>
+      <c r="H127" s="19">
         <v>2</v>
       </c>
-      <c r="I127" s="25" t="s">
+      <c r="I127" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="J127" s="23">
-        <v>0</v>
-      </c>
-      <c r="K127" s="23" t="s">
+      <c r="J127" s="19">
+        <v>0</v>
+      </c>
+      <c r="K127" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="L127" s="23">
+      <c r="L127" s="19">
         <v>800001021</v>
       </c>
-      <c r="M127" s="23">
-        <v>1</v>
-      </c>
-      <c r="N127" s="26">
+      <c r="M127" s="19">
+        <v>1</v>
+      </c>
+      <c r="N127" s="21">
         <v>3</v>
       </c>
-      <c r="O127" s="23">
-        <v>1</v>
-      </c>
-      <c r="P127" s="23">
+      <c r="O127" s="19">
+        <v>1</v>
+      </c>
+      <c r="P127" s="19">
         <v>8</v>
       </c>
-      <c r="Q127" s="23">
-        <v>0</v>
-      </c>
-      <c r="R127" s="23">
+      <c r="Q127" s="19">
+        <v>0</v>
+      </c>
+      <c r="R127" s="19">
         <v>25</v>
       </c>
-      <c r="S127" s="23">
+      <c r="S127" s="19">
         <v>-5000</v>
       </c>
-      <c r="T127" s="23">
-        <v>1</v>
-      </c>
-      <c r="U127" s="23">
-        <v>0</v>
-      </c>
-      <c r="V127" s="23" t="s">
+      <c r="T127" s="19">
+        <v>1</v>
+      </c>
+      <c r="U127" s="19">
+        <v>0</v>
+      </c>
+      <c r="V127" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="W127" s="23" t="s">
+      <c r="W127" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="X127" s="23" t="s">
+      <c r="X127" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="Y127" s="24">
+      <c r="Y127" s="23">
         <v>20010001</v>
       </c>
-      <c r="Z127" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA127" s="23">
-        <v>1</v>
-      </c>
-      <c r="AB127" s="22" t="s">
+      <c r="Z127" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA127" s="19">
+        <v>1</v>
+      </c>
+      <c r="AB127" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="AC127" s="23">
-        <v>10000</v>
-      </c>
-      <c r="AD127" s="23">
-        <v>10000</v>
-      </c>
-      <c r="AE127" s="23">
-        <v>0</v>
-      </c>
-      <c r="AF127" s="22">
+      <c r="AC127" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AD127" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AE127" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF127" s="24">
         <v>40</v>
       </c>
-      <c r="AG127" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH127" s="22">
-        <v>0</v>
-      </c>
-      <c r="AI127" s="22">
-        <v>0</v>
-      </c>
-      <c r="AJ127" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A128" s="23">
+      <c r="AG127" s="24">
+        <v>0</v>
+      </c>
+      <c r="AH127" s="24">
+        <v>0</v>
+      </c>
+      <c r="AI127" s="24">
+        <v>0</v>
+      </c>
+      <c r="AJ127" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" ht="14.25" spans="1:36">
+      <c r="A128" s="19">
         <v>90000604</v>
       </c>
-      <c r="B128" s="23">
+      <c r="B128" s="19">
         <v>3</v>
       </c>
-      <c r="C128" s="23" t="s">
-        <v>209</v>
-      </c>
-      <c r="D128" s="23"/>
-      <c r="E128" s="21"/>
-      <c r="F128" s="23"/>
-      <c r="G128" s="25">
-        <v>1</v>
-      </c>
-      <c r="H128" s="25">
+      <c r="C128" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="D128" s="19"/>
+      <c r="E128" s="20"/>
+      <c r="F128" s="19"/>
+      <c r="G128" s="19">
+        <v>1</v>
+      </c>
+      <c r="H128" s="19">
         <v>2</v>
       </c>
-      <c r="I128" s="25" t="s">
+      <c r="I128" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="J128" s="23">
-        <v>0</v>
-      </c>
-      <c r="K128" s="23" t="s">
+      <c r="J128" s="19">
+        <v>0</v>
+      </c>
+      <c r="K128" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="L128" s="23">
+      <c r="L128" s="19">
         <v>800001021</v>
       </c>
-      <c r="M128" s="23">
-        <v>1</v>
-      </c>
-      <c r="N128" s="26">
+      <c r="M128" s="19">
+        <v>1</v>
+      </c>
+      <c r="N128" s="21">
         <v>5</v>
       </c>
-      <c r="O128" s="23">
-        <v>1</v>
-      </c>
-      <c r="P128" s="23">
+      <c r="O128" s="19">
+        <v>1</v>
+      </c>
+      <c r="P128" s="19">
         <v>8</v>
       </c>
-      <c r="Q128" s="23">
-        <v>0</v>
-      </c>
-      <c r="R128" s="23">
+      <c r="Q128" s="19">
+        <v>0</v>
+      </c>
+      <c r="R128" s="19">
         <v>25</v>
       </c>
-      <c r="S128" s="23">
+      <c r="S128" s="19">
         <v>-5000</v>
       </c>
-      <c r="T128" s="23">
-        <v>1</v>
-      </c>
-      <c r="U128" s="23">
-        <v>0</v>
-      </c>
-      <c r="V128" s="23" t="s">
+      <c r="T128" s="19">
+        <v>1</v>
+      </c>
+      <c r="U128" s="19">
+        <v>0</v>
+      </c>
+      <c r="V128" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="W128" s="23" t="s">
+      <c r="W128" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="X128" s="23" t="s">
+      <c r="X128" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="Y128" s="24">
+      <c r="Y128" s="23">
         <v>20010001</v>
       </c>
-      <c r="Z128" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA128" s="23">
-        <v>1</v>
-      </c>
-      <c r="AB128" s="22" t="s">
+      <c r="Z128" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA128" s="19">
+        <v>1</v>
+      </c>
+      <c r="AB128" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="AC128" s="23">
-        <v>10000</v>
-      </c>
-      <c r="AD128" s="23">
-        <v>10000</v>
-      </c>
-      <c r="AE128" s="23">
-        <v>0</v>
-      </c>
-      <c r="AF128" s="22">
+      <c r="AC128" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AD128" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AE128" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF128" s="24">
         <v>40</v>
       </c>
-      <c r="AG128" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH128" s="22">
-        <v>0</v>
-      </c>
-      <c r="AI128" s="22">
-        <v>0</v>
-      </c>
-      <c r="AJ128" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A129" s="23">
+      <c r="AG128" s="24">
+        <v>0</v>
+      </c>
+      <c r="AH128" s="24">
+        <v>0</v>
+      </c>
+      <c r="AI128" s="24">
+        <v>0</v>
+      </c>
+      <c r="AJ128" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" ht="14.25" spans="1:36">
+      <c r="A129" s="19">
         <v>90000605</v>
       </c>
-      <c r="B129" s="23">
+      <c r="B129" s="19">
         <v>3</v>
       </c>
-      <c r="C129" s="23" t="s">
-        <v>210</v>
-      </c>
-      <c r="D129" s="23"/>
-      <c r="E129" s="21"/>
-      <c r="F129" s="23"/>
-      <c r="G129" s="25">
-        <v>1</v>
-      </c>
-      <c r="H129" s="25">
+      <c r="C129" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="D129" s="19"/>
+      <c r="E129" s="20"/>
+      <c r="F129" s="19"/>
+      <c r="G129" s="19">
+        <v>1</v>
+      </c>
+      <c r="H129" s="19">
         <v>2</v>
       </c>
-      <c r="I129" s="25" t="s">
+      <c r="I129" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="J129" s="23">
-        <v>0</v>
-      </c>
-      <c r="K129" s="23" t="s">
+      <c r="J129" s="19">
+        <v>0</v>
+      </c>
+      <c r="K129" s="19" t="s">
         <v>155</v>
       </c>
-      <c r="L129" s="23">
+      <c r="L129" s="19">
         <v>800011011</v>
       </c>
-      <c r="M129" s="23">
-        <v>1</v>
-      </c>
-      <c r="N129" s="26">
+      <c r="M129" s="19">
+        <v>1</v>
+      </c>
+      <c r="N129" s="21">
         <v>10</v>
       </c>
-      <c r="O129" s="23">
-        <v>1</v>
-      </c>
-      <c r="P129" s="23">
+      <c r="O129" s="19">
+        <v>1</v>
+      </c>
+      <c r="P129" s="19">
         <v>8</v>
       </c>
-      <c r="Q129" s="23">
-        <v>0</v>
-      </c>
-      <c r="R129" s="23">
+      <c r="Q129" s="19">
+        <v>0</v>
+      </c>
+      <c r="R129" s="19">
         <v>25</v>
       </c>
-      <c r="S129" s="23">
+      <c r="S129" s="19">
         <v>-5000</v>
       </c>
-      <c r="T129" s="23">
-        <v>1</v>
-      </c>
-      <c r="U129" s="23">
-        <v>0</v>
-      </c>
-      <c r="V129" s="23" t="s">
+      <c r="T129" s="19">
+        <v>1</v>
+      </c>
+      <c r="U129" s="19">
+        <v>0</v>
+      </c>
+      <c r="V129" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="W129" s="23" t="s">
+      <c r="W129" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="X129" s="23" t="s">
+      <c r="X129" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="Y129" s="24">
+      <c r="Y129" s="23">
         <v>20010001</v>
       </c>
-      <c r="Z129" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA129" s="23">
-        <v>1</v>
-      </c>
-      <c r="AB129" s="22" t="s">
+      <c r="Z129" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA129" s="19">
+        <v>1</v>
+      </c>
+      <c r="AB129" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="AC129" s="23">
-        <v>10000</v>
-      </c>
-      <c r="AD129" s="23">
-        <v>10000</v>
-      </c>
-      <c r="AE129" s="23">
-        <v>0</v>
-      </c>
-      <c r="AF129" s="22">
+      <c r="AC129" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AD129" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AE129" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF129" s="24">
         <v>40</v>
       </c>
-      <c r="AG129" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH129" s="22">
-        <v>0</v>
-      </c>
-      <c r="AI129" s="22">
-        <v>0</v>
-      </c>
-      <c r="AJ129" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A130" s="23">
+      <c r="AG129" s="24">
+        <v>0</v>
+      </c>
+      <c r="AH129" s="24">
+        <v>0</v>
+      </c>
+      <c r="AI129" s="24">
+        <v>0</v>
+      </c>
+      <c r="AJ129" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" ht="14.25" spans="1:36">
+      <c r="A130" s="19">
         <v>90000606</v>
       </c>
-      <c r="B130" s="23">
+      <c r="B130" s="19">
         <v>3</v>
       </c>
-      <c r="C130" s="23" t="s">
-        <v>211</v>
-      </c>
-      <c r="D130" s="23"/>
-      <c r="E130" s="21"/>
-      <c r="F130" s="23"/>
-      <c r="G130" s="25">
-        <v>1</v>
-      </c>
-      <c r="H130" s="25">
+      <c r="C130" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="D130" s="19"/>
+      <c r="E130" s="20"/>
+      <c r="F130" s="19"/>
+      <c r="G130" s="19">
+        <v>1</v>
+      </c>
+      <c r="H130" s="19">
         <v>2</v>
       </c>
-      <c r="I130" s="25" t="s">
+      <c r="I130" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="J130" s="23">
-        <v>0</v>
-      </c>
-      <c r="K130" s="23" t="s">
+      <c r="J130" s="19">
+        <v>0</v>
+      </c>
+      <c r="K130" s="19" t="s">
         <v>155</v>
       </c>
-      <c r="L130" s="23">
+      <c r="L130" s="19">
         <v>800011011</v>
       </c>
-      <c r="M130" s="23">
-        <v>1</v>
-      </c>
-      <c r="N130" s="26">
+      <c r="M130" s="19">
+        <v>1</v>
+      </c>
+      <c r="N130" s="21">
         <v>14</v>
       </c>
-      <c r="O130" s="23">
-        <v>1</v>
-      </c>
-      <c r="P130" s="23">
+      <c r="O130" s="19">
+        <v>1</v>
+      </c>
+      <c r="P130" s="19">
         <v>8</v>
       </c>
-      <c r="Q130" s="23">
-        <v>0</v>
-      </c>
-      <c r="R130" s="23">
+      <c r="Q130" s="19">
+        <v>0</v>
+      </c>
+      <c r="R130" s="19">
         <v>25</v>
       </c>
-      <c r="S130" s="23">
+      <c r="S130" s="19">
         <v>-5000</v>
       </c>
-      <c r="T130" s="23">
-        <v>1</v>
-      </c>
-      <c r="U130" s="23">
-        <v>0</v>
-      </c>
-      <c r="V130" s="23" t="s">
+      <c r="T130" s="19">
+        <v>1</v>
+      </c>
+      <c r="U130" s="19">
+        <v>0</v>
+      </c>
+      <c r="V130" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="W130" s="23" t="s">
+      <c r="W130" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="X130" s="23" t="s">
+      <c r="X130" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="Y130" s="24">
+      <c r="Y130" s="23">
         <v>20010001</v>
       </c>
-      <c r="Z130" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA130" s="23">
-        <v>1</v>
-      </c>
-      <c r="AB130" s="22" t="s">
+      <c r="Z130" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA130" s="19">
+        <v>1</v>
+      </c>
+      <c r="AB130" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="AC130" s="23">
-        <v>10000</v>
-      </c>
-      <c r="AD130" s="23">
-        <v>10000</v>
-      </c>
-      <c r="AE130" s="23">
-        <v>0</v>
-      </c>
-      <c r="AF130" s="22">
+      <c r="AC130" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AD130" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AE130" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF130" s="24">
         <v>40</v>
       </c>
-      <c r="AG130" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH130" s="22">
-        <v>0</v>
-      </c>
-      <c r="AI130" s="22">
-        <v>0</v>
-      </c>
-      <c r="AJ130" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A131" s="23">
+      <c r="AG130" s="24">
+        <v>0</v>
+      </c>
+      <c r="AH130" s="24">
+        <v>0</v>
+      </c>
+      <c r="AI130" s="24">
+        <v>0</v>
+      </c>
+      <c r="AJ130" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" ht="14.25" spans="1:36">
+      <c r="A131" s="19">
         <v>90000607</v>
       </c>
-      <c r="B131" s="23">
+      <c r="B131" s="19">
         <v>3</v>
       </c>
-      <c r="C131" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="D131" s="23"/>
-      <c r="E131" s="21"/>
-      <c r="F131" s="23"/>
-      <c r="G131" s="25">
-        <v>1</v>
-      </c>
-      <c r="H131" s="25">
+      <c r="C131" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="D131" s="19"/>
+      <c r="E131" s="20"/>
+      <c r="F131" s="19"/>
+      <c r="G131" s="19">
+        <v>1</v>
+      </c>
+      <c r="H131" s="19">
         <v>2</v>
       </c>
-      <c r="I131" s="25" t="s">
+      <c r="I131" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="J131" s="23">
-        <v>0</v>
-      </c>
-      <c r="K131" s="23" t="s">
+      <c r="J131" s="19">
+        <v>0</v>
+      </c>
+      <c r="K131" s="19" t="s">
         <v>156</v>
       </c>
-      <c r="L131" s="23">
+      <c r="L131" s="19">
         <v>800011021</v>
       </c>
-      <c r="M131" s="23">
-        <v>1</v>
-      </c>
-      <c r="N131" s="26">
+      <c r="M131" s="19">
+        <v>1</v>
+      </c>
+      <c r="N131" s="21">
         <v>18</v>
       </c>
-      <c r="O131" s="23">
-        <v>1</v>
-      </c>
-      <c r="P131" s="23">
+      <c r="O131" s="19">
+        <v>1</v>
+      </c>
+      <c r="P131" s="19">
         <v>8</v>
       </c>
-      <c r="Q131" s="23">
-        <v>0</v>
-      </c>
-      <c r="R131" s="23">
+      <c r="Q131" s="19">
+        <v>0</v>
+      </c>
+      <c r="R131" s="19">
         <v>25</v>
       </c>
-      <c r="S131" s="23">
+      <c r="S131" s="19">
         <v>-5000</v>
       </c>
-      <c r="T131" s="23">
-        <v>1</v>
-      </c>
-      <c r="U131" s="23">
-        <v>0</v>
-      </c>
-      <c r="V131" s="23" t="s">
+      <c r="T131" s="19">
+        <v>1</v>
+      </c>
+      <c r="U131" s="19">
+        <v>0</v>
+      </c>
+      <c r="V131" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="W131" s="23" t="s">
+      <c r="W131" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="X131" s="23" t="s">
+      <c r="X131" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="Y131" s="24">
+      <c r="Y131" s="23">
         <v>20010001</v>
       </c>
-      <c r="Z131" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA131" s="23">
-        <v>1</v>
-      </c>
-      <c r="AB131" s="22" t="s">
+      <c r="Z131" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA131" s="19">
+        <v>1</v>
+      </c>
+      <c r="AB131" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="AC131" s="23">
-        <v>10000</v>
-      </c>
-      <c r="AD131" s="23">
-        <v>10000</v>
-      </c>
-      <c r="AE131" s="23">
-        <v>0</v>
-      </c>
-      <c r="AF131" s="22">
+      <c r="AC131" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AD131" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AE131" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF131" s="24">
         <v>40</v>
       </c>
-      <c r="AG131" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH131" s="22">
-        <v>0</v>
-      </c>
-      <c r="AI131" s="22">
-        <v>0</v>
-      </c>
-      <c r="AJ131" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A132" s="23">
+      <c r="AG131" s="24">
+        <v>0</v>
+      </c>
+      <c r="AH131" s="24">
+        <v>0</v>
+      </c>
+      <c r="AI131" s="24">
+        <v>0</v>
+      </c>
+      <c r="AJ131" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" ht="14.25" spans="1:36">
+      <c r="A132" s="19">
         <v>90000608</v>
       </c>
-      <c r="B132" s="23">
+      <c r="B132" s="19">
         <v>3</v>
       </c>
-      <c r="C132" s="23" t="s">
-        <v>213</v>
-      </c>
-      <c r="D132" s="23"/>
-      <c r="E132" s="21"/>
-      <c r="F132" s="23"/>
-      <c r="G132" s="25">
-        <v>1</v>
-      </c>
-      <c r="H132" s="25">
+      <c r="C132" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="D132" s="19"/>
+      <c r="E132" s="20"/>
+      <c r="F132" s="19"/>
+      <c r="G132" s="19">
+        <v>1</v>
+      </c>
+      <c r="H132" s="19">
         <v>2</v>
       </c>
-      <c r="I132" s="25" t="s">
+      <c r="I132" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="J132" s="23">
-        <v>0</v>
-      </c>
-      <c r="K132" s="23" t="s">
+      <c r="J132" s="19">
+        <v>0</v>
+      </c>
+      <c r="K132" s="19" t="s">
         <v>156</v>
       </c>
-      <c r="L132" s="23">
+      <c r="L132" s="19">
         <v>800011021</v>
       </c>
-      <c r="M132" s="23">
-        <v>1</v>
-      </c>
-      <c r="N132" s="26">
+      <c r="M132" s="19">
+        <v>1</v>
+      </c>
+      <c r="N132" s="21">
         <v>45</v>
       </c>
-      <c r="O132" s="23">
-        <v>1</v>
-      </c>
-      <c r="P132" s="23">
+      <c r="O132" s="19">
+        <v>1</v>
+      </c>
+      <c r="P132" s="19">
         <v>8</v>
       </c>
-      <c r="Q132" s="23">
-        <v>0</v>
-      </c>
-      <c r="R132" s="23">
+      <c r="Q132" s="19">
+        <v>0</v>
+      </c>
+      <c r="R132" s="19">
         <v>25</v>
       </c>
-      <c r="S132" s="23">
+      <c r="S132" s="19">
         <v>-5000</v>
       </c>
-      <c r="T132" s="23">
-        <v>1</v>
-      </c>
-      <c r="U132" s="23">
-        <v>0</v>
-      </c>
-      <c r="V132" s="23" t="s">
+      <c r="T132" s="19">
+        <v>1</v>
+      </c>
+      <c r="U132" s="19">
+        <v>0</v>
+      </c>
+      <c r="V132" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="W132" s="23" t="s">
+      <c r="W132" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="X132" s="23" t="s">
+      <c r="X132" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="Y132" s="24">
+      <c r="Y132" s="23">
         <v>20010001</v>
       </c>
-      <c r="Z132" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA132" s="23">
-        <v>1</v>
-      </c>
-      <c r="AB132" s="22" t="s">
+      <c r="Z132" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA132" s="19">
+        <v>1</v>
+      </c>
+      <c r="AB132" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="AC132" s="23">
-        <v>10000</v>
-      </c>
-      <c r="AD132" s="23">
-        <v>10000</v>
-      </c>
-      <c r="AE132" s="23">
-        <v>0</v>
-      </c>
-      <c r="AF132" s="22">
+      <c r="AC132" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AD132" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AE132" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF132" s="24">
         <v>40</v>
       </c>
-      <c r="AG132" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH132" s="22">
-        <v>0</v>
-      </c>
-      <c r="AI132" s="22">
-        <v>0</v>
-      </c>
-      <c r="AJ132" s="22">
+      <c r="AG132" s="24">
+        <v>0</v>
+      </c>
+      <c r="AH132" s="24">
+        <v>0</v>
+      </c>
+      <c r="AI132" s="24">
+        <v>0</v>
+      </c>
+      <c r="AJ132" s="24">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:AD61">
+  <sortState ref="A5:AD61">
     <sortCondition ref="A5:A61"/>
   </sortState>
-  <phoneticPr fontId="15" type="noConversion"/>
   <conditionalFormatting sqref="A1:A65 A71:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="33"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="I1:S28"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="9:19" x14ac:dyDescent="0.15">
+    <row r="1" spans="9:19">
       <c r="I1" s="6">
         <v>1</v>
       </c>
@@ -14970,7 +15518,7 @@
         <v>65000</v>
       </c>
     </row>
-    <row r="2" spans="9:19" x14ac:dyDescent="0.15">
+    <row r="2" spans="9:19">
       <c r="I2" s="6">
         <v>2</v>
       </c>
@@ -15001,7 +15549,7 @@
         <v>85000</v>
       </c>
     </row>
-    <row r="3" spans="9:19" x14ac:dyDescent="0.15">
+    <row r="3" spans="9:19">
       <c r="I3" s="6">
         <v>2</v>
       </c>
@@ -15032,7 +15580,7 @@
         <v>110000</v>
       </c>
     </row>
-    <row r="4" spans="9:19" x14ac:dyDescent="0.15">
+    <row r="4" spans="9:19">
       <c r="I4" s="6">
         <v>3</v>
       </c>
@@ -15063,7 +15611,7 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="5" spans="9:19" x14ac:dyDescent="0.15">
+    <row r="5" spans="9:19">
       <c r="I5" s="6">
         <v>3</v>
       </c>
@@ -15094,7 +15642,7 @@
         <v>180000</v>
       </c>
     </row>
-    <row r="6" spans="9:19" x14ac:dyDescent="0.15">
+    <row r="6" spans="9:19">
       <c r="I6" s="6">
         <v>4</v>
       </c>
@@ -15125,7 +15673,7 @@
         <v>350000</v>
       </c>
     </row>
-    <row r="7" spans="9:19" x14ac:dyDescent="0.15">
+    <row r="7" spans="9:19">
       <c r="I7" s="6">
         <v>4</v>
       </c>
@@ -15156,7 +15704,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="8" spans="9:19" x14ac:dyDescent="0.15">
+    <row r="8" spans="9:19">
       <c r="I8" s="6">
         <v>5</v>
       </c>
@@ -15187,7 +15735,7 @@
         <v>800000</v>
       </c>
     </row>
-    <row r="9" spans="9:19" x14ac:dyDescent="0.15">
+    <row r="9" spans="9:19">
       <c r="I9" s="6">
         <v>5</v>
       </c>
@@ -15218,7 +15766,7 @@
         <v>1400000</v>
       </c>
     </row>
-    <row r="10" spans="9:19" x14ac:dyDescent="0.15">
+    <row r="10" spans="9:19">
       <c r="I10" s="6">
         <v>6</v>
       </c>
@@ -15249,7 +15797,7 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="11" spans="9:19" x14ac:dyDescent="0.15">
+    <row r="11" spans="9:14">
       <c r="I11" s="6">
         <v>6</v>
       </c>
@@ -15271,7 +15819,7 @@
         <v>350000</v>
       </c>
     </row>
-    <row r="12" spans="9:19" x14ac:dyDescent="0.15">
+    <row r="12" spans="9:14">
       <c r="I12" s="6">
         <v>6</v>
       </c>
@@ -15293,7 +15841,7 @@
         <v>350000</v>
       </c>
     </row>
-    <row r="13" spans="9:19" x14ac:dyDescent="0.15">
+    <row r="13" spans="9:14">
       <c r="I13" s="6">
         <v>7</v>
       </c>
@@ -15315,7 +15863,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="14" spans="9:19" x14ac:dyDescent="0.15">
+    <row r="14" spans="9:14">
       <c r="I14" s="6">
         <v>7</v>
       </c>
@@ -15337,7 +15885,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="15" spans="9:19" x14ac:dyDescent="0.15">
+    <row r="15" spans="9:14">
       <c r="I15" s="6">
         <v>7</v>
       </c>
@@ -15359,7 +15907,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="16" spans="9:19" x14ac:dyDescent="0.15">
+    <row r="16" spans="9:14">
       <c r="I16" s="6">
         <v>7</v>
       </c>
@@ -15381,7 +15929,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="17" spans="9:14" x14ac:dyDescent="0.15">
+    <row r="17" spans="9:14">
       <c r="I17" s="6">
         <v>8</v>
       </c>
@@ -15403,7 +15951,7 @@
         <v>800000</v>
       </c>
     </row>
-    <row r="18" spans="9:14" x14ac:dyDescent="0.15">
+    <row r="18" spans="9:14">
       <c r="I18" s="6">
         <v>8</v>
       </c>
@@ -15425,7 +15973,7 @@
         <v>800000</v>
       </c>
     </row>
-    <row r="19" spans="9:14" x14ac:dyDescent="0.15">
+    <row r="19" spans="9:14">
       <c r="I19" s="6">
         <v>8</v>
       </c>
@@ -15447,7 +15995,7 @@
         <v>800000</v>
       </c>
     </row>
-    <row r="20" spans="9:14" x14ac:dyDescent="0.15">
+    <row r="20" spans="9:14">
       <c r="I20" s="6">
         <v>8</v>
       </c>
@@ -15469,7 +16017,7 @@
         <v>800000</v>
       </c>
     </row>
-    <row r="21" spans="9:14" x14ac:dyDescent="0.15">
+    <row r="21" spans="9:14">
       <c r="I21" s="6">
         <v>9</v>
       </c>
@@ -15491,7 +16039,7 @@
         <v>1400000</v>
       </c>
     </row>
-    <row r="22" spans="9:14" x14ac:dyDescent="0.15">
+    <row r="22" spans="9:14">
       <c r="I22" s="6">
         <v>9</v>
       </c>
@@ -15513,7 +16061,7 @@
         <v>1400000</v>
       </c>
     </row>
-    <row r="23" spans="9:14" x14ac:dyDescent="0.15">
+    <row r="23" spans="9:14">
       <c r="I23" s="6">
         <v>9</v>
       </c>
@@ -15535,7 +16083,7 @@
         <v>1400000</v>
       </c>
     </row>
-    <row r="24" spans="9:14" x14ac:dyDescent="0.15">
+    <row r="24" spans="9:14">
       <c r="I24" s="6">
         <v>9</v>
       </c>
@@ -15557,7 +16105,7 @@
         <v>1400000</v>
       </c>
     </row>
-    <row r="25" spans="9:14" x14ac:dyDescent="0.15">
+    <row r="25" spans="9:14">
       <c r="I25" s="6">
         <v>10</v>
       </c>
@@ -15579,7 +16127,7 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="26" spans="9:14" x14ac:dyDescent="0.15">
+    <row r="26" spans="9:14">
       <c r="I26" s="6">
         <v>10</v>
       </c>
@@ -15601,7 +16149,7 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="27" spans="9:14" x14ac:dyDescent="0.15">
+    <row r="27" spans="9:14">
       <c r="I27" s="6">
         <v>10</v>
       </c>
@@ -15623,7 +16171,7 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="28" spans="9:14" x14ac:dyDescent="0.15">
+    <row r="28" spans="9:14">
       <c r="I28" s="6">
         <v>10</v>
       </c>
@@ -15646,16 +16194,16 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A6:O22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="8.625" style="1" customWidth="1"/>
@@ -15674,30 +16222,30 @@
     <col min="16" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="6" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="6" ht="14.25" spans="2:14">
       <c r="B6" t="s">
         <v>55</v>
       </c>
       <c r="C6" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
       <c r="F6"/>
       <c r="G6" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="J6" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="K6"/>
       <c r="L6"/>
       <c r="M6"/>
       <c r="N6" s="1" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25" spans="1:15">
       <c r="A7" s="2" t="s">
         <v>128</v>
       </c>
@@ -15709,7 +16257,7 @@
         <v>20030001</v>
       </c>
       <c r="D7" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="E7" t="str">
         <f t="shared" ref="E7:E14" si="0">LEFT(D7,3)</f>
@@ -15720,16 +16268,16 @@
         <v>3</v>
       </c>
       <c r="G7" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="J7">
         <v>990101</v>
       </c>
       <c r="K7" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="L7" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="M7">
         <v>1</v>
@@ -15738,10 +16286,10 @@
         <v>20010001</v>
       </c>
       <c r="O7" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25" spans="1:15">
       <c r="A8" s="2" t="s">
         <v>128</v>
       </c>
@@ -15753,7 +16301,7 @@
         <v>20030001</v>
       </c>
       <c r="D8" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="E8" t="str">
         <f t="shared" si="0"/>
@@ -15764,16 +16312,16 @@
         <v>3</v>
       </c>
       <c r="G8" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="J8">
         <v>990102</v>
       </c>
       <c r="K8" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="L8" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="M8">
         <v>1</v>
@@ -15782,10 +16330,10 @@
         <v>20010002</v>
       </c>
       <c r="O8" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="9" ht="14.25" spans="1:15">
       <c r="A9" s="2" t="s">
         <v>128</v>
       </c>
@@ -15797,7 +16345,7 @@
         <v>20030001</v>
       </c>
       <c r="D9" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="E9" t="str">
         <f t="shared" si="0"/>
@@ -15808,16 +16356,16 @@
         <v>3</v>
       </c>
       <c r="G9" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="J9">
         <v>990201</v>
       </c>
       <c r="K9" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="L9" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="M9">
         <v>2</v>
@@ -15826,10 +16374,10 @@
         <v>20020001</v>
       </c>
       <c r="O9" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25" spans="1:15">
       <c r="A10" s="2" t="s">
         <v>128</v>
       </c>
@@ -15841,7 +16389,7 @@
         <v>20030001</v>
       </c>
       <c r="D10" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="E10" t="str">
         <f t="shared" si="0"/>
@@ -15852,16 +16400,16 @@
         <v>3</v>
       </c>
       <c r="G10" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="J10">
         <v>990202</v>
       </c>
       <c r="K10" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="L10" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="M10">
         <v>2</v>
@@ -15870,10 +16418,10 @@
         <v>20020002</v>
       </c>
       <c r="O10" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25" spans="1:15">
       <c r="A11" s="3" t="s">
         <v>125</v>
       </c>
@@ -15885,7 +16433,7 @@
         <v>20040001</v>
       </c>
       <c r="D11" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="E11" t="str">
         <f t="shared" si="0"/>
@@ -15896,16 +16444,16 @@
         <v>4</v>
       </c>
       <c r="G11" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="J11">
         <v>990301</v>
       </c>
       <c r="K11" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="L11" t="s">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="M11">
         <v>3</v>
@@ -15914,10 +16462,10 @@
         <v>20030001</v>
       </c>
       <c r="O11" s="5" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25" spans="1:15">
       <c r="A12" s="3" t="s">
         <v>125</v>
       </c>
@@ -15929,7 +16477,7 @@
         <v>20040001</v>
       </c>
       <c r="D12" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="E12" t="str">
         <f t="shared" si="0"/>
@@ -15940,16 +16488,16 @@
         <v>4</v>
       </c>
       <c r="G12" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="J12">
         <v>990302</v>
       </c>
       <c r="K12" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="L12" t="s">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="M12">
         <v>3</v>
@@ -15958,10 +16506,10 @@
         <v>20030002</v>
       </c>
       <c r="O12" s="5" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25" spans="1:15">
       <c r="A13" s="3" t="s">
         <v>125</v>
       </c>
@@ -15973,7 +16521,7 @@
         <v>20040001</v>
       </c>
       <c r="D13" t="s">
-        <v>177</v>
+        <v>194</v>
       </c>
       <c r="E13" t="str">
         <f t="shared" si="0"/>
@@ -15984,16 +16532,16 @@
         <v>4</v>
       </c>
       <c r="G13" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="J13">
         <v>990401</v>
       </c>
       <c r="K13" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="L13" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="M13">
         <v>4</v>
@@ -16002,10 +16550,10 @@
         <v>20040001</v>
       </c>
       <c r="O13" s="5" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25" spans="1:15">
       <c r="A14" s="3" t="s">
         <v>125</v>
       </c>
@@ -16017,7 +16565,7 @@
         <v>20040001</v>
       </c>
       <c r="D14" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="E14" t="str">
         <f t="shared" si="0"/>
@@ -16028,16 +16576,16 @@
         <v>4</v>
       </c>
       <c r="G14" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="J14">
         <v>990402</v>
       </c>
       <c r="K14" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="L14" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="M14">
         <v>4</v>
@@ -16046,10 +16594,10 @@
         <v>20040002</v>
       </c>
       <c r="O14" s="5" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25" spans="1:15">
       <c r="A15" s="2" t="s">
         <v>140</v>
       </c>
@@ -16061,26 +16609,26 @@
         <v>20050001</v>
       </c>
       <c r="D15" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="E15" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="F15">
         <f>VLOOKUP(E15,备注资源组与动作id!$L$7:$M$16,2,FALSE)</f>
         <v>5</v>
       </c>
       <c r="G15" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="J15">
         <v>990501</v>
       </c>
       <c r="K15" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="L15" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="M15">
         <v>5</v>
@@ -16089,10 +16637,10 @@
         <v>20050001</v>
       </c>
       <c r="O15" s="5" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="16" ht="14.25" spans="1:15">
       <c r="A16" s="2" t="s">
         <v>140</v>
       </c>
@@ -16104,26 +16652,26 @@
         <v>20050001</v>
       </c>
       <c r="D16" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="E16" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="F16">
         <f>VLOOKUP(E16,备注资源组与动作id!$L$7:$M$16,2,FALSE)</f>
         <v>5</v>
       </c>
       <c r="G16" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="J16">
         <v>990502</v>
       </c>
       <c r="K16" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="L16" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="M16">
         <v>5</v>
@@ -16132,10 +16680,10 @@
         <v>20050002</v>
       </c>
       <c r="O16" s="5" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25" spans="1:7">
       <c r="A17" s="2" t="s">
         <v>140</v>
       </c>
@@ -16147,20 +16695,20 @@
         <v>20050001</v>
       </c>
       <c r="D17" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="E17" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="F17">
         <f>VLOOKUP(E17,备注资源组与动作id!$L$7:$M$16,2,FALSE)</f>
         <v>5</v>
       </c>
       <c r="G17" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="18" ht="14.25" spans="1:7">
       <c r="A18" s="2" t="s">
         <v>140</v>
       </c>
@@ -16172,22 +16720,22 @@
         <v>20050001</v>
       </c>
       <c r="D18" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="E18" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="F18">
         <f>VLOOKUP(E18,备注资源组与动作id!$L$7:$M$16,2,FALSE)</f>
         <v>5</v>
       </c>
       <c r="G18" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25" spans="1:7">
       <c r="A19" s="2" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="B19">
         <v>1000101</v>
@@ -16197,7 +16745,7 @@
         <v>20010001</v>
       </c>
       <c r="D19" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="E19" t="str">
         <f>LEFT(D19,3)</f>
@@ -16208,12 +16756,12 @@
         <v>1</v>
       </c>
       <c r="G19" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="20" ht="14.25" spans="1:7">
       <c r="A20" s="2" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="B20">
         <v>1000102</v>
@@ -16223,7 +16771,7 @@
         <v>20010001</v>
       </c>
       <c r="D20" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="E20" t="str">
         <f>LEFT(D20,3)</f>
@@ -16234,10 +16782,10 @@
         <v>1</v>
       </c>
       <c r="G20" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25" spans="1:7">
       <c r="A21" s="2" t="s">
         <v>132</v>
       </c>
@@ -16249,7 +16797,7 @@
         <v>20020001</v>
       </c>
       <c r="D21" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="E21" t="str">
         <f>LEFT(D21,3)</f>
@@ -16260,10 +16808,10 @@
         <v>2</v>
       </c>
       <c r="G21" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="22" ht="14.25" spans="1:7">
       <c r="A22" s="2" t="s">
         <v>132</v>
       </c>
@@ -16275,7 +16823,7 @@
         <v>20020001</v>
       </c>
       <c r="D22" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="E22" t="str">
         <f>LEFT(D22,3)</f>
@@ -16286,51 +16834,51 @@
         <v>2</v>
       </c>
       <c r="G22" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="B2:K162"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="3:11">
       <c r="C2" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="D2" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="E2" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="F2" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="G2" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="H2" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="I2" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="J2" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="K2" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11">
       <c r="B3">
         <v>1</v>
       </c>
@@ -16370,7 +16918,7 @@
         <v>1:10_2:10_3:10_4:10_5:10_6:10_7:10_8:10_9:10_10:10_11:10_12:10_13:10_14:10_15:10_16:10_17:10_18:10_19:10_20:10_21:10_22:10_23:10_24:10_25:10_26:10_27:10_28:10_29:10_30:10_31:10_32:10_33:10_34:10_35:10_36:10_37:10_38:10_39:10_40:10_41:10_42:10_43:10_44:10_45:10_46:10_47:10_48:10_49:10_50:10_51:10_52:10_53:10_54:10_55:10_56:10_57:10_58:10_59:10_60:10_61:10_62:10_63:10_64:10_65:10_66:10_67:10_68:10_69:10_70:10_71:10_72:10_73:10_74:10_75:10_76:10_77:10_78:10_79:10_80:10_81:10_82:10_83:10_84:10_85:10_86:10_87:10_88:10_89:10_90:10_91:10_92:10_93:10_94:10_95:10_96:10_97:10_98:10_99:10_100:10_101:10_102:10_103:10_104:10_105:10_106:10_107:10_108:10_109:10_110:10_111:10_112:10_113:10_114:10_115:10_116:10_117:10_118:10_119:10_120:10_121:10_122:10_123:10_124:10_125:10_126:10_127:10_128:10_129:10_130:10_131:10_132:10_133:10_134:10_135:10_136:10_137:10_138:10_139:10_140:10_141:10_142:10_143:10_144:10_145:10_146:10_147:10_148:10_149:10_150:10_151:10_152:10_153:10_154:10_155:10_156:10_157:10_158:10_159:10_160:10</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:8">
       <c r="B4">
         <f t="shared" ref="B4:B35" si="0">B3+1</f>
         <v>2</v>
@@ -16399,7 +16947,7 @@
         <v>2:10</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8">
       <c r="B5">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -16428,7 +16976,7 @@
         <v>3:10</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:8">
       <c r="B6">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -16457,7 +17005,7 @@
         <v>4:10</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:8">
       <c r="B7">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -16486,7 +17034,7 @@
         <v>5:10</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:8">
       <c r="B8">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -16515,7 +17063,7 @@
         <v>6:10</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:8">
       <c r="B9">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -16544,7 +17092,7 @@
         <v>7:10</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:8">
       <c r="B10">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -16573,7 +17121,7 @@
         <v>8:10</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:8">
       <c r="B11">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -16602,7 +17150,7 @@
         <v>9:10</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:8">
       <c r="B12">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -16631,7 +17179,7 @@
         <v>10:10</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:8">
       <c r="B13">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -16660,7 +17208,7 @@
         <v>11:10</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:8">
       <c r="B14">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -16689,7 +17237,7 @@
         <v>12:10</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:8">
       <c r="B15">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -16718,7 +17266,7 @@
         <v>13:10</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:8">
       <c r="B16">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -16747,7 +17295,7 @@
         <v>14:10</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:8">
       <c r="B17">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -16776,7 +17324,7 @@
         <v>15:10</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:8">
       <c r="B18">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -16805,7 +17353,7 @@
         <v>16:10</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:8">
       <c r="B19">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -16834,7 +17382,7 @@
         <v>17:10</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:8">
       <c r="B20">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -16863,7 +17411,7 @@
         <v>18:10</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:8">
       <c r="B21">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -16892,7 +17440,7 @@
         <v>19:10</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:8">
       <c r="B22">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -16921,7 +17469,7 @@
         <v>20:10</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:8">
       <c r="B23">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -16950,7 +17498,7 @@
         <v>21:10</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:8">
       <c r="B24">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -16979,7 +17527,7 @@
         <v>22:10</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:8">
       <c r="B25">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -17008,7 +17556,7 @@
         <v>23:10</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:8">
       <c r="B26">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -17037,7 +17585,7 @@
         <v>24:10</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:8">
       <c r="B27">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -17066,7 +17614,7 @@
         <v>25:10</v>
       </c>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:8">
       <c r="B28">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -17095,7 +17643,7 @@
         <v>26:10</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:8">
       <c r="B29">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -17124,7 +17672,7 @@
         <v>27:10</v>
       </c>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:8">
       <c r="B30">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -17153,7 +17701,7 @@
         <v>28:10</v>
       </c>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:8">
       <c r="B31">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -17182,7 +17730,7 @@
         <v>29:10</v>
       </c>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:8">
       <c r="B32">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -17211,7 +17759,7 @@
         <v>30:10</v>
       </c>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:8">
       <c r="B33">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -17240,7 +17788,7 @@
         <v>31:10</v>
       </c>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:8">
       <c r="B34">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -17269,7 +17817,7 @@
         <v>32:10</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:8">
       <c r="B35">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -17298,7 +17846,7 @@
         <v>33:10</v>
       </c>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:8">
       <c r="B36">
         <f t="shared" ref="B36:B67" si="6">B35+1</f>
         <v>34</v>
@@ -17327,7 +17875,7 @@
         <v>34:10</v>
       </c>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:8">
       <c r="B37">
         <f t="shared" si="6"/>
         <v>35</v>
@@ -17356,7 +17904,7 @@
         <v>35:10</v>
       </c>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:8">
       <c r="B38">
         <f t="shared" si="6"/>
         <v>36</v>
@@ -17385,7 +17933,7 @@
         <v>36:10</v>
       </c>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:8">
       <c r="B39">
         <f t="shared" si="6"/>
         <v>37</v>
@@ -17414,7 +17962,7 @@
         <v>37:10</v>
       </c>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:8">
       <c r="B40">
         <f t="shared" si="6"/>
         <v>38</v>
@@ -17443,7 +17991,7 @@
         <v>38:10</v>
       </c>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:8">
       <c r="B41">
         <f t="shared" si="6"/>
         <v>39</v>
@@ -17472,7 +18020,7 @@
         <v>39:10</v>
       </c>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:8">
       <c r="B42">
         <f t="shared" si="6"/>
         <v>40</v>
@@ -17501,7 +18049,7 @@
         <v>40:10</v>
       </c>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:8">
       <c r="B43">
         <f t="shared" si="6"/>
         <v>41</v>
@@ -17530,7 +18078,7 @@
         <v>41:10</v>
       </c>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:8">
       <c r="B44">
         <f t="shared" si="6"/>
         <v>42</v>
@@ -17559,7 +18107,7 @@
         <v>42:10</v>
       </c>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:8">
       <c r="B45">
         <f t="shared" si="6"/>
         <v>43</v>
@@ -17588,7 +18136,7 @@
         <v>43:10</v>
       </c>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:8">
       <c r="B46">
         <f t="shared" si="6"/>
         <v>44</v>
@@ -17617,7 +18165,7 @@
         <v>44:10</v>
       </c>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:8">
       <c r="B47">
         <f t="shared" si="6"/>
         <v>45</v>
@@ -17646,7 +18194,7 @@
         <v>45:10</v>
       </c>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:8">
       <c r="B48">
         <f t="shared" si="6"/>
         <v>46</v>
@@ -17675,7 +18223,7 @@
         <v>46:10</v>
       </c>
     </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:8">
       <c r="B49">
         <f t="shared" si="6"/>
         <v>47</v>
@@ -17704,7 +18252,7 @@
         <v>47:10</v>
       </c>
     </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:8">
       <c r="B50">
         <f t="shared" si="6"/>
         <v>48</v>
@@ -17733,7 +18281,7 @@
         <v>48:10</v>
       </c>
     </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:8">
       <c r="B51">
         <f t="shared" si="6"/>
         <v>49</v>
@@ -17762,7 +18310,7 @@
         <v>49:10</v>
       </c>
     </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:8">
       <c r="B52">
         <f t="shared" si="6"/>
         <v>50</v>
@@ -17791,7 +18339,7 @@
         <v>50:10</v>
       </c>
     </row>
-    <row r="53" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:8">
       <c r="B53">
         <f t="shared" si="6"/>
         <v>51</v>
@@ -17820,7 +18368,7 @@
         <v>51:10</v>
       </c>
     </row>
-    <row r="54" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:8">
       <c r="B54">
         <f t="shared" si="6"/>
         <v>52</v>
@@ -17849,7 +18397,7 @@
         <v>52:10</v>
       </c>
     </row>
-    <row r="55" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:8">
       <c r="B55">
         <f t="shared" si="6"/>
         <v>53</v>
@@ -17878,7 +18426,7 @@
         <v>53:10</v>
       </c>
     </row>
-    <row r="56" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:8">
       <c r="B56">
         <f t="shared" si="6"/>
         <v>54</v>
@@ -17907,7 +18455,7 @@
         <v>54:10</v>
       </c>
     </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:8">
       <c r="B57">
         <f t="shared" si="6"/>
         <v>55</v>
@@ -17936,7 +18484,7 @@
         <v>55:10</v>
       </c>
     </row>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:8">
       <c r="B58">
         <f t="shared" si="6"/>
         <v>56</v>
@@ -17965,7 +18513,7 @@
         <v>56:10</v>
       </c>
     </row>
-    <row r="59" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:8">
       <c r="B59">
         <f t="shared" si="6"/>
         <v>57</v>
@@ -17994,7 +18542,7 @@
         <v>57:10</v>
       </c>
     </row>
-    <row r="60" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:8">
       <c r="B60">
         <f t="shared" si="6"/>
         <v>58</v>
@@ -18023,7 +18571,7 @@
         <v>58:10</v>
       </c>
     </row>
-    <row r="61" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:8">
       <c r="B61">
         <f t="shared" si="6"/>
         <v>59</v>
@@ -18052,7 +18600,7 @@
         <v>59:10</v>
       </c>
     </row>
-    <row r="62" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:8">
       <c r="B62">
         <f t="shared" si="6"/>
         <v>60</v>
@@ -18081,7 +18629,7 @@
         <v>60:10</v>
       </c>
     </row>
-    <row r="63" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:8">
       <c r="B63">
         <f t="shared" si="6"/>
         <v>61</v>
@@ -18110,7 +18658,7 @@
         <v>61:10</v>
       </c>
     </row>
-    <row r="64" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:8">
       <c r="B64">
         <f t="shared" si="6"/>
         <v>62</v>
@@ -18139,7 +18687,7 @@
         <v>62:10</v>
       </c>
     </row>
-    <row r="65" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:8">
       <c r="B65">
         <f t="shared" si="6"/>
         <v>63</v>
@@ -18168,7 +18716,7 @@
         <v>63:10</v>
       </c>
     </row>
-    <row r="66" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:8">
       <c r="B66">
         <f t="shared" si="6"/>
         <v>64</v>
@@ -18197,7 +18745,7 @@
         <v>64:10</v>
       </c>
     </row>
-    <row r="67" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:8">
       <c r="B67">
         <f t="shared" si="6"/>
         <v>65</v>
@@ -18226,7 +18774,7 @@
         <v>65:10</v>
       </c>
     </row>
-    <row r="68" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:8">
       <c r="B68">
         <f t="shared" ref="B68:B94" si="7">B67+1</f>
         <v>66</v>
@@ -18255,7 +18803,7 @@
         <v>66:10</v>
       </c>
     </row>
-    <row r="69" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:8">
       <c r="B69">
         <f t="shared" si="7"/>
         <v>67</v>
@@ -18284,7 +18832,7 @@
         <v>67:10</v>
       </c>
     </row>
-    <row r="70" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:8">
       <c r="B70">
         <f t="shared" si="7"/>
         <v>68</v>
@@ -18313,7 +18861,7 @@
         <v>68:10</v>
       </c>
     </row>
-    <row r="71" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:8">
       <c r="B71">
         <f t="shared" si="7"/>
         <v>69</v>
@@ -18342,7 +18890,7 @@
         <v>69:10</v>
       </c>
     </row>
-    <row r="72" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:8">
       <c r="B72">
         <f t="shared" si="7"/>
         <v>70</v>
@@ -18371,7 +18919,7 @@
         <v>70:10</v>
       </c>
     </row>
-    <row r="73" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:8">
       <c r="B73">
         <f t="shared" si="7"/>
         <v>71</v>
@@ -18400,7 +18948,7 @@
         <v>71:10</v>
       </c>
     </row>
-    <row r="74" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:8">
       <c r="B74">
         <f t="shared" si="7"/>
         <v>72</v>
@@ -18429,7 +18977,7 @@
         <v>72:10</v>
       </c>
     </row>
-    <row r="75" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:8">
       <c r="B75">
         <f t="shared" si="7"/>
         <v>73</v>
@@ -18458,7 +19006,7 @@
         <v>73:10</v>
       </c>
     </row>
-    <row r="76" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:8">
       <c r="B76">
         <f t="shared" si="7"/>
         <v>74</v>
@@ -18487,7 +19035,7 @@
         <v>74:10</v>
       </c>
     </row>
-    <row r="77" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:8">
       <c r="B77">
         <f t="shared" si="7"/>
         <v>75</v>
@@ -18516,7 +19064,7 @@
         <v>75:10</v>
       </c>
     </row>
-    <row r="78" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:8">
       <c r="B78">
         <f t="shared" si="7"/>
         <v>76</v>
@@ -18545,7 +19093,7 @@
         <v>76:10</v>
       </c>
     </row>
-    <row r="79" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:8">
       <c r="B79">
         <f t="shared" si="7"/>
         <v>77</v>
@@ -18574,7 +19122,7 @@
         <v>77:10</v>
       </c>
     </row>
-    <row r="80" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:8">
       <c r="B80">
         <f t="shared" si="7"/>
         <v>78</v>
@@ -18603,7 +19151,7 @@
         <v>78:10</v>
       </c>
     </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="81" spans="2:8">
       <c r="B81">
         <f t="shared" si="7"/>
         <v>79</v>
@@ -18632,7 +19180,7 @@
         <v>79:10</v>
       </c>
     </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:8">
       <c r="B82">
         <f t="shared" si="7"/>
         <v>80</v>
@@ -18661,7 +19209,7 @@
         <v>80:10</v>
       </c>
     </row>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:8">
       <c r="B83">
         <f t="shared" si="7"/>
         <v>81</v>
@@ -18690,7 +19238,7 @@
         <v>81:10</v>
       </c>
     </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="84" spans="2:8">
       <c r="B84">
         <f t="shared" si="7"/>
         <v>82</v>
@@ -18719,7 +19267,7 @@
         <v>82:10</v>
       </c>
     </row>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="85" spans="2:8">
       <c r="B85">
         <f t="shared" si="7"/>
         <v>83</v>
@@ -18748,7 +19296,7 @@
         <v>83:10</v>
       </c>
     </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="86" spans="2:8">
       <c r="B86">
         <f t="shared" si="7"/>
         <v>84</v>
@@ -18777,7 +19325,7 @@
         <v>84:10</v>
       </c>
     </row>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="87" spans="2:8">
       <c r="B87">
         <f t="shared" si="7"/>
         <v>85</v>
@@ -18806,7 +19354,7 @@
         <v>85:10</v>
       </c>
     </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="88" spans="2:8">
       <c r="B88">
         <f t="shared" si="7"/>
         <v>86</v>
@@ -18835,7 +19383,7 @@
         <v>86:10</v>
       </c>
     </row>
-    <row r="89" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="89" spans="2:8">
       <c r="B89">
         <f t="shared" si="7"/>
         <v>87</v>
@@ -18864,7 +19412,7 @@
         <v>87:10</v>
       </c>
     </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="90" spans="2:8">
       <c r="B90">
         <f t="shared" si="7"/>
         <v>88</v>
@@ -18893,7 +19441,7 @@
         <v>88:10</v>
       </c>
     </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="91" spans="2:8">
       <c r="B91">
         <f t="shared" si="7"/>
         <v>89</v>
@@ -18922,7 +19470,7 @@
         <v>89:10</v>
       </c>
     </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="92" spans="2:8">
       <c r="B92">
         <f t="shared" si="7"/>
         <v>90</v>
@@ -18951,7 +19499,7 @@
         <v>90:10</v>
       </c>
     </row>
-    <row r="93" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="93" spans="2:8">
       <c r="B93">
         <f t="shared" si="7"/>
         <v>91</v>
@@ -18980,7 +19528,7 @@
         <v>91:10</v>
       </c>
     </row>
-    <row r="94" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="94" spans="2:8">
       <c r="B94">
         <f t="shared" si="7"/>
         <v>92</v>
@@ -19009,7 +19557,7 @@
         <v>92:10</v>
       </c>
     </row>
-    <row r="95" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="95" spans="2:8">
       <c r="B95">
         <f t="shared" ref="B95:B158" si="13">B94+1</f>
         <v>93</v>
@@ -19038,7 +19586,7 @@
         <v>93:10</v>
       </c>
     </row>
-    <row r="96" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="96" spans="2:8">
       <c r="B96">
         <f t="shared" si="13"/>
         <v>94</v>
@@ -19067,7 +19615,7 @@
         <v>94:10</v>
       </c>
     </row>
-    <row r="97" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="97" spans="2:8">
       <c r="B97">
         <f t="shared" si="13"/>
         <v>95</v>
@@ -19096,7 +19644,7 @@
         <v>95:10</v>
       </c>
     </row>
-    <row r="98" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="98" spans="2:8">
       <c r="B98">
         <f t="shared" si="13"/>
         <v>96</v>
@@ -19125,7 +19673,7 @@
         <v>96:10</v>
       </c>
     </row>
-    <row r="99" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="99" spans="2:8">
       <c r="B99">
         <f t="shared" si="13"/>
         <v>97</v>
@@ -19154,7 +19702,7 @@
         <v>97:10</v>
       </c>
     </row>
-    <row r="100" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="100" spans="2:8">
       <c r="B100">
         <f t="shared" si="13"/>
         <v>98</v>
@@ -19183,7 +19731,7 @@
         <v>98:10</v>
       </c>
     </row>
-    <row r="101" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="101" spans="2:8">
       <c r="B101">
         <f t="shared" si="13"/>
         <v>99</v>
@@ -19212,7 +19760,7 @@
         <v>99:10</v>
       </c>
     </row>
-    <row r="102" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="102" spans="2:8">
       <c r="B102">
         <f t="shared" si="13"/>
         <v>100</v>
@@ -19241,7 +19789,7 @@
         <v>100:10</v>
       </c>
     </row>
-    <row r="103" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="103" spans="2:8">
       <c r="B103">
         <f t="shared" si="13"/>
         <v>101</v>
@@ -19270,7 +19818,7 @@
         <v>101:10</v>
       </c>
     </row>
-    <row r="104" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="104" spans="2:8">
       <c r="B104">
         <f t="shared" si="13"/>
         <v>102</v>
@@ -19299,7 +19847,7 @@
         <v>102:10</v>
       </c>
     </row>
-    <row r="105" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="105" spans="2:8">
       <c r="B105">
         <f t="shared" si="13"/>
         <v>103</v>
@@ -19328,7 +19876,7 @@
         <v>103:10</v>
       </c>
     </row>
-    <row r="106" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="106" spans="2:8">
       <c r="B106">
         <f t="shared" si="13"/>
         <v>104</v>
@@ -19357,7 +19905,7 @@
         <v>104:10</v>
       </c>
     </row>
-    <row r="107" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="107" spans="2:8">
       <c r="B107">
         <f t="shared" si="13"/>
         <v>105</v>
@@ -19386,7 +19934,7 @@
         <v>105:10</v>
       </c>
     </row>
-    <row r="108" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="108" spans="2:8">
       <c r="B108">
         <f t="shared" si="13"/>
         <v>106</v>
@@ -19415,7 +19963,7 @@
         <v>106:10</v>
       </c>
     </row>
-    <row r="109" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="109" spans="2:8">
       <c r="B109">
         <f t="shared" si="13"/>
         <v>107</v>
@@ -19444,7 +19992,7 @@
         <v>107:10</v>
       </c>
     </row>
-    <row r="110" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="110" spans="2:8">
       <c r="B110">
         <f t="shared" si="13"/>
         <v>108</v>
@@ -19473,7 +20021,7 @@
         <v>108:10</v>
       </c>
     </row>
-    <row r="111" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="111" spans="2:8">
       <c r="B111">
         <f t="shared" si="13"/>
         <v>109</v>
@@ -19502,7 +20050,7 @@
         <v>109:10</v>
       </c>
     </row>
-    <row r="112" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="112" spans="2:8">
       <c r="B112">
         <f t="shared" si="13"/>
         <v>110</v>
@@ -19531,7 +20079,7 @@
         <v>110:10</v>
       </c>
     </row>
-    <row r="113" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="113" spans="2:8">
       <c r="B113">
         <f t="shared" si="13"/>
         <v>111</v>
@@ -19560,7 +20108,7 @@
         <v>111:10</v>
       </c>
     </row>
-    <row r="114" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="114" spans="2:8">
       <c r="B114">
         <f t="shared" si="13"/>
         <v>112</v>
@@ -19589,7 +20137,7 @@
         <v>112:10</v>
       </c>
     </row>
-    <row r="115" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="115" spans="2:8">
       <c r="B115">
         <f t="shared" si="13"/>
         <v>113</v>
@@ -19618,7 +20166,7 @@
         <v>113:10</v>
       </c>
     </row>
-    <row r="116" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="116" spans="2:8">
       <c r="B116">
         <f t="shared" si="13"/>
         <v>114</v>
@@ -19647,7 +20195,7 @@
         <v>114:10</v>
       </c>
     </row>
-    <row r="117" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="117" spans="2:8">
       <c r="B117">
         <f t="shared" si="13"/>
         <v>115</v>
@@ -19676,7 +20224,7 @@
         <v>115:10</v>
       </c>
     </row>
-    <row r="118" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="118" spans="2:8">
       <c r="B118">
         <f t="shared" si="13"/>
         <v>116</v>
@@ -19705,7 +20253,7 @@
         <v>116:10</v>
       </c>
     </row>
-    <row r="119" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="119" spans="2:8">
       <c r="B119">
         <f t="shared" si="13"/>
         <v>117</v>
@@ -19734,7 +20282,7 @@
         <v>117:10</v>
       </c>
     </row>
-    <row r="120" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="120" spans="2:8">
       <c r="B120">
         <f t="shared" si="13"/>
         <v>118</v>
@@ -19763,7 +20311,7 @@
         <v>118:10</v>
       </c>
     </row>
-    <row r="121" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="121" spans="2:8">
       <c r="B121">
         <f t="shared" si="13"/>
         <v>119</v>
@@ -19792,7 +20340,7 @@
         <v>119:10</v>
       </c>
     </row>
-    <row r="122" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="122" spans="2:8">
       <c r="B122">
         <f t="shared" si="13"/>
         <v>120</v>
@@ -19821,7 +20369,7 @@
         <v>120:10</v>
       </c>
     </row>
-    <row r="123" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="123" spans="2:8">
       <c r="B123">
         <f t="shared" si="13"/>
         <v>121</v>
@@ -19850,7 +20398,7 @@
         <v>121:10</v>
       </c>
     </row>
-    <row r="124" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="124" spans="2:8">
       <c r="B124">
         <f t="shared" si="13"/>
         <v>122</v>
@@ -19879,7 +20427,7 @@
         <v>122:10</v>
       </c>
     </row>
-    <row r="125" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="125" spans="2:8">
       <c r="B125">
         <f t="shared" si="13"/>
         <v>123</v>
@@ -19908,7 +20456,7 @@
         <v>123:10</v>
       </c>
     </row>
-    <row r="126" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="126" spans="2:8">
       <c r="B126">
         <f t="shared" si="13"/>
         <v>124</v>
@@ -19937,7 +20485,7 @@
         <v>124:10</v>
       </c>
     </row>
-    <row r="127" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="127" spans="2:8">
       <c r="B127">
         <f t="shared" si="13"/>
         <v>125</v>
@@ -19966,7 +20514,7 @@
         <v>125:10</v>
       </c>
     </row>
-    <row r="128" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="128" spans="2:8">
       <c r="B128">
         <f t="shared" si="13"/>
         <v>126</v>
@@ -19995,7 +20543,7 @@
         <v>126:10</v>
       </c>
     </row>
-    <row r="129" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="129" spans="2:8">
       <c r="B129">
         <f t="shared" si="13"/>
         <v>127</v>
@@ -20024,7 +20572,7 @@
         <v>127:10</v>
       </c>
     </row>
-    <row r="130" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="130" spans="2:8">
       <c r="B130">
         <f t="shared" si="13"/>
         <v>128</v>
@@ -20053,7 +20601,7 @@
         <v>128:10</v>
       </c>
     </row>
-    <row r="131" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="131" spans="2:8">
       <c r="B131">
         <f t="shared" si="13"/>
         <v>129</v>
@@ -20082,7 +20630,7 @@
         <v>129:10</v>
       </c>
     </row>
-    <row r="132" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="132" spans="2:8">
       <c r="B132">
         <f t="shared" si="13"/>
         <v>130</v>
@@ -20111,7 +20659,7 @@
         <v>130:10</v>
       </c>
     </row>
-    <row r="133" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="133" spans="2:8">
       <c r="B133">
         <f t="shared" si="13"/>
         <v>131</v>
@@ -20140,7 +20688,7 @@
         <v>131:10</v>
       </c>
     </row>
-    <row r="134" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="134" spans="2:8">
       <c r="B134">
         <f t="shared" si="13"/>
         <v>132</v>
@@ -20169,7 +20717,7 @@
         <v>132:10</v>
       </c>
     </row>
-    <row r="135" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="135" spans="2:8">
       <c r="B135">
         <f t="shared" si="13"/>
         <v>133</v>
@@ -20198,7 +20746,7 @@
         <v>133:10</v>
       </c>
     </row>
-    <row r="136" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="136" spans="2:8">
       <c r="B136">
         <f t="shared" si="13"/>
         <v>134</v>
@@ -20227,7 +20775,7 @@
         <v>134:10</v>
       </c>
     </row>
-    <row r="137" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="137" spans="2:8">
       <c r="B137">
         <f t="shared" si="13"/>
         <v>135</v>
@@ -20256,7 +20804,7 @@
         <v>135:10</v>
       </c>
     </row>
-    <row r="138" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="138" spans="2:8">
       <c r="B138">
         <f t="shared" si="13"/>
         <v>136</v>
@@ -20285,7 +20833,7 @@
         <v>136:10</v>
       </c>
     </row>
-    <row r="139" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="139" spans="2:8">
       <c r="B139">
         <f t="shared" si="13"/>
         <v>137</v>
@@ -20314,7 +20862,7 @@
         <v>137:10</v>
       </c>
     </row>
-    <row r="140" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="140" spans="2:8">
       <c r="B140">
         <f t="shared" si="13"/>
         <v>138</v>
@@ -20343,7 +20891,7 @@
         <v>138:10</v>
       </c>
     </row>
-    <row r="141" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="141" spans="2:8">
       <c r="B141">
         <f t="shared" si="13"/>
         <v>139</v>
@@ -20372,7 +20920,7 @@
         <v>139:10</v>
       </c>
     </row>
-    <row r="142" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="142" spans="2:8">
       <c r="B142">
         <f t="shared" si="13"/>
         <v>140</v>
@@ -20401,7 +20949,7 @@
         <v>140:10</v>
       </c>
     </row>
-    <row r="143" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="143" spans="2:8">
       <c r="B143">
         <f t="shared" si="13"/>
         <v>141</v>
@@ -20430,7 +20978,7 @@
         <v>141:10</v>
       </c>
     </row>
-    <row r="144" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="144" spans="2:8">
       <c r="B144">
         <f t="shared" si="13"/>
         <v>142</v>
@@ -20459,7 +21007,7 @@
         <v>142:10</v>
       </c>
     </row>
-    <row r="145" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="145" spans="2:8">
       <c r="B145">
         <f t="shared" si="13"/>
         <v>143</v>
@@ -20488,7 +21036,7 @@
         <v>143:10</v>
       </c>
     </row>
-    <row r="146" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="146" spans="2:8">
       <c r="B146">
         <f t="shared" si="13"/>
         <v>144</v>
@@ -20517,7 +21065,7 @@
         <v>144:10</v>
       </c>
     </row>
-    <row r="147" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="147" spans="2:8">
       <c r="B147">
         <f t="shared" si="13"/>
         <v>145</v>
@@ -20546,7 +21094,7 @@
         <v>145:10</v>
       </c>
     </row>
-    <row r="148" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="148" spans="2:8">
       <c r="B148">
         <f t="shared" si="13"/>
         <v>146</v>
@@ -20575,7 +21123,7 @@
         <v>146:10</v>
       </c>
     </row>
-    <row r="149" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="149" spans="2:8">
       <c r="B149">
         <f t="shared" si="13"/>
         <v>147</v>
@@ -20604,7 +21152,7 @@
         <v>147:10</v>
       </c>
     </row>
-    <row r="150" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="150" spans="2:8">
       <c r="B150">
         <f t="shared" si="13"/>
         <v>148</v>
@@ -20633,7 +21181,7 @@
         <v>148:10</v>
       </c>
     </row>
-    <row r="151" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="151" spans="2:8">
       <c r="B151">
         <f t="shared" si="13"/>
         <v>149</v>
@@ -20662,7 +21210,7 @@
         <v>149:10</v>
       </c>
     </row>
-    <row r="152" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="152" spans="2:8">
       <c r="B152">
         <f t="shared" si="13"/>
         <v>150</v>
@@ -20691,7 +21239,7 @@
         <v>150:10</v>
       </c>
     </row>
-    <row r="153" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="153" spans="2:8">
       <c r="B153">
         <f t="shared" si="13"/>
         <v>151</v>
@@ -20720,7 +21268,7 @@
         <v>151:10</v>
       </c>
     </row>
-    <row r="154" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="154" spans="2:8">
       <c r="B154">
         <f t="shared" si="13"/>
         <v>152</v>
@@ -20749,7 +21297,7 @@
         <v>152:10</v>
       </c>
     </row>
-    <row r="155" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="155" spans="2:8">
       <c r="B155">
         <f t="shared" si="13"/>
         <v>153</v>
@@ -20778,7 +21326,7 @@
         <v>153:10</v>
       </c>
     </row>
-    <row r="156" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="156" spans="2:8">
       <c r="B156">
         <f t="shared" si="13"/>
         <v>154</v>
@@ -20807,7 +21355,7 @@
         <v>154:10</v>
       </c>
     </row>
-    <row r="157" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="157" spans="2:8">
       <c r="B157">
         <f t="shared" si="13"/>
         <v>155</v>
@@ -20836,7 +21384,7 @@
         <v>155:10</v>
       </c>
     </row>
-    <row r="158" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="158" spans="2:8">
       <c r="B158">
         <f t="shared" si="13"/>
         <v>156</v>
@@ -20865,7 +21413,7 @@
         <v>156:10</v>
       </c>
     </row>
-    <row r="159" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="159" spans="2:8">
       <c r="B159">
         <f t="shared" ref="B159:B162" si="19">B158+1</f>
         <v>157</v>
@@ -20894,7 +21442,7 @@
         <v>157:10</v>
       </c>
     </row>
-    <row r="160" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="160" spans="2:8">
       <c r="B160">
         <f t="shared" si="19"/>
         <v>158</v>
@@ -20923,7 +21471,7 @@
         <v>158:10</v>
       </c>
     </row>
-    <row r="161" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="161" spans="2:8">
       <c r="B161">
         <f t="shared" si="19"/>
         <v>159</v>
@@ -20952,7 +21500,7 @@
         <v>159:10</v>
       </c>
     </row>
-    <row r="162" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="162" spans="2:8">
       <c r="B162">
         <f t="shared" si="19"/>
         <v>160</v>
@@ -20982,7 +21530,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{003A0442-2D4A-426C-A31D-1015A8BF7E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_foe_v8" sheetId="1" r:id="rId1"/>
@@ -24,8 +30,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -33,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="216">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -675,19 +679,19 @@
   </si>
   <si>
     <t>装备分数</t>
+  </si>
+  <si>
+    <t>1:32_2:32_3:32_4:32_5:32_6:32_7:32_8:32_9:32_10:32_11:32_12:32_13:32_14:32_15:32_16:32_17:32_18:32_19:32_20:32_21:32_22:32_23:32_24:32_25:32_26:32_27:32_28:32_29:32_30:32_31:32_32:32_33:32_34:32_35:32_36:32_37:32_38:32_39:32_40:32_41:32_42:32_43:32_44:32_45:32_46:32_47:32_48:32_49:32_50:32_51:32_52:32_53:32_54:32_55:32_56:32_57:32_58:32_59:32_60:32_61:32_62:32_63:32_64:32_65:32_66:32_67:32_68:32_69:32_70:32_71:32_72:32_73:32_74:32_75:32_76:32_77:32_78:32_79:32_80:32_81:32_82:32_83:32_84:32_85:32_86:32_87:32_88:32_89:32_90:32_91:32_92:32_93:32_94:32_95:32_96:32_97:32_98:32_99:32_100:32_101:32_102:32_103:32_104:32_105:32_106:32_107:32_108:32_109:32_110:32_111:32_112:32_113:32_114:32_115:32_116:32_117:32_118:32_119:32_120:32_121:32_122:32_123:32_124:32_125:32_126:32_127:32_128:32_129:32_130:32_131:32_132:32_133:32_134:32_135:32_136:32_137:32_138:32_139:32_140:32_141:32_142:32_143:32_144:32_145:32_146:32_147:32_148:32_149:32_150:32_151:32_152:32_153:32_154:32_155:32_156:32_157:32_158:32_159:32_160:32</t>
+  </si>
+  <si>
+    <t>1:18_2:18_3:18_4:18_5:18_6:18_7:18_8:18_9:18_10:18_11:18_12:18_13:18_14:18_15:18_16:18_17:18_18:18_19:18_20:18_21:18_22:18_23:18_24:18_25:18_26:18_27:18_28:18_29:18_30:18_31:18_32:18_33:18_34:18_35:18_36:18_37:18_38:18_39:18_40:18_41:18_42:18_43:18_44:18_45:18_46:18_47:18_48:18_49:18_50:18_51:18_52:18_53:18_54:18_55:18_56:18_57:18_58:18_59:18_60:18_61:18_62:18_63:18_64:18_65:18_66:18_67:18_68:18_69:18_70:18_71:18_72:18_73:18_74:18_75:18_76:18_77:18_78:18_79:18_80:18_81:18_82:18_83:18_84:18_85:18_86:18_87:18_88:18_89:18_90:18_91:18_92:18_93:18_94:18_95:18_96:18_97:18_98:18_99:18_100:18_101:18_102:18_103:18_104:18_105:18_106:18_107:18_108:18_109:18_110:18_111:18_112:18_113:18_114:18_115:18_116:18_117:18_118:18_119:18_120:18_121:18_122:18_123:18_124:18_125:18_126:18_127:18_128:18_129:18_130:18_131:18_132:18_133:18_134:18_135:18_136:18_137:18_138:18_139:18_140:18_141:18_142:18_143:18_144:18_145:18_146:18_147:18_148:18_149:18_150:18_151:18_152:18_153:18_154:18_155:18_156:18_157:18_158:18_159:18_160:18</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="32">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -699,52 +703,61 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="5" tint="0.799951170384838"/>
+      <color theme="5" tint="0.79992065187536243"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFEE0000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -752,6 +765,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -759,160 +773,33 @@
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="38">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -921,13 +808,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.349986266670736"/>
+        <fgColor theme="0" tint="-0.34998626667073579"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799768059327982"/>
+        <fgColor theme="5" tint="0.79973754081850645"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -951,192 +838,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="12">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1194,248 +901,24 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="53">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="31" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1444,16 +927,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1478,92 +961,45 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="16" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="16" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="51"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="4"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="52" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="53">
+  <cellStyles count="6">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 2" xfId="49"/>
-    <cellStyle name="常规 2 2" xfId="50"/>
-    <cellStyle name="常规 3" xfId="51"/>
-    <cellStyle name="输入 2" xfId="52"/>
+    <cellStyle name="常规 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="常规 2 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="常规 3" xfId="4" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
+    <cellStyle name="输入" xfId="1" builtinId="20"/>
+    <cellStyle name="输入 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -1581,6 +1017,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1838,14 +1277,15 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:AJ132"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.125" style="8" customWidth="1"/>
     <col min="2" max="2" width="10.625" style="8" customWidth="1"/>
@@ -1870,7 +1310,7 @@
     <col min="37" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1902,7 +1342,7 @@
       <c r="AD1" s="3"/>
       <c r="AE1" s="3"/>
     </row>
-    <row r="2" ht="14.25" spans="1:36">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
@@ -2012,7 +1452,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" ht="14.25" spans="1:36">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
         <v>9</v>
       </c>
@@ -2122,7 +1562,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" ht="25.5" customHeight="1" spans="1:36">
+    <row r="4" spans="1:36" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="11" t="s">
         <v>45</v>
       </c>
@@ -2232,7 +1672,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:36">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>10201</v>
       </c>
@@ -2335,7 +1775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>10301</v>
       </c>
@@ -2438,7 +1878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:36">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>10302</v>
       </c>
@@ -2541,7 +1981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:36">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>10303</v>
       </c>
@@ -2644,7 +2084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>10304</v>
       </c>
@@ -2747,7 +2187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:36">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>10305</v>
       </c>
@@ -2850,7 +2290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:36">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>10306</v>
       </c>
@@ -2953,7 +2393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:36">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>10307</v>
       </c>
@@ -3056,7 +2496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:36">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>10308</v>
       </c>
@@ -3159,7 +2599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:36">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>10309</v>
       </c>
@@ -3262,7 +2702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:36">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>10310</v>
       </c>
@@ -3365,7 +2805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:36">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>10401</v>
       </c>
@@ -3468,7 +2908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:36">
+    <row r="17" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>10402</v>
       </c>
@@ -3571,7 +3011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:36">
+    <row r="18" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>10403</v>
       </c>
@@ -3674,7 +3114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:36">
+    <row r="19" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>20201</v>
       </c>
@@ -3777,7 +3217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:36">
+    <row r="20" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>20301</v>
       </c>
@@ -3880,7 +3320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:36">
+    <row r="21" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>20302</v>
       </c>
@@ -3983,7 +3423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:36">
+    <row r="22" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>20303</v>
       </c>
@@ -4086,7 +3526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:36">
+    <row r="23" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>20304</v>
       </c>
@@ -4189,7 +3629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:36">
+    <row r="24" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>20305</v>
       </c>
@@ -4292,7 +3732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:36">
+    <row r="25" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
         <v>20306</v>
       </c>
@@ -4395,7 +3835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:36">
+    <row r="26" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
         <v>20307</v>
       </c>
@@ -4498,7 +3938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:36">
+    <row r="27" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
         <v>20308</v>
       </c>
@@ -4601,7 +4041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:36">
+    <row r="28" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
         <v>20309</v>
       </c>
@@ -4704,7 +4144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:36">
+    <row r="29" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
         <v>20310</v>
       </c>
@@ -4807,7 +4247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:36">
+    <row r="30" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
         <v>20401</v>
       </c>
@@ -4910,7 +4350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:36">
+    <row r="31" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A31" s="3">
         <v>20402</v>
       </c>
@@ -5013,7 +4453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:36">
+    <row r="32" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A32" s="3">
         <v>20403</v>
       </c>
@@ -5116,7 +4556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:36">
+    <row r="33" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A33" s="3">
         <v>110201</v>
       </c>
@@ -5219,7 +4659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:36">
+    <row r="34" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A34" s="3">
         <v>110301</v>
       </c>
@@ -5322,7 +4762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:36">
+    <row r="35" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A35" s="3">
         <v>110302</v>
       </c>
@@ -5425,7 +4865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:36">
+    <row r="36" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A36" s="3">
         <v>110303</v>
       </c>
@@ -5528,7 +4968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:36">
+    <row r="37" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A37" s="3">
         <v>110304</v>
       </c>
@@ -5631,7 +5071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:36">
+    <row r="38" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A38" s="3">
         <v>110305</v>
       </c>
@@ -5734,7 +5174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:36">
+    <row r="39" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A39" s="3">
         <v>110306</v>
       </c>
@@ -5837,7 +5277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:36">
+    <row r="40" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A40" s="3">
         <v>110307</v>
       </c>
@@ -5940,7 +5380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:36">
+    <row r="41" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A41" s="3">
         <v>110308</v>
       </c>
@@ -6043,7 +5483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:36">
+    <row r="42" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A42" s="3">
         <v>110309</v>
       </c>
@@ -6146,7 +5586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:36">
+    <row r="43" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A43" s="3">
         <v>110310</v>
       </c>
@@ -6249,7 +5689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:36">
+    <row r="44" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A44" s="3">
         <v>110401</v>
       </c>
@@ -6352,7 +5792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:36">
+    <row r="45" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A45" s="3">
         <v>110402</v>
       </c>
@@ -6455,7 +5895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:36">
+    <row r="46" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A46" s="3">
         <v>110403</v>
       </c>
@@ -6558,7 +5998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:36">
+    <row r="47" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A47" s="3">
         <v>121101</v>
       </c>
@@ -6661,7 +6101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:36">
+    <row r="48" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A48" s="3">
         <v>121102</v>
       </c>
@@ -6764,7 +6204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:36">
+    <row r="49" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
         <v>121103</v>
       </c>
@@ -6868,7 +6308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:36">
+    <row r="50" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A50" s="3">
         <v>121104</v>
       </c>
@@ -6971,7 +6411,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="51" spans="1:36">
+    <row r="51" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A51" s="3">
         <v>121105</v>
       </c>
@@ -7074,7 +6514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:36">
+    <row r="52" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
         <v>121106</v>
       </c>
@@ -7178,7 +6618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:36">
+    <row r="53" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
         <v>121107</v>
       </c>
@@ -7282,7 +6722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:36">
+    <row r="54" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
         <v>121108</v>
       </c>
@@ -7386,7 +6826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:36">
+    <row r="55" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
         <v>121109</v>
       </c>
@@ -7490,7 +6930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:36">
+    <row r="56" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
         <v>121110</v>
       </c>
@@ -7594,7 +7034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:36">
+    <row r="57" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
         <v>121111</v>
       </c>
@@ -7698,7 +7138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:36">
+    <row r="58" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
         <v>121112</v>
       </c>
@@ -7802,7 +7242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" ht="14.25" spans="1:36">
+    <row r="59" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A59" s="3">
         <v>121113</v>
       </c>
@@ -7905,7 +7345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:36">
+    <row r="60" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
         <v>121114</v>
       </c>
@@ -8009,7 +7449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:36">
+    <row r="61" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
         <v>121115</v>
       </c>
@@ -8113,7 +7553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:36">
+    <row r="62" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A62" s="3">
         <v>999001</v>
       </c>
@@ -8216,7 +7656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:36">
+    <row r="63" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A63" s="3">
         <v>999002</v>
       </c>
@@ -8319,7 +7759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:36">
+    <row r="64" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A64" s="3">
         <v>999003</v>
       </c>
@@ -8422,7 +7862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:36">
+    <row r="65" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A65" s="3">
         <v>999004</v>
       </c>
@@ -8525,7 +7965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" ht="14.25" spans="1:36">
+    <row r="66" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A66" s="18">
         <v>9999001</v>
       </c>
@@ -8629,7 +8069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" ht="14.25" spans="1:36">
+    <row r="67" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A67" s="18">
         <v>9999002</v>
       </c>
@@ -8733,7 +8173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" ht="14.25" spans="1:36">
+    <row r="68" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A68" s="18">
         <v>9999004</v>
       </c>
@@ -8837,7 +8277,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="69" ht="14.25" spans="1:36">
+    <row r="69" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A69" s="18">
         <v>9999005</v>
       </c>
@@ -8941,7 +8381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" ht="14.25" spans="1:36">
+    <row r="70" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A70" s="18">
         <v>9999013</v>
       </c>
@@ -9045,7 +8485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:36">
+    <row r="71" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A71" s="3">
         <v>301101</v>
       </c>
@@ -9085,7 +8525,7 @@
         <v>0</v>
       </c>
       <c r="P71" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q71" s="3">
         <v>0</v>
@@ -9109,7 +8549,7 @@
         <v>111</v>
       </c>
       <c r="X71" s="3" t="s">
-        <v>152</v>
+        <v>214</v>
       </c>
       <c r="Y71" s="16">
         <v>201001011</v>
@@ -9148,7 +8588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:36">
+    <row r="72" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A72" s="3">
         <v>301102</v>
       </c>
@@ -9188,7 +8628,7 @@
         <v>0</v>
       </c>
       <c r="P72" s="3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Q72" s="3">
         <v>2</v>
@@ -9212,7 +8652,7 @@
         <v>111</v>
       </c>
       <c r="X72" s="3" t="s">
-        <v>152</v>
+        <v>214</v>
       </c>
       <c r="Y72" s="16">
         <v>201002011</v>
@@ -9251,7 +8691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:36">
+    <row r="73" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
         <v>301103</v>
       </c>
@@ -9314,7 +8754,7 @@
         <v>111</v>
       </c>
       <c r="X73" s="2" t="s">
-        <v>152</v>
+        <v>214</v>
       </c>
       <c r="Y73" s="17">
         <v>201001011</v>
@@ -9353,7 +8793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:36">
+    <row r="74" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A74" s="3">
         <v>301104</v>
       </c>
@@ -9393,7 +8833,7 @@
         <v>0</v>
       </c>
       <c r="P74" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q74" s="3">
         <v>0</v>
@@ -9417,7 +8857,7 @@
         <v>111</v>
       </c>
       <c r="X74" s="3" t="s">
-        <v>152</v>
+        <v>214</v>
       </c>
       <c r="Y74" s="16">
         <v>201004011</v>
@@ -9456,7 +8896,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="75" spans="1:36">
+    <row r="75" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A75" s="3">
         <v>301105</v>
       </c>
@@ -9496,7 +8936,7 @@
         <v>0</v>
       </c>
       <c r="P75" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="Q75" s="3">
         <v>1</v>
@@ -9520,7 +8960,7 @@
         <v>111</v>
       </c>
       <c r="X75" s="3" t="s">
-        <v>152</v>
+        <v>214</v>
       </c>
       <c r="Y75" s="16">
         <v>214001011</v>
@@ -9559,7 +8999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:36">
+    <row r="76" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
         <v>301106</v>
       </c>
@@ -9661,7 +9101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:36">
+    <row r="77" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
         <v>301107</v>
       </c>
@@ -9765,7 +9205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" ht="14.25" spans="1:36">
+    <row r="78" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A78" s="3">
         <v>301108</v>
       </c>
@@ -9868,7 +9308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" ht="14.25" spans="1:36">
+    <row r="79" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A79" s="3">
         <v>301109</v>
       </c>
@@ -9971,7 +9411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" ht="14.25" spans="1:36">
+    <row r="80" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A80" s="3">
         <v>301110</v>
       </c>
@@ -10074,7 +9514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" ht="14.25" spans="1:36">
+    <row r="81" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A81" s="3">
         <v>301111</v>
       </c>
@@ -10177,7 +9617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" ht="14.25" spans="1:36">
+    <row r="82" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A82" s="3">
         <v>301112</v>
       </c>
@@ -10280,7 +9720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" ht="14.25" spans="1:36">
+    <row r="83" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A83" s="3">
         <v>301113</v>
       </c>
@@ -10383,7 +9823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" ht="14.25" spans="1:36">
+    <row r="84" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A84" s="3">
         <v>301114</v>
       </c>
@@ -10486,7 +9926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:36">
+    <row r="85" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
         <v>301115</v>
       </c>
@@ -10588,7 +10028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:36">
+    <row r="86" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A86" s="3">
         <v>302101</v>
       </c>
@@ -10628,7 +10068,7 @@
         <v>0</v>
       </c>
       <c r="P86" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q86" s="3">
         <v>0</v>
@@ -10652,7 +10092,7 @@
         <v>111</v>
       </c>
       <c r="X86" s="3" t="s">
-        <v>152</v>
+        <v>215</v>
       </c>
       <c r="Y86" s="16">
         <v>201001011</v>
@@ -10691,7 +10131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:36">
+    <row r="87" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A87" s="3">
         <v>302102</v>
       </c>
@@ -10731,7 +10171,7 @@
         <v>0</v>
       </c>
       <c r="P87" s="3">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Q87" s="3">
         <v>3</v>
@@ -10755,7 +10195,7 @@
         <v>111</v>
       </c>
       <c r="X87" s="3" t="s">
-        <v>152</v>
+        <v>215</v>
       </c>
       <c r="Y87" s="16">
         <v>201002011</v>
@@ -10794,7 +10234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:36">
+    <row r="88" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
         <v>302103</v>
       </c>
@@ -10859,7 +10299,7 @@
         <v>111</v>
       </c>
       <c r="X88" s="2" t="s">
-        <v>152</v>
+        <v>215</v>
       </c>
       <c r="Y88" s="17">
         <v>201002011</v>
@@ -10898,7 +10338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:36">
+    <row r="89" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A89" s="3">
         <v>302104</v>
       </c>
@@ -10938,7 +10378,7 @@
         <v>0</v>
       </c>
       <c r="P89" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Q89" s="3">
         <v>0</v>
@@ -10962,7 +10402,7 @@
         <v>111</v>
       </c>
       <c r="X89" s="3" t="s">
-        <v>152</v>
+        <v>215</v>
       </c>
       <c r="Y89" s="16">
         <v>201004011</v>
@@ -11001,7 +10441,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="1:36">
+    <row r="90" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A90" s="3">
         <v>302105</v>
       </c>
@@ -11041,13 +10481,13 @@
         <v>0</v>
       </c>
       <c r="P90" s="3">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="Q90" s="3">
         <v>2</v>
       </c>
       <c r="R90" s="3">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="S90" s="3">
         <v>-5500</v>
@@ -11065,7 +10505,7 @@
         <v>111</v>
       </c>
       <c r="X90" s="3" t="s">
-        <v>152</v>
+        <v>215</v>
       </c>
       <c r="Y90" s="16">
         <v>214001011</v>
@@ -11104,7 +10544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:36">
+    <row r="91" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
         <v>302106</v>
       </c>
@@ -11208,7 +10648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:36">
+    <row r="92" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
         <v>302107</v>
       </c>
@@ -11312,7 +10752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:36">
+    <row r="93" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
         <v>302108</v>
       </c>
@@ -11416,7 +10856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:36">
+    <row r="94" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
         <v>302109</v>
       </c>
@@ -11520,7 +10960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:36">
+    <row r="95" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
         <v>302110</v>
       </c>
@@ -11624,7 +11064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:36">
+    <row r="96" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
         <v>302111</v>
       </c>
@@ -11728,7 +11168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:36">
+    <row r="97" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
         <v>302112</v>
       </c>
@@ -11832,7 +11272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" ht="14.25" spans="1:36">
+    <row r="98" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A98" s="3">
         <v>302113</v>
       </c>
@@ -11935,7 +11375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:36">
+    <row r="99" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
         <v>302114</v>
       </c>
@@ -12039,7 +11479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:36">
+    <row r="100" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A100" s="2">
         <v>302115</v>
       </c>
@@ -12143,7 +11583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:36">
+    <row r="101" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A101" s="3">
         <v>303101</v>
       </c>
@@ -12183,7 +11623,7 @@
         <v>0</v>
       </c>
       <c r="P101" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -12246,7 +11686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:36">
+    <row r="102" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A102" s="3">
         <v>303102</v>
       </c>
@@ -12286,7 +11726,7 @@
         <v>0</v>
       </c>
       <c r="P102" s="3">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="Q102" s="3">
         <v>4</v>
@@ -12349,7 +11789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:36">
+    <row r="103" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A103" s="2">
         <v>303103</v>
       </c>
@@ -12453,7 +11893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:36">
+    <row r="104" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A104" s="3">
         <v>303104</v>
       </c>
@@ -12493,7 +11933,7 @@
         <v>0</v>
       </c>
       <c r="P104" s="3">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Q104" s="3">
         <v>0</v>
@@ -12556,7 +11996,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="105" spans="1:36">
+    <row r="105" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A105" s="3">
         <v>303105</v>
       </c>
@@ -12596,13 +12036,13 @@
         <v>0</v>
       </c>
       <c r="P105" s="3">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="Q105" s="3">
         <v>2</v>
       </c>
       <c r="R105" s="3">
-        <v>268</v>
+        <v>301</v>
       </c>
       <c r="S105" s="3">
         <v>-5500</v>
@@ -12659,7 +12099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:36">
+    <row r="106" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A106" s="2">
         <v>303106</v>
       </c>
@@ -12763,7 +12203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:36">
+    <row r="107" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A107" s="2">
         <v>303107</v>
       </c>
@@ -12867,7 +12307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:36">
+    <row r="108" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A108" s="2">
         <v>303108</v>
       </c>
@@ -12971,7 +12411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:36">
+    <row r="109" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A109" s="2">
         <v>303109</v>
       </c>
@@ -13075,7 +12515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:36">
+    <row r="110" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A110" s="2">
         <v>303110</v>
       </c>
@@ -13179,7 +12619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:36">
+    <row r="111" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A111" s="2">
         <v>303111</v>
       </c>
@@ -13283,7 +12723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:36">
+    <row r="112" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A112" s="2">
         <v>303112</v>
       </c>
@@ -13387,7 +12827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" ht="14.25" spans="1:36">
+    <row r="113" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A113" s="3">
         <v>303113</v>
       </c>
@@ -13490,7 +12930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:36">
+    <row r="114" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A114" s="2">
         <v>303114</v>
       </c>
@@ -13594,7 +13034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" ht="14.25" spans="1:36">
+    <row r="115" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A115" s="3">
         <v>303115</v>
       </c>
@@ -13634,7 +13074,7 @@
         <v>0</v>
       </c>
       <c r="P115" s="3">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="Q115" s="3">
         <v>7</v>
@@ -13697,7 +13137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" ht="14.25" spans="1:36">
+    <row r="116" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A116" s="19">
         <v>90000201</v>
       </c>
@@ -13801,7 +13241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" ht="14.25" spans="1:36">
+    <row r="117" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A117" s="19">
         <v>90000301</v>
       </c>
@@ -13905,7 +13345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" ht="14.25" spans="1:36">
+    <row r="118" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A118" s="19">
         <v>90000302</v>
       </c>
@@ -14009,7 +13449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" ht="14.25" spans="1:36">
+    <row r="119" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A119" s="19">
         <v>90000401</v>
       </c>
@@ -14113,7 +13553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" ht="14.25" spans="1:36">
+    <row r="120" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A120" s="19">
         <v>90000402</v>
       </c>
@@ -14217,7 +13657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" ht="14.25" spans="1:36">
+    <row r="121" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A121" s="19">
         <v>90000501</v>
       </c>
@@ -14321,7 +13761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" ht="14.25" spans="1:36">
+    <row r="122" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A122" s="19">
         <v>90000502</v>
       </c>
@@ -14425,7 +13865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" ht="14.25" spans="1:36">
+    <row r="123" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A123" s="19">
         <v>90000503</v>
       </c>
@@ -14529,7 +13969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" ht="14.25" spans="1:36">
+    <row r="124" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A124" s="19">
         <v>90000504</v>
       </c>
@@ -14633,7 +14073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" ht="14.25" spans="1:36">
+    <row r="125" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A125" s="19">
         <v>90000601</v>
       </c>
@@ -14737,7 +14177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" ht="14.25" spans="1:36">
+    <row r="126" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A126" s="19">
         <v>90000602</v>
       </c>
@@ -14841,7 +14281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" ht="14.25" spans="1:36">
+    <row r="127" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A127" s="19">
         <v>90000603</v>
       </c>
@@ -14945,7 +14385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" ht="14.25" spans="1:36">
+    <row r="128" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A128" s="19">
         <v>90000604</v>
       </c>
@@ -15049,7 +14489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" ht="14.25" spans="1:36">
+    <row r="129" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A129" s="19">
         <v>90000605</v>
       </c>
@@ -15153,7 +14593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" ht="14.25" spans="1:36">
+    <row r="130" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A130" s="19">
         <v>90000606</v>
       </c>
@@ -15257,7 +14697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" ht="14.25" spans="1:36">
+    <row r="131" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A131" s="19">
         <v>90000607</v>
       </c>
@@ -15361,7 +14801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" ht="14.25" spans="1:36">
+    <row r="132" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A132" s="19">
         <v>90000608</v>
       </c>
@@ -15466,28 +14906,28 @@
       </c>
     </row>
   </sheetData>
-  <sortState ref="A5:AD61">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:AD61">
     <sortCondition ref="A5:A61"/>
   </sortState>
+  <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="A1:A65 A71:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="33"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="I1:S28"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="9:19">
+    <row r="1" spans="9:19" x14ac:dyDescent="0.15">
       <c r="I1" s="6">
         <v>1</v>
       </c>
@@ -15518,7 +14958,7 @@
         <v>65000</v>
       </c>
     </row>
-    <row r="2" spans="9:19">
+    <row r="2" spans="9:19" x14ac:dyDescent="0.15">
       <c r="I2" s="6">
         <v>2</v>
       </c>
@@ -15549,7 +14989,7 @@
         <v>85000</v>
       </c>
     </row>
-    <row r="3" spans="9:19">
+    <row r="3" spans="9:19" x14ac:dyDescent="0.15">
       <c r="I3" s="6">
         <v>2</v>
       </c>
@@ -15580,7 +15020,7 @@
         <v>110000</v>
       </c>
     </row>
-    <row r="4" spans="9:19">
+    <row r="4" spans="9:19" x14ac:dyDescent="0.15">
       <c r="I4" s="6">
         <v>3</v>
       </c>
@@ -15611,7 +15051,7 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="5" spans="9:19">
+    <row r="5" spans="9:19" x14ac:dyDescent="0.15">
       <c r="I5" s="6">
         <v>3</v>
       </c>
@@ -15642,7 +15082,7 @@
         <v>180000</v>
       </c>
     </row>
-    <row r="6" spans="9:19">
+    <row r="6" spans="9:19" x14ac:dyDescent="0.15">
       <c r="I6" s="6">
         <v>4</v>
       </c>
@@ -15673,7 +15113,7 @@
         <v>350000</v>
       </c>
     </row>
-    <row r="7" spans="9:19">
+    <row r="7" spans="9:19" x14ac:dyDescent="0.15">
       <c r="I7" s="6">
         <v>4</v>
       </c>
@@ -15704,7 +15144,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="8" spans="9:19">
+    <row r="8" spans="9:19" x14ac:dyDescent="0.15">
       <c r="I8" s="6">
         <v>5</v>
       </c>
@@ -15735,7 +15175,7 @@
         <v>800000</v>
       </c>
     </row>
-    <row r="9" spans="9:19">
+    <row r="9" spans="9:19" x14ac:dyDescent="0.15">
       <c r="I9" s="6">
         <v>5</v>
       </c>
@@ -15766,7 +15206,7 @@
         <v>1400000</v>
       </c>
     </row>
-    <row r="10" spans="9:19">
+    <row r="10" spans="9:19" x14ac:dyDescent="0.15">
       <c r="I10" s="6">
         <v>6</v>
       </c>
@@ -15797,7 +15237,7 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="11" spans="9:14">
+    <row r="11" spans="9:19" x14ac:dyDescent="0.15">
       <c r="I11" s="6">
         <v>6</v>
       </c>
@@ -15819,7 +15259,7 @@
         <v>350000</v>
       </c>
     </row>
-    <row r="12" spans="9:14">
+    <row r="12" spans="9:19" x14ac:dyDescent="0.15">
       <c r="I12" s="6">
         <v>6</v>
       </c>
@@ -15841,7 +15281,7 @@
         <v>350000</v>
       </c>
     </row>
-    <row r="13" spans="9:14">
+    <row r="13" spans="9:19" x14ac:dyDescent="0.15">
       <c r="I13" s="6">
         <v>7</v>
       </c>
@@ -15863,7 +15303,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="14" spans="9:14">
+    <row r="14" spans="9:19" x14ac:dyDescent="0.15">
       <c r="I14" s="6">
         <v>7</v>
       </c>
@@ -15885,7 +15325,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="15" spans="9:14">
+    <row r="15" spans="9:19" x14ac:dyDescent="0.15">
       <c r="I15" s="6">
         <v>7</v>
       </c>
@@ -15907,7 +15347,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="16" spans="9:14">
+    <row r="16" spans="9:19" x14ac:dyDescent="0.15">
       <c r="I16" s="6">
         <v>7</v>
       </c>
@@ -15929,7 +15369,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="17" spans="9:14">
+    <row r="17" spans="9:14" x14ac:dyDescent="0.15">
       <c r="I17" s="6">
         <v>8</v>
       </c>
@@ -15951,7 +15391,7 @@
         <v>800000</v>
       </c>
     </row>
-    <row r="18" spans="9:14">
+    <row r="18" spans="9:14" x14ac:dyDescent="0.15">
       <c r="I18" s="6">
         <v>8</v>
       </c>
@@ -15973,7 +15413,7 @@
         <v>800000</v>
       </c>
     </row>
-    <row r="19" spans="9:14">
+    <row r="19" spans="9:14" x14ac:dyDescent="0.15">
       <c r="I19" s="6">
         <v>8</v>
       </c>
@@ -15995,7 +15435,7 @@
         <v>800000</v>
       </c>
     </row>
-    <row r="20" spans="9:14">
+    <row r="20" spans="9:14" x14ac:dyDescent="0.15">
       <c r="I20" s="6">
         <v>8</v>
       </c>
@@ -16017,7 +15457,7 @@
         <v>800000</v>
       </c>
     </row>
-    <row r="21" spans="9:14">
+    <row r="21" spans="9:14" x14ac:dyDescent="0.15">
       <c r="I21" s="6">
         <v>9</v>
       </c>
@@ -16039,7 +15479,7 @@
         <v>1400000</v>
       </c>
     </row>
-    <row r="22" spans="9:14">
+    <row r="22" spans="9:14" x14ac:dyDescent="0.15">
       <c r="I22" s="6">
         <v>9</v>
       </c>
@@ -16061,7 +15501,7 @@
         <v>1400000</v>
       </c>
     </row>
-    <row r="23" spans="9:14">
+    <row r="23" spans="9:14" x14ac:dyDescent="0.15">
       <c r="I23" s="6">
         <v>9</v>
       </c>
@@ -16083,7 +15523,7 @@
         <v>1400000</v>
       </c>
     </row>
-    <row r="24" spans="9:14">
+    <row r="24" spans="9:14" x14ac:dyDescent="0.15">
       <c r="I24" s="6">
         <v>9</v>
       </c>
@@ -16105,7 +15545,7 @@
         <v>1400000</v>
       </c>
     </row>
-    <row r="25" spans="9:14">
+    <row r="25" spans="9:14" x14ac:dyDescent="0.15">
       <c r="I25" s="6">
         <v>10</v>
       </c>
@@ -16127,7 +15567,7 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="26" spans="9:14">
+    <row r="26" spans="9:14" x14ac:dyDescent="0.15">
       <c r="I26" s="6">
         <v>10</v>
       </c>
@@ -16149,7 +15589,7 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="27" spans="9:14">
+    <row r="27" spans="9:14" x14ac:dyDescent="0.15">
       <c r="I27" s="6">
         <v>10</v>
       </c>
@@ -16171,7 +15611,7 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="28" spans="9:14">
+    <row r="28" spans="9:14" x14ac:dyDescent="0.15">
       <c r="I28" s="6">
         <v>10</v>
       </c>
@@ -16194,16 +15634,16 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A6:O22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="8.625" style="1" customWidth="1"/>
@@ -16222,7 +15662,7 @@
     <col min="16" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="6" ht="14.25" spans="2:14">
+    <row r="6" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>55</v>
       </c>
@@ -16245,7 +15685,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="7" ht="14.25" spans="1:15">
+    <row r="7" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>128</v>
       </c>
@@ -16289,7 +15729,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="8" ht="14.25" spans="1:15">
+    <row r="8" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>128</v>
       </c>
@@ -16333,7 +15773,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="9" ht="14.25" spans="1:15">
+    <row r="9" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>128</v>
       </c>
@@ -16377,7 +15817,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="10" ht="14.25" spans="1:15">
+    <row r="10" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>128</v>
       </c>
@@ -16421,7 +15861,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="11" ht="14.25" spans="1:15">
+    <row r="11" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>125</v>
       </c>
@@ -16465,7 +15905,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="12" ht="14.25" spans="1:15">
+    <row r="12" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>125</v>
       </c>
@@ -16509,7 +15949,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="13" ht="14.25" spans="1:15">
+    <row r="13" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>125</v>
       </c>
@@ -16553,7 +15993,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="14" ht="14.25" spans="1:15">
+    <row r="14" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>125</v>
       </c>
@@ -16597,7 +16037,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="15" ht="14.25" spans="1:15">
+    <row r="15" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>140</v>
       </c>
@@ -16640,7 +16080,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="16" ht="14.25" spans="1:15">
+    <row r="16" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>140</v>
       </c>
@@ -16683,7 +16123,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="17" ht="14.25" spans="1:7">
+    <row r="17" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>140</v>
       </c>
@@ -16708,7 +16148,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="18" ht="14.25" spans="1:7">
+    <row r="18" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>140</v>
       </c>
@@ -16733,7 +16173,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="19" ht="14.25" spans="1:7">
+    <row r="19" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>204</v>
       </c>
@@ -16759,7 +16199,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="20" ht="14.25" spans="1:7">
+    <row r="20" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>204</v>
       </c>
@@ -16785,7 +16225,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="21" ht="14.25" spans="1:7">
+    <row r="21" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>132</v>
       </c>
@@ -16811,7 +16251,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="22" ht="14.25" spans="1:7">
+    <row r="22" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>132</v>
       </c>
@@ -16838,18 +16278,18 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="B2:K162"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="3:11">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C2" t="s">
         <v>211</v>
       </c>
@@ -16878,7 +16318,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="3" spans="2:11">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B3">
         <v>1</v>
       </c>
@@ -16918,7 +16358,7 @@
         <v>1:10_2:10_3:10_4:10_5:10_6:10_7:10_8:10_9:10_10:10_11:10_12:10_13:10_14:10_15:10_16:10_17:10_18:10_19:10_20:10_21:10_22:10_23:10_24:10_25:10_26:10_27:10_28:10_29:10_30:10_31:10_32:10_33:10_34:10_35:10_36:10_37:10_38:10_39:10_40:10_41:10_42:10_43:10_44:10_45:10_46:10_47:10_48:10_49:10_50:10_51:10_52:10_53:10_54:10_55:10_56:10_57:10_58:10_59:10_60:10_61:10_62:10_63:10_64:10_65:10_66:10_67:10_68:10_69:10_70:10_71:10_72:10_73:10_74:10_75:10_76:10_77:10_78:10_79:10_80:10_81:10_82:10_83:10_84:10_85:10_86:10_87:10_88:10_89:10_90:10_91:10_92:10_93:10_94:10_95:10_96:10_97:10_98:10_99:10_100:10_101:10_102:10_103:10_104:10_105:10_106:10_107:10_108:10_109:10_110:10_111:10_112:10_113:10_114:10_115:10_116:10_117:10_118:10_119:10_120:10_121:10_122:10_123:10_124:10_125:10_126:10_127:10_128:10_129:10_130:10_131:10_132:10_133:10_134:10_135:10_136:10_137:10_138:10_139:10_140:10_141:10_142:10_143:10_144:10_145:10_146:10_147:10_148:10_149:10_150:10_151:10_152:10_153:10_154:10_155:10_156:10_157:10_158:10_159:10_160:10</v>
       </c>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B4">
         <f t="shared" ref="B4:B35" si="0">B3+1</f>
         <v>2</v>
@@ -16947,7 +16387,7 @@
         <v>2:10</v>
       </c>
     </row>
-    <row r="5" spans="2:8">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B5">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -16976,7 +16416,7 @@
         <v>3:10</v>
       </c>
     </row>
-    <row r="6" spans="2:8">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B6">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -17005,7 +16445,7 @@
         <v>4:10</v>
       </c>
     </row>
-    <row r="7" spans="2:8">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B7">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -17034,7 +16474,7 @@
         <v>5:10</v>
       </c>
     </row>
-    <row r="8" spans="2:8">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -17063,7 +16503,7 @@
         <v>6:10</v>
       </c>
     </row>
-    <row r="9" spans="2:8">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B9">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -17092,7 +16532,7 @@
         <v>7:10</v>
       </c>
     </row>
-    <row r="10" spans="2:8">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -17121,7 +16561,7 @@
         <v>8:10</v>
       </c>
     </row>
-    <row r="11" spans="2:8">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B11">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -17150,7 +16590,7 @@
         <v>9:10</v>
       </c>
     </row>
-    <row r="12" spans="2:8">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B12">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -17179,7 +16619,7 @@
         <v>10:10</v>
       </c>
     </row>
-    <row r="13" spans="2:8">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B13">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -17208,7 +16648,7 @@
         <v>11:10</v>
       </c>
     </row>
-    <row r="14" spans="2:8">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B14">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -17237,7 +16677,7 @@
         <v>12:10</v>
       </c>
     </row>
-    <row r="15" spans="2:8">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B15">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -17266,7 +16706,7 @@
         <v>13:10</v>
       </c>
     </row>
-    <row r="16" spans="2:8">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B16">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -17295,7 +16735,7 @@
         <v>14:10</v>
       </c>
     </row>
-    <row r="17" spans="2:8">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B17">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -17324,7 +16764,7 @@
         <v>15:10</v>
       </c>
     </row>
-    <row r="18" spans="2:8">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B18">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -17353,7 +16793,7 @@
         <v>16:10</v>
       </c>
     </row>
-    <row r="19" spans="2:8">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B19">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -17382,7 +16822,7 @@
         <v>17:10</v>
       </c>
     </row>
-    <row r="20" spans="2:8">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B20">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -17411,7 +16851,7 @@
         <v>18:10</v>
       </c>
     </row>
-    <row r="21" spans="2:8">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B21">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -17440,7 +16880,7 @@
         <v>19:10</v>
       </c>
     </row>
-    <row r="22" spans="2:8">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B22">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -17469,7 +16909,7 @@
         <v>20:10</v>
       </c>
     </row>
-    <row r="23" spans="2:8">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B23">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -17498,7 +16938,7 @@
         <v>21:10</v>
       </c>
     </row>
-    <row r="24" spans="2:8">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B24">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -17527,7 +16967,7 @@
         <v>22:10</v>
       </c>
     </row>
-    <row r="25" spans="2:8">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B25">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -17556,7 +16996,7 @@
         <v>23:10</v>
       </c>
     </row>
-    <row r="26" spans="2:8">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B26">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -17585,7 +17025,7 @@
         <v>24:10</v>
       </c>
     </row>
-    <row r="27" spans="2:8">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B27">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -17614,7 +17054,7 @@
         <v>25:10</v>
       </c>
     </row>
-    <row r="28" spans="2:8">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B28">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -17643,7 +17083,7 @@
         <v>26:10</v>
       </c>
     </row>
-    <row r="29" spans="2:8">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B29">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -17672,7 +17112,7 @@
         <v>27:10</v>
       </c>
     </row>
-    <row r="30" spans="2:8">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B30">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -17701,7 +17141,7 @@
         <v>28:10</v>
       </c>
     </row>
-    <row r="31" spans="2:8">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B31">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -17730,7 +17170,7 @@
         <v>29:10</v>
       </c>
     </row>
-    <row r="32" spans="2:8">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B32">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -17759,7 +17199,7 @@
         <v>30:10</v>
       </c>
     </row>
-    <row r="33" spans="2:8">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -17788,7 +17228,7 @@
         <v>31:10</v>
       </c>
     </row>
-    <row r="34" spans="2:8">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B34">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -17817,7 +17257,7 @@
         <v>32:10</v>
       </c>
     </row>
-    <row r="35" spans="2:8">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -17846,7 +17286,7 @@
         <v>33:10</v>
       </c>
     </row>
-    <row r="36" spans="2:8">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B36">
         <f t="shared" ref="B36:B67" si="6">B35+1</f>
         <v>34</v>
@@ -17875,7 +17315,7 @@
         <v>34:10</v>
       </c>
     </row>
-    <row r="37" spans="2:8">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B37">
         <f t="shared" si="6"/>
         <v>35</v>
@@ -17904,7 +17344,7 @@
         <v>35:10</v>
       </c>
     </row>
-    <row r="38" spans="2:8">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B38">
         <f t="shared" si="6"/>
         <v>36</v>
@@ -17933,7 +17373,7 @@
         <v>36:10</v>
       </c>
     </row>
-    <row r="39" spans="2:8">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B39">
         <f t="shared" si="6"/>
         <v>37</v>
@@ -17962,7 +17402,7 @@
         <v>37:10</v>
       </c>
     </row>
-    <row r="40" spans="2:8">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B40">
         <f t="shared" si="6"/>
         <v>38</v>
@@ -17991,7 +17431,7 @@
         <v>38:10</v>
       </c>
     </row>
-    <row r="41" spans="2:8">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B41">
         <f t="shared" si="6"/>
         <v>39</v>
@@ -18020,7 +17460,7 @@
         <v>39:10</v>
       </c>
     </row>
-    <row r="42" spans="2:8">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B42">
         <f t="shared" si="6"/>
         <v>40</v>
@@ -18049,7 +17489,7 @@
         <v>40:10</v>
       </c>
     </row>
-    <row r="43" spans="2:8">
+    <row r="43" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B43">
         <f t="shared" si="6"/>
         <v>41</v>
@@ -18078,7 +17518,7 @@
         <v>41:10</v>
       </c>
     </row>
-    <row r="44" spans="2:8">
+    <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44">
         <f t="shared" si="6"/>
         <v>42</v>
@@ -18107,7 +17547,7 @@
         <v>42:10</v>
       </c>
     </row>
-    <row r="45" spans="2:8">
+    <row r="45" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B45">
         <f t="shared" si="6"/>
         <v>43</v>
@@ -18136,7 +17576,7 @@
         <v>43:10</v>
       </c>
     </row>
-    <row r="46" spans="2:8">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B46">
         <f t="shared" si="6"/>
         <v>44</v>
@@ -18165,7 +17605,7 @@
         <v>44:10</v>
       </c>
     </row>
-    <row r="47" spans="2:8">
+    <row r="47" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B47">
         <f t="shared" si="6"/>
         <v>45</v>
@@ -18194,7 +17634,7 @@
         <v>45:10</v>
       </c>
     </row>
-    <row r="48" spans="2:8">
+    <row r="48" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B48">
         <f t="shared" si="6"/>
         <v>46</v>
@@ -18223,7 +17663,7 @@
         <v>46:10</v>
       </c>
     </row>
-    <row r="49" spans="2:8">
+    <row r="49" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B49">
         <f t="shared" si="6"/>
         <v>47</v>
@@ -18252,7 +17692,7 @@
         <v>47:10</v>
       </c>
     </row>
-    <row r="50" spans="2:8">
+    <row r="50" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B50">
         <f t="shared" si="6"/>
         <v>48</v>
@@ -18281,7 +17721,7 @@
         <v>48:10</v>
       </c>
     </row>
-    <row r="51" spans="2:8">
+    <row r="51" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B51">
         <f t="shared" si="6"/>
         <v>49</v>
@@ -18310,7 +17750,7 @@
         <v>49:10</v>
       </c>
     </row>
-    <row r="52" spans="2:8">
+    <row r="52" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B52">
         <f t="shared" si="6"/>
         <v>50</v>
@@ -18339,7 +17779,7 @@
         <v>50:10</v>
       </c>
     </row>
-    <row r="53" spans="2:8">
+    <row r="53" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B53">
         <f t="shared" si="6"/>
         <v>51</v>
@@ -18368,7 +17808,7 @@
         <v>51:10</v>
       </c>
     </row>
-    <row r="54" spans="2:8">
+    <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54">
         <f t="shared" si="6"/>
         <v>52</v>
@@ -18397,7 +17837,7 @@
         <v>52:10</v>
       </c>
     </row>
-    <row r="55" spans="2:8">
+    <row r="55" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B55">
         <f t="shared" si="6"/>
         <v>53</v>
@@ -18426,7 +17866,7 @@
         <v>53:10</v>
       </c>
     </row>
-    <row r="56" spans="2:8">
+    <row r="56" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B56">
         <f t="shared" si="6"/>
         <v>54</v>
@@ -18455,7 +17895,7 @@
         <v>54:10</v>
       </c>
     </row>
-    <row r="57" spans="2:8">
+    <row r="57" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B57">
         <f t="shared" si="6"/>
         <v>55</v>
@@ -18484,7 +17924,7 @@
         <v>55:10</v>
       </c>
     </row>
-    <row r="58" spans="2:8">
+    <row r="58" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B58">
         <f t="shared" si="6"/>
         <v>56</v>
@@ -18513,7 +17953,7 @@
         <v>56:10</v>
       </c>
     </row>
-    <row r="59" spans="2:8">
+    <row r="59" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B59">
         <f t="shared" si="6"/>
         <v>57</v>
@@ -18542,7 +17982,7 @@
         <v>57:10</v>
       </c>
     </row>
-    <row r="60" spans="2:8">
+    <row r="60" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B60">
         <f t="shared" si="6"/>
         <v>58</v>
@@ -18571,7 +18011,7 @@
         <v>58:10</v>
       </c>
     </row>
-    <row r="61" spans="2:8">
+    <row r="61" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B61">
         <f t="shared" si="6"/>
         <v>59</v>
@@ -18600,7 +18040,7 @@
         <v>59:10</v>
       </c>
     </row>
-    <row r="62" spans="2:8">
+    <row r="62" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B62">
         <f t="shared" si="6"/>
         <v>60</v>
@@ -18629,7 +18069,7 @@
         <v>60:10</v>
       </c>
     </row>
-    <row r="63" spans="2:8">
+    <row r="63" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B63">
         <f t="shared" si="6"/>
         <v>61</v>
@@ -18658,7 +18098,7 @@
         <v>61:10</v>
       </c>
     </row>
-    <row r="64" spans="2:8">
+    <row r="64" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B64">
         <f t="shared" si="6"/>
         <v>62</v>
@@ -18687,7 +18127,7 @@
         <v>62:10</v>
       </c>
     </row>
-    <row r="65" spans="2:8">
+    <row r="65" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B65">
         <f t="shared" si="6"/>
         <v>63</v>
@@ -18716,7 +18156,7 @@
         <v>63:10</v>
       </c>
     </row>
-    <row r="66" spans="2:8">
+    <row r="66" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B66">
         <f t="shared" si="6"/>
         <v>64</v>
@@ -18745,7 +18185,7 @@
         <v>64:10</v>
       </c>
     </row>
-    <row r="67" spans="2:8">
+    <row r="67" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B67">
         <f t="shared" si="6"/>
         <v>65</v>
@@ -18774,7 +18214,7 @@
         <v>65:10</v>
       </c>
     </row>
-    <row r="68" spans="2:8">
+    <row r="68" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B68">
         <f t="shared" ref="B68:B94" si="7">B67+1</f>
         <v>66</v>
@@ -18803,7 +18243,7 @@
         <v>66:10</v>
       </c>
     </row>
-    <row r="69" spans="2:8">
+    <row r="69" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B69">
         <f t="shared" si="7"/>
         <v>67</v>
@@ -18832,7 +18272,7 @@
         <v>67:10</v>
       </c>
     </row>
-    <row r="70" spans="2:8">
+    <row r="70" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B70">
         <f t="shared" si="7"/>
         <v>68</v>
@@ -18861,7 +18301,7 @@
         <v>68:10</v>
       </c>
     </row>
-    <row r="71" spans="2:8">
+    <row r="71" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B71">
         <f t="shared" si="7"/>
         <v>69</v>
@@ -18890,7 +18330,7 @@
         <v>69:10</v>
       </c>
     </row>
-    <row r="72" spans="2:8">
+    <row r="72" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B72">
         <f t="shared" si="7"/>
         <v>70</v>
@@ -18919,7 +18359,7 @@
         <v>70:10</v>
       </c>
     </row>
-    <row r="73" spans="2:8">
+    <row r="73" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B73">
         <f t="shared" si="7"/>
         <v>71</v>
@@ -18948,7 +18388,7 @@
         <v>71:10</v>
       </c>
     </row>
-    <row r="74" spans="2:8">
+    <row r="74" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B74">
         <f t="shared" si="7"/>
         <v>72</v>
@@ -18977,7 +18417,7 @@
         <v>72:10</v>
       </c>
     </row>
-    <row r="75" spans="2:8">
+    <row r="75" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B75">
         <f t="shared" si="7"/>
         <v>73</v>
@@ -19006,7 +18446,7 @@
         <v>73:10</v>
       </c>
     </row>
-    <row r="76" spans="2:8">
+    <row r="76" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B76">
         <f t="shared" si="7"/>
         <v>74</v>
@@ -19035,7 +18475,7 @@
         <v>74:10</v>
       </c>
     </row>
-    <row r="77" spans="2:8">
+    <row r="77" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B77">
         <f t="shared" si="7"/>
         <v>75</v>
@@ -19064,7 +18504,7 @@
         <v>75:10</v>
       </c>
     </row>
-    <row r="78" spans="2:8">
+    <row r="78" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B78">
         <f t="shared" si="7"/>
         <v>76</v>
@@ -19093,7 +18533,7 @@
         <v>76:10</v>
       </c>
     </row>
-    <row r="79" spans="2:8">
+    <row r="79" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B79">
         <f t="shared" si="7"/>
         <v>77</v>
@@ -19122,7 +18562,7 @@
         <v>77:10</v>
       </c>
     </row>
-    <row r="80" spans="2:8">
+    <row r="80" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B80">
         <f t="shared" si="7"/>
         <v>78</v>
@@ -19151,7 +18591,7 @@
         <v>78:10</v>
       </c>
     </row>
-    <row r="81" spans="2:8">
+    <row r="81" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B81">
         <f t="shared" si="7"/>
         <v>79</v>
@@ -19180,7 +18620,7 @@
         <v>79:10</v>
       </c>
     </row>
-    <row r="82" spans="2:8">
+    <row r="82" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B82">
         <f t="shared" si="7"/>
         <v>80</v>
@@ -19209,7 +18649,7 @@
         <v>80:10</v>
       </c>
     </row>
-    <row r="83" spans="2:8">
+    <row r="83" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B83">
         <f t="shared" si="7"/>
         <v>81</v>
@@ -19238,7 +18678,7 @@
         <v>81:10</v>
       </c>
     </row>
-    <row r="84" spans="2:8">
+    <row r="84" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B84">
         <f t="shared" si="7"/>
         <v>82</v>
@@ -19267,7 +18707,7 @@
         <v>82:10</v>
       </c>
     </row>
-    <row r="85" spans="2:8">
+    <row r="85" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B85">
         <f t="shared" si="7"/>
         <v>83</v>
@@ -19296,7 +18736,7 @@
         <v>83:10</v>
       </c>
     </row>
-    <row r="86" spans="2:8">
+    <row r="86" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B86">
         <f t="shared" si="7"/>
         <v>84</v>
@@ -19325,7 +18765,7 @@
         <v>84:10</v>
       </c>
     </row>
-    <row r="87" spans="2:8">
+    <row r="87" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B87">
         <f t="shared" si="7"/>
         <v>85</v>
@@ -19354,7 +18794,7 @@
         <v>85:10</v>
       </c>
     </row>
-    <row r="88" spans="2:8">
+    <row r="88" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B88">
         <f t="shared" si="7"/>
         <v>86</v>
@@ -19383,7 +18823,7 @@
         <v>86:10</v>
       </c>
     </row>
-    <row r="89" spans="2:8">
+    <row r="89" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B89">
         <f t="shared" si="7"/>
         <v>87</v>
@@ -19412,7 +18852,7 @@
         <v>87:10</v>
       </c>
     </row>
-    <row r="90" spans="2:8">
+    <row r="90" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B90">
         <f t="shared" si="7"/>
         <v>88</v>
@@ -19441,7 +18881,7 @@
         <v>88:10</v>
       </c>
     </row>
-    <row r="91" spans="2:8">
+    <row r="91" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B91">
         <f t="shared" si="7"/>
         <v>89</v>
@@ -19470,7 +18910,7 @@
         <v>89:10</v>
       </c>
     </row>
-    <row r="92" spans="2:8">
+    <row r="92" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B92">
         <f t="shared" si="7"/>
         <v>90</v>
@@ -19499,7 +18939,7 @@
         <v>90:10</v>
       </c>
     </row>
-    <row r="93" spans="2:8">
+    <row r="93" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B93">
         <f t="shared" si="7"/>
         <v>91</v>
@@ -19528,7 +18968,7 @@
         <v>91:10</v>
       </c>
     </row>
-    <row r="94" spans="2:8">
+    <row r="94" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B94">
         <f t="shared" si="7"/>
         <v>92</v>
@@ -19557,7 +18997,7 @@
         <v>92:10</v>
       </c>
     </row>
-    <row r="95" spans="2:8">
+    <row r="95" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B95">
         <f t="shared" ref="B95:B158" si="13">B94+1</f>
         <v>93</v>
@@ -19586,7 +19026,7 @@
         <v>93:10</v>
       </c>
     </row>
-    <row r="96" spans="2:8">
+    <row r="96" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B96">
         <f t="shared" si="13"/>
         <v>94</v>
@@ -19615,7 +19055,7 @@
         <v>94:10</v>
       </c>
     </row>
-    <row r="97" spans="2:8">
+    <row r="97" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B97">
         <f t="shared" si="13"/>
         <v>95</v>
@@ -19644,7 +19084,7 @@
         <v>95:10</v>
       </c>
     </row>
-    <row r="98" spans="2:8">
+    <row r="98" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B98">
         <f t="shared" si="13"/>
         <v>96</v>
@@ -19673,7 +19113,7 @@
         <v>96:10</v>
       </c>
     </row>
-    <row r="99" spans="2:8">
+    <row r="99" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B99">
         <f t="shared" si="13"/>
         <v>97</v>
@@ -19702,7 +19142,7 @@
         <v>97:10</v>
       </c>
     </row>
-    <row r="100" spans="2:8">
+    <row r="100" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B100">
         <f t="shared" si="13"/>
         <v>98</v>
@@ -19731,7 +19171,7 @@
         <v>98:10</v>
       </c>
     </row>
-    <row r="101" spans="2:8">
+    <row r="101" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B101">
         <f t="shared" si="13"/>
         <v>99</v>
@@ -19760,7 +19200,7 @@
         <v>99:10</v>
       </c>
     </row>
-    <row r="102" spans="2:8">
+    <row r="102" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B102">
         <f t="shared" si="13"/>
         <v>100</v>
@@ -19789,7 +19229,7 @@
         <v>100:10</v>
       </c>
     </row>
-    <row r="103" spans="2:8">
+    <row r="103" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B103">
         <f t="shared" si="13"/>
         <v>101</v>
@@ -19818,7 +19258,7 @@
         <v>101:10</v>
       </c>
     </row>
-    <row r="104" spans="2:8">
+    <row r="104" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B104">
         <f t="shared" si="13"/>
         <v>102</v>
@@ -19847,7 +19287,7 @@
         <v>102:10</v>
       </c>
     </row>
-    <row r="105" spans="2:8">
+    <row r="105" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B105">
         <f t="shared" si="13"/>
         <v>103</v>
@@ -19876,7 +19316,7 @@
         <v>103:10</v>
       </c>
     </row>
-    <row r="106" spans="2:8">
+    <row r="106" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B106">
         <f t="shared" si="13"/>
         <v>104</v>
@@ -19905,7 +19345,7 @@
         <v>104:10</v>
       </c>
     </row>
-    <row r="107" spans="2:8">
+    <row r="107" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B107">
         <f t="shared" si="13"/>
         <v>105</v>
@@ -19934,7 +19374,7 @@
         <v>105:10</v>
       </c>
     </row>
-    <row r="108" spans="2:8">
+    <row r="108" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B108">
         <f t="shared" si="13"/>
         <v>106</v>
@@ -19963,7 +19403,7 @@
         <v>106:10</v>
       </c>
     </row>
-    <row r="109" spans="2:8">
+    <row r="109" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B109">
         <f t="shared" si="13"/>
         <v>107</v>
@@ -19992,7 +19432,7 @@
         <v>107:10</v>
       </c>
     </row>
-    <row r="110" spans="2:8">
+    <row r="110" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B110">
         <f t="shared" si="13"/>
         <v>108</v>
@@ -20021,7 +19461,7 @@
         <v>108:10</v>
       </c>
     </row>
-    <row r="111" spans="2:8">
+    <row r="111" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B111">
         <f t="shared" si="13"/>
         <v>109</v>
@@ -20050,7 +19490,7 @@
         <v>109:10</v>
       </c>
     </row>
-    <row r="112" spans="2:8">
+    <row r="112" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B112">
         <f t="shared" si="13"/>
         <v>110</v>
@@ -20079,7 +19519,7 @@
         <v>110:10</v>
       </c>
     </row>
-    <row r="113" spans="2:8">
+    <row r="113" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B113">
         <f t="shared" si="13"/>
         <v>111</v>
@@ -20108,7 +19548,7 @@
         <v>111:10</v>
       </c>
     </row>
-    <row r="114" spans="2:8">
+    <row r="114" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B114">
         <f t="shared" si="13"/>
         <v>112</v>
@@ -20137,7 +19577,7 @@
         <v>112:10</v>
       </c>
     </row>
-    <row r="115" spans="2:8">
+    <row r="115" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B115">
         <f t="shared" si="13"/>
         <v>113</v>
@@ -20166,7 +19606,7 @@
         <v>113:10</v>
       </c>
     </row>
-    <row r="116" spans="2:8">
+    <row r="116" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B116">
         <f t="shared" si="13"/>
         <v>114</v>
@@ -20195,7 +19635,7 @@
         <v>114:10</v>
       </c>
     </row>
-    <row r="117" spans="2:8">
+    <row r="117" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B117">
         <f t="shared" si="13"/>
         <v>115</v>
@@ -20224,7 +19664,7 @@
         <v>115:10</v>
       </c>
     </row>
-    <row r="118" spans="2:8">
+    <row r="118" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B118">
         <f t="shared" si="13"/>
         <v>116</v>
@@ -20253,7 +19693,7 @@
         <v>116:10</v>
       </c>
     </row>
-    <row r="119" spans="2:8">
+    <row r="119" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B119">
         <f t="shared" si="13"/>
         <v>117</v>
@@ -20282,7 +19722,7 @@
         <v>117:10</v>
       </c>
     </row>
-    <row r="120" spans="2:8">
+    <row r="120" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B120">
         <f t="shared" si="13"/>
         <v>118</v>
@@ -20311,7 +19751,7 @@
         <v>118:10</v>
       </c>
     </row>
-    <row r="121" spans="2:8">
+    <row r="121" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B121">
         <f t="shared" si="13"/>
         <v>119</v>
@@ -20340,7 +19780,7 @@
         <v>119:10</v>
       </c>
     </row>
-    <row r="122" spans="2:8">
+    <row r="122" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B122">
         <f t="shared" si="13"/>
         <v>120</v>
@@ -20369,7 +19809,7 @@
         <v>120:10</v>
       </c>
     </row>
-    <row r="123" spans="2:8">
+    <row r="123" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B123">
         <f t="shared" si="13"/>
         <v>121</v>
@@ -20398,7 +19838,7 @@
         <v>121:10</v>
       </c>
     </row>
-    <row r="124" spans="2:8">
+    <row r="124" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B124">
         <f t="shared" si="13"/>
         <v>122</v>
@@ -20427,7 +19867,7 @@
         <v>122:10</v>
       </c>
     </row>
-    <row r="125" spans="2:8">
+    <row r="125" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B125">
         <f t="shared" si="13"/>
         <v>123</v>
@@ -20456,7 +19896,7 @@
         <v>123:10</v>
       </c>
     </row>
-    <row r="126" spans="2:8">
+    <row r="126" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B126">
         <f t="shared" si="13"/>
         <v>124</v>
@@ -20485,7 +19925,7 @@
         <v>124:10</v>
       </c>
     </row>
-    <row r="127" spans="2:8">
+    <row r="127" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B127">
         <f t="shared" si="13"/>
         <v>125</v>
@@ -20514,7 +19954,7 @@
         <v>125:10</v>
       </c>
     </row>
-    <row r="128" spans="2:8">
+    <row r="128" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B128">
         <f t="shared" si="13"/>
         <v>126</v>
@@ -20543,7 +19983,7 @@
         <v>126:10</v>
       </c>
     </row>
-    <row r="129" spans="2:8">
+    <row r="129" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B129">
         <f t="shared" si="13"/>
         <v>127</v>
@@ -20572,7 +20012,7 @@
         <v>127:10</v>
       </c>
     </row>
-    <row r="130" spans="2:8">
+    <row r="130" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B130">
         <f t="shared" si="13"/>
         <v>128</v>
@@ -20601,7 +20041,7 @@
         <v>128:10</v>
       </c>
     </row>
-    <row r="131" spans="2:8">
+    <row r="131" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B131">
         <f t="shared" si="13"/>
         <v>129</v>
@@ -20630,7 +20070,7 @@
         <v>129:10</v>
       </c>
     </row>
-    <row r="132" spans="2:8">
+    <row r="132" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B132">
         <f t="shared" si="13"/>
         <v>130</v>
@@ -20659,7 +20099,7 @@
         <v>130:10</v>
       </c>
     </row>
-    <row r="133" spans="2:8">
+    <row r="133" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B133">
         <f t="shared" si="13"/>
         <v>131</v>
@@ -20688,7 +20128,7 @@
         <v>131:10</v>
       </c>
     </row>
-    <row r="134" spans="2:8">
+    <row r="134" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B134">
         <f t="shared" si="13"/>
         <v>132</v>
@@ -20717,7 +20157,7 @@
         <v>132:10</v>
       </c>
     </row>
-    <row r="135" spans="2:8">
+    <row r="135" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B135">
         <f t="shared" si="13"/>
         <v>133</v>
@@ -20746,7 +20186,7 @@
         <v>133:10</v>
       </c>
     </row>
-    <row r="136" spans="2:8">
+    <row r="136" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B136">
         <f t="shared" si="13"/>
         <v>134</v>
@@ -20775,7 +20215,7 @@
         <v>134:10</v>
       </c>
     </row>
-    <row r="137" spans="2:8">
+    <row r="137" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B137">
         <f t="shared" si="13"/>
         <v>135</v>
@@ -20804,7 +20244,7 @@
         <v>135:10</v>
       </c>
     </row>
-    <row r="138" spans="2:8">
+    <row r="138" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B138">
         <f t="shared" si="13"/>
         <v>136</v>
@@ -20833,7 +20273,7 @@
         <v>136:10</v>
       </c>
     </row>
-    <row r="139" spans="2:8">
+    <row r="139" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B139">
         <f t="shared" si="13"/>
         <v>137</v>
@@ -20862,7 +20302,7 @@
         <v>137:10</v>
       </c>
     </row>
-    <row r="140" spans="2:8">
+    <row r="140" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B140">
         <f t="shared" si="13"/>
         <v>138</v>
@@ -20891,7 +20331,7 @@
         <v>138:10</v>
       </c>
     </row>
-    <row r="141" spans="2:8">
+    <row r="141" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B141">
         <f t="shared" si="13"/>
         <v>139</v>
@@ -20920,7 +20360,7 @@
         <v>139:10</v>
       </c>
     </row>
-    <row r="142" spans="2:8">
+    <row r="142" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B142">
         <f t="shared" si="13"/>
         <v>140</v>
@@ -20949,7 +20389,7 @@
         <v>140:10</v>
       </c>
     </row>
-    <row r="143" spans="2:8">
+    <row r="143" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B143">
         <f t="shared" si="13"/>
         <v>141</v>
@@ -20978,7 +20418,7 @@
         <v>141:10</v>
       </c>
     </row>
-    <row r="144" spans="2:8">
+    <row r="144" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B144">
         <f t="shared" si="13"/>
         <v>142</v>
@@ -21007,7 +20447,7 @@
         <v>142:10</v>
       </c>
     </row>
-    <row r="145" spans="2:8">
+    <row r="145" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B145">
         <f t="shared" si="13"/>
         <v>143</v>
@@ -21036,7 +20476,7 @@
         <v>143:10</v>
       </c>
     </row>
-    <row r="146" spans="2:8">
+    <row r="146" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B146">
         <f t="shared" si="13"/>
         <v>144</v>
@@ -21065,7 +20505,7 @@
         <v>144:10</v>
       </c>
     </row>
-    <row r="147" spans="2:8">
+    <row r="147" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B147">
         <f t="shared" si="13"/>
         <v>145</v>
@@ -21094,7 +20534,7 @@
         <v>145:10</v>
       </c>
     </row>
-    <row r="148" spans="2:8">
+    <row r="148" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B148">
         <f t="shared" si="13"/>
         <v>146</v>
@@ -21123,7 +20563,7 @@
         <v>146:10</v>
       </c>
     </row>
-    <row r="149" spans="2:8">
+    <row r="149" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B149">
         <f t="shared" si="13"/>
         <v>147</v>
@@ -21152,7 +20592,7 @@
         <v>147:10</v>
       </c>
     </row>
-    <row r="150" spans="2:8">
+    <row r="150" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B150">
         <f t="shared" si="13"/>
         <v>148</v>
@@ -21181,7 +20621,7 @@
         <v>148:10</v>
       </c>
     </row>
-    <row r="151" spans="2:8">
+    <row r="151" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B151">
         <f t="shared" si="13"/>
         <v>149</v>
@@ -21210,7 +20650,7 @@
         <v>149:10</v>
       </c>
     </row>
-    <row r="152" spans="2:8">
+    <row r="152" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B152">
         <f t="shared" si="13"/>
         <v>150</v>
@@ -21239,7 +20679,7 @@
         <v>150:10</v>
       </c>
     </row>
-    <row r="153" spans="2:8">
+    <row r="153" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B153">
         <f t="shared" si="13"/>
         <v>151</v>
@@ -21268,7 +20708,7 @@
         <v>151:10</v>
       </c>
     </row>
-    <row r="154" spans="2:8">
+    <row r="154" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B154">
         <f t="shared" si="13"/>
         <v>152</v>
@@ -21297,7 +20737,7 @@
         <v>152:10</v>
       </c>
     </row>
-    <row r="155" spans="2:8">
+    <row r="155" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B155">
         <f t="shared" si="13"/>
         <v>153</v>
@@ -21326,7 +20766,7 @@
         <v>153:10</v>
       </c>
     </row>
-    <row r="156" spans="2:8">
+    <row r="156" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B156">
         <f t="shared" si="13"/>
         <v>154</v>
@@ -21355,7 +20795,7 @@
         <v>154:10</v>
       </c>
     </row>
-    <row r="157" spans="2:8">
+    <row r="157" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B157">
         <f t="shared" si="13"/>
         <v>155</v>
@@ -21384,7 +20824,7 @@
         <v>155:10</v>
       </c>
     </row>
-    <row r="158" spans="2:8">
+    <row r="158" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B158">
         <f t="shared" si="13"/>
         <v>156</v>
@@ -21413,7 +20853,7 @@
         <v>156:10</v>
       </c>
     </row>
-    <row r="159" spans="2:8">
+    <row r="159" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B159">
         <f t="shared" ref="B159:B162" si="19">B158+1</f>
         <v>157</v>
@@ -21442,7 +20882,7 @@
         <v>157:10</v>
       </c>
     </row>
-    <row r="160" spans="2:8">
+    <row r="160" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B160">
         <f t="shared" si="19"/>
         <v>158</v>
@@ -21471,7 +20911,7 @@
         <v>158:10</v>
       </c>
     </row>
-    <row r="161" spans="2:8">
+    <row r="161" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B161">
         <f t="shared" si="19"/>
         <v>159</v>
@@ -21500,7 +20940,7 @@
         <v>159:10</v>
       </c>
     </row>
-    <row r="162" spans="2:8">
+    <row r="162" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B162">
         <f t="shared" si="19"/>
         <v>160</v>
@@ -21530,7 +20970,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{003A0442-2D4A-426C-A31D-1015A8BF7E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47EF2079-17C6-4BFA-8D0D-8F8BCC0BCAEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_foe_v8" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="235">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -685,6 +685,65 @@
   </si>
   <si>
     <t>1:18_2:18_3:18_4:18_5:18_6:18_7:18_8:18_9:18_10:18_11:18_12:18_13:18_14:18_15:18_16:18_17:18_18:18_19:18_20:18_21:18_22:18_23:18_24:18_25:18_26:18_27:18_28:18_29:18_30:18_31:18_32:18_33:18_34:18_35:18_36:18_37:18_38:18_39:18_40:18_41:18_42:18_43:18_44:18_45:18_46:18_47:18_48:18_49:18_50:18_51:18_52:18_53:18_54:18_55:18_56:18_57:18_58:18_59:18_60:18_61:18_62:18_63:18_64:18_65:18_66:18_67:18_68:18_69:18_70:18_71:18_72:18_73:18_74:18_75:18_76:18_77:18_78:18_79:18_80:18_81:18_82:18_83:18_84:18_85:18_86:18_87:18_88:18_89:18_90:18_91:18_92:18_93:18_94:18_95:18_96:18_97:18_98:18_99:18_100:18_101:18_102:18_103:18_104:18_105:18_106:18_107:18_108:18_109:18_110:18_111:18_112:18_113:18_114:18_115:18_116:18_117:18_118:18_119:18_120:18_121:18_122:18_123:18_124:18_125:18_126:18_127:18_128:18_129:18_130:18_131:18_132:18_133:18_134:18_135:18_136:18_137:18_138:18_139:18_140:18_141:18_142:18_143:18_144:18_145:18_146:18_147:18_148:18_149:18_150:18_151:18_152:18_153:18_154:18_155:18_156:18_157:18_158:18_159:18_160:18</t>
+  </si>
+  <si>
+    <t>7-守卫1</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>7-守卫2</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>7-守卫3</t>
+  </si>
+  <si>
+    <t>7-守卫4</t>
+  </si>
+  <si>
+    <t>7-守卫5</t>
+  </si>
+  <si>
+    <t>7-守卫6</t>
+  </si>
+  <si>
+    <t>7-守卫7</t>
+  </si>
+  <si>
+    <t>7-守卫8</t>
+  </si>
+  <si>
+    <t>7-守卫9</t>
+  </si>
+  <si>
+    <t>7-守卫10</t>
+  </si>
+  <si>
+    <t>7-守卫11</t>
+  </si>
+  <si>
+    <t>7-守卫12</t>
+  </si>
+  <si>
+    <t>7-守卫13</t>
+  </si>
+  <si>
+    <t>7-守卫14</t>
+  </si>
+  <si>
+    <t>7-守卫15</t>
+  </si>
+  <si>
+    <t>7-守卫16</t>
+  </si>
+  <si>
+    <t>7-守卫17</t>
+  </si>
+  <si>
+    <t>7-守卫18</t>
+  </si>
+  <si>
+    <t>7-守卫19</t>
   </si>
 </sst>
 </file>
@@ -1284,7 +1343,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AJ132"/>
+  <dimension ref="A1:AJ151"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.125" style="8" customWidth="1"/>
@@ -14902,6 +14961,1982 @@
         <v>0</v>
       </c>
       <c r="AJ132" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A133" s="19">
+        <v>90000701</v>
+      </c>
+      <c r="B133" s="19">
+        <v>3</v>
+      </c>
+      <c r="C133" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="D133" s="19"/>
+      <c r="E133" s="20"/>
+      <c r="F133" s="19"/>
+      <c r="G133" s="19">
+        <v>1</v>
+      </c>
+      <c r="H133" s="19">
+        <v>2</v>
+      </c>
+      <c r="I133" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="J133" s="19">
+        <v>0</v>
+      </c>
+      <c r="K133" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="L133" s="19">
+        <v>800001011</v>
+      </c>
+      <c r="M133" s="19">
+        <v>1</v>
+      </c>
+      <c r="N133" s="21">
+        <v>1</v>
+      </c>
+      <c r="O133" s="19">
+        <v>1</v>
+      </c>
+      <c r="P133" s="19">
+        <v>8</v>
+      </c>
+      <c r="Q133" s="19">
+        <v>0</v>
+      </c>
+      <c r="R133" s="19">
+        <v>25</v>
+      </c>
+      <c r="S133" s="19">
+        <v>-5000</v>
+      </c>
+      <c r="T133" s="19">
+        <v>1</v>
+      </c>
+      <c r="U133" s="19">
+        <v>0</v>
+      </c>
+      <c r="V133" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="W133" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="X133" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y133" s="23">
+        <v>20010001</v>
+      </c>
+      <c r="Z133" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA133" s="19">
+        <v>1</v>
+      </c>
+      <c r="AB133" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC133" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AD133" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AE133" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF133" s="24">
+        <v>40</v>
+      </c>
+      <c r="AG133" s="24">
+        <v>0</v>
+      </c>
+      <c r="AH133" s="24">
+        <v>0</v>
+      </c>
+      <c r="AI133" s="24">
+        <v>0</v>
+      </c>
+      <c r="AJ133" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A134" s="19">
+        <v>90000702</v>
+      </c>
+      <c r="B134" s="19">
+        <v>3</v>
+      </c>
+      <c r="C134" s="19" t="s">
+        <v>217</v>
+      </c>
+      <c r="D134" s="19"/>
+      <c r="E134" s="20"/>
+      <c r="F134" s="19"/>
+      <c r="G134" s="19">
+        <v>1</v>
+      </c>
+      <c r="H134" s="19">
+        <v>2</v>
+      </c>
+      <c r="I134" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="J134" s="19">
+        <v>0</v>
+      </c>
+      <c r="K134" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="L134" s="19">
+        <v>800001011</v>
+      </c>
+      <c r="M134" s="19">
+        <v>1</v>
+      </c>
+      <c r="N134" s="21">
+        <v>2</v>
+      </c>
+      <c r="O134" s="19">
+        <v>1</v>
+      </c>
+      <c r="P134" s="19">
+        <v>8</v>
+      </c>
+      <c r="Q134" s="19">
+        <v>0</v>
+      </c>
+      <c r="R134" s="19">
+        <v>25</v>
+      </c>
+      <c r="S134" s="19">
+        <v>-5000</v>
+      </c>
+      <c r="T134" s="19">
+        <v>1</v>
+      </c>
+      <c r="U134" s="19">
+        <v>0</v>
+      </c>
+      <c r="V134" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="W134" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="X134" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y134" s="23">
+        <v>20010001</v>
+      </c>
+      <c r="Z134" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA134" s="19">
+        <v>1</v>
+      </c>
+      <c r="AB134" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC134" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AD134" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AE134" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF134" s="24">
+        <v>40</v>
+      </c>
+      <c r="AG134" s="24">
+        <v>0</v>
+      </c>
+      <c r="AH134" s="24">
+        <v>0</v>
+      </c>
+      <c r="AI134" s="24">
+        <v>0</v>
+      </c>
+      <c r="AJ134" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A135" s="19">
+        <v>90000703</v>
+      </c>
+      <c r="B135" s="19">
+        <v>3</v>
+      </c>
+      <c r="C135" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="D135" s="19"/>
+      <c r="E135" s="20"/>
+      <c r="F135" s="19"/>
+      <c r="G135" s="19">
+        <v>1</v>
+      </c>
+      <c r="H135" s="19">
+        <v>2</v>
+      </c>
+      <c r="I135" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="J135" s="19">
+        <v>0</v>
+      </c>
+      <c r="K135" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="L135" s="19">
+        <v>800001011</v>
+      </c>
+      <c r="M135" s="19">
+        <v>1</v>
+      </c>
+      <c r="N135" s="21">
+        <v>3</v>
+      </c>
+      <c r="O135" s="19">
+        <v>1</v>
+      </c>
+      <c r="P135" s="19">
+        <v>8</v>
+      </c>
+      <c r="Q135" s="19">
+        <v>0</v>
+      </c>
+      <c r="R135" s="19">
+        <v>25</v>
+      </c>
+      <c r="S135" s="19">
+        <v>-5000</v>
+      </c>
+      <c r="T135" s="19">
+        <v>1</v>
+      </c>
+      <c r="U135" s="19">
+        <v>0</v>
+      </c>
+      <c r="V135" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="W135" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="X135" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y135" s="23">
+        <v>20010001</v>
+      </c>
+      <c r="Z135" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA135" s="19">
+        <v>1</v>
+      </c>
+      <c r="AB135" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC135" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AD135" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AE135" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF135" s="24">
+        <v>40</v>
+      </c>
+      <c r="AG135" s="24">
+        <v>0</v>
+      </c>
+      <c r="AH135" s="24">
+        <v>0</v>
+      </c>
+      <c r="AI135" s="24">
+        <v>0</v>
+      </c>
+      <c r="AJ135" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A136" s="19">
+        <v>90000704</v>
+      </c>
+      <c r="B136" s="19">
+        <v>3</v>
+      </c>
+      <c r="C136" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="D136" s="19"/>
+      <c r="E136" s="20"/>
+      <c r="F136" s="19"/>
+      <c r="G136" s="19">
+        <v>1</v>
+      </c>
+      <c r="H136" s="19">
+        <v>2</v>
+      </c>
+      <c r="I136" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="J136" s="19">
+        <v>0</v>
+      </c>
+      <c r="K136" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="L136" s="19">
+        <v>800001021</v>
+      </c>
+      <c r="M136" s="19">
+        <v>1</v>
+      </c>
+      <c r="N136" s="21">
+        <v>4</v>
+      </c>
+      <c r="O136" s="19">
+        <v>1</v>
+      </c>
+      <c r="P136" s="19">
+        <v>8</v>
+      </c>
+      <c r="Q136" s="19">
+        <v>0</v>
+      </c>
+      <c r="R136" s="19">
+        <v>25</v>
+      </c>
+      <c r="S136" s="19">
+        <v>-5000</v>
+      </c>
+      <c r="T136" s="19">
+        <v>1</v>
+      </c>
+      <c r="U136" s="19">
+        <v>0</v>
+      </c>
+      <c r="V136" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="W136" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="X136" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y136" s="23">
+        <v>20010001</v>
+      </c>
+      <c r="Z136" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA136" s="19">
+        <v>1</v>
+      </c>
+      <c r="AB136" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC136" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AD136" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AE136" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF136" s="24">
+        <v>40</v>
+      </c>
+      <c r="AG136" s="24">
+        <v>0</v>
+      </c>
+      <c r="AH136" s="24">
+        <v>0</v>
+      </c>
+      <c r="AI136" s="24">
+        <v>0</v>
+      </c>
+      <c r="AJ136" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A137" s="19">
+        <v>90000705</v>
+      </c>
+      <c r="B137" s="19">
+        <v>3</v>
+      </c>
+      <c r="C137" s="19" t="s">
+        <v>220</v>
+      </c>
+      <c r="D137" s="19"/>
+      <c r="E137" s="20"/>
+      <c r="F137" s="19"/>
+      <c r="G137" s="19">
+        <v>1</v>
+      </c>
+      <c r="H137" s="19">
+        <v>2</v>
+      </c>
+      <c r="I137" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="J137" s="19">
+        <v>0</v>
+      </c>
+      <c r="K137" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="L137" s="19">
+        <v>800001021</v>
+      </c>
+      <c r="M137" s="19">
+        <v>1</v>
+      </c>
+      <c r="N137" s="21">
+        <v>5</v>
+      </c>
+      <c r="O137" s="19">
+        <v>1</v>
+      </c>
+      <c r="P137" s="19">
+        <v>8</v>
+      </c>
+      <c r="Q137" s="19">
+        <v>0</v>
+      </c>
+      <c r="R137" s="19">
+        <v>25</v>
+      </c>
+      <c r="S137" s="19">
+        <v>-5000</v>
+      </c>
+      <c r="T137" s="19">
+        <v>1</v>
+      </c>
+      <c r="U137" s="19">
+        <v>0</v>
+      </c>
+      <c r="V137" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="W137" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="X137" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y137" s="23">
+        <v>20010001</v>
+      </c>
+      <c r="Z137" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA137" s="19">
+        <v>1</v>
+      </c>
+      <c r="AB137" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC137" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AD137" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AE137" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF137" s="24">
+        <v>40</v>
+      </c>
+      <c r="AG137" s="24">
+        <v>0</v>
+      </c>
+      <c r="AH137" s="24">
+        <v>0</v>
+      </c>
+      <c r="AI137" s="24">
+        <v>0</v>
+      </c>
+      <c r="AJ137" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A138" s="19">
+        <v>90000706</v>
+      </c>
+      <c r="B138" s="19">
+        <v>3</v>
+      </c>
+      <c r="C138" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="D138" s="19"/>
+      <c r="E138" s="20"/>
+      <c r="F138" s="19"/>
+      <c r="G138" s="19">
+        <v>1</v>
+      </c>
+      <c r="H138" s="19">
+        <v>2</v>
+      </c>
+      <c r="I138" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="J138" s="19">
+        <v>0</v>
+      </c>
+      <c r="K138" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="L138" s="19">
+        <v>800001021</v>
+      </c>
+      <c r="M138" s="19">
+        <v>1</v>
+      </c>
+      <c r="N138" s="21">
+        <v>13</v>
+      </c>
+      <c r="O138" s="19">
+        <v>1</v>
+      </c>
+      <c r="P138" s="19">
+        <v>8</v>
+      </c>
+      <c r="Q138" s="19">
+        <v>0</v>
+      </c>
+      <c r="R138" s="19">
+        <v>25</v>
+      </c>
+      <c r="S138" s="19">
+        <v>-5000</v>
+      </c>
+      <c r="T138" s="19">
+        <v>1</v>
+      </c>
+      <c r="U138" s="19">
+        <v>0</v>
+      </c>
+      <c r="V138" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="W138" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="X138" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y138" s="23">
+        <v>20010001</v>
+      </c>
+      <c r="Z138" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA138" s="19">
+        <v>1</v>
+      </c>
+      <c r="AB138" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC138" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AD138" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AE138" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF138" s="24">
+        <v>40</v>
+      </c>
+      <c r="AG138" s="24">
+        <v>0</v>
+      </c>
+      <c r="AH138" s="24">
+        <v>0</v>
+      </c>
+      <c r="AI138" s="24">
+        <v>0</v>
+      </c>
+      <c r="AJ138" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A139" s="19">
+        <v>90000707</v>
+      </c>
+      <c r="B139" s="19">
+        <v>3</v>
+      </c>
+      <c r="C139" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="D139" s="19"/>
+      <c r="E139" s="20"/>
+      <c r="F139" s="19"/>
+      <c r="G139" s="19">
+        <v>1</v>
+      </c>
+      <c r="H139" s="19">
+        <v>2</v>
+      </c>
+      <c r="I139" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="J139" s="19">
+        <v>0</v>
+      </c>
+      <c r="K139" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="L139" s="19">
+        <v>800001021</v>
+      </c>
+      <c r="M139" s="19">
+        <v>1</v>
+      </c>
+      <c r="N139" s="21">
+        <v>15</v>
+      </c>
+      <c r="O139" s="19">
+        <v>1</v>
+      </c>
+      <c r="P139" s="19">
+        <v>8</v>
+      </c>
+      <c r="Q139" s="19">
+        <v>0</v>
+      </c>
+      <c r="R139" s="19">
+        <v>25</v>
+      </c>
+      <c r="S139" s="19">
+        <v>-5000</v>
+      </c>
+      <c r="T139" s="19">
+        <v>1</v>
+      </c>
+      <c r="U139" s="19">
+        <v>0</v>
+      </c>
+      <c r="V139" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="W139" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="X139" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y139" s="23">
+        <v>20010001</v>
+      </c>
+      <c r="Z139" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA139" s="19">
+        <v>1</v>
+      </c>
+      <c r="AB139" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC139" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AD139" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AE139" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF139" s="24">
+        <v>40</v>
+      </c>
+      <c r="AG139" s="24">
+        <v>0</v>
+      </c>
+      <c r="AH139" s="24">
+        <v>0</v>
+      </c>
+      <c r="AI139" s="24">
+        <v>0</v>
+      </c>
+      <c r="AJ139" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A140" s="19">
+        <v>90000708</v>
+      </c>
+      <c r="B140" s="19">
+        <v>3</v>
+      </c>
+      <c r="C140" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="D140" s="19"/>
+      <c r="E140" s="20"/>
+      <c r="F140" s="19"/>
+      <c r="G140" s="19">
+        <v>1</v>
+      </c>
+      <c r="H140" s="19">
+        <v>2</v>
+      </c>
+      <c r="I140" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="J140" s="19">
+        <v>0</v>
+      </c>
+      <c r="K140" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="L140" s="19">
+        <v>800011011</v>
+      </c>
+      <c r="M140" s="19">
+        <v>1</v>
+      </c>
+      <c r="N140" s="21">
+        <v>35</v>
+      </c>
+      <c r="O140" s="19">
+        <v>1</v>
+      </c>
+      <c r="P140" s="19">
+        <v>8</v>
+      </c>
+      <c r="Q140" s="19">
+        <v>0</v>
+      </c>
+      <c r="R140" s="19">
+        <v>25</v>
+      </c>
+      <c r="S140" s="19">
+        <v>-5000</v>
+      </c>
+      <c r="T140" s="19">
+        <v>1</v>
+      </c>
+      <c r="U140" s="19">
+        <v>0</v>
+      </c>
+      <c r="V140" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="W140" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="X140" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y140" s="23">
+        <v>20010001</v>
+      </c>
+      <c r="Z140" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA140" s="19">
+        <v>1</v>
+      </c>
+      <c r="AB140" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC140" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AD140" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AE140" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF140" s="24">
+        <v>40</v>
+      </c>
+      <c r="AG140" s="24">
+        <v>0</v>
+      </c>
+      <c r="AH140" s="24">
+        <v>0</v>
+      </c>
+      <c r="AI140" s="24">
+        <v>0</v>
+      </c>
+      <c r="AJ140" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A141" s="19">
+        <v>90000709</v>
+      </c>
+      <c r="B141" s="19">
+        <v>3</v>
+      </c>
+      <c r="C141" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="D141" s="19"/>
+      <c r="E141" s="20"/>
+      <c r="F141" s="19"/>
+      <c r="G141" s="19">
+        <v>1</v>
+      </c>
+      <c r="H141" s="19">
+        <v>2</v>
+      </c>
+      <c r="I141" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="J141" s="19">
+        <v>0</v>
+      </c>
+      <c r="K141" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="L141" s="19">
+        <v>800011011</v>
+      </c>
+      <c r="M141" s="19">
+        <v>1</v>
+      </c>
+      <c r="N141" s="21">
+        <v>40</v>
+      </c>
+      <c r="O141" s="19">
+        <v>1</v>
+      </c>
+      <c r="P141" s="19">
+        <v>8</v>
+      </c>
+      <c r="Q141" s="19">
+        <v>0</v>
+      </c>
+      <c r="R141" s="19">
+        <v>25</v>
+      </c>
+      <c r="S141" s="19">
+        <v>-5000</v>
+      </c>
+      <c r="T141" s="19">
+        <v>1</v>
+      </c>
+      <c r="U141" s="19">
+        <v>0</v>
+      </c>
+      <c r="V141" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="W141" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="X141" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y141" s="23">
+        <v>20010001</v>
+      </c>
+      <c r="Z141" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA141" s="19">
+        <v>1</v>
+      </c>
+      <c r="AB141" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC141" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AD141" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AE141" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF141" s="24">
+        <v>40</v>
+      </c>
+      <c r="AG141" s="24">
+        <v>0</v>
+      </c>
+      <c r="AH141" s="24">
+        <v>0</v>
+      </c>
+      <c r="AI141" s="24">
+        <v>0</v>
+      </c>
+      <c r="AJ141" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A142" s="19">
+        <v>90000710</v>
+      </c>
+      <c r="B142" s="19">
+        <v>3</v>
+      </c>
+      <c r="C142" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="D142" s="19"/>
+      <c r="E142" s="20"/>
+      <c r="F142" s="19"/>
+      <c r="G142" s="19">
+        <v>1</v>
+      </c>
+      <c r="H142" s="19">
+        <v>2</v>
+      </c>
+      <c r="I142" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="J142" s="19">
+        <v>0</v>
+      </c>
+      <c r="K142" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="L142" s="19">
+        <v>800011011</v>
+      </c>
+      <c r="M142" s="19">
+        <v>1</v>
+      </c>
+      <c r="N142" s="21">
+        <v>90</v>
+      </c>
+      <c r="O142" s="19">
+        <v>1</v>
+      </c>
+      <c r="P142" s="19">
+        <v>8</v>
+      </c>
+      <c r="Q142" s="19">
+        <v>0</v>
+      </c>
+      <c r="R142" s="19">
+        <v>25</v>
+      </c>
+      <c r="S142" s="19">
+        <v>-5000</v>
+      </c>
+      <c r="T142" s="19">
+        <v>1</v>
+      </c>
+      <c r="U142" s="19">
+        <v>0</v>
+      </c>
+      <c r="V142" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="W142" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="X142" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y142" s="23">
+        <v>20010001</v>
+      </c>
+      <c r="Z142" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA142" s="19">
+        <v>1</v>
+      </c>
+      <c r="AB142" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC142" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AD142" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AE142" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF142" s="24">
+        <v>40</v>
+      </c>
+      <c r="AG142" s="24">
+        <v>0</v>
+      </c>
+      <c r="AH142" s="24">
+        <v>0</v>
+      </c>
+      <c r="AI142" s="24">
+        <v>0</v>
+      </c>
+      <c r="AJ142" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A143" s="19">
+        <v>90000711</v>
+      </c>
+      <c r="B143" s="19">
+        <v>3</v>
+      </c>
+      <c r="C143" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="D143" s="19"/>
+      <c r="E143" s="20"/>
+      <c r="F143" s="19"/>
+      <c r="G143" s="19">
+        <v>1</v>
+      </c>
+      <c r="H143" s="19">
+        <v>2</v>
+      </c>
+      <c r="I143" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="J143" s="19">
+        <v>0</v>
+      </c>
+      <c r="K143" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="L143" s="19">
+        <v>800011011</v>
+      </c>
+      <c r="M143" s="19">
+        <v>1</v>
+      </c>
+      <c r="N143" s="21">
+        <v>100</v>
+      </c>
+      <c r="O143" s="19">
+        <v>1</v>
+      </c>
+      <c r="P143" s="19">
+        <v>8</v>
+      </c>
+      <c r="Q143" s="19">
+        <v>0</v>
+      </c>
+      <c r="R143" s="19">
+        <v>25</v>
+      </c>
+      <c r="S143" s="19">
+        <v>-5000</v>
+      </c>
+      <c r="T143" s="19">
+        <v>1</v>
+      </c>
+      <c r="U143" s="19">
+        <v>0</v>
+      </c>
+      <c r="V143" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="W143" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="X143" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y143" s="23">
+        <v>20010001</v>
+      </c>
+      <c r="Z143" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA143" s="19">
+        <v>1</v>
+      </c>
+      <c r="AB143" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC143" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AD143" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AE143" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF143" s="24">
+        <v>40</v>
+      </c>
+      <c r="AG143" s="24">
+        <v>0</v>
+      </c>
+      <c r="AH143" s="24">
+        <v>0</v>
+      </c>
+      <c r="AI143" s="24">
+        <v>0</v>
+      </c>
+      <c r="AJ143" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A144" s="19">
+        <v>90000712</v>
+      </c>
+      <c r="B144" s="19">
+        <v>3</v>
+      </c>
+      <c r="C144" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D144" s="19"/>
+      <c r="E144" s="20"/>
+      <c r="F144" s="19"/>
+      <c r="G144" s="19">
+        <v>1</v>
+      </c>
+      <c r="H144" s="19">
+        <v>2</v>
+      </c>
+      <c r="I144" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="J144" s="19">
+        <v>0</v>
+      </c>
+      <c r="K144" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="L144" s="19">
+        <v>800011021</v>
+      </c>
+      <c r="M144" s="19">
+        <v>1</v>
+      </c>
+      <c r="N144" s="21">
+        <v>240</v>
+      </c>
+      <c r="O144" s="19">
+        <v>1</v>
+      </c>
+      <c r="P144" s="19">
+        <v>8</v>
+      </c>
+      <c r="Q144" s="19">
+        <v>0</v>
+      </c>
+      <c r="R144" s="19">
+        <v>25</v>
+      </c>
+      <c r="S144" s="19">
+        <v>-5000</v>
+      </c>
+      <c r="T144" s="19">
+        <v>1</v>
+      </c>
+      <c r="U144" s="19">
+        <v>0</v>
+      </c>
+      <c r="V144" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="W144" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="X144" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y144" s="23">
+        <v>20010001</v>
+      </c>
+      <c r="Z144" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA144" s="19">
+        <v>1</v>
+      </c>
+      <c r="AB144" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC144" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AD144" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AE144" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF144" s="24">
+        <v>40</v>
+      </c>
+      <c r="AG144" s="24">
+        <v>0</v>
+      </c>
+      <c r="AH144" s="24">
+        <v>0</v>
+      </c>
+      <c r="AI144" s="24">
+        <v>0</v>
+      </c>
+      <c r="AJ144" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A145" s="19">
+        <v>90000713</v>
+      </c>
+      <c r="B145" s="19">
+        <v>3</v>
+      </c>
+      <c r="C145" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="D145" s="19"/>
+      <c r="E145" s="20"/>
+      <c r="F145" s="19"/>
+      <c r="G145" s="19">
+        <v>1</v>
+      </c>
+      <c r="H145" s="19">
+        <v>2</v>
+      </c>
+      <c r="I145" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="J145" s="19">
+        <v>0</v>
+      </c>
+      <c r="K145" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="L145" s="19">
+        <v>800011021</v>
+      </c>
+      <c r="M145" s="19">
+        <v>1</v>
+      </c>
+      <c r="N145" s="21">
+        <v>300</v>
+      </c>
+      <c r="O145" s="19">
+        <v>1</v>
+      </c>
+      <c r="P145" s="19">
+        <v>8</v>
+      </c>
+      <c r="Q145" s="19">
+        <v>0</v>
+      </c>
+      <c r="R145" s="19">
+        <v>25</v>
+      </c>
+      <c r="S145" s="19">
+        <v>-5000</v>
+      </c>
+      <c r="T145" s="19">
+        <v>1</v>
+      </c>
+      <c r="U145" s="19">
+        <v>0</v>
+      </c>
+      <c r="V145" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="W145" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="X145" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y145" s="23">
+        <v>20010001</v>
+      </c>
+      <c r="Z145" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA145" s="19">
+        <v>1</v>
+      </c>
+      <c r="AB145" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC145" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AD145" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AE145" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF145" s="24">
+        <v>40</v>
+      </c>
+      <c r="AG145" s="24">
+        <v>0</v>
+      </c>
+      <c r="AH145" s="24">
+        <v>0</v>
+      </c>
+      <c r="AI145" s="24">
+        <v>0</v>
+      </c>
+      <c r="AJ145" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A146" s="19">
+        <v>90000714</v>
+      </c>
+      <c r="B146" s="19">
+        <v>3</v>
+      </c>
+      <c r="C146" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="D146" s="19"/>
+      <c r="E146" s="20"/>
+      <c r="F146" s="19"/>
+      <c r="G146" s="19">
+        <v>1</v>
+      </c>
+      <c r="H146" s="19">
+        <v>2</v>
+      </c>
+      <c r="I146" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="J146" s="19">
+        <v>0</v>
+      </c>
+      <c r="K146" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="L146" s="19">
+        <v>800011021</v>
+      </c>
+      <c r="M146" s="19">
+        <v>1</v>
+      </c>
+      <c r="N146" s="21">
+        <v>700</v>
+      </c>
+      <c r="O146" s="19">
+        <v>1</v>
+      </c>
+      <c r="P146" s="19">
+        <v>8</v>
+      </c>
+      <c r="Q146" s="19">
+        <v>0</v>
+      </c>
+      <c r="R146" s="19">
+        <v>25</v>
+      </c>
+      <c r="S146" s="19">
+        <v>-5000</v>
+      </c>
+      <c r="T146" s="19">
+        <v>1</v>
+      </c>
+      <c r="U146" s="19">
+        <v>0</v>
+      </c>
+      <c r="V146" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="W146" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="X146" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y146" s="23">
+        <v>20010001</v>
+      </c>
+      <c r="Z146" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA146" s="19">
+        <v>1</v>
+      </c>
+      <c r="AB146" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC146" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AD146" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AE146" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF146" s="24">
+        <v>40</v>
+      </c>
+      <c r="AG146" s="24">
+        <v>0</v>
+      </c>
+      <c r="AH146" s="24">
+        <v>0</v>
+      </c>
+      <c r="AI146" s="24">
+        <v>0</v>
+      </c>
+      <c r="AJ146" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A147" s="19">
+        <v>90000715</v>
+      </c>
+      <c r="B147" s="19">
+        <v>3</v>
+      </c>
+      <c r="C147" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="D147" s="19"/>
+      <c r="E147" s="20"/>
+      <c r="F147" s="19"/>
+      <c r="G147" s="19">
+        <v>1</v>
+      </c>
+      <c r="H147" s="19">
+        <v>2</v>
+      </c>
+      <c r="I147" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="J147" s="19">
+        <v>0</v>
+      </c>
+      <c r="K147" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="L147" s="19">
+        <v>800011021</v>
+      </c>
+      <c r="M147" s="19">
+        <v>1</v>
+      </c>
+      <c r="N147" s="21">
+        <v>800</v>
+      </c>
+      <c r="O147" s="19">
+        <v>1</v>
+      </c>
+      <c r="P147" s="19">
+        <v>8</v>
+      </c>
+      <c r="Q147" s="19">
+        <v>0</v>
+      </c>
+      <c r="R147" s="19">
+        <v>25</v>
+      </c>
+      <c r="S147" s="19">
+        <v>-5000</v>
+      </c>
+      <c r="T147" s="19">
+        <v>1</v>
+      </c>
+      <c r="U147" s="19">
+        <v>0</v>
+      </c>
+      <c r="V147" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="W147" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="X147" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y147" s="23">
+        <v>20010001</v>
+      </c>
+      <c r="Z147" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA147" s="19">
+        <v>1</v>
+      </c>
+      <c r="AB147" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC147" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AD147" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AE147" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF147" s="24">
+        <v>40</v>
+      </c>
+      <c r="AG147" s="24">
+        <v>0</v>
+      </c>
+      <c r="AH147" s="24">
+        <v>0</v>
+      </c>
+      <c r="AI147" s="24">
+        <v>0</v>
+      </c>
+      <c r="AJ147" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A148" s="19">
+        <v>90000716</v>
+      </c>
+      <c r="B148" s="19">
+        <v>3</v>
+      </c>
+      <c r="C148" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="D148" s="19"/>
+      <c r="E148" s="20"/>
+      <c r="F148" s="19"/>
+      <c r="G148" s="19">
+        <v>1</v>
+      </c>
+      <c r="H148" s="19">
+        <v>2</v>
+      </c>
+      <c r="I148" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="J148" s="19">
+        <v>0</v>
+      </c>
+      <c r="K148" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="L148" s="19">
+        <v>800011021</v>
+      </c>
+      <c r="M148" s="19">
+        <v>1</v>
+      </c>
+      <c r="N148" s="21">
+        <v>1500</v>
+      </c>
+      <c r="O148" s="19">
+        <v>1</v>
+      </c>
+      <c r="P148" s="19">
+        <v>8</v>
+      </c>
+      <c r="Q148" s="19">
+        <v>0</v>
+      </c>
+      <c r="R148" s="19">
+        <v>25</v>
+      </c>
+      <c r="S148" s="19">
+        <v>-5000</v>
+      </c>
+      <c r="T148" s="19">
+        <v>1</v>
+      </c>
+      <c r="U148" s="19">
+        <v>0</v>
+      </c>
+      <c r="V148" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="W148" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="X148" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y148" s="23">
+        <v>20010001</v>
+      </c>
+      <c r="Z148" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA148" s="19">
+        <v>1</v>
+      </c>
+      <c r="AB148" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC148" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AD148" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AE148" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF148" s="24">
+        <v>40</v>
+      </c>
+      <c r="AG148" s="24">
+        <v>0</v>
+      </c>
+      <c r="AH148" s="24">
+        <v>0</v>
+      </c>
+      <c r="AI148" s="24">
+        <v>0</v>
+      </c>
+      <c r="AJ148" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A149" s="19">
+        <v>90000717</v>
+      </c>
+      <c r="B149" s="19">
+        <v>3</v>
+      </c>
+      <c r="C149" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="D149" s="19"/>
+      <c r="E149" s="20"/>
+      <c r="F149" s="19"/>
+      <c r="G149" s="19">
+        <v>1</v>
+      </c>
+      <c r="H149" s="19">
+        <v>2</v>
+      </c>
+      <c r="I149" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="J149" s="19">
+        <v>0</v>
+      </c>
+      <c r="K149" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="L149" s="19">
+        <v>800011021</v>
+      </c>
+      <c r="M149" s="19">
+        <v>1</v>
+      </c>
+      <c r="N149" s="21">
+        <v>3000</v>
+      </c>
+      <c r="O149" s="19">
+        <v>1</v>
+      </c>
+      <c r="P149" s="19">
+        <v>8</v>
+      </c>
+      <c r="Q149" s="19">
+        <v>0</v>
+      </c>
+      <c r="R149" s="19">
+        <v>25</v>
+      </c>
+      <c r="S149" s="19">
+        <v>-5000</v>
+      </c>
+      <c r="T149" s="19">
+        <v>1</v>
+      </c>
+      <c r="U149" s="19">
+        <v>0</v>
+      </c>
+      <c r="V149" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="W149" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="X149" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y149" s="23">
+        <v>20010001</v>
+      </c>
+      <c r="Z149" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA149" s="19">
+        <v>1</v>
+      </c>
+      <c r="AB149" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC149" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AD149" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AE149" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF149" s="24">
+        <v>40</v>
+      </c>
+      <c r="AG149" s="24">
+        <v>0</v>
+      </c>
+      <c r="AH149" s="24">
+        <v>0</v>
+      </c>
+      <c r="AI149" s="24">
+        <v>0</v>
+      </c>
+      <c r="AJ149" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A150" s="19">
+        <v>90000718</v>
+      </c>
+      <c r="B150" s="19">
+        <v>3</v>
+      </c>
+      <c r="C150" s="19" t="s">
+        <v>233</v>
+      </c>
+      <c r="D150" s="19"/>
+      <c r="E150" s="20"/>
+      <c r="F150" s="19"/>
+      <c r="G150" s="19">
+        <v>1</v>
+      </c>
+      <c r="H150" s="19">
+        <v>2</v>
+      </c>
+      <c r="I150" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="J150" s="19">
+        <v>0</v>
+      </c>
+      <c r="K150" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="L150" s="19">
+        <v>800011021</v>
+      </c>
+      <c r="M150" s="19">
+        <v>1</v>
+      </c>
+      <c r="N150" s="21">
+        <v>4800</v>
+      </c>
+      <c r="O150" s="19">
+        <v>1</v>
+      </c>
+      <c r="P150" s="19">
+        <v>8</v>
+      </c>
+      <c r="Q150" s="19">
+        <v>0</v>
+      </c>
+      <c r="R150" s="19">
+        <v>25</v>
+      </c>
+      <c r="S150" s="19">
+        <v>-5000</v>
+      </c>
+      <c r="T150" s="19">
+        <v>1</v>
+      </c>
+      <c r="U150" s="19">
+        <v>0</v>
+      </c>
+      <c r="V150" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="W150" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="X150" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y150" s="23">
+        <v>20010001</v>
+      </c>
+      <c r="Z150" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA150" s="19">
+        <v>1</v>
+      </c>
+      <c r="AB150" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC150" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AD150" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AE150" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF150" s="24">
+        <v>40</v>
+      </c>
+      <c r="AG150" s="24">
+        <v>0</v>
+      </c>
+      <c r="AH150" s="24">
+        <v>0</v>
+      </c>
+      <c r="AI150" s="24">
+        <v>0</v>
+      </c>
+      <c r="AJ150" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A151" s="19">
+        <v>90000719</v>
+      </c>
+      <c r="B151" s="19">
+        <v>3</v>
+      </c>
+      <c r="C151" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="D151" s="19"/>
+      <c r="E151" s="20"/>
+      <c r="F151" s="19"/>
+      <c r="G151" s="19">
+        <v>1</v>
+      </c>
+      <c r="H151" s="19">
+        <v>2</v>
+      </c>
+      <c r="I151" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="J151" s="19">
+        <v>0</v>
+      </c>
+      <c r="K151" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="L151" s="19">
+        <v>800011021</v>
+      </c>
+      <c r="M151" s="19">
+        <v>1</v>
+      </c>
+      <c r="N151" s="21">
+        <v>8000</v>
+      </c>
+      <c r="O151" s="19">
+        <v>1</v>
+      </c>
+      <c r="P151" s="19">
+        <v>8</v>
+      </c>
+      <c r="Q151" s="19">
+        <v>0</v>
+      </c>
+      <c r="R151" s="19">
+        <v>25</v>
+      </c>
+      <c r="S151" s="19">
+        <v>-5000</v>
+      </c>
+      <c r="T151" s="19">
+        <v>1</v>
+      </c>
+      <c r="U151" s="19">
+        <v>0</v>
+      </c>
+      <c r="V151" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="W151" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="X151" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y151" s="23">
+        <v>20010001</v>
+      </c>
+      <c r="Z151" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA151" s="19">
+        <v>1</v>
+      </c>
+      <c r="AB151" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC151" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AD151" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AE151" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF151" s="24">
+        <v>40</v>
+      </c>
+      <c r="AG151" s="24">
+        <v>0</v>
+      </c>
+      <c r="AH151" s="24">
+        <v>0</v>
+      </c>
+      <c r="AI151" s="24">
+        <v>0</v>
+      </c>
+      <c r="AJ151" s="24">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47EF2079-17C6-4BFA-8D0D-8F8BCC0BCAEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DB7F066-DF0F-4B0C-A99D-407326EF3AA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_foe_v8" sheetId="1" r:id="rId1"/>
@@ -8995,7 +8995,7 @@
         <v>0</v>
       </c>
       <c r="P75" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Q75" s="3">
         <v>1</v>
@@ -10540,7 +10540,7 @@
         <v>0</v>
       </c>
       <c r="P90" s="3">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Q90" s="3">
         <v>2</v>
@@ -12095,7 +12095,7 @@
         <v>0</v>
       </c>
       <c r="P105" s="3">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="Q105" s="3">
         <v>2</v>
@@ -13133,13 +13133,13 @@
         <v>0</v>
       </c>
       <c r="P115" s="3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Q115" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R115" s="15">
-        <v>4356</v>
+        <v>3740</v>
       </c>
       <c r="S115" s="3">
         <v>-5500</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -750,7 +750,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -803,13 +803,6 @@
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1339,13 +1332,16 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1354,118 +1350,115 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
@@ -1474,7 +1467,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -1528,16 +1521,16 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="16" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="51"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="51"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -22485,7 +22478,7 @@
         <v>0</v>
       </c>
       <c r="P201" s="3">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="Q201" s="3">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -22065,13 +22065,13 @@
         <v>0</v>
       </c>
       <c r="P197" s="3">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Q197" s="3">
         <v>1</v>
       </c>
       <c r="R197" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="S197" s="3">
         <v>-6500</v>
@@ -22168,13 +22168,13 @@
         <v>0</v>
       </c>
       <c r="P198" s="3">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="Q198" s="3">
         <v>4</v>
       </c>
       <c r="R198" s="3">
-        <v>56</v>
+        <v>73.24</v>
       </c>
       <c r="S198" s="3">
         <v>-4750</v>
@@ -22478,13 +22478,13 @@
         <v>0</v>
       </c>
       <c r="P201" s="3">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="Q201" s="3">
         <v>1</v>
       </c>
       <c r="R201" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="S201" s="3">
         <v>-6500</v>
@@ -23309,13 +23309,13 @@
         <v>0</v>
       </c>
       <c r="P209" s="3">
-        <v>18</v>
+        <v>120</v>
       </c>
       <c r="Q209" s="3">
         <v>6</v>
       </c>
       <c r="R209" s="15">
-        <v>227</v>
+        <v>308</v>
       </c>
       <c r="S209" s="3">
         <v>-1600</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -22174,7 +22174,7 @@
         <v>4</v>
       </c>
       <c r="R198" s="3">
-        <v>73.24</v>
+        <v>73</v>
       </c>
       <c r="S198" s="3">
         <v>-4750</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -22071,7 +22071,7 @@
         <v>1</v>
       </c>
       <c r="R197" s="3">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="S197" s="3">
         <v>-6500</v>
@@ -22168,13 +22168,13 @@
         <v>0</v>
       </c>
       <c r="P198" s="3">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="Q198" s="3">
         <v>4</v>
       </c>
       <c r="R198" s="3">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="S198" s="3">
         <v>-4750</v>
@@ -22375,13 +22375,13 @@
         <v>0</v>
       </c>
       <c r="P200" s="3">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="Q200" s="3">
         <v>1</v>
       </c>
       <c r="R200" s="3">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="S200" s="3">
         <v>-6500</v>
@@ -22484,7 +22484,7 @@
         <v>1</v>
       </c>
       <c r="R201" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="S201" s="3">
         <v>-6500</v>
@@ -23309,13 +23309,13 @@
         <v>0</v>
       </c>
       <c r="P209" s="3">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="Q209" s="3">
         <v>6</v>
       </c>
       <c r="R209" s="15">
-        <v>308</v>
+        <v>247</v>
       </c>
       <c r="S209" s="3">
         <v>-1600</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6D45741-951D-4A80-A926-DB8856DAFE92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06FE205B-6C39-48F7-B61D-278556BDD119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_foe_v8" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2214" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2235" uniqueCount="242">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -743,6 +743,33 @@
   <si>
     <t>装备分数</t>
   </si>
+  <si>
+    <t>2-守卫2</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>1-守卫1</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>1-守卫2</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>骷髅1</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>骷髅2</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>骷髅3</t>
+  </si>
+  <si>
+    <t>吸血鬼3</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1341,7 +1368,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AJ301"/>
+  <dimension ref="A1:AJ304"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.125" style="8" customWidth="1"/>
@@ -28525,7 +28552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="3">
         <v>303115</v>
       </c>
@@ -28630,13 +28657,13 @@
     </row>
     <row r="266" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A266" s="19">
-        <v>90000201</v>
+        <v>90000101</v>
       </c>
       <c r="B266" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C266" s="19" t="s">
-        <v>162</v>
+        <v>236</v>
       </c>
       <c r="D266" s="19"/>
       <c r="E266" s="20"/>
@@ -28654,7 +28681,7 @@
         <v>0</v>
       </c>
       <c r="K266" s="19" t="s">
-        <v>109</v>
+        <v>238</v>
       </c>
       <c r="L266" s="19">
         <v>800001011</v>
@@ -28734,13 +28761,13 @@
     </row>
     <row r="267" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A267" s="19">
-        <v>90000301</v>
+        <v>90000102</v>
       </c>
       <c r="B267" s="19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C267" s="19" t="s">
-        <v>163</v>
+        <v>237</v>
       </c>
       <c r="D267" s="19"/>
       <c r="E267" s="20"/>
@@ -28758,16 +28785,16 @@
         <v>0</v>
       </c>
       <c r="K267" s="19" t="s">
-        <v>109</v>
+        <v>239</v>
       </c>
       <c r="L267" s="19">
-        <v>800001011</v>
+        <v>800001021</v>
       </c>
       <c r="M267" s="19">
         <v>1</v>
       </c>
       <c r="N267" s="21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O267" s="19">
         <v>1</v>
@@ -28838,13 +28865,13 @@
     </row>
     <row r="268" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A268" s="19">
-        <v>90000302</v>
+        <v>90000201</v>
       </c>
       <c r="B268" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C268" s="19" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D268" s="19"/>
       <c r="E268" s="20"/>
@@ -28862,7 +28889,7 @@
         <v>0</v>
       </c>
       <c r="K268" s="19" t="s">
-        <v>109</v>
+        <v>238</v>
       </c>
       <c r="L268" s="19">
         <v>800001011</v>
@@ -28871,7 +28898,7 @@
         <v>1</v>
       </c>
       <c r="N268" s="21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O268" s="19">
         <v>1</v>
@@ -28942,13 +28969,13 @@
     </row>
     <row r="269" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A269" s="19">
-        <v>90000401</v>
+        <v>90000202</v>
       </c>
       <c r="B269" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C269" s="19" t="s">
-        <v>165</v>
+        <v>235</v>
       </c>
       <c r="D269" s="19"/>
       <c r="E269" s="20"/>
@@ -28966,16 +28993,16 @@
         <v>0</v>
       </c>
       <c r="K269" s="19" t="s">
-        <v>109</v>
+        <v>239</v>
       </c>
       <c r="L269" s="19">
-        <v>800001011</v>
+        <v>800001021</v>
       </c>
       <c r="M269" s="19">
         <v>1</v>
       </c>
       <c r="N269" s="21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O269" s="19">
         <v>1</v>
@@ -29046,13 +29073,13 @@
     </row>
     <row r="270" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A270" s="19">
-        <v>90000402</v>
+        <v>90000301</v>
       </c>
       <c r="B270" s="19">
         <v>3</v>
       </c>
       <c r="C270" s="19" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D270" s="19"/>
       <c r="E270" s="20"/>
@@ -29070,7 +29097,7 @@
         <v>0</v>
       </c>
       <c r="K270" s="19" t="s">
-        <v>109</v>
+        <v>238</v>
       </c>
       <c r="L270" s="19">
         <v>800001011</v>
@@ -29079,7 +29106,7 @@
         <v>1</v>
       </c>
       <c r="N270" s="21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O270" s="19">
         <v>1</v>
@@ -29150,13 +29177,13 @@
     </row>
     <row r="271" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A271" s="19">
-        <v>90000501</v>
+        <v>90000302</v>
       </c>
       <c r="B271" s="19">
         <v>3</v>
       </c>
       <c r="C271" s="19" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D271" s="19"/>
       <c r="E271" s="20"/>
@@ -29174,16 +29201,16 @@
         <v>0</v>
       </c>
       <c r="K271" s="19" t="s">
-        <v>109</v>
+        <v>239</v>
       </c>
       <c r="L271" s="19">
-        <v>800001011</v>
+        <v>800001021</v>
       </c>
       <c r="M271" s="19">
         <v>1</v>
       </c>
       <c r="N271" s="21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O271" s="19">
         <v>1</v>
@@ -29254,13 +29281,13 @@
     </row>
     <row r="272" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A272" s="19">
-        <v>90000502</v>
+        <v>90000401</v>
       </c>
       <c r="B272" s="19">
         <v>3</v>
       </c>
       <c r="C272" s="19" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D272" s="19"/>
       <c r="E272" s="20"/>
@@ -29278,7 +29305,7 @@
         <v>0</v>
       </c>
       <c r="K272" s="19" t="s">
-        <v>109</v>
+        <v>238</v>
       </c>
       <c r="L272" s="19">
         <v>800001011</v>
@@ -29287,7 +29314,7 @@
         <v>1</v>
       </c>
       <c r="N272" s="21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O272" s="19">
         <v>1</v>
@@ -29358,13 +29385,13 @@
     </row>
     <row r="273" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A273" s="19">
-        <v>90000503</v>
+        <v>90000402</v>
       </c>
       <c r="B273" s="19">
         <v>3</v>
       </c>
       <c r="C273" s="19" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D273" s="19"/>
       <c r="E273" s="20"/>
@@ -29382,7 +29409,7 @@
         <v>0</v>
       </c>
       <c r="K273" s="19" t="s">
-        <v>115</v>
+        <v>239</v>
       </c>
       <c r="L273" s="19">
         <v>800001021</v>
@@ -29391,7 +29418,7 @@
         <v>1</v>
       </c>
       <c r="N273" s="21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O273" s="19">
         <v>1</v>
@@ -29462,13 +29489,13 @@
     </row>
     <row r="274" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A274" s="19">
-        <v>90000504</v>
+        <v>90000501</v>
       </c>
       <c r="B274" s="19">
         <v>3</v>
       </c>
       <c r="C274" s="19" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D274" s="19"/>
       <c r="E274" s="20"/>
@@ -29486,16 +29513,16 @@
         <v>0</v>
       </c>
       <c r="K274" s="19" t="s">
-        <v>131</v>
+        <v>238</v>
       </c>
       <c r="L274" s="19">
-        <v>800011011</v>
+        <v>800001011</v>
       </c>
       <c r="M274" s="19">
         <v>1</v>
       </c>
       <c r="N274" s="21">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O274" s="19">
         <v>1</v>
@@ -29566,13 +29593,13 @@
     </row>
     <row r="275" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A275" s="19">
-        <v>90000601</v>
+        <v>90000502</v>
       </c>
       <c r="B275" s="19">
         <v>3</v>
       </c>
       <c r="C275" s="19" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D275" s="19"/>
       <c r="E275" s="20"/>
@@ -29590,16 +29617,16 @@
         <v>0</v>
       </c>
       <c r="K275" s="19" t="s">
-        <v>109</v>
+        <v>239</v>
       </c>
       <c r="L275" s="19">
-        <v>800001011</v>
+        <v>800001021</v>
       </c>
       <c r="M275" s="19">
         <v>1</v>
       </c>
       <c r="N275" s="21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O275" s="19">
         <v>1</v>
@@ -29670,13 +29697,13 @@
     </row>
     <row r="276" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A276" s="19">
-        <v>90000602</v>
+        <v>90000503</v>
       </c>
       <c r="B276" s="19">
         <v>3</v>
       </c>
       <c r="C276" s="19" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D276" s="19"/>
       <c r="E276" s="20"/>
@@ -29694,16 +29721,16 @@
         <v>0</v>
       </c>
       <c r="K276" s="19" t="s">
-        <v>109</v>
+        <v>240</v>
       </c>
       <c r="L276" s="19">
-        <v>800001011</v>
+        <v>800001031</v>
       </c>
       <c r="M276" s="19">
         <v>1</v>
       </c>
       <c r="N276" s="21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O276" s="19">
         <v>1</v>
@@ -29774,13 +29801,13 @@
     </row>
     <row r="277" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A277" s="19">
-        <v>90000603</v>
+        <v>90000504</v>
       </c>
       <c r="B277" s="19">
         <v>3</v>
       </c>
       <c r="C277" s="19" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D277" s="19"/>
       <c r="E277" s="20"/>
@@ -29798,16 +29825,16 @@
         <v>0</v>
       </c>
       <c r="K277" s="19" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="L277" s="19">
-        <v>800001021</v>
+        <v>800011011</v>
       </c>
       <c r="M277" s="19">
         <v>1</v>
       </c>
       <c r="N277" s="21">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O277" s="19">
         <v>1</v>
@@ -29878,13 +29905,13 @@
     </row>
     <row r="278" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A278" s="19">
-        <v>90000604</v>
+        <v>90000601</v>
       </c>
       <c r="B278" s="19">
         <v>3</v>
       </c>
       <c r="C278" s="19" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D278" s="19"/>
       <c r="E278" s="20"/>
@@ -29902,16 +29929,16 @@
         <v>0</v>
       </c>
       <c r="K278" s="19" t="s">
-        <v>115</v>
+        <v>238</v>
       </c>
       <c r="L278" s="19">
-        <v>800001021</v>
+        <v>800001011</v>
       </c>
       <c r="M278" s="19">
         <v>1</v>
       </c>
       <c r="N278" s="21">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O278" s="19">
         <v>1</v>
@@ -29982,13 +30009,13 @@
     </row>
     <row r="279" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A279" s="19">
-        <v>90000605</v>
+        <v>90000602</v>
       </c>
       <c r="B279" s="19">
         <v>3</v>
       </c>
       <c r="C279" s="19" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D279" s="19"/>
       <c r="E279" s="20"/>
@@ -30006,16 +30033,16 @@
         <v>0</v>
       </c>
       <c r="K279" s="19" t="s">
-        <v>131</v>
+        <v>239</v>
       </c>
       <c r="L279" s="19">
-        <v>800011011</v>
+        <v>800001021</v>
       </c>
       <c r="M279" s="19">
         <v>1</v>
       </c>
       <c r="N279" s="21">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="O279" s="19">
         <v>1</v>
@@ -30086,13 +30113,13 @@
     </row>
     <row r="280" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A280" s="19">
-        <v>90000606</v>
+        <v>90000603</v>
       </c>
       <c r="B280" s="19">
         <v>3</v>
       </c>
       <c r="C280" s="19" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D280" s="19"/>
       <c r="E280" s="20"/>
@@ -30110,16 +30137,16 @@
         <v>0</v>
       </c>
       <c r="K280" s="19" t="s">
-        <v>131</v>
+        <v>240</v>
       </c>
       <c r="L280" s="19">
-        <v>800011011</v>
+        <v>800001031</v>
       </c>
       <c r="M280" s="19">
         <v>1</v>
       </c>
       <c r="N280" s="21">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="O280" s="19">
         <v>1</v>
@@ -30190,13 +30217,13 @@
     </row>
     <row r="281" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A281" s="19">
-        <v>90000607</v>
+        <v>90000604</v>
       </c>
       <c r="B281" s="19">
         <v>3</v>
       </c>
       <c r="C281" s="19" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D281" s="19"/>
       <c r="E281" s="20"/>
@@ -30214,16 +30241,16 @@
         <v>0</v>
       </c>
       <c r="K281" s="19" t="s">
-        <v>133</v>
+        <v>240</v>
       </c>
       <c r="L281" s="19">
-        <v>800011021</v>
+        <v>800001031</v>
       </c>
       <c r="M281" s="19">
         <v>1</v>
       </c>
       <c r="N281" s="21">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="O281" s="19">
         <v>1</v>
@@ -30294,13 +30321,13 @@
     </row>
     <row r="282" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A282" s="19">
-        <v>90000608</v>
+        <v>90000605</v>
       </c>
       <c r="B282" s="19">
         <v>3</v>
       </c>
       <c r="C282" s="19" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D282" s="19"/>
       <c r="E282" s="20"/>
@@ -30318,16 +30345,16 @@
         <v>0</v>
       </c>
       <c r="K282" s="19" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L282" s="19">
-        <v>800011021</v>
+        <v>800011011</v>
       </c>
       <c r="M282" s="19">
         <v>1</v>
       </c>
       <c r="N282" s="21">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="O282" s="19">
         <v>1</v>
@@ -30398,13 +30425,13 @@
     </row>
     <row r="283" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A283" s="19">
-        <v>90000701</v>
+        <v>90000606</v>
       </c>
       <c r="B283" s="19">
         <v>3</v>
       </c>
       <c r="C283" s="19" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D283" s="19"/>
       <c r="E283" s="20"/>
@@ -30422,16 +30449,16 @@
         <v>0</v>
       </c>
       <c r="K283" s="19" t="s">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="L283" s="19">
-        <v>800001011</v>
+        <v>800011011</v>
       </c>
       <c r="M283" s="19">
         <v>1</v>
       </c>
       <c r="N283" s="21">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="O283" s="19">
         <v>1</v>
@@ -30502,13 +30529,13 @@
     </row>
     <row r="284" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A284" s="19">
-        <v>90000702</v>
+        <v>90000607</v>
       </c>
       <c r="B284" s="19">
         <v>3</v>
       </c>
       <c r="C284" s="19" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D284" s="19"/>
       <c r="E284" s="20"/>
@@ -30526,16 +30553,16 @@
         <v>0</v>
       </c>
       <c r="K284" s="19" t="s">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="L284" s="19">
-        <v>800001011</v>
+        <v>800011021</v>
       </c>
       <c r="M284" s="19">
         <v>1</v>
       </c>
       <c r="N284" s="21">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="O284" s="19">
         <v>1</v>
@@ -30606,13 +30633,13 @@
     </row>
     <row r="285" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A285" s="19">
-        <v>90000703</v>
+        <v>90000608</v>
       </c>
       <c r="B285" s="19">
         <v>3</v>
       </c>
       <c r="C285" s="19" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D285" s="19"/>
       <c r="E285" s="20"/>
@@ -30630,16 +30657,16 @@
         <v>0</v>
       </c>
       <c r="K285" s="19" t="s">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="L285" s="19">
-        <v>800001011</v>
+        <v>800011021</v>
       </c>
       <c r="M285" s="19">
         <v>1</v>
       </c>
       <c r="N285" s="21">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="O285" s="19">
         <v>1</v>
@@ -30710,13 +30737,13 @@
     </row>
     <row r="286" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A286" s="19">
-        <v>90000704</v>
+        <v>90000701</v>
       </c>
       <c r="B286" s="19">
         <v>3</v>
       </c>
       <c r="C286" s="19" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D286" s="19"/>
       <c r="E286" s="20"/>
@@ -30734,16 +30761,16 @@
         <v>0</v>
       </c>
       <c r="K286" s="19" t="s">
-        <v>115</v>
+        <v>238</v>
       </c>
       <c r="L286" s="19">
-        <v>800001021</v>
+        <v>800001011</v>
       </c>
       <c r="M286" s="19">
         <v>1</v>
       </c>
       <c r="N286" s="21">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O286" s="19">
         <v>1</v>
@@ -30814,13 +30841,13 @@
     </row>
     <row r="287" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A287" s="19">
-        <v>90000705</v>
+        <v>90000702</v>
       </c>
       <c r="B287" s="19">
         <v>3</v>
       </c>
       <c r="C287" s="19" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D287" s="19"/>
       <c r="E287" s="20"/>
@@ -30838,16 +30865,16 @@
         <v>0</v>
       </c>
       <c r="K287" s="19" t="s">
-        <v>115</v>
+        <v>238</v>
       </c>
       <c r="L287" s="19">
-        <v>800001021</v>
+        <v>800001011</v>
       </c>
       <c r="M287" s="19">
         <v>1</v>
       </c>
       <c r="N287" s="21">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O287" s="19">
         <v>1</v>
@@ -30918,13 +30945,13 @@
     </row>
     <row r="288" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A288" s="19">
-        <v>90000706</v>
+        <v>90000703</v>
       </c>
       <c r="B288" s="19">
         <v>3</v>
       </c>
       <c r="C288" s="19" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D288" s="19"/>
       <c r="E288" s="20"/>
@@ -30942,7 +30969,7 @@
         <v>0</v>
       </c>
       <c r="K288" s="19" t="s">
-        <v>115</v>
+        <v>239</v>
       </c>
       <c r="L288" s="19">
         <v>800001021</v>
@@ -30951,7 +30978,7 @@
         <v>1</v>
       </c>
       <c r="N288" s="21">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="O288" s="19">
         <v>1</v>
@@ -31022,13 +31049,13 @@
     </row>
     <row r="289" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A289" s="19">
-        <v>90000707</v>
+        <v>90000704</v>
       </c>
       <c r="B289" s="19">
         <v>3</v>
       </c>
       <c r="C289" s="19" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D289" s="19"/>
       <c r="E289" s="20"/>
@@ -31046,7 +31073,7 @@
         <v>0</v>
       </c>
       <c r="K289" s="19" t="s">
-        <v>115</v>
+        <v>239</v>
       </c>
       <c r="L289" s="19">
         <v>800001021</v>
@@ -31055,7 +31082,7 @@
         <v>1</v>
       </c>
       <c r="N289" s="21">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="O289" s="19">
         <v>1</v>
@@ -31126,13 +31153,13 @@
     </row>
     <row r="290" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A290" s="19">
-        <v>90000708</v>
+        <v>90000705</v>
       </c>
       <c r="B290" s="19">
         <v>3</v>
       </c>
       <c r="C290" s="19" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D290" s="19"/>
       <c r="E290" s="20"/>
@@ -31150,16 +31177,16 @@
         <v>0</v>
       </c>
       <c r="K290" s="19" t="s">
-        <v>131</v>
+        <v>239</v>
       </c>
       <c r="L290" s="19">
-        <v>800011011</v>
+        <v>800001021</v>
       </c>
       <c r="M290" s="19">
         <v>1</v>
       </c>
       <c r="N290" s="21">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="O290" s="19">
         <v>1</v>
@@ -31230,13 +31257,13 @@
     </row>
     <row r="291" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A291" s="19">
-        <v>90000709</v>
+        <v>90000706</v>
       </c>
       <c r="B291" s="19">
         <v>3</v>
       </c>
       <c r="C291" s="19" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D291" s="19"/>
       <c r="E291" s="20"/>
@@ -31254,16 +31281,16 @@
         <v>0</v>
       </c>
       <c r="K291" s="19" t="s">
-        <v>131</v>
+        <v>240</v>
       </c>
       <c r="L291" s="19">
-        <v>800011011</v>
+        <v>800001031</v>
       </c>
       <c r="M291" s="19">
         <v>1</v>
       </c>
       <c r="N291" s="21">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="O291" s="19">
         <v>1</v>
@@ -31334,13 +31361,13 @@
     </row>
     <row r="292" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A292" s="19">
-        <v>90000710</v>
+        <v>90000707</v>
       </c>
       <c r="B292" s="19">
         <v>3</v>
       </c>
       <c r="C292" s="19" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D292" s="19"/>
       <c r="E292" s="20"/>
@@ -31358,16 +31385,16 @@
         <v>0</v>
       </c>
       <c r="K292" s="19" t="s">
-        <v>131</v>
+        <v>240</v>
       </c>
       <c r="L292" s="19">
-        <v>800011011</v>
+        <v>800001031</v>
       </c>
       <c r="M292" s="19">
         <v>1</v>
       </c>
       <c r="N292" s="21">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="O292" s="19">
         <v>1</v>
@@ -31438,13 +31465,13 @@
     </row>
     <row r="293" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A293" s="19">
-        <v>90000711</v>
+        <v>90000708</v>
       </c>
       <c r="B293" s="19">
         <v>3</v>
       </c>
       <c r="C293" s="19" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D293" s="19"/>
       <c r="E293" s="20"/>
@@ -31462,16 +31489,16 @@
         <v>0</v>
       </c>
       <c r="K293" s="19" t="s">
-        <v>131</v>
+        <v>240</v>
       </c>
       <c r="L293" s="19">
-        <v>800011011</v>
+        <v>800001031</v>
       </c>
       <c r="M293" s="19">
         <v>1</v>
       </c>
       <c r="N293" s="21">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="O293" s="19">
         <v>1</v>
@@ -31542,13 +31569,13 @@
     </row>
     <row r="294" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A294" s="19">
-        <v>90000712</v>
+        <v>90000709</v>
       </c>
       <c r="B294" s="19">
         <v>3</v>
       </c>
       <c r="C294" s="19" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D294" s="19"/>
       <c r="E294" s="20"/>
@@ -31566,16 +31593,16 @@
         <v>0</v>
       </c>
       <c r="K294" s="19" t="s">
-        <v>133</v>
+        <v>240</v>
       </c>
       <c r="L294" s="19">
-        <v>800011021</v>
+        <v>800001031</v>
       </c>
       <c r="M294" s="19">
         <v>1</v>
       </c>
       <c r="N294" s="21">
-        <v>240</v>
+        <v>40</v>
       </c>
       <c r="O294" s="19">
         <v>1</v>
@@ -31646,13 +31673,13 @@
     </row>
     <row r="295" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A295" s="19">
-        <v>90000713</v>
+        <v>90000710</v>
       </c>
       <c r="B295" s="19">
         <v>3</v>
       </c>
       <c r="C295" s="19" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D295" s="19"/>
       <c r="E295" s="20"/>
@@ -31670,16 +31697,16 @@
         <v>0</v>
       </c>
       <c r="K295" s="19" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L295" s="19">
-        <v>800011021</v>
+        <v>800011011</v>
       </c>
       <c r="M295" s="19">
         <v>1</v>
       </c>
       <c r="N295" s="21">
-        <v>300</v>
+        <v>90</v>
       </c>
       <c r="O295" s="19">
         <v>1</v>
@@ -31750,13 +31777,13 @@
     </row>
     <row r="296" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A296" s="19">
-        <v>90000714</v>
+        <v>90000711</v>
       </c>
       <c r="B296" s="19">
         <v>3</v>
       </c>
       <c r="C296" s="19" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D296" s="19"/>
       <c r="E296" s="20"/>
@@ -31774,16 +31801,16 @@
         <v>0</v>
       </c>
       <c r="K296" s="19" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L296" s="19">
-        <v>800011021</v>
+        <v>800011011</v>
       </c>
       <c r="M296" s="19">
         <v>1</v>
       </c>
       <c r="N296" s="21">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="O296" s="19">
         <v>1</v>
@@ -31854,13 +31881,13 @@
     </row>
     <row r="297" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A297" s="19">
-        <v>90000715</v>
+        <v>90000712</v>
       </c>
       <c r="B297" s="19">
         <v>3</v>
       </c>
       <c r="C297" s="19" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D297" s="19"/>
       <c r="E297" s="20"/>
@@ -31887,7 +31914,7 @@
         <v>1</v>
       </c>
       <c r="N297" s="21">
-        <v>800</v>
+        <v>240</v>
       </c>
       <c r="O297" s="19">
         <v>1</v>
@@ -31958,13 +31985,13 @@
     </row>
     <row r="298" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A298" s="19">
-        <v>90000716</v>
+        <v>90000713</v>
       </c>
       <c r="B298" s="19">
         <v>3</v>
       </c>
       <c r="C298" s="19" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D298" s="19"/>
       <c r="E298" s="20"/>
@@ -31991,7 +32018,7 @@
         <v>1</v>
       </c>
       <c r="N298" s="21">
-        <v>1500</v>
+        <v>300</v>
       </c>
       <c r="O298" s="19">
         <v>1</v>
@@ -32062,13 +32089,13 @@
     </row>
     <row r="299" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A299" s="19">
-        <v>90000717</v>
+        <v>90000714</v>
       </c>
       <c r="B299" s="19">
         <v>3</v>
       </c>
       <c r="C299" s="19" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D299" s="19"/>
       <c r="E299" s="20"/>
@@ -32095,7 +32122,7 @@
         <v>1</v>
       </c>
       <c r="N299" s="21">
-        <v>3000</v>
+        <v>700</v>
       </c>
       <c r="O299" s="19">
         <v>1</v>
@@ -32166,13 +32193,13 @@
     </row>
     <row r="300" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A300" s="19">
-        <v>90000718</v>
+        <v>90000715</v>
       </c>
       <c r="B300" s="19">
         <v>3</v>
       </c>
       <c r="C300" s="19" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D300" s="19"/>
       <c r="E300" s="20"/>
@@ -32199,7 +32226,7 @@
         <v>1</v>
       </c>
       <c r="N300" s="21">
-        <v>4800</v>
+        <v>800</v>
       </c>
       <c r="O300" s="19">
         <v>1</v>
@@ -32270,13 +32297,13 @@
     </row>
     <row r="301" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A301" s="19">
-        <v>90000719</v>
+        <v>90000716</v>
       </c>
       <c r="B301" s="19">
         <v>3</v>
       </c>
       <c r="C301" s="19" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D301" s="19"/>
       <c r="E301" s="20"/>
@@ -32294,16 +32321,16 @@
         <v>0</v>
       </c>
       <c r="K301" s="19" t="s">
-        <v>133</v>
+        <v>241</v>
       </c>
       <c r="L301" s="19">
-        <v>800011021</v>
+        <v>800013031</v>
       </c>
       <c r="M301" s="19">
         <v>1</v>
       </c>
       <c r="N301" s="21">
-        <v>8000</v>
+        <v>1500</v>
       </c>
       <c r="O301" s="19">
         <v>1</v>
@@ -32369,6 +32396,318 @@
         <v>0</v>
       </c>
       <c r="AJ301" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A302" s="19">
+        <v>90000717</v>
+      </c>
+      <c r="B302" s="19">
+        <v>3</v>
+      </c>
+      <c r="C302" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="D302" s="19"/>
+      <c r="E302" s="20"/>
+      <c r="F302" s="19"/>
+      <c r="G302" s="19">
+        <v>1</v>
+      </c>
+      <c r="H302" s="19">
+        <v>2</v>
+      </c>
+      <c r="I302" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="J302" s="19">
+        <v>0</v>
+      </c>
+      <c r="K302" s="19" t="s">
+        <v>241</v>
+      </c>
+      <c r="L302" s="19">
+        <v>800013031</v>
+      </c>
+      <c r="M302" s="19">
+        <v>1</v>
+      </c>
+      <c r="N302" s="21">
+        <v>3000</v>
+      </c>
+      <c r="O302" s="19">
+        <v>1</v>
+      </c>
+      <c r="P302" s="19">
+        <v>8</v>
+      </c>
+      <c r="Q302" s="19">
+        <v>0</v>
+      </c>
+      <c r="R302" s="19">
+        <v>25</v>
+      </c>
+      <c r="S302" s="19">
+        <v>-5000</v>
+      </c>
+      <c r="T302" s="19">
+        <v>1</v>
+      </c>
+      <c r="U302" s="19">
+        <v>0</v>
+      </c>
+      <c r="V302" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="W302" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="X302" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y302" s="22">
+        <v>20010001</v>
+      </c>
+      <c r="Z302" s="22">
+        <v>0</v>
+      </c>
+      <c r="AA302" s="19">
+        <v>1</v>
+      </c>
+      <c r="AB302" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC302" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AD302" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AE302" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF302" s="23">
+        <v>40</v>
+      </c>
+      <c r="AG302" s="23">
+        <v>0</v>
+      </c>
+      <c r="AH302" s="23">
+        <v>0</v>
+      </c>
+      <c r="AI302" s="23">
+        <v>0</v>
+      </c>
+      <c r="AJ302" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A303" s="19">
+        <v>90000718</v>
+      </c>
+      <c r="B303" s="19">
+        <v>3</v>
+      </c>
+      <c r="C303" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="D303" s="19"/>
+      <c r="E303" s="20"/>
+      <c r="F303" s="19"/>
+      <c r="G303" s="19">
+        <v>1</v>
+      </c>
+      <c r="H303" s="19">
+        <v>2</v>
+      </c>
+      <c r="I303" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="J303" s="19">
+        <v>0</v>
+      </c>
+      <c r="K303" s="19" t="s">
+        <v>241</v>
+      </c>
+      <c r="L303" s="19">
+        <v>800013031</v>
+      </c>
+      <c r="M303" s="19">
+        <v>1</v>
+      </c>
+      <c r="N303" s="21">
+        <v>4800</v>
+      </c>
+      <c r="O303" s="19">
+        <v>1</v>
+      </c>
+      <c r="P303" s="19">
+        <v>8</v>
+      </c>
+      <c r="Q303" s="19">
+        <v>0</v>
+      </c>
+      <c r="R303" s="19">
+        <v>25</v>
+      </c>
+      <c r="S303" s="19">
+        <v>-5000</v>
+      </c>
+      <c r="T303" s="19">
+        <v>1</v>
+      </c>
+      <c r="U303" s="19">
+        <v>0</v>
+      </c>
+      <c r="V303" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="W303" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="X303" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y303" s="22">
+        <v>20010001</v>
+      </c>
+      <c r="Z303" s="22">
+        <v>0</v>
+      </c>
+      <c r="AA303" s="19">
+        <v>1</v>
+      </c>
+      <c r="AB303" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC303" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AD303" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AE303" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF303" s="23">
+        <v>40</v>
+      </c>
+      <c r="AG303" s="23">
+        <v>0</v>
+      </c>
+      <c r="AH303" s="23">
+        <v>0</v>
+      </c>
+      <c r="AI303" s="23">
+        <v>0</v>
+      </c>
+      <c r="AJ303" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A304" s="19">
+        <v>90000719</v>
+      </c>
+      <c r="B304" s="19">
+        <v>3</v>
+      </c>
+      <c r="C304" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="D304" s="19"/>
+      <c r="E304" s="20"/>
+      <c r="F304" s="19"/>
+      <c r="G304" s="19">
+        <v>1</v>
+      </c>
+      <c r="H304" s="19">
+        <v>2</v>
+      </c>
+      <c r="I304" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="J304" s="19">
+        <v>0</v>
+      </c>
+      <c r="K304" s="19" t="s">
+        <v>241</v>
+      </c>
+      <c r="L304" s="19">
+        <v>800013031</v>
+      </c>
+      <c r="M304" s="19">
+        <v>1</v>
+      </c>
+      <c r="N304" s="21">
+        <v>8000</v>
+      </c>
+      <c r="O304" s="19">
+        <v>1</v>
+      </c>
+      <c r="P304" s="19">
+        <v>8</v>
+      </c>
+      <c r="Q304" s="19">
+        <v>0</v>
+      </c>
+      <c r="R304" s="19">
+        <v>25</v>
+      </c>
+      <c r="S304" s="19">
+        <v>-5000</v>
+      </c>
+      <c r="T304" s="19">
+        <v>1</v>
+      </c>
+      <c r="U304" s="19">
+        <v>0</v>
+      </c>
+      <c r="V304" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="W304" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="X304" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y304" s="22">
+        <v>20010001</v>
+      </c>
+      <c r="Z304" s="22">
+        <v>0</v>
+      </c>
+      <c r="AA304" s="19">
+        <v>1</v>
+      </c>
+      <c r="AB304" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC304" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AD304" s="19">
+        <v>10000</v>
+      </c>
+      <c r="AE304" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF304" s="23">
+        <v>40</v>
+      </c>
+      <c r="AG304" s="23">
+        <v>0</v>
+      </c>
+      <c r="AH304" s="23">
+        <v>0</v>
+      </c>
+      <c r="AI304" s="23">
+        <v>0</v>
+      </c>
+      <c r="AJ304" s="23">
         <v>0</v>
       </c>
     </row>
@@ -32377,7 +32716,7 @@
     <sortCondition ref="A5:A211"/>
   </sortState>
   <phoneticPr fontId="13" type="noConversion"/>
-  <conditionalFormatting sqref="A221:A1048576 A1:A211">
+  <conditionalFormatting sqref="A1:A211 A221:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="33"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06FE205B-6C39-48F7-B61D-278556BDD119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BC0A49A-B278-4CCA-90DF-9211ED918CF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6087,7 +6087,7 @@
         <v>11101</v>
       </c>
       <c r="B47" s="3">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>108</v>
@@ -6167,7 +6167,7 @@
         <v>10000</v>
       </c>
       <c r="AE47" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF47" s="8">
         <v>40</v>
@@ -6190,7 +6190,7 @@
         <v>11102</v>
       </c>
       <c r="B48" s="3">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>114</v>
@@ -6270,7 +6270,7 @@
         <v>10000</v>
       </c>
       <c r="AE48" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF48" s="8">
         <v>40</v>
@@ -6293,7 +6293,7 @@
         <v>11103</v>
       </c>
       <c r="B49" s="2">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>117</v>
@@ -6371,8 +6371,8 @@
       <c r="AD49" s="2">
         <v>10000</v>
       </c>
-      <c r="AE49" s="2">
-        <v>25010001</v>
+      <c r="AE49" s="3">
+        <v>0</v>
       </c>
       <c r="AF49" s="8">
         <v>40</v>
@@ -6395,7 +6395,7 @@
         <v>11104</v>
       </c>
       <c r="B50" s="3">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>118</v>
@@ -6475,7 +6475,7 @@
         <v>10000</v>
       </c>
       <c r="AE50" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF50" s="8">
         <v>40</v>
@@ -6498,7 +6498,7 @@
         <v>11105</v>
       </c>
       <c r="B51" s="3">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>120</v>
@@ -6578,7 +6578,7 @@
         <v>10000</v>
       </c>
       <c r="AE51" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF51" s="8">
         <v>40</v>
@@ -6601,7 +6601,7 @@
         <v>11106</v>
       </c>
       <c r="B52" s="2">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>123</v>
@@ -6622,8 +6622,8 @@
         <v>0</v>
       </c>
       <c r="K52" s="2"/>
-      <c r="L52" s="2">
-        <v>1000010</v>
+      <c r="L52" s="3">
+        <v>800001011</v>
       </c>
       <c r="M52" s="2">
         <v>1</v>
@@ -6679,8 +6679,8 @@
       <c r="AD52" s="2">
         <v>10000</v>
       </c>
-      <c r="AE52" s="2">
-        <v>25010001</v>
+      <c r="AE52" s="3">
+        <v>0</v>
       </c>
       <c r="AF52" s="8">
         <v>40</v>
@@ -6703,7 +6703,7 @@
         <v>11107</v>
       </c>
       <c r="B53" s="2">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>125</v>
@@ -6783,8 +6783,8 @@
       <c r="AD53" s="2">
         <v>10000</v>
       </c>
-      <c r="AE53" s="2">
-        <v>25010001</v>
+      <c r="AE53" s="3">
+        <v>0</v>
       </c>
       <c r="AF53" s="8">
         <v>40</v>
@@ -6807,7 +6807,7 @@
         <v>11108</v>
       </c>
       <c r="B54" s="3">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>126</v>
@@ -6887,7 +6887,7 @@
         <v>10000</v>
       </c>
       <c r="AE54" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF54" s="8">
         <v>40</v>
@@ -6910,7 +6910,7 @@
         <v>11109</v>
       </c>
       <c r="B55" s="3">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>128</v>
@@ -6990,7 +6990,7 @@
         <v>10000</v>
       </c>
       <c r="AE55" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF55" s="8">
         <v>40</v>
@@ -7013,7 +7013,7 @@
         <v>11110</v>
       </c>
       <c r="B56" s="3">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>130</v>
@@ -7093,7 +7093,7 @@
         <v>10000</v>
       </c>
       <c r="AE56" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF56" s="8">
         <v>40</v>
@@ -7116,7 +7116,7 @@
         <v>11111</v>
       </c>
       <c r="B57" s="3">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>132</v>
@@ -7196,7 +7196,7 @@
         <v>10000</v>
       </c>
       <c r="AE57" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF57" s="8">
         <v>40</v>
@@ -7219,7 +7219,7 @@
         <v>11112</v>
       </c>
       <c r="B58" s="3">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>134</v>
@@ -7299,7 +7299,7 @@
         <v>10000</v>
       </c>
       <c r="AE58" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF58" s="8">
         <v>40</v>
@@ -7322,7 +7322,7 @@
         <v>11113</v>
       </c>
       <c r="B59" s="3">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>136</v>
@@ -7402,7 +7402,7 @@
         <v>10000</v>
       </c>
       <c r="AE59" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF59" s="8">
         <v>40</v>
@@ -7425,7 +7425,7 @@
         <v>11114</v>
       </c>
       <c r="B60" s="3">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>140</v>
@@ -7528,7 +7528,7 @@
         <v>11115</v>
       </c>
       <c r="B61" s="2">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>142</v>
@@ -7549,8 +7549,8 @@
         <v>0</v>
       </c>
       <c r="K61" s="2"/>
-      <c r="L61" s="2">
-        <v>1000011</v>
+      <c r="L61" s="3">
+        <v>800001011</v>
       </c>
       <c r="M61" s="2">
         <v>1</v>
@@ -7606,7 +7606,7 @@
       <c r="AD61" s="2">
         <v>10000</v>
       </c>
-      <c r="AE61" s="2">
+      <c r="AE61" s="3">
         <v>0</v>
       </c>
       <c r="AF61" s="8">
@@ -7630,7 +7630,7 @@
         <v>21101</v>
       </c>
       <c r="B62" s="3">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>108</v>
@@ -7710,7 +7710,7 @@
         <v>10000</v>
       </c>
       <c r="AE62" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF62" s="8">
         <v>40</v>
@@ -7733,7 +7733,7 @@
         <v>21102</v>
       </c>
       <c r="B63" s="3">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>114</v>
@@ -7813,13 +7813,13 @@
         <v>10000</v>
       </c>
       <c r="AE63" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF63" s="8">
         <v>40</v>
       </c>
       <c r="AG63" s="8">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="AH63" s="8">
         <v>10000</v>
@@ -7836,7 +7836,7 @@
         <v>21103</v>
       </c>
       <c r="B64" s="2">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>117</v>
@@ -7914,17 +7914,17 @@
       <c r="AD64" s="2">
         <v>10000</v>
       </c>
-      <c r="AE64" s="2">
-        <v>25010001</v>
+      <c r="AE64" s="3">
+        <v>0</v>
       </c>
       <c r="AF64" s="8">
         <v>40</v>
       </c>
       <c r="AG64" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH64" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI64" s="8">
         <v>0</v>
@@ -7938,7 +7938,7 @@
         <v>21104</v>
       </c>
       <c r="B65" s="3">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>118</v>
@@ -8018,7 +8018,7 @@
         <v>10000</v>
       </c>
       <c r="AE65" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF65" s="8">
         <v>40</v>
@@ -8041,7 +8041,7 @@
         <v>21105</v>
       </c>
       <c r="B66" s="3">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>120</v>
@@ -8121,7 +8121,7 @@
         <v>10000</v>
       </c>
       <c r="AE66" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF66" s="8">
         <v>40</v>
@@ -8144,7 +8144,7 @@
         <v>21106</v>
       </c>
       <c r="B67" s="2">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>123</v>
@@ -8165,8 +8165,8 @@
         <v>0</v>
       </c>
       <c r="K67" s="2"/>
-      <c r="L67" s="2">
-        <v>1000010</v>
+      <c r="L67" s="3">
+        <v>800001011</v>
       </c>
       <c r="M67" s="2">
         <v>1</v>
@@ -8222,17 +8222,17 @@
       <c r="AD67" s="2">
         <v>10000</v>
       </c>
-      <c r="AE67" s="2">
-        <v>25010001</v>
+      <c r="AE67" s="3">
+        <v>0</v>
       </c>
       <c r="AF67" s="8">
         <v>40</v>
       </c>
       <c r="AG67" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH67" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI67" s="8">
         <v>0</v>
@@ -8246,7 +8246,7 @@
         <v>21107</v>
       </c>
       <c r="B68" s="2">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>125</v>
@@ -8326,17 +8326,17 @@
       <c r="AD68" s="2">
         <v>10000</v>
       </c>
-      <c r="AE68" s="2">
-        <v>25010001</v>
+      <c r="AE68" s="3">
+        <v>0</v>
       </c>
       <c r="AF68" s="8">
         <v>40</v>
       </c>
       <c r="AG68" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH68" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI68" s="8">
         <v>0</v>
@@ -8350,7 +8350,7 @@
         <v>21108</v>
       </c>
       <c r="B69" s="3">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>126</v>
@@ -8430,16 +8430,16 @@
         <v>10000</v>
       </c>
       <c r="AE69" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF69" s="8">
         <v>40</v>
       </c>
       <c r="AG69" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH69" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI69" s="8">
         <v>0</v>
@@ -8453,7 +8453,7 @@
         <v>21109</v>
       </c>
       <c r="B70" s="3">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>128</v>
@@ -8533,16 +8533,16 @@
         <v>10000</v>
       </c>
       <c r="AE70" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF70" s="8">
         <v>40</v>
       </c>
       <c r="AG70" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH70" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI70" s="8">
         <v>0</v>
@@ -8556,7 +8556,7 @@
         <v>21110</v>
       </c>
       <c r="B71" s="3">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>130</v>
@@ -8636,16 +8636,16 @@
         <v>10000</v>
       </c>
       <c r="AE71" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF71" s="8">
         <v>40</v>
       </c>
       <c r="AG71" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH71" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI71" s="8">
         <v>0</v>
@@ -8659,7 +8659,7 @@
         <v>21111</v>
       </c>
       <c r="B72" s="3">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>132</v>
@@ -8739,16 +8739,16 @@
         <v>10000</v>
       </c>
       <c r="AE72" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF72" s="8">
         <v>40</v>
       </c>
       <c r="AG72" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH72" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI72" s="8">
         <v>0</v>
@@ -8762,7 +8762,7 @@
         <v>21112</v>
       </c>
       <c r="B73" s="3">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>134</v>
@@ -8842,16 +8842,16 @@
         <v>10000</v>
       </c>
       <c r="AE73" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF73" s="8">
         <v>40</v>
       </c>
       <c r="AG73" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH73" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI73" s="8">
         <v>0</v>
@@ -8865,7 +8865,7 @@
         <v>21113</v>
       </c>
       <c r="B74" s="3">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>136</v>
@@ -8945,16 +8945,16 @@
         <v>10000</v>
       </c>
       <c r="AE74" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF74" s="8">
         <v>40</v>
       </c>
       <c r="AG74" s="8">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="AH74" s="8">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="AI74" s="8">
         <v>40</v>
@@ -8968,7 +8968,7 @@
         <v>21114</v>
       </c>
       <c r="B75" s="3">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>140</v>
@@ -9054,10 +9054,10 @@
         <v>40</v>
       </c>
       <c r="AG75" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH75" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI75" s="8">
         <v>0</v>
@@ -9071,7 +9071,7 @@
         <v>21115</v>
       </c>
       <c r="B76" s="2">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>142</v>
@@ -9092,8 +9092,8 @@
         <v>0</v>
       </c>
       <c r="K76" s="2"/>
-      <c r="L76" s="2">
-        <v>1000011</v>
+      <c r="L76" s="3">
+        <v>800001011</v>
       </c>
       <c r="M76" s="2">
         <v>1</v>
@@ -9149,17 +9149,17 @@
       <c r="AD76" s="2">
         <v>10000</v>
       </c>
-      <c r="AE76" s="2">
+      <c r="AE76" s="3">
         <v>0</v>
       </c>
       <c r="AF76" s="8">
         <v>40</v>
       </c>
       <c r="AG76" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH76" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI76" s="8">
         <v>0</v>
@@ -9173,7 +9173,7 @@
         <v>31101</v>
       </c>
       <c r="B77" s="3">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>108</v>
@@ -9253,7 +9253,7 @@
         <v>10000</v>
       </c>
       <c r="AE77" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF77" s="8">
         <v>40</v>
@@ -9276,7 +9276,7 @@
         <v>31102</v>
       </c>
       <c r="B78" s="3">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>114</v>
@@ -9356,13 +9356,13 @@
         <v>10000</v>
       </c>
       <c r="AE78" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF78" s="8">
         <v>40</v>
       </c>
       <c r="AG78" s="8">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="AH78" s="8">
         <v>10000</v>
@@ -9379,7 +9379,7 @@
         <v>31103</v>
       </c>
       <c r="B79" s="2">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>117</v>
@@ -9457,17 +9457,17 @@
       <c r="AD79" s="2">
         <v>10000</v>
       </c>
-      <c r="AE79" s="2">
-        <v>25010001</v>
+      <c r="AE79" s="3">
+        <v>0</v>
       </c>
       <c r="AF79" s="8">
         <v>40</v>
       </c>
       <c r="AG79" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH79" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI79" s="8">
         <v>0</v>
@@ -9481,7 +9481,7 @@
         <v>31104</v>
       </c>
       <c r="B80" s="3">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>118</v>
@@ -9561,7 +9561,7 @@
         <v>10000</v>
       </c>
       <c r="AE80" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF80" s="8">
         <v>40</v>
@@ -9584,7 +9584,7 @@
         <v>31105</v>
       </c>
       <c r="B81" s="3">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>120</v>
@@ -9664,7 +9664,7 @@
         <v>10000</v>
       </c>
       <c r="AE81" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF81" s="8">
         <v>40</v>
@@ -9687,7 +9687,7 @@
         <v>31106</v>
       </c>
       <c r="B82" s="2">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>123</v>
@@ -9708,8 +9708,8 @@
         <v>0</v>
       </c>
       <c r="K82" s="2"/>
-      <c r="L82" s="2">
-        <v>1000010</v>
+      <c r="L82" s="3">
+        <v>800001011</v>
       </c>
       <c r="M82" s="2">
         <v>1</v>
@@ -9765,17 +9765,17 @@
       <c r="AD82" s="2">
         <v>10000</v>
       </c>
-      <c r="AE82" s="2">
-        <v>25010001</v>
+      <c r="AE82" s="3">
+        <v>0</v>
       </c>
       <c r="AF82" s="8">
         <v>40</v>
       </c>
       <c r="AG82" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH82" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI82" s="8">
         <v>0</v>
@@ -9789,7 +9789,7 @@
         <v>31107</v>
       </c>
       <c r="B83" s="2">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>125</v>
@@ -9869,17 +9869,17 @@
       <c r="AD83" s="2">
         <v>10000</v>
       </c>
-      <c r="AE83" s="2">
-        <v>25010001</v>
+      <c r="AE83" s="3">
+        <v>0</v>
       </c>
       <c r="AF83" s="8">
         <v>40</v>
       </c>
       <c r="AG83" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH83" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI83" s="8">
         <v>0</v>
@@ -9893,7 +9893,7 @@
         <v>31108</v>
       </c>
       <c r="B84" s="3">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>126</v>
@@ -9973,16 +9973,16 @@
         <v>10000</v>
       </c>
       <c r="AE84" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF84" s="8">
         <v>40</v>
       </c>
       <c r="AG84" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH84" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI84" s="8">
         <v>0</v>
@@ -9996,7 +9996,7 @@
         <v>31109</v>
       </c>
       <c r="B85" s="3">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="C85" s="3" t="s">
         <v>128</v>
@@ -10076,16 +10076,16 @@
         <v>10000</v>
       </c>
       <c r="AE85" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF85" s="8">
         <v>40</v>
       </c>
       <c r="AG85" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH85" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI85" s="8">
         <v>0</v>
@@ -10099,7 +10099,7 @@
         <v>31110</v>
       </c>
       <c r="B86" s="3">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="C86" s="3" t="s">
         <v>130</v>
@@ -10179,16 +10179,16 @@
         <v>10000</v>
       </c>
       <c r="AE86" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF86" s="8">
         <v>40</v>
       </c>
       <c r="AG86" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH86" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI86" s="8">
         <v>0</v>
@@ -10202,7 +10202,7 @@
         <v>31111</v>
       </c>
       <c r="B87" s="3">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="C87" s="3" t="s">
         <v>132</v>
@@ -10282,16 +10282,16 @@
         <v>10000</v>
       </c>
       <c r="AE87" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF87" s="8">
         <v>40</v>
       </c>
       <c r="AG87" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH87" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI87" s="8">
         <v>0</v>
@@ -10305,7 +10305,7 @@
         <v>31112</v>
       </c>
       <c r="B88" s="3">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="C88" s="3" t="s">
         <v>134</v>
@@ -10385,16 +10385,16 @@
         <v>10000</v>
       </c>
       <c r="AE88" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF88" s="8">
         <v>40</v>
       </c>
       <c r="AG88" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH88" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI88" s="8">
         <v>0</v>
@@ -10408,7 +10408,7 @@
         <v>31113</v>
       </c>
       <c r="B89" s="3">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>136</v>
@@ -10488,16 +10488,16 @@
         <v>10000</v>
       </c>
       <c r="AE89" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF89" s="8">
         <v>40</v>
       </c>
       <c r="AG89" s="8">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="AH89" s="8">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="AI89" s="8">
         <v>40</v>
@@ -10511,7 +10511,7 @@
         <v>31114</v>
       </c>
       <c r="B90" s="3">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>140</v>
@@ -10597,10 +10597,10 @@
         <v>40</v>
       </c>
       <c r="AG90" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH90" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI90" s="8">
         <v>0</v>
@@ -10614,7 +10614,7 @@
         <v>31115</v>
       </c>
       <c r="B91" s="2">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>142</v>
@@ -10635,8 +10635,8 @@
         <v>0</v>
       </c>
       <c r="K91" s="2"/>
-      <c r="L91" s="2">
-        <v>1000011</v>
+      <c r="L91" s="3">
+        <v>800001011</v>
       </c>
       <c r="M91" s="2">
         <v>1</v>
@@ -10692,17 +10692,17 @@
       <c r="AD91" s="2">
         <v>10000</v>
       </c>
-      <c r="AE91" s="2">
+      <c r="AE91" s="3">
         <v>0</v>
       </c>
       <c r="AF91" s="8">
         <v>40</v>
       </c>
       <c r="AG91" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH91" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI91" s="8">
         <v>0</v>
@@ -10716,7 +10716,7 @@
         <v>41101</v>
       </c>
       <c r="B92" s="3">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>108</v>
@@ -10796,7 +10796,7 @@
         <v>10000</v>
       </c>
       <c r="AE92" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF92" s="8">
         <v>40</v>
@@ -10819,7 +10819,7 @@
         <v>41102</v>
       </c>
       <c r="B93" s="3">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>114</v>
@@ -10899,13 +10899,13 @@
         <v>10000</v>
       </c>
       <c r="AE93" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF93" s="8">
         <v>40</v>
       </c>
       <c r="AG93" s="8">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="AH93" s="8">
         <v>10000</v>
@@ -10921,8 +10921,8 @@
       <c r="A94" s="3">
         <v>41103</v>
       </c>
-      <c r="B94" s="2">
-        <v>30</v>
+      <c r="B94" s="3">
+        <v>4</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>117</v>
@@ -11000,17 +11000,17 @@
       <c r="AD94" s="2">
         <v>10000</v>
       </c>
-      <c r="AE94" s="2">
-        <v>25010001</v>
+      <c r="AE94" s="3">
+        <v>0</v>
       </c>
       <c r="AF94" s="8">
         <v>40</v>
       </c>
       <c r="AG94" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH94" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI94" s="8">
         <v>0</v>
@@ -11024,7 +11024,7 @@
         <v>41104</v>
       </c>
       <c r="B95" s="3">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>118</v>
@@ -11104,7 +11104,7 @@
         <v>10000</v>
       </c>
       <c r="AE95" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF95" s="8">
         <v>40</v>
@@ -11127,7 +11127,7 @@
         <v>41105</v>
       </c>
       <c r="B96" s="3">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C96" s="3" t="s">
         <v>120</v>
@@ -11207,7 +11207,7 @@
         <v>10000</v>
       </c>
       <c r="AE96" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF96" s="8">
         <v>40</v>
@@ -11229,8 +11229,8 @@
       <c r="A97" s="3">
         <v>41106</v>
       </c>
-      <c r="B97" s="2">
-        <v>30</v>
+      <c r="B97" s="3">
+        <v>4</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>123</v>
@@ -11251,8 +11251,8 @@
         <v>0</v>
       </c>
       <c r="K97" s="2"/>
-      <c r="L97" s="2">
-        <v>1000010</v>
+      <c r="L97" s="3">
+        <v>800001011</v>
       </c>
       <c r="M97" s="2">
         <v>1</v>
@@ -11308,17 +11308,17 @@
       <c r="AD97" s="2">
         <v>10000</v>
       </c>
-      <c r="AE97" s="2">
-        <v>25010001</v>
+      <c r="AE97" s="3">
+        <v>0</v>
       </c>
       <c r="AF97" s="8">
         <v>40</v>
       </c>
       <c r="AG97" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH97" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI97" s="8">
         <v>0</v>
@@ -11331,8 +11331,8 @@
       <c r="A98" s="3">
         <v>41107</v>
       </c>
-      <c r="B98" s="2">
-        <v>30</v>
+      <c r="B98" s="3">
+        <v>4</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>125</v>
@@ -11412,17 +11412,17 @@
       <c r="AD98" s="2">
         <v>10000</v>
       </c>
-      <c r="AE98" s="2">
-        <v>25010001</v>
+      <c r="AE98" s="3">
+        <v>0</v>
       </c>
       <c r="AF98" s="8">
         <v>40</v>
       </c>
       <c r="AG98" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH98" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI98" s="8">
         <v>0</v>
@@ -11436,7 +11436,7 @@
         <v>41108</v>
       </c>
       <c r="B99" s="3">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C99" s="3" t="s">
         <v>126</v>
@@ -11516,16 +11516,16 @@
         <v>10000</v>
       </c>
       <c r="AE99" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF99" s="8">
         <v>40</v>
       </c>
       <c r="AG99" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH99" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI99" s="8">
         <v>0</v>
@@ -11539,7 +11539,7 @@
         <v>41109</v>
       </c>
       <c r="B100" s="3">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C100" s="3" t="s">
         <v>128</v>
@@ -11619,16 +11619,16 @@
         <v>10000</v>
       </c>
       <c r="AE100" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF100" s="8">
         <v>40</v>
       </c>
       <c r="AG100" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH100" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI100" s="8">
         <v>0</v>
@@ -11642,7 +11642,7 @@
         <v>41110</v>
       </c>
       <c r="B101" s="3">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C101" s="3" t="s">
         <v>130</v>
@@ -11722,16 +11722,16 @@
         <v>10000</v>
       </c>
       <c r="AE101" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF101" s="8">
         <v>40</v>
       </c>
       <c r="AG101" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH101" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI101" s="8">
         <v>0</v>
@@ -11745,7 +11745,7 @@
         <v>41111</v>
       </c>
       <c r="B102" s="3">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C102" s="3" t="s">
         <v>132</v>
@@ -11825,16 +11825,16 @@
         <v>10000</v>
       </c>
       <c r="AE102" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF102" s="8">
         <v>40</v>
       </c>
       <c r="AG102" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH102" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI102" s="8">
         <v>0</v>
@@ -11848,7 +11848,7 @@
         <v>41112</v>
       </c>
       <c r="B103" s="3">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C103" s="3" t="s">
         <v>134</v>
@@ -11928,16 +11928,16 @@
         <v>10000</v>
       </c>
       <c r="AE103" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF103" s="8">
         <v>40</v>
       </c>
       <c r="AG103" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH103" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI103" s="8">
         <v>0</v>
@@ -11951,7 +11951,7 @@
         <v>41113</v>
       </c>
       <c r="B104" s="3">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C104" s="3" t="s">
         <v>136</v>
@@ -12031,16 +12031,16 @@
         <v>10000</v>
       </c>
       <c r="AE104" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF104" s="8">
         <v>40</v>
       </c>
       <c r="AG104" s="8">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="AH104" s="8">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="AI104" s="8">
         <v>40</v>
@@ -12054,7 +12054,7 @@
         <v>41114</v>
       </c>
       <c r="B105" s="3">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C105" s="3" t="s">
         <v>140</v>
@@ -12140,10 +12140,10 @@
         <v>40</v>
       </c>
       <c r="AG105" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH105" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI105" s="8">
         <v>0</v>
@@ -12156,8 +12156,8 @@
       <c r="A106" s="3">
         <v>41115</v>
       </c>
-      <c r="B106" s="2">
-        <v>30</v>
+      <c r="B106" s="3">
+        <v>4</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>142</v>
@@ -12178,8 +12178,8 @@
         <v>0</v>
       </c>
       <c r="K106" s="2"/>
-      <c r="L106" s="2">
-        <v>1000011</v>
+      <c r="L106" s="3">
+        <v>800001011</v>
       </c>
       <c r="M106" s="2">
         <v>1</v>
@@ -12235,17 +12235,17 @@
       <c r="AD106" s="2">
         <v>10000</v>
       </c>
-      <c r="AE106" s="2">
+      <c r="AE106" s="3">
         <v>0</v>
       </c>
       <c r="AF106" s="8">
         <v>40</v>
       </c>
       <c r="AG106" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH106" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI106" s="8">
         <v>0</v>
@@ -12259,7 +12259,7 @@
         <v>51101</v>
       </c>
       <c r="B107" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C107" s="3" t="s">
         <v>108</v>
@@ -12339,7 +12339,7 @@
         <v>10000</v>
       </c>
       <c r="AE107" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF107" s="8">
         <v>40</v>
@@ -12362,7 +12362,7 @@
         <v>51102</v>
       </c>
       <c r="B108" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C108" s="3" t="s">
         <v>114</v>
@@ -12442,13 +12442,13 @@
         <v>10000</v>
       </c>
       <c r="AE108" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF108" s="8">
         <v>40</v>
       </c>
       <c r="AG108" s="8">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="AH108" s="8">
         <v>10000</v>
@@ -12465,7 +12465,7 @@
         <v>51103</v>
       </c>
       <c r="B109" s="2">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>117</v>
@@ -12543,17 +12543,17 @@
       <c r="AD109" s="2">
         <v>10000</v>
       </c>
-      <c r="AE109" s="2">
-        <v>25010001</v>
+      <c r="AE109" s="3">
+        <v>0</v>
       </c>
       <c r="AF109" s="8">
         <v>40</v>
       </c>
       <c r="AG109" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH109" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI109" s="8">
         <v>0</v>
@@ -12567,7 +12567,7 @@
         <v>51104</v>
       </c>
       <c r="B110" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C110" s="3" t="s">
         <v>118</v>
@@ -12647,7 +12647,7 @@
         <v>10000</v>
       </c>
       <c r="AE110" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF110" s="8">
         <v>40</v>
@@ -12670,7 +12670,7 @@
         <v>51105</v>
       </c>
       <c r="B111" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C111" s="3" t="s">
         <v>120</v>
@@ -12750,7 +12750,7 @@
         <v>10000</v>
       </c>
       <c r="AE111" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF111" s="8">
         <v>40</v>
@@ -12773,7 +12773,7 @@
         <v>51106</v>
       </c>
       <c r="B112" s="2">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>123</v>
@@ -12794,8 +12794,8 @@
         <v>0</v>
       </c>
       <c r="K112" s="2"/>
-      <c r="L112" s="2">
-        <v>1000010</v>
+      <c r="L112" s="3">
+        <v>800001011</v>
       </c>
       <c r="M112" s="2">
         <v>1</v>
@@ -12851,17 +12851,17 @@
       <c r="AD112" s="2">
         <v>10000</v>
       </c>
-      <c r="AE112" s="2">
-        <v>25010001</v>
+      <c r="AE112" s="3">
+        <v>0</v>
       </c>
       <c r="AF112" s="8">
         <v>40</v>
       </c>
       <c r="AG112" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH112" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI112" s="8">
         <v>0</v>
@@ -12875,7 +12875,7 @@
         <v>51107</v>
       </c>
       <c r="B113" s="2">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>125</v>
@@ -12955,17 +12955,17 @@
       <c r="AD113" s="2">
         <v>10000</v>
       </c>
-      <c r="AE113" s="2">
-        <v>25010001</v>
+      <c r="AE113" s="3">
+        <v>0</v>
       </c>
       <c r="AF113" s="8">
         <v>40</v>
       </c>
       <c r="AG113" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH113" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI113" s="8">
         <v>0</v>
@@ -12979,7 +12979,7 @@
         <v>51108</v>
       </c>
       <c r="B114" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C114" s="3" t="s">
         <v>126</v>
@@ -13059,16 +13059,16 @@
         <v>10000</v>
       </c>
       <c r="AE114" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF114" s="8">
         <v>40</v>
       </c>
       <c r="AG114" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH114" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI114" s="8">
         <v>0</v>
@@ -13082,7 +13082,7 @@
         <v>51109</v>
       </c>
       <c r="B115" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C115" s="3" t="s">
         <v>128</v>
@@ -13162,16 +13162,16 @@
         <v>10000</v>
       </c>
       <c r="AE115" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF115" s="8">
         <v>40</v>
       </c>
       <c r="AG115" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH115" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI115" s="8">
         <v>0</v>
@@ -13185,7 +13185,7 @@
         <v>51110</v>
       </c>
       <c r="B116" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C116" s="3" t="s">
         <v>130</v>
@@ -13265,16 +13265,16 @@
         <v>10000</v>
       </c>
       <c r="AE116" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF116" s="8">
         <v>40</v>
       </c>
       <c r="AG116" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH116" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI116" s="8">
         <v>0</v>
@@ -13288,7 +13288,7 @@
         <v>51111</v>
       </c>
       <c r="B117" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C117" s="3" t="s">
         <v>132</v>
@@ -13368,16 +13368,16 @@
         <v>10000</v>
       </c>
       <c r="AE117" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF117" s="8">
         <v>40</v>
       </c>
       <c r="AG117" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH117" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI117" s="8">
         <v>0</v>
@@ -13391,7 +13391,7 @@
         <v>51112</v>
       </c>
       <c r="B118" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C118" s="3" t="s">
         <v>134</v>
@@ -13471,16 +13471,16 @@
         <v>10000</v>
       </c>
       <c r="AE118" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF118" s="8">
         <v>40</v>
       </c>
       <c r="AG118" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH118" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI118" s="8">
         <v>0</v>
@@ -13494,7 +13494,7 @@
         <v>51113</v>
       </c>
       <c r="B119" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C119" s="3" t="s">
         <v>136</v>
@@ -13574,16 +13574,16 @@
         <v>10000</v>
       </c>
       <c r="AE119" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF119" s="8">
         <v>40</v>
       </c>
       <c r="AG119" s="8">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="AH119" s="8">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="AI119" s="8">
         <v>40</v>
@@ -13597,7 +13597,7 @@
         <v>51114</v>
       </c>
       <c r="B120" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C120" s="3" t="s">
         <v>140</v>
@@ -13683,10 +13683,10 @@
         <v>40</v>
       </c>
       <c r="AG120" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH120" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI120" s="8">
         <v>0</v>
@@ -13700,7 +13700,7 @@
         <v>51115</v>
       </c>
       <c r="B121" s="2">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>142</v>
@@ -13721,8 +13721,8 @@
         <v>0</v>
       </c>
       <c r="K121" s="2"/>
-      <c r="L121" s="2">
-        <v>1000011</v>
+      <c r="L121" s="3">
+        <v>800001011</v>
       </c>
       <c r="M121" s="2">
         <v>1</v>
@@ -13778,17 +13778,17 @@
       <c r="AD121" s="2">
         <v>10000</v>
       </c>
-      <c r="AE121" s="2">
+      <c r="AE121" s="3">
         <v>0</v>
       </c>
       <c r="AF121" s="8">
         <v>40</v>
       </c>
       <c r="AG121" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH121" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI121" s="8">
         <v>0</v>
@@ -13802,7 +13802,7 @@
         <v>52101</v>
       </c>
       <c r="B122" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C122" s="3" t="s">
         <v>108</v>
@@ -13882,7 +13882,7 @@
         <v>10000</v>
       </c>
       <c r="AE122" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF122" s="8">
         <v>40</v>
@@ -13905,7 +13905,7 @@
         <v>52102</v>
       </c>
       <c r="B123" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C123" s="3" t="s">
         <v>114</v>
@@ -13985,13 +13985,13 @@
         <v>10000</v>
       </c>
       <c r="AE123" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF123" s="8">
         <v>40</v>
       </c>
       <c r="AG123" s="8">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="AH123" s="8">
         <v>10000</v>
@@ -14008,7 +14008,7 @@
         <v>52103</v>
       </c>
       <c r="B124" s="2">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>117</v>
@@ -14086,17 +14086,17 @@
       <c r="AD124" s="2">
         <v>10000</v>
       </c>
-      <c r="AE124" s="2">
-        <v>25010001</v>
+      <c r="AE124" s="3">
+        <v>0</v>
       </c>
       <c r="AF124" s="8">
         <v>40</v>
       </c>
       <c r="AG124" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH124" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI124" s="8">
         <v>0</v>
@@ -14110,7 +14110,7 @@
         <v>52104</v>
       </c>
       <c r="B125" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C125" s="3" t="s">
         <v>118</v>
@@ -14190,7 +14190,7 @@
         <v>10000</v>
       </c>
       <c r="AE125" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF125" s="8">
         <v>40</v>
@@ -14213,7 +14213,7 @@
         <v>52105</v>
       </c>
       <c r="B126" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C126" s="3" t="s">
         <v>120</v>
@@ -14293,7 +14293,7 @@
         <v>10000</v>
       </c>
       <c r="AE126" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF126" s="8">
         <v>40</v>
@@ -14316,7 +14316,7 @@
         <v>52106</v>
       </c>
       <c r="B127" s="2">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>123</v>
@@ -14337,8 +14337,8 @@
         <v>0</v>
       </c>
       <c r="K127" s="2"/>
-      <c r="L127" s="2">
-        <v>1000010</v>
+      <c r="L127" s="3">
+        <v>800001011</v>
       </c>
       <c r="M127" s="2">
         <v>1</v>
@@ -14394,17 +14394,17 @@
       <c r="AD127" s="2">
         <v>10000</v>
       </c>
-      <c r="AE127" s="2">
-        <v>25010001</v>
+      <c r="AE127" s="3">
+        <v>0</v>
       </c>
       <c r="AF127" s="8">
         <v>40</v>
       </c>
       <c r="AG127" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH127" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI127" s="8">
         <v>0</v>
@@ -14418,7 +14418,7 @@
         <v>52107</v>
       </c>
       <c r="B128" s="2">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>125</v>
@@ -14498,17 +14498,17 @@
       <c r="AD128" s="2">
         <v>10000</v>
       </c>
-      <c r="AE128" s="2">
-        <v>25010001</v>
+      <c r="AE128" s="3">
+        <v>0</v>
       </c>
       <c r="AF128" s="8">
         <v>40</v>
       </c>
       <c r="AG128" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH128" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI128" s="8">
         <v>0</v>
@@ -14522,7 +14522,7 @@
         <v>52108</v>
       </c>
       <c r="B129" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C129" s="3" t="s">
         <v>126</v>
@@ -14602,16 +14602,16 @@
         <v>10000</v>
       </c>
       <c r="AE129" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF129" s="8">
         <v>40</v>
       </c>
       <c r="AG129" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH129" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI129" s="8">
         <v>0</v>
@@ -14625,7 +14625,7 @@
         <v>52109</v>
       </c>
       <c r="B130" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C130" s="3" t="s">
         <v>128</v>
@@ -14705,16 +14705,16 @@
         <v>10000</v>
       </c>
       <c r="AE130" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF130" s="8">
         <v>40</v>
       </c>
       <c r="AG130" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH130" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI130" s="8">
         <v>0</v>
@@ -14728,7 +14728,7 @@
         <v>52110</v>
       </c>
       <c r="B131" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C131" s="3" t="s">
         <v>130</v>
@@ -14808,16 +14808,16 @@
         <v>10000</v>
       </c>
       <c r="AE131" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF131" s="8">
         <v>40</v>
       </c>
       <c r="AG131" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH131" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI131" s="8">
         <v>0</v>
@@ -14831,7 +14831,7 @@
         <v>52111</v>
       </c>
       <c r="B132" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C132" s="3" t="s">
         <v>132</v>
@@ -14911,16 +14911,16 @@
         <v>10000</v>
       </c>
       <c r="AE132" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF132" s="8">
         <v>40</v>
       </c>
       <c r="AG132" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH132" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI132" s="8">
         <v>0</v>
@@ -14934,7 +14934,7 @@
         <v>52112</v>
       </c>
       <c r="B133" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C133" s="3" t="s">
         <v>134</v>
@@ -15014,16 +15014,16 @@
         <v>10000</v>
       </c>
       <c r="AE133" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF133" s="8">
         <v>40</v>
       </c>
       <c r="AG133" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH133" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI133" s="8">
         <v>0</v>
@@ -15037,7 +15037,7 @@
         <v>52113</v>
       </c>
       <c r="B134" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C134" s="3" t="s">
         <v>136</v>
@@ -15117,16 +15117,16 @@
         <v>10000</v>
       </c>
       <c r="AE134" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF134" s="8">
         <v>40</v>
       </c>
       <c r="AG134" s="8">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="AH134" s="8">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="AI134" s="8">
         <v>40</v>
@@ -15140,7 +15140,7 @@
         <v>52114</v>
       </c>
       <c r="B135" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C135" s="3" t="s">
         <v>140</v>
@@ -15226,10 +15226,10 @@
         <v>40</v>
       </c>
       <c r="AG135" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH135" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI135" s="8">
         <v>0</v>
@@ -15243,7 +15243,7 @@
         <v>52115</v>
       </c>
       <c r="B136" s="2">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>142</v>
@@ -15264,8 +15264,8 @@
         <v>0</v>
       </c>
       <c r="K136" s="2"/>
-      <c r="L136" s="2">
-        <v>1000011</v>
+      <c r="L136" s="3">
+        <v>800001011</v>
       </c>
       <c r="M136" s="2">
         <v>1</v>
@@ -15321,17 +15321,17 @@
       <c r="AD136" s="2">
         <v>10000</v>
       </c>
-      <c r="AE136" s="2">
+      <c r="AE136" s="3">
         <v>0</v>
       </c>
       <c r="AF136" s="8">
         <v>40</v>
       </c>
       <c r="AG136" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH136" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI136" s="8">
         <v>0</v>
@@ -15345,7 +15345,7 @@
         <v>61101</v>
       </c>
       <c r="B137" s="3">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C137" s="3" t="s">
         <v>108</v>
@@ -15425,7 +15425,7 @@
         <v>10000</v>
       </c>
       <c r="AE137" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF137" s="8">
         <v>40</v>
@@ -15448,7 +15448,7 @@
         <v>61102</v>
       </c>
       <c r="B138" s="3">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C138" s="3" t="s">
         <v>114</v>
@@ -15528,13 +15528,13 @@
         <v>10000</v>
       </c>
       <c r="AE138" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF138" s="8">
         <v>40</v>
       </c>
       <c r="AG138" s="8">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="AH138" s="8">
         <v>10000</v>
@@ -15550,8 +15550,8 @@
       <c r="A139" s="3">
         <v>61103</v>
       </c>
-      <c r="B139" s="2">
-        <v>30</v>
+      <c r="B139" s="3">
+        <v>6</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>117</v>
@@ -15629,17 +15629,17 @@
       <c r="AD139" s="2">
         <v>10000</v>
       </c>
-      <c r="AE139" s="2">
-        <v>25010001</v>
+      <c r="AE139" s="3">
+        <v>0</v>
       </c>
       <c r="AF139" s="8">
         <v>40</v>
       </c>
       <c r="AG139" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH139" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI139" s="8">
         <v>0</v>
@@ -15653,7 +15653,7 @@
         <v>61104</v>
       </c>
       <c r="B140" s="3">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C140" s="3" t="s">
         <v>118</v>
@@ -15733,7 +15733,7 @@
         <v>10000</v>
       </c>
       <c r="AE140" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF140" s="8">
         <v>40</v>
@@ -15756,7 +15756,7 @@
         <v>61105</v>
       </c>
       <c r="B141" s="3">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C141" s="3" t="s">
         <v>120</v>
@@ -15836,7 +15836,7 @@
         <v>10000</v>
       </c>
       <c r="AE141" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF141" s="8">
         <v>40</v>
@@ -15858,8 +15858,8 @@
       <c r="A142" s="3">
         <v>61106</v>
       </c>
-      <c r="B142" s="2">
-        <v>30</v>
+      <c r="B142" s="3">
+        <v>6</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>123</v>
@@ -15880,8 +15880,8 @@
         <v>0</v>
       </c>
       <c r="K142" s="2"/>
-      <c r="L142" s="2">
-        <v>1000010</v>
+      <c r="L142" s="3">
+        <v>800001011</v>
       </c>
       <c r="M142" s="2">
         <v>1</v>
@@ -15937,17 +15937,17 @@
       <c r="AD142" s="2">
         <v>10000</v>
       </c>
-      <c r="AE142" s="2">
-        <v>25010001</v>
+      <c r="AE142" s="3">
+        <v>0</v>
       </c>
       <c r="AF142" s="8">
         <v>40</v>
       </c>
       <c r="AG142" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH142" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI142" s="8">
         <v>0</v>
@@ -15960,8 +15960,8 @@
       <c r="A143" s="3">
         <v>61107</v>
       </c>
-      <c r="B143" s="2">
-        <v>30</v>
+      <c r="B143" s="3">
+        <v>6</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>125</v>
@@ -16041,17 +16041,17 @@
       <c r="AD143" s="2">
         <v>10000</v>
       </c>
-      <c r="AE143" s="2">
-        <v>25010001</v>
+      <c r="AE143" s="3">
+        <v>0</v>
       </c>
       <c r="AF143" s="8">
         <v>40</v>
       </c>
       <c r="AG143" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH143" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI143" s="8">
         <v>0</v>
@@ -16065,7 +16065,7 @@
         <v>61108</v>
       </c>
       <c r="B144" s="3">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C144" s="3" t="s">
         <v>126</v>
@@ -16145,16 +16145,16 @@
         <v>10000</v>
       </c>
       <c r="AE144" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF144" s="8">
         <v>40</v>
       </c>
       <c r="AG144" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH144" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI144" s="8">
         <v>0</v>
@@ -16168,7 +16168,7 @@
         <v>61109</v>
       </c>
       <c r="B145" s="3">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C145" s="3" t="s">
         <v>128</v>
@@ -16248,16 +16248,16 @@
         <v>10000</v>
       </c>
       <c r="AE145" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF145" s="8">
         <v>40</v>
       </c>
       <c r="AG145" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH145" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI145" s="8">
         <v>0</v>
@@ -16271,7 +16271,7 @@
         <v>61110</v>
       </c>
       <c r="B146" s="3">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C146" s="3" t="s">
         <v>130</v>
@@ -16351,16 +16351,16 @@
         <v>10000</v>
       </c>
       <c r="AE146" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF146" s="8">
         <v>40</v>
       </c>
       <c r="AG146" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH146" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI146" s="8">
         <v>0</v>
@@ -16374,7 +16374,7 @@
         <v>61111</v>
       </c>
       <c r="B147" s="3">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C147" s="3" t="s">
         <v>132</v>
@@ -16454,16 +16454,16 @@
         <v>10000</v>
       </c>
       <c r="AE147" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF147" s="8">
         <v>40</v>
       </c>
       <c r="AG147" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH147" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI147" s="8">
         <v>0</v>
@@ -16477,7 +16477,7 @@
         <v>61112</v>
       </c>
       <c r="B148" s="3">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C148" s="3" t="s">
         <v>134</v>
@@ -16557,16 +16557,16 @@
         <v>10000</v>
       </c>
       <c r="AE148" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF148" s="8">
         <v>40</v>
       </c>
       <c r="AG148" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH148" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI148" s="8">
         <v>0</v>
@@ -16580,7 +16580,7 @@
         <v>61113</v>
       </c>
       <c r="B149" s="3">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C149" s="3" t="s">
         <v>136</v>
@@ -16660,16 +16660,16 @@
         <v>10000</v>
       </c>
       <c r="AE149" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF149" s="8">
         <v>40</v>
       </c>
       <c r="AG149" s="8">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="AH149" s="8">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="AI149" s="8">
         <v>40</v>
@@ -16683,7 +16683,7 @@
         <v>61114</v>
       </c>
       <c r="B150" s="3">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C150" s="3" t="s">
         <v>140</v>
@@ -16769,10 +16769,10 @@
         <v>40</v>
       </c>
       <c r="AG150" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH150" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI150" s="8">
         <v>0</v>
@@ -16785,8 +16785,8 @@
       <c r="A151" s="3">
         <v>61115</v>
       </c>
-      <c r="B151" s="2">
-        <v>30</v>
+      <c r="B151" s="3">
+        <v>6</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>142</v>
@@ -16807,8 +16807,8 @@
         <v>0</v>
       </c>
       <c r="K151" s="2"/>
-      <c r="L151" s="2">
-        <v>1000011</v>
+      <c r="L151" s="3">
+        <v>800001011</v>
       </c>
       <c r="M151" s="2">
         <v>1</v>
@@ -16864,17 +16864,17 @@
       <c r="AD151" s="2">
         <v>10000</v>
       </c>
-      <c r="AE151" s="2">
+      <c r="AE151" s="3">
         <v>0</v>
       </c>
       <c r="AF151" s="8">
         <v>40</v>
       </c>
       <c r="AG151" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH151" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI151" s="8">
         <v>0</v>
@@ -16888,7 +16888,7 @@
         <v>62101</v>
       </c>
       <c r="B152" s="3">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C152" s="3" t="s">
         <v>108</v>
@@ -16968,7 +16968,7 @@
         <v>10000</v>
       </c>
       <c r="AE152" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF152" s="8">
         <v>40</v>
@@ -16991,7 +16991,7 @@
         <v>62102</v>
       </c>
       <c r="B153" s="3">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C153" s="3" t="s">
         <v>114</v>
@@ -17071,13 +17071,13 @@
         <v>10000</v>
       </c>
       <c r="AE153" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF153" s="8">
         <v>40</v>
       </c>
       <c r="AG153" s="8">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="AH153" s="8">
         <v>10000</v>
@@ -17093,8 +17093,8 @@
       <c r="A154" s="3">
         <v>62103</v>
       </c>
-      <c r="B154" s="2">
-        <v>30</v>
+      <c r="B154" s="3">
+        <v>6</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>117</v>
@@ -17172,17 +17172,17 @@
       <c r="AD154" s="2">
         <v>10000</v>
       </c>
-      <c r="AE154" s="2">
-        <v>25010001</v>
+      <c r="AE154" s="3">
+        <v>0</v>
       </c>
       <c r="AF154" s="8">
         <v>40</v>
       </c>
       <c r="AG154" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH154" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI154" s="8">
         <v>0</v>
@@ -17196,7 +17196,7 @@
         <v>62104</v>
       </c>
       <c r="B155" s="3">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C155" s="3" t="s">
         <v>118</v>
@@ -17276,7 +17276,7 @@
         <v>10000</v>
       </c>
       <c r="AE155" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF155" s="8">
         <v>40</v>
@@ -17299,7 +17299,7 @@
         <v>62105</v>
       </c>
       <c r="B156" s="3">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C156" s="3" t="s">
         <v>120</v>
@@ -17379,7 +17379,7 @@
         <v>10000</v>
       </c>
       <c r="AE156" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF156" s="8">
         <v>40</v>
@@ -17401,8 +17401,8 @@
       <c r="A157" s="3">
         <v>62106</v>
       </c>
-      <c r="B157" s="2">
-        <v>30</v>
+      <c r="B157" s="3">
+        <v>6</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>123</v>
@@ -17423,8 +17423,8 @@
         <v>0</v>
       </c>
       <c r="K157" s="2"/>
-      <c r="L157" s="2">
-        <v>1000010</v>
+      <c r="L157" s="3">
+        <v>800001011</v>
       </c>
       <c r="M157" s="2">
         <v>1</v>
@@ -17480,17 +17480,17 @@
       <c r="AD157" s="2">
         <v>10000</v>
       </c>
-      <c r="AE157" s="2">
-        <v>25010001</v>
+      <c r="AE157" s="3">
+        <v>0</v>
       </c>
       <c r="AF157" s="8">
         <v>40</v>
       </c>
       <c r="AG157" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH157" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI157" s="8">
         <v>0</v>
@@ -17503,8 +17503,8 @@
       <c r="A158" s="3">
         <v>62107</v>
       </c>
-      <c r="B158" s="2">
-        <v>30</v>
+      <c r="B158" s="3">
+        <v>6</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>125</v>
@@ -17584,17 +17584,17 @@
       <c r="AD158" s="2">
         <v>10000</v>
       </c>
-      <c r="AE158" s="2">
-        <v>25010001</v>
+      <c r="AE158" s="3">
+        <v>0</v>
       </c>
       <c r="AF158" s="8">
         <v>40</v>
       </c>
       <c r="AG158" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH158" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI158" s="8">
         <v>0</v>
@@ -17608,7 +17608,7 @@
         <v>62108</v>
       </c>
       <c r="B159" s="3">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C159" s="3" t="s">
         <v>126</v>
@@ -17688,16 +17688,16 @@
         <v>10000</v>
       </c>
       <c r="AE159" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF159" s="8">
         <v>40</v>
       </c>
       <c r="AG159" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH159" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI159" s="8">
         <v>0</v>
@@ -17711,7 +17711,7 @@
         <v>62109</v>
       </c>
       <c r="B160" s="3">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C160" s="3" t="s">
         <v>128</v>
@@ -17791,16 +17791,16 @@
         <v>10000</v>
       </c>
       <c r="AE160" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF160" s="8">
         <v>40</v>
       </c>
       <c r="AG160" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH160" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI160" s="8">
         <v>0</v>
@@ -17814,7 +17814,7 @@
         <v>62110</v>
       </c>
       <c r="B161" s="3">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C161" s="3" t="s">
         <v>130</v>
@@ -17894,16 +17894,16 @@
         <v>10000</v>
       </c>
       <c r="AE161" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF161" s="8">
         <v>40</v>
       </c>
       <c r="AG161" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH161" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI161" s="8">
         <v>0</v>
@@ -17917,7 +17917,7 @@
         <v>62111</v>
       </c>
       <c r="B162" s="3">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C162" s="3" t="s">
         <v>132</v>
@@ -17997,16 +17997,16 @@
         <v>10000</v>
       </c>
       <c r="AE162" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF162" s="8">
         <v>40</v>
       </c>
       <c r="AG162" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH162" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI162" s="8">
         <v>0</v>
@@ -18020,7 +18020,7 @@
         <v>62112</v>
       </c>
       <c r="B163" s="3">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C163" s="3" t="s">
         <v>134</v>
@@ -18100,16 +18100,16 @@
         <v>10000</v>
       </c>
       <c r="AE163" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF163" s="8">
         <v>40</v>
       </c>
       <c r="AG163" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH163" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI163" s="8">
         <v>0</v>
@@ -18123,7 +18123,7 @@
         <v>62113</v>
       </c>
       <c r="B164" s="3">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C164" s="3" t="s">
         <v>136</v>
@@ -18203,16 +18203,16 @@
         <v>10000</v>
       </c>
       <c r="AE164" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF164" s="8">
         <v>40</v>
       </c>
       <c r="AG164" s="8">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="AH164" s="8">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="AI164" s="8">
         <v>40</v>
@@ -18226,7 +18226,7 @@
         <v>62114</v>
       </c>
       <c r="B165" s="3">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C165" s="3" t="s">
         <v>140</v>
@@ -18312,10 +18312,10 @@
         <v>40</v>
       </c>
       <c r="AG165" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH165" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI165" s="8">
         <v>0</v>
@@ -18328,8 +18328,8 @@
       <c r="A166" s="3">
         <v>62115</v>
       </c>
-      <c r="B166" s="2">
-        <v>30</v>
+      <c r="B166" s="3">
+        <v>6</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>142</v>
@@ -18350,8 +18350,8 @@
         <v>0</v>
       </c>
       <c r="K166" s="2"/>
-      <c r="L166" s="2">
-        <v>1000011</v>
+      <c r="L166" s="3">
+        <v>800001011</v>
       </c>
       <c r="M166" s="2">
         <v>1</v>
@@ -18407,17 +18407,17 @@
       <c r="AD166" s="2">
         <v>10000</v>
       </c>
-      <c r="AE166" s="2">
+      <c r="AE166" s="3">
         <v>0</v>
       </c>
       <c r="AF166" s="8">
         <v>40</v>
       </c>
       <c r="AG166" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH166" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI166" s="8">
         <v>0</v>
@@ -18431,7 +18431,7 @@
         <v>71101</v>
       </c>
       <c r="B167" s="3">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="C167" s="3" t="s">
         <v>108</v>
@@ -18511,7 +18511,7 @@
         <v>10000</v>
       </c>
       <c r="AE167" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF167" s="8">
         <v>40</v>
@@ -18534,7 +18534,7 @@
         <v>71102</v>
       </c>
       <c r="B168" s="3">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="C168" s="3" t="s">
         <v>114</v>
@@ -18614,13 +18614,13 @@
         <v>10000</v>
       </c>
       <c r="AE168" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF168" s="8">
         <v>40</v>
       </c>
       <c r="AG168" s="8">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="AH168" s="8">
         <v>10000</v>
@@ -18636,8 +18636,8 @@
       <c r="A169" s="3">
         <v>71103</v>
       </c>
-      <c r="B169" s="2">
-        <v>30</v>
+      <c r="B169" s="3">
+        <v>7</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>117</v>
@@ -18715,17 +18715,17 @@
       <c r="AD169" s="2">
         <v>10000</v>
       </c>
-      <c r="AE169" s="2">
-        <v>25010001</v>
+      <c r="AE169" s="3">
+        <v>0</v>
       </c>
       <c r="AF169" s="8">
         <v>40</v>
       </c>
       <c r="AG169" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH169" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI169" s="8">
         <v>0</v>
@@ -18739,7 +18739,7 @@
         <v>71104</v>
       </c>
       <c r="B170" s="3">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="C170" s="3" t="s">
         <v>118</v>
@@ -18819,7 +18819,7 @@
         <v>10000</v>
       </c>
       <c r="AE170" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF170" s="8">
         <v>40</v>
@@ -18842,7 +18842,7 @@
         <v>71105</v>
       </c>
       <c r="B171" s="3">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="C171" s="3" t="s">
         <v>120</v>
@@ -18922,7 +18922,7 @@
         <v>10000</v>
       </c>
       <c r="AE171" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF171" s="8">
         <v>40</v>
@@ -18944,8 +18944,8 @@
       <c r="A172" s="3">
         <v>71106</v>
       </c>
-      <c r="B172" s="2">
-        <v>30</v>
+      <c r="B172" s="3">
+        <v>7</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>123</v>
@@ -18966,8 +18966,8 @@
         <v>0</v>
       </c>
       <c r="K172" s="2"/>
-      <c r="L172" s="2">
-        <v>1000010</v>
+      <c r="L172" s="3">
+        <v>800001011</v>
       </c>
       <c r="M172" s="2">
         <v>1</v>
@@ -19023,17 +19023,17 @@
       <c r="AD172" s="2">
         <v>10000</v>
       </c>
-      <c r="AE172" s="2">
-        <v>25010001</v>
+      <c r="AE172" s="3">
+        <v>0</v>
       </c>
       <c r="AF172" s="8">
         <v>40</v>
       </c>
       <c r="AG172" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH172" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI172" s="8">
         <v>0</v>
@@ -19046,8 +19046,8 @@
       <c r="A173" s="3">
         <v>71107</v>
       </c>
-      <c r="B173" s="2">
-        <v>30</v>
+      <c r="B173" s="3">
+        <v>7</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>125</v>
@@ -19127,17 +19127,17 @@
       <c r="AD173" s="2">
         <v>10000</v>
       </c>
-      <c r="AE173" s="2">
-        <v>25010001</v>
+      <c r="AE173" s="3">
+        <v>0</v>
       </c>
       <c r="AF173" s="8">
         <v>40</v>
       </c>
       <c r="AG173" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH173" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI173" s="8">
         <v>0</v>
@@ -19151,7 +19151,7 @@
         <v>71108</v>
       </c>
       <c r="B174" s="3">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="C174" s="3" t="s">
         <v>126</v>
@@ -19231,16 +19231,16 @@
         <v>10000</v>
       </c>
       <c r="AE174" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF174" s="8">
         <v>40</v>
       </c>
       <c r="AG174" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH174" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI174" s="8">
         <v>0</v>
@@ -19254,7 +19254,7 @@
         <v>71109</v>
       </c>
       <c r="B175" s="3">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="C175" s="3" t="s">
         <v>128</v>
@@ -19334,16 +19334,16 @@
         <v>10000</v>
       </c>
       <c r="AE175" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF175" s="8">
         <v>40</v>
       </c>
       <c r="AG175" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH175" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI175" s="8">
         <v>0</v>
@@ -19357,7 +19357,7 @@
         <v>71110</v>
       </c>
       <c r="B176" s="3">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="C176" s="3" t="s">
         <v>130</v>
@@ -19437,16 +19437,16 @@
         <v>10000</v>
       </c>
       <c r="AE176" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF176" s="8">
         <v>40</v>
       </c>
       <c r="AG176" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH176" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI176" s="8">
         <v>0</v>
@@ -19460,7 +19460,7 @@
         <v>71111</v>
       </c>
       <c r="B177" s="3">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="C177" s="3" t="s">
         <v>132</v>
@@ -19540,16 +19540,16 @@
         <v>10000</v>
       </c>
       <c r="AE177" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF177" s="8">
         <v>40</v>
       </c>
       <c r="AG177" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH177" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI177" s="8">
         <v>0</v>
@@ -19563,7 +19563,7 @@
         <v>71112</v>
       </c>
       <c r="B178" s="3">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="C178" s="3" t="s">
         <v>134</v>
@@ -19643,16 +19643,16 @@
         <v>10000</v>
       </c>
       <c r="AE178" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF178" s="8">
         <v>40</v>
       </c>
       <c r="AG178" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH178" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI178" s="8">
         <v>0</v>
@@ -19666,7 +19666,7 @@
         <v>71113</v>
       </c>
       <c r="B179" s="3">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="C179" s="3" t="s">
         <v>136</v>
@@ -19746,16 +19746,16 @@
         <v>10000</v>
       </c>
       <c r="AE179" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF179" s="8">
         <v>40</v>
       </c>
       <c r="AG179" s="8">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="AH179" s="8">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="AI179" s="8">
         <v>40</v>
@@ -19769,7 +19769,7 @@
         <v>71114</v>
       </c>
       <c r="B180" s="3">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="C180" s="3" t="s">
         <v>140</v>
@@ -19855,10 +19855,10 @@
         <v>40</v>
       </c>
       <c r="AG180" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH180" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI180" s="8">
         <v>0</v>
@@ -19871,8 +19871,8 @@
       <c r="A181" s="3">
         <v>71115</v>
       </c>
-      <c r="B181" s="2">
-        <v>30</v>
+      <c r="B181" s="3">
+        <v>7</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>142</v>
@@ -19893,8 +19893,8 @@
         <v>0</v>
       </c>
       <c r="K181" s="2"/>
-      <c r="L181" s="2">
-        <v>1000011</v>
+      <c r="L181" s="3">
+        <v>800001011</v>
       </c>
       <c r="M181" s="2">
         <v>1</v>
@@ -19950,17 +19950,17 @@
       <c r="AD181" s="2">
         <v>10000</v>
       </c>
-      <c r="AE181" s="2">
+      <c r="AE181" s="3">
         <v>0</v>
       </c>
       <c r="AF181" s="8">
         <v>40</v>
       </c>
       <c r="AG181" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH181" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI181" s="8">
         <v>0</v>
@@ -19974,7 +19974,7 @@
         <v>72101</v>
       </c>
       <c r="B182" s="3">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="C182" s="3" t="s">
         <v>108</v>
@@ -20054,7 +20054,7 @@
         <v>10000</v>
       </c>
       <c r="AE182" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF182" s="8">
         <v>40</v>
@@ -20077,7 +20077,7 @@
         <v>72102</v>
       </c>
       <c r="B183" s="3">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="C183" s="3" t="s">
         <v>114</v>
@@ -20157,13 +20157,13 @@
         <v>10000</v>
       </c>
       <c r="AE183" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF183" s="8">
         <v>40</v>
       </c>
       <c r="AG183" s="8">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="AH183" s="8">
         <v>10000</v>
@@ -20179,8 +20179,8 @@
       <c r="A184" s="3">
         <v>72103</v>
       </c>
-      <c r="B184" s="2">
-        <v>30</v>
+      <c r="B184" s="3">
+        <v>7</v>
       </c>
       <c r="C184" s="2" t="s">
         <v>117</v>
@@ -20258,17 +20258,17 @@
       <c r="AD184" s="2">
         <v>10000</v>
       </c>
-      <c r="AE184" s="2">
-        <v>25010001</v>
+      <c r="AE184" s="3">
+        <v>0</v>
       </c>
       <c r="AF184" s="8">
         <v>40</v>
       </c>
       <c r="AG184" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH184" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI184" s="8">
         <v>0</v>
@@ -20282,7 +20282,7 @@
         <v>72104</v>
       </c>
       <c r="B185" s="3">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="C185" s="3" t="s">
         <v>118</v>
@@ -20362,7 +20362,7 @@
         <v>10000</v>
       </c>
       <c r="AE185" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF185" s="8">
         <v>40</v>
@@ -20385,7 +20385,7 @@
         <v>72105</v>
       </c>
       <c r="B186" s="3">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="C186" s="3" t="s">
         <v>120</v>
@@ -20465,7 +20465,7 @@
         <v>10000</v>
       </c>
       <c r="AE186" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF186" s="8">
         <v>40</v>
@@ -20487,8 +20487,8 @@
       <c r="A187" s="3">
         <v>72106</v>
       </c>
-      <c r="B187" s="2">
-        <v>30</v>
+      <c r="B187" s="3">
+        <v>7</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>123</v>
@@ -20509,8 +20509,8 @@
         <v>0</v>
       </c>
       <c r="K187" s="2"/>
-      <c r="L187" s="2">
-        <v>1000010</v>
+      <c r="L187" s="3">
+        <v>800001011</v>
       </c>
       <c r="M187" s="2">
         <v>1</v>
@@ -20566,17 +20566,17 @@
       <c r="AD187" s="2">
         <v>10000</v>
       </c>
-      <c r="AE187" s="2">
-        <v>25010001</v>
+      <c r="AE187" s="3">
+        <v>0</v>
       </c>
       <c r="AF187" s="8">
         <v>40</v>
       </c>
       <c r="AG187" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH187" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI187" s="8">
         <v>0</v>
@@ -20589,8 +20589,8 @@
       <c r="A188" s="3">
         <v>72107</v>
       </c>
-      <c r="B188" s="2">
-        <v>30</v>
+      <c r="B188" s="3">
+        <v>7</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>125</v>
@@ -20670,17 +20670,17 @@
       <c r="AD188" s="2">
         <v>10000</v>
       </c>
-      <c r="AE188" s="2">
-        <v>25010001</v>
+      <c r="AE188" s="3">
+        <v>0</v>
       </c>
       <c r="AF188" s="8">
         <v>40</v>
       </c>
       <c r="AG188" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH188" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI188" s="8">
         <v>0</v>
@@ -20694,7 +20694,7 @@
         <v>72108</v>
       </c>
       <c r="B189" s="3">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="C189" s="3" t="s">
         <v>126</v>
@@ -20774,16 +20774,16 @@
         <v>10000</v>
       </c>
       <c r="AE189" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF189" s="8">
         <v>40</v>
       </c>
       <c r="AG189" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH189" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI189" s="8">
         <v>0</v>
@@ -20797,7 +20797,7 @@
         <v>72109</v>
       </c>
       <c r="B190" s="3">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="C190" s="3" t="s">
         <v>128</v>
@@ -20877,16 +20877,16 @@
         <v>10000</v>
       </c>
       <c r="AE190" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF190" s="8">
         <v>40</v>
       </c>
       <c r="AG190" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH190" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI190" s="8">
         <v>0</v>
@@ -20900,7 +20900,7 @@
         <v>72110</v>
       </c>
       <c r="B191" s="3">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="C191" s="3" t="s">
         <v>130</v>
@@ -20980,16 +20980,16 @@
         <v>10000</v>
       </c>
       <c r="AE191" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF191" s="8">
         <v>40</v>
       </c>
       <c r="AG191" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH191" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI191" s="8">
         <v>0</v>
@@ -21003,7 +21003,7 @@
         <v>72111</v>
       </c>
       <c r="B192" s="3">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="C192" s="3" t="s">
         <v>132</v>
@@ -21083,16 +21083,16 @@
         <v>10000</v>
       </c>
       <c r="AE192" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF192" s="8">
         <v>40</v>
       </c>
       <c r="AG192" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH192" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI192" s="8">
         <v>0</v>
@@ -21106,7 +21106,7 @@
         <v>72112</v>
       </c>
       <c r="B193" s="3">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="C193" s="3" t="s">
         <v>134</v>
@@ -21186,16 +21186,16 @@
         <v>10000</v>
       </c>
       <c r="AE193" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF193" s="8">
         <v>40</v>
       </c>
       <c r="AG193" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH193" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI193" s="8">
         <v>0</v>
@@ -21209,7 +21209,7 @@
         <v>72113</v>
       </c>
       <c r="B194" s="3">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="C194" s="3" t="s">
         <v>136</v>
@@ -21289,16 +21289,16 @@
         <v>10000</v>
       </c>
       <c r="AE194" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF194" s="8">
         <v>40</v>
       </c>
       <c r="AG194" s="8">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="AH194" s="8">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="AI194" s="8">
         <v>40</v>
@@ -21312,7 +21312,7 @@
         <v>72114</v>
       </c>
       <c r="B195" s="3">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="C195" s="3" t="s">
         <v>140</v>
@@ -21398,10 +21398,10 @@
         <v>40</v>
       </c>
       <c r="AG195" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH195" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI195" s="8">
         <v>0</v>
@@ -21414,8 +21414,8 @@
       <c r="A196" s="3">
         <v>72115</v>
       </c>
-      <c r="B196" s="2">
-        <v>30</v>
+      <c r="B196" s="3">
+        <v>7</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>142</v>
@@ -21436,8 +21436,8 @@
         <v>0</v>
       </c>
       <c r="K196" s="2"/>
-      <c r="L196" s="2">
-        <v>1000011</v>
+      <c r="L196" s="3">
+        <v>800001011</v>
       </c>
       <c r="M196" s="2">
         <v>1</v>
@@ -21500,10 +21500,10 @@
         <v>40</v>
       </c>
       <c r="AG196" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH196" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI196" s="8">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BC0A49A-B278-4CCA-90DF-9211ED918CF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17A2B1A6-F62F-4261-9C03-E6205367B437}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6276,7 +6276,7 @@
         <v>40</v>
       </c>
       <c r="AG48" s="8">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="AH48" s="8">
         <v>10000</v>
@@ -6378,10 +6378,10 @@
         <v>40</v>
       </c>
       <c r="AG49" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH49" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI49" s="8">
         <v>0</v>
@@ -6686,10 +6686,10 @@
         <v>40</v>
       </c>
       <c r="AG52" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH52" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI52" s="8">
         <v>0</v>
@@ -6790,10 +6790,10 @@
         <v>40</v>
       </c>
       <c r="AG53" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH53" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI53" s="8">
         <v>0</v>
@@ -6893,10 +6893,10 @@
         <v>40</v>
       </c>
       <c r="AG54" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH54" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI54" s="8">
         <v>0</v>
@@ -6996,10 +6996,10 @@
         <v>40</v>
       </c>
       <c r="AG55" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH55" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI55" s="8">
         <v>0</v>
@@ -7099,10 +7099,10 @@
         <v>40</v>
       </c>
       <c r="AG56" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH56" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI56" s="8">
         <v>0</v>
@@ -7202,10 +7202,10 @@
         <v>40</v>
       </c>
       <c r="AG57" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH57" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI57" s="8">
         <v>0</v>
@@ -7305,10 +7305,10 @@
         <v>40</v>
       </c>
       <c r="AG58" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH58" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI58" s="8">
         <v>0</v>
@@ -7408,10 +7408,10 @@
         <v>40</v>
       </c>
       <c r="AG59" s="8">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="AH59" s="8">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="AI59" s="8">
         <v>40</v>
@@ -7511,10 +7511,10 @@
         <v>40</v>
       </c>
       <c r="AG60" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH60" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI60" s="8">
         <v>0</v>
@@ -7613,10 +7613,10 @@
         <v>40</v>
       </c>
       <c r="AG61" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH61" s="8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI61" s="8">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17A2B1A6-F62F-4261-9C03-E6205367B437}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AEAAE18-5BF7-41E9-ABD1-4211787D8EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2235" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2235" uniqueCount="241">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -756,18 +756,15 @@
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
-    <t>骷髅1</t>
+    <t>骷髅3</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
-    <t>骷髅2</t>
+    <t>狼3</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
-    <t>骷髅3</t>
-  </si>
-  <si>
-    <t>吸血鬼3</t>
+    <t>僵尸3</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
 </sst>
@@ -775,7 +772,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -871,6 +868,14 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -996,7 +1001,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1074,6 +1079,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -28683,14 +28694,14 @@
       <c r="K266" s="19" t="s">
         <v>238</v>
       </c>
-      <c r="L266" s="19">
-        <v>800001011</v>
+      <c r="L266" s="29">
+        <v>800001031</v>
       </c>
       <c r="M266" s="19">
         <v>1</v>
       </c>
       <c r="N266" s="21">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O266" s="19">
         <v>1</v>
@@ -28785,16 +28796,16 @@
         <v>0</v>
       </c>
       <c r="K267" s="19" t="s">
-        <v>239</v>
-      </c>
-      <c r="L267" s="19">
-        <v>800001021</v>
+        <v>238</v>
+      </c>
+      <c r="L267" s="29">
+        <v>800001031</v>
       </c>
       <c r="M267" s="19">
         <v>1</v>
       </c>
       <c r="N267" s="21">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="O267" s="19">
         <v>1</v>
@@ -28889,16 +28900,16 @@
         <v>0</v>
       </c>
       <c r="K268" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="L268" s="19">
-        <v>800001011</v>
+        <v>239</v>
+      </c>
+      <c r="L268" s="29">
+        <v>800004031</v>
       </c>
       <c r="M268" s="19">
         <v>1</v>
       </c>
       <c r="N268" s="21">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O268" s="19">
         <v>1</v>
@@ -28995,14 +29006,14 @@
       <c r="K269" s="19" t="s">
         <v>239</v>
       </c>
-      <c r="L269" s="19">
-        <v>800001021</v>
+      <c r="L269" s="29">
+        <v>800004031</v>
       </c>
       <c r="M269" s="19">
         <v>1</v>
       </c>
       <c r="N269" s="21">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="O269" s="19">
         <v>1</v>
@@ -29097,16 +29108,16 @@
         <v>0</v>
       </c>
       <c r="K270" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="L270" s="19">
-        <v>800001011</v>
+        <v>239</v>
+      </c>
+      <c r="L270" s="29">
+        <v>800004031</v>
       </c>
       <c r="M270" s="19">
         <v>1</v>
       </c>
       <c r="N270" s="21">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O270" s="19">
         <v>1</v>
@@ -29203,14 +29214,14 @@
       <c r="K271" s="19" t="s">
         <v>239</v>
       </c>
-      <c r="L271" s="19">
-        <v>800001021</v>
+      <c r="L271" s="29">
+        <v>800004031</v>
       </c>
       <c r="M271" s="19">
         <v>1</v>
       </c>
       <c r="N271" s="21">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="O271" s="19">
         <v>1</v>
@@ -29305,16 +29316,16 @@
         <v>0</v>
       </c>
       <c r="K272" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="L272" s="19">
-        <v>800001011</v>
+        <v>240</v>
+      </c>
+      <c r="L272" s="30">
+        <v>800003031</v>
       </c>
       <c r="M272" s="19">
         <v>1</v>
       </c>
       <c r="N272" s="21">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O272" s="19">
         <v>1</v>
@@ -29409,16 +29420,16 @@
         <v>0</v>
       </c>
       <c r="K273" s="19" t="s">
-        <v>239</v>
-      </c>
-      <c r="L273" s="19">
-        <v>800001021</v>
+        <v>240</v>
+      </c>
+      <c r="L273" s="30">
+        <v>800003031</v>
       </c>
       <c r="M273" s="19">
         <v>1</v>
       </c>
       <c r="N273" s="21">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="O273" s="19">
         <v>1</v>
@@ -29515,14 +29526,14 @@
       <c r="K274" s="19" t="s">
         <v>238</v>
       </c>
-      <c r="L274" s="19">
-        <v>800001011</v>
+      <c r="L274" s="29">
+        <v>800001031</v>
       </c>
       <c r="M274" s="19">
         <v>1</v>
       </c>
       <c r="N274" s="21">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O274" s="19">
         <v>1</v>
@@ -29617,16 +29628,16 @@
         <v>0</v>
       </c>
       <c r="K275" s="19" t="s">
-        <v>239</v>
-      </c>
-      <c r="L275" s="19">
-        <v>800001021</v>
+        <v>238</v>
+      </c>
+      <c r="L275" s="29">
+        <v>800001031</v>
       </c>
       <c r="M275" s="19">
         <v>1</v>
       </c>
       <c r="N275" s="21">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="O275" s="19">
         <v>1</v>
@@ -29721,16 +29732,16 @@
         <v>0</v>
       </c>
       <c r="K276" s="19" t="s">
-        <v>240</v>
-      </c>
-      <c r="L276" s="19">
+        <v>238</v>
+      </c>
+      <c r="L276" s="29">
         <v>800001031</v>
       </c>
       <c r="M276" s="19">
         <v>1</v>
       </c>
       <c r="N276" s="21">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="O276" s="19">
         <v>1</v>
@@ -29825,16 +29836,16 @@
         <v>0</v>
       </c>
       <c r="K277" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="L277" s="19">
-        <v>800011011</v>
+        <v>238</v>
+      </c>
+      <c r="L277" s="29">
+        <v>800001031</v>
       </c>
       <c r="M277" s="19">
         <v>1</v>
       </c>
       <c r="N277" s="21">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="O277" s="19">
         <v>1</v>
@@ -29929,16 +29940,16 @@
         <v>0</v>
       </c>
       <c r="K278" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="L278" s="19">
-        <v>800001011</v>
+        <v>239</v>
+      </c>
+      <c r="L278" s="29">
+        <v>800004031</v>
       </c>
       <c r="M278" s="19">
         <v>1</v>
       </c>
       <c r="N278" s="21">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O278" s="19">
         <v>1</v>
@@ -30035,14 +30046,14 @@
       <c r="K279" s="19" t="s">
         <v>239</v>
       </c>
-      <c r="L279" s="19">
-        <v>800001021</v>
+      <c r="L279" s="29">
+        <v>800004031</v>
       </c>
       <c r="M279" s="19">
         <v>1</v>
       </c>
       <c r="N279" s="21">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="O279" s="19">
         <v>1</v>
@@ -30137,16 +30148,16 @@
         <v>0</v>
       </c>
       <c r="K280" s="19" t="s">
-        <v>240</v>
-      </c>
-      <c r="L280" s="19">
-        <v>800001031</v>
+        <v>239</v>
+      </c>
+      <c r="L280" s="29">
+        <v>800004031</v>
       </c>
       <c r="M280" s="19">
         <v>1</v>
       </c>
       <c r="N280" s="21">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="O280" s="19">
         <v>1</v>
@@ -30241,16 +30252,16 @@
         <v>0</v>
       </c>
       <c r="K281" s="19" t="s">
-        <v>240</v>
-      </c>
-      <c r="L281" s="19">
-        <v>800001031</v>
+        <v>239</v>
+      </c>
+      <c r="L281" s="29">
+        <v>800004031</v>
       </c>
       <c r="M281" s="19">
         <v>1</v>
       </c>
       <c r="N281" s="21">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="O281" s="19">
         <v>1</v>
@@ -30345,16 +30356,16 @@
         <v>0</v>
       </c>
       <c r="K282" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="L282" s="19">
-        <v>800011011</v>
+        <v>239</v>
+      </c>
+      <c r="L282" s="29">
+        <v>800004031</v>
       </c>
       <c r="M282" s="19">
         <v>1</v>
       </c>
       <c r="N282" s="21">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="O282" s="19">
         <v>1</v>
@@ -30449,16 +30460,16 @@
         <v>0</v>
       </c>
       <c r="K283" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="L283" s="19">
-        <v>800011011</v>
+        <v>239</v>
+      </c>
+      <c r="L283" s="29">
+        <v>800004031</v>
       </c>
       <c r="M283" s="19">
         <v>1</v>
       </c>
       <c r="N283" s="21">
-        <v>14</v>
+        <v>150</v>
       </c>
       <c r="O283" s="19">
         <v>1</v>
@@ -30553,16 +30564,16 @@
         <v>0</v>
       </c>
       <c r="K284" s="19" t="s">
-        <v>133</v>
-      </c>
-      <c r="L284" s="19">
-        <v>800011021</v>
+        <v>239</v>
+      </c>
+      <c r="L284" s="29">
+        <v>800004031</v>
       </c>
       <c r="M284" s="19">
         <v>1</v>
       </c>
       <c r="N284" s="21">
-        <v>18</v>
+        <v>180</v>
       </c>
       <c r="O284" s="19">
         <v>1</v>
@@ -30657,16 +30668,16 @@
         <v>0</v>
       </c>
       <c r="K285" s="19" t="s">
-        <v>133</v>
-      </c>
-      <c r="L285" s="19">
-        <v>800011021</v>
+        <v>239</v>
+      </c>
+      <c r="L285" s="29">
+        <v>800004031</v>
       </c>
       <c r="M285" s="19">
         <v>1</v>
       </c>
       <c r="N285" s="21">
-        <v>45</v>
+        <v>450</v>
       </c>
       <c r="O285" s="19">
         <v>1</v>
@@ -30763,14 +30774,14 @@
       <c r="K286" s="19" t="s">
         <v>238</v>
       </c>
-      <c r="L286" s="19">
-        <v>800001011</v>
+      <c r="L286" s="29">
+        <v>800001031</v>
       </c>
       <c r="M286" s="19">
         <v>1</v>
       </c>
       <c r="N286" s="21">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O286" s="19">
         <v>1</v>
@@ -30867,14 +30878,14 @@
       <c r="K287" s="19" t="s">
         <v>238</v>
       </c>
-      <c r="L287" s="19">
-        <v>800001011</v>
+      <c r="L287" s="29">
+        <v>800001031</v>
       </c>
       <c r="M287" s="19">
         <v>1</v>
       </c>
       <c r="N287" s="21">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="O287" s="19">
         <v>1</v>
@@ -30969,16 +30980,16 @@
         <v>0</v>
       </c>
       <c r="K288" s="19" t="s">
-        <v>239</v>
-      </c>
-      <c r="L288" s="19">
-        <v>800001021</v>
+        <v>238</v>
+      </c>
+      <c r="L288" s="29">
+        <v>800001031</v>
       </c>
       <c r="M288" s="19">
         <v>1</v>
       </c>
       <c r="N288" s="21">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="O288" s="19">
         <v>1</v>
@@ -31073,16 +31084,16 @@
         <v>0</v>
       </c>
       <c r="K289" s="19" t="s">
-        <v>239</v>
-      </c>
-      <c r="L289" s="19">
-        <v>800001021</v>
+        <v>238</v>
+      </c>
+      <c r="L289" s="29">
+        <v>800001031</v>
       </c>
       <c r="M289" s="19">
         <v>1</v>
       </c>
       <c r="N289" s="21">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="O289" s="19">
         <v>1</v>
@@ -31177,16 +31188,16 @@
         <v>0</v>
       </c>
       <c r="K290" s="19" t="s">
-        <v>239</v>
-      </c>
-      <c r="L290" s="19">
-        <v>800001021</v>
+        <v>238</v>
+      </c>
+      <c r="L290" s="29">
+        <v>800001031</v>
       </c>
       <c r="M290" s="19">
         <v>1</v>
       </c>
       <c r="N290" s="21">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="O290" s="19">
         <v>1</v>
@@ -31281,16 +31292,16 @@
         <v>0</v>
       </c>
       <c r="K291" s="19" t="s">
-        <v>240</v>
-      </c>
-      <c r="L291" s="19">
+        <v>238</v>
+      </c>
+      <c r="L291" s="29">
         <v>800001031</v>
       </c>
       <c r="M291" s="19">
         <v>1</v>
       </c>
       <c r="N291" s="21">
-        <v>13</v>
+        <v>135</v>
       </c>
       <c r="O291" s="19">
         <v>1</v>
@@ -31385,16 +31396,16 @@
         <v>0</v>
       </c>
       <c r="K292" s="19" t="s">
-        <v>240</v>
-      </c>
-      <c r="L292" s="19">
+        <v>238</v>
+      </c>
+      <c r="L292" s="29">
         <v>800001031</v>
       </c>
       <c r="M292" s="19">
         <v>1</v>
       </c>
       <c r="N292" s="21">
-        <v>15</v>
+        <v>150</v>
       </c>
       <c r="O292" s="19">
         <v>1</v>
@@ -31489,16 +31500,16 @@
         <v>0</v>
       </c>
       <c r="K293" s="19" t="s">
-        <v>240</v>
-      </c>
-      <c r="L293" s="19">
+        <v>238</v>
+      </c>
+      <c r="L293" s="29">
         <v>800001031</v>
       </c>
       <c r="M293" s="19">
         <v>1</v>
       </c>
       <c r="N293" s="21">
-        <v>35</v>
+        <v>350</v>
       </c>
       <c r="O293" s="19">
         <v>1</v>
@@ -31593,16 +31604,16 @@
         <v>0</v>
       </c>
       <c r="K294" s="19" t="s">
-        <v>240</v>
-      </c>
-      <c r="L294" s="19">
+        <v>238</v>
+      </c>
+      <c r="L294" s="29">
         <v>800001031</v>
       </c>
       <c r="M294" s="19">
         <v>1</v>
       </c>
       <c r="N294" s="21">
-        <v>40</v>
+        <v>400</v>
       </c>
       <c r="O294" s="19">
         <v>1</v>
@@ -31697,16 +31708,16 @@
         <v>0</v>
       </c>
       <c r="K295" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="L295" s="19">
-        <v>800011011</v>
+        <v>238</v>
+      </c>
+      <c r="L295" s="29">
+        <v>800001031</v>
       </c>
       <c r="M295" s="19">
         <v>1</v>
       </c>
       <c r="N295" s="21">
-        <v>90</v>
+        <v>900</v>
       </c>
       <c r="O295" s="19">
         <v>1</v>
@@ -31801,16 +31812,16 @@
         <v>0</v>
       </c>
       <c r="K296" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="L296" s="19">
-        <v>800011011</v>
+        <v>238</v>
+      </c>
+      <c r="L296" s="29">
+        <v>800001031</v>
       </c>
       <c r="M296" s="19">
         <v>1</v>
       </c>
       <c r="N296" s="21">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="O296" s="19">
         <v>1</v>
@@ -31905,16 +31916,16 @@
         <v>0</v>
       </c>
       <c r="K297" s="19" t="s">
-        <v>133</v>
-      </c>
-      <c r="L297" s="19">
-        <v>800011021</v>
+        <v>238</v>
+      </c>
+      <c r="L297" s="29">
+        <v>800001031</v>
       </c>
       <c r="M297" s="19">
         <v>1</v>
       </c>
       <c r="N297" s="21">
-        <v>240</v>
+        <v>2400</v>
       </c>
       <c r="O297" s="19">
         <v>1</v>
@@ -32009,16 +32020,16 @@
         <v>0</v>
       </c>
       <c r="K298" s="19" t="s">
-        <v>133</v>
-      </c>
-      <c r="L298" s="19">
-        <v>800011021</v>
+        <v>238</v>
+      </c>
+      <c r="L298" s="29">
+        <v>800001031</v>
       </c>
       <c r="M298" s="19">
         <v>1</v>
       </c>
       <c r="N298" s="21">
-        <v>300</v>
+        <v>3000</v>
       </c>
       <c r="O298" s="19">
         <v>1</v>
@@ -32113,16 +32124,16 @@
         <v>0</v>
       </c>
       <c r="K299" s="19" t="s">
-        <v>133</v>
-      </c>
-      <c r="L299" s="19">
-        <v>800011021</v>
+        <v>238</v>
+      </c>
+      <c r="L299" s="29">
+        <v>800001031</v>
       </c>
       <c r="M299" s="19">
         <v>1</v>
       </c>
       <c r="N299" s="21">
-        <v>700</v>
+        <v>7000</v>
       </c>
       <c r="O299" s="19">
         <v>1</v>
@@ -32217,16 +32228,16 @@
         <v>0</v>
       </c>
       <c r="K300" s="19" t="s">
-        <v>133</v>
-      </c>
-      <c r="L300" s="19">
-        <v>800011021</v>
+        <v>238</v>
+      </c>
+      <c r="L300" s="29">
+        <v>800001031</v>
       </c>
       <c r="M300" s="19">
         <v>1</v>
       </c>
       <c r="N300" s="21">
-        <v>800</v>
+        <v>8000</v>
       </c>
       <c r="O300" s="19">
         <v>1</v>
@@ -32321,16 +32332,16 @@
         <v>0</v>
       </c>
       <c r="K301" s="19" t="s">
-        <v>241</v>
-      </c>
-      <c r="L301" s="19">
-        <v>800013031</v>
+        <v>238</v>
+      </c>
+      <c r="L301" s="29">
+        <v>800001031</v>
       </c>
       <c r="M301" s="19">
         <v>1</v>
       </c>
       <c r="N301" s="21">
-        <v>1500</v>
+        <v>15000</v>
       </c>
       <c r="O301" s="19">
         <v>1</v>
@@ -32425,16 +32436,16 @@
         <v>0</v>
       </c>
       <c r="K302" s="19" t="s">
-        <v>241</v>
-      </c>
-      <c r="L302" s="19">
-        <v>800013031</v>
+        <v>238</v>
+      </c>
+      <c r="L302" s="29">
+        <v>800001031</v>
       </c>
       <c r="M302" s="19">
         <v>1</v>
       </c>
       <c r="N302" s="21">
-        <v>3000</v>
+        <v>30000</v>
       </c>
       <c r="O302" s="19">
         <v>1</v>
@@ -32529,16 +32540,16 @@
         <v>0</v>
       </c>
       <c r="K303" s="19" t="s">
-        <v>241</v>
-      </c>
-      <c r="L303" s="19">
-        <v>800013031</v>
+        <v>238</v>
+      </c>
+      <c r="L303" s="29">
+        <v>800001031</v>
       </c>
       <c r="M303" s="19">
         <v>1</v>
       </c>
       <c r="N303" s="21">
-        <v>4800</v>
+        <v>48000</v>
       </c>
       <c r="O303" s="19">
         <v>1</v>
@@ -32633,16 +32644,16 @@
         <v>0</v>
       </c>
       <c r="K304" s="19" t="s">
-        <v>241</v>
-      </c>
-      <c r="L304" s="19">
-        <v>800013031</v>
+        <v>238</v>
+      </c>
+      <c r="L304" s="29">
+        <v>800001031</v>
       </c>
       <c r="M304" s="19">
         <v>1</v>
       </c>
       <c r="N304" s="21">
-        <v>8000</v>
+        <v>80000</v>
       </c>
       <c r="O304" s="19">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AEAAE18-5BF7-41E9-ABD1-4211787D8EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAB5830F-080A-49DD-A850-4032BCC36D83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28701,7 +28701,7 @@
         <v>1</v>
       </c>
       <c r="N266" s="21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O266" s="19">
         <v>1</v>
@@ -28805,7 +28805,7 @@
         <v>1</v>
       </c>
       <c r="N267" s="21">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="O267" s="19">
         <v>1</v>
@@ -29013,7 +29013,7 @@
         <v>1</v>
       </c>
       <c r="N269" s="21">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="O269" s="19">
         <v>1</v>
@@ -29221,7 +29221,7 @@
         <v>1</v>
       </c>
       <c r="N271" s="21">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="O271" s="19">
         <v>1</v>
@@ -29325,7 +29325,7 @@
         <v>1</v>
       </c>
       <c r="N272" s="21">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="O272" s="19">
         <v>1</v>
@@ -29429,7 +29429,7 @@
         <v>1</v>
       </c>
       <c r="N273" s="21">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="O273" s="19">
         <v>1</v>
@@ -29741,7 +29741,7 @@
         <v>1</v>
       </c>
       <c r="N276" s="21">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="O276" s="19">
         <v>1</v>
@@ -29845,7 +29845,7 @@
         <v>1</v>
       </c>
       <c r="N277" s="21">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="O277" s="19">
         <v>1</v>
@@ -30157,7 +30157,7 @@
         <v>1</v>
       </c>
       <c r="N280" s="21">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="O280" s="19">
         <v>1</v>
@@ -30261,7 +30261,7 @@
         <v>1</v>
       </c>
       <c r="N281" s="21">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="O281" s="19">
         <v>1</v>
@@ -30365,7 +30365,7 @@
         <v>1</v>
       </c>
       <c r="N282" s="21">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="O282" s="19">
         <v>1</v>
@@ -30469,7 +30469,7 @@
         <v>1</v>
       </c>
       <c r="N283" s="21">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="O283" s="19">
         <v>1</v>
@@ -30573,7 +30573,7 @@
         <v>1</v>
       </c>
       <c r="N284" s="21">
-        <v>180</v>
+        <v>350</v>
       </c>
       <c r="O284" s="19">
         <v>1</v>
@@ -30677,7 +30677,7 @@
         <v>1</v>
       </c>
       <c r="N285" s="21">
-        <v>450</v>
+        <v>900</v>
       </c>
       <c r="O285" s="19">
         <v>1</v>
@@ -31405,7 +31405,7 @@
         <v>1</v>
       </c>
       <c r="N292" s="21">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="O292" s="19">
         <v>1</v>
@@ -31509,7 +31509,7 @@
         <v>1</v>
       </c>
       <c r="N293" s="21">
-        <v>350</v>
+        <v>450</v>
       </c>
       <c r="O293" s="19">
         <v>1</v>
@@ -31613,7 +31613,7 @@
         <v>1</v>
       </c>
       <c r="N294" s="21">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="O294" s="19">
         <v>1</v>
@@ -31717,7 +31717,7 @@
         <v>1</v>
       </c>
       <c r="N295" s="21">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="O295" s="19">
         <v>1</v>
@@ -31821,7 +31821,7 @@
         <v>1</v>
       </c>
       <c r="N296" s="21">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="O296" s="19">
         <v>1</v>
@@ -31925,7 +31925,7 @@
         <v>1</v>
       </c>
       <c r="N297" s="21">
-        <v>2400</v>
+        <v>3200</v>
       </c>
       <c r="O297" s="19">
         <v>1</v>
@@ -32029,7 +32029,7 @@
         <v>1</v>
       </c>
       <c r="N298" s="21">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="O298" s="19">
         <v>1</v>
@@ -32133,7 +32133,7 @@
         <v>1</v>
       </c>
       <c r="N299" s="21">
-        <v>7000</v>
+        <v>11000</v>
       </c>
       <c r="O299" s="19">
         <v>1</v>
@@ -32237,7 +32237,7 @@
         <v>1</v>
       </c>
       <c r="N300" s="21">
-        <v>8000</v>
+        <v>12000</v>
       </c>
       <c r="O300" s="19">
         <v>1</v>
@@ -32341,7 +32341,7 @@
         <v>1</v>
       </c>
       <c r="N301" s="21">
-        <v>15000</v>
+        <v>22000</v>
       </c>
       <c r="O301" s="19">
         <v>1</v>
@@ -32445,7 +32445,7 @@
         <v>1</v>
       </c>
       <c r="N302" s="21">
-        <v>30000</v>
+        <v>50000</v>
       </c>
       <c r="O302" s="19">
         <v>1</v>
@@ -32549,7 +32549,7 @@
         <v>1</v>
       </c>
       <c r="N303" s="21">
-        <v>48000</v>
+        <v>70000</v>
       </c>
       <c r="O303" s="19">
         <v>1</v>
@@ -32653,7 +32653,7 @@
         <v>1</v>
       </c>
       <c r="N304" s="21">
-        <v>80000</v>
+        <v>120000</v>
       </c>
       <c r="O304" s="19">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07DDE2EA-0F5B-4702-8E39-5A9AAE63906F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_foe_v8" sheetId="1" r:id="rId1"/>
@@ -24,8 +30,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -33,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2237" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2244" uniqueCount="248">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -772,18 +776,20 @@
   <si>
     <t>装备分数</t>
   </si>
+  <si>
+    <t>熊3</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>4-守卫0</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="31">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -795,52 +801,61 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="5" tint="0.79985961485641"/>
+      <color theme="5" tint="0.79982909634693444"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFEE0000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -848,6 +863,7 @@
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -855,6 +871,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -862,148 +879,19 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="9"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="39">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1012,13 +900,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.349986266670736"/>
+        <fgColor theme="0" tint="-0.34998626667073579"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799676503799554"/>
+        <fgColor theme="5" tint="0.79964598529007846"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1048,192 +936,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="12">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1291,234 +999,10 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="53">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
@@ -1528,11 +1012,11 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1541,16 +1025,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1575,10 +1059,10 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="16" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="16" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1596,92 +1080,45 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="16" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="51"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="4"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="52" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="5" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="53">
+  <cellStyles count="6">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 2" xfId="49"/>
-    <cellStyle name="常规 2 2" xfId="50"/>
-    <cellStyle name="常规 3" xfId="51"/>
-    <cellStyle name="输入 2" xfId="52"/>
+    <cellStyle name="常规 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="常规 2 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="常规 3" xfId="4" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
+    <cellStyle name="输入" xfId="1" builtinId="20"/>
+    <cellStyle name="输入 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -1699,6 +1136,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1956,14 +1396,15 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AJ304"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:AJ305"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.125" style="9" customWidth="1"/>
     <col min="2" max="2" width="10.625" style="9" customWidth="1"/>
@@ -1988,7 +1429,7 @@
     <col min="37" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2020,7 +1461,7 @@
       <c r="AD1" s="3"/>
       <c r="AE1" s="3"/>
     </row>
-    <row r="2" ht="14.25" spans="1:36">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
@@ -2130,7 +1571,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" ht="14.25" spans="1:36">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A3" s="12" t="s">
         <v>9</v>
       </c>
@@ -2240,7 +1681,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" ht="25.5" customHeight="1" spans="1:36">
+    <row r="4" spans="1:36" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
         <v>45</v>
       </c>
@@ -2350,7 +1791,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:36">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>10201</v>
       </c>
@@ -2453,7 +1894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>10301</v>
       </c>
@@ -2556,7 +1997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:36">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>10302</v>
       </c>
@@ -2659,7 +2100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:36">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>10303</v>
       </c>
@@ -2762,7 +2203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>10304</v>
       </c>
@@ -2865,7 +2306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:36">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>10305</v>
       </c>
@@ -2968,7 +2409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:36">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>10306</v>
       </c>
@@ -3071,7 +2512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:36">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>10307</v>
       </c>
@@ -3174,7 +2615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:36">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>10308</v>
       </c>
@@ -3277,7 +2718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:36">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>10309</v>
       </c>
@@ -3380,7 +2821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:36">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>10310</v>
       </c>
@@ -3483,7 +2924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:36">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>10401</v>
       </c>
@@ -3586,7 +3027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:36">
+    <row r="17" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>10402</v>
       </c>
@@ -3689,7 +3130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:36">
+    <row r="18" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>10403</v>
       </c>
@@ -3792,7 +3233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:36">
+    <row r="19" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>20201</v>
       </c>
@@ -3895,7 +3336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:36">
+    <row r="20" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>20301</v>
       </c>
@@ -3998,7 +3439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:36">
+    <row r="21" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>20302</v>
       </c>
@@ -4101,7 +3542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:36">
+    <row r="22" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>20303</v>
       </c>
@@ -4204,7 +3645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:36">
+    <row r="23" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>20304</v>
       </c>
@@ -4307,7 +3748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:36">
+    <row r="24" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>20305</v>
       </c>
@@ -4410,7 +3851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:36">
+    <row r="25" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
         <v>20306</v>
       </c>
@@ -4513,7 +3954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:36">
+    <row r="26" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
         <v>20307</v>
       </c>
@@ -4616,7 +4057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:36">
+    <row r="27" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
         <v>20308</v>
       </c>
@@ -4719,7 +4160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:36">
+    <row r="28" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
         <v>20309</v>
       </c>
@@ -4822,7 +4263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:36">
+    <row r="29" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
         <v>20310</v>
       </c>
@@ -4925,7 +4366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:36">
+    <row r="30" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
         <v>20401</v>
       </c>
@@ -5028,7 +4469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:36">
+    <row r="31" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A31" s="3">
         <v>20402</v>
       </c>
@@ -5131,7 +4572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:36">
+    <row r="32" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A32" s="3">
         <v>20403</v>
       </c>
@@ -5234,7 +4675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:36">
+    <row r="33" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A33" s="3">
         <v>110201</v>
       </c>
@@ -5337,7 +4778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:36">
+    <row r="34" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A34" s="3">
         <v>110301</v>
       </c>
@@ -5440,7 +4881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:36">
+    <row r="35" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A35" s="3">
         <v>110302</v>
       </c>
@@ -5543,7 +4984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:36">
+    <row r="36" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A36" s="3">
         <v>110303</v>
       </c>
@@ -5646,7 +5087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:36">
+    <row r="37" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A37" s="3">
         <v>110304</v>
       </c>
@@ -5749,7 +5190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:36">
+    <row r="38" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A38" s="3">
         <v>110305</v>
       </c>
@@ -5852,7 +5293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:36">
+    <row r="39" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A39" s="3">
         <v>110306</v>
       </c>
@@ -5955,7 +5396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:36">
+    <row r="40" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A40" s="3">
         <v>110307</v>
       </c>
@@ -6058,7 +5499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:36">
+    <row r="41" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A41" s="3">
         <v>110308</v>
       </c>
@@ -6161,7 +5602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:36">
+    <row r="42" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A42" s="3">
         <v>110309</v>
       </c>
@@ -6264,7 +5705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:36">
+    <row r="43" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A43" s="3">
         <v>110310</v>
       </c>
@@ -6367,7 +5808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:36">
+    <row r="44" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A44" s="3">
         <v>110401</v>
       </c>
@@ -6470,7 +5911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:36">
+    <row r="45" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A45" s="3">
         <v>110402</v>
       </c>
@@ -6573,7 +6014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:36">
+    <row r="46" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A46" s="3">
         <v>110403</v>
       </c>
@@ -6676,7 +6117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" s="8" customFormat="1" spans="1:36">
+    <row r="47" spans="1:36" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A47" s="13">
         <v>11101</v>
       </c>
@@ -6779,7 +6220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:36">
+    <row r="48" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A48" s="3">
         <v>11102</v>
       </c>
@@ -6882,7 +6323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:36">
+    <row r="49" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A49" s="3">
         <v>11103</v>
       </c>
@@ -6983,7 +6424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:36">
+    <row r="50" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A50" s="3">
         <v>11104</v>
       </c>
@@ -7086,7 +6527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:36">
+    <row r="51" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A51" s="3">
         <v>11105</v>
       </c>
@@ -7189,7 +6630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" s="8" customFormat="1" spans="1:36">
+    <row r="52" spans="1:36" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A52" s="13">
         <v>11106</v>
       </c>
@@ -7292,7 +6733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:36">
+    <row r="53" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A53" s="3">
         <v>11107</v>
       </c>
@@ -7395,7 +6836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:36">
+    <row r="54" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A54" s="3">
         <v>11108</v>
       </c>
@@ -7498,7 +6939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:36">
+    <row r="55" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A55" s="3">
         <v>11109</v>
       </c>
@@ -7601,7 +7042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:36">
+    <row r="56" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A56" s="3">
         <v>11110</v>
       </c>
@@ -7704,7 +7145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:36">
+    <row r="57" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A57" s="3">
         <v>11111</v>
       </c>
@@ -7807,7 +7248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" s="8" customFormat="1" spans="1:36">
+    <row r="58" spans="1:36" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A58" s="13">
         <v>11112</v>
       </c>
@@ -7910,7 +7351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:36">
+    <row r="59" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A59" s="3">
         <v>11113</v>
       </c>
@@ -8013,7 +7454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:36">
+    <row r="60" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A60" s="3">
         <v>11114</v>
       </c>
@@ -8116,7 +7557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:36">
+    <row r="61" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A61" s="3">
         <v>11115</v>
       </c>
@@ -8217,7 +7658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" s="8" customFormat="1" spans="1:36">
+    <row r="62" spans="1:36" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A62" s="13">
         <v>21101</v>
       </c>
@@ -8320,7 +7761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:36">
+    <row r="63" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A63" s="3">
         <v>21102</v>
       </c>
@@ -8423,7 +7864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:36">
+    <row r="64" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A64" s="3">
         <v>21103</v>
       </c>
@@ -8524,7 +7965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:36">
+    <row r="65" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A65" s="3">
         <v>21104</v>
       </c>
@@ -8627,7 +8068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:36">
+    <row r="66" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A66" s="3">
         <v>21105</v>
       </c>
@@ -8730,7 +8171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" s="8" customFormat="1" spans="1:36">
+    <row r="67" spans="1:36" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A67" s="13">
         <v>21106</v>
       </c>
@@ -8833,7 +8274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" s="8" customFormat="1" spans="1:36">
+    <row r="68" spans="1:36" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A68" s="13">
         <v>21107</v>
       </c>
@@ -8936,7 +8377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:36">
+    <row r="69" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A69" s="3">
         <v>21108</v>
       </c>
@@ -9039,7 +8480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:36">
+    <row r="70" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A70" s="3">
         <v>21109</v>
       </c>
@@ -9142,7 +8583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:36">
+    <row r="71" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A71" s="3">
         <v>21110</v>
       </c>
@@ -9245,7 +8686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:36">
+    <row r="72" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A72" s="3">
         <v>21111</v>
       </c>
@@ -9348,7 +8789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:36">
+    <row r="73" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A73" s="3">
         <v>21112</v>
       </c>
@@ -9451,7 +8892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:36">
+    <row r="74" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A74" s="3">
         <v>21113</v>
       </c>
@@ -9554,7 +8995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:36">
+    <row r="75" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A75" s="3">
         <v>21114</v>
       </c>
@@ -9657,7 +9098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:36">
+    <row r="76" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A76" s="3">
         <v>21115</v>
       </c>
@@ -9758,7 +9199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:36">
+    <row r="77" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A77" s="3">
         <v>31101</v>
       </c>
@@ -9861,7 +9302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:36">
+    <row r="78" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A78" s="3">
         <v>31102</v>
       </c>
@@ -9964,7 +9405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:36">
+    <row r="79" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A79" s="3">
         <v>31103</v>
       </c>
@@ -10065,7 +9506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:36">
+    <row r="80" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A80" s="3">
         <v>31104</v>
       </c>
@@ -10168,7 +9609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:36">
+    <row r="81" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A81" s="3">
         <v>31105</v>
       </c>
@@ -10271,7 +9712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:36">
+    <row r="82" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A82" s="3">
         <v>31106</v>
       </c>
@@ -10372,7 +9813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:36">
+    <row r="83" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A83" s="3">
         <v>31107</v>
       </c>
@@ -10475,7 +9916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:36">
+    <row r="84" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A84" s="3">
         <v>31108</v>
       </c>
@@ -10578,7 +10019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:36">
+    <row r="85" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A85" s="3">
         <v>31109</v>
       </c>
@@ -10681,7 +10122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:36">
+    <row r="86" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A86" s="3">
         <v>31110</v>
       </c>
@@ -10784,7 +10225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:36">
+    <row r="87" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A87" s="3">
         <v>31111</v>
       </c>
@@ -10887,7 +10328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:36">
+    <row r="88" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A88" s="3">
         <v>31112</v>
       </c>
@@ -10990,7 +10431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:36">
+    <row r="89" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A89" s="3">
         <v>31113</v>
       </c>
@@ -11093,7 +10534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:36">
+    <row r="90" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A90" s="3">
         <v>31114</v>
       </c>
@@ -11196,7 +10637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:36">
+    <row r="91" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A91" s="3">
         <v>31115</v>
       </c>
@@ -11297,7 +10738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:36">
+    <row r="92" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A92" s="3">
         <v>41101</v>
       </c>
@@ -11400,7 +10841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:36">
+    <row r="93" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A93" s="3">
         <v>41102</v>
       </c>
@@ -11503,7 +10944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:36">
+    <row r="94" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A94" s="3">
         <v>41103</v>
       </c>
@@ -11604,7 +11045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:36">
+    <row r="95" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A95" s="3">
         <v>41104</v>
       </c>
@@ -11707,7 +11148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:36">
+    <row r="96" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A96" s="3">
         <v>41105</v>
       </c>
@@ -11810,7 +11251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:36">
+    <row r="97" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A97" s="3">
         <v>41106</v>
       </c>
@@ -11911,7 +11352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:36">
+    <row r="98" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A98" s="3">
         <v>41107</v>
       </c>
@@ -12014,7 +11455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:36">
+    <row r="99" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A99" s="3">
         <v>41108</v>
       </c>
@@ -12117,7 +11558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:36">
+    <row r="100" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A100" s="3">
         <v>41109</v>
       </c>
@@ -12220,7 +11661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:36">
+    <row r="101" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A101" s="3">
         <v>41110</v>
       </c>
@@ -12323,7 +11764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:36">
+    <row r="102" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A102" s="3">
         <v>41111</v>
       </c>
@@ -12426,7 +11867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:36">
+    <row r="103" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A103" s="3">
         <v>41112</v>
       </c>
@@ -12529,7 +11970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:36">
+    <row r="104" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A104" s="3">
         <v>41113</v>
       </c>
@@ -12632,7 +12073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:36">
+    <row r="105" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A105" s="3">
         <v>41114</v>
       </c>
@@ -12735,7 +12176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:36">
+    <row r="106" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A106" s="3">
         <v>41115</v>
       </c>
@@ -12836,7 +12277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:36">
+    <row r="107" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A107" s="3">
         <v>51101</v>
       </c>
@@ -12939,7 +12380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:36">
+    <row r="108" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A108" s="3">
         <v>51102</v>
       </c>
@@ -13042,7 +12483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:36">
+    <row r="109" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A109" s="3">
         <v>51103</v>
       </c>
@@ -13143,7 +12584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:36">
+    <row r="110" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A110" s="3">
         <v>51104</v>
       </c>
@@ -13246,7 +12687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:36">
+    <row r="111" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A111" s="3">
         <v>51105</v>
       </c>
@@ -13349,7 +12790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:36">
+    <row r="112" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A112" s="3">
         <v>51106</v>
       </c>
@@ -13450,7 +12891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:36">
+    <row r="113" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A113" s="3">
         <v>51107</v>
       </c>
@@ -13553,7 +12994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:36">
+    <row r="114" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A114" s="3">
         <v>51108</v>
       </c>
@@ -13656,7 +13097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:36">
+    <row r="115" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A115" s="3">
         <v>51109</v>
       </c>
@@ -13759,7 +13200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:36">
+    <row r="116" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A116" s="3">
         <v>51110</v>
       </c>
@@ -13862,7 +13303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:36">
+    <row r="117" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A117" s="3">
         <v>51111</v>
       </c>
@@ -13965,7 +13406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:36">
+    <row r="118" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A118" s="3">
         <v>51112</v>
       </c>
@@ -14068,7 +13509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:36">
+    <row r="119" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A119" s="3">
         <v>51113</v>
       </c>
@@ -14171,7 +13612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:36">
+    <row r="120" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A120" s="3">
         <v>51114</v>
       </c>
@@ -14274,7 +13715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:36">
+    <row r="121" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A121" s="3">
         <v>51115</v>
       </c>
@@ -14375,7 +13816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:36">
+    <row r="122" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A122" s="3">
         <v>52101</v>
       </c>
@@ -14478,7 +13919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:36">
+    <row r="123" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A123" s="3">
         <v>52102</v>
       </c>
@@ -14581,7 +14022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:36">
+    <row r="124" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A124" s="3">
         <v>52103</v>
       </c>
@@ -14682,7 +14123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:36">
+    <row r="125" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A125" s="3">
         <v>52104</v>
       </c>
@@ -14785,7 +14226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:36">
+    <row r="126" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A126" s="3">
         <v>52105</v>
       </c>
@@ -14888,7 +14329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:36">
+    <row r="127" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A127" s="3">
         <v>52106</v>
       </c>
@@ -14989,7 +14430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:36">
+    <row r="128" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A128" s="3">
         <v>52107</v>
       </c>
@@ -15092,7 +14533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:36">
+    <row r="129" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A129" s="3">
         <v>52108</v>
       </c>
@@ -15195,7 +14636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:36">
+    <row r="130" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A130" s="3">
         <v>52109</v>
       </c>
@@ -15298,7 +14739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:36">
+    <row r="131" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A131" s="3">
         <v>52110</v>
       </c>
@@ -15401,7 +14842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:36">
+    <row r="132" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A132" s="3">
         <v>52111</v>
       </c>
@@ -15504,7 +14945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:36">
+    <row r="133" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A133" s="3">
         <v>52112</v>
       </c>
@@ -15607,7 +15048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:36">
+    <row r="134" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A134" s="3">
         <v>52113</v>
       </c>
@@ -15710,7 +15151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:36">
+    <row r="135" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A135" s="3">
         <v>52114</v>
       </c>
@@ -15813,7 +15254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:36">
+    <row r="136" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A136" s="3">
         <v>52115</v>
       </c>
@@ -15914,7 +15355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:36">
+    <row r="137" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A137" s="3">
         <v>61101</v>
       </c>
@@ -16017,7 +15458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:36">
+    <row r="138" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A138" s="3">
         <v>61102</v>
       </c>
@@ -16120,7 +15561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:36">
+    <row r="139" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A139" s="3">
         <v>61103</v>
       </c>
@@ -16221,7 +15662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:36">
+    <row r="140" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A140" s="3">
         <v>61104</v>
       </c>
@@ -16324,7 +15765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:36">
+    <row r="141" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A141" s="3">
         <v>61105</v>
       </c>
@@ -16427,7 +15868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:36">
+    <row r="142" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A142" s="3">
         <v>61106</v>
       </c>
@@ -16528,7 +15969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:36">
+    <row r="143" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A143" s="3">
         <v>61107</v>
       </c>
@@ -16631,7 +16072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:36">
+    <row r="144" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A144" s="3">
         <v>61108</v>
       </c>
@@ -16734,7 +16175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:36">
+    <row r="145" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A145" s="3">
         <v>61109</v>
       </c>
@@ -16837,7 +16278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:36">
+    <row r="146" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A146" s="3">
         <v>61110</v>
       </c>
@@ -16940,7 +16381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:36">
+    <row r="147" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A147" s="3">
         <v>61111</v>
       </c>
@@ -17043,7 +16484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:36">
+    <row r="148" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A148" s="3">
         <v>61112</v>
       </c>
@@ -17146,7 +16587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:36">
+    <row r="149" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A149" s="3">
         <v>61113</v>
       </c>
@@ -17249,7 +16690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:36">
+    <row r="150" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A150" s="3">
         <v>61114</v>
       </c>
@@ -17352,7 +16793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:36">
+    <row r="151" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A151" s="3">
         <v>61115</v>
       </c>
@@ -17453,7 +16894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:36">
+    <row r="152" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A152" s="3">
         <v>62101</v>
       </c>
@@ -17556,7 +16997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:36">
+    <row r="153" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A153" s="3">
         <v>62102</v>
       </c>
@@ -17659,7 +17100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:36">
+    <row r="154" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A154" s="3">
         <v>62103</v>
       </c>
@@ -17760,7 +17201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:36">
+    <row r="155" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A155" s="3">
         <v>62104</v>
       </c>
@@ -17863,7 +17304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:36">
+    <row r="156" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A156" s="3">
         <v>62105</v>
       </c>
@@ -17966,7 +17407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:36">
+    <row r="157" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A157" s="3">
         <v>62106</v>
       </c>
@@ -18067,7 +17508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:36">
+    <row r="158" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A158" s="3">
         <v>62107</v>
       </c>
@@ -18170,7 +17611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:36">
+    <row r="159" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A159" s="3">
         <v>62108</v>
       </c>
@@ -18273,7 +17714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:36">
+    <row r="160" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A160" s="3">
         <v>62109</v>
       </c>
@@ -18376,7 +17817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:36">
+    <row r="161" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A161" s="3">
         <v>62110</v>
       </c>
@@ -18479,7 +17920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:36">
+    <row r="162" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A162" s="3">
         <v>62111</v>
       </c>
@@ -18582,7 +18023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:36">
+    <row r="163" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A163" s="3">
         <v>62112</v>
       </c>
@@ -18685,7 +18126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:36">
+    <row r="164" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A164" s="3">
         <v>62113</v>
       </c>
@@ -18788,7 +18229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:36">
+    <row r="165" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A165" s="3">
         <v>62114</v>
       </c>
@@ -18891,7 +18332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:36">
+    <row r="166" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A166" s="3">
         <v>62115</v>
       </c>
@@ -18992,7 +18433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:36">
+    <row r="167" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A167" s="3">
         <v>71101</v>
       </c>
@@ -19095,7 +18536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:36">
+    <row r="168" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A168" s="3">
         <v>71102</v>
       </c>
@@ -19198,7 +18639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:36">
+    <row r="169" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A169" s="3">
         <v>71103</v>
       </c>
@@ -19299,7 +18740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:36">
+    <row r="170" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A170" s="3">
         <v>71104</v>
       </c>
@@ -19402,7 +18843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:36">
+    <row r="171" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A171" s="3">
         <v>71105</v>
       </c>
@@ -19505,7 +18946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:36">
+    <row r="172" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A172" s="3">
         <v>71106</v>
       </c>
@@ -19606,7 +19047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:36">
+    <row r="173" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A173" s="3">
         <v>71107</v>
       </c>
@@ -19709,7 +19150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:36">
+    <row r="174" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A174" s="3">
         <v>71108</v>
       </c>
@@ -19812,7 +19253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:36">
+    <row r="175" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A175" s="3">
         <v>71109</v>
       </c>
@@ -19915,7 +19356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:36">
+    <row r="176" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A176" s="3">
         <v>71110</v>
       </c>
@@ -20018,7 +19459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:36">
+    <row r="177" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A177" s="3">
         <v>71111</v>
       </c>
@@ -20121,7 +19562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:36">
+    <row r="178" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A178" s="3">
         <v>71112</v>
       </c>
@@ -20224,7 +19665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:36">
+    <row r="179" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A179" s="3">
         <v>71113</v>
       </c>
@@ -20327,7 +19768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:36">
+    <row r="180" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A180" s="3">
         <v>71114</v>
       </c>
@@ -20430,7 +19871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:36">
+    <row r="181" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A181" s="3">
         <v>71115</v>
       </c>
@@ -20531,7 +19972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:36">
+    <row r="182" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A182" s="3">
         <v>72101</v>
       </c>
@@ -20634,7 +20075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:36">
+    <row r="183" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A183" s="3">
         <v>72102</v>
       </c>
@@ -20737,7 +20178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:36">
+    <row r="184" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A184" s="3">
         <v>72103</v>
       </c>
@@ -20838,7 +20279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:36">
+    <row r="185" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A185" s="3">
         <v>72104</v>
       </c>
@@ -20941,7 +20382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:36">
+    <row r="186" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A186" s="3">
         <v>72105</v>
       </c>
@@ -21044,7 +20485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:36">
+    <row r="187" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A187" s="3">
         <v>72106</v>
       </c>
@@ -21145,7 +20586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:36">
+    <row r="188" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A188" s="3">
         <v>72107</v>
       </c>
@@ -21248,7 +20689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:36">
+    <row r="189" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A189" s="3">
         <v>72108</v>
       </c>
@@ -21351,7 +20792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:36">
+    <row r="190" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A190" s="3">
         <v>72109</v>
       </c>
@@ -21454,7 +20895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:36">
+    <row r="191" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A191" s="3">
         <v>72110</v>
       </c>
@@ -21557,7 +20998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:36">
+    <row r="192" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A192" s="3">
         <v>72111</v>
       </c>
@@ -21660,7 +21101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:36">
+    <row r="193" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A193" s="3">
         <v>72112</v>
       </c>
@@ -21763,7 +21204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:36">
+    <row r="194" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A194" s="3">
         <v>72113</v>
       </c>
@@ -21866,7 +21307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:36">
+    <row r="195" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A195" s="3">
         <v>72114</v>
       </c>
@@ -21969,7 +21410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:36">
+    <row r="196" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A196" s="3">
         <v>72115</v>
       </c>
@@ -22070,7 +21511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:36">
+    <row r="197" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A197" s="3">
         <v>121101</v>
       </c>
@@ -22173,7 +21614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:36">
+    <row r="198" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A198" s="3">
         <v>121102</v>
       </c>
@@ -22276,7 +21717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:36">
+    <row r="199" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A199" s="2">
         <v>121103</v>
       </c>
@@ -22380,7 +21821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:36">
+    <row r="200" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A200" s="3">
         <v>121104</v>
       </c>
@@ -22483,7 +21924,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="201" spans="1:36">
+    <row r="201" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A201" s="3">
         <v>121105</v>
       </c>
@@ -22586,7 +22027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:36">
+    <row r="202" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A202" s="2">
         <v>121106</v>
       </c>
@@ -22690,7 +22131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:36">
+    <row r="203" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A203" s="2">
         <v>121107</v>
       </c>
@@ -22794,7 +22235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:36">
+    <row r="204" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A204" s="2">
         <v>121108</v>
       </c>
@@ -22898,7 +22339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:36">
+    <row r="205" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A205" s="2">
         <v>121109</v>
       </c>
@@ -23002,7 +22443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:36">
+    <row r="206" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A206" s="2">
         <v>121110</v>
       </c>
@@ -23106,7 +22547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:36">
+    <row r="207" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A207" s="2">
         <v>121111</v>
       </c>
@@ -23210,7 +22651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:36">
+    <row r="208" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A208" s="2">
         <v>121112</v>
       </c>
@@ -23314,7 +22755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" ht="14.25" spans="1:36">
+    <row r="209" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A209" s="3">
         <v>121113</v>
       </c>
@@ -23417,7 +22858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:36">
+    <row r="210" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A210" s="2">
         <v>121114</v>
       </c>
@@ -23521,7 +22962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:36">
+    <row r="211" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A211" s="2">
         <v>121115</v>
       </c>
@@ -23625,7 +23066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" ht="14.25" spans="1:36">
+    <row r="212" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A212" s="19">
         <v>999001</v>
       </c>
@@ -23729,7 +23170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" ht="14.25" spans="1:36">
+    <row r="213" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A213" s="19">
         <v>999002</v>
       </c>
@@ -23833,7 +23274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" ht="14.25" spans="1:36">
+    <row r="214" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A214" s="19">
         <v>999003</v>
       </c>
@@ -23937,7 +23378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" ht="14.25" spans="1:36">
+    <row r="215" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A215" s="19">
         <v>999004</v>
       </c>
@@ -24041,7 +23482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" ht="14.25" spans="1:36">
+    <row r="216" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A216" s="19">
         <v>9999001</v>
       </c>
@@ -24145,7 +23586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" ht="14.25" spans="1:36">
+    <row r="217" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A217" s="19">
         <v>9999002</v>
       </c>
@@ -24249,7 +23690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" ht="14.25" spans="1:36">
+    <row r="218" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A218" s="19">
         <v>9999004</v>
       </c>
@@ -24353,7 +23794,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="219" ht="14.25" spans="1:36">
+    <row r="219" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A219" s="19">
         <v>9999005</v>
       </c>
@@ -24457,7 +23898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" ht="14.25" spans="1:36">
+    <row r="220" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A220" s="19">
         <v>9999013</v>
       </c>
@@ -24561,7 +24002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:36">
+    <row r="221" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A221" s="3">
         <v>301101</v>
       </c>
@@ -24664,7 +24105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:36">
+    <row r="222" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A222" s="3">
         <v>301102</v>
       </c>
@@ -24767,7 +24208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:36">
+    <row r="223" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A223" s="2">
         <v>301103</v>
       </c>
@@ -24869,7 +24310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:36">
+    <row r="224" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A224" s="3">
         <v>301104</v>
       </c>
@@ -24972,7 +24413,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="225" spans="1:36">
+    <row r="225" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A225" s="3">
         <v>301105</v>
       </c>
@@ -25075,7 +24516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:36">
+    <row r="226" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A226" s="2">
         <v>301106</v>
       </c>
@@ -25177,7 +24618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:36">
+    <row r="227" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A227" s="2">
         <v>301107</v>
       </c>
@@ -25281,7 +24722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" ht="14.25" spans="1:36">
+    <row r="228" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A228" s="3">
         <v>301108</v>
       </c>
@@ -25384,7 +24825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" ht="14.25" spans="1:36">
+    <row r="229" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A229" s="3">
         <v>301109</v>
       </c>
@@ -25487,7 +24928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" ht="14.25" spans="1:36">
+    <row r="230" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A230" s="3">
         <v>301110</v>
       </c>
@@ -25590,7 +25031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" ht="14.25" spans="1:36">
+    <row r="231" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A231" s="3">
         <v>301111</v>
       </c>
@@ -25693,7 +25134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" ht="14.25" spans="1:36">
+    <row r="232" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A232" s="3">
         <v>301112</v>
       </c>
@@ -25796,7 +25237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" ht="14.25" spans="1:36">
+    <row r="233" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A233" s="3">
         <v>301113</v>
       </c>
@@ -25899,7 +25340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" ht="14.25" spans="1:36">
+    <row r="234" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A234" s="3">
         <v>301114</v>
       </c>
@@ -26002,7 +25443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:36">
+    <row r="235" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A235" s="2">
         <v>301115</v>
       </c>
@@ -26104,7 +25545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:36">
+    <row r="236" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A236" s="3">
         <v>302101</v>
       </c>
@@ -26207,7 +25648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:36">
+    <row r="237" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A237" s="3">
         <v>302102</v>
       </c>
@@ -26310,7 +25751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:36">
+    <row r="238" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A238" s="2">
         <v>302103</v>
       </c>
@@ -26414,7 +25855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:36">
+    <row r="239" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A239" s="3">
         <v>302104</v>
       </c>
@@ -26517,7 +25958,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="240" spans="1:36">
+    <row r="240" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A240" s="3">
         <v>302105</v>
       </c>
@@ -26620,7 +26061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:36">
+    <row r="241" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A241" s="2">
         <v>302106</v>
       </c>
@@ -26724,7 +26165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:36">
+    <row r="242" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A242" s="2">
         <v>302107</v>
       </c>
@@ -26828,7 +26269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:36">
+    <row r="243" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A243" s="2">
         <v>302108</v>
       </c>
@@ -26932,7 +26373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:36">
+    <row r="244" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A244" s="2">
         <v>302109</v>
       </c>
@@ -27036,7 +26477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:36">
+    <row r="245" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A245" s="2">
         <v>302110</v>
       </c>
@@ -27140,7 +26581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:36">
+    <row r="246" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A246" s="2">
         <v>302111</v>
       </c>
@@ -27244,7 +26685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:36">
+    <row r="247" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A247" s="2">
         <v>302112</v>
       </c>
@@ -27348,7 +26789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" ht="14.25" spans="1:36">
+    <row r="248" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A248" s="3">
         <v>302113</v>
       </c>
@@ -27451,7 +26892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:36">
+    <row r="249" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A249" s="2">
         <v>302114</v>
       </c>
@@ -27555,7 +26996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:36">
+    <row r="250" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A250" s="2">
         <v>302115</v>
       </c>
@@ -27659,7 +27100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:36">
+    <row r="251" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A251" s="3">
         <v>303101</v>
       </c>
@@ -27762,7 +27203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:36">
+    <row r="252" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A252" s="3">
         <v>303102</v>
       </c>
@@ -27865,7 +27306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:36">
+    <row r="253" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A253" s="2">
         <v>303103</v>
       </c>
@@ -27969,7 +27410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:36">
+    <row r="254" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A254" s="3">
         <v>303104</v>
       </c>
@@ -28072,7 +27513,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="255" spans="1:36">
+    <row r="255" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A255" s="3">
         <v>303105</v>
       </c>
@@ -28175,7 +27616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:36">
+    <row r="256" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A256" s="2">
         <v>303106</v>
       </c>
@@ -28279,7 +27720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:36">
+    <row r="257" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A257" s="2">
         <v>303107</v>
       </c>
@@ -28383,7 +27824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:36">
+    <row r="258" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A258" s="2">
         <v>303108</v>
       </c>
@@ -28487,7 +27928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:36">
+    <row r="259" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A259" s="2">
         <v>303109</v>
       </c>
@@ -28591,7 +28032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:36">
+    <row r="260" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A260" s="2">
         <v>303110</v>
       </c>
@@ -28695,7 +28136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:36">
+    <row r="261" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A261" s="2">
         <v>303111</v>
       </c>
@@ -28799,7 +28240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:36">
+    <row r="262" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A262" s="2">
         <v>303112</v>
       </c>
@@ -28903,7 +28344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" ht="14.25" spans="1:36">
+    <row r="263" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A263" s="3">
         <v>303113</v>
       </c>
@@ -29006,7 +28447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:36">
+    <row r="264" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A264" s="2">
         <v>303114</v>
       </c>
@@ -29110,7 +28551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" ht="15" customHeight="1" spans="1:36">
+    <row r="265" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="3">
         <v>303115</v>
       </c>
@@ -29213,7 +28654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" ht="14.25" spans="1:36">
+    <row r="266" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A266" s="25">
         <v>90000101</v>
       </c>
@@ -29317,7 +28758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" ht="14.25" spans="1:36">
+    <row r="267" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A267" s="25">
         <v>90000102</v>
       </c>
@@ -29421,7 +28862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" ht="14.25" spans="1:36">
+    <row r="268" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A268" s="25">
         <v>90000201</v>
       </c>
@@ -29525,7 +28966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" ht="14.25" spans="1:36">
+    <row r="269" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A269" s="25">
         <v>90000202</v>
       </c>
@@ -29629,7 +29070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" ht="14.25" spans="1:36">
+    <row r="270" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A270" s="25">
         <v>90000301</v>
       </c>
@@ -29655,10 +29096,10 @@
         <v>0</v>
       </c>
       <c r="K270" s="25" t="s">
-        <v>171</v>
+        <v>246</v>
       </c>
       <c r="L270" s="27">
-        <v>800004031</v>
+        <v>800007031</v>
       </c>
       <c r="M270" s="25">
         <v>1</v>
@@ -29733,7 +29174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" ht="14.25" spans="1:36">
+    <row r="271" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A271" s="25">
         <v>90000302</v>
       </c>
@@ -29759,10 +29200,10 @@
         <v>0</v>
       </c>
       <c r="K271" s="25" t="s">
-        <v>171</v>
+        <v>246</v>
       </c>
       <c r="L271" s="27">
-        <v>800004031</v>
+        <v>800007031</v>
       </c>
       <c r="M271" s="25">
         <v>1</v>
@@ -29837,15 +29278,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" ht="14.25" spans="1:36">
+    <row r="272" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A272" s="25">
-        <v>90000401</v>
+        <v>90000400</v>
       </c>
       <c r="B272" s="25">
         <v>3</v>
       </c>
       <c r="C272" s="25" t="s">
-        <v>175</v>
+        <v>247</v>
       </c>
       <c r="D272" s="25"/>
       <c r="E272" s="26"/>
@@ -29872,7 +29313,7 @@
         <v>1</v>
       </c>
       <c r="N272" s="28">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="O272" s="25">
         <v>1</v>
@@ -29941,15 +29382,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" ht="14.25" spans="1:36">
+    <row r="273" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A273" s="25">
-        <v>90000402</v>
+        <v>90000401</v>
       </c>
       <c r="B273" s="25">
         <v>3</v>
       </c>
       <c r="C273" s="25" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D273" s="25"/>
       <c r="E273" s="26"/>
@@ -29976,7 +29417,7 @@
         <v>1</v>
       </c>
       <c r="N273" s="28">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="O273" s="25">
         <v>1</v>
@@ -30045,15 +29486,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" ht="14.25" spans="1:36">
+    <row r="274" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A274" s="25">
-        <v>90000501</v>
+        <v>90000402</v>
       </c>
       <c r="B274" s="25">
         <v>3</v>
       </c>
       <c r="C274" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D274" s="25"/>
       <c r="E274" s="26"/>
@@ -30071,16 +29512,16 @@
         <v>0</v>
       </c>
       <c r="K274" s="25" t="s">
-        <v>168</v>
-      </c>
-      <c r="L274" s="27">
-        <v>800001031</v>
+        <v>176</v>
+      </c>
+      <c r="L274" s="29">
+        <v>800003031</v>
       </c>
       <c r="M274" s="25">
         <v>1</v>
       </c>
       <c r="N274" s="28">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="O274" s="25">
         <v>1</v>
@@ -30149,15 +29590,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" ht="14.25" spans="1:36">
+    <row r="275" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A275" s="25">
-        <v>90000502</v>
+        <v>90000501</v>
       </c>
       <c r="B275" s="25">
         <v>3</v>
       </c>
       <c r="C275" s="25" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D275" s="25"/>
       <c r="E275" s="26"/>
@@ -30184,7 +29625,7 @@
         <v>1</v>
       </c>
       <c r="N275" s="28">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="O275" s="25">
         <v>1</v>
@@ -30253,15 +29694,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" ht="14.25" spans="1:36">
+    <row r="276" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A276" s="25">
-        <v>90000503</v>
+        <v>90000502</v>
       </c>
       <c r="B276" s="25">
         <v>3</v>
       </c>
       <c r="C276" s="25" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D276" s="25"/>
       <c r="E276" s="26"/>
@@ -30288,7 +29729,7 @@
         <v>1</v>
       </c>
       <c r="N276" s="28">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="O276" s="25">
         <v>1</v>
@@ -30357,15 +29798,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" ht="14.25" spans="1:36">
+    <row r="277" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A277" s="25">
-        <v>90000504</v>
+        <v>90000503</v>
       </c>
       <c r="B277" s="25">
         <v>3</v>
       </c>
       <c r="C277" s="25" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D277" s="25"/>
       <c r="E277" s="26"/>
@@ -30392,7 +29833,7 @@
         <v>1</v>
       </c>
       <c r="N277" s="28">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="O277" s="25">
         <v>1</v>
@@ -30461,15 +29902,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" ht="14.25" spans="1:36">
+    <row r="278" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A278" s="25">
-        <v>90000601</v>
+        <v>90000504</v>
       </c>
       <c r="B278" s="25">
         <v>3</v>
       </c>
       <c r="C278" s="25" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D278" s="25"/>
       <c r="E278" s="26"/>
@@ -30487,16 +29928,16 @@
         <v>0</v>
       </c>
       <c r="K278" s="25" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="L278" s="27">
-        <v>800004031</v>
+        <v>800001031</v>
       </c>
       <c r="M278" s="25">
         <v>1</v>
       </c>
       <c r="N278" s="28">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="O278" s="25">
         <v>1</v>
@@ -30565,15 +30006,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" ht="14.25" spans="1:36">
+    <row r="279" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A279" s="25">
-        <v>90000602</v>
+        <v>90000601</v>
       </c>
       <c r="B279" s="25">
         <v>3</v>
       </c>
       <c r="C279" s="25" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D279" s="25"/>
       <c r="E279" s="26"/>
@@ -30600,7 +30041,7 @@
         <v>1</v>
       </c>
       <c r="N279" s="28">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O279" s="25">
         <v>1</v>
@@ -30669,15 +30110,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" ht="14.25" spans="1:36">
+    <row r="280" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A280" s="25">
-        <v>90000603</v>
+        <v>90000602</v>
       </c>
       <c r="B280" s="25">
         <v>3</v>
       </c>
       <c r="C280" s="25" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D280" s="25"/>
       <c r="E280" s="26"/>
@@ -30704,7 +30145,7 @@
         <v>1</v>
       </c>
       <c r="N280" s="28">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="O280" s="25">
         <v>1</v>
@@ -30773,15 +30214,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" ht="14.25" spans="1:36">
+    <row r="281" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A281" s="25">
-        <v>90000604</v>
+        <v>90000603</v>
       </c>
       <c r="B281" s="25">
         <v>3</v>
       </c>
       <c r="C281" s="25" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D281" s="25"/>
       <c r="E281" s="26"/>
@@ -30808,7 +30249,7 @@
         <v>1</v>
       </c>
       <c r="N281" s="28">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="O281" s="25">
         <v>1</v>
@@ -30877,15 +30318,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" ht="14.25" spans="1:36">
+    <row r="282" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A282" s="25">
-        <v>90000605</v>
+        <v>90000604</v>
       </c>
       <c r="B282" s="25">
         <v>3</v>
       </c>
       <c r="C282" s="25" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D282" s="25"/>
       <c r="E282" s="26"/>
@@ -30912,7 +30353,7 @@
         <v>1</v>
       </c>
       <c r="N282" s="28">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="O282" s="25">
         <v>1</v>
@@ -30981,15 +30422,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" ht="14.25" spans="1:36">
+    <row r="283" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A283" s="25">
-        <v>90000606</v>
+        <v>90000605</v>
       </c>
       <c r="B283" s="25">
         <v>3</v>
       </c>
       <c r="C283" s="25" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D283" s="25"/>
       <c r="E283" s="26"/>
@@ -31016,7 +30457,7 @@
         <v>1</v>
       </c>
       <c r="N283" s="28">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="O283" s="25">
         <v>1</v>
@@ -31085,15 +30526,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" ht="14.25" spans="1:36">
+    <row r="284" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A284" s="25">
-        <v>90000607</v>
+        <v>90000606</v>
       </c>
       <c r="B284" s="25">
         <v>3</v>
       </c>
       <c r="C284" s="25" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D284" s="25"/>
       <c r="E284" s="26"/>
@@ -31120,7 +30561,7 @@
         <v>1</v>
       </c>
       <c r="N284" s="28">
-        <v>350</v>
+        <v>240</v>
       </c>
       <c r="O284" s="25">
         <v>1</v>
@@ -31189,15 +30630,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" ht="14.25" spans="1:36">
+    <row r="285" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A285" s="25">
-        <v>90000608</v>
+        <v>90000607</v>
       </c>
       <c r="B285" s="25">
         <v>3</v>
       </c>
       <c r="C285" s="25" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D285" s="25"/>
       <c r="E285" s="26"/>
@@ -31224,7 +30665,7 @@
         <v>1</v>
       </c>
       <c r="N285" s="28">
-        <v>900</v>
+        <v>350</v>
       </c>
       <c r="O285" s="25">
         <v>1</v>
@@ -31293,15 +30734,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" ht="14.25" spans="1:36">
+    <row r="286" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A286" s="25">
-        <v>90000701</v>
+        <v>90000608</v>
       </c>
       <c r="B286" s="25">
         <v>3</v>
       </c>
       <c r="C286" s="25" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D286" s="25"/>
       <c r="E286" s="26"/>
@@ -31319,16 +30760,16 @@
         <v>0</v>
       </c>
       <c r="K286" s="25" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="L286" s="27">
-        <v>800001031</v>
+        <v>800004031</v>
       </c>
       <c r="M286" s="25">
         <v>1</v>
       </c>
       <c r="N286" s="28">
-        <v>9</v>
+        <v>900</v>
       </c>
       <c r="O286" s="25">
         <v>1</v>
@@ -31397,15 +30838,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" ht="14.25" spans="1:36">
+    <row r="287" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A287" s="25">
-        <v>90000702</v>
+        <v>90000701</v>
       </c>
       <c r="B287" s="25">
         <v>3</v>
       </c>
       <c r="C287" s="25" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D287" s="25"/>
       <c r="E287" s="26"/>
@@ -31432,7 +30873,7 @@
         <v>1</v>
       </c>
       <c r="N287" s="28">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="O287" s="25">
         <v>1</v>
@@ -31501,15 +30942,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" ht="14.25" spans="1:36">
+    <row r="288" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A288" s="25">
-        <v>90000703</v>
+        <v>90000702</v>
       </c>
       <c r="B288" s="25">
         <v>3</v>
       </c>
       <c r="C288" s="25" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D288" s="25"/>
       <c r="E288" s="26"/>
@@ -31536,7 +30977,7 @@
         <v>1</v>
       </c>
       <c r="N288" s="28">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="O288" s="25">
         <v>1</v>
@@ -31605,15 +31046,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" ht="14.25" spans="1:36">
+    <row r="289" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A289" s="25">
-        <v>90000704</v>
+        <v>90000703</v>
       </c>
       <c r="B289" s="25">
         <v>3</v>
       </c>
       <c r="C289" s="25" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D289" s="25"/>
       <c r="E289" s="26"/>
@@ -31640,7 +31081,7 @@
         <v>1</v>
       </c>
       <c r="N289" s="28">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="O289" s="25">
         <v>1</v>
@@ -31709,15 +31150,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" ht="14.25" spans="1:36">
+    <row r="290" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A290" s="25">
-        <v>90000705</v>
+        <v>90000704</v>
       </c>
       <c r="B290" s="25">
         <v>3</v>
       </c>
       <c r="C290" s="25" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D290" s="25"/>
       <c r="E290" s="26"/>
@@ -31744,7 +31185,7 @@
         <v>1</v>
       </c>
       <c r="N290" s="28">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="O290" s="25">
         <v>1</v>
@@ -31813,15 +31254,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" ht="14.25" spans="1:36">
+    <row r="291" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A291" s="25">
-        <v>90000706</v>
+        <v>90000705</v>
       </c>
       <c r="B291" s="25">
         <v>3</v>
       </c>
       <c r="C291" s="25" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D291" s="25"/>
       <c r="E291" s="26"/>
@@ -31848,7 +31289,7 @@
         <v>1</v>
       </c>
       <c r="N291" s="28">
-        <v>135</v>
+        <v>48</v>
       </c>
       <c r="O291" s="25">
         <v>1</v>
@@ -31917,15 +31358,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" ht="14.25" spans="1:36">
+    <row r="292" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A292" s="25">
-        <v>90000707</v>
+        <v>90000706</v>
       </c>
       <c r="B292" s="25">
         <v>3</v>
       </c>
       <c r="C292" s="25" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D292" s="25"/>
       <c r="E292" s="26"/>
@@ -31952,7 +31393,7 @@
         <v>1</v>
       </c>
       <c r="N292" s="28">
-        <v>250</v>
+        <v>135</v>
       </c>
       <c r="O292" s="25">
         <v>1</v>
@@ -32021,15 +31462,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" ht="14.25" spans="1:36">
+    <row r="293" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A293" s="25">
-        <v>90000708</v>
+        <v>90000707</v>
       </c>
       <c r="B293" s="25">
         <v>3</v>
       </c>
       <c r="C293" s="25" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D293" s="25"/>
       <c r="E293" s="26"/>
@@ -32056,7 +31497,7 @@
         <v>1</v>
       </c>
       <c r="N293" s="28">
-        <v>450</v>
+        <v>250</v>
       </c>
       <c r="O293" s="25">
         <v>1</v>
@@ -32125,15 +31566,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" ht="14.25" spans="1:36">
+    <row r="294" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A294" s="25">
-        <v>90000709</v>
+        <v>90000708</v>
       </c>
       <c r="B294" s="25">
         <v>3</v>
       </c>
       <c r="C294" s="25" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D294" s="25"/>
       <c r="E294" s="26"/>
@@ -32160,7 +31601,7 @@
         <v>1</v>
       </c>
       <c r="N294" s="28">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="O294" s="25">
         <v>1</v>
@@ -32229,15 +31670,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" ht="14.25" spans="1:36">
+    <row r="295" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A295" s="25">
-        <v>90000710</v>
+        <v>90000709</v>
       </c>
       <c r="B295" s="25">
         <v>3</v>
       </c>
       <c r="C295" s="25" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D295" s="25"/>
       <c r="E295" s="26"/>
@@ -32264,7 +31705,7 @@
         <v>1</v>
       </c>
       <c r="N295" s="28">
-        <v>1200</v>
+        <v>500</v>
       </c>
       <c r="O295" s="25">
         <v>1</v>
@@ -32333,15 +31774,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" ht="14.25" spans="1:36">
+    <row r="296" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A296" s="25">
-        <v>90000711</v>
+        <v>90000710</v>
       </c>
       <c r="B296" s="25">
         <v>3</v>
       </c>
       <c r="C296" s="25" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D296" s="25"/>
       <c r="E296" s="26"/>
@@ -32368,7 +31809,7 @@
         <v>1</v>
       </c>
       <c r="N296" s="28">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="O296" s="25">
         <v>1</v>
@@ -32437,15 +31878,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" ht="14.25" spans="1:36">
+    <row r="297" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A297" s="25">
-        <v>90000712</v>
+        <v>90000711</v>
       </c>
       <c r="B297" s="25">
         <v>3</v>
       </c>
       <c r="C297" s="25" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D297" s="25"/>
       <c r="E297" s="26"/>
@@ -32472,7 +31913,7 @@
         <v>1</v>
       </c>
       <c r="N297" s="28">
-        <v>3200</v>
+        <v>1500</v>
       </c>
       <c r="O297" s="25">
         <v>1</v>
@@ -32541,15 +31982,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" ht="14.25" spans="1:36">
+    <row r="298" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A298" s="25">
-        <v>90000713</v>
+        <v>90000712</v>
       </c>
       <c r="B298" s="25">
         <v>3</v>
       </c>
       <c r="C298" s="25" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D298" s="25"/>
       <c r="E298" s="26"/>
@@ -32576,7 +32017,7 @@
         <v>1</v>
       </c>
       <c r="N298" s="28">
-        <v>3500</v>
+        <v>3200</v>
       </c>
       <c r="O298" s="25">
         <v>1</v>
@@ -32645,15 +32086,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" ht="14.25" spans="1:36">
+    <row r="299" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A299" s="25">
-        <v>90000714</v>
+        <v>90000713</v>
       </c>
       <c r="B299" s="25">
         <v>3</v>
       </c>
       <c r="C299" s="25" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D299" s="25"/>
       <c r="E299" s="26"/>
@@ -32680,7 +32121,7 @@
         <v>1</v>
       </c>
       <c r="N299" s="28">
-        <v>11000</v>
+        <v>3500</v>
       </c>
       <c r="O299" s="25">
         <v>1</v>
@@ -32749,15 +32190,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" ht="14.25" spans="1:36">
+    <row r="300" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A300" s="25">
-        <v>90000715</v>
+        <v>90000714</v>
       </c>
       <c r="B300" s="25">
         <v>3</v>
       </c>
       <c r="C300" s="25" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D300" s="25"/>
       <c r="E300" s="26"/>
@@ -32784,7 +32225,7 @@
         <v>1</v>
       </c>
       <c r="N300" s="28">
-        <v>12000</v>
+        <v>11000</v>
       </c>
       <c r="O300" s="25">
         <v>1</v>
@@ -32853,15 +32294,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" ht="14.25" spans="1:36">
+    <row r="301" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A301" s="25">
-        <v>90000716</v>
+        <v>90000715</v>
       </c>
       <c r="B301" s="25">
         <v>3</v>
       </c>
       <c r="C301" s="25" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D301" s="25"/>
       <c r="E301" s="26"/>
@@ -32888,7 +32329,7 @@
         <v>1</v>
       </c>
       <c r="N301" s="28">
-        <v>22000</v>
+        <v>12000</v>
       </c>
       <c r="O301" s="25">
         <v>1</v>
@@ -32957,15 +32398,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" ht="14.25" spans="1:36">
+    <row r="302" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A302" s="25">
-        <v>90000717</v>
+        <v>90000716</v>
       </c>
       <c r="B302" s="25">
         <v>3</v>
       </c>
       <c r="C302" s="25" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D302" s="25"/>
       <c r="E302" s="26"/>
@@ -32992,7 +32433,7 @@
         <v>1</v>
       </c>
       <c r="N302" s="28">
-        <v>50000</v>
+        <v>22000</v>
       </c>
       <c r="O302" s="25">
         <v>1</v>
@@ -33061,15 +32502,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" ht="14.25" spans="1:36">
+    <row r="303" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A303" s="25">
-        <v>90000718</v>
+        <v>90000717</v>
       </c>
       <c r="B303" s="25">
         <v>3</v>
       </c>
       <c r="C303" s="25" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D303" s="25"/>
       <c r="E303" s="26"/>
@@ -33096,7 +32537,7 @@
         <v>1</v>
       </c>
       <c r="N303" s="28">
-        <v>70000</v>
+        <v>50000</v>
       </c>
       <c r="O303" s="25">
         <v>1</v>
@@ -33165,15 +32606,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" ht="14.25" spans="1:36">
+    <row r="304" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A304" s="25">
-        <v>90000719</v>
+        <v>90000718</v>
       </c>
       <c r="B304" s="25">
         <v>3</v>
       </c>
       <c r="C304" s="25" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D304" s="25"/>
       <c r="E304" s="26"/>
@@ -33200,7 +32641,7 @@
         <v>1</v>
       </c>
       <c r="N304" s="28">
-        <v>120000</v>
+        <v>70000</v>
       </c>
       <c r="O304" s="25">
         <v>1</v>
@@ -33269,29 +32710,133 @@
         <v>0</v>
       </c>
     </row>
+    <row r="305" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A305" s="25">
+        <v>90000719</v>
+      </c>
+      <c r="B305" s="25">
+        <v>3</v>
+      </c>
+      <c r="C305" s="25" t="s">
+        <v>208</v>
+      </c>
+      <c r="D305" s="25"/>
+      <c r="E305" s="26"/>
+      <c r="F305" s="25"/>
+      <c r="G305" s="25">
+        <v>1</v>
+      </c>
+      <c r="H305" s="25">
+        <v>2</v>
+      </c>
+      <c r="I305" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="J305" s="25">
+        <v>0</v>
+      </c>
+      <c r="K305" s="25" t="s">
+        <v>168</v>
+      </c>
+      <c r="L305" s="27">
+        <v>800001031</v>
+      </c>
+      <c r="M305" s="25">
+        <v>1</v>
+      </c>
+      <c r="N305" s="28">
+        <v>120000</v>
+      </c>
+      <c r="O305" s="25">
+        <v>1</v>
+      </c>
+      <c r="P305" s="25">
+        <v>8</v>
+      </c>
+      <c r="Q305" s="25">
+        <v>0</v>
+      </c>
+      <c r="R305" s="25">
+        <v>25</v>
+      </c>
+      <c r="S305" s="25">
+        <v>-5000</v>
+      </c>
+      <c r="T305" s="25">
+        <v>1</v>
+      </c>
+      <c r="U305" s="25">
+        <v>0</v>
+      </c>
+      <c r="V305" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="W305" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="X305" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y305" s="30">
+        <v>20010001</v>
+      </c>
+      <c r="Z305" s="30">
+        <v>0</v>
+      </c>
+      <c r="AA305" s="25">
+        <v>1</v>
+      </c>
+      <c r="AB305" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC305" s="25">
+        <v>10000</v>
+      </c>
+      <c r="AD305" s="25">
+        <v>10000</v>
+      </c>
+      <c r="AE305" s="25">
+        <v>0</v>
+      </c>
+      <c r="AF305" s="31">
+        <v>40</v>
+      </c>
+      <c r="AG305" s="31">
+        <v>0</v>
+      </c>
+      <c r="AH305" s="31">
+        <v>0</v>
+      </c>
+      <c r="AI305" s="31">
+        <v>0</v>
+      </c>
+      <c r="AJ305" s="31">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState ref="A5:AD211">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:AD211">
     <sortCondition ref="A5:A211"/>
   </sortState>
-  <conditionalFormatting sqref="A221:A1048576 A1:A211">
+  <phoneticPr fontId="13" type="noConversion"/>
+  <conditionalFormatting sqref="A1:A211 A221:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="33"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="I1:S28"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="9:19">
+    <row r="1" spans="9:19" x14ac:dyDescent="0.15">
       <c r="I1" s="6">
         <v>1</v>
       </c>
@@ -33322,7 +32867,7 @@
         <v>65000</v>
       </c>
     </row>
-    <row r="2" spans="9:19">
+    <row r="2" spans="9:19" x14ac:dyDescent="0.15">
       <c r="I2" s="6">
         <v>2</v>
       </c>
@@ -33353,7 +32898,7 @@
         <v>85000</v>
       </c>
     </row>
-    <row r="3" spans="9:19">
+    <row r="3" spans="9:19" x14ac:dyDescent="0.15">
       <c r="I3" s="6">
         <v>2</v>
       </c>
@@ -33384,7 +32929,7 @@
         <v>110000</v>
       </c>
     </row>
-    <row r="4" spans="9:19">
+    <row r="4" spans="9:19" x14ac:dyDescent="0.15">
       <c r="I4" s="6">
         <v>3</v>
       </c>
@@ -33415,7 +32960,7 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="5" spans="9:19">
+    <row r="5" spans="9:19" x14ac:dyDescent="0.15">
       <c r="I5" s="6">
         <v>3</v>
       </c>
@@ -33446,7 +32991,7 @@
         <v>180000</v>
       </c>
     </row>
-    <row r="6" spans="9:19">
+    <row r="6" spans="9:19" x14ac:dyDescent="0.15">
       <c r="I6" s="6">
         <v>4</v>
       </c>
@@ -33477,7 +33022,7 @@
         <v>350000</v>
       </c>
     </row>
-    <row r="7" spans="9:19">
+    <row r="7" spans="9:19" x14ac:dyDescent="0.15">
       <c r="I7" s="6">
         <v>4</v>
       </c>
@@ -33508,7 +33053,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="8" spans="9:19">
+    <row r="8" spans="9:19" x14ac:dyDescent="0.15">
       <c r="I8" s="6">
         <v>5</v>
       </c>
@@ -33539,7 +33084,7 @@
         <v>800000</v>
       </c>
     </row>
-    <row r="9" spans="9:19">
+    <row r="9" spans="9:19" x14ac:dyDescent="0.15">
       <c r="I9" s="6">
         <v>5</v>
       </c>
@@ -33570,7 +33115,7 @@
         <v>1400000</v>
       </c>
     </row>
-    <row r="10" spans="9:19">
+    <row r="10" spans="9:19" x14ac:dyDescent="0.15">
       <c r="I10" s="6">
         <v>6</v>
       </c>
@@ -33601,7 +33146,7 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="11" spans="9:14">
+    <row r="11" spans="9:19" x14ac:dyDescent="0.15">
       <c r="I11" s="6">
         <v>6</v>
       </c>
@@ -33623,7 +33168,7 @@
         <v>350000</v>
       </c>
     </row>
-    <row r="12" spans="9:14">
+    <row r="12" spans="9:19" x14ac:dyDescent="0.15">
       <c r="I12" s="6">
         <v>6</v>
       </c>
@@ -33645,7 +33190,7 @@
         <v>350000</v>
       </c>
     </row>
-    <row r="13" spans="9:14">
+    <row r="13" spans="9:19" x14ac:dyDescent="0.15">
       <c r="I13" s="6">
         <v>7</v>
       </c>
@@ -33667,7 +33212,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="14" spans="9:14">
+    <row r="14" spans="9:19" x14ac:dyDescent="0.15">
       <c r="I14" s="6">
         <v>7</v>
       </c>
@@ -33689,7 +33234,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="15" spans="9:14">
+    <row r="15" spans="9:19" x14ac:dyDescent="0.15">
       <c r="I15" s="6">
         <v>7</v>
       </c>
@@ -33711,7 +33256,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="16" spans="9:14">
+    <row r="16" spans="9:19" x14ac:dyDescent="0.15">
       <c r="I16" s="6">
         <v>7</v>
       </c>
@@ -33733,7 +33278,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="17" spans="9:14">
+    <row r="17" spans="9:14" x14ac:dyDescent="0.15">
       <c r="I17" s="6">
         <v>8</v>
       </c>
@@ -33755,7 +33300,7 @@
         <v>800000</v>
       </c>
     </row>
-    <row r="18" spans="9:14">
+    <row r="18" spans="9:14" x14ac:dyDescent="0.15">
       <c r="I18" s="6">
         <v>8</v>
       </c>
@@ -33777,7 +33322,7 @@
         <v>800000</v>
       </c>
     </row>
-    <row r="19" spans="9:14">
+    <row r="19" spans="9:14" x14ac:dyDescent="0.15">
       <c r="I19" s="6">
         <v>8</v>
       </c>
@@ -33799,7 +33344,7 @@
         <v>800000</v>
       </c>
     </row>
-    <row r="20" spans="9:14">
+    <row r="20" spans="9:14" x14ac:dyDescent="0.15">
       <c r="I20" s="6">
         <v>8</v>
       </c>
@@ -33821,7 +33366,7 @@
         <v>800000</v>
       </c>
     </row>
-    <row r="21" spans="9:14">
+    <row r="21" spans="9:14" x14ac:dyDescent="0.15">
       <c r="I21" s="6">
         <v>9</v>
       </c>
@@ -33843,7 +33388,7 @@
         <v>1400000</v>
       </c>
     </row>
-    <row r="22" spans="9:14">
+    <row r="22" spans="9:14" x14ac:dyDescent="0.15">
       <c r="I22" s="6">
         <v>9</v>
       </c>
@@ -33865,7 +33410,7 @@
         <v>1400000</v>
       </c>
     </row>
-    <row r="23" spans="9:14">
+    <row r="23" spans="9:14" x14ac:dyDescent="0.15">
       <c r="I23" s="6">
         <v>9</v>
       </c>
@@ -33887,7 +33432,7 @@
         <v>1400000</v>
       </c>
     </row>
-    <row r="24" spans="9:14">
+    <row r="24" spans="9:14" x14ac:dyDescent="0.15">
       <c r="I24" s="6">
         <v>9</v>
       </c>
@@ -33909,7 +33454,7 @@
         <v>1400000</v>
       </c>
     </row>
-    <row r="25" spans="9:14">
+    <row r="25" spans="9:14" x14ac:dyDescent="0.15">
       <c r="I25" s="6">
         <v>10</v>
       </c>
@@ -33931,7 +33476,7 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="26" spans="9:14">
+    <row r="26" spans="9:14" x14ac:dyDescent="0.15">
       <c r="I26" s="6">
         <v>10</v>
       </c>
@@ -33953,7 +33498,7 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="27" spans="9:14">
+    <row r="27" spans="9:14" x14ac:dyDescent="0.15">
       <c r="I27" s="6">
         <v>10</v>
       </c>
@@ -33975,7 +33520,7 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="28" spans="9:14">
+    <row r="28" spans="9:14" x14ac:dyDescent="0.15">
       <c r="I28" s="6">
         <v>10</v>
       </c>
@@ -33998,16 +33543,16 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A6:O22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="8.625" style="1" customWidth="1"/>
@@ -34026,7 +33571,7 @@
     <col min="16" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="6" ht="14.25" spans="2:14">
+    <row r="6" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>55</v>
       </c>
@@ -34049,7 +33594,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="7" ht="14.25" spans="1:15">
+    <row r="7" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>151</v>
       </c>
@@ -34093,7 +33638,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="8" ht="14.25" spans="1:15">
+    <row r="8" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>151</v>
       </c>
@@ -34137,7 +33682,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="9" ht="14.25" spans="1:15">
+    <row r="9" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>151</v>
       </c>
@@ -34181,7 +33726,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="10" ht="14.25" spans="1:15">
+    <row r="10" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>151</v>
       </c>
@@ -34225,7 +33770,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="11" ht="14.25" spans="1:15">
+    <row r="11" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>150</v>
       </c>
@@ -34269,7 +33814,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="12" ht="14.25" spans="1:15">
+    <row r="12" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>150</v>
       </c>
@@ -34313,7 +33858,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="13" ht="14.25" spans="1:15">
+    <row r="13" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>150</v>
       </c>
@@ -34357,7 +33902,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="14" ht="14.25" spans="1:15">
+    <row r="14" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>150</v>
       </c>
@@ -34401,7 +33946,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="15" ht="14.25" spans="1:15">
+    <row r="15" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>153</v>
       </c>
@@ -34444,7 +33989,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="16" ht="14.25" spans="1:15">
+    <row r="16" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>153</v>
       </c>
@@ -34487,7 +34032,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="17" ht="14.25" spans="1:7">
+    <row r="17" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>153</v>
       </c>
@@ -34512,7 +34057,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="18" ht="14.25" spans="1:7">
+    <row r="18" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>153</v>
       </c>
@@ -34537,7 +34082,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="19" ht="14.25" spans="1:7">
+    <row r="19" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>236</v>
       </c>
@@ -34563,7 +34108,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="20" ht="14.25" spans="1:7">
+    <row r="20" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>236</v>
       </c>
@@ -34589,7 +34134,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="21" ht="14.25" spans="1:7">
+    <row r="21" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>152</v>
       </c>
@@ -34615,7 +34160,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="22" ht="14.25" spans="1:7">
+    <row r="22" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>152</v>
       </c>
@@ -34642,18 +34187,18 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="B2:K162"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="3:11">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C2" t="s">
         <v>243</v>
       </c>
@@ -34682,7 +34227,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="3" spans="2:11">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B3">
         <v>1</v>
       </c>
@@ -34722,7 +34267,7 @@
         <v>1:10_2:10_3:10_4:10_5:10_6:10_7:10_8:10_9:10_10:10_11:10_12:10_13:10_14:10_15:10_16:10_17:10_18:10_19:10_20:10_21:10_22:10_23:10_24:10_25:10_26:10_27:10_28:10_29:10_30:10_31:10_32:10_33:10_34:10_35:10_36:10_37:10_38:10_39:10_40:10_41:10_42:10_43:10_44:10_45:10_46:10_47:10_48:10_49:10_50:10_51:10_52:10_53:10_54:10_55:10_56:10_57:10_58:10_59:10_60:10_61:10_62:10_63:10_64:10_65:10_66:10_67:10_68:10_69:10_70:10_71:10_72:10_73:10_74:10_75:10_76:10_77:10_78:10_79:10_80:10_81:10_82:10_83:10_84:10_85:10_86:10_87:10_88:10_89:10_90:10_91:10_92:10_93:10_94:10_95:10_96:10_97:10_98:10_99:10_100:10_101:10_102:10_103:10_104:10_105:10_106:10_107:10_108:10_109:10_110:10_111:10_112:10_113:10_114:10_115:10_116:10_117:10_118:10_119:10_120:10_121:10_122:10_123:10_124:10_125:10_126:10_127:10_128:10_129:10_130:10_131:10_132:10_133:10_134:10_135:10_136:10_137:10_138:10_139:10_140:10_141:10_142:10_143:10_144:10_145:10_146:10_147:10_148:10_149:10_150:10_151:10_152:10_153:10_154:10_155:10_156:10_157:10_158:10_159:10_160:10</v>
       </c>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B4">
         <f t="shared" ref="B4:B35" si="0">B3+1</f>
         <v>2</v>
@@ -34751,7 +34296,7 @@
         <v>2:10</v>
       </c>
     </row>
-    <row r="5" spans="2:8">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B5">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -34780,7 +34325,7 @@
         <v>3:10</v>
       </c>
     </row>
-    <row r="6" spans="2:8">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B6">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -34809,7 +34354,7 @@
         <v>4:10</v>
       </c>
     </row>
-    <row r="7" spans="2:8">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B7">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -34838,7 +34383,7 @@
         <v>5:10</v>
       </c>
     </row>
-    <row r="8" spans="2:8">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -34867,7 +34412,7 @@
         <v>6:10</v>
       </c>
     </row>
-    <row r="9" spans="2:8">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B9">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -34896,7 +34441,7 @@
         <v>7:10</v>
       </c>
     </row>
-    <row r="10" spans="2:8">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -34925,7 +34470,7 @@
         <v>8:10</v>
       </c>
     </row>
-    <row r="11" spans="2:8">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B11">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -34954,7 +34499,7 @@
         <v>9:10</v>
       </c>
     </row>
-    <row r="12" spans="2:8">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B12">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -34983,7 +34528,7 @@
         <v>10:10</v>
       </c>
     </row>
-    <row r="13" spans="2:8">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B13">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -35012,7 +34557,7 @@
         <v>11:10</v>
       </c>
     </row>
-    <row r="14" spans="2:8">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B14">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -35041,7 +34586,7 @@
         <v>12:10</v>
       </c>
     </row>
-    <row r="15" spans="2:8">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B15">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -35070,7 +34615,7 @@
         <v>13:10</v>
       </c>
     </row>
-    <row r="16" spans="2:8">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B16">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -35099,7 +34644,7 @@
         <v>14:10</v>
       </c>
     </row>
-    <row r="17" spans="2:8">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B17">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -35128,7 +34673,7 @@
         <v>15:10</v>
       </c>
     </row>
-    <row r="18" spans="2:8">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B18">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -35157,7 +34702,7 @@
         <v>16:10</v>
       </c>
     </row>
-    <row r="19" spans="2:8">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B19">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -35186,7 +34731,7 @@
         <v>17:10</v>
       </c>
     </row>
-    <row r="20" spans="2:8">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B20">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -35215,7 +34760,7 @@
         <v>18:10</v>
       </c>
     </row>
-    <row r="21" spans="2:8">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B21">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -35244,7 +34789,7 @@
         <v>19:10</v>
       </c>
     </row>
-    <row r="22" spans="2:8">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B22">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -35273,7 +34818,7 @@
         <v>20:10</v>
       </c>
     </row>
-    <row r="23" spans="2:8">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B23">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -35302,7 +34847,7 @@
         <v>21:10</v>
       </c>
     </row>
-    <row r="24" spans="2:8">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B24">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -35331,7 +34876,7 @@
         <v>22:10</v>
       </c>
     </row>
-    <row r="25" spans="2:8">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B25">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -35360,7 +34905,7 @@
         <v>23:10</v>
       </c>
     </row>
-    <row r="26" spans="2:8">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B26">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -35389,7 +34934,7 @@
         <v>24:10</v>
       </c>
     </row>
-    <row r="27" spans="2:8">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B27">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -35418,7 +34963,7 @@
         <v>25:10</v>
       </c>
     </row>
-    <row r="28" spans="2:8">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B28">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -35447,7 +34992,7 @@
         <v>26:10</v>
       </c>
     </row>
-    <row r="29" spans="2:8">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B29">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -35476,7 +35021,7 @@
         <v>27:10</v>
       </c>
     </row>
-    <row r="30" spans="2:8">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B30">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -35505,7 +35050,7 @@
         <v>28:10</v>
       </c>
     </row>
-    <row r="31" spans="2:8">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B31">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -35534,7 +35079,7 @@
         <v>29:10</v>
       </c>
     </row>
-    <row r="32" spans="2:8">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B32">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -35563,7 +35108,7 @@
         <v>30:10</v>
       </c>
     </row>
-    <row r="33" spans="2:8">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -35592,7 +35137,7 @@
         <v>31:10</v>
       </c>
     </row>
-    <row r="34" spans="2:8">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B34">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -35621,7 +35166,7 @@
         <v>32:10</v>
       </c>
     </row>
-    <row r="35" spans="2:8">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -35650,7 +35195,7 @@
         <v>33:10</v>
       </c>
     </row>
-    <row r="36" spans="2:8">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B36">
         <f t="shared" ref="B36:B67" si="6">B35+1</f>
         <v>34</v>
@@ -35679,7 +35224,7 @@
         <v>34:10</v>
       </c>
     </row>
-    <row r="37" spans="2:8">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B37">
         <f t="shared" si="6"/>
         <v>35</v>
@@ -35708,7 +35253,7 @@
         <v>35:10</v>
       </c>
     </row>
-    <row r="38" spans="2:8">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B38">
         <f t="shared" si="6"/>
         <v>36</v>
@@ -35737,7 +35282,7 @@
         <v>36:10</v>
       </c>
     </row>
-    <row r="39" spans="2:8">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B39">
         <f t="shared" si="6"/>
         <v>37</v>
@@ -35766,7 +35311,7 @@
         <v>37:10</v>
       </c>
     </row>
-    <row r="40" spans="2:8">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B40">
         <f t="shared" si="6"/>
         <v>38</v>
@@ -35795,7 +35340,7 @@
         <v>38:10</v>
       </c>
     </row>
-    <row r="41" spans="2:8">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B41">
         <f t="shared" si="6"/>
         <v>39</v>
@@ -35824,7 +35369,7 @@
         <v>39:10</v>
       </c>
     </row>
-    <row r="42" spans="2:8">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B42">
         <f t="shared" si="6"/>
         <v>40</v>
@@ -35853,7 +35398,7 @@
         <v>40:10</v>
       </c>
     </row>
-    <row r="43" spans="2:8">
+    <row r="43" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B43">
         <f t="shared" si="6"/>
         <v>41</v>
@@ -35882,7 +35427,7 @@
         <v>41:10</v>
       </c>
     </row>
-    <row r="44" spans="2:8">
+    <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44">
         <f t="shared" si="6"/>
         <v>42</v>
@@ -35911,7 +35456,7 @@
         <v>42:10</v>
       </c>
     </row>
-    <row r="45" spans="2:8">
+    <row r="45" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B45">
         <f t="shared" si="6"/>
         <v>43</v>
@@ -35940,7 +35485,7 @@
         <v>43:10</v>
       </c>
     </row>
-    <row r="46" spans="2:8">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B46">
         <f t="shared" si="6"/>
         <v>44</v>
@@ -35969,7 +35514,7 @@
         <v>44:10</v>
       </c>
     </row>
-    <row r="47" spans="2:8">
+    <row r="47" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B47">
         <f t="shared" si="6"/>
         <v>45</v>
@@ -35998,7 +35543,7 @@
         <v>45:10</v>
       </c>
     </row>
-    <row r="48" spans="2:8">
+    <row r="48" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B48">
         <f t="shared" si="6"/>
         <v>46</v>
@@ -36027,7 +35572,7 @@
         <v>46:10</v>
       </c>
     </row>
-    <row r="49" spans="2:8">
+    <row r="49" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B49">
         <f t="shared" si="6"/>
         <v>47</v>
@@ -36056,7 +35601,7 @@
         <v>47:10</v>
       </c>
     </row>
-    <row r="50" spans="2:8">
+    <row r="50" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B50">
         <f t="shared" si="6"/>
         <v>48</v>
@@ -36085,7 +35630,7 @@
         <v>48:10</v>
       </c>
     </row>
-    <row r="51" spans="2:8">
+    <row r="51" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B51">
         <f t="shared" si="6"/>
         <v>49</v>
@@ -36114,7 +35659,7 @@
         <v>49:10</v>
       </c>
     </row>
-    <row r="52" spans="2:8">
+    <row r="52" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B52">
         <f t="shared" si="6"/>
         <v>50</v>
@@ -36143,7 +35688,7 @@
         <v>50:10</v>
       </c>
     </row>
-    <row r="53" spans="2:8">
+    <row r="53" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B53">
         <f t="shared" si="6"/>
         <v>51</v>
@@ -36172,7 +35717,7 @@
         <v>51:10</v>
       </c>
     </row>
-    <row r="54" spans="2:8">
+    <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54">
         <f t="shared" si="6"/>
         <v>52</v>
@@ -36201,7 +35746,7 @@
         <v>52:10</v>
       </c>
     </row>
-    <row r="55" spans="2:8">
+    <row r="55" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B55">
         <f t="shared" si="6"/>
         <v>53</v>
@@ -36230,7 +35775,7 @@
         <v>53:10</v>
       </c>
     </row>
-    <row r="56" spans="2:8">
+    <row r="56" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B56">
         <f t="shared" si="6"/>
         <v>54</v>
@@ -36259,7 +35804,7 @@
         <v>54:10</v>
       </c>
     </row>
-    <row r="57" spans="2:8">
+    <row r="57" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B57">
         <f t="shared" si="6"/>
         <v>55</v>
@@ -36288,7 +35833,7 @@
         <v>55:10</v>
       </c>
     </row>
-    <row r="58" spans="2:8">
+    <row r="58" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B58">
         <f t="shared" si="6"/>
         <v>56</v>
@@ -36317,7 +35862,7 @@
         <v>56:10</v>
       </c>
     </row>
-    <row r="59" spans="2:8">
+    <row r="59" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B59">
         <f t="shared" si="6"/>
         <v>57</v>
@@ -36346,7 +35891,7 @@
         <v>57:10</v>
       </c>
     </row>
-    <row r="60" spans="2:8">
+    <row r="60" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B60">
         <f t="shared" si="6"/>
         <v>58</v>
@@ -36375,7 +35920,7 @@
         <v>58:10</v>
       </c>
     </row>
-    <row r="61" spans="2:8">
+    <row r="61" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B61">
         <f t="shared" si="6"/>
         <v>59</v>
@@ -36404,7 +35949,7 @@
         <v>59:10</v>
       </c>
     </row>
-    <row r="62" spans="2:8">
+    <row r="62" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B62">
         <f t="shared" si="6"/>
         <v>60</v>
@@ -36433,7 +35978,7 @@
         <v>60:10</v>
       </c>
     </row>
-    <row r="63" spans="2:8">
+    <row r="63" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B63">
         <f t="shared" si="6"/>
         <v>61</v>
@@ -36462,7 +36007,7 @@
         <v>61:10</v>
       </c>
     </row>
-    <row r="64" spans="2:8">
+    <row r="64" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B64">
         <f t="shared" si="6"/>
         <v>62</v>
@@ -36491,7 +36036,7 @@
         <v>62:10</v>
       </c>
     </row>
-    <row r="65" spans="2:8">
+    <row r="65" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B65">
         <f t="shared" si="6"/>
         <v>63</v>
@@ -36520,7 +36065,7 @@
         <v>63:10</v>
       </c>
     </row>
-    <row r="66" spans="2:8">
+    <row r="66" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B66">
         <f t="shared" si="6"/>
         <v>64</v>
@@ -36549,7 +36094,7 @@
         <v>64:10</v>
       </c>
     </row>
-    <row r="67" spans="2:8">
+    <row r="67" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B67">
         <f t="shared" si="6"/>
         <v>65</v>
@@ -36578,7 +36123,7 @@
         <v>65:10</v>
       </c>
     </row>
-    <row r="68" spans="2:8">
+    <row r="68" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B68">
         <f t="shared" ref="B68:B94" si="7">B67+1</f>
         <v>66</v>
@@ -36607,7 +36152,7 @@
         <v>66:10</v>
       </c>
     </row>
-    <row r="69" spans="2:8">
+    <row r="69" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B69">
         <f t="shared" si="7"/>
         <v>67</v>
@@ -36636,7 +36181,7 @@
         <v>67:10</v>
       </c>
     </row>
-    <row r="70" spans="2:8">
+    <row r="70" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B70">
         <f t="shared" si="7"/>
         <v>68</v>
@@ -36665,7 +36210,7 @@
         <v>68:10</v>
       </c>
     </row>
-    <row r="71" spans="2:8">
+    <row r="71" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B71">
         <f t="shared" si="7"/>
         <v>69</v>
@@ -36694,7 +36239,7 @@
         <v>69:10</v>
       </c>
     </row>
-    <row r="72" spans="2:8">
+    <row r="72" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B72">
         <f t="shared" si="7"/>
         <v>70</v>
@@ -36723,7 +36268,7 @@
         <v>70:10</v>
       </c>
     </row>
-    <row r="73" spans="2:8">
+    <row r="73" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B73">
         <f t="shared" si="7"/>
         <v>71</v>
@@ -36752,7 +36297,7 @@
         <v>71:10</v>
       </c>
     </row>
-    <row r="74" spans="2:8">
+    <row r="74" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B74">
         <f t="shared" si="7"/>
         <v>72</v>
@@ -36781,7 +36326,7 @@
         <v>72:10</v>
       </c>
     </row>
-    <row r="75" spans="2:8">
+    <row r="75" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B75">
         <f t="shared" si="7"/>
         <v>73</v>
@@ -36810,7 +36355,7 @@
         <v>73:10</v>
       </c>
     </row>
-    <row r="76" spans="2:8">
+    <row r="76" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B76">
         <f t="shared" si="7"/>
         <v>74</v>
@@ -36839,7 +36384,7 @@
         <v>74:10</v>
       </c>
     </row>
-    <row r="77" spans="2:8">
+    <row r="77" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B77">
         <f t="shared" si="7"/>
         <v>75</v>
@@ -36868,7 +36413,7 @@
         <v>75:10</v>
       </c>
     </row>
-    <row r="78" spans="2:8">
+    <row r="78" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B78">
         <f t="shared" si="7"/>
         <v>76</v>
@@ -36897,7 +36442,7 @@
         <v>76:10</v>
       </c>
     </row>
-    <row r="79" spans="2:8">
+    <row r="79" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B79">
         <f t="shared" si="7"/>
         <v>77</v>
@@ -36926,7 +36471,7 @@
         <v>77:10</v>
       </c>
     </row>
-    <row r="80" spans="2:8">
+    <row r="80" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B80">
         <f t="shared" si="7"/>
         <v>78</v>
@@ -36955,7 +36500,7 @@
         <v>78:10</v>
       </c>
     </row>
-    <row r="81" spans="2:8">
+    <row r="81" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B81">
         <f t="shared" si="7"/>
         <v>79</v>
@@ -36984,7 +36529,7 @@
         <v>79:10</v>
       </c>
     </row>
-    <row r="82" spans="2:8">
+    <row r="82" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B82">
         <f t="shared" si="7"/>
         <v>80</v>
@@ -37013,7 +36558,7 @@
         <v>80:10</v>
       </c>
     </row>
-    <row r="83" spans="2:8">
+    <row r="83" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B83">
         <f t="shared" si="7"/>
         <v>81</v>
@@ -37042,7 +36587,7 @@
         <v>81:10</v>
       </c>
     </row>
-    <row r="84" spans="2:8">
+    <row r="84" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B84">
         <f t="shared" si="7"/>
         <v>82</v>
@@ -37071,7 +36616,7 @@
         <v>82:10</v>
       </c>
     </row>
-    <row r="85" spans="2:8">
+    <row r="85" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B85">
         <f t="shared" si="7"/>
         <v>83</v>
@@ -37100,7 +36645,7 @@
         <v>83:10</v>
       </c>
     </row>
-    <row r="86" spans="2:8">
+    <row r="86" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B86">
         <f t="shared" si="7"/>
         <v>84</v>
@@ -37129,7 +36674,7 @@
         <v>84:10</v>
       </c>
     </row>
-    <row r="87" spans="2:8">
+    <row r="87" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B87">
         <f t="shared" si="7"/>
         <v>85</v>
@@ -37158,7 +36703,7 @@
         <v>85:10</v>
       </c>
     </row>
-    <row r="88" spans="2:8">
+    <row r="88" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B88">
         <f t="shared" si="7"/>
         <v>86</v>
@@ -37187,7 +36732,7 @@
         <v>86:10</v>
       </c>
     </row>
-    <row r="89" spans="2:8">
+    <row r="89" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B89">
         <f t="shared" si="7"/>
         <v>87</v>
@@ -37216,7 +36761,7 @@
         <v>87:10</v>
       </c>
     </row>
-    <row r="90" spans="2:8">
+    <row r="90" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B90">
         <f t="shared" si="7"/>
         <v>88</v>
@@ -37245,7 +36790,7 @@
         <v>88:10</v>
       </c>
     </row>
-    <row r="91" spans="2:8">
+    <row r="91" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B91">
         <f t="shared" si="7"/>
         <v>89</v>
@@ -37274,7 +36819,7 @@
         <v>89:10</v>
       </c>
     </row>
-    <row r="92" spans="2:8">
+    <row r="92" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B92">
         <f t="shared" si="7"/>
         <v>90</v>
@@ -37303,7 +36848,7 @@
         <v>90:10</v>
       </c>
     </row>
-    <row r="93" spans="2:8">
+    <row r="93" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B93">
         <f t="shared" si="7"/>
         <v>91</v>
@@ -37332,7 +36877,7 @@
         <v>91:10</v>
       </c>
     </row>
-    <row r="94" spans="2:8">
+    <row r="94" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B94">
         <f t="shared" si="7"/>
         <v>92</v>
@@ -37361,7 +36906,7 @@
         <v>92:10</v>
       </c>
     </row>
-    <row r="95" spans="2:8">
+    <row r="95" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B95">
         <f t="shared" ref="B95:B158" si="13">B94+1</f>
         <v>93</v>
@@ -37390,7 +36935,7 @@
         <v>93:10</v>
       </c>
     </row>
-    <row r="96" spans="2:8">
+    <row r="96" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B96">
         <f t="shared" si="13"/>
         <v>94</v>
@@ -37419,7 +36964,7 @@
         <v>94:10</v>
       </c>
     </row>
-    <row r="97" spans="2:8">
+    <row r="97" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B97">
         <f t="shared" si="13"/>
         <v>95</v>
@@ -37448,7 +36993,7 @@
         <v>95:10</v>
       </c>
     </row>
-    <row r="98" spans="2:8">
+    <row r="98" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B98">
         <f t="shared" si="13"/>
         <v>96</v>
@@ -37477,7 +37022,7 @@
         <v>96:10</v>
       </c>
     </row>
-    <row r="99" spans="2:8">
+    <row r="99" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B99">
         <f t="shared" si="13"/>
         <v>97</v>
@@ -37506,7 +37051,7 @@
         <v>97:10</v>
       </c>
     </row>
-    <row r="100" spans="2:8">
+    <row r="100" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B100">
         <f t="shared" si="13"/>
         <v>98</v>
@@ -37535,7 +37080,7 @@
         <v>98:10</v>
       </c>
     </row>
-    <row r="101" spans="2:8">
+    <row r="101" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B101">
         <f t="shared" si="13"/>
         <v>99</v>
@@ -37564,7 +37109,7 @@
         <v>99:10</v>
       </c>
     </row>
-    <row r="102" spans="2:8">
+    <row r="102" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B102">
         <f t="shared" si="13"/>
         <v>100</v>
@@ -37593,7 +37138,7 @@
         <v>100:10</v>
       </c>
     </row>
-    <row r="103" spans="2:8">
+    <row r="103" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B103">
         <f t="shared" si="13"/>
         <v>101</v>
@@ -37622,7 +37167,7 @@
         <v>101:10</v>
       </c>
     </row>
-    <row r="104" spans="2:8">
+    <row r="104" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B104">
         <f t="shared" si="13"/>
         <v>102</v>
@@ -37651,7 +37196,7 @@
         <v>102:10</v>
       </c>
     </row>
-    <row r="105" spans="2:8">
+    <row r="105" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B105">
         <f t="shared" si="13"/>
         <v>103</v>
@@ -37680,7 +37225,7 @@
         <v>103:10</v>
       </c>
     </row>
-    <row r="106" spans="2:8">
+    <row r="106" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B106">
         <f t="shared" si="13"/>
         <v>104</v>
@@ -37709,7 +37254,7 @@
         <v>104:10</v>
       </c>
     </row>
-    <row r="107" spans="2:8">
+    <row r="107" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B107">
         <f t="shared" si="13"/>
         <v>105</v>
@@ -37738,7 +37283,7 @@
         <v>105:10</v>
       </c>
     </row>
-    <row r="108" spans="2:8">
+    <row r="108" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B108">
         <f t="shared" si="13"/>
         <v>106</v>
@@ -37767,7 +37312,7 @@
         <v>106:10</v>
       </c>
     </row>
-    <row r="109" spans="2:8">
+    <row r="109" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B109">
         <f t="shared" si="13"/>
         <v>107</v>
@@ -37796,7 +37341,7 @@
         <v>107:10</v>
       </c>
     </row>
-    <row r="110" spans="2:8">
+    <row r="110" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B110">
         <f t="shared" si="13"/>
         <v>108</v>
@@ -37825,7 +37370,7 @@
         <v>108:10</v>
       </c>
     </row>
-    <row r="111" spans="2:8">
+    <row r="111" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B111">
         <f t="shared" si="13"/>
         <v>109</v>
@@ -37854,7 +37399,7 @@
         <v>109:10</v>
       </c>
     </row>
-    <row r="112" spans="2:8">
+    <row r="112" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B112">
         <f t="shared" si="13"/>
         <v>110</v>
@@ -37883,7 +37428,7 @@
         <v>110:10</v>
       </c>
     </row>
-    <row r="113" spans="2:8">
+    <row r="113" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B113">
         <f t="shared" si="13"/>
         <v>111</v>
@@ -37912,7 +37457,7 @@
         <v>111:10</v>
       </c>
     </row>
-    <row r="114" spans="2:8">
+    <row r="114" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B114">
         <f t="shared" si="13"/>
         <v>112</v>
@@ -37941,7 +37486,7 @@
         <v>112:10</v>
       </c>
     </row>
-    <row r="115" spans="2:8">
+    <row r="115" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B115">
         <f t="shared" si="13"/>
         <v>113</v>
@@ -37970,7 +37515,7 @@
         <v>113:10</v>
       </c>
     </row>
-    <row r="116" spans="2:8">
+    <row r="116" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B116">
         <f t="shared" si="13"/>
         <v>114</v>
@@ -37999,7 +37544,7 @@
         <v>114:10</v>
       </c>
     </row>
-    <row r="117" spans="2:8">
+    <row r="117" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B117">
         <f t="shared" si="13"/>
         <v>115</v>
@@ -38028,7 +37573,7 @@
         <v>115:10</v>
       </c>
     </row>
-    <row r="118" spans="2:8">
+    <row r="118" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B118">
         <f t="shared" si="13"/>
         <v>116</v>
@@ -38057,7 +37602,7 @@
         <v>116:10</v>
       </c>
     </row>
-    <row r="119" spans="2:8">
+    <row r="119" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B119">
         <f t="shared" si="13"/>
         <v>117</v>
@@ -38086,7 +37631,7 @@
         <v>117:10</v>
       </c>
     </row>
-    <row r="120" spans="2:8">
+    <row r="120" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B120">
         <f t="shared" si="13"/>
         <v>118</v>
@@ -38115,7 +37660,7 @@
         <v>118:10</v>
       </c>
     </row>
-    <row r="121" spans="2:8">
+    <row r="121" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B121">
         <f t="shared" si="13"/>
         <v>119</v>
@@ -38144,7 +37689,7 @@
         <v>119:10</v>
       </c>
     </row>
-    <row r="122" spans="2:8">
+    <row r="122" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B122">
         <f t="shared" si="13"/>
         <v>120</v>
@@ -38173,7 +37718,7 @@
         <v>120:10</v>
       </c>
     </row>
-    <row r="123" spans="2:8">
+    <row r="123" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B123">
         <f t="shared" si="13"/>
         <v>121</v>
@@ -38202,7 +37747,7 @@
         <v>121:10</v>
       </c>
     </row>
-    <row r="124" spans="2:8">
+    <row r="124" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B124">
         <f t="shared" si="13"/>
         <v>122</v>
@@ -38231,7 +37776,7 @@
         <v>122:10</v>
       </c>
     </row>
-    <row r="125" spans="2:8">
+    <row r="125" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B125">
         <f t="shared" si="13"/>
         <v>123</v>
@@ -38260,7 +37805,7 @@
         <v>123:10</v>
       </c>
     </row>
-    <row r="126" spans="2:8">
+    <row r="126" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B126">
         <f t="shared" si="13"/>
         <v>124</v>
@@ -38289,7 +37834,7 @@
         <v>124:10</v>
       </c>
     </row>
-    <row r="127" spans="2:8">
+    <row r="127" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B127">
         <f t="shared" si="13"/>
         <v>125</v>
@@ -38318,7 +37863,7 @@
         <v>125:10</v>
       </c>
     </row>
-    <row r="128" spans="2:8">
+    <row r="128" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B128">
         <f t="shared" si="13"/>
         <v>126</v>
@@ -38347,7 +37892,7 @@
         <v>126:10</v>
       </c>
     </row>
-    <row r="129" spans="2:8">
+    <row r="129" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B129">
         <f t="shared" si="13"/>
         <v>127</v>
@@ -38376,7 +37921,7 @@
         <v>127:10</v>
       </c>
     </row>
-    <row r="130" spans="2:8">
+    <row r="130" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B130">
         <f t="shared" si="13"/>
         <v>128</v>
@@ -38405,7 +37950,7 @@
         <v>128:10</v>
       </c>
     </row>
-    <row r="131" spans="2:8">
+    <row r="131" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B131">
         <f t="shared" si="13"/>
         <v>129</v>
@@ -38434,7 +37979,7 @@
         <v>129:10</v>
       </c>
     </row>
-    <row r="132" spans="2:8">
+    <row r="132" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B132">
         <f t="shared" si="13"/>
         <v>130</v>
@@ -38463,7 +38008,7 @@
         <v>130:10</v>
       </c>
     </row>
-    <row r="133" spans="2:8">
+    <row r="133" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B133">
         <f t="shared" si="13"/>
         <v>131</v>
@@ -38492,7 +38037,7 @@
         <v>131:10</v>
       </c>
     </row>
-    <row r="134" spans="2:8">
+    <row r="134" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B134">
         <f t="shared" si="13"/>
         <v>132</v>
@@ -38521,7 +38066,7 @@
         <v>132:10</v>
       </c>
     </row>
-    <row r="135" spans="2:8">
+    <row r="135" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B135">
         <f t="shared" si="13"/>
         <v>133</v>
@@ -38550,7 +38095,7 @@
         <v>133:10</v>
       </c>
     </row>
-    <row r="136" spans="2:8">
+    <row r="136" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B136">
         <f t="shared" si="13"/>
         <v>134</v>
@@ -38579,7 +38124,7 @@
         <v>134:10</v>
       </c>
     </row>
-    <row r="137" spans="2:8">
+    <row r="137" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B137">
         <f t="shared" si="13"/>
         <v>135</v>
@@ -38608,7 +38153,7 @@
         <v>135:10</v>
       </c>
     </row>
-    <row r="138" spans="2:8">
+    <row r="138" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B138">
         <f t="shared" si="13"/>
         <v>136</v>
@@ -38637,7 +38182,7 @@
         <v>136:10</v>
       </c>
     </row>
-    <row r="139" spans="2:8">
+    <row r="139" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B139">
         <f t="shared" si="13"/>
         <v>137</v>
@@ -38666,7 +38211,7 @@
         <v>137:10</v>
       </c>
     </row>
-    <row r="140" spans="2:8">
+    <row r="140" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B140">
         <f t="shared" si="13"/>
         <v>138</v>
@@ -38695,7 +38240,7 @@
         <v>138:10</v>
       </c>
     </row>
-    <row r="141" spans="2:8">
+    <row r="141" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B141">
         <f t="shared" si="13"/>
         <v>139</v>
@@ -38724,7 +38269,7 @@
         <v>139:10</v>
       </c>
     </row>
-    <row r="142" spans="2:8">
+    <row r="142" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B142">
         <f t="shared" si="13"/>
         <v>140</v>
@@ -38753,7 +38298,7 @@
         <v>140:10</v>
       </c>
     </row>
-    <row r="143" spans="2:8">
+    <row r="143" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B143">
         <f t="shared" si="13"/>
         <v>141</v>
@@ -38782,7 +38327,7 @@
         <v>141:10</v>
       </c>
     </row>
-    <row r="144" spans="2:8">
+    <row r="144" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B144">
         <f t="shared" si="13"/>
         <v>142</v>
@@ -38811,7 +38356,7 @@
         <v>142:10</v>
       </c>
     </row>
-    <row r="145" spans="2:8">
+    <row r="145" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B145">
         <f t="shared" si="13"/>
         <v>143</v>
@@ -38840,7 +38385,7 @@
         <v>143:10</v>
       </c>
     </row>
-    <row r="146" spans="2:8">
+    <row r="146" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B146">
         <f t="shared" si="13"/>
         <v>144</v>
@@ -38869,7 +38414,7 @@
         <v>144:10</v>
       </c>
     </row>
-    <row r="147" spans="2:8">
+    <row r="147" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B147">
         <f t="shared" si="13"/>
         <v>145</v>
@@ -38898,7 +38443,7 @@
         <v>145:10</v>
       </c>
     </row>
-    <row r="148" spans="2:8">
+    <row r="148" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B148">
         <f t="shared" si="13"/>
         <v>146</v>
@@ -38927,7 +38472,7 @@
         <v>146:10</v>
       </c>
     </row>
-    <row r="149" spans="2:8">
+    <row r="149" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B149">
         <f t="shared" si="13"/>
         <v>147</v>
@@ -38956,7 +38501,7 @@
         <v>147:10</v>
       </c>
     </row>
-    <row r="150" spans="2:8">
+    <row r="150" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B150">
         <f t="shared" si="13"/>
         <v>148</v>
@@ -38985,7 +38530,7 @@
         <v>148:10</v>
       </c>
     </row>
-    <row r="151" spans="2:8">
+    <row r="151" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B151">
         <f t="shared" si="13"/>
         <v>149</v>
@@ -39014,7 +38559,7 @@
         <v>149:10</v>
       </c>
     </row>
-    <row r="152" spans="2:8">
+    <row r="152" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B152">
         <f t="shared" si="13"/>
         <v>150</v>
@@ -39043,7 +38588,7 @@
         <v>150:10</v>
       </c>
     </row>
-    <row r="153" spans="2:8">
+    <row r="153" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B153">
         <f t="shared" si="13"/>
         <v>151</v>
@@ -39072,7 +38617,7 @@
         <v>151:10</v>
       </c>
     </row>
-    <row r="154" spans="2:8">
+    <row r="154" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B154">
         <f t="shared" si="13"/>
         <v>152</v>
@@ -39101,7 +38646,7 @@
         <v>152:10</v>
       </c>
     </row>
-    <row r="155" spans="2:8">
+    <row r="155" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B155">
         <f t="shared" si="13"/>
         <v>153</v>
@@ -39130,7 +38675,7 @@
         <v>153:10</v>
       </c>
     </row>
-    <row r="156" spans="2:8">
+    <row r="156" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B156">
         <f t="shared" si="13"/>
         <v>154</v>
@@ -39159,7 +38704,7 @@
         <v>154:10</v>
       </c>
     </row>
-    <row r="157" spans="2:8">
+    <row r="157" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B157">
         <f t="shared" si="13"/>
         <v>155</v>
@@ -39188,7 +38733,7 @@
         <v>155:10</v>
       </c>
     </row>
-    <row r="158" spans="2:8">
+    <row r="158" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B158">
         <f t="shared" si="13"/>
         <v>156</v>
@@ -39217,7 +38762,7 @@
         <v>156:10</v>
       </c>
     </row>
-    <row r="159" spans="2:8">
+    <row r="159" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B159">
         <f t="shared" ref="B159:B162" si="19">B158+1</f>
         <v>157</v>
@@ -39246,7 +38791,7 @@
         <v>157:10</v>
       </c>
     </row>
-    <row r="160" spans="2:8">
+    <row r="160" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B160">
         <f t="shared" si="19"/>
         <v>158</v>
@@ -39275,7 +38820,7 @@
         <v>158:10</v>
       </c>
     </row>
-    <row r="161" spans="2:8">
+    <row r="161" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B161">
         <f t="shared" si="19"/>
         <v>159</v>
@@ -39304,7 +38849,7 @@
         <v>159:10</v>
       </c>
     </row>
-    <row r="162" spans="2:8">
+    <row r="162" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B162">
         <f t="shared" si="19"/>
         <v>160</v>
@@ -39334,7 +38879,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07DDE2EA-0F5B-4702-8E39-5A9AAE63906F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD4BA7A6-D71E-47FA-B800-93E317B5EE35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_foe_v8" sheetId="1" r:id="rId1"/>
@@ -6694,7 +6694,7 @@
         <v>111</v>
       </c>
       <c r="X52" s="13" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="Y52" s="17">
         <v>214001011</v>
@@ -6797,7 +6797,7 @@
         <v>111</v>
       </c>
       <c r="X53" s="3" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="Y53" s="16">
         <v>214001011</v>
@@ -6900,7 +6900,7 @@
         <v>111</v>
       </c>
       <c r="X54" s="3" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="Y54" s="16">
         <v>204001001</v>
@@ -7003,7 +7003,7 @@
         <v>111</v>
       </c>
       <c r="X55" s="3" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="Y55" s="16">
         <v>204002001</v>
@@ -7106,7 +7106,7 @@
         <v>111</v>
       </c>
       <c r="X56" s="3" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="Y56" s="16">
         <v>211001001</v>
@@ -7209,7 +7209,7 @@
         <v>111</v>
       </c>
       <c r="X57" s="3" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="Y57" s="16">
         <v>211002001</v>
@@ -7312,7 +7312,7 @@
         <v>111</v>
       </c>
       <c r="X58" s="13" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="Y58" s="17">
         <v>203001001</v>
@@ -7415,7 +7415,7 @@
         <v>111</v>
       </c>
       <c r="X59" s="3" t="s">
-        <v>139</v>
+        <v>112</v>
       </c>
       <c r="Y59" s="16">
         <v>203002011</v>
@@ -7518,7 +7518,7 @@
         <v>111</v>
       </c>
       <c r="X60" s="3" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="Y60" s="16">
         <v>203003001</v>
@@ -7619,7 +7619,7 @@
         <v>111</v>
       </c>
       <c r="X61" s="3" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="Y61" s="16">
         <v>201002011</v>
@@ -8235,7 +8235,7 @@
         <v>111</v>
       </c>
       <c r="X67" s="13" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="Y67" s="17">
         <v>214001011</v>
@@ -8338,7 +8338,7 @@
         <v>111</v>
       </c>
       <c r="X68" s="13" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="Y68" s="17">
         <v>204001001</v>
@@ -8441,7 +8441,7 @@
         <v>111</v>
       </c>
       <c r="X69" s="3" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="Y69" s="16">
         <v>204001001</v>
@@ -8544,7 +8544,7 @@
         <v>111</v>
       </c>
       <c r="X70" s="3" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="Y70" s="16">
         <v>204002001</v>
@@ -8647,7 +8647,7 @@
         <v>111</v>
       </c>
       <c r="X71" s="3" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="Y71" s="16">
         <v>211001001</v>
@@ -8750,7 +8750,7 @@
         <v>111</v>
       </c>
       <c r="X72" s="3" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="Y72" s="16">
         <v>211002001</v>
@@ -8853,7 +8853,7 @@
         <v>111</v>
       </c>
       <c r="X73" s="3" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="Y73" s="16">
         <v>203001001</v>
@@ -8956,7 +8956,7 @@
         <v>111</v>
       </c>
       <c r="X74" s="3" t="s">
-        <v>139</v>
+        <v>112</v>
       </c>
       <c r="Y74" s="16">
         <v>203002011</v>
@@ -9059,7 +9059,7 @@
         <v>111</v>
       </c>
       <c r="X75" s="3" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="Y75" s="16">
         <v>203003001</v>
@@ -9160,7 +9160,7 @@
         <v>111</v>
       </c>
       <c r="X76" s="3" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="Y76" s="16">
         <v>201002011</v>
@@ -9774,7 +9774,7 @@
         <v>111</v>
       </c>
       <c r="X82" s="3" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="Y82" s="16">
         <v>201002011</v>
@@ -9877,7 +9877,7 @@
         <v>111</v>
       </c>
       <c r="X83" s="3" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="Y83" s="16">
         <v>214001011</v>
@@ -9980,7 +9980,7 @@
         <v>111</v>
       </c>
       <c r="X84" s="3" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="Y84" s="16">
         <v>204001001</v>
@@ -10083,7 +10083,7 @@
         <v>111</v>
       </c>
       <c r="X85" s="3" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="Y85" s="16">
         <v>204002001</v>
@@ -10186,7 +10186,7 @@
         <v>111</v>
       </c>
       <c r="X86" s="3" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="Y86" s="16">
         <v>211001001</v>
@@ -10289,7 +10289,7 @@
         <v>111</v>
       </c>
       <c r="X87" s="3" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="Y87" s="16">
         <v>211002001</v>
@@ -10392,7 +10392,7 @@
         <v>111</v>
       </c>
       <c r="X88" s="3" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="Y88" s="16">
         <v>203001001</v>
@@ -10495,7 +10495,7 @@
         <v>111</v>
       </c>
       <c r="X89" s="3" t="s">
-        <v>139</v>
+        <v>112</v>
       </c>
       <c r="Y89" s="16">
         <v>203002011</v>
@@ -10598,7 +10598,7 @@
         <v>111</v>
       </c>
       <c r="X90" s="3" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="Y90" s="16">
         <v>203003001</v>
@@ -10699,7 +10699,7 @@
         <v>111</v>
       </c>
       <c r="X91" s="3" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="Y91" s="16">
         <v>201002011</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD4BA7A6-D71E-47FA-B800-93E317B5EE35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2061F313-B810-4B01-9833-2319EA00C569}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_foe_v8" sheetId="1" r:id="rId1"/>
@@ -6160,10 +6160,10 @@
         <v>15</v>
       </c>
       <c r="Q47" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R47" s="13">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="S47" s="13">
         <v>-5500</v>
@@ -6670,13 +6670,13 @@
         <v>0</v>
       </c>
       <c r="P52" s="13">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Q52" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R52" s="13">
-        <v>36</v>
+        <v>192</v>
       </c>
       <c r="S52" s="13">
         <v>-5500</v>
@@ -7288,13 +7288,13 @@
         <v>0</v>
       </c>
       <c r="P58" s="13">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Q58" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R58" s="13">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="S58" s="13">
         <v>-5500</v>
@@ -7698,13 +7698,13 @@
         <v>0</v>
       </c>
       <c r="P62" s="13">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Q62" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R62" s="13">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="S62" s="13">
         <v>-5500</v>
@@ -8211,13 +8211,13 @@
         <v>0</v>
       </c>
       <c r="P67" s="13">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q67" s="13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R67" s="13">
-        <v>36</v>
+        <v>403</v>
       </c>
       <c r="S67" s="13">
         <v>-5500</v>
@@ -8314,13 +8314,13 @@
         <v>0</v>
       </c>
       <c r="P68" s="13">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="Q68" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R68" s="13">
-        <v>36</v>
+        <v>92</v>
       </c>
       <c r="S68" s="13">
         <v>-5500</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2061F313-B810-4B01-9833-2319EA00C569}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5650F34-0DA7-43C7-9B57-1D2A5FE1B7CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_foe_v8" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2244" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2272" uniqueCount="252">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -784,6 +784,19 @@
     <t>4-守卫0</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
+  <si>
+    <t>木桩怪1</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>木桩怪2</t>
+  </si>
+  <si>
+    <t>木桩怪3</t>
+  </si>
+  <si>
+    <t>木桩怪4</t>
+  </si>
 </sst>
 </file>
 
@@ -1120,7 +1133,27 @@
     <cellStyle name="输入" xfId="1" builtinId="20"/>
     <cellStyle name="输入 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1403,7 +1436,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AJ305"/>
+  <dimension ref="A1:AJ309"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.125" style="9" customWidth="1"/>
@@ -24002,426 +24035,427 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A221" s="3">
-        <v>301101</v>
-      </c>
-      <c r="B221" s="3">
+    <row r="221" spans="1:36" s="8" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A221" s="19">
+        <v>9999101</v>
+      </c>
+      <c r="B221" s="13">
+        <v>1</v>
+      </c>
+      <c r="C221" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="D221" s="13"/>
+      <c r="F221" s="13"/>
+      <c r="G221" s="13">
+        <v>21</v>
+      </c>
+      <c r="H221" s="13">
+        <v>9</v>
+      </c>
+      <c r="I221" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="J221" s="13">
+        <v>0</v>
+      </c>
+      <c r="K221" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="L221" s="13">
+        <v>800001011</v>
+      </c>
+      <c r="M221" s="13">
+        <v>1</v>
+      </c>
+      <c r="N221" s="13">
+        <v>100</v>
+      </c>
+      <c r="O221" s="13">
+        <v>0</v>
+      </c>
+      <c r="P221" s="13">
+        <v>15</v>
+      </c>
+      <c r="Q221" s="13">
+        <v>1</v>
+      </c>
+      <c r="R221" s="13">
+        <v>99999999</v>
+      </c>
+      <c r="S221" s="13">
+        <v>-5500</v>
+      </c>
+      <c r="T221" s="13">
+        <v>1</v>
+      </c>
+      <c r="U221" s="13">
+        <v>0</v>
+      </c>
+      <c r="V221" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="W221" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="X221" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="Y221" s="17">
+        <v>201001011</v>
+      </c>
+      <c r="Z221" s="17">
+        <v>0</v>
+      </c>
+      <c r="AA221" s="13">
+        <v>1</v>
+      </c>
+      <c r="AB221" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC221" s="13">
+        <v>15000</v>
+      </c>
+      <c r="AD221" s="13">
+        <v>10000</v>
+      </c>
+      <c r="AE221" s="13">
+        <v>0</v>
+      </c>
+      <c r="AF221" s="8">
+        <v>40</v>
+      </c>
+      <c r="AG221" s="8">
+        <v>0</v>
+      </c>
+      <c r="AH221" s="8">
+        <v>0</v>
+      </c>
+      <c r="AI221" s="8">
         <v>30</v>
       </c>
-      <c r="C221" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="D221" s="3"/>
-      <c r="F221" s="3"/>
-      <c r="G221" s="3">
+      <c r="AJ221" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="1:36" s="8" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A222" s="19">
+        <v>9999102</v>
+      </c>
+      <c r="B222" s="13">
+        <v>1</v>
+      </c>
+      <c r="C222" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="D222" s="13"/>
+      <c r="F222" s="13"/>
+      <c r="G222" s="13">
+        <v>21</v>
+      </c>
+      <c r="H222" s="13">
+        <v>9</v>
+      </c>
+      <c r="I222" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="J222" s="13">
+        <v>0</v>
+      </c>
+      <c r="K222" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="L222" s="13">
+        <v>800014011</v>
+      </c>
+      <c r="M222" s="13">
+        <v>1</v>
+      </c>
+      <c r="N222" s="13">
+        <v>100</v>
+      </c>
+      <c r="O222" s="13">
+        <v>0</v>
+      </c>
+      <c r="P222" s="13">
+        <v>18</v>
+      </c>
+      <c r="Q222" s="13">
+        <v>2</v>
+      </c>
+      <c r="R222" s="13">
+        <v>99999999</v>
+      </c>
+      <c r="S222" s="13">
+        <v>-5500</v>
+      </c>
+      <c r="T222" s="13">
+        <v>1</v>
+      </c>
+      <c r="U222" s="13">
+        <v>0</v>
+      </c>
+      <c r="V222" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="W222" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="X222" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="Y222" s="17">
+        <v>214001011</v>
+      </c>
+      <c r="Z222" s="17">
+        <v>0</v>
+      </c>
+      <c r="AA222" s="13">
+        <v>1</v>
+      </c>
+      <c r="AB222" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC222" s="13">
+        <v>15000</v>
+      </c>
+      <c r="AD222" s="13">
+        <v>10000</v>
+      </c>
+      <c r="AE222" s="13">
+        <v>0</v>
+      </c>
+      <c r="AF222" s="8">
+        <v>40</v>
+      </c>
+      <c r="AG222" s="8">
+        <v>0</v>
+      </c>
+      <c r="AH222" s="8">
+        <v>0</v>
+      </c>
+      <c r="AI222" s="8">
+        <v>4</v>
+      </c>
+      <c r="AJ222" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:36" s="8" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A223" s="19">
+        <v>9999103</v>
+      </c>
+      <c r="B223" s="13">
+        <v>1</v>
+      </c>
+      <c r="C223" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="D223" s="13"/>
+      <c r="F223" s="13"/>
+      <c r="G223" s="13">
+        <v>21</v>
+      </c>
+      <c r="H223" s="13">
+        <v>9</v>
+      </c>
+      <c r="I223" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="J223" s="13">
+        <v>0</v>
+      </c>
+      <c r="K223" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="L223" s="13">
+        <v>800003011</v>
+      </c>
+      <c r="M223" s="13">
+        <v>1</v>
+      </c>
+      <c r="N223" s="13">
+        <v>100</v>
+      </c>
+      <c r="O223" s="13">
+        <v>0</v>
+      </c>
+      <c r="P223" s="13">
+        <v>18</v>
+      </c>
+      <c r="Q223" s="13">
+        <v>3</v>
+      </c>
+      <c r="R223" s="13">
+        <v>99999999</v>
+      </c>
+      <c r="S223" s="13">
+        <v>-5500</v>
+      </c>
+      <c r="T223" s="13">
+        <v>1</v>
+      </c>
+      <c r="U223" s="13">
+        <v>0</v>
+      </c>
+      <c r="V223" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="W223" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="X223" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="Y223" s="17">
+        <v>203001001</v>
+      </c>
+      <c r="Z223" s="17">
+        <v>0</v>
+      </c>
+      <c r="AA223" s="13">
+        <v>1</v>
+      </c>
+      <c r="AB223" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC223" s="13">
+        <v>15000</v>
+      </c>
+      <c r="AD223" s="13">
+        <v>10000</v>
+      </c>
+      <c r="AE223" s="13">
+        <v>0</v>
+      </c>
+      <c r="AF223" s="8">
+        <v>40</v>
+      </c>
+      <c r="AG223" s="8">
+        <v>0</v>
+      </c>
+      <c r="AH223" s="8">
+        <v>0</v>
+      </c>
+      <c r="AI223" s="8">
+        <v>16</v>
+      </c>
+      <c r="AJ223" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:36" s="8" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A224" s="19">
+        <v>9999104</v>
+      </c>
+      <c r="B224" s="13">
+        <v>2</v>
+      </c>
+      <c r="C224" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="D224" s="13"/>
+      <c r="F224" s="13"/>
+      <c r="G224" s="13">
+        <v>21</v>
+      </c>
+      <c r="H224" s="13">
+        <v>9</v>
+      </c>
+      <c r="I224" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="J224" s="13">
+        <v>0</v>
+      </c>
+      <c r="K224" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="L224" s="13">
+        <v>800004011</v>
+      </c>
+      <c r="M224" s="13">
+        <v>1</v>
+      </c>
+      <c r="N224" s="13">
+        <v>100</v>
+      </c>
+      <c r="O224" s="13">
+        <v>0</v>
+      </c>
+      <c r="P224" s="13">
+        <v>25</v>
+      </c>
+      <c r="Q224" s="13">
+        <v>4</v>
+      </c>
+      <c r="R224" s="13">
+        <v>99999999</v>
+      </c>
+      <c r="S224" s="13">
+        <v>-5500</v>
+      </c>
+      <c r="T224" s="13">
+        <v>1</v>
+      </c>
+      <c r="U224" s="13">
+        <v>0</v>
+      </c>
+      <c r="V224" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="W224" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="X224" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="Y224" s="17">
+        <v>204001001</v>
+      </c>
+      <c r="Z224" s="17">
+        <v>0</v>
+      </c>
+      <c r="AA224" s="13">
+        <v>1</v>
+      </c>
+      <c r="AB224" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC224" s="13">
+        <v>15000</v>
+      </c>
+      <c r="AD224" s="13">
+        <v>10000</v>
+      </c>
+      <c r="AE224" s="13">
+        <v>0</v>
+      </c>
+      <c r="AF224" s="8">
+        <v>40</v>
+      </c>
+      <c r="AG224" s="8">
+        <v>0</v>
+      </c>
+      <c r="AH224" s="8">
+        <v>0</v>
+      </c>
+      <c r="AI224" s="8">
         <v>12</v>
       </c>
-      <c r="H221" s="3">
-        <v>1</v>
-      </c>
-      <c r="I221" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="J221" s="3">
-        <v>0</v>
-      </c>
-      <c r="K221" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="L221" s="3">
-        <v>800001011</v>
-      </c>
-      <c r="M221" s="3">
-        <v>1</v>
-      </c>
-      <c r="N221" s="3">
-        <v>70</v>
-      </c>
-      <c r="O221" s="3">
-        <v>0</v>
-      </c>
-      <c r="P221" s="3">
-        <v>15</v>
-      </c>
-      <c r="Q221" s="3">
-        <v>0</v>
-      </c>
-      <c r="R221" s="3">
-        <v>20</v>
-      </c>
-      <c r="S221" s="3">
-        <v>-5500</v>
-      </c>
-      <c r="T221" s="3">
-        <v>1</v>
-      </c>
-      <c r="U221" s="3">
-        <v>0</v>
-      </c>
-      <c r="V221" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="W221" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="X221" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="Y221" s="16">
-        <v>201001011</v>
-      </c>
-      <c r="Z221" s="16">
-        <v>0</v>
-      </c>
-      <c r="AA221" s="3">
-        <v>1</v>
-      </c>
-      <c r="AB221" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="AC221" s="3">
-        <v>15000</v>
-      </c>
-      <c r="AD221" s="3">
-        <v>10000</v>
-      </c>
-      <c r="AE221" s="3">
-        <v>25010001</v>
-      </c>
-      <c r="AF221" s="9">
-        <v>40</v>
-      </c>
-      <c r="AG221" s="9">
-        <v>10000</v>
-      </c>
-      <c r="AH221" s="9">
-        <v>10000</v>
-      </c>
-      <c r="AI221" s="9">
-        <v>50</v>
-      </c>
-      <c r="AJ221" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="222" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A222" s="3">
-        <v>301102</v>
-      </c>
-      <c r="B222" s="3">
-        <v>30</v>
-      </c>
-      <c r="C222" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D222" s="3"/>
-      <c r="F222" s="3"/>
-      <c r="G222" s="3">
-        <v>12</v>
-      </c>
-      <c r="H222" s="3">
-        <v>1</v>
-      </c>
-      <c r="I222" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="J222" s="3">
-        <v>0</v>
-      </c>
-      <c r="K222" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="L222" s="3">
-        <v>800001021</v>
-      </c>
-      <c r="M222" s="3">
-        <v>1</v>
-      </c>
-      <c r="N222" s="3">
-        <v>200</v>
-      </c>
-      <c r="O222" s="3">
-        <v>0</v>
-      </c>
-      <c r="P222" s="3">
-        <v>30</v>
-      </c>
-      <c r="Q222" s="3">
-        <v>2</v>
-      </c>
-      <c r="R222" s="3">
-        <v>105</v>
-      </c>
-      <c r="S222" s="3">
-        <v>-5500</v>
-      </c>
-      <c r="T222" s="3">
-        <v>1</v>
-      </c>
-      <c r="U222" s="3">
-        <v>0</v>
-      </c>
-      <c r="V222" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="W222" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="X222" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="Y222" s="16">
-        <v>201002011</v>
-      </c>
-      <c r="Z222" s="16">
-        <v>0</v>
-      </c>
-      <c r="AA222" s="3">
-        <v>1</v>
-      </c>
-      <c r="AB222" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="AC222" s="3">
-        <v>15000</v>
-      </c>
-      <c r="AD222" s="3">
-        <v>10000</v>
-      </c>
-      <c r="AE222" s="3">
-        <v>25010001</v>
-      </c>
-      <c r="AF222" s="9">
-        <v>40</v>
-      </c>
-      <c r="AG222" s="9">
-        <v>3000</v>
-      </c>
-      <c r="AH222" s="9">
-        <v>10000</v>
-      </c>
-      <c r="AI222" s="9">
-        <v>15</v>
-      </c>
-      <c r="AJ222" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="223" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A223" s="2">
-        <v>301103</v>
-      </c>
-      <c r="B223" s="2">
-        <v>30</v>
-      </c>
-      <c r="C223" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="D223" s="2"/>
-      <c r="E223" s="18"/>
-      <c r="F223" s="2"/>
-      <c r="G223" s="2">
-        <v>12</v>
-      </c>
-      <c r="H223" s="2">
-        <v>1</v>
-      </c>
-      <c r="I223" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="J223" s="2">
-        <v>0</v>
-      </c>
-      <c r="K223" s="2"/>
-      <c r="L223" s="2">
-        <v>800001021</v>
-      </c>
-      <c r="M223" s="2">
-        <v>1</v>
-      </c>
-      <c r="N223" s="2">
-        <v>70</v>
-      </c>
-      <c r="O223" s="2">
-        <v>0</v>
-      </c>
-      <c r="P223" s="2">
-        <v>15</v>
-      </c>
-      <c r="Q223" s="2">
-        <v>1</v>
-      </c>
-      <c r="R223" s="2">
-        <v>300</v>
-      </c>
-      <c r="S223" s="2">
-        <v>-5500</v>
-      </c>
-      <c r="T223" s="2">
-        <v>1</v>
-      </c>
-      <c r="U223" s="2">
-        <v>250</v>
-      </c>
-      <c r="V223" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="W223" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="X223" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="Y223" s="23">
-        <v>201001011</v>
-      </c>
-      <c r="Z223" s="23">
-        <v>0</v>
-      </c>
-      <c r="AA223" s="2">
-        <v>1</v>
-      </c>
-      <c r="AB223" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="AC223" s="2">
-        <v>15000</v>
-      </c>
-      <c r="AD223" s="2">
-        <v>10000</v>
-      </c>
-      <c r="AE223" s="2">
-        <v>25010001</v>
-      </c>
-      <c r="AF223" s="9">
-        <v>40</v>
-      </c>
-      <c r="AG223" s="9">
-        <v>0</v>
-      </c>
-      <c r="AH223" s="9">
-        <v>0</v>
-      </c>
-      <c r="AI223" s="9">
-        <v>0</v>
-      </c>
-      <c r="AJ223" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="224" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A224" s="3">
-        <v>301104</v>
-      </c>
-      <c r="B224" s="3">
-        <v>30</v>
-      </c>
-      <c r="C224" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="D224" s="3"/>
-      <c r="F224" s="3"/>
-      <c r="G224" s="3">
-        <v>12</v>
-      </c>
-      <c r="H224" s="3">
-        <v>1</v>
-      </c>
-      <c r="I224" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="J224" s="3">
-        <v>0</v>
-      </c>
-      <c r="K224" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="L224" s="3">
-        <v>800001041</v>
-      </c>
-      <c r="M224" s="3">
-        <v>1</v>
-      </c>
-      <c r="N224" s="3">
-        <v>70</v>
-      </c>
-      <c r="O224" s="3">
-        <v>0</v>
-      </c>
-      <c r="P224" s="3">
-        <v>24</v>
-      </c>
-      <c r="Q224" s="3">
-        <v>0</v>
-      </c>
-      <c r="R224" s="3">
-        <v>17</v>
-      </c>
-      <c r="S224" s="3">
-        <v>-5500</v>
-      </c>
-      <c r="T224" s="3">
-        <v>1</v>
-      </c>
-      <c r="U224" s="3">
-        <v>0</v>
-      </c>
-      <c r="V224" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="W224" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="X224" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="Y224" s="16">
-        <v>201004011</v>
-      </c>
-      <c r="Z224" s="16">
-        <v>0</v>
-      </c>
-      <c r="AA224" s="3">
-        <v>1</v>
-      </c>
-      <c r="AB224" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="AC224" s="3">
-        <v>15000</v>
-      </c>
-      <c r="AD224" s="3">
-        <v>10000</v>
-      </c>
-      <c r="AE224" s="3">
-        <v>25010001</v>
-      </c>
-      <c r="AF224" s="9">
-        <v>40</v>
-      </c>
-      <c r="AG224" s="9">
-        <v>10000</v>
-      </c>
-      <c r="AH224" s="9">
-        <v>10000</v>
-      </c>
-      <c r="AI224" s="9">
-        <v>80</v>
-      </c>
-      <c r="AJ224" s="9">
-        <v>10</v>
+      <c r="AJ224" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="225" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A225" s="3">
-        <v>301105</v>
+        <v>301101</v>
       </c>
       <c r="B225" s="3">
         <v>30</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="D225" s="3"/>
       <c r="F225" s="3"/>
@@ -24438,28 +24472,28 @@
         <v>0</v>
       </c>
       <c r="K225" s="3" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="L225" s="3">
-        <v>800014011</v>
+        <v>800001011</v>
       </c>
       <c r="M225" s="3">
         <v>1</v>
       </c>
       <c r="N225" s="3">
-        <v>125</v>
+        <v>70</v>
       </c>
       <c r="O225" s="3">
         <v>0</v>
       </c>
       <c r="P225" s="3">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="Q225" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R225" s="3">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="S225" s="3">
         <v>-5500</v>
@@ -24480,7 +24514,7 @@
         <v>147</v>
       </c>
       <c r="Y225" s="16">
-        <v>214001011</v>
+        <v>201001011</v>
       </c>
       <c r="Z225" s="16">
         <v>0</v>
@@ -24489,7 +24523,7 @@
         <v>1</v>
       </c>
       <c r="AB225" s="9" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="AC225" s="3">
         <v>15000</v>
@@ -24510,109 +24544,110 @@
         <v>10000</v>
       </c>
       <c r="AI225" s="9">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AJ225" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="226" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A226" s="2">
-        <v>301106</v>
-      </c>
-      <c r="B226" s="2">
+      <c r="A226" s="3">
+        <v>301102</v>
+      </c>
+      <c r="B226" s="3">
         <v>30</v>
       </c>
-      <c r="C226" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="D226" s="2"/>
-      <c r="E226" s="18"/>
-      <c r="F226" s="2"/>
-      <c r="G226" s="2">
+      <c r="C226" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D226" s="3"/>
+      <c r="F226" s="3"/>
+      <c r="G226" s="3">
         <v>12</v>
       </c>
-      <c r="H226" s="2">
-        <v>1</v>
-      </c>
-      <c r="I226" s="2" t="s">
+      <c r="H226" s="3">
+        <v>1</v>
+      </c>
+      <c r="I226" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="J226" s="2">
-        <v>0</v>
-      </c>
-      <c r="K226" s="2"/>
-      <c r="L226" s="2">
-        <v>1000010</v>
-      </c>
-      <c r="M226" s="2">
-        <v>1</v>
-      </c>
-      <c r="N226" s="2">
-        <v>100</v>
-      </c>
-      <c r="O226" s="2">
-        <v>0</v>
-      </c>
-      <c r="P226" s="2">
-        <v>15</v>
-      </c>
-      <c r="Q226" s="2">
-        <v>0</v>
-      </c>
-      <c r="R226" s="2">
-        <v>36</v>
-      </c>
-      <c r="S226" s="2">
+      <c r="J226" s="3">
+        <v>0</v>
+      </c>
+      <c r="K226" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="L226" s="3">
+        <v>800001021</v>
+      </c>
+      <c r="M226" s="3">
+        <v>1</v>
+      </c>
+      <c r="N226" s="3">
+        <v>200</v>
+      </c>
+      <c r="O226" s="3">
+        <v>0</v>
+      </c>
+      <c r="P226" s="3">
+        <v>30</v>
+      </c>
+      <c r="Q226" s="3">
+        <v>2</v>
+      </c>
+      <c r="R226" s="3">
+        <v>105</v>
+      </c>
+      <c r="S226" s="3">
         <v>-5500</v>
       </c>
-      <c r="T226" s="2">
-        <v>1</v>
-      </c>
-      <c r="U226" s="2">
-        <v>0</v>
-      </c>
-      <c r="V226" s="2" t="s">
+      <c r="T226" s="3">
+        <v>1</v>
+      </c>
+      <c r="U226" s="3">
+        <v>0</v>
+      </c>
+      <c r="V226" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="W226" s="2" t="s">
+      <c r="W226" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="X226" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="Y226" s="2">
+      <c r="X226" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y226" s="16">
         <v>201002011</v>
       </c>
-      <c r="Z226" s="23">
-        <v>0</v>
-      </c>
-      <c r="AA226" s="2">
-        <v>1</v>
-      </c>
-      <c r="AB226" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="AC226" s="2">
+      <c r="Z226" s="16">
+        <v>0</v>
+      </c>
+      <c r="AA226" s="3">
+        <v>1</v>
+      </c>
+      <c r="AB226" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="AC226" s="3">
         <v>15000</v>
       </c>
-      <c r="AD226" s="2">
-        <v>10000</v>
-      </c>
-      <c r="AE226" s="2">
+      <c r="AD226" s="3">
+        <v>10000</v>
+      </c>
+      <c r="AE226" s="3">
         <v>25010001</v>
       </c>
       <c r="AF226" s="9">
         <v>40</v>
       </c>
       <c r="AG226" s="9">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="AH226" s="9">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI226" s="9">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AJ226" s="9">
         <v>0</v>
@@ -24620,13 +24655,13 @@
     </row>
     <row r="227" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A227" s="2">
-        <v>301107</v>
+        <v>301103</v>
       </c>
       <c r="B227" s="2">
         <v>30</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D227" s="2"/>
       <c r="E227" s="18"/>
@@ -24643,17 +24678,15 @@
       <c r="J227" s="2">
         <v>0</v>
       </c>
-      <c r="K227" s="2" t="s">
-        <v>121</v>
-      </c>
+      <c r="K227" s="2"/>
       <c r="L227" s="2">
-        <v>800014011</v>
+        <v>800001021</v>
       </c>
       <c r="M227" s="2">
         <v>1</v>
       </c>
       <c r="N227" s="2">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="O227" s="2">
         <v>0</v>
@@ -24662,10 +24695,10 @@
         <v>15</v>
       </c>
       <c r="Q227" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R227" s="2">
-        <v>36</v>
+        <v>300</v>
       </c>
       <c r="S227" s="2">
         <v>-5500</v>
@@ -24674,7 +24707,7 @@
         <v>1</v>
       </c>
       <c r="U227" s="2">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="V227" s="2" t="s">
         <v>110</v>
@@ -24683,10 +24716,10 @@
         <v>111</v>
       </c>
       <c r="X227" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="Y227" s="2">
-        <v>214001011</v>
+        <v>147</v>
+      </c>
+      <c r="Y227" s="23">
+        <v>201001011</v>
       </c>
       <c r="Z227" s="23">
         <v>0</v>
@@ -24695,7 +24728,7 @@
         <v>1</v>
       </c>
       <c r="AB227" s="18" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="AC227" s="2">
         <v>15000</v>
@@ -24722,15 +24755,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A228" s="3">
-        <v>301108</v>
+        <v>301104</v>
       </c>
       <c r="B228" s="3">
         <v>30</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D228" s="3"/>
       <c r="F228" s="3"/>
@@ -24747,28 +24780,28 @@
         <v>0</v>
       </c>
       <c r="K228" s="3" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="L228" s="3">
-        <v>800004011</v>
+        <v>800001041</v>
       </c>
       <c r="M228" s="3">
         <v>1</v>
       </c>
       <c r="N228" s="3">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="O228" s="3">
         <v>0</v>
       </c>
       <c r="P228" s="3">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="Q228" s="3">
         <v>0</v>
       </c>
-      <c r="R228" s="22">
-        <v>36</v>
+      <c r="R228" s="3">
+        <v>17</v>
       </c>
       <c r="S228" s="3">
         <v>-5500</v>
@@ -24786,10 +24819,10 @@
         <v>111</v>
       </c>
       <c r="X228" s="3" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="Y228" s="16">
-        <v>204001001</v>
+        <v>201004011</v>
       </c>
       <c r="Z228" s="16">
         <v>0</v>
@@ -24798,7 +24831,7 @@
         <v>1</v>
       </c>
       <c r="AB228" s="9" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="AC228" s="3">
         <v>15000</v>
@@ -24813,27 +24846,27 @@
         <v>40</v>
       </c>
       <c r="AG228" s="9">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH228" s="9">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI228" s="9">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AJ228" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="229" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="229" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A229" s="3">
-        <v>301109</v>
+        <v>301105</v>
       </c>
       <c r="B229" s="3">
         <v>30</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="D229" s="3"/>
       <c r="F229" s="3"/>
@@ -24850,28 +24883,28 @@
         <v>0</v>
       </c>
       <c r="K229" s="3" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="L229" s="3">
-        <v>800004021</v>
+        <v>800014011</v>
       </c>
       <c r="M229" s="3">
         <v>1</v>
       </c>
       <c r="N229" s="3">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="O229" s="3">
         <v>0</v>
       </c>
       <c r="P229" s="3">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Q229" s="3">
-        <v>0</v>
-      </c>
-      <c r="R229" s="22">
-        <v>36</v>
+        <v>1</v>
+      </c>
+      <c r="R229" s="3">
+        <v>43</v>
       </c>
       <c r="S229" s="3">
         <v>-5500</v>
@@ -24889,10 +24922,10 @@
         <v>111</v>
       </c>
       <c r="X229" s="3" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="Y229" s="16">
-        <v>204002001</v>
+        <v>214001011</v>
       </c>
       <c r="Z229" s="16">
         <v>0</v>
@@ -24901,7 +24934,7 @@
         <v>1</v>
       </c>
       <c r="AB229" s="9" t="s">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="AC229" s="3">
         <v>15000</v>
@@ -24916,103 +24949,102 @@
         <v>40</v>
       </c>
       <c r="AG229" s="9">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH229" s="9">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI229" s="9">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AJ229" s="9">
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A230" s="3">
-        <v>301110</v>
-      </c>
-      <c r="B230" s="3">
+    <row r="230" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A230" s="2">
+        <v>301106</v>
+      </c>
+      <c r="B230" s="2">
         <v>30</v>
       </c>
-      <c r="C230" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="D230" s="3"/>
-      <c r="F230" s="3"/>
-      <c r="G230" s="3">
+      <c r="C230" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D230" s="2"/>
+      <c r="E230" s="18"/>
+      <c r="F230" s="2"/>
+      <c r="G230" s="2">
         <v>12</v>
       </c>
-      <c r="H230" s="3">
-        <v>1</v>
-      </c>
-      <c r="I230" s="3" t="s">
+      <c r="H230" s="2">
+        <v>1</v>
+      </c>
+      <c r="I230" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="J230" s="3">
-        <v>0</v>
-      </c>
-      <c r="K230" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="L230" s="3">
-        <v>800011011</v>
-      </c>
-      <c r="M230" s="3">
-        <v>1</v>
-      </c>
-      <c r="N230" s="3">
+      <c r="J230" s="2">
+        <v>0</v>
+      </c>
+      <c r="K230" s="2"/>
+      <c r="L230" s="2">
+        <v>1000010</v>
+      </c>
+      <c r="M230" s="2">
+        <v>1</v>
+      </c>
+      <c r="N230" s="2">
         <v>100</v>
       </c>
-      <c r="O230" s="3">
-        <v>0</v>
-      </c>
-      <c r="P230" s="3">
+      <c r="O230" s="2">
+        <v>0</v>
+      </c>
+      <c r="P230" s="2">
         <v>15</v>
       </c>
-      <c r="Q230" s="3">
-        <v>0</v>
-      </c>
-      <c r="R230" s="22">
+      <c r="Q230" s="2">
+        <v>0</v>
+      </c>
+      <c r="R230" s="2">
         <v>36</v>
       </c>
-      <c r="S230" s="3">
+      <c r="S230" s="2">
         <v>-5500</v>
       </c>
-      <c r="T230" s="3">
-        <v>1</v>
-      </c>
-      <c r="U230" s="3">
-        <v>0</v>
-      </c>
-      <c r="V230" s="3" t="s">
+      <c r="T230" s="2">
+        <v>1</v>
+      </c>
+      <c r="U230" s="2">
+        <v>0</v>
+      </c>
+      <c r="V230" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="W230" s="3" t="s">
+      <c r="W230" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="X230" s="3" t="s">
+      <c r="X230" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="Y230" s="16">
-        <v>211001001</v>
-      </c>
-      <c r="Z230" s="16">
-        <v>0</v>
-      </c>
-      <c r="AA230" s="3">
-        <v>1</v>
-      </c>
-      <c r="AB230" s="9" t="s">
+      <c r="Y230" s="2">
+        <v>201002011</v>
+      </c>
+      <c r="Z230" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA230" s="2">
+        <v>1</v>
+      </c>
+      <c r="AB230" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="AC230" s="3">
+      <c r="AC230" s="2">
         <v>15000</v>
       </c>
-      <c r="AD230" s="3">
-        <v>10000</v>
-      </c>
-      <c r="AE230" s="3">
+      <c r="AD230" s="2">
+        <v>10000</v>
+      </c>
+      <c r="AE230" s="2">
         <v>25010001</v>
       </c>
       <c r="AF230" s="9">
@@ -25031,91 +25063,92 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A231" s="3">
-        <v>301111</v>
-      </c>
-      <c r="B231" s="3">
+    <row r="231" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A231" s="2">
+        <v>301107</v>
+      </c>
+      <c r="B231" s="2">
         <v>30</v>
       </c>
-      <c r="C231" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="D231" s="3"/>
-      <c r="F231" s="3"/>
-      <c r="G231" s="3">
+      <c r="C231" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D231" s="2"/>
+      <c r="E231" s="18"/>
+      <c r="F231" s="2"/>
+      <c r="G231" s="2">
         <v>12</v>
       </c>
-      <c r="H231" s="3">
-        <v>1</v>
-      </c>
-      <c r="I231" s="3" t="s">
+      <c r="H231" s="2">
+        <v>1</v>
+      </c>
+      <c r="I231" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="J231" s="3">
-        <v>0</v>
-      </c>
-      <c r="K231" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="L231" s="3">
-        <v>800011021</v>
-      </c>
-      <c r="M231" s="3">
-        <v>1</v>
-      </c>
-      <c r="N231" s="3">
+      <c r="J231" s="2">
+        <v>0</v>
+      </c>
+      <c r="K231" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="L231" s="2">
+        <v>800014011</v>
+      </c>
+      <c r="M231" s="2">
+        <v>1</v>
+      </c>
+      <c r="N231" s="2">
         <v>100</v>
       </c>
-      <c r="O231" s="3">
-        <v>0</v>
-      </c>
-      <c r="P231" s="3">
+      <c r="O231" s="2">
+        <v>0</v>
+      </c>
+      <c r="P231" s="2">
         <v>15</v>
       </c>
-      <c r="Q231" s="3">
-        <v>0</v>
-      </c>
-      <c r="R231" s="22">
+      <c r="Q231" s="2">
+        <v>0</v>
+      </c>
+      <c r="R231" s="2">
         <v>36</v>
       </c>
-      <c r="S231" s="3">
+      <c r="S231" s="2">
         <v>-5500</v>
       </c>
-      <c r="T231" s="3">
-        <v>1</v>
-      </c>
-      <c r="U231" s="3">
-        <v>0</v>
-      </c>
-      <c r="V231" s="3" t="s">
+      <c r="T231" s="2">
+        <v>1</v>
+      </c>
+      <c r="U231" s="2">
+        <v>0</v>
+      </c>
+      <c r="V231" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="W231" s="3" t="s">
+      <c r="W231" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="X231" s="3" t="s">
+      <c r="X231" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="Y231" s="16">
-        <v>211002001</v>
-      </c>
-      <c r="Z231" s="16">
-        <v>0</v>
-      </c>
-      <c r="AA231" s="3">
-        <v>1</v>
-      </c>
-      <c r="AB231" s="9" t="s">
+      <c r="Y231" s="2">
+        <v>214001011</v>
+      </c>
+      <c r="Z231" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA231" s="2">
+        <v>1</v>
+      </c>
+      <c r="AB231" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="AC231" s="3">
+      <c r="AC231" s="2">
         <v>15000</v>
       </c>
-      <c r="AD231" s="3">
-        <v>10000</v>
-      </c>
-      <c r="AE231" s="3">
+      <c r="AD231" s="2">
+        <v>10000</v>
+      </c>
+      <c r="AE231" s="2">
         <v>25010001</v>
       </c>
       <c r="AF231" s="9">
@@ -25136,13 +25169,13 @@
     </row>
     <row r="232" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A232" s="3">
-        <v>301112</v>
+        <v>301108</v>
       </c>
       <c r="B232" s="3">
         <v>30</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="D232" s="3"/>
       <c r="F232" s="3"/>
@@ -25159,10 +25192,10 @@
         <v>0</v>
       </c>
       <c r="K232" s="3" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="L232" s="3">
-        <v>800003011</v>
+        <v>800004011</v>
       </c>
       <c r="M232" s="3">
         <v>1</v>
@@ -25201,7 +25234,7 @@
         <v>125</v>
       </c>
       <c r="Y232" s="16">
-        <v>203001001</v>
+        <v>204001001</v>
       </c>
       <c r="Z232" s="16">
         <v>0</v>
@@ -25239,13 +25272,13 @@
     </row>
     <row r="233" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A233" s="3">
-        <v>301113</v>
+        <v>301109</v>
       </c>
       <c r="B233" s="3">
         <v>30</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="D233" s="3"/>
       <c r="F233" s="3"/>
@@ -25262,28 +25295,28 @@
         <v>0</v>
       </c>
       <c r="K233" s="3" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="L233" s="3">
-        <v>800003021</v>
+        <v>800004021</v>
       </c>
       <c r="M233" s="3">
         <v>1</v>
       </c>
       <c r="N233" s="3">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="O233" s="3">
         <v>0</v>
       </c>
       <c r="P233" s="3">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="Q233" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R233" s="22">
-        <v>1496</v>
+        <v>36</v>
       </c>
       <c r="S233" s="3">
         <v>-5500</v>
@@ -25292,7 +25325,7 @@
         <v>1</v>
       </c>
       <c r="U233" s="3">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="V233" s="3" t="s">
         <v>110</v>
@@ -25301,10 +25334,10 @@
         <v>111</v>
       </c>
       <c r="X233" s="3" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="Y233" s="16">
-        <v>203002011</v>
+        <v>204002001</v>
       </c>
       <c r="Z233" s="16">
         <v>0</v>
@@ -25313,7 +25346,7 @@
         <v>1</v>
       </c>
       <c r="AB233" s="9" t="s">
-        <v>140</v>
+        <v>83</v>
       </c>
       <c r="AC233" s="3">
         <v>15000</v>
@@ -25328,13 +25361,13 @@
         <v>40</v>
       </c>
       <c r="AG233" s="9">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH233" s="9">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="AI233" s="9">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AJ233" s="9">
         <v>0</v>
@@ -25342,13 +25375,13 @@
     </row>
     <row r="234" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A234" s="3">
-        <v>301114</v>
+        <v>301110</v>
       </c>
       <c r="B234" s="3">
         <v>30</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="D234" s="3"/>
       <c r="F234" s="3"/>
@@ -25365,10 +25398,10 @@
         <v>0</v>
       </c>
       <c r="K234" s="3" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="L234" s="3">
-        <v>800003031</v>
+        <v>800011011</v>
       </c>
       <c r="M234" s="3">
         <v>1</v>
@@ -25407,7 +25440,7 @@
         <v>125</v>
       </c>
       <c r="Y234" s="16">
-        <v>203003001</v>
+        <v>211001001</v>
       </c>
       <c r="Z234" s="16">
         <v>0</v>
@@ -25425,7 +25458,7 @@
         <v>10000</v>
       </c>
       <c r="AE234" s="3">
-        <v>0</v>
+        <v>25010001</v>
       </c>
       <c r="AF234" s="9">
         <v>40</v>
@@ -25443,91 +25476,92 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A235" s="2">
-        <v>301115</v>
-      </c>
-      <c r="B235" s="2">
+    <row r="235" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A235" s="3">
+        <v>301111</v>
+      </c>
+      <c r="B235" s="3">
         <v>30</v>
       </c>
-      <c r="C235" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D235" s="2"/>
-      <c r="E235" s="18"/>
-      <c r="F235" s="2"/>
-      <c r="G235" s="2">
+      <c r="C235" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D235" s="3"/>
+      <c r="F235" s="3"/>
+      <c r="G235" s="3">
         <v>12</v>
       </c>
-      <c r="H235" s="2">
-        <v>1</v>
-      </c>
-      <c r="I235" s="2" t="s">
+      <c r="H235" s="3">
+        <v>1</v>
+      </c>
+      <c r="I235" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="J235" s="2">
-        <v>0</v>
-      </c>
-      <c r="K235" s="2"/>
-      <c r="L235" s="2">
-        <v>1000011</v>
-      </c>
-      <c r="M235" s="2">
-        <v>1</v>
-      </c>
-      <c r="N235" s="2">
+      <c r="J235" s="3">
+        <v>0</v>
+      </c>
+      <c r="K235" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="L235" s="3">
+        <v>800011021</v>
+      </c>
+      <c r="M235" s="3">
+        <v>1</v>
+      </c>
+      <c r="N235" s="3">
         <v>100</v>
       </c>
-      <c r="O235" s="2">
-        <v>0</v>
-      </c>
-      <c r="P235" s="2">
+      <c r="O235" s="3">
+        <v>0</v>
+      </c>
+      <c r="P235" s="3">
         <v>15</v>
       </c>
-      <c r="Q235" s="2">
-        <v>0</v>
-      </c>
-      <c r="R235" s="2">
+      <c r="Q235" s="3">
+        <v>0</v>
+      </c>
+      <c r="R235" s="22">
         <v>36</v>
       </c>
-      <c r="S235" s="2">
+      <c r="S235" s="3">
         <v>-5500</v>
       </c>
-      <c r="T235" s="2">
-        <v>1</v>
-      </c>
-      <c r="U235" s="2">
-        <v>0</v>
-      </c>
-      <c r="V235" s="2" t="s">
+      <c r="T235" s="3">
+        <v>1</v>
+      </c>
+      <c r="U235" s="3">
+        <v>0</v>
+      </c>
+      <c r="V235" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="W235" s="2" t="s">
+      <c r="W235" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="X235" s="2" t="s">
+      <c r="X235" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="Y235" s="23">
-        <v>201002011</v>
-      </c>
-      <c r="Z235" s="23">
-        <v>0</v>
-      </c>
-      <c r="AA235" s="2">
-        <v>1</v>
-      </c>
-      <c r="AB235" s="18" t="s">
+      <c r="Y235" s="16">
+        <v>211002001</v>
+      </c>
+      <c r="Z235" s="16">
+        <v>0</v>
+      </c>
+      <c r="AA235" s="3">
+        <v>1</v>
+      </c>
+      <c r="AB235" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="AC235" s="2">
+      <c r="AC235" s="3">
         <v>15000</v>
       </c>
-      <c r="AD235" s="2">
-        <v>10000</v>
-      </c>
-      <c r="AE235" s="2">
-        <v>0</v>
+      <c r="AD235" s="3">
+        <v>10000</v>
+      </c>
+      <c r="AE235" s="3">
+        <v>25010001</v>
       </c>
       <c r="AF235" s="9">
         <v>40</v>
@@ -25545,15 +25579,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A236" s="3">
-        <v>302101</v>
+        <v>301112</v>
       </c>
       <c r="B236" s="3">
         <v>30</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="D236" s="3"/>
       <c r="F236" s="3"/>
@@ -25570,28 +25604,28 @@
         <v>0</v>
       </c>
       <c r="K236" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L236" s="3">
-        <v>800001011</v>
+        <v>800003011</v>
       </c>
       <c r="M236" s="3">
         <v>1</v>
       </c>
       <c r="N236" s="3">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="O236" s="3">
         <v>0</v>
       </c>
       <c r="P236" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q236" s="3">
         <v>0</v>
       </c>
-      <c r="R236" s="3">
-        <v>86</v>
+      <c r="R236" s="22">
+        <v>36</v>
       </c>
       <c r="S236" s="3">
         <v>-5500</v>
@@ -25609,10 +25643,10 @@
         <v>111</v>
       </c>
       <c r="X236" s="3" t="s">
-        <v>164</v>
+        <v>125</v>
       </c>
       <c r="Y236" s="16">
-        <v>201001011</v>
+        <v>203001001</v>
       </c>
       <c r="Z236" s="16">
         <v>0</v>
@@ -25621,7 +25655,7 @@
         <v>1</v>
       </c>
       <c r="AB236" s="9" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="AC236" s="3">
         <v>15000</v>
@@ -25636,27 +25670,27 @@
         <v>40</v>
       </c>
       <c r="AG236" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AH236" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AI236" s="9">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AJ236" s="9">
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A237" s="3">
-        <v>302102</v>
+        <v>301113</v>
       </c>
       <c r="B237" s="3">
         <v>30</v>
       </c>
       <c r="C237" s="3" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="D237" s="3"/>
       <c r="F237" s="3"/>
@@ -25673,28 +25707,28 @@
         <v>0</v>
       </c>
       <c r="K237" s="3" t="s">
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="L237" s="3">
-        <v>800001021</v>
+        <v>800003021</v>
       </c>
       <c r="M237" s="3">
         <v>1</v>
       </c>
       <c r="N237" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="O237" s="3">
         <v>0</v>
       </c>
       <c r="P237" s="3">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="Q237" s="3">
         <v>3</v>
       </c>
-      <c r="R237" s="3">
-        <v>292</v>
+      <c r="R237" s="22">
+        <v>1496</v>
       </c>
       <c r="S237" s="3">
         <v>-5500</v>
@@ -25703,7 +25737,7 @@
         <v>1</v>
       </c>
       <c r="U237" s="3">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="V237" s="3" t="s">
         <v>110</v>
@@ -25712,10 +25746,10 @@
         <v>111</v>
       </c>
       <c r="X237" s="3" t="s">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="Y237" s="16">
-        <v>201002011</v>
+        <v>203002011</v>
       </c>
       <c r="Z237" s="16">
         <v>0</v>
@@ -25724,7 +25758,7 @@
         <v>1</v>
       </c>
       <c r="AB237" s="9" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="AC237" s="3">
         <v>15000</v>
@@ -25739,105 +25773,104 @@
         <v>40</v>
       </c>
       <c r="AG237" s="9">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="AH237" s="9">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="AI237" s="9">
+        <v>40</v>
+      </c>
+      <c r="AJ237" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A238" s="3">
+        <v>301114</v>
+      </c>
+      <c r="B238" s="3">
+        <v>30</v>
+      </c>
+      <c r="C238" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D238" s="3"/>
+      <c r="F238" s="3"/>
+      <c r="G238" s="3">
+        <v>12</v>
+      </c>
+      <c r="H238" s="3">
+        <v>1</v>
+      </c>
+      <c r="I238" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="J238" s="3">
+        <v>0</v>
+      </c>
+      <c r="K238" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="L238" s="3">
+        <v>800003031</v>
+      </c>
+      <c r="M238" s="3">
+        <v>1</v>
+      </c>
+      <c r="N238" s="3">
+        <v>100</v>
+      </c>
+      <c r="O238" s="3">
+        <v>0</v>
+      </c>
+      <c r="P238" s="3">
         <v>15</v>
       </c>
-      <c r="AJ237" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="238" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A238" s="2">
-        <v>302103</v>
-      </c>
-      <c r="B238" s="2">
-        <v>30</v>
-      </c>
-      <c r="C238" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="D238" s="2"/>
-      <c r="E238" s="18"/>
-      <c r="F238" s="2"/>
-      <c r="G238" s="2">
-        <v>12</v>
-      </c>
-      <c r="H238" s="2">
-        <v>1</v>
-      </c>
-      <c r="I238" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="J238" s="2">
-        <v>0</v>
-      </c>
-      <c r="K238" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="L238" s="2">
-        <v>800001021</v>
-      </c>
-      <c r="M238" s="2">
-        <v>1</v>
-      </c>
-      <c r="N238" s="2">
-        <v>70</v>
-      </c>
-      <c r="O238" s="2">
-        <v>0</v>
-      </c>
-      <c r="P238" s="2">
-        <v>15</v>
-      </c>
-      <c r="Q238" s="2">
-        <v>1</v>
-      </c>
-      <c r="R238" s="2">
-        <v>300</v>
-      </c>
-      <c r="S238" s="2">
+      <c r="Q238" s="3">
+        <v>0</v>
+      </c>
+      <c r="R238" s="22">
+        <v>36</v>
+      </c>
+      <c r="S238" s="3">
         <v>-5500</v>
       </c>
-      <c r="T238" s="2">
-        <v>1</v>
-      </c>
-      <c r="U238" s="2">
-        <v>250</v>
-      </c>
-      <c r="V238" s="2" t="s">
+      <c r="T238" s="3">
+        <v>1</v>
+      </c>
+      <c r="U238" s="3">
+        <v>0</v>
+      </c>
+      <c r="V238" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="W238" s="2" t="s">
+      <c r="W238" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="X238" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="Y238" s="23">
-        <v>201002011</v>
-      </c>
-      <c r="Z238" s="23">
-        <v>0</v>
-      </c>
-      <c r="AA238" s="2">
-        <v>1</v>
-      </c>
-      <c r="AB238" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="AC238" s="2">
+      <c r="X238" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y238" s="16">
+        <v>203003001</v>
+      </c>
+      <c r="Z238" s="16">
+        <v>0</v>
+      </c>
+      <c r="AA238" s="3">
+        <v>1</v>
+      </c>
+      <c r="AB238" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC238" s="3">
         <v>15000</v>
       </c>
-      <c r="AD238" s="2">
-        <v>10000</v>
-      </c>
-      <c r="AE238" s="2">
-        <v>25010001</v>
+      <c r="AD238" s="3">
+        <v>10000</v>
+      </c>
+      <c r="AE238" s="3">
+        <v>0</v>
       </c>
       <c r="AF238" s="9">
         <v>40</v>
@@ -25856,117 +25889,116 @@
       </c>
     </row>
     <row r="239" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A239" s="3">
-        <v>302104</v>
-      </c>
-      <c r="B239" s="3">
+      <c r="A239" s="2">
+        <v>301115</v>
+      </c>
+      <c r="B239" s="2">
         <v>30</v>
       </c>
-      <c r="C239" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="D239" s="3"/>
-      <c r="F239" s="3"/>
-      <c r="G239" s="3">
+      <c r="C239" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D239" s="2"/>
+      <c r="E239" s="18"/>
+      <c r="F239" s="2"/>
+      <c r="G239" s="2">
         <v>12</v>
       </c>
-      <c r="H239" s="3">
-        <v>1</v>
-      </c>
-      <c r="I239" s="3" t="s">
+      <c r="H239" s="2">
+        <v>1</v>
+      </c>
+      <c r="I239" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="J239" s="3">
-        <v>0</v>
-      </c>
-      <c r="K239" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="L239" s="3">
-        <v>800001041</v>
-      </c>
-      <c r="M239" s="3">
-        <v>1</v>
-      </c>
-      <c r="N239" s="3">
-        <v>70</v>
-      </c>
-      <c r="O239" s="3">
-        <v>0</v>
-      </c>
-      <c r="P239" s="3">
-        <v>24</v>
-      </c>
-      <c r="Q239" s="3">
-        <v>0</v>
-      </c>
-      <c r="R239" s="3">
-        <v>69</v>
-      </c>
-      <c r="S239" s="3">
+      <c r="J239" s="2">
+        <v>0</v>
+      </c>
+      <c r="K239" s="2"/>
+      <c r="L239" s="2">
+        <v>1000011</v>
+      </c>
+      <c r="M239" s="2">
+        <v>1</v>
+      </c>
+      <c r="N239" s="2">
+        <v>100</v>
+      </c>
+      <c r="O239" s="2">
+        <v>0</v>
+      </c>
+      <c r="P239" s="2">
+        <v>15</v>
+      </c>
+      <c r="Q239" s="2">
+        <v>0</v>
+      </c>
+      <c r="R239" s="2">
+        <v>36</v>
+      </c>
+      <c r="S239" s="2">
         <v>-5500</v>
       </c>
-      <c r="T239" s="3">
-        <v>1</v>
-      </c>
-      <c r="U239" s="3">
-        <v>0</v>
-      </c>
-      <c r="V239" s="3" t="s">
+      <c r="T239" s="2">
+        <v>1</v>
+      </c>
+      <c r="U239" s="2">
+        <v>0</v>
+      </c>
+      <c r="V239" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="W239" s="3" t="s">
+      <c r="W239" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="X239" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="Y239" s="16">
-        <v>201004011</v>
-      </c>
-      <c r="Z239" s="16">
-        <v>0</v>
-      </c>
-      <c r="AA239" s="3">
-        <v>1</v>
-      </c>
-      <c r="AB239" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="AC239" s="3">
+      <c r="X239" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y239" s="23">
+        <v>201002011</v>
+      </c>
+      <c r="Z239" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA239" s="2">
+        <v>1</v>
+      </c>
+      <c r="AB239" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC239" s="2">
         <v>15000</v>
       </c>
-      <c r="AD239" s="3">
-        <v>10000</v>
-      </c>
-      <c r="AE239" s="3">
-        <v>25010001</v>
+      <c r="AD239" s="2">
+        <v>10000</v>
+      </c>
+      <c r="AE239" s="2">
+        <v>0</v>
       </c>
       <c r="AF239" s="9">
         <v>40</v>
       </c>
       <c r="AG239" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AH239" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AI239" s="9">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AJ239" s="9">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A240" s="3">
-        <v>302105</v>
+        <v>302101</v>
       </c>
       <c r="B240" s="3">
         <v>30</v>
       </c>
       <c r="C240" s="3" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="D240" s="3"/>
       <c r="F240" s="3"/>
@@ -25983,28 +26015,28 @@
         <v>0</v>
       </c>
       <c r="K240" s="3" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="L240" s="3">
-        <v>800014011</v>
+        <v>800001011</v>
       </c>
       <c r="M240" s="3">
         <v>1</v>
       </c>
       <c r="N240" s="3">
-        <v>125</v>
+        <v>70</v>
       </c>
       <c r="O240" s="3">
         <v>0</v>
       </c>
       <c r="P240" s="3">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="Q240" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R240" s="3">
-        <v>131</v>
+        <v>86</v>
       </c>
       <c r="S240" s="3">
         <v>-5500</v>
@@ -26025,7 +26057,7 @@
         <v>164</v>
       </c>
       <c r="Y240" s="16">
-        <v>214001011</v>
+        <v>201001011</v>
       </c>
       <c r="Z240" s="16">
         <v>0</v>
@@ -26034,7 +26066,7 @@
         <v>1</v>
       </c>
       <c r="AB240" s="9" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="AC240" s="3">
         <v>15000</v>
@@ -26055,111 +26087,110 @@
         <v>10000</v>
       </c>
       <c r="AI240" s="9">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AJ240" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="241" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A241" s="2">
-        <v>302106</v>
-      </c>
-      <c r="B241" s="2">
+      <c r="A241" s="3">
+        <v>302102</v>
+      </c>
+      <c r="B241" s="3">
         <v>30</v>
       </c>
-      <c r="C241" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="D241" s="2"/>
-      <c r="E241" s="18"/>
-      <c r="F241" s="2"/>
-      <c r="G241" s="2">
+      <c r="C241" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D241" s="3"/>
+      <c r="F241" s="3"/>
+      <c r="G241" s="3">
         <v>12</v>
       </c>
-      <c r="H241" s="2">
-        <v>1</v>
-      </c>
-      <c r="I241" s="2" t="s">
+      <c r="H241" s="3">
+        <v>1</v>
+      </c>
+      <c r="I241" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="J241" s="2">
-        <v>0</v>
-      </c>
-      <c r="K241" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="L241" s="2">
-        <v>1000010</v>
-      </c>
-      <c r="M241" s="2">
-        <v>1</v>
-      </c>
-      <c r="N241" s="2">
-        <v>100</v>
-      </c>
-      <c r="O241" s="2">
-        <v>0</v>
-      </c>
-      <c r="P241" s="2">
-        <v>15</v>
-      </c>
-      <c r="Q241" s="2">
-        <v>0</v>
-      </c>
-      <c r="R241" s="2">
-        <v>36</v>
-      </c>
-      <c r="S241" s="2">
+      <c r="J241" s="3">
+        <v>0</v>
+      </c>
+      <c r="K241" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="L241" s="3">
+        <v>800001021</v>
+      </c>
+      <c r="M241" s="3">
+        <v>1</v>
+      </c>
+      <c r="N241" s="3">
+        <v>200</v>
+      </c>
+      <c r="O241" s="3">
+        <v>0</v>
+      </c>
+      <c r="P241" s="3">
+        <v>32</v>
+      </c>
+      <c r="Q241" s="3">
+        <v>3</v>
+      </c>
+      <c r="R241" s="3">
+        <v>292</v>
+      </c>
+      <c r="S241" s="3">
         <v>-5500</v>
       </c>
-      <c r="T241" s="2">
-        <v>1</v>
-      </c>
-      <c r="U241" s="2">
-        <v>0</v>
-      </c>
-      <c r="V241" s="2" t="s">
+      <c r="T241" s="3">
+        <v>1</v>
+      </c>
+      <c r="U241" s="3">
+        <v>0</v>
+      </c>
+      <c r="V241" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="W241" s="2" t="s">
+      <c r="W241" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="X241" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="Y241" s="23">
+      <c r="X241" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="Y241" s="16">
         <v>201002011</v>
       </c>
-      <c r="Z241" s="23">
-        <v>0</v>
-      </c>
-      <c r="AA241" s="2">
-        <v>1</v>
-      </c>
-      <c r="AB241" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="AC241" s="2">
+      <c r="Z241" s="16">
+        <v>0</v>
+      </c>
+      <c r="AA241" s="3">
+        <v>1</v>
+      </c>
+      <c r="AB241" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="AC241" s="3">
         <v>15000</v>
       </c>
-      <c r="AD241" s="2">
-        <v>10000</v>
-      </c>
-      <c r="AE241" s="2">
+      <c r="AD241" s="3">
+        <v>10000</v>
+      </c>
+      <c r="AE241" s="3">
         <v>25010001</v>
       </c>
       <c r="AF241" s="9">
         <v>40</v>
       </c>
       <c r="AG241" s="9">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="AH241" s="9">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI241" s="9">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AJ241" s="9">
         <v>0</v>
@@ -26167,13 +26198,13 @@
     </row>
     <row r="242" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A242" s="2">
-        <v>302107</v>
+        <v>302103</v>
       </c>
       <c r="B242" s="2">
         <v>30</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D242" s="2"/>
       <c r="E242" s="18"/>
@@ -26191,16 +26222,16 @@
         <v>0</v>
       </c>
       <c r="K242" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="L242" s="2">
-        <v>1000006</v>
+        <v>800001021</v>
       </c>
       <c r="M242" s="2">
         <v>1</v>
       </c>
       <c r="N242" s="2">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="O242" s="2">
         <v>0</v>
@@ -26209,10 +26240,10 @@
         <v>15</v>
       </c>
       <c r="Q242" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R242" s="2">
-        <v>36</v>
+        <v>300</v>
       </c>
       <c r="S242" s="2">
         <v>-5500</v>
@@ -26221,7 +26252,7 @@
         <v>1</v>
       </c>
       <c r="U242" s="2">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="V242" s="2" t="s">
         <v>110</v>
@@ -26230,7 +26261,7 @@
         <v>111</v>
       </c>
       <c r="X242" s="2" t="s">
-        <v>125</v>
+        <v>164</v>
       </c>
       <c r="Y242" s="23">
         <v>201002011</v>
@@ -26242,7 +26273,7 @@
         <v>1</v>
       </c>
       <c r="AB242" s="18" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="AC242" s="2">
         <v>15000</v>
@@ -26270,208 +26301,206 @@
       </c>
     </row>
     <row r="243" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A243" s="2">
-        <v>302108</v>
-      </c>
-      <c r="B243" s="2">
+      <c r="A243" s="3">
+        <v>302104</v>
+      </c>
+      <c r="B243" s="3">
         <v>30</v>
       </c>
-      <c r="C243" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D243" s="2"/>
-      <c r="E243" s="18"/>
-      <c r="F243" s="2"/>
-      <c r="G243" s="2">
+      <c r="C243" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D243" s="3"/>
+      <c r="F243" s="3"/>
+      <c r="G243" s="3">
         <v>12</v>
       </c>
-      <c r="H243" s="2">
-        <v>1</v>
-      </c>
-      <c r="I243" s="2" t="s">
+      <c r="H243" s="3">
+        <v>1</v>
+      </c>
+      <c r="I243" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="J243" s="2">
-        <v>0</v>
-      </c>
-      <c r="K243" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="L243" s="2">
-        <v>1000006</v>
-      </c>
-      <c r="M243" s="2">
-        <v>1</v>
-      </c>
-      <c r="N243" s="2">
-        <v>100</v>
-      </c>
-      <c r="O243" s="2">
-        <v>0</v>
-      </c>
-      <c r="P243" s="2">
-        <v>15</v>
-      </c>
-      <c r="Q243" s="2">
-        <v>0</v>
-      </c>
-      <c r="R243" s="2">
-        <v>36</v>
-      </c>
-      <c r="S243" s="2">
+      <c r="J243" s="3">
+        <v>0</v>
+      </c>
+      <c r="K243" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="L243" s="3">
+        <v>800001041</v>
+      </c>
+      <c r="M243" s="3">
+        <v>1</v>
+      </c>
+      <c r="N243" s="3">
+        <v>70</v>
+      </c>
+      <c r="O243" s="3">
+        <v>0</v>
+      </c>
+      <c r="P243" s="3">
+        <v>24</v>
+      </c>
+      <c r="Q243" s="3">
+        <v>0</v>
+      </c>
+      <c r="R243" s="3">
+        <v>69</v>
+      </c>
+      <c r="S243" s="3">
         <v>-5500</v>
       </c>
-      <c r="T243" s="2">
-        <v>1</v>
-      </c>
-      <c r="U243" s="2">
-        <v>0</v>
-      </c>
-      <c r="V243" s="2" t="s">
+      <c r="T243" s="3">
+        <v>1</v>
+      </c>
+      <c r="U243" s="3">
+        <v>0</v>
+      </c>
+      <c r="V243" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="W243" s="2" t="s">
+      <c r="W243" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="X243" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="Y243" s="23">
-        <v>201002011</v>
-      </c>
-      <c r="Z243" s="23">
-        <v>0</v>
-      </c>
-      <c r="AA243" s="2">
-        <v>1</v>
-      </c>
-      <c r="AB243" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="AC243" s="2">
+      <c r="X243" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="Y243" s="16">
+        <v>201004011</v>
+      </c>
+      <c r="Z243" s="16">
+        <v>0</v>
+      </c>
+      <c r="AA243" s="3">
+        <v>1</v>
+      </c>
+      <c r="AB243" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC243" s="3">
         <v>15000</v>
       </c>
-      <c r="AD243" s="2">
-        <v>10000</v>
-      </c>
-      <c r="AE243" s="2">
+      <c r="AD243" s="3">
+        <v>10000</v>
+      </c>
+      <c r="AE243" s="3">
         <v>25010001</v>
       </c>
       <c r="AF243" s="9">
         <v>40</v>
       </c>
       <c r="AG243" s="9">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH243" s="9">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI243" s="9">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AJ243" s="9">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="244" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A244" s="2">
-        <v>302109</v>
-      </c>
-      <c r="B244" s="2">
+      <c r="A244" s="3">
+        <v>302105</v>
+      </c>
+      <c r="B244" s="3">
         <v>30</v>
       </c>
-      <c r="C244" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="D244" s="2"/>
-      <c r="E244" s="18"/>
-      <c r="F244" s="2"/>
-      <c r="G244" s="2">
+      <c r="C244" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D244" s="3"/>
+      <c r="F244" s="3"/>
+      <c r="G244" s="3">
         <v>12</v>
       </c>
-      <c r="H244" s="2">
-        <v>1</v>
-      </c>
-      <c r="I244" s="2" t="s">
+      <c r="H244" s="3">
+        <v>1</v>
+      </c>
+      <c r="I244" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="J244" s="2">
-        <v>0</v>
-      </c>
-      <c r="K244" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="L244" s="2">
-        <v>1000006</v>
-      </c>
-      <c r="M244" s="2">
-        <v>1</v>
-      </c>
-      <c r="N244" s="2">
-        <v>100</v>
-      </c>
-      <c r="O244" s="2">
-        <v>0</v>
-      </c>
-      <c r="P244" s="2">
-        <v>15</v>
-      </c>
-      <c r="Q244" s="2">
-        <v>0</v>
-      </c>
-      <c r="R244" s="2">
-        <v>36</v>
-      </c>
-      <c r="S244" s="2">
+      <c r="J244" s="3">
+        <v>0</v>
+      </c>
+      <c r="K244" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="L244" s="3">
+        <v>800014011</v>
+      </c>
+      <c r="M244" s="3">
+        <v>1</v>
+      </c>
+      <c r="N244" s="3">
+        <v>125</v>
+      </c>
+      <c r="O244" s="3">
+        <v>0</v>
+      </c>
+      <c r="P244" s="3">
+        <v>21</v>
+      </c>
+      <c r="Q244" s="3">
+        <v>2</v>
+      </c>
+      <c r="R244" s="3">
+        <v>131</v>
+      </c>
+      <c r="S244" s="3">
         <v>-5500</v>
       </c>
-      <c r="T244" s="2">
-        <v>1</v>
-      </c>
-      <c r="U244" s="2">
-        <v>0</v>
-      </c>
-      <c r="V244" s="2" t="s">
+      <c r="T244" s="3">
+        <v>1</v>
+      </c>
+      <c r="U244" s="3">
+        <v>0</v>
+      </c>
+      <c r="V244" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="W244" s="2" t="s">
+      <c r="W244" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="X244" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="Y244" s="23">
-        <v>201002011</v>
-      </c>
-      <c r="Z244" s="23">
-        <v>0</v>
-      </c>
-      <c r="AA244" s="2">
-        <v>1</v>
-      </c>
-      <c r="AB244" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="AC244" s="2">
+      <c r="X244" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="Y244" s="16">
+        <v>214001011</v>
+      </c>
+      <c r="Z244" s="16">
+        <v>0</v>
+      </c>
+      <c r="AA244" s="3">
+        <v>1</v>
+      </c>
+      <c r="AB244" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="AC244" s="3">
         <v>15000</v>
       </c>
-      <c r="AD244" s="2">
-        <v>10000</v>
-      </c>
-      <c r="AE244" s="2">
+      <c r="AD244" s="3">
+        <v>10000</v>
+      </c>
+      <c r="AE244" s="3">
         <v>25010001</v>
       </c>
       <c r="AF244" s="9">
         <v>40</v>
       </c>
       <c r="AG244" s="9">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH244" s="9">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI244" s="9">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AJ244" s="9">
         <v>0</v>
@@ -26479,13 +26508,13 @@
     </row>
     <row r="245" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A245" s="2">
-        <v>302110</v>
+        <v>302106</v>
       </c>
       <c r="B245" s="2">
         <v>30</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="D245" s="2"/>
       <c r="E245" s="18"/>
@@ -26503,10 +26532,10 @@
         <v>0</v>
       </c>
       <c r="K245" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="L245" s="2">
-        <v>1000103</v>
+        <v>1000010</v>
       </c>
       <c r="M245" s="2">
         <v>1</v>
@@ -26583,13 +26612,13 @@
     </row>
     <row r="246" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A246" s="2">
-        <v>302111</v>
+        <v>302107</v>
       </c>
       <c r="B246" s="2">
         <v>30</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="D246" s="2"/>
       <c r="E246" s="18"/>
@@ -26607,10 +26636,10 @@
         <v>0</v>
       </c>
       <c r="K246" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L246" s="2">
-        <v>1000103</v>
+        <v>1000006</v>
       </c>
       <c r="M246" s="2">
         <v>1</v>
@@ -26687,13 +26716,13 @@
     </row>
     <row r="247" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A247" s="2">
-        <v>302112</v>
+        <v>302108</v>
       </c>
       <c r="B247" s="2">
         <v>30</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="D247" s="2"/>
       <c r="E247" s="18"/>
@@ -26711,10 +26740,10 @@
         <v>0</v>
       </c>
       <c r="K247" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L247" s="2">
-        <v>1000103</v>
+        <v>1000006</v>
       </c>
       <c r="M247" s="2">
         <v>1</v>
@@ -26789,104 +26818,105 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A248" s="3">
-        <v>302113</v>
-      </c>
-      <c r="B248" s="3">
+    <row r="248" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A248" s="2">
+        <v>302109</v>
+      </c>
+      <c r="B248" s="2">
         <v>30</v>
       </c>
-      <c r="C248" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="D248" s="3"/>
-      <c r="F248" s="3"/>
-      <c r="G248" s="3">
+      <c r="C248" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D248" s="2"/>
+      <c r="E248" s="18"/>
+      <c r="F248" s="2"/>
+      <c r="G248" s="2">
         <v>12</v>
       </c>
-      <c r="H248" s="3">
-        <v>1</v>
-      </c>
-      <c r="I248" s="3" t="s">
+      <c r="H248" s="2">
+        <v>1</v>
+      </c>
+      <c r="I248" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="J248" s="3">
-        <v>0</v>
-      </c>
-      <c r="K248" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="L248" s="3">
-        <v>800003021</v>
-      </c>
-      <c r="M248" s="3">
-        <v>1</v>
-      </c>
-      <c r="N248" s="3">
-        <v>500</v>
-      </c>
-      <c r="O248" s="3">
-        <v>0</v>
-      </c>
-      <c r="P248" s="3">
-        <v>42</v>
-      </c>
-      <c r="Q248" s="3">
-        <v>3</v>
-      </c>
-      <c r="R248" s="22">
-        <v>1496</v>
-      </c>
-      <c r="S248" s="3">
+      <c r="J248" s="2">
+        <v>0</v>
+      </c>
+      <c r="K248" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="L248" s="2">
+        <v>1000006</v>
+      </c>
+      <c r="M248" s="2">
+        <v>1</v>
+      </c>
+      <c r="N248" s="2">
+        <v>100</v>
+      </c>
+      <c r="O248" s="2">
+        <v>0</v>
+      </c>
+      <c r="P248" s="2">
+        <v>15</v>
+      </c>
+      <c r="Q248" s="2">
+        <v>0</v>
+      </c>
+      <c r="R248" s="2">
+        <v>36</v>
+      </c>
+      <c r="S248" s="2">
         <v>-5500</v>
       </c>
-      <c r="T248" s="3">
-        <v>1</v>
-      </c>
-      <c r="U248" s="3">
-        <v>30000</v>
-      </c>
-      <c r="V248" s="3" t="s">
+      <c r="T248" s="2">
+        <v>1</v>
+      </c>
+      <c r="U248" s="2">
+        <v>0</v>
+      </c>
+      <c r="V248" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="W248" s="3" t="s">
+      <c r="W248" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="X248" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="Y248" s="16">
-        <v>203002011</v>
-      </c>
-      <c r="Z248" s="16">
-        <v>0</v>
-      </c>
-      <c r="AA248" s="3">
-        <v>1</v>
-      </c>
-      <c r="AB248" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="AC248" s="3">
+      <c r="X248" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y248" s="23">
+        <v>201002011</v>
+      </c>
+      <c r="Z248" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA248" s="2">
+        <v>1</v>
+      </c>
+      <c r="AB248" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC248" s="2">
         <v>15000</v>
       </c>
-      <c r="AD248" s="3">
-        <v>10000</v>
-      </c>
-      <c r="AE248" s="3">
+      <c r="AD248" s="2">
+        <v>10000</v>
+      </c>
+      <c r="AE248" s="2">
         <v>25010001</v>
       </c>
       <c r="AF248" s="9">
         <v>40</v>
       </c>
       <c r="AG248" s="9">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH248" s="9">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="AI248" s="9">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AJ248" s="9">
         <v>0</v>
@@ -26894,13 +26924,13 @@
     </row>
     <row r="249" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A249" s="2">
-        <v>302114</v>
+        <v>302110</v>
       </c>
       <c r="B249" s="2">
         <v>30</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="D249" s="2"/>
       <c r="E249" s="18"/>
@@ -26918,10 +26948,10 @@
         <v>0</v>
       </c>
       <c r="K249" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="L249" s="2">
-        <v>1000011</v>
+        <v>1000103</v>
       </c>
       <c r="M249" s="2">
         <v>1</v>
@@ -26978,7 +27008,7 @@
         <v>10000</v>
       </c>
       <c r="AE249" s="2">
-        <v>0</v>
+        <v>25010001</v>
       </c>
       <c r="AF249" s="9">
         <v>40</v>
@@ -26998,13 +27028,13 @@
     </row>
     <row r="250" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A250" s="2">
-        <v>302115</v>
+        <v>302111</v>
       </c>
       <c r="B250" s="2">
         <v>30</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D250" s="2"/>
       <c r="E250" s="18"/>
@@ -27022,10 +27052,10 @@
         <v>0</v>
       </c>
       <c r="K250" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="L250" s="2">
-        <v>1000011</v>
+        <v>1000103</v>
       </c>
       <c r="M250" s="2">
         <v>1</v>
@@ -27082,7 +27112,7 @@
         <v>10000</v>
       </c>
       <c r="AE250" s="2">
-        <v>0</v>
+        <v>25010001</v>
       </c>
       <c r="AF250" s="9">
         <v>40</v>
@@ -27101,117 +27131,118 @@
       </c>
     </row>
     <row r="251" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A251" s="3">
-        <v>303101</v>
-      </c>
-      <c r="B251" s="3">
+      <c r="A251" s="2">
+        <v>302112</v>
+      </c>
+      <c r="B251" s="2">
         <v>30</v>
       </c>
-      <c r="C251" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="D251" s="3"/>
-      <c r="F251" s="3"/>
-      <c r="G251" s="3">
+      <c r="C251" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D251" s="2"/>
+      <c r="E251" s="18"/>
+      <c r="F251" s="2"/>
+      <c r="G251" s="2">
         <v>12</v>
       </c>
-      <c r="H251" s="3">
-        <v>1</v>
-      </c>
-      <c r="I251" s="3" t="s">
+      <c r="H251" s="2">
+        <v>1</v>
+      </c>
+      <c r="I251" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="J251" s="3">
-        <v>0</v>
-      </c>
-      <c r="K251" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="L251" s="3">
-        <v>800001011</v>
-      </c>
-      <c r="M251" s="3">
-        <v>1</v>
-      </c>
-      <c r="N251" s="3">
-        <v>70</v>
-      </c>
-      <c r="O251" s="3">
-        <v>0</v>
-      </c>
-      <c r="P251" s="3">
-        <v>18</v>
-      </c>
-      <c r="Q251" s="3">
-        <v>0</v>
-      </c>
-      <c r="R251" s="3">
-        <v>211</v>
-      </c>
-      <c r="S251" s="3">
+      <c r="J251" s="2">
+        <v>0</v>
+      </c>
+      <c r="K251" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="L251" s="2">
+        <v>1000103</v>
+      </c>
+      <c r="M251" s="2">
+        <v>1</v>
+      </c>
+      <c r="N251" s="2">
+        <v>100</v>
+      </c>
+      <c r="O251" s="2">
+        <v>0</v>
+      </c>
+      <c r="P251" s="2">
+        <v>15</v>
+      </c>
+      <c r="Q251" s="2">
+        <v>0</v>
+      </c>
+      <c r="R251" s="2">
+        <v>36</v>
+      </c>
+      <c r="S251" s="2">
         <v>-5500</v>
       </c>
-      <c r="T251" s="3">
-        <v>1</v>
-      </c>
-      <c r="U251" s="3">
-        <v>0</v>
-      </c>
-      <c r="V251" s="3" t="s">
+      <c r="T251" s="2">
+        <v>1</v>
+      </c>
+      <c r="U251" s="2">
+        <v>0</v>
+      </c>
+      <c r="V251" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="W251" s="3" t="s">
+      <c r="W251" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="X251" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="Y251" s="16">
-        <v>201001011</v>
-      </c>
-      <c r="Z251" s="16">
-        <v>0</v>
-      </c>
-      <c r="AA251" s="3">
-        <v>1</v>
-      </c>
-      <c r="AB251" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="AC251" s="3">
+      <c r="X251" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y251" s="23">
+        <v>201002011</v>
+      </c>
+      <c r="Z251" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA251" s="2">
+        <v>1</v>
+      </c>
+      <c r="AB251" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC251" s="2">
         <v>15000</v>
       </c>
-      <c r="AD251" s="3">
-        <v>10000</v>
-      </c>
-      <c r="AE251" s="3">
+      <c r="AD251" s="2">
+        <v>10000</v>
+      </c>
+      <c r="AE251" s="2">
         <v>25010001</v>
       </c>
       <c r="AF251" s="9">
         <v>40</v>
       </c>
       <c r="AG251" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AH251" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AI251" s="9">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AJ251" s="9">
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A252" s="3">
-        <v>303102</v>
+        <v>302113</v>
       </c>
       <c r="B252" s="3">
         <v>30</v>
       </c>
       <c r="C252" s="3" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="D252" s="3"/>
       <c r="F252" s="3"/>
@@ -27228,28 +27259,28 @@
         <v>0</v>
       </c>
       <c r="K252" s="3" t="s">
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="L252" s="3">
-        <v>800001021</v>
+        <v>800003021</v>
       </c>
       <c r="M252" s="3">
         <v>1</v>
       </c>
       <c r="N252" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="O252" s="3">
         <v>0</v>
       </c>
       <c r="P252" s="3">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="Q252" s="3">
-        <v>4</v>
-      </c>
-      <c r="R252" s="3">
-        <v>570</v>
+        <v>3</v>
+      </c>
+      <c r="R252" s="22">
+        <v>1496</v>
       </c>
       <c r="S252" s="3">
         <v>-5500</v>
@@ -27258,7 +27289,7 @@
         <v>1</v>
       </c>
       <c r="U252" s="3">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="V252" s="3" t="s">
         <v>110</v>
@@ -27267,10 +27298,10 @@
         <v>111</v>
       </c>
       <c r="X252" s="3" t="s">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="Y252" s="16">
-        <v>201002011</v>
+        <v>203002011</v>
       </c>
       <c r="Z252" s="16">
         <v>0</v>
@@ -27279,7 +27310,7 @@
         <v>1</v>
       </c>
       <c r="AB252" s="9" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="AC252" s="3">
         <v>15000</v>
@@ -27294,13 +27325,13 @@
         <v>40</v>
       </c>
       <c r="AG252" s="9">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="AH252" s="9">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="AI252" s="9">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="AJ252" s="9">
         <v>0</v>
@@ -27308,13 +27339,13 @@
     </row>
     <row r="253" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A253" s="2">
-        <v>303103</v>
+        <v>302114</v>
       </c>
       <c r="B253" s="2">
         <v>30</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>117</v>
+        <v>141</v>
       </c>
       <c r="D253" s="2"/>
       <c r="E253" s="18"/>
@@ -27332,16 +27363,16 @@
         <v>0</v>
       </c>
       <c r="K253" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="L253" s="2">
-        <v>800001021</v>
+        <v>1000011</v>
       </c>
       <c r="M253" s="2">
         <v>1</v>
       </c>
       <c r="N253" s="2">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="O253" s="2">
         <v>0</v>
@@ -27350,10 +27381,10 @@
         <v>15</v>
       </c>
       <c r="Q253" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R253" s="2">
-        <v>300</v>
+        <v>36</v>
       </c>
       <c r="S253" s="2">
         <v>-5500</v>
@@ -27362,7 +27393,7 @@
         <v>1</v>
       </c>
       <c r="U253" s="2">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="V253" s="2" t="s">
         <v>110</v>
@@ -27371,7 +27402,7 @@
         <v>111</v>
       </c>
       <c r="X253" s="2" t="s">
-        <v>165</v>
+        <v>125</v>
       </c>
       <c r="Y253" s="23">
         <v>201002011</v>
@@ -27383,7 +27414,7 @@
         <v>1</v>
       </c>
       <c r="AB253" s="18" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="AC253" s="2">
         <v>15000</v>
@@ -27392,7 +27423,7 @@
         <v>10000</v>
       </c>
       <c r="AE253" s="2">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AF253" s="9">
         <v>40</v>
@@ -27411,117 +27442,118 @@
       </c>
     </row>
     <row r="254" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A254" s="3">
-        <v>303104</v>
-      </c>
-      <c r="B254" s="3">
+      <c r="A254" s="2">
+        <v>302115</v>
+      </c>
+      <c r="B254" s="2">
         <v>30</v>
       </c>
-      <c r="C254" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="D254" s="3"/>
-      <c r="F254" s="3"/>
-      <c r="G254" s="3">
+      <c r="C254" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D254" s="2"/>
+      <c r="E254" s="18"/>
+      <c r="F254" s="2"/>
+      <c r="G254" s="2">
         <v>12</v>
       </c>
-      <c r="H254" s="3">
-        <v>1</v>
-      </c>
-      <c r="I254" s="3" t="s">
+      <c r="H254" s="2">
+        <v>1</v>
+      </c>
+      <c r="I254" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="J254" s="3">
-        <v>0</v>
-      </c>
-      <c r="K254" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="L254" s="3">
-        <v>800001041</v>
-      </c>
-      <c r="M254" s="3">
-        <v>1</v>
-      </c>
-      <c r="N254" s="3">
-        <v>70</v>
-      </c>
-      <c r="O254" s="3">
-        <v>0</v>
-      </c>
-      <c r="P254" s="3">
-        <v>27</v>
-      </c>
-      <c r="Q254" s="3">
-        <v>0</v>
-      </c>
-      <c r="R254" s="3">
-        <v>169</v>
-      </c>
-      <c r="S254" s="3">
+      <c r="J254" s="2">
+        <v>0</v>
+      </c>
+      <c r="K254" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="L254" s="2">
+        <v>1000011</v>
+      </c>
+      <c r="M254" s="2">
+        <v>1</v>
+      </c>
+      <c r="N254" s="2">
+        <v>100</v>
+      </c>
+      <c r="O254" s="2">
+        <v>0</v>
+      </c>
+      <c r="P254" s="2">
+        <v>15</v>
+      </c>
+      <c r="Q254" s="2">
+        <v>0</v>
+      </c>
+      <c r="R254" s="2">
+        <v>36</v>
+      </c>
+      <c r="S254" s="2">
         <v>-5500</v>
       </c>
-      <c r="T254" s="3">
-        <v>1</v>
-      </c>
-      <c r="U254" s="3">
-        <v>0</v>
-      </c>
-      <c r="V254" s="3" t="s">
+      <c r="T254" s="2">
+        <v>1</v>
+      </c>
+      <c r="U254" s="2">
+        <v>0</v>
+      </c>
+      <c r="V254" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="W254" s="3" t="s">
+      <c r="W254" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="X254" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="Y254" s="16">
-        <v>201004011</v>
-      </c>
-      <c r="Z254" s="16">
-        <v>0</v>
-      </c>
-      <c r="AA254" s="3">
-        <v>1</v>
-      </c>
-      <c r="AB254" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="AC254" s="3">
+      <c r="X254" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y254" s="23">
+        <v>201002011</v>
+      </c>
+      <c r="Z254" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA254" s="2">
+        <v>1</v>
+      </c>
+      <c r="AB254" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC254" s="2">
         <v>15000</v>
       </c>
-      <c r="AD254" s="3">
-        <v>10000</v>
-      </c>
-      <c r="AE254" s="3">
-        <v>25010001</v>
+      <c r="AD254" s="2">
+        <v>10000</v>
+      </c>
+      <c r="AE254" s="2">
+        <v>0</v>
       </c>
       <c r="AF254" s="9">
         <v>40</v>
       </c>
       <c r="AG254" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AH254" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AI254" s="9">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AJ254" s="9">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="255" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A255" s="3">
-        <v>303105</v>
+        <v>303101</v>
       </c>
       <c r="B255" s="3">
         <v>30</v>
       </c>
       <c r="C255" s="3" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="D255" s="3"/>
       <c r="F255" s="3"/>
@@ -27538,28 +27570,28 @@
         <v>0</v>
       </c>
       <c r="K255" s="3" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="L255" s="3">
-        <v>800014011</v>
+        <v>800001011</v>
       </c>
       <c r="M255" s="3">
         <v>1</v>
       </c>
       <c r="N255" s="3">
-        <v>125</v>
+        <v>70</v>
       </c>
       <c r="O255" s="3">
         <v>0</v>
       </c>
       <c r="P255" s="3">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="Q255" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R255" s="3">
-        <v>301</v>
+        <v>211</v>
       </c>
       <c r="S255" s="3">
         <v>-5500</v>
@@ -27580,7 +27612,7 @@
         <v>165</v>
       </c>
       <c r="Y255" s="16">
-        <v>214001011</v>
+        <v>201001011</v>
       </c>
       <c r="Z255" s="16">
         <v>0</v>
@@ -27589,7 +27621,7 @@
         <v>1</v>
       </c>
       <c r="AB255" s="9" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="AC255" s="3">
         <v>15000</v>
@@ -27610,111 +27642,110 @@
         <v>10000</v>
       </c>
       <c r="AI255" s="9">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AJ255" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="256" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A256" s="2">
-        <v>303106</v>
-      </c>
-      <c r="B256" s="2">
+      <c r="A256" s="3">
+        <v>303102</v>
+      </c>
+      <c r="B256" s="3">
         <v>30</v>
       </c>
-      <c r="C256" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="D256" s="2"/>
-      <c r="E256" s="18"/>
-      <c r="F256" s="2"/>
-      <c r="G256" s="2">
+      <c r="C256" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D256" s="3"/>
+      <c r="F256" s="3"/>
+      <c r="G256" s="3">
         <v>12</v>
       </c>
-      <c r="H256" s="2">
-        <v>1</v>
-      </c>
-      <c r="I256" s="2" t="s">
+      <c r="H256" s="3">
+        <v>1</v>
+      </c>
+      <c r="I256" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="J256" s="2">
-        <v>0</v>
-      </c>
-      <c r="K256" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="L256" s="2">
-        <v>1000010</v>
-      </c>
-      <c r="M256" s="2">
-        <v>1</v>
-      </c>
-      <c r="N256" s="2">
-        <v>100</v>
-      </c>
-      <c r="O256" s="2">
-        <v>0</v>
-      </c>
-      <c r="P256" s="2">
-        <v>15</v>
-      </c>
-      <c r="Q256" s="2">
-        <v>0</v>
-      </c>
-      <c r="R256" s="2">
-        <v>36</v>
-      </c>
-      <c r="S256" s="2">
+      <c r="J256" s="3">
+        <v>0</v>
+      </c>
+      <c r="K256" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="L256" s="3">
+        <v>800001021</v>
+      </c>
+      <c r="M256" s="3">
+        <v>1</v>
+      </c>
+      <c r="N256" s="3">
+        <v>200</v>
+      </c>
+      <c r="O256" s="3">
+        <v>0</v>
+      </c>
+      <c r="P256" s="3">
+        <v>35</v>
+      </c>
+      <c r="Q256" s="3">
+        <v>4</v>
+      </c>
+      <c r="R256" s="3">
+        <v>570</v>
+      </c>
+      <c r="S256" s="3">
         <v>-5500</v>
       </c>
-      <c r="T256" s="2">
-        <v>1</v>
-      </c>
-      <c r="U256" s="2">
-        <v>0</v>
-      </c>
-      <c r="V256" s="2" t="s">
+      <c r="T256" s="3">
+        <v>1</v>
+      </c>
+      <c r="U256" s="3">
+        <v>0</v>
+      </c>
+      <c r="V256" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="W256" s="2" t="s">
+      <c r="W256" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="X256" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="Y256" s="23">
+      <c r="X256" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="Y256" s="16">
         <v>201002011</v>
       </c>
-      <c r="Z256" s="23">
-        <v>0</v>
-      </c>
-      <c r="AA256" s="2">
-        <v>1</v>
-      </c>
-      <c r="AB256" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="AC256" s="2">
+      <c r="Z256" s="16">
+        <v>0</v>
+      </c>
+      <c r="AA256" s="3">
+        <v>1</v>
+      </c>
+      <c r="AB256" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="AC256" s="3">
         <v>15000</v>
       </c>
-      <c r="AD256" s="2">
-        <v>10000</v>
-      </c>
-      <c r="AE256" s="2">
+      <c r="AD256" s="3">
+        <v>10000</v>
+      </c>
+      <c r="AE256" s="3">
         <v>25010001</v>
       </c>
       <c r="AF256" s="9">
         <v>40</v>
       </c>
       <c r="AG256" s="9">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="AH256" s="9">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI256" s="9">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AJ256" s="9">
         <v>0</v>
@@ -27722,13 +27753,13 @@
     </row>
     <row r="257" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A257" s="2">
-        <v>303107</v>
+        <v>303103</v>
       </c>
       <c r="B257" s="2">
         <v>30</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D257" s="2"/>
       <c r="E257" s="18"/>
@@ -27746,16 +27777,16 @@
         <v>0</v>
       </c>
       <c r="K257" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="L257" s="2">
-        <v>1000006</v>
+        <v>800001021</v>
       </c>
       <c r="M257" s="2">
         <v>1</v>
       </c>
       <c r="N257" s="2">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="O257" s="2">
         <v>0</v>
@@ -27764,10 +27795,10 @@
         <v>15</v>
       </c>
       <c r="Q257" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R257" s="2">
-        <v>36</v>
+        <v>300</v>
       </c>
       <c r="S257" s="2">
         <v>-5500</v>
@@ -27776,7 +27807,7 @@
         <v>1</v>
       </c>
       <c r="U257" s="2">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="V257" s="2" t="s">
         <v>110</v>
@@ -27785,7 +27816,7 @@
         <v>111</v>
       </c>
       <c r="X257" s="2" t="s">
-        <v>125</v>
+        <v>165</v>
       </c>
       <c r="Y257" s="23">
         <v>201002011</v>
@@ -27797,7 +27828,7 @@
         <v>1</v>
       </c>
       <c r="AB257" s="18" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="AC257" s="2">
         <v>15000</v>
@@ -27825,208 +27856,206 @@
       </c>
     </row>
     <row r="258" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A258" s="2">
-        <v>303108</v>
-      </c>
-      <c r="B258" s="2">
+      <c r="A258" s="3">
+        <v>303104</v>
+      </c>
+      <c r="B258" s="3">
         <v>30</v>
       </c>
-      <c r="C258" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D258" s="2"/>
-      <c r="E258" s="18"/>
-      <c r="F258" s="2"/>
-      <c r="G258" s="2">
+      <c r="C258" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D258" s="3"/>
+      <c r="F258" s="3"/>
+      <c r="G258" s="3">
         <v>12</v>
       </c>
-      <c r="H258" s="2">
-        <v>1</v>
-      </c>
-      <c r="I258" s="2" t="s">
+      <c r="H258" s="3">
+        <v>1</v>
+      </c>
+      <c r="I258" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="J258" s="2">
-        <v>0</v>
-      </c>
-      <c r="K258" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="L258" s="2">
-        <v>1000006</v>
-      </c>
-      <c r="M258" s="2">
-        <v>1</v>
-      </c>
-      <c r="N258" s="2">
-        <v>100</v>
-      </c>
-      <c r="O258" s="2">
-        <v>0</v>
-      </c>
-      <c r="P258" s="2">
-        <v>15</v>
-      </c>
-      <c r="Q258" s="2">
-        <v>0</v>
-      </c>
-      <c r="R258" s="2">
-        <v>36</v>
-      </c>
-      <c r="S258" s="2">
+      <c r="J258" s="3">
+        <v>0</v>
+      </c>
+      <c r="K258" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="L258" s="3">
+        <v>800001041</v>
+      </c>
+      <c r="M258" s="3">
+        <v>1</v>
+      </c>
+      <c r="N258" s="3">
+        <v>70</v>
+      </c>
+      <c r="O258" s="3">
+        <v>0</v>
+      </c>
+      <c r="P258" s="3">
+        <v>27</v>
+      </c>
+      <c r="Q258" s="3">
+        <v>0</v>
+      </c>
+      <c r="R258" s="3">
+        <v>169</v>
+      </c>
+      <c r="S258" s="3">
         <v>-5500</v>
       </c>
-      <c r="T258" s="2">
-        <v>1</v>
-      </c>
-      <c r="U258" s="2">
-        <v>0</v>
-      </c>
-      <c r="V258" s="2" t="s">
+      <c r="T258" s="3">
+        <v>1</v>
+      </c>
+      <c r="U258" s="3">
+        <v>0</v>
+      </c>
+      <c r="V258" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="W258" s="2" t="s">
+      <c r="W258" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="X258" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="Y258" s="23">
-        <v>201002011</v>
-      </c>
-      <c r="Z258" s="23">
-        <v>0</v>
-      </c>
-      <c r="AA258" s="2">
-        <v>1</v>
-      </c>
-      <c r="AB258" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="AC258" s="2">
+      <c r="X258" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="Y258" s="16">
+        <v>201004011</v>
+      </c>
+      <c r="Z258" s="16">
+        <v>0</v>
+      </c>
+      <c r="AA258" s="3">
+        <v>1</v>
+      </c>
+      <c r="AB258" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC258" s="3">
         <v>15000</v>
       </c>
-      <c r="AD258" s="2">
-        <v>10000</v>
-      </c>
-      <c r="AE258" s="2">
+      <c r="AD258" s="3">
+        <v>10000</v>
+      </c>
+      <c r="AE258" s="3">
         <v>25010001</v>
       </c>
       <c r="AF258" s="9">
         <v>40</v>
       </c>
       <c r="AG258" s="9">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH258" s="9">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI258" s="9">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AJ258" s="9">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="259" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A259" s="2">
-        <v>303109</v>
-      </c>
-      <c r="B259" s="2">
+      <c r="A259" s="3">
+        <v>303105</v>
+      </c>
+      <c r="B259" s="3">
         <v>30</v>
       </c>
-      <c r="C259" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="D259" s="2"/>
-      <c r="E259" s="18"/>
-      <c r="F259" s="2"/>
-      <c r="G259" s="2">
+      <c r="C259" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D259" s="3"/>
+      <c r="F259" s="3"/>
+      <c r="G259" s="3">
         <v>12</v>
       </c>
-      <c r="H259" s="2">
-        <v>1</v>
-      </c>
-      <c r="I259" s="2" t="s">
+      <c r="H259" s="3">
+        <v>1</v>
+      </c>
+      <c r="I259" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="J259" s="2">
-        <v>0</v>
-      </c>
-      <c r="K259" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="L259" s="2">
-        <v>1000006</v>
-      </c>
-      <c r="M259" s="2">
-        <v>1</v>
-      </c>
-      <c r="N259" s="2">
-        <v>100</v>
-      </c>
-      <c r="O259" s="2">
-        <v>0</v>
-      </c>
-      <c r="P259" s="2">
-        <v>15</v>
-      </c>
-      <c r="Q259" s="2">
-        <v>0</v>
-      </c>
-      <c r="R259" s="2">
-        <v>36</v>
-      </c>
-      <c r="S259" s="2">
+      <c r="J259" s="3">
+        <v>0</v>
+      </c>
+      <c r="K259" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="L259" s="3">
+        <v>800014011</v>
+      </c>
+      <c r="M259" s="3">
+        <v>1</v>
+      </c>
+      <c r="N259" s="3">
+        <v>125</v>
+      </c>
+      <c r="O259" s="3">
+        <v>0</v>
+      </c>
+      <c r="P259" s="3">
+        <v>24</v>
+      </c>
+      <c r="Q259" s="3">
+        <v>2</v>
+      </c>
+      <c r="R259" s="3">
+        <v>301</v>
+      </c>
+      <c r="S259" s="3">
         <v>-5500</v>
       </c>
-      <c r="T259" s="2">
-        <v>1</v>
-      </c>
-      <c r="U259" s="2">
-        <v>0</v>
-      </c>
-      <c r="V259" s="2" t="s">
+      <c r="T259" s="3">
+        <v>1</v>
+      </c>
+      <c r="U259" s="3">
+        <v>0</v>
+      </c>
+      <c r="V259" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="W259" s="2" t="s">
+      <c r="W259" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="X259" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="Y259" s="23">
-        <v>201002011</v>
-      </c>
-      <c r="Z259" s="23">
-        <v>0</v>
-      </c>
-      <c r="AA259" s="2">
-        <v>1</v>
-      </c>
-      <c r="AB259" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="AC259" s="2">
+      <c r="X259" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="Y259" s="16">
+        <v>214001011</v>
+      </c>
+      <c r="Z259" s="16">
+        <v>0</v>
+      </c>
+      <c r="AA259" s="3">
+        <v>1</v>
+      </c>
+      <c r="AB259" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="AC259" s="3">
         <v>15000</v>
       </c>
-      <c r="AD259" s="2">
-        <v>10000</v>
-      </c>
-      <c r="AE259" s="2">
+      <c r="AD259" s="3">
+        <v>10000</v>
+      </c>
+      <c r="AE259" s="3">
         <v>25010001</v>
       </c>
       <c r="AF259" s="9">
         <v>40</v>
       </c>
       <c r="AG259" s="9">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AH259" s="9">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AI259" s="9">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AJ259" s="9">
         <v>0</v>
@@ -28034,13 +28063,13 @@
     </row>
     <row r="260" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A260" s="2">
-        <v>303110</v>
+        <v>303106</v>
       </c>
       <c r="B260" s="2">
         <v>30</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="D260" s="2"/>
       <c r="E260" s="18"/>
@@ -28058,10 +28087,10 @@
         <v>0</v>
       </c>
       <c r="K260" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="L260" s="2">
-        <v>1000103</v>
+        <v>1000010</v>
       </c>
       <c r="M260" s="2">
         <v>1</v>
@@ -28138,13 +28167,13 @@
     </row>
     <row r="261" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A261" s="2">
-        <v>303111</v>
+        <v>303107</v>
       </c>
       <c r="B261" s="2">
         <v>30</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="D261" s="2"/>
       <c r="E261" s="18"/>
@@ -28162,10 +28191,10 @@
         <v>0</v>
       </c>
       <c r="K261" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L261" s="2">
-        <v>1000103</v>
+        <v>1000006</v>
       </c>
       <c r="M261" s="2">
         <v>1</v>
@@ -28242,13 +28271,13 @@
     </row>
     <row r="262" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A262" s="2">
-        <v>303112</v>
+        <v>303108</v>
       </c>
       <c r="B262" s="2">
         <v>30</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="D262" s="2"/>
       <c r="E262" s="18"/>
@@ -28266,10 +28295,10 @@
         <v>0</v>
       </c>
       <c r="K262" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L262" s="2">
-        <v>1000103</v>
+        <v>1000006</v>
       </c>
       <c r="M262" s="2">
         <v>1</v>
@@ -28344,104 +28373,105 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A263" s="3">
-        <v>303113</v>
-      </c>
-      <c r="B263" s="3">
+    <row r="263" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A263" s="2">
+        <v>303109</v>
+      </c>
+      <c r="B263" s="2">
         <v>30</v>
       </c>
-      <c r="C263" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="D263" s="3"/>
-      <c r="F263" s="3"/>
-      <c r="G263" s="3">
+      <c r="C263" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D263" s="2"/>
+      <c r="E263" s="18"/>
+      <c r="F263" s="2"/>
+      <c r="G263" s="2">
         <v>12</v>
       </c>
-      <c r="H263" s="3">
-        <v>1</v>
-      </c>
-      <c r="I263" s="3" t="s">
+      <c r="H263" s="2">
+        <v>1</v>
+      </c>
+      <c r="I263" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="J263" s="3">
-        <v>0</v>
-      </c>
-      <c r="K263" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="L263" s="3">
-        <v>800003021</v>
-      </c>
-      <c r="M263" s="3">
-        <v>1</v>
-      </c>
-      <c r="N263" s="3">
-        <v>500</v>
-      </c>
-      <c r="O263" s="3">
-        <v>0</v>
-      </c>
-      <c r="P263" s="3">
-        <v>38</v>
-      </c>
-      <c r="Q263" s="3">
-        <v>4</v>
-      </c>
-      <c r="R263" s="22">
-        <v>570</v>
-      </c>
-      <c r="S263" s="3">
+      <c r="J263" s="2">
+        <v>0</v>
+      </c>
+      <c r="K263" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="L263" s="2">
+        <v>1000006</v>
+      </c>
+      <c r="M263" s="2">
+        <v>1</v>
+      </c>
+      <c r="N263" s="2">
+        <v>100</v>
+      </c>
+      <c r="O263" s="2">
+        <v>0</v>
+      </c>
+      <c r="P263" s="2">
+        <v>15</v>
+      </c>
+      <c r="Q263" s="2">
+        <v>0</v>
+      </c>
+      <c r="R263" s="2">
+        <v>36</v>
+      </c>
+      <c r="S263" s="2">
         <v>-5500</v>
       </c>
-      <c r="T263" s="3">
-        <v>1</v>
-      </c>
-      <c r="U263" s="3">
-        <v>0</v>
-      </c>
-      <c r="V263" s="3" t="s">
+      <c r="T263" s="2">
+        <v>1</v>
+      </c>
+      <c r="U263" s="2">
+        <v>0</v>
+      </c>
+      <c r="V263" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="W263" s="3" t="s">
+      <c r="W263" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="X263" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="Y263" s="16">
-        <v>203002011</v>
-      </c>
-      <c r="Z263" s="16">
-        <v>0</v>
-      </c>
-      <c r="AA263" s="3">
-        <v>1</v>
-      </c>
-      <c r="AB263" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="AC263" s="3">
+      <c r="X263" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y263" s="23">
+        <v>201002011</v>
+      </c>
+      <c r="Z263" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA263" s="2">
+        <v>1</v>
+      </c>
+      <c r="AB263" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC263" s="2">
         <v>15000</v>
       </c>
-      <c r="AD263" s="3">
-        <v>10000</v>
-      </c>
-      <c r="AE263" s="3">
+      <c r="AD263" s="2">
+        <v>10000</v>
+      </c>
+      <c r="AE263" s="2">
         <v>25010001</v>
       </c>
       <c r="AF263" s="9">
         <v>40</v>
       </c>
       <c r="AG263" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AH263" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AI263" s="9">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AJ263" s="9">
         <v>0</v>
@@ -28449,13 +28479,13 @@
     </row>
     <row r="264" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A264" s="2">
-        <v>303114</v>
+        <v>303110</v>
       </c>
       <c r="B264" s="2">
         <v>30</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="D264" s="2"/>
       <c r="E264" s="18"/>
@@ -28473,10 +28503,10 @@
         <v>0</v>
       </c>
       <c r="K264" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="L264" s="2">
-        <v>1000011</v>
+        <v>1000103</v>
       </c>
       <c r="M264" s="2">
         <v>1</v>
@@ -28533,7 +28563,7 @@
         <v>10000</v>
       </c>
       <c r="AE264" s="2">
-        <v>0</v>
+        <v>25010001</v>
       </c>
       <c r="AF264" s="9">
         <v>40</v>
@@ -28551,534 +28581,533 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A265" s="3">
-        <v>303115</v>
-      </c>
-      <c r="B265" s="3">
+    <row r="265" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A265" s="2">
+        <v>303111</v>
+      </c>
+      <c r="B265" s="2">
         <v>30</v>
       </c>
-      <c r="C265" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="D265" s="3"/>
-      <c r="F265" s="3"/>
-      <c r="G265" s="3">
+      <c r="C265" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D265" s="2"/>
+      <c r="E265" s="18"/>
+      <c r="F265" s="2"/>
+      <c r="G265" s="2">
         <v>12</v>
       </c>
-      <c r="H265" s="3">
-        <v>4</v>
-      </c>
-      <c r="I265" s="3" t="s">
+      <c r="H265" s="2">
+        <v>1</v>
+      </c>
+      <c r="I265" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="J265" s="3">
-        <v>0</v>
-      </c>
-      <c r="K265" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="L265" s="3">
-        <v>800016011</v>
-      </c>
-      <c r="M265" s="3">
-        <v>1</v>
-      </c>
-      <c r="N265" s="3">
+      <c r="J265" s="2">
+        <v>0</v>
+      </c>
+      <c r="K265" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="L265" s="2">
+        <v>1000103</v>
+      </c>
+      <c r="M265" s="2">
+        <v>1</v>
+      </c>
+      <c r="N265" s="2">
         <v>100</v>
       </c>
-      <c r="O265" s="3">
-        <v>0</v>
-      </c>
-      <c r="P265" s="3">
-        <v>50</v>
-      </c>
-      <c r="Q265" s="3">
-        <v>6</v>
-      </c>
-      <c r="R265" s="22">
-        <v>3740</v>
-      </c>
-      <c r="S265" s="3">
+      <c r="O265" s="2">
+        <v>0</v>
+      </c>
+      <c r="P265" s="2">
+        <v>15</v>
+      </c>
+      <c r="Q265" s="2">
+        <v>0</v>
+      </c>
+      <c r="R265" s="2">
+        <v>36</v>
+      </c>
+      <c r="S265" s="2">
         <v>-5500</v>
       </c>
-      <c r="T265" s="3">
-        <v>1</v>
-      </c>
-      <c r="U265" s="3">
-        <v>30000</v>
-      </c>
-      <c r="V265" s="3" t="s">
+      <c r="T265" s="2">
+        <v>1</v>
+      </c>
+      <c r="U265" s="2">
+        <v>0</v>
+      </c>
+      <c r="V265" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="W265" s="3" t="s">
+      <c r="W265" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="X265" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="Y265" s="16">
-        <v>216001001</v>
-      </c>
-      <c r="Z265" s="16">
-        <v>0</v>
-      </c>
-      <c r="AA265" s="3">
-        <v>1</v>
-      </c>
-      <c r="AB265" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="AC265" s="3">
+      <c r="X265" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y265" s="23">
+        <v>201002011</v>
+      </c>
+      <c r="Z265" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA265" s="2">
+        <v>1</v>
+      </c>
+      <c r="AB265" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC265" s="2">
         <v>15000</v>
       </c>
-      <c r="AD265" s="3">
-        <v>10000</v>
-      </c>
-      <c r="AE265" s="3">
+      <c r="AD265" s="2">
+        <v>10000</v>
+      </c>
+      <c r="AE265" s="2">
         <v>25010001</v>
       </c>
       <c r="AF265" s="9">
         <v>40</v>
       </c>
       <c r="AG265" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH265" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI265" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ265" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A266" s="2">
+        <v>303112</v>
+      </c>
+      <c r="B266" s="2">
+        <v>30</v>
+      </c>
+      <c r="C266" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D266" s="2"/>
+      <c r="E266" s="18"/>
+      <c r="F266" s="2"/>
+      <c r="G266" s="2">
+        <v>12</v>
+      </c>
+      <c r="H266" s="2">
+        <v>1</v>
+      </c>
+      <c r="I266" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J266" s="2">
+        <v>0</v>
+      </c>
+      <c r="K266" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="L266" s="2">
+        <v>1000103</v>
+      </c>
+      <c r="M266" s="2">
+        <v>1</v>
+      </c>
+      <c r="N266" s="2">
+        <v>100</v>
+      </c>
+      <c r="O266" s="2">
+        <v>0</v>
+      </c>
+      <c r="P266" s="2">
+        <v>15</v>
+      </c>
+      <c r="Q266" s="2">
+        <v>0</v>
+      </c>
+      <c r="R266" s="2">
+        <v>36</v>
+      </c>
+      <c r="S266" s="2">
+        <v>-5500</v>
+      </c>
+      <c r="T266" s="2">
+        <v>1</v>
+      </c>
+      <c r="U266" s="2">
+        <v>0</v>
+      </c>
+      <c r="V266" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="W266" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="X266" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y266" s="23">
+        <v>201002011</v>
+      </c>
+      <c r="Z266" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA266" s="2">
+        <v>1</v>
+      </c>
+      <c r="AB266" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC266" s="2">
+        <v>15000</v>
+      </c>
+      <c r="AD266" s="2">
+        <v>10000</v>
+      </c>
+      <c r="AE266" s="2">
+        <v>25010001</v>
+      </c>
+      <c r="AF266" s="9">
+        <v>40</v>
+      </c>
+      <c r="AG266" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH266" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI266" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ266" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A267" s="3">
+        <v>303113</v>
+      </c>
+      <c r="B267" s="3">
+        <v>30</v>
+      </c>
+      <c r="C267" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D267" s="3"/>
+      <c r="F267" s="3"/>
+      <c r="G267" s="3">
+        <v>12</v>
+      </c>
+      <c r="H267" s="3">
+        <v>1</v>
+      </c>
+      <c r="I267" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="J267" s="3">
+        <v>0</v>
+      </c>
+      <c r="K267" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L267" s="3">
+        <v>800003021</v>
+      </c>
+      <c r="M267" s="3">
+        <v>1</v>
+      </c>
+      <c r="N267" s="3">
+        <v>500</v>
+      </c>
+      <c r="O267" s="3">
+        <v>0</v>
+      </c>
+      <c r="P267" s="3">
+        <v>38</v>
+      </c>
+      <c r="Q267" s="3">
+        <v>4</v>
+      </c>
+      <c r="R267" s="22">
+        <v>570</v>
+      </c>
+      <c r="S267" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="T267" s="3">
+        <v>1</v>
+      </c>
+      <c r="U267" s="3">
+        <v>0</v>
+      </c>
+      <c r="V267" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="W267" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="X267" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="Y267" s="16">
+        <v>203002011</v>
+      </c>
+      <c r="Z267" s="16">
+        <v>0</v>
+      </c>
+      <c r="AA267" s="3">
+        <v>1</v>
+      </c>
+      <c r="AB267" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC267" s="3">
+        <v>15000</v>
+      </c>
+      <c r="AD267" s="3">
+        <v>10000</v>
+      </c>
+      <c r="AE267" s="3">
+        <v>25010001</v>
+      </c>
+      <c r="AF267" s="9">
+        <v>40</v>
+      </c>
+      <c r="AG267" s="9">
+        <v>10000</v>
+      </c>
+      <c r="AH267" s="9">
+        <v>10000</v>
+      </c>
+      <c r="AI267" s="9">
+        <v>40</v>
+      </c>
+      <c r="AJ267" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A268" s="2">
+        <v>303114</v>
+      </c>
+      <c r="B268" s="2">
+        <v>30</v>
+      </c>
+      <c r="C268" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D268" s="2"/>
+      <c r="E268" s="18"/>
+      <c r="F268" s="2"/>
+      <c r="G268" s="2">
+        <v>12</v>
+      </c>
+      <c r="H268" s="2">
+        <v>1</v>
+      </c>
+      <c r="I268" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J268" s="2">
+        <v>0</v>
+      </c>
+      <c r="K268" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="L268" s="2">
+        <v>1000011</v>
+      </c>
+      <c r="M268" s="2">
+        <v>1</v>
+      </c>
+      <c r="N268" s="2">
+        <v>100</v>
+      </c>
+      <c r="O268" s="2">
+        <v>0</v>
+      </c>
+      <c r="P268" s="2">
+        <v>15</v>
+      </c>
+      <c r="Q268" s="2">
+        <v>0</v>
+      </c>
+      <c r="R268" s="2">
+        <v>36</v>
+      </c>
+      <c r="S268" s="2">
+        <v>-5500</v>
+      </c>
+      <c r="T268" s="2">
+        <v>1</v>
+      </c>
+      <c r="U268" s="2">
+        <v>0</v>
+      </c>
+      <c r="V268" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="W268" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="X268" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y268" s="23">
+        <v>201002011</v>
+      </c>
+      <c r="Z268" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA268" s="2">
+        <v>1</v>
+      </c>
+      <c r="AB268" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC268" s="2">
+        <v>15000</v>
+      </c>
+      <c r="AD268" s="2">
+        <v>10000</v>
+      </c>
+      <c r="AE268" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF268" s="9">
+        <v>40</v>
+      </c>
+      <c r="AG268" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH268" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI268" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ268" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A269" s="3">
+        <v>303115</v>
+      </c>
+      <c r="B269" s="3">
+        <v>30</v>
+      </c>
+      <c r="C269" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D269" s="3"/>
+      <c r="F269" s="3"/>
+      <c r="G269" s="3">
+        <v>12</v>
+      </c>
+      <c r="H269" s="3">
+        <v>4</v>
+      </c>
+      <c r="I269" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="J269" s="3">
+        <v>0</v>
+      </c>
+      <c r="K269" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="L269" s="3">
+        <v>800016011</v>
+      </c>
+      <c r="M269" s="3">
+        <v>1</v>
+      </c>
+      <c r="N269" s="3">
+        <v>100</v>
+      </c>
+      <c r="O269" s="3">
+        <v>0</v>
+      </c>
+      <c r="P269" s="3">
+        <v>50</v>
+      </c>
+      <c r="Q269" s="3">
+        <v>6</v>
+      </c>
+      <c r="R269" s="22">
+        <v>3740</v>
+      </c>
+      <c r="S269" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="T269" s="3">
+        <v>1</v>
+      </c>
+      <c r="U269" s="3">
+        <v>30000</v>
+      </c>
+      <c r="V269" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="W269" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="X269" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="Y269" s="16">
+        <v>216001001</v>
+      </c>
+      <c r="Z269" s="16">
+        <v>0</v>
+      </c>
+      <c r="AA269" s="3">
+        <v>1</v>
+      </c>
+      <c r="AB269" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="AC269" s="3">
+        <v>15000</v>
+      </c>
+      <c r="AD269" s="3">
+        <v>10000</v>
+      </c>
+      <c r="AE269" s="3">
+        <v>25010001</v>
+      </c>
+      <c r="AF269" s="9">
+        <v>40</v>
+      </c>
+      <c r="AG269" s="9">
         <v>1000</v>
       </c>
-      <c r="AH265" s="9">
+      <c r="AH269" s="9">
         <v>5000</v>
       </c>
-      <c r="AI265" s="9">
+      <c r="AI269" s="9">
         <v>5</v>
       </c>
-      <c r="AJ265" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="266" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A266" s="25">
-        <v>90000101</v>
-      </c>
-      <c r="B266" s="25">
-        <v>1</v>
-      </c>
-      <c r="C266" s="25" t="s">
-        <v>167</v>
-      </c>
-      <c r="D266" s="25"/>
-      <c r="E266" s="26"/>
-      <c r="F266" s="25"/>
-      <c r="G266" s="25">
-        <v>1</v>
-      </c>
-      <c r="H266" s="25">
-        <v>2</v>
-      </c>
-      <c r="I266" s="33" t="s">
-        <v>81</v>
-      </c>
-      <c r="J266" s="25">
-        <v>0</v>
-      </c>
-      <c r="K266" s="25" t="s">
-        <v>168</v>
-      </c>
-      <c r="L266" s="27">
-        <v>800001031</v>
-      </c>
-      <c r="M266" s="25">
-        <v>1</v>
-      </c>
-      <c r="N266" s="28">
-        <v>5</v>
-      </c>
-      <c r="O266" s="25">
-        <v>1</v>
-      </c>
-      <c r="P266" s="25">
-        <v>8</v>
-      </c>
-      <c r="Q266" s="25">
-        <v>0</v>
-      </c>
-      <c r="R266" s="25">
-        <v>25</v>
-      </c>
-      <c r="S266" s="25">
-        <v>-5000</v>
-      </c>
-      <c r="T266" s="25">
-        <v>1</v>
-      </c>
-      <c r="U266" s="25">
-        <v>0</v>
-      </c>
-      <c r="V266" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="W266" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="X266" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="Y266" s="30">
-        <v>20010001</v>
-      </c>
-      <c r="Z266" s="30">
-        <v>0</v>
-      </c>
-      <c r="AA266" s="25">
-        <v>1</v>
-      </c>
-      <c r="AB266" s="31" t="s">
-        <v>83</v>
-      </c>
-      <c r="AC266" s="25">
-        <v>10000</v>
-      </c>
-      <c r="AD266" s="25">
-        <v>10000</v>
-      </c>
-      <c r="AE266" s="25">
-        <v>0</v>
-      </c>
-      <c r="AF266" s="31">
-        <v>40</v>
-      </c>
-      <c r="AG266" s="31">
-        <v>0</v>
-      </c>
-      <c r="AH266" s="31">
-        <v>0</v>
-      </c>
-      <c r="AI266" s="31">
-        <v>0</v>
-      </c>
-      <c r="AJ266" s="31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="267" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A267" s="25">
-        <v>90000102</v>
-      </c>
-      <c r="B267" s="25">
-        <v>1</v>
-      </c>
-      <c r="C267" s="25" t="s">
-        <v>169</v>
-      </c>
-      <c r="D267" s="25"/>
-      <c r="E267" s="26"/>
-      <c r="F267" s="25"/>
-      <c r="G267" s="25">
-        <v>1</v>
-      </c>
-      <c r="H267" s="25">
-        <v>2</v>
-      </c>
-      <c r="I267" s="33" t="s">
-        <v>81</v>
-      </c>
-      <c r="J267" s="25">
-        <v>0</v>
-      </c>
-      <c r="K267" s="25" t="s">
-        <v>168</v>
-      </c>
-      <c r="L267" s="27">
-        <v>800001031</v>
-      </c>
-      <c r="M267" s="25">
-        <v>1</v>
-      </c>
-      <c r="N267" s="28">
-        <v>20</v>
-      </c>
-      <c r="O267" s="25">
-        <v>1</v>
-      </c>
-      <c r="P267" s="25">
-        <v>8</v>
-      </c>
-      <c r="Q267" s="25">
-        <v>0</v>
-      </c>
-      <c r="R267" s="25">
-        <v>25</v>
-      </c>
-      <c r="S267" s="25">
-        <v>-5000</v>
-      </c>
-      <c r="T267" s="25">
-        <v>1</v>
-      </c>
-      <c r="U267" s="25">
-        <v>0</v>
-      </c>
-      <c r="V267" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="W267" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="X267" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="Y267" s="30">
-        <v>20010001</v>
-      </c>
-      <c r="Z267" s="30">
-        <v>0</v>
-      </c>
-      <c r="AA267" s="25">
-        <v>1</v>
-      </c>
-      <c r="AB267" s="31" t="s">
-        <v>83</v>
-      </c>
-      <c r="AC267" s="25">
-        <v>10000</v>
-      </c>
-      <c r="AD267" s="25">
-        <v>10000</v>
-      </c>
-      <c r="AE267" s="25">
-        <v>0</v>
-      </c>
-      <c r="AF267" s="31">
-        <v>40</v>
-      </c>
-      <c r="AG267" s="31">
-        <v>0</v>
-      </c>
-      <c r="AH267" s="31">
-        <v>0</v>
-      </c>
-      <c r="AI267" s="31">
-        <v>0</v>
-      </c>
-      <c r="AJ267" s="31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="268" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A268" s="25">
-        <v>90000201</v>
-      </c>
-      <c r="B268" s="25">
-        <v>2</v>
-      </c>
-      <c r="C268" s="25" t="s">
-        <v>170</v>
-      </c>
-      <c r="D268" s="25"/>
-      <c r="E268" s="26"/>
-      <c r="F268" s="25"/>
-      <c r="G268" s="25">
-        <v>1</v>
-      </c>
-      <c r="H268" s="25">
-        <v>2</v>
-      </c>
-      <c r="I268" s="33" t="s">
-        <v>81</v>
-      </c>
-      <c r="J268" s="25">
-        <v>0</v>
-      </c>
-      <c r="K268" s="25" t="s">
-        <v>171</v>
-      </c>
-      <c r="L268" s="27">
-        <v>800004031</v>
-      </c>
-      <c r="M268" s="25">
-        <v>1</v>
-      </c>
-      <c r="N268" s="28">
-        <v>6</v>
-      </c>
-      <c r="O268" s="25">
-        <v>1</v>
-      </c>
-      <c r="P268" s="25">
-        <v>8</v>
-      </c>
-      <c r="Q268" s="25">
-        <v>0</v>
-      </c>
-      <c r="R268" s="25">
-        <v>25</v>
-      </c>
-      <c r="S268" s="25">
-        <v>-5000</v>
-      </c>
-      <c r="T268" s="25">
-        <v>1</v>
-      </c>
-      <c r="U268" s="25">
-        <v>0</v>
-      </c>
-      <c r="V268" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="W268" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="X268" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="Y268" s="30">
-        <v>20010001</v>
-      </c>
-      <c r="Z268" s="30">
-        <v>0</v>
-      </c>
-      <c r="AA268" s="25">
-        <v>1</v>
-      </c>
-      <c r="AB268" s="31" t="s">
-        <v>83</v>
-      </c>
-      <c r="AC268" s="25">
-        <v>10000</v>
-      </c>
-      <c r="AD268" s="25">
-        <v>10000</v>
-      </c>
-      <c r="AE268" s="25">
-        <v>0</v>
-      </c>
-      <c r="AF268" s="31">
-        <v>40</v>
-      </c>
-      <c r="AG268" s="31">
-        <v>0</v>
-      </c>
-      <c r="AH268" s="31">
-        <v>0</v>
-      </c>
-      <c r="AI268" s="31">
-        <v>0</v>
-      </c>
-      <c r="AJ268" s="31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="269" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A269" s="25">
-        <v>90000202</v>
-      </c>
-      <c r="B269" s="25">
-        <v>2</v>
-      </c>
-      <c r="C269" s="25" t="s">
-        <v>172</v>
-      </c>
-      <c r="D269" s="25"/>
-      <c r="E269" s="26"/>
-      <c r="F269" s="25"/>
-      <c r="G269" s="25">
-        <v>1</v>
-      </c>
-      <c r="H269" s="25">
-        <v>2</v>
-      </c>
-      <c r="I269" s="33" t="s">
-        <v>81</v>
-      </c>
-      <c r="J269" s="25">
-        <v>0</v>
-      </c>
-      <c r="K269" s="25" t="s">
-        <v>171</v>
-      </c>
-      <c r="L269" s="27">
-        <v>800004031</v>
-      </c>
-      <c r="M269" s="25">
-        <v>1</v>
-      </c>
-      <c r="N269" s="28">
-        <v>24</v>
-      </c>
-      <c r="O269" s="25">
-        <v>1</v>
-      </c>
-      <c r="P269" s="25">
-        <v>8</v>
-      </c>
-      <c r="Q269" s="25">
-        <v>0</v>
-      </c>
-      <c r="R269" s="25">
-        <v>25</v>
-      </c>
-      <c r="S269" s="25">
-        <v>-5000</v>
-      </c>
-      <c r="T269" s="25">
-        <v>1</v>
-      </c>
-      <c r="U269" s="25">
-        <v>0</v>
-      </c>
-      <c r="V269" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="W269" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="X269" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="Y269" s="30">
-        <v>20010001</v>
-      </c>
-      <c r="Z269" s="30">
-        <v>0</v>
-      </c>
-      <c r="AA269" s="25">
-        <v>1</v>
-      </c>
-      <c r="AB269" s="31" t="s">
-        <v>83</v>
-      </c>
-      <c r="AC269" s="25">
-        <v>10000</v>
-      </c>
-      <c r="AD269" s="25">
-        <v>10000</v>
-      </c>
-      <c r="AE269" s="25">
-        <v>0</v>
-      </c>
-      <c r="AF269" s="31">
-        <v>40</v>
-      </c>
-      <c r="AG269" s="31">
-        <v>0</v>
-      </c>
-      <c r="AH269" s="31">
-        <v>0</v>
-      </c>
-      <c r="AI269" s="31">
-        <v>0</v>
-      </c>
-      <c r="AJ269" s="31">
+      <c r="AJ269" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="270" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A270" s="25">
-        <v>90000301</v>
+        <v>90000101</v>
       </c>
       <c r="B270" s="25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C270" s="25" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="D270" s="25"/>
       <c r="E270" s="26"/>
@@ -29096,16 +29125,16 @@
         <v>0</v>
       </c>
       <c r="K270" s="25" t="s">
-        <v>246</v>
+        <v>168</v>
       </c>
       <c r="L270" s="27">
-        <v>800007031</v>
+        <v>800001031</v>
       </c>
       <c r="M270" s="25">
         <v>1</v>
       </c>
       <c r="N270" s="28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O270" s="25">
         <v>1</v>
@@ -29176,13 +29205,13 @@
     </row>
     <row r="271" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A271" s="25">
-        <v>90000302</v>
+        <v>90000102</v>
       </c>
       <c r="B271" s="25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C271" s="25" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D271" s="25"/>
       <c r="E271" s="26"/>
@@ -29200,16 +29229,16 @@
         <v>0</v>
       </c>
       <c r="K271" s="25" t="s">
-        <v>246</v>
+        <v>168</v>
       </c>
       <c r="L271" s="27">
-        <v>800007031</v>
+        <v>800001031</v>
       </c>
       <c r="M271" s="25">
         <v>1</v>
       </c>
       <c r="N271" s="28">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="O271" s="25">
         <v>1</v>
@@ -29280,13 +29309,13 @@
     </row>
     <row r="272" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A272" s="25">
-        <v>90000400</v>
+        <v>90000201</v>
       </c>
       <c r="B272" s="25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C272" s="25" t="s">
-        <v>247</v>
+        <v>170</v>
       </c>
       <c r="D272" s="25"/>
       <c r="E272" s="26"/>
@@ -29304,16 +29333,16 @@
         <v>0</v>
       </c>
       <c r="K272" s="25" t="s">
-        <v>176</v>
-      </c>
-      <c r="L272" s="29">
-        <v>800003031</v>
+        <v>171</v>
+      </c>
+      <c r="L272" s="27">
+        <v>800004031</v>
       </c>
       <c r="M272" s="25">
         <v>1</v>
       </c>
       <c r="N272" s="28">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O272" s="25">
         <v>1</v>
@@ -29384,13 +29413,13 @@
     </row>
     <row r="273" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A273" s="25">
-        <v>90000401</v>
+        <v>90000202</v>
       </c>
       <c r="B273" s="25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C273" s="25" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D273" s="25"/>
       <c r="E273" s="26"/>
@@ -29408,16 +29437,16 @@
         <v>0</v>
       </c>
       <c r="K273" s="25" t="s">
-        <v>176</v>
-      </c>
-      <c r="L273" s="29">
-        <v>800003031</v>
+        <v>171</v>
+      </c>
+      <c r="L273" s="27">
+        <v>800004031</v>
       </c>
       <c r="M273" s="25">
         <v>1</v>
       </c>
       <c r="N273" s="28">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O273" s="25">
         <v>1</v>
@@ -29488,13 +29517,13 @@
     </row>
     <row r="274" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A274" s="25">
-        <v>90000402</v>
+        <v>90000301</v>
       </c>
       <c r="B274" s="25">
         <v>3</v>
       </c>
       <c r="C274" s="25" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D274" s="25"/>
       <c r="E274" s="26"/>
@@ -29512,16 +29541,16 @@
         <v>0</v>
       </c>
       <c r="K274" s="25" t="s">
-        <v>176</v>
-      </c>
-      <c r="L274" s="29">
-        <v>800003031</v>
+        <v>246</v>
+      </c>
+      <c r="L274" s="27">
+        <v>800007031</v>
       </c>
       <c r="M274" s="25">
         <v>1</v>
       </c>
       <c r="N274" s="28">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="O274" s="25">
         <v>1</v>
@@ -29592,13 +29621,13 @@
     </row>
     <row r="275" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A275" s="25">
-        <v>90000501</v>
+        <v>90000302</v>
       </c>
       <c r="B275" s="25">
         <v>3</v>
       </c>
       <c r="C275" s="25" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D275" s="25"/>
       <c r="E275" s="26"/>
@@ -29616,16 +29645,16 @@
         <v>0</v>
       </c>
       <c r="K275" s="25" t="s">
-        <v>168</v>
+        <v>246</v>
       </c>
       <c r="L275" s="27">
-        <v>800001031</v>
+        <v>800007031</v>
       </c>
       <c r="M275" s="25">
         <v>1</v>
       </c>
       <c r="N275" s="28">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="O275" s="25">
         <v>1</v>
@@ -29696,13 +29725,13 @@
     </row>
     <row r="276" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A276" s="25">
-        <v>90000502</v>
+        <v>90000400</v>
       </c>
       <c r="B276" s="25">
         <v>3</v>
       </c>
       <c r="C276" s="25" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="D276" s="25"/>
       <c r="E276" s="26"/>
@@ -29720,16 +29749,16 @@
         <v>0</v>
       </c>
       <c r="K276" s="25" t="s">
-        <v>168</v>
-      </c>
-      <c r="L276" s="27">
-        <v>800001031</v>
+        <v>176</v>
+      </c>
+      <c r="L276" s="29">
+        <v>800003031</v>
       </c>
       <c r="M276" s="25">
         <v>1</v>
       </c>
       <c r="N276" s="28">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="O276" s="25">
         <v>1</v>
@@ -29800,13 +29829,13 @@
     </row>
     <row r="277" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A277" s="25">
-        <v>90000503</v>
+        <v>90000401</v>
       </c>
       <c r="B277" s="25">
         <v>3</v>
       </c>
       <c r="C277" s="25" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D277" s="25"/>
       <c r="E277" s="26"/>
@@ -29824,16 +29853,16 @@
         <v>0</v>
       </c>
       <c r="K277" s="25" t="s">
-        <v>168</v>
-      </c>
-      <c r="L277" s="27">
-        <v>800001031</v>
+        <v>176</v>
+      </c>
+      <c r="L277" s="29">
+        <v>800003031</v>
       </c>
       <c r="M277" s="25">
         <v>1</v>
       </c>
       <c r="N277" s="28">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="O277" s="25">
         <v>1</v>
@@ -29904,13 +29933,13 @@
     </row>
     <row r="278" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A278" s="25">
-        <v>90000504</v>
+        <v>90000402</v>
       </c>
       <c r="B278" s="25">
         <v>3</v>
       </c>
       <c r="C278" s="25" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D278" s="25"/>
       <c r="E278" s="26"/>
@@ -29928,16 +29957,16 @@
         <v>0</v>
       </c>
       <c r="K278" s="25" t="s">
-        <v>168</v>
-      </c>
-      <c r="L278" s="27">
-        <v>800001031</v>
+        <v>176</v>
+      </c>
+      <c r="L278" s="29">
+        <v>800003031</v>
       </c>
       <c r="M278" s="25">
         <v>1</v>
       </c>
       <c r="N278" s="28">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="O278" s="25">
         <v>1</v>
@@ -30008,13 +30037,13 @@
     </row>
     <row r="279" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A279" s="25">
-        <v>90000601</v>
+        <v>90000501</v>
       </c>
       <c r="B279" s="25">
         <v>3</v>
       </c>
       <c r="C279" s="25" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D279" s="25"/>
       <c r="E279" s="26"/>
@@ -30032,10 +30061,10 @@
         <v>0</v>
       </c>
       <c r="K279" s="25" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="L279" s="27">
-        <v>800004031</v>
+        <v>800001031</v>
       </c>
       <c r="M279" s="25">
         <v>1</v>
@@ -30112,13 +30141,13 @@
     </row>
     <row r="280" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A280" s="25">
-        <v>90000602</v>
+        <v>90000502</v>
       </c>
       <c r="B280" s="25">
         <v>3</v>
       </c>
       <c r="C280" s="25" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D280" s="25"/>
       <c r="E280" s="26"/>
@@ -30136,16 +30165,16 @@
         <v>0</v>
       </c>
       <c r="K280" s="25" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="L280" s="27">
-        <v>800004031</v>
+        <v>800001031</v>
       </c>
       <c r="M280" s="25">
         <v>1</v>
       </c>
       <c r="N280" s="28">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="O280" s="25">
         <v>1</v>
@@ -30216,13 +30245,13 @@
     </row>
     <row r="281" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A281" s="25">
-        <v>90000603</v>
+        <v>90000503</v>
       </c>
       <c r="B281" s="25">
         <v>3</v>
       </c>
       <c r="C281" s="25" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D281" s="25"/>
       <c r="E281" s="26"/>
@@ -30240,16 +30269,16 @@
         <v>0</v>
       </c>
       <c r="K281" s="25" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="L281" s="27">
-        <v>800004031</v>
+        <v>800001031</v>
       </c>
       <c r="M281" s="25">
         <v>1</v>
       </c>
       <c r="N281" s="28">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="O281" s="25">
         <v>1</v>
@@ -30320,13 +30349,13 @@
     </row>
     <row r="282" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A282" s="25">
-        <v>90000604</v>
+        <v>90000504</v>
       </c>
       <c r="B282" s="25">
         <v>3</v>
       </c>
       <c r="C282" s="25" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D282" s="25"/>
       <c r="E282" s="26"/>
@@ -30344,16 +30373,16 @@
         <v>0</v>
       </c>
       <c r="K282" s="25" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="L282" s="27">
-        <v>800004031</v>
+        <v>800001031</v>
       </c>
       <c r="M282" s="25">
         <v>1</v>
       </c>
       <c r="N282" s="28">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="O282" s="25">
         <v>1</v>
@@ -30424,13 +30453,13 @@
     </row>
     <row r="283" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A283" s="25">
-        <v>90000605</v>
+        <v>90000601</v>
       </c>
       <c r="B283" s="25">
         <v>3</v>
       </c>
       <c r="C283" s="25" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D283" s="25"/>
       <c r="E283" s="26"/>
@@ -30457,7 +30486,7 @@
         <v>1</v>
       </c>
       <c r="N283" s="28">
-        <v>120</v>
+        <v>8</v>
       </c>
       <c r="O283" s="25">
         <v>1</v>
@@ -30528,13 +30557,13 @@
     </row>
     <row r="284" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A284" s="25">
-        <v>90000606</v>
+        <v>90000602</v>
       </c>
       <c r="B284" s="25">
         <v>3</v>
       </c>
       <c r="C284" s="25" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D284" s="25"/>
       <c r="E284" s="26"/>
@@ -30561,7 +30590,7 @@
         <v>1</v>
       </c>
       <c r="N284" s="28">
-        <v>240</v>
+        <v>16</v>
       </c>
       <c r="O284" s="25">
         <v>1</v>
@@ -30632,13 +30661,13 @@
     </row>
     <row r="285" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A285" s="25">
-        <v>90000607</v>
+        <v>90000603</v>
       </c>
       <c r="B285" s="25">
         <v>3</v>
       </c>
       <c r="C285" s="25" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D285" s="25"/>
       <c r="E285" s="26"/>
@@ -30665,7 +30694,7 @@
         <v>1</v>
       </c>
       <c r="N285" s="28">
-        <v>350</v>
+        <v>36</v>
       </c>
       <c r="O285" s="25">
         <v>1</v>
@@ -30736,13 +30765,13 @@
     </row>
     <row r="286" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A286" s="25">
-        <v>90000608</v>
+        <v>90000604</v>
       </c>
       <c r="B286" s="25">
         <v>3</v>
       </c>
       <c r="C286" s="25" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D286" s="25"/>
       <c r="E286" s="26"/>
@@ -30769,7 +30798,7 @@
         <v>1</v>
       </c>
       <c r="N286" s="28">
-        <v>900</v>
+        <v>60</v>
       </c>
       <c r="O286" s="25">
         <v>1</v>
@@ -30840,13 +30869,13 @@
     </row>
     <row r="287" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A287" s="25">
-        <v>90000701</v>
+        <v>90000605</v>
       </c>
       <c r="B287" s="25">
         <v>3</v>
       </c>
       <c r="C287" s="25" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D287" s="25"/>
       <c r="E287" s="26"/>
@@ -30864,16 +30893,16 @@
         <v>0</v>
       </c>
       <c r="K287" s="25" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="L287" s="27">
-        <v>800001031</v>
+        <v>800004031</v>
       </c>
       <c r="M287" s="25">
         <v>1</v>
       </c>
       <c r="N287" s="28">
-        <v>9</v>
+        <v>120</v>
       </c>
       <c r="O287" s="25">
         <v>1</v>
@@ -30944,13 +30973,13 @@
     </row>
     <row r="288" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A288" s="25">
-        <v>90000702</v>
+        <v>90000606</v>
       </c>
       <c r="B288" s="25">
         <v>3</v>
       </c>
       <c r="C288" s="25" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D288" s="25"/>
       <c r="E288" s="26"/>
@@ -30968,16 +30997,16 @@
         <v>0</v>
       </c>
       <c r="K288" s="25" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="L288" s="27">
-        <v>800001031</v>
+        <v>800004031</v>
       </c>
       <c r="M288" s="25">
         <v>1</v>
       </c>
       <c r="N288" s="28">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="O288" s="25">
         <v>1</v>
@@ -31048,13 +31077,13 @@
     </row>
     <row r="289" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A289" s="25">
-        <v>90000703</v>
+        <v>90000607</v>
       </c>
       <c r="B289" s="25">
         <v>3</v>
       </c>
       <c r="C289" s="25" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D289" s="25"/>
       <c r="E289" s="26"/>
@@ -31072,16 +31101,16 @@
         <v>0</v>
       </c>
       <c r="K289" s="25" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="L289" s="27">
-        <v>800001031</v>
+        <v>800004031</v>
       </c>
       <c r="M289" s="25">
         <v>1</v>
       </c>
       <c r="N289" s="28">
-        <v>27</v>
+        <v>350</v>
       </c>
       <c r="O289" s="25">
         <v>1</v>
@@ -31152,13 +31181,13 @@
     </row>
     <row r="290" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A290" s="25">
-        <v>90000704</v>
+        <v>90000608</v>
       </c>
       <c r="B290" s="25">
         <v>3</v>
       </c>
       <c r="C290" s="25" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="D290" s="25"/>
       <c r="E290" s="26"/>
@@ -31176,16 +31205,16 @@
         <v>0</v>
       </c>
       <c r="K290" s="25" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="L290" s="27">
-        <v>800001031</v>
+        <v>800004031</v>
       </c>
       <c r="M290" s="25">
         <v>1</v>
       </c>
       <c r="N290" s="28">
-        <v>32</v>
+        <v>900</v>
       </c>
       <c r="O290" s="25">
         <v>1</v>
@@ -31256,13 +31285,13 @@
     </row>
     <row r="291" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A291" s="25">
-        <v>90000705</v>
+        <v>90000701</v>
       </c>
       <c r="B291" s="25">
         <v>3</v>
       </c>
       <c r="C291" s="25" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D291" s="25"/>
       <c r="E291" s="26"/>
@@ -31289,7 +31318,7 @@
         <v>1</v>
       </c>
       <c r="N291" s="28">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="O291" s="25">
         <v>1</v>
@@ -31360,13 +31389,13 @@
     </row>
     <row r="292" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A292" s="25">
-        <v>90000706</v>
+        <v>90000702</v>
       </c>
       <c r="B292" s="25">
         <v>3</v>
       </c>
       <c r="C292" s="25" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D292" s="25"/>
       <c r="E292" s="26"/>
@@ -31393,7 +31422,7 @@
         <v>1</v>
       </c>
       <c r="N292" s="28">
-        <v>135</v>
+        <v>18</v>
       </c>
       <c r="O292" s="25">
         <v>1</v>
@@ -31464,13 +31493,13 @@
     </row>
     <row r="293" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A293" s="25">
-        <v>90000707</v>
+        <v>90000703</v>
       </c>
       <c r="B293" s="25">
         <v>3</v>
       </c>
       <c r="C293" s="25" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D293" s="25"/>
       <c r="E293" s="26"/>
@@ -31497,7 +31526,7 @@
         <v>1</v>
       </c>
       <c r="N293" s="28">
-        <v>250</v>
+        <v>27</v>
       </c>
       <c r="O293" s="25">
         <v>1</v>
@@ -31568,13 +31597,13 @@
     </row>
     <row r="294" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A294" s="25">
-        <v>90000708</v>
+        <v>90000704</v>
       </c>
       <c r="B294" s="25">
         <v>3</v>
       </c>
       <c r="C294" s="25" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D294" s="25"/>
       <c r="E294" s="26"/>
@@ -31601,7 +31630,7 @@
         <v>1</v>
       </c>
       <c r="N294" s="28">
-        <v>450</v>
+        <v>32</v>
       </c>
       <c r="O294" s="25">
         <v>1</v>
@@ -31672,13 +31701,13 @@
     </row>
     <row r="295" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A295" s="25">
-        <v>90000709</v>
+        <v>90000705</v>
       </c>
       <c r="B295" s="25">
         <v>3</v>
       </c>
       <c r="C295" s="25" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D295" s="25"/>
       <c r="E295" s="26"/>
@@ -31705,7 +31734,7 @@
         <v>1</v>
       </c>
       <c r="N295" s="28">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="O295" s="25">
         <v>1</v>
@@ -31776,13 +31805,13 @@
     </row>
     <row r="296" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A296" s="25">
-        <v>90000710</v>
+        <v>90000706</v>
       </c>
       <c r="B296" s="25">
         <v>3</v>
       </c>
       <c r="C296" s="25" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="D296" s="25"/>
       <c r="E296" s="26"/>
@@ -31809,7 +31838,7 @@
         <v>1</v>
       </c>
       <c r="N296" s="28">
-        <v>1200</v>
+        <v>135</v>
       </c>
       <c r="O296" s="25">
         <v>1</v>
@@ -31880,13 +31909,13 @@
     </row>
     <row r="297" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A297" s="25">
-        <v>90000711</v>
+        <v>90000707</v>
       </c>
       <c r="B297" s="25">
         <v>3</v>
       </c>
       <c r="C297" s="25" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D297" s="25"/>
       <c r="E297" s="26"/>
@@ -31913,7 +31942,7 @@
         <v>1</v>
       </c>
       <c r="N297" s="28">
-        <v>1500</v>
+        <v>250</v>
       </c>
       <c r="O297" s="25">
         <v>1</v>
@@ -31984,13 +32013,13 @@
     </row>
     <row r="298" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A298" s="25">
-        <v>90000712</v>
+        <v>90000708</v>
       </c>
       <c r="B298" s="25">
         <v>3</v>
       </c>
       <c r="C298" s="25" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D298" s="25"/>
       <c r="E298" s="26"/>
@@ -32017,7 +32046,7 @@
         <v>1</v>
       </c>
       <c r="N298" s="28">
-        <v>3200</v>
+        <v>450</v>
       </c>
       <c r="O298" s="25">
         <v>1</v>
@@ -32088,13 +32117,13 @@
     </row>
     <row r="299" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A299" s="25">
-        <v>90000713</v>
+        <v>90000709</v>
       </c>
       <c r="B299" s="25">
         <v>3</v>
       </c>
       <c r="C299" s="25" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D299" s="25"/>
       <c r="E299" s="26"/>
@@ -32121,7 +32150,7 @@
         <v>1</v>
       </c>
       <c r="N299" s="28">
-        <v>3500</v>
+        <v>500</v>
       </c>
       <c r="O299" s="25">
         <v>1</v>
@@ -32192,13 +32221,13 @@
     </row>
     <row r="300" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A300" s="25">
-        <v>90000714</v>
+        <v>90000710</v>
       </c>
       <c r="B300" s="25">
         <v>3</v>
       </c>
       <c r="C300" s="25" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D300" s="25"/>
       <c r="E300" s="26"/>
@@ -32225,7 +32254,7 @@
         <v>1</v>
       </c>
       <c r="N300" s="28">
-        <v>11000</v>
+        <v>1200</v>
       </c>
       <c r="O300" s="25">
         <v>1</v>
@@ -32296,13 +32325,13 @@
     </row>
     <row r="301" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A301" s="25">
-        <v>90000715</v>
+        <v>90000711</v>
       </c>
       <c r="B301" s="25">
         <v>3</v>
       </c>
       <c r="C301" s="25" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="D301" s="25"/>
       <c r="E301" s="26"/>
@@ -32329,7 +32358,7 @@
         <v>1</v>
       </c>
       <c r="N301" s="28">
-        <v>12000</v>
+        <v>1500</v>
       </c>
       <c r="O301" s="25">
         <v>1</v>
@@ -32400,13 +32429,13 @@
     </row>
     <row r="302" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A302" s="25">
-        <v>90000716</v>
+        <v>90000712</v>
       </c>
       <c r="B302" s="25">
         <v>3</v>
       </c>
       <c r="C302" s="25" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="D302" s="25"/>
       <c r="E302" s="26"/>
@@ -32433,7 +32462,7 @@
         <v>1</v>
       </c>
       <c r="N302" s="28">
-        <v>22000</v>
+        <v>3200</v>
       </c>
       <c r="O302" s="25">
         <v>1</v>
@@ -32504,13 +32533,13 @@
     </row>
     <row r="303" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A303" s="25">
-        <v>90000717</v>
+        <v>90000713</v>
       </c>
       <c r="B303" s="25">
         <v>3</v>
       </c>
       <c r="C303" s="25" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D303" s="25"/>
       <c r="E303" s="26"/>
@@ -32537,7 +32566,7 @@
         <v>1</v>
       </c>
       <c r="N303" s="28">
-        <v>50000</v>
+        <v>3500</v>
       </c>
       <c r="O303" s="25">
         <v>1</v>
@@ -32608,13 +32637,13 @@
     </row>
     <row r="304" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A304" s="25">
-        <v>90000718</v>
+        <v>90000714</v>
       </c>
       <c r="B304" s="25">
         <v>3</v>
       </c>
       <c r="C304" s="25" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D304" s="25"/>
       <c r="E304" s="26"/>
@@ -32641,7 +32670,7 @@
         <v>1</v>
       </c>
       <c r="N304" s="28">
-        <v>70000</v>
+        <v>11000</v>
       </c>
       <c r="O304" s="25">
         <v>1</v>
@@ -32712,13 +32741,13 @@
     </row>
     <row r="305" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A305" s="25">
-        <v>90000719</v>
+        <v>90000715</v>
       </c>
       <c r="B305" s="25">
         <v>3</v>
       </c>
       <c r="C305" s="25" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D305" s="25"/>
       <c r="E305" s="26"/>
@@ -32745,7 +32774,7 @@
         <v>1</v>
       </c>
       <c r="N305" s="28">
-        <v>120000</v>
+        <v>12000</v>
       </c>
       <c r="O305" s="25">
         <v>1</v>
@@ -32811,6 +32840,422 @@
         <v>0</v>
       </c>
       <c r="AJ305" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A306" s="25">
+        <v>90000716</v>
+      </c>
+      <c r="B306" s="25">
+        <v>3</v>
+      </c>
+      <c r="C306" s="25" t="s">
+        <v>205</v>
+      </c>
+      <c r="D306" s="25"/>
+      <c r="E306" s="26"/>
+      <c r="F306" s="25"/>
+      <c r="G306" s="25">
+        <v>1</v>
+      </c>
+      <c r="H306" s="25">
+        <v>2</v>
+      </c>
+      <c r="I306" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="J306" s="25">
+        <v>0</v>
+      </c>
+      <c r="K306" s="25" t="s">
+        <v>168</v>
+      </c>
+      <c r="L306" s="27">
+        <v>800001031</v>
+      </c>
+      <c r="M306" s="25">
+        <v>1</v>
+      </c>
+      <c r="N306" s="28">
+        <v>22000</v>
+      </c>
+      <c r="O306" s="25">
+        <v>1</v>
+      </c>
+      <c r="P306" s="25">
+        <v>8</v>
+      </c>
+      <c r="Q306" s="25">
+        <v>0</v>
+      </c>
+      <c r="R306" s="25">
+        <v>25</v>
+      </c>
+      <c r="S306" s="25">
+        <v>-5000</v>
+      </c>
+      <c r="T306" s="25">
+        <v>1</v>
+      </c>
+      <c r="U306" s="25">
+        <v>0</v>
+      </c>
+      <c r="V306" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="W306" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="X306" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y306" s="30">
+        <v>20010001</v>
+      </c>
+      <c r="Z306" s="30">
+        <v>0</v>
+      </c>
+      <c r="AA306" s="25">
+        <v>1</v>
+      </c>
+      <c r="AB306" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC306" s="25">
+        <v>10000</v>
+      </c>
+      <c r="AD306" s="25">
+        <v>10000</v>
+      </c>
+      <c r="AE306" s="25">
+        <v>0</v>
+      </c>
+      <c r="AF306" s="31">
+        <v>40</v>
+      </c>
+      <c r="AG306" s="31">
+        <v>0</v>
+      </c>
+      <c r="AH306" s="31">
+        <v>0</v>
+      </c>
+      <c r="AI306" s="31">
+        <v>0</v>
+      </c>
+      <c r="AJ306" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A307" s="25">
+        <v>90000717</v>
+      </c>
+      <c r="B307" s="25">
+        <v>3</v>
+      </c>
+      <c r="C307" s="25" t="s">
+        <v>206</v>
+      </c>
+      <c r="D307" s="25"/>
+      <c r="E307" s="26"/>
+      <c r="F307" s="25"/>
+      <c r="G307" s="25">
+        <v>1</v>
+      </c>
+      <c r="H307" s="25">
+        <v>2</v>
+      </c>
+      <c r="I307" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="J307" s="25">
+        <v>0</v>
+      </c>
+      <c r="K307" s="25" t="s">
+        <v>168</v>
+      </c>
+      <c r="L307" s="27">
+        <v>800001031</v>
+      </c>
+      <c r="M307" s="25">
+        <v>1</v>
+      </c>
+      <c r="N307" s="28">
+        <v>50000</v>
+      </c>
+      <c r="O307" s="25">
+        <v>1</v>
+      </c>
+      <c r="P307" s="25">
+        <v>8</v>
+      </c>
+      <c r="Q307" s="25">
+        <v>0</v>
+      </c>
+      <c r="R307" s="25">
+        <v>25</v>
+      </c>
+      <c r="S307" s="25">
+        <v>-5000</v>
+      </c>
+      <c r="T307" s="25">
+        <v>1</v>
+      </c>
+      <c r="U307" s="25">
+        <v>0</v>
+      </c>
+      <c r="V307" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="W307" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="X307" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y307" s="30">
+        <v>20010001</v>
+      </c>
+      <c r="Z307" s="30">
+        <v>0</v>
+      </c>
+      <c r="AA307" s="25">
+        <v>1</v>
+      </c>
+      <c r="AB307" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC307" s="25">
+        <v>10000</v>
+      </c>
+      <c r="AD307" s="25">
+        <v>10000</v>
+      </c>
+      <c r="AE307" s="25">
+        <v>0</v>
+      </c>
+      <c r="AF307" s="31">
+        <v>40</v>
+      </c>
+      <c r="AG307" s="31">
+        <v>0</v>
+      </c>
+      <c r="AH307" s="31">
+        <v>0</v>
+      </c>
+      <c r="AI307" s="31">
+        <v>0</v>
+      </c>
+      <c r="AJ307" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A308" s="25">
+        <v>90000718</v>
+      </c>
+      <c r="B308" s="25">
+        <v>3</v>
+      </c>
+      <c r="C308" s="25" t="s">
+        <v>207</v>
+      </c>
+      <c r="D308" s="25"/>
+      <c r="E308" s="26"/>
+      <c r="F308" s="25"/>
+      <c r="G308" s="25">
+        <v>1</v>
+      </c>
+      <c r="H308" s="25">
+        <v>2</v>
+      </c>
+      <c r="I308" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="J308" s="25">
+        <v>0</v>
+      </c>
+      <c r="K308" s="25" t="s">
+        <v>168</v>
+      </c>
+      <c r="L308" s="27">
+        <v>800001031</v>
+      </c>
+      <c r="M308" s="25">
+        <v>1</v>
+      </c>
+      <c r="N308" s="28">
+        <v>70000</v>
+      </c>
+      <c r="O308" s="25">
+        <v>1</v>
+      </c>
+      <c r="P308" s="25">
+        <v>8</v>
+      </c>
+      <c r="Q308" s="25">
+        <v>0</v>
+      </c>
+      <c r="R308" s="25">
+        <v>25</v>
+      </c>
+      <c r="S308" s="25">
+        <v>-5000</v>
+      </c>
+      <c r="T308" s="25">
+        <v>1</v>
+      </c>
+      <c r="U308" s="25">
+        <v>0</v>
+      </c>
+      <c r="V308" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="W308" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="X308" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y308" s="30">
+        <v>20010001</v>
+      </c>
+      <c r="Z308" s="30">
+        <v>0</v>
+      </c>
+      <c r="AA308" s="25">
+        <v>1</v>
+      </c>
+      <c r="AB308" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC308" s="25">
+        <v>10000</v>
+      </c>
+      <c r="AD308" s="25">
+        <v>10000</v>
+      </c>
+      <c r="AE308" s="25">
+        <v>0</v>
+      </c>
+      <c r="AF308" s="31">
+        <v>40</v>
+      </c>
+      <c r="AG308" s="31">
+        <v>0</v>
+      </c>
+      <c r="AH308" s="31">
+        <v>0</v>
+      </c>
+      <c r="AI308" s="31">
+        <v>0</v>
+      </c>
+      <c r="AJ308" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309" spans="1:36" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A309" s="25">
+        <v>90000719</v>
+      </c>
+      <c r="B309" s="25">
+        <v>3</v>
+      </c>
+      <c r="C309" s="25" t="s">
+        <v>208</v>
+      </c>
+      <c r="D309" s="25"/>
+      <c r="E309" s="26"/>
+      <c r="F309" s="25"/>
+      <c r="G309" s="25">
+        <v>1</v>
+      </c>
+      <c r="H309" s="25">
+        <v>2</v>
+      </c>
+      <c r="I309" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="J309" s="25">
+        <v>0</v>
+      </c>
+      <c r="K309" s="25" t="s">
+        <v>168</v>
+      </c>
+      <c r="L309" s="27">
+        <v>800001031</v>
+      </c>
+      <c r="M309" s="25">
+        <v>1</v>
+      </c>
+      <c r="N309" s="28">
+        <v>120000</v>
+      </c>
+      <c r="O309" s="25">
+        <v>1</v>
+      </c>
+      <c r="P309" s="25">
+        <v>8</v>
+      </c>
+      <c r="Q309" s="25">
+        <v>0</v>
+      </c>
+      <c r="R309" s="25">
+        <v>25</v>
+      </c>
+      <c r="S309" s="25">
+        <v>-5000</v>
+      </c>
+      <c r="T309" s="25">
+        <v>1</v>
+      </c>
+      <c r="U309" s="25">
+        <v>0</v>
+      </c>
+      <c r="V309" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="W309" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="X309" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y309" s="30">
+        <v>20010001</v>
+      </c>
+      <c r="Z309" s="30">
+        <v>0</v>
+      </c>
+      <c r="AA309" s="25">
+        <v>1</v>
+      </c>
+      <c r="AB309" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC309" s="25">
+        <v>10000</v>
+      </c>
+      <c r="AD309" s="25">
+        <v>10000</v>
+      </c>
+      <c r="AE309" s="25">
+        <v>0</v>
+      </c>
+      <c r="AF309" s="31">
+        <v>40</v>
+      </c>
+      <c r="AG309" s="31">
+        <v>0</v>
+      </c>
+      <c r="AH309" s="31">
+        <v>0</v>
+      </c>
+      <c r="AI309" s="31">
+        <v>0</v>
+      </c>
+      <c r="AJ309" s="31">
         <v>0</v>
       </c>
     </row>
@@ -32819,8 +33264,8 @@
     <sortCondition ref="A5:A211"/>
   </sortState>
   <phoneticPr fontId="13" type="noConversion"/>
-  <conditionalFormatting sqref="A1:A211 A221:A1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="33"/>
+  <conditionalFormatting sqref="A1:A211 A225:A1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="34"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{193C1193-258F-42A2-9833-63E40747C0DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64595629-ADAF-42E2-B248-C7C801767B4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_foe_v8" sheetId="1" r:id="rId1"/>
@@ -1015,7 +1015,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1104,6 +1104,27 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="5" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -29368,104 +29389,104 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A279" s="24">
+    <row r="279" spans="1:33" s="38" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A279" s="32">
         <v>90000501</v>
       </c>
-      <c r="B279" s="24">
+      <c r="B279" s="32">
         <v>3</v>
       </c>
-      <c r="C279" s="24" t="s">
+      <c r="C279" s="32" t="s">
         <v>172</v>
       </c>
-      <c r="D279" s="24">
-        <v>1</v>
-      </c>
-      <c r="E279" s="24">
+      <c r="D279" s="32">
+        <v>1</v>
+      </c>
+      <c r="E279" s="32">
         <v>2</v>
       </c>
-      <c r="F279" s="31" t="s">
+      <c r="F279" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="G279" s="24">
-        <v>0</v>
-      </c>
-      <c r="H279" s="24" t="s">
+      <c r="G279" s="32">
+        <v>0</v>
+      </c>
+      <c r="H279" s="32" t="s">
         <v>162</v>
       </c>
-      <c r="I279" s="25">
+      <c r="I279" s="34">
         <v>800001031</v>
       </c>
-      <c r="J279" s="24">
-        <v>1</v>
-      </c>
-      <c r="K279" s="26">
+      <c r="J279" s="32">
+        <v>1</v>
+      </c>
+      <c r="K279" s="35">
         <v>8</v>
       </c>
-      <c r="L279" s="24">
-        <v>1</v>
-      </c>
-      <c r="M279" s="24">
+      <c r="L279" s="32">
+        <v>1</v>
+      </c>
+      <c r="M279" s="32">
         <v>8</v>
       </c>
-      <c r="N279" s="24">
-        <v>0</v>
-      </c>
-      <c r="O279" s="24">
+      <c r="N279" s="32">
+        <v>0</v>
+      </c>
+      <c r="O279" s="32">
         <v>25</v>
       </c>
-      <c r="P279" s="24">
+      <c r="P279" s="32">
         <v>-5000</v>
       </c>
-      <c r="Q279" s="24">
-        <v>1</v>
-      </c>
-      <c r="R279" s="24">
-        <v>0</v>
-      </c>
-      <c r="S279" s="24" t="s">
+      <c r="Q279" s="32">
+        <v>1</v>
+      </c>
+      <c r="R279" s="32">
+        <v>0</v>
+      </c>
+      <c r="S279" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="T279" s="24" t="s">
+      <c r="T279" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="U279" s="24" t="s">
+      <c r="U279" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="V279" s="28">
+      <c r="V279" s="36">
         <v>20010001</v>
       </c>
-      <c r="W279" s="28">
-        <v>0</v>
-      </c>
-      <c r="X279" s="24">
-        <v>1</v>
-      </c>
-      <c r="Y279" s="29" t="s">
+      <c r="W279" s="36">
+        <v>0</v>
+      </c>
+      <c r="X279" s="32">
+        <v>1</v>
+      </c>
+      <c r="Y279" s="37" t="s">
         <v>77</v>
       </c>
-      <c r="Z279" s="24">
-        <v>10000</v>
-      </c>
-      <c r="AA279" s="24">
-        <v>10000</v>
-      </c>
-      <c r="AB279" s="24">
-        <v>0</v>
-      </c>
-      <c r="AC279" s="29">
+      <c r="Z279" s="32">
+        <v>10000</v>
+      </c>
+      <c r="AA279" s="32">
+        <v>10000</v>
+      </c>
+      <c r="AB279" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC279" s="37">
         <v>40</v>
       </c>
-      <c r="AD279" s="29">
-        <v>0</v>
-      </c>
-      <c r="AE279" s="29">
-        <v>0</v>
-      </c>
-      <c r="AF279" s="29">
-        <v>0</v>
-      </c>
-      <c r="AG279" s="29">
+      <c r="AD279" s="37">
+        <v>0</v>
+      </c>
+      <c r="AE279" s="37">
+        <v>0</v>
+      </c>
+      <c r="AF279" s="37">
+        <v>0</v>
+      </c>
+      <c r="AG279" s="37">
         <v>0</v>
       </c>
     </row>
@@ -29501,7 +29522,7 @@
         <v>1</v>
       </c>
       <c r="K280" s="26">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L280" s="24">
         <v>1</v>
@@ -29602,7 +29623,7 @@
         <v>1</v>
       </c>
       <c r="K281" s="26">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="L281" s="24">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F914FEDC-D57A-4859-B4A1-73145DC318FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05F53AA1-94A2-43D4-B6DB-494E4BF8E24B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6450,7 +6450,7 @@
         <v>1</v>
       </c>
       <c r="O48" s="3">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="P48" s="3">
         <v>-5500</v>
@@ -6507,7 +6507,7 @@
         <v>10000</v>
       </c>
       <c r="AH48" s="9">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AI48" s="9">
         <v>0</v>
@@ -6557,7 +6557,7 @@
         <v>1</v>
       </c>
       <c r="O49" s="3">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="P49" s="3">
         <v>-5500</v>
@@ -6614,7 +6614,7 @@
         <v>10000</v>
       </c>
       <c r="AH49" s="9">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="AI49" s="9">
         <v>0</v>
@@ -6771,7 +6771,7 @@
         <v>1</v>
       </c>
       <c r="O51" s="3">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="P51" s="3">
         <v>-5500</v>
@@ -6828,7 +6828,7 @@
         <v>10000</v>
       </c>
       <c r="AH51" s="9">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="AI51" s="9">
         <v>0</v>
@@ -6878,7 +6878,7 @@
         <v>2</v>
       </c>
       <c r="O52" s="13">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="P52" s="13">
         <v>-5500</v>
@@ -6935,7 +6935,7 @@
         <v>10000</v>
       </c>
       <c r="AH52" s="8">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="AI52" s="8">
         <v>0</v>
@@ -7092,7 +7092,7 @@
         <v>3</v>
       </c>
       <c r="O54" s="3">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="P54" s="3">
         <v>-5500</v>
@@ -7149,7 +7149,7 @@
         <v>10000</v>
       </c>
       <c r="AH54" s="9">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="AI54" s="9">
         <v>0</v>
@@ -7199,7 +7199,7 @@
         <v>4</v>
       </c>
       <c r="O55" s="3">
-        <v>714</v>
+        <v>748</v>
       </c>
       <c r="P55" s="3">
         <v>-5500</v>
@@ -7256,7 +7256,7 @@
         <v>10000</v>
       </c>
       <c r="AH55" s="9">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AI55" s="9">
         <v>0</v>
@@ -7413,7 +7413,7 @@
         <v>5</v>
       </c>
       <c r="O57" s="3">
-        <v>338</v>
+        <v>360</v>
       </c>
       <c r="P57" s="3">
         <v>-5500</v>
@@ -7470,7 +7470,7 @@
         <v>10000</v>
       </c>
       <c r="AH57" s="9">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="AI57" s="9">
         <v>0</v>
@@ -7520,7 +7520,7 @@
         <v>8</v>
       </c>
       <c r="O58" s="13">
-        <v>1420</v>
+        <v>1488</v>
       </c>
       <c r="P58" s="13">
         <v>-5500</v>
@@ -7577,7 +7577,7 @@
         <v>10000</v>
       </c>
       <c r="AH58" s="8">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AI58" s="8">
         <v>0</v>
@@ -7734,7 +7734,7 @@
         <v>9</v>
       </c>
       <c r="O60" s="3">
-        <v>543</v>
+        <v>580</v>
       </c>
       <c r="P60" s="3">
         <v>-5500</v>
@@ -7791,7 +7791,7 @@
         <v>10000</v>
       </c>
       <c r="AH60" s="9">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="AI60" s="9">
         <v>0</v>
@@ -7841,7 +7841,7 @@
         <v>12</v>
       </c>
       <c r="O61" s="3">
-        <v>2193</v>
+        <v>2297</v>
       </c>
       <c r="P61" s="3">
         <v>-5500</v>
@@ -7898,7 +7898,7 @@
         <v>10000</v>
       </c>
       <c r="AH61" s="9">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AI61" s="9">
         <v>0</v>
@@ -7948,7 +7948,7 @@
         <v>4</v>
       </c>
       <c r="O62" s="13">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="P62" s="13">
         <v>-5500</v>
@@ -8005,7 +8005,7 @@
         <v>10000</v>
       </c>
       <c r="AH62" s="8">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AI62" s="8">
         <v>10</v>
@@ -8055,7 +8055,7 @@
         <v>8</v>
       </c>
       <c r="O63" s="3">
-        <v>1373</v>
+        <v>1344</v>
       </c>
       <c r="P63" s="3">
         <v>-5500</v>
@@ -8162,7 +8162,7 @@
         <v>9</v>
       </c>
       <c r="O64" s="3">
-        <v>2334</v>
+        <v>2424</v>
       </c>
       <c r="P64" s="3">
         <v>-5500</v>
@@ -8219,7 +8219,7 @@
         <v>10000</v>
       </c>
       <c r="AH64" s="9">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI64" s="9">
         <v>0</v>
@@ -8269,7 +8269,7 @@
         <v>13</v>
       </c>
       <c r="O65" s="3">
-        <v>7756</v>
+        <v>8919</v>
       </c>
       <c r="P65" s="3">
         <v>-5500</v>
@@ -8326,7 +8326,7 @@
         <v>10000</v>
       </c>
       <c r="AH65" s="9">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AI65" s="9">
         <v>0</v>
@@ -8376,7 +8376,7 @@
         <v>4</v>
       </c>
       <c r="O66" s="3">
-        <v>1044</v>
+        <v>1022</v>
       </c>
       <c r="P66" s="3">
         <v>-5500</v>
@@ -8590,7 +8590,7 @@
         <v>14</v>
       </c>
       <c r="O68" s="13">
-        <v>891</v>
+        <v>950</v>
       </c>
       <c r="P68" s="13">
         <v>-5500</v>
@@ -8647,7 +8647,7 @@
         <v>10000</v>
       </c>
       <c r="AH68" s="8">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="AI68" s="8">
         <v>0</v>
@@ -8697,7 +8697,7 @@
         <v>21</v>
       </c>
       <c r="O69" s="3">
-        <v>3730</v>
+        <v>3907</v>
       </c>
       <c r="P69" s="3">
         <v>-5500</v>
@@ -8754,7 +8754,7 @@
         <v>10000</v>
       </c>
       <c r="AH69" s="9">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="AI69" s="9">
         <v>0</v>
@@ -8804,7 +8804,7 @@
         <v>6</v>
       </c>
       <c r="O70" s="3">
-        <v>347</v>
+        <v>375</v>
       </c>
       <c r="P70" s="3">
         <v>-5500</v>
@@ -8861,7 +8861,7 @@
         <v>10000</v>
       </c>
       <c r="AH70" s="9">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AI70" s="9">
         <v>10</v>
@@ -8911,7 +8911,7 @@
         <v>13</v>
       </c>
       <c r="O71" s="3">
-        <v>2064</v>
+        <v>2021</v>
       </c>
       <c r="P71" s="3">
         <v>-5500</v>
@@ -9018,7 +9018,7 @@
         <v>14</v>
       </c>
       <c r="O72" s="3">
-        <v>3514</v>
+        <v>3649</v>
       </c>
       <c r="P72" s="3">
         <v>-5500</v>
@@ -9075,7 +9075,7 @@
         <v>10000</v>
       </c>
       <c r="AH72" s="9">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI72" s="9">
         <v>0</v>
@@ -9125,7 +9125,7 @@
         <v>21</v>
       </c>
       <c r="O73" s="3">
-        <v>12154</v>
+        <v>13977</v>
       </c>
       <c r="P73" s="3">
         <v>-5500</v>
@@ -9182,7 +9182,7 @@
         <v>10000</v>
       </c>
       <c r="AH73" s="9">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AI73" s="9">
         <v>0</v>
@@ -9232,7 +9232,7 @@
         <v>6</v>
       </c>
       <c r="O74" s="3">
-        <v>1573</v>
+        <v>1540</v>
       </c>
       <c r="P74" s="3">
         <v>-5500</v>
@@ -9446,7 +9446,7 @@
         <v>24</v>
       </c>
       <c r="O76" s="3">
-        <v>1452</v>
+        <v>1548</v>
       </c>
       <c r="P76" s="3">
         <v>-5500</v>
@@ -9503,7 +9503,7 @@
         <v>10000</v>
       </c>
       <c r="AH76" s="9">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AI76" s="9">
         <v>0</v>
@@ -9553,7 +9553,7 @@
         <v>29</v>
       </c>
       <c r="O77" s="3">
-        <v>5371</v>
+        <v>5627</v>
       </c>
       <c r="P77" s="3">
         <v>-5500</v>
@@ -9610,7 +9610,7 @@
         <v>10000</v>
       </c>
       <c r="AH77" s="9">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AI77" s="9">
         <v>0</v>
@@ -9660,7 +9660,7 @@
         <v>10</v>
       </c>
       <c r="O78" s="3">
-        <v>587</v>
+        <v>635</v>
       </c>
       <c r="P78" s="3">
         <v>-5500</v>
@@ -9717,7 +9717,7 @@
         <v>10000</v>
       </c>
       <c r="AH78" s="9">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI78" s="9">
         <v>10</v>
@@ -9767,7 +9767,7 @@
         <v>19</v>
       </c>
       <c r="O79" s="3">
-        <v>2942</v>
+        <v>2881</v>
       </c>
       <c r="P79" s="3">
         <v>-5500</v>
@@ -9874,7 +9874,7 @@
         <v>24</v>
       </c>
       <c r="O80" s="3">
-        <v>5454</v>
+        <v>5664</v>
       </c>
       <c r="P80" s="3">
         <v>-5500</v>
@@ -9981,7 +9981,7 @@
         <v>29</v>
       </c>
       <c r="O81" s="3">
-        <v>16643</v>
+        <v>19139</v>
       </c>
       <c r="P81" s="3">
         <v>-5500</v>
@@ -10038,7 +10038,7 @@
         <v>10000</v>
       </c>
       <c r="AH81" s="9">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AI81" s="9">
         <v>0</v>
@@ -10088,7 +10088,7 @@
         <v>10</v>
       </c>
       <c r="O82" s="3">
-        <v>2538</v>
+        <v>2485</v>
       </c>
       <c r="P82" s="3">
         <v>-5500</v>
@@ -10145,7 +10145,7 @@
         <v>10000</v>
       </c>
       <c r="AH82" s="9">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI82" s="9">
         <v>10</v>
@@ -10195,7 +10195,7 @@
         <v>19</v>
       </c>
       <c r="O83" s="3">
-        <v>5394</v>
+        <v>8092</v>
       </c>
       <c r="P83" s="3">
         <v>-5500</v>
@@ -10252,7 +10252,7 @@
         <v>10000</v>
       </c>
       <c r="AH83" s="9">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AI83" s="9">
         <v>0</v>
@@ -10302,7 +10302,7 @@
         <v>24</v>
       </c>
       <c r="O84" s="3">
-        <v>9229</v>
+        <v>13844</v>
       </c>
       <c r="P84" s="3">
         <v>-5500</v>
@@ -10359,7 +10359,7 @@
         <v>10000</v>
       </c>
       <c r="AH84" s="9">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AI84" s="9">
         <v>0</v>
@@ -10409,7 +10409,7 @@
         <v>29</v>
       </c>
       <c r="O85" s="3">
-        <v>24409</v>
+        <v>36614</v>
       </c>
       <c r="P85" s="3">
         <v>-5500</v>
@@ -10466,7 +10466,7 @@
         <v>10000</v>
       </c>
       <c r="AH85" s="9">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AI85" s="9">
         <v>0</v>
@@ -10516,7 +10516,7 @@
         <v>10</v>
       </c>
       <c r="O86" s="3">
-        <v>4653</v>
+        <v>6979</v>
       </c>
       <c r="P86" s="3">
         <v>-5500</v>
@@ -10573,7 +10573,7 @@
         <v>10000</v>
       </c>
       <c r="AH86" s="9">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AI86" s="9">
         <v>10</v>
@@ -10623,7 +10623,7 @@
         <v>77</v>
       </c>
       <c r="O87" s="3">
-        <v>98901</v>
+        <v>148352</v>
       </c>
       <c r="P87" s="3">
         <v>-5500</v>
@@ -10680,7 +10680,7 @@
         <v>10000</v>
       </c>
       <c r="AH87" s="9">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AI87" s="9">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05F53AA1-94A2-43D4-B6DB-494E4BF8E24B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D082CA1A-D22F-40F4-83BF-0621319924D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6337,7 +6337,7 @@
         <v>0</v>
       </c>
       <c r="M47" s="13">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N47" s="13">
         <v>1</v>
@@ -6400,7 +6400,7 @@
         <v>10000</v>
       </c>
       <c r="AH47" s="8">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="AI47" s="8">
         <v>0</v>
@@ -6444,7 +6444,7 @@
         <v>0</v>
       </c>
       <c r="M48" s="3">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N48" s="3">
         <v>1</v>
@@ -6507,7 +6507,7 @@
         <v>10000</v>
       </c>
       <c r="AH48" s="9">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AI48" s="9">
         <v>0</v>
@@ -6551,7 +6551,7 @@
         <v>0</v>
       </c>
       <c r="M49" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N49" s="3">
         <v>1</v>
@@ -6614,7 +6614,7 @@
         <v>10000</v>
       </c>
       <c r="AH49" s="9">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="AI49" s="9">
         <v>0</v>
@@ -6658,7 +6658,7 @@
         <v>0</v>
       </c>
       <c r="M50" s="3">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N50" s="3">
         <v>1</v>
@@ -6721,7 +6721,7 @@
         <v>10000</v>
       </c>
       <c r="AH50" s="9">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="AI50" s="9">
         <v>0</v>
@@ -6765,7 +6765,7 @@
         <v>0</v>
       </c>
       <c r="M51" s="3">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N51" s="3">
         <v>1</v>
@@ -6828,7 +6828,7 @@
         <v>10000</v>
       </c>
       <c r="AH51" s="9">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="AI51" s="9">
         <v>0</v>
@@ -6872,7 +6872,7 @@
         <v>0</v>
       </c>
       <c r="M52" s="13">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N52" s="13">
         <v>2</v>
@@ -6935,7 +6935,7 @@
         <v>10000</v>
       </c>
       <c r="AH52" s="8">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="AI52" s="8">
         <v>0</v>
@@ -6979,7 +6979,7 @@
         <v>0</v>
       </c>
       <c r="M53" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="N53" s="3">
         <v>3</v>
@@ -7042,7 +7042,7 @@
         <v>10000</v>
       </c>
       <c r="AH53" s="9">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="AI53" s="9">
         <v>0</v>
@@ -7086,7 +7086,7 @@
         <v>0</v>
       </c>
       <c r="M54" s="3">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N54" s="3">
         <v>3</v>
@@ -7149,7 +7149,7 @@
         <v>10000</v>
       </c>
       <c r="AH54" s="9">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="AI54" s="9">
         <v>0</v>
@@ -7193,7 +7193,7 @@
         <v>0</v>
       </c>
       <c r="M55" s="3">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="N55" s="3">
         <v>4</v>
@@ -7256,7 +7256,7 @@
         <v>10000</v>
       </c>
       <c r="AH55" s="9">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="AI55" s="9">
         <v>0</v>
@@ -7300,7 +7300,7 @@
         <v>0</v>
       </c>
       <c r="M56" s="3">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="N56" s="3">
         <v>6</v>
@@ -7363,7 +7363,7 @@
         <v>10000</v>
       </c>
       <c r="AH56" s="9">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="AI56" s="9">
         <v>0</v>
@@ -7407,7 +7407,7 @@
         <v>0</v>
       </c>
       <c r="M57" s="3">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="N57" s="3">
         <v>5</v>
@@ -7470,7 +7470,7 @@
         <v>10000</v>
       </c>
       <c r="AH57" s="9">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="AI57" s="9">
         <v>0</v>
@@ -7514,7 +7514,7 @@
         <v>0</v>
       </c>
       <c r="M58" s="13">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="N58" s="13">
         <v>8</v>
@@ -7577,7 +7577,7 @@
         <v>10000</v>
       </c>
       <c r="AH58" s="8">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AI58" s="8">
         <v>0</v>
@@ -7621,7 +7621,7 @@
         <v>0</v>
       </c>
       <c r="M59" s="3">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="N59" s="3">
         <v>8</v>
@@ -7684,7 +7684,7 @@
         <v>10000</v>
       </c>
       <c r="AH59" s="9">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="AI59" s="9">
         <v>0</v>
@@ -7728,7 +7728,7 @@
         <v>0</v>
       </c>
       <c r="M60" s="3">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="N60" s="3">
         <v>9</v>
@@ -7791,7 +7791,7 @@
         <v>10000</v>
       </c>
       <c r="AH60" s="9">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="AI60" s="9">
         <v>0</v>
@@ -7835,7 +7835,7 @@
         <v>0</v>
       </c>
       <c r="M61" s="3">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="N61" s="3">
         <v>12</v>
@@ -7898,7 +7898,7 @@
         <v>10000</v>
       </c>
       <c r="AH61" s="9">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AI61" s="9">
         <v>0</v>
@@ -7942,7 +7942,7 @@
         <v>0</v>
       </c>
       <c r="M62" s="13">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="N62" s="13">
         <v>4</v>
@@ -8005,7 +8005,7 @@
         <v>10000</v>
       </c>
       <c r="AH62" s="8">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="AI62" s="8">
         <v>10</v>
@@ -8049,7 +8049,7 @@
         <v>0</v>
       </c>
       <c r="M63" s="3">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="N63" s="3">
         <v>8</v>
@@ -8112,7 +8112,7 @@
         <v>10000</v>
       </c>
       <c r="AH63" s="9">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI63" s="9">
         <v>0</v>
@@ -8156,7 +8156,7 @@
         <v>0</v>
       </c>
       <c r="M64" s="3">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="N64" s="3">
         <v>9</v>
@@ -8219,7 +8219,7 @@
         <v>10000</v>
       </c>
       <c r="AH64" s="9">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AI64" s="9">
         <v>0</v>
@@ -8263,7 +8263,7 @@
         <v>0</v>
       </c>
       <c r="M65" s="3">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="N65" s="3">
         <v>13</v>
@@ -8326,7 +8326,7 @@
         <v>10000</v>
       </c>
       <c r="AH65" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI65" s="9">
         <v>0</v>
@@ -8370,7 +8370,7 @@
         <v>0</v>
       </c>
       <c r="M66" s="3">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="N66" s="3">
         <v>4</v>
@@ -8433,7 +8433,7 @@
         <v>10000</v>
       </c>
       <c r="AH66" s="9">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI66" s="9">
         <v>10</v>
@@ -8477,7 +8477,7 @@
         <v>0</v>
       </c>
       <c r="M67" s="13">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="N67" s="13">
         <v>13</v>
@@ -8540,7 +8540,7 @@
         <v>10000</v>
       </c>
       <c r="AH67" s="8">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="AI67" s="8">
         <v>0</v>
@@ -8584,7 +8584,7 @@
         <v>0</v>
       </c>
       <c r="M68" s="13">
-        <v>262</v>
+        <v>236</v>
       </c>
       <c r="N68" s="13">
         <v>14</v>
@@ -8647,7 +8647,7 @@
         <v>10000</v>
       </c>
       <c r="AH68" s="8">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="AI68" s="8">
         <v>0</v>
@@ -8691,7 +8691,7 @@
         <v>0</v>
       </c>
       <c r="M69" s="3">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="N69" s="3">
         <v>21</v>
@@ -8754,7 +8754,7 @@
         <v>10000</v>
       </c>
       <c r="AH69" s="9">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="AI69" s="9">
         <v>0</v>
@@ -8798,7 +8798,7 @@
         <v>0</v>
       </c>
       <c r="M70" s="3">
-        <v>256</v>
+        <v>234</v>
       </c>
       <c r="N70" s="3">
         <v>6</v>
@@ -8861,7 +8861,7 @@
         <v>10000</v>
       </c>
       <c r="AH70" s="9">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="AI70" s="9">
         <v>10</v>
@@ -8905,7 +8905,7 @@
         <v>0</v>
       </c>
       <c r="M71" s="3">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="N71" s="3">
         <v>13</v>
@@ -8968,7 +8968,7 @@
         <v>10000</v>
       </c>
       <c r="AH71" s="9">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI71" s="9">
         <v>0</v>
@@ -9012,7 +9012,7 @@
         <v>0</v>
       </c>
       <c r="M72" s="3">
-        <v>269</v>
+        <v>242</v>
       </c>
       <c r="N72" s="3">
         <v>14</v>
@@ -9075,7 +9075,7 @@
         <v>10000</v>
       </c>
       <c r="AH72" s="9">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AI72" s="9">
         <v>0</v>
@@ -9119,7 +9119,7 @@
         <v>0</v>
       </c>
       <c r="M73" s="3">
-        <v>230</v>
+        <v>212</v>
       </c>
       <c r="N73" s="3">
         <v>21</v>
@@ -9182,7 +9182,7 @@
         <v>10000</v>
       </c>
       <c r="AH73" s="9">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AI73" s="9">
         <v>0</v>
@@ -9226,7 +9226,7 @@
         <v>0</v>
       </c>
       <c r="M74" s="3">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="N74" s="3">
         <v>6</v>
@@ -9289,7 +9289,7 @@
         <v>10000</v>
       </c>
       <c r="AH74" s="9">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI74" s="9">
         <v>10</v>
@@ -9333,7 +9333,7 @@
         <v>0</v>
       </c>
       <c r="M75" s="3">
-        <v>296</v>
+        <v>270</v>
       </c>
       <c r="N75" s="3">
         <v>19</v>
@@ -9396,7 +9396,7 @@
         <v>10000</v>
       </c>
       <c r="AH75" s="9">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="AI75" s="9">
         <v>0</v>
@@ -9440,7 +9440,7 @@
         <v>0</v>
       </c>
       <c r="M76" s="3">
-        <v>348</v>
+        <v>314</v>
       </c>
       <c r="N76" s="3">
         <v>24</v>
@@ -9503,7 +9503,7 @@
         <v>10000</v>
       </c>
       <c r="AH76" s="9">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AI76" s="9">
         <v>0</v>
@@ -9547,7 +9547,7 @@
         <v>0</v>
       </c>
       <c r="M77" s="3">
-        <v>362</v>
+        <v>333</v>
       </c>
       <c r="N77" s="3">
         <v>29</v>
@@ -9610,7 +9610,7 @@
         <v>10000</v>
       </c>
       <c r="AH77" s="9">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AI77" s="9">
         <v>0</v>
@@ -9654,7 +9654,7 @@
         <v>0</v>
       </c>
       <c r="M78" s="3">
-        <v>418</v>
+        <v>379</v>
       </c>
       <c r="N78" s="3">
         <v>10</v>
@@ -9717,7 +9717,7 @@
         <v>10000</v>
       </c>
       <c r="AH78" s="9">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="AI78" s="9">
         <v>10</v>
@@ -9761,7 +9761,7 @@
         <v>0</v>
       </c>
       <c r="M79" s="3">
-        <v>303</v>
+        <v>276</v>
       </c>
       <c r="N79" s="3">
         <v>19</v>
@@ -9824,7 +9824,7 @@
         <v>10000</v>
       </c>
       <c r="AH79" s="9">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI79" s="9">
         <v>0</v>
@@ -9868,7 +9868,7 @@
         <v>0</v>
       </c>
       <c r="M80" s="3">
-        <v>357</v>
+        <v>322</v>
       </c>
       <c r="N80" s="3">
         <v>24</v>
@@ -9931,7 +9931,7 @@
         <v>10000</v>
       </c>
       <c r="AH80" s="9">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AI80" s="9">
         <v>0</v>
@@ -9975,7 +9975,7 @@
         <v>0</v>
       </c>
       <c r="M81" s="3">
-        <v>372</v>
+        <v>341</v>
       </c>
       <c r="N81" s="3">
         <v>29</v>
@@ -10038,7 +10038,7 @@
         <v>10000</v>
       </c>
       <c r="AH81" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI81" s="9">
         <v>0</v>
@@ -10082,7 +10082,7 @@
         <v>0</v>
       </c>
       <c r="M82" s="3">
-        <v>429</v>
+        <v>389</v>
       </c>
       <c r="N82" s="3">
         <v>10</v>
@@ -10145,7 +10145,7 @@
         <v>10000</v>
       </c>
       <c r="AH82" s="9">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AI82" s="9">
         <v>10</v>
@@ -10189,7 +10189,7 @@
         <v>0</v>
       </c>
       <c r="M83" s="3">
-        <v>303</v>
+        <v>276</v>
       </c>
       <c r="N83" s="3">
         <v>19</v>
@@ -10252,7 +10252,7 @@
         <v>10000</v>
       </c>
       <c r="AH83" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI83" s="9">
         <v>0</v>
@@ -10296,7 +10296,7 @@
         <v>0</v>
       </c>
       <c r="M84" s="3">
-        <v>357</v>
+        <v>322</v>
       </c>
       <c r="N84" s="3">
         <v>24</v>
@@ -10359,7 +10359,7 @@
         <v>10000</v>
       </c>
       <c r="AH84" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI84" s="9">
         <v>0</v>
@@ -10403,7 +10403,7 @@
         <v>0</v>
       </c>
       <c r="M85" s="3">
-        <v>372</v>
+        <v>341</v>
       </c>
       <c r="N85" s="3">
         <v>29</v>
@@ -10510,7 +10510,7 @@
         <v>0</v>
       </c>
       <c r="M86" s="3">
-        <v>429</v>
+        <v>389</v>
       </c>
       <c r="N86" s="3">
         <v>10</v>
@@ -10573,7 +10573,7 @@
         <v>10000</v>
       </c>
       <c r="AH86" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI86" s="9">
         <v>10</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D082CA1A-D22F-40F4-83BF-0621319924D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F64EA45-F28A-4F11-8FE1-807D7535F420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6625,7 +6625,7 @@
         <v>21101</v>
       </c>
       <c r="B50" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>99</v>
@@ -6732,7 +6732,7 @@
         <v>21102</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>101</v>
@@ -6839,7 +6839,7 @@
         <v>21103</v>
       </c>
       <c r="B52" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C52" s="13" t="s">
         <v>104</v>
@@ -6946,7 +6946,7 @@
         <v>31101</v>
       </c>
       <c r="B53" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>106</v>
@@ -6973,19 +6973,19 @@
         <v>3</v>
       </c>
       <c r="K53" s="3">
-        <v>254</v>
+        <v>221</v>
       </c>
       <c r="L53" s="3">
         <v>0</v>
       </c>
       <c r="M53" s="3">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="N53" s="3">
         <v>3</v>
       </c>
       <c r="O53" s="3">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="P53" s="3">
         <v>-5500</v>
@@ -7053,7 +7053,7 @@
         <v>31102</v>
       </c>
       <c r="B54" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>107</v>
@@ -7080,19 +7080,19 @@
         <v>3</v>
       </c>
       <c r="K54" s="3">
-        <v>290</v>
+        <v>252</v>
       </c>
       <c r="L54" s="3">
         <v>0</v>
       </c>
       <c r="M54" s="3">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="N54" s="3">
         <v>3</v>
       </c>
       <c r="O54" s="3">
-        <v>206</v>
+        <v>158</v>
       </c>
       <c r="P54" s="3">
         <v>-5500</v>
@@ -7160,7 +7160,7 @@
         <v>31103</v>
       </c>
       <c r="B55" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>109</v>
@@ -7187,19 +7187,19 @@
         <v>3</v>
       </c>
       <c r="K55" s="3">
-        <v>399</v>
+        <v>347</v>
       </c>
       <c r="L55" s="3">
         <v>0</v>
       </c>
       <c r="M55" s="3">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="N55" s="3">
         <v>4</v>
       </c>
       <c r="O55" s="3">
-        <v>748</v>
+        <v>572</v>
       </c>
       <c r="P55" s="3">
         <v>-5500</v>
@@ -7267,7 +7267,7 @@
         <v>41101</v>
       </c>
       <c r="B56" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>111</v>
@@ -7294,19 +7294,19 @@
         <v>4</v>
       </c>
       <c r="K56" s="3">
-        <v>456</v>
+        <v>412</v>
       </c>
       <c r="L56" s="3">
         <v>0</v>
       </c>
       <c r="M56" s="3">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="N56" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O56" s="3">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="P56" s="3">
         <v>-5500</v>
@@ -7374,7 +7374,7 @@
         <v>41102</v>
       </c>
       <c r="B57" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>113</v>
@@ -7401,19 +7401,19 @@
         <v>4</v>
       </c>
       <c r="K57" s="3">
-        <v>522</v>
+        <v>470</v>
       </c>
       <c r="L57" s="3">
         <v>0</v>
       </c>
       <c r="M57" s="3">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="N57" s="3">
         <v>5</v>
       </c>
       <c r="O57" s="3">
-        <v>360</v>
+        <v>334</v>
       </c>
       <c r="P57" s="3">
         <v>-5500</v>
@@ -7481,7 +7481,7 @@
         <v>41103</v>
       </c>
       <c r="B58" s="13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C58" s="13" t="s">
         <v>115</v>
@@ -7508,19 +7508,19 @@
         <v>4</v>
       </c>
       <c r="K58" s="13">
-        <v>717</v>
+        <v>647</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
       <c r="M58" s="13">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="N58" s="13">
         <v>8</v>
       </c>
       <c r="O58" s="13">
-        <v>1488</v>
+        <v>1376</v>
       </c>
       <c r="P58" s="13">
         <v>-5500</v>
@@ -7588,7 +7588,7 @@
         <v>51101</v>
       </c>
       <c r="B59" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>117</v>
@@ -7615,13 +7615,13 @@
         <v>5</v>
       </c>
       <c r="K59" s="3">
-        <v>705</v>
+        <v>685</v>
       </c>
       <c r="L59" s="3">
         <v>0</v>
       </c>
       <c r="M59" s="3">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="N59" s="3">
         <v>8</v>
@@ -7695,7 +7695,7 @@
         <v>51102</v>
       </c>
       <c r="B60" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>120</v>
@@ -7722,13 +7722,13 @@
         <v>5</v>
       </c>
       <c r="K60" s="3">
-        <v>806</v>
+        <v>783</v>
       </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
       <c r="M60" s="3">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N60" s="3">
         <v>9</v>
@@ -7802,7 +7802,7 @@
         <v>51103</v>
       </c>
       <c r="B61" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>122</v>
@@ -7829,13 +7829,13 @@
         <v>5</v>
       </c>
       <c r="K61" s="3">
-        <v>1108</v>
+        <v>1077</v>
       </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
       <c r="M61" s="3">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="N61" s="3">
         <v>12</v>
@@ -7909,7 +7909,7 @@
         <v>51104</v>
       </c>
       <c r="B62" s="13">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C62" s="13" t="s">
         <v>92</v>
@@ -7936,13 +7936,13 @@
         <v>5</v>
       </c>
       <c r="K62" s="13">
-        <v>705</v>
+        <v>685</v>
       </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
       <c r="M62" s="13">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="N62" s="13">
         <v>4</v>
@@ -8016,7 +8016,7 @@
         <v>52101</v>
       </c>
       <c r="B63" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>95</v>
@@ -8043,19 +8043,19 @@
         <v>5</v>
       </c>
       <c r="K63" s="3">
-        <v>841</v>
+        <v>794</v>
       </c>
       <c r="L63" s="3">
         <v>0</v>
       </c>
       <c r="M63" s="3">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="N63" s="3">
         <v>8</v>
       </c>
       <c r="O63" s="3">
-        <v>1344</v>
+        <v>1269</v>
       </c>
       <c r="P63" s="3">
         <v>-5500</v>
@@ -8123,7 +8123,7 @@
         <v>52102</v>
       </c>
       <c r="B64" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>98</v>
@@ -8150,19 +8150,19 @@
         <v>5</v>
       </c>
       <c r="K64" s="3">
-        <v>961</v>
+        <v>907</v>
       </c>
       <c r="L64" s="3">
         <v>0</v>
       </c>
       <c r="M64" s="3">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="N64" s="3">
         <v>9</v>
       </c>
       <c r="O64" s="3">
-        <v>2424</v>
+        <v>2288</v>
       </c>
       <c r="P64" s="3">
         <v>-5500</v>
@@ -8230,7 +8230,7 @@
         <v>52103</v>
       </c>
       <c r="B65" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>99</v>
@@ -8257,19 +8257,19 @@
         <v>5</v>
       </c>
       <c r="K65" s="3">
-        <v>1321</v>
+        <v>1247</v>
       </c>
       <c r="L65" s="3">
         <v>0</v>
       </c>
       <c r="M65" s="3">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N65" s="3">
         <v>13</v>
       </c>
       <c r="O65" s="3">
-        <v>8919</v>
+        <v>8411</v>
       </c>
       <c r="P65" s="3">
         <v>-5500</v>
@@ -8337,7 +8337,7 @@
         <v>52104</v>
       </c>
       <c r="B66" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>101</v>
@@ -8364,19 +8364,19 @@
         <v>5</v>
       </c>
       <c r="K66" s="3">
-        <v>841</v>
+        <v>794</v>
       </c>
       <c r="L66" s="3">
         <v>0</v>
       </c>
       <c r="M66" s="3">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="N66" s="3">
         <v>4</v>
       </c>
       <c r="O66" s="3">
-        <v>1022</v>
+        <v>966</v>
       </c>
       <c r="P66" s="3">
         <v>-5500</v>
@@ -8444,7 +8444,7 @@
         <v>61101</v>
       </c>
       <c r="B67" s="13">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C67" s="13" t="s">
         <v>104</v>
@@ -8471,19 +8471,19 @@
         <v>6</v>
       </c>
       <c r="K67" s="13">
-        <v>1119</v>
+        <v>1072</v>
       </c>
       <c r="L67" s="3">
         <v>0</v>
       </c>
       <c r="M67" s="13">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="N67" s="13">
         <v>13</v>
       </c>
       <c r="O67" s="13">
-        <v>378</v>
+        <v>362</v>
       </c>
       <c r="P67" s="13">
         <v>-5500</v>
@@ -8551,7 +8551,7 @@
         <v>61102</v>
       </c>
       <c r="B68" s="13">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C68" s="13" t="s">
         <v>106</v>
@@ -8578,19 +8578,19 @@
         <v>6</v>
       </c>
       <c r="K68" s="13">
-        <v>1278</v>
+        <v>1225</v>
       </c>
       <c r="L68" s="3">
         <v>0</v>
       </c>
       <c r="M68" s="13">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="N68" s="13">
         <v>14</v>
       </c>
       <c r="O68" s="13">
-        <v>950</v>
+        <v>910</v>
       </c>
       <c r="P68" s="13">
         <v>-5500</v>
@@ -8658,7 +8658,7 @@
         <v>61103</v>
       </c>
       <c r="B69" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>107</v>
@@ -8685,19 +8685,19 @@
         <v>6</v>
       </c>
       <c r="K69" s="3">
-        <v>1758</v>
+        <v>1684</v>
       </c>
       <c r="L69" s="3">
         <v>0</v>
       </c>
       <c r="M69" s="3">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="N69" s="3">
         <v>21</v>
       </c>
       <c r="O69" s="3">
-        <v>3907</v>
+        <v>3738</v>
       </c>
       <c r="P69" s="3">
         <v>-5500</v>
@@ -8765,7 +8765,7 @@
         <v>61104</v>
       </c>
       <c r="B70" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>109</v>
@@ -8792,19 +8792,19 @@
         <v>6</v>
       </c>
       <c r="K70" s="3">
-        <v>1119</v>
+        <v>1072</v>
       </c>
       <c r="L70" s="3">
         <v>0</v>
       </c>
       <c r="M70" s="3">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="N70" s="3">
         <v>6</v>
       </c>
       <c r="O70" s="3">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="P70" s="3">
         <v>-5500</v>
@@ -8872,7 +8872,7 @@
         <v>62101</v>
       </c>
       <c r="B71" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>111</v>
@@ -8899,7 +8899,7 @@
         <v>6</v>
       </c>
       <c r="K71" s="3">
-        <v>1240</v>
+        <v>1224</v>
       </c>
       <c r="L71" s="3">
         <v>0</v>
@@ -8911,7 +8911,7 @@
         <v>13</v>
       </c>
       <c r="O71" s="3">
-        <v>2021</v>
+        <v>1965</v>
       </c>
       <c r="P71" s="3">
         <v>-5500</v>
@@ -8979,7 +8979,7 @@
         <v>62102</v>
       </c>
       <c r="B72" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>113</v>
@@ -9006,7 +9006,7 @@
         <v>6</v>
       </c>
       <c r="K72" s="3">
-        <v>1418</v>
+        <v>1398</v>
       </c>
       <c r="L72" s="3">
         <v>0</v>
@@ -9018,7 +9018,7 @@
         <v>14</v>
       </c>
       <c r="O72" s="3">
-        <v>3649</v>
+        <v>3547</v>
       </c>
       <c r="P72" s="3">
         <v>-5500</v>
@@ -9086,7 +9086,7 @@
         <v>62103</v>
       </c>
       <c r="B73" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>115</v>
@@ -9113,7 +9113,7 @@
         <v>6</v>
       </c>
       <c r="K73" s="3">
-        <v>1949</v>
+        <v>1923</v>
       </c>
       <c r="L73" s="3">
         <v>0</v>
@@ -9125,7 +9125,7 @@
         <v>21</v>
       </c>
       <c r="O73" s="3">
-        <v>13977</v>
+        <v>13579</v>
       </c>
       <c r="P73" s="3">
         <v>-5500</v>
@@ -9193,7 +9193,7 @@
         <v>62104</v>
       </c>
       <c r="B74" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>117</v>
@@ -9220,7 +9220,7 @@
         <v>6</v>
       </c>
       <c r="K74" s="3">
-        <v>1240</v>
+        <v>1224</v>
       </c>
       <c r="L74" s="3">
         <v>0</v>
@@ -9232,7 +9232,7 @@
         <v>6</v>
       </c>
       <c r="O74" s="3">
-        <v>1540</v>
+        <v>1498</v>
       </c>
       <c r="P74" s="3">
         <v>-5500</v>
@@ -9300,7 +9300,7 @@
         <v>71101</v>
       </c>
       <c r="B75" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>120</v>
@@ -9327,7 +9327,7 @@
         <v>7</v>
       </c>
       <c r="K75" s="3">
-        <v>1632</v>
+        <v>1616</v>
       </c>
       <c r="L75" s="3">
         <v>0</v>
@@ -9339,7 +9339,7 @@
         <v>19</v>
       </c>
       <c r="O75" s="3">
-        <v>566</v>
+        <v>554</v>
       </c>
       <c r="P75" s="3">
         <v>-5500</v>
@@ -9407,7 +9407,7 @@
         <v>71102</v>
       </c>
       <c r="B76" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>122</v>
@@ -9434,7 +9434,7 @@
         <v>7</v>
       </c>
       <c r="K76" s="3">
-        <v>1866</v>
+        <v>1846</v>
       </c>
       <c r="L76" s="3">
         <v>0</v>
@@ -9446,7 +9446,7 @@
         <v>24</v>
       </c>
       <c r="O76" s="3">
-        <v>1548</v>
+        <v>1515</v>
       </c>
       <c r="P76" s="3">
         <v>-5500</v>
@@ -9514,7 +9514,7 @@
         <v>71103</v>
       </c>
       <c r="B77" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>92</v>
@@ -9541,7 +9541,7 @@
         <v>7</v>
       </c>
       <c r="K77" s="3">
-        <v>2565</v>
+        <v>2539</v>
       </c>
       <c r="L77" s="3">
         <v>0</v>
@@ -9553,7 +9553,7 @@
         <v>29</v>
       </c>
       <c r="O77" s="3">
-        <v>5627</v>
+        <v>5505</v>
       </c>
       <c r="P77" s="3">
         <v>-5500</v>
@@ -9621,7 +9621,7 @@
         <v>71104</v>
       </c>
       <c r="B78" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>95</v>
@@ -9648,7 +9648,7 @@
         <v>7</v>
       </c>
       <c r="K78" s="3">
-        <v>1632</v>
+        <v>1616</v>
       </c>
       <c r="L78" s="3">
         <v>0</v>
@@ -9660,7 +9660,7 @@
         <v>10</v>
       </c>
       <c r="O78" s="3">
-        <v>635</v>
+        <v>622</v>
       </c>
       <c r="P78" s="3">
         <v>-5500</v>
@@ -9728,7 +9728,7 @@
         <v>72101</v>
       </c>
       <c r="B79" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>98</v>
@@ -9755,19 +9755,19 @@
         <v>7</v>
       </c>
       <c r="K79" s="3">
-        <v>1782</v>
+        <v>1753</v>
       </c>
       <c r="L79" s="3">
         <v>0</v>
       </c>
       <c r="M79" s="3">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="N79" s="3">
         <v>19</v>
       </c>
       <c r="O79" s="3">
-        <v>2881</v>
+        <v>2829</v>
       </c>
       <c r="P79" s="3">
         <v>-5500</v>
@@ -9835,7 +9835,7 @@
         <v>72102</v>
       </c>
       <c r="B80" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>99</v>
@@ -9862,19 +9862,19 @@
         <v>7</v>
       </c>
       <c r="K80" s="3">
-        <v>2036</v>
+        <v>2003</v>
       </c>
       <c r="L80" s="3">
         <v>0</v>
       </c>
       <c r="M80" s="3">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="N80" s="3">
         <v>24</v>
       </c>
       <c r="O80" s="3">
-        <v>5664</v>
+        <v>5561</v>
       </c>
       <c r="P80" s="3">
         <v>-5500</v>
@@ -9942,7 +9942,7 @@
         <v>72103</v>
       </c>
       <c r="B81" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>101</v>
@@ -9969,19 +9969,19 @@
         <v>7</v>
       </c>
       <c r="K81" s="3">
-        <v>2800</v>
+        <v>2754</v>
       </c>
       <c r="L81" s="3">
         <v>0</v>
       </c>
       <c r="M81" s="3">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="N81" s="3">
         <v>29</v>
       </c>
       <c r="O81" s="3">
-        <v>19139</v>
+        <v>18790</v>
       </c>
       <c r="P81" s="3">
         <v>-5500</v>
@@ -10049,7 +10049,7 @@
         <v>72104</v>
       </c>
       <c r="B82" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>104</v>
@@ -10076,19 +10076,19 @@
         <v>7</v>
       </c>
       <c r="K82" s="3">
-        <v>1782</v>
+        <v>1753</v>
       </c>
       <c r="L82" s="3">
         <v>0</v>
       </c>
       <c r="M82" s="3">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="N82" s="3">
         <v>10</v>
       </c>
       <c r="O82" s="3">
-        <v>2485</v>
+        <v>2441</v>
       </c>
       <c r="P82" s="3">
         <v>-5500</v>
@@ -10156,7 +10156,7 @@
         <v>73101</v>
       </c>
       <c r="B83" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>106</v>
@@ -10183,19 +10183,19 @@
         <v>7</v>
       </c>
       <c r="K83" s="3">
-        <v>1782</v>
+        <v>1753</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
       </c>
       <c r="M83" s="3">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="N83" s="3">
         <v>19</v>
       </c>
       <c r="O83" s="3">
-        <v>8092</v>
+        <v>7946</v>
       </c>
       <c r="P83" s="3">
         <v>-5500</v>
@@ -10263,7 +10263,7 @@
         <v>73102</v>
       </c>
       <c r="B84" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>107</v>
@@ -10290,19 +10290,19 @@
         <v>7</v>
       </c>
       <c r="K84" s="3">
-        <v>2036</v>
+        <v>2003</v>
       </c>
       <c r="L84" s="3">
         <v>0</v>
       </c>
       <c r="M84" s="3">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="N84" s="3">
         <v>24</v>
       </c>
       <c r="O84" s="3">
-        <v>13844</v>
+        <v>13594</v>
       </c>
       <c r="P84" s="3">
         <v>-5500</v>
@@ -10370,7 +10370,7 @@
         <v>73103</v>
       </c>
       <c r="B85" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C85" s="3" t="s">
         <v>109</v>
@@ -10397,19 +10397,19 @@
         <v>7</v>
       </c>
       <c r="K85" s="3">
-        <v>2800</v>
+        <v>2754</v>
       </c>
       <c r="L85" s="3">
         <v>0</v>
       </c>
       <c r="M85" s="3">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="N85" s="3">
         <v>29</v>
       </c>
       <c r="O85" s="3">
-        <v>36614</v>
+        <v>35946</v>
       </c>
       <c r="P85" s="3">
         <v>-5500</v>
@@ -10477,7 +10477,7 @@
         <v>73104</v>
       </c>
       <c r="B86" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C86" s="3" t="s">
         <v>111</v>
@@ -10504,19 +10504,19 @@
         <v>7</v>
       </c>
       <c r="K86" s="3">
-        <v>1782</v>
+        <v>1753</v>
       </c>
       <c r="L86" s="3">
         <v>0</v>
       </c>
       <c r="M86" s="3">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="N86" s="3">
         <v>10</v>
       </c>
       <c r="O86" s="3">
-        <v>6979</v>
+        <v>6855</v>
       </c>
       <c r="P86" s="3">
         <v>-5500</v>
@@ -10584,7 +10584,7 @@
         <v>73105</v>
       </c>
       <c r="B87" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C87" s="3" t="s">
         <v>113</v>
@@ -10611,19 +10611,19 @@
         <v>7</v>
       </c>
       <c r="K87" s="3">
-        <v>7635</v>
+        <v>7512</v>
       </c>
       <c r="L87" s="3">
         <v>0</v>
       </c>
       <c r="M87" s="3">
-        <v>990</v>
+        <v>985</v>
       </c>
       <c r="N87" s="3">
         <v>77</v>
       </c>
       <c r="O87" s="3">
-        <v>148352</v>
+        <v>145411</v>
       </c>
       <c r="P87" s="3">
         <v>-5500</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8475BB57-416B-4E6D-B0B5-72218FC79F13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78184F42-94C1-4EFF-97F2-193C47C83671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_foe_v8" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="939" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="246">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -6306,9 +6306,7 @@
       <c r="B47" s="13">
         <v>1</v>
       </c>
-      <c r="C47" s="13" t="s">
-        <v>92</v>
-      </c>
+      <c r="C47" s="13"/>
       <c r="D47" s="13">
         <v>1</v>
       </c>
@@ -6413,9 +6411,7 @@
       <c r="B48" s="3">
         <v>1</v>
       </c>
-      <c r="C48" s="3" t="s">
-        <v>95</v>
-      </c>
+      <c r="C48" s="3"/>
       <c r="D48" s="3">
         <v>1</v>
       </c>
@@ -6520,9 +6516,7 @@
       <c r="B49" s="3">
         <v>1</v>
       </c>
-      <c r="C49" s="3" t="s">
-        <v>98</v>
-      </c>
+      <c r="C49" s="3"/>
       <c r="D49" s="3">
         <v>1</v>
       </c>
@@ -6627,9 +6621,7 @@
       <c r="B50" s="3">
         <v>1</v>
       </c>
-      <c r="C50" s="3" t="s">
-        <v>99</v>
-      </c>
+      <c r="C50" s="3"/>
       <c r="D50" s="3">
         <v>2</v>
       </c>
@@ -6734,9 +6726,7 @@
       <c r="B51" s="3">
         <v>1</v>
       </c>
-      <c r="C51" s="3" t="s">
-        <v>101</v>
-      </c>
+      <c r="C51" s="3"/>
       <c r="D51" s="3">
         <v>2</v>
       </c>
@@ -6841,9 +6831,7 @@
       <c r="B52" s="13">
         <v>1</v>
       </c>
-      <c r="C52" s="13" t="s">
-        <v>104</v>
-      </c>
+      <c r="C52" s="13"/>
       <c r="D52" s="13">
         <v>2</v>
       </c>
@@ -6948,9 +6936,7 @@
       <c r="B53" s="3">
         <v>1</v>
       </c>
-      <c r="C53" s="3" t="s">
-        <v>106</v>
-      </c>
+      <c r="C53" s="3"/>
       <c r="D53" s="3">
         <v>3</v>
       </c>
@@ -7055,9 +7041,7 @@
       <c r="B54" s="3">
         <v>1</v>
       </c>
-      <c r="C54" s="3" t="s">
-        <v>107</v>
-      </c>
+      <c r="C54" s="3"/>
       <c r="D54" s="3">
         <v>3</v>
       </c>
@@ -7162,9 +7146,7 @@
       <c r="B55" s="3">
         <v>1</v>
       </c>
-      <c r="C55" s="3" t="s">
-        <v>109</v>
-      </c>
+      <c r="C55" s="3"/>
       <c r="D55" s="3">
         <v>3</v>
       </c>
@@ -7269,9 +7251,7 @@
       <c r="B56" s="3">
         <v>1</v>
       </c>
-      <c r="C56" s="3" t="s">
-        <v>111</v>
-      </c>
+      <c r="C56" s="3"/>
       <c r="D56" s="3">
         <v>4</v>
       </c>
@@ -7376,9 +7356,7 @@
       <c r="B57" s="3">
         <v>1</v>
       </c>
-      <c r="C57" s="3" t="s">
-        <v>113</v>
-      </c>
+      <c r="C57" s="3"/>
       <c r="D57" s="3">
         <v>4</v>
       </c>
@@ -7483,9 +7461,7 @@
       <c r="B58" s="13">
         <v>1</v>
       </c>
-      <c r="C58" s="13" t="s">
-        <v>115</v>
-      </c>
+      <c r="C58" s="13"/>
       <c r="D58" s="13">
         <v>4</v>
       </c>
@@ -7590,9 +7566,7 @@
       <c r="B59" s="3">
         <v>1</v>
       </c>
-      <c r="C59" s="3" t="s">
-        <v>117</v>
-      </c>
+      <c r="C59" s="3"/>
       <c r="D59" s="3">
         <v>5</v>
       </c>
@@ -7639,7 +7613,7 @@
         <v>0</v>
       </c>
       <c r="S59" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T59" s="3">
         <v>0</v>
@@ -7697,9 +7671,7 @@
       <c r="B60" s="3">
         <v>1</v>
       </c>
-      <c r="C60" s="3" t="s">
-        <v>120</v>
-      </c>
+      <c r="C60" s="3"/>
       <c r="D60" s="3">
         <v>5</v>
       </c>
@@ -7746,7 +7718,7 @@
         <v>0</v>
       </c>
       <c r="S60" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T60" s="3">
         <v>0</v>
@@ -7804,9 +7776,7 @@
       <c r="B61" s="3">
         <v>1</v>
       </c>
-      <c r="C61" s="3" t="s">
-        <v>122</v>
-      </c>
+      <c r="C61" s="3"/>
       <c r="D61" s="3">
         <v>5</v>
       </c>
@@ -7853,7 +7823,7 @@
         <v>0</v>
       </c>
       <c r="S61" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T61" s="3">
         <v>0</v>
@@ -7911,9 +7881,7 @@
       <c r="B62" s="13">
         <v>2</v>
       </c>
-      <c r="C62" s="13" t="s">
-        <v>92</v>
-      </c>
+      <c r="C62" s="13"/>
       <c r="D62" s="13">
         <v>5</v>
       </c>
@@ -8018,9 +7986,7 @@
       <c r="B63" s="13">
         <v>6</v>
       </c>
-      <c r="C63" s="13" t="s">
-        <v>104</v>
-      </c>
+      <c r="C63" s="13"/>
       <c r="D63" s="13">
         <v>6</v>
       </c>
@@ -8125,9 +8091,7 @@
       <c r="B64" s="13">
         <v>6</v>
       </c>
-      <c r="C64" s="13" t="s">
-        <v>106</v>
-      </c>
+      <c r="C64" s="13"/>
       <c r="D64" s="13">
         <v>6</v>
       </c>
@@ -8232,9 +8196,7 @@
       <c r="B65" s="3">
         <v>6</v>
       </c>
-      <c r="C65" s="3" t="s">
-        <v>107</v>
-      </c>
+      <c r="C65" s="3"/>
       <c r="D65" s="3">
         <v>6</v>
       </c>
@@ -8339,9 +8301,7 @@
       <c r="B66" s="3">
         <v>6</v>
       </c>
-      <c r="C66" s="3" t="s">
-        <v>109</v>
-      </c>
+      <c r="C66" s="3"/>
       <c r="D66" s="3">
         <v>6</v>
       </c>
@@ -8446,9 +8406,7 @@
       <c r="B67" s="3">
         <v>6</v>
       </c>
-      <c r="C67" s="3" t="s">
-        <v>111</v>
-      </c>
+      <c r="C67" s="3"/>
       <c r="D67" s="3">
         <v>6</v>
       </c>
@@ -8553,9 +8511,7 @@
       <c r="B68" s="3">
         <v>6</v>
       </c>
-      <c r="C68" s="3" t="s">
-        <v>113</v>
-      </c>
+      <c r="C68" s="3"/>
       <c r="D68" s="3">
         <v>6</v>
       </c>
@@ -8660,9 +8616,7 @@
       <c r="B69" s="3">
         <v>6</v>
       </c>
-      <c r="C69" s="3" t="s">
-        <v>115</v>
-      </c>
+      <c r="C69" s="3"/>
       <c r="D69" s="3">
         <v>6</v>
       </c>
@@ -8767,9 +8721,7 @@
       <c r="B70" s="3">
         <v>6</v>
       </c>
-      <c r="C70" s="3" t="s">
-        <v>117</v>
-      </c>
+      <c r="C70" s="3"/>
       <c r="D70" s="3">
         <v>6</v>
       </c>
@@ -8874,9 +8826,7 @@
       <c r="B71" s="3">
         <v>7</v>
       </c>
-      <c r="C71" s="3" t="s">
-        <v>120</v>
-      </c>
+      <c r="C71" s="3"/>
       <c r="D71" s="3">
         <v>7</v>
       </c>
@@ -8981,9 +8931,7 @@
       <c r="B72" s="3">
         <v>7</v>
       </c>
-      <c r="C72" s="3" t="s">
-        <v>122</v>
-      </c>
+      <c r="C72" s="3"/>
       <c r="D72" s="3">
         <v>7</v>
       </c>
@@ -9088,9 +9036,7 @@
       <c r="B73" s="3">
         <v>7</v>
       </c>
-      <c r="C73" s="3" t="s">
-        <v>92</v>
-      </c>
+      <c r="C73" s="3"/>
       <c r="D73" s="3">
         <v>7</v>
       </c>
@@ -9195,9 +9141,7 @@
       <c r="B74" s="3">
         <v>7</v>
       </c>
-      <c r="C74" s="3" t="s">
-        <v>95</v>
-      </c>
+      <c r="C74" s="3"/>
       <c r="D74" s="3">
         <v>7</v>
       </c>
@@ -9302,9 +9246,7 @@
       <c r="B75" s="3">
         <v>7</v>
       </c>
-      <c r="C75" s="3" t="s">
-        <v>98</v>
-      </c>
+      <c r="C75" s="3"/>
       <c r="D75" s="3">
         <v>7</v>
       </c>
@@ -9409,9 +9351,7 @@
       <c r="B76" s="3">
         <v>7</v>
       </c>
-      <c r="C76" s="3" t="s">
-        <v>99</v>
-      </c>
+      <c r="C76" s="3"/>
       <c r="D76" s="3">
         <v>7</v>
       </c>
@@ -9516,9 +9456,7 @@
       <c r="B77" s="3">
         <v>7</v>
       </c>
-      <c r="C77" s="3" t="s">
-        <v>101</v>
-      </c>
+      <c r="C77" s="3"/>
       <c r="D77" s="3">
         <v>7</v>
       </c>
@@ -9623,9 +9561,7 @@
       <c r="B78" s="3">
         <v>7</v>
       </c>
-      <c r="C78" s="3" t="s">
-        <v>104</v>
-      </c>
+      <c r="C78" s="3"/>
       <c r="D78" s="3">
         <v>7</v>
       </c>
@@ -9730,9 +9666,7 @@
       <c r="B79" s="3">
         <v>7</v>
       </c>
-      <c r="C79" s="3" t="s">
-        <v>106</v>
-      </c>
+      <c r="C79" s="3"/>
       <c r="D79" s="3">
         <v>7</v>
       </c>
@@ -9837,9 +9771,7 @@
       <c r="B80" s="3">
         <v>7</v>
       </c>
-      <c r="C80" s="3" t="s">
-        <v>107</v>
-      </c>
+      <c r="C80" s="3"/>
       <c r="D80" s="3">
         <v>7</v>
       </c>
@@ -9944,9 +9876,7 @@
       <c r="B81" s="3">
         <v>7</v>
       </c>
-      <c r="C81" s="3" t="s">
-        <v>109</v>
-      </c>
+      <c r="C81" s="3"/>
       <c r="D81" s="3">
         <v>7</v>
       </c>
@@ -10051,9 +9981,7 @@
       <c r="B82" s="3">
         <v>7</v>
       </c>
-      <c r="C82" s="3" t="s">
-        <v>111</v>
-      </c>
+      <c r="C82" s="3"/>
       <c r="D82" s="3">
         <v>7</v>
       </c>
@@ -10158,9 +10086,7 @@
       <c r="B83" s="3">
         <v>7</v>
       </c>
-      <c r="C83" s="3" t="s">
-        <v>113</v>
-      </c>
+      <c r="C83" s="3"/>
       <c r="D83" s="3">
         <v>7</v>
       </c>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78184F42-94C1-4EFF-97F2-193C47C83671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78D48979-59F8-4102-9E46-77CB14B2838B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_foe_v8" sheetId="1" r:id="rId1"/>
@@ -6359,13 +6359,13 @@
         <v>0</v>
       </c>
       <c r="U47" s="13">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="V47" s="13">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="W47" s="13">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="X47" s="17">
         <v>201001011</v>
@@ -6464,13 +6464,13 @@
         <v>0</v>
       </c>
       <c r="U48" s="3">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="V48" s="3">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="W48" s="3">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="X48" s="16">
         <v>203001001</v>
@@ -6569,13 +6569,13 @@
         <v>0</v>
       </c>
       <c r="U49" s="3">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="V49" s="3">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="W49" s="3">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="X49" s="16">
         <v>214001011</v>
@@ -6674,13 +6674,13 @@
         <v>0</v>
       </c>
       <c r="U50" s="3">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="V50" s="3">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="W50" s="3">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="X50" s="16">
         <v>201001011</v>
@@ -6779,13 +6779,13 @@
         <v>0</v>
       </c>
       <c r="U51" s="3">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="V51" s="3">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="W51" s="3">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="X51" s="16">
         <v>204001001</v>
@@ -6884,13 +6884,13 @@
         <v>0</v>
       </c>
       <c r="U52" s="13">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="V52" s="13">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="W52" s="13">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="X52" s="17">
         <v>214001011</v>
@@ -6989,13 +6989,13 @@
         <v>0</v>
       </c>
       <c r="U53" s="3">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="V53" s="3">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="W53" s="3">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="X53" s="16">
         <v>201001011</v>
@@ -7094,13 +7094,13 @@
         <v>0</v>
       </c>
       <c r="U54" s="3">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="V54" s="3">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="W54" s="3">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="X54" s="16">
         <v>204001001</v>
@@ -7199,13 +7199,13 @@
         <v>0</v>
       </c>
       <c r="U55" s="3">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="V55" s="3">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="W55" s="3">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="X55" s="16">
         <v>201002011</v>
@@ -7304,13 +7304,13 @@
         <v>0</v>
       </c>
       <c r="U56" s="3">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="V56" s="3">
-        <v>183</v>
+        <v>205</v>
       </c>
       <c r="W56" s="3">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="X56" s="16">
         <v>203001001</v>
@@ -7409,13 +7409,13 @@
         <v>0</v>
       </c>
       <c r="U57" s="3">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="V57" s="3">
-        <v>183</v>
+        <v>205</v>
       </c>
       <c r="W57" s="3">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="X57" s="16">
         <v>204001001</v>
@@ -7514,13 +7514,13 @@
         <v>0</v>
       </c>
       <c r="U58" s="13">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="V58" s="13">
-        <v>183</v>
+        <v>205</v>
       </c>
       <c r="W58" s="13">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="X58" s="17">
         <v>203002011</v>
@@ -7619,13 +7619,13 @@
         <v>0</v>
       </c>
       <c r="U59" s="3">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="V59" s="3">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="W59" s="3">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="X59" s="16">
         <v>201002011</v>
@@ -7724,13 +7724,13 @@
         <v>0</v>
       </c>
       <c r="U60" s="3">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="V60" s="3">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="W60" s="3">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="X60" s="16">
         <v>204002001</v>
@@ -7829,13 +7829,13 @@
         <v>0</v>
       </c>
       <c r="U61" s="3">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="V61" s="3">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="W61" s="3">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="X61" s="16">
         <v>201003001</v>
@@ -7934,13 +7934,13 @@
         <v>0</v>
       </c>
       <c r="U62" s="13">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="V62" s="13">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="W62" s="13">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="X62" s="17">
         <v>201004011</v>
@@ -8039,13 +8039,13 @@
         <v>0</v>
       </c>
       <c r="U63" s="13">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="V63" s="13">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="W63" s="13">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="X63" s="17">
         <v>201002011</v>
@@ -8144,13 +8144,13 @@
         <v>0</v>
       </c>
       <c r="U64" s="13">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="V64" s="13">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="W64" s="13">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="X64" s="17">
         <v>204002001</v>
@@ -8249,13 +8249,13 @@
         <v>0</v>
       </c>
       <c r="U65" s="3">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="V65" s="3">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="W65" s="3">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="X65" s="16">
         <v>214001011</v>
@@ -8354,13 +8354,13 @@
         <v>0</v>
       </c>
       <c r="U66" s="3">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="V66" s="3">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="W66" s="3">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="X66" s="16">
         <v>201004011</v>
@@ -8459,13 +8459,13 @@
         <v>0</v>
       </c>
       <c r="U67" s="3">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="V67" s="3">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="W67" s="3">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="X67" s="16">
         <v>201002011</v>
@@ -8564,13 +8564,13 @@
         <v>0</v>
       </c>
       <c r="U68" s="3">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="V68" s="3">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="W68" s="3">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="X68" s="16">
         <v>204002001</v>
@@ -8669,13 +8669,13 @@
         <v>0</v>
       </c>
       <c r="U69" s="3">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="V69" s="3">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="W69" s="3">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="X69" s="16">
         <v>214001011</v>
@@ -8774,13 +8774,13 @@
         <v>0</v>
       </c>
       <c r="U70" s="3">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="V70" s="3">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="W70" s="3">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="X70" s="16">
         <v>201004011</v>
@@ -8879,13 +8879,13 @@
         <v>0</v>
       </c>
       <c r="U71" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="V71" s="3">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="W71" s="3">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="X71" s="16">
         <v>201002011</v>
@@ -8984,13 +8984,13 @@
         <v>0</v>
       </c>
       <c r="U72" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="V72" s="3">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="W72" s="3">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="X72" s="16">
         <v>203002011</v>
@@ -9089,13 +9089,13 @@
         <v>0</v>
       </c>
       <c r="U73" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="V73" s="3">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="W73" s="3">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="X73" s="16">
         <v>201003001</v>
@@ -9194,13 +9194,13 @@
         <v>0</v>
       </c>
       <c r="U74" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="V74" s="3">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="W74" s="3">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="X74" s="16">
         <v>211002001</v>
@@ -9299,13 +9299,13 @@
         <v>0</v>
       </c>
       <c r="U75" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="V75" s="3">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="W75" s="3">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="X75" s="16">
         <v>201002011</v>
@@ -9404,13 +9404,13 @@
         <v>0</v>
       </c>
       <c r="U76" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="V76" s="3">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="W76" s="3">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="X76" s="16">
         <v>203002011</v>
@@ -9509,13 +9509,13 @@
         <v>0</v>
       </c>
       <c r="U77" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="V77" s="3">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="W77" s="3">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="X77" s="16">
         <v>201003001</v>
@@ -9614,13 +9614,13 @@
         <v>0</v>
       </c>
       <c r="U78" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="V78" s="3">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="W78" s="3">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="X78" s="16">
         <v>211002001</v>
@@ -9719,13 +9719,13 @@
         <v>0</v>
       </c>
       <c r="U79" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="V79" s="3">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="W79" s="3">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="X79" s="16">
         <v>201002011</v>
@@ -9824,13 +9824,13 @@
         <v>0</v>
       </c>
       <c r="U80" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="V80" s="3">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="W80" s="3">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="X80" s="16">
         <v>203002011</v>
@@ -9929,13 +9929,13 @@
         <v>0</v>
       </c>
       <c r="U81" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="V81" s="3">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="W81" s="3">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="X81" s="16">
         <v>201003001</v>
@@ -10034,13 +10034,13 @@
         <v>0</v>
       </c>
       <c r="U82" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="V82" s="3">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="W82" s="3">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="X82" s="16">
         <v>211002001</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78D48979-59F8-4102-9E46-77CB14B2838B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8513ECB7-1EFA-46B4-AAE7-DF4F16CFE9DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_foe_v8" sheetId="1" r:id="rId1"/>
@@ -6299,108 +6299,108 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:35" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="13">
+    <row r="47" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A47" s="3">
         <v>11101</v>
       </c>
-      <c r="B47" s="13">
-        <v>1</v>
-      </c>
-      <c r="C47" s="13"/>
-      <c r="D47" s="13">
-        <v>1</v>
-      </c>
-      <c r="E47" s="13">
-        <v>1</v>
-      </c>
-      <c r="F47" s="13" t="s">
+      <c r="B47" s="3">
+        <v>1</v>
+      </c>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3">
+        <v>1</v>
+      </c>
+      <c r="E47" s="3">
+        <v>1</v>
+      </c>
+      <c r="F47" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G47" s="13">
-        <v>0</v>
-      </c>
-      <c r="H47" s="13" t="s">
+      <c r="G47" s="3">
+        <v>0</v>
+      </c>
+      <c r="H47" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="I47" s="13">
+      <c r="I47" s="3">
         <v>800001011</v>
       </c>
-      <c r="J47" s="13">
-        <v>1</v>
-      </c>
-      <c r="K47" s="13">
+      <c r="J47" s="3">
+        <v>1</v>
+      </c>
+      <c r="K47" s="3">
         <v>67</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
-      <c r="M47" s="13">
-        <v>11</v>
-      </c>
-      <c r="N47" s="13">
-        <v>1</v>
-      </c>
-      <c r="O47" s="13">
-        <v>17</v>
-      </c>
-      <c r="P47" s="13">
+      <c r="M47" s="3">
+        <v>30</v>
+      </c>
+      <c r="N47" s="3">
+        <v>1</v>
+      </c>
+      <c r="O47" s="3">
+        <v>30</v>
+      </c>
+      <c r="P47" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q47" s="13">
-        <v>1</v>
-      </c>
-      <c r="R47" s="13">
-        <v>0</v>
-      </c>
-      <c r="S47" s="13">
+      <c r="Q47" s="3">
+        <v>1</v>
+      </c>
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3">
         <v>2</v>
       </c>
-      <c r="T47" s="13">
-        <v>0</v>
-      </c>
-      <c r="U47" s="13">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+      <c r="U47" s="3">
         <v>98</v>
       </c>
-      <c r="V47" s="13">
+      <c r="V47" s="3">
         <v>174</v>
       </c>
-      <c r="W47" s="13">
+      <c r="W47" s="3">
         <v>106</v>
       </c>
-      <c r="X47" s="17">
+      <c r="X47" s="16">
         <v>201001011</v>
       </c>
-      <c r="Y47" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z47" s="13">
-        <v>1</v>
-      </c>
-      <c r="AA47" s="8" t="s">
+      <c r="Y47" s="16">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="3">
+        <v>1</v>
+      </c>
+      <c r="AA47" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="AB47" s="13">
+      <c r="AB47" s="3">
         <v>15000</v>
       </c>
-      <c r="AC47" s="13">
-        <v>10000</v>
-      </c>
-      <c r="AD47" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE47" s="8">
+      <c r="AC47" s="3">
+        <v>10000</v>
+      </c>
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE47" s="9">
         <v>40</v>
       </c>
-      <c r="AF47" s="8">
-        <v>10000</v>
-      </c>
-      <c r="AG47" s="8">
-        <v>10000</v>
-      </c>
-      <c r="AH47" s="8">
+      <c r="AF47" s="9">
+        <v>10000</v>
+      </c>
+      <c r="AG47" s="9">
+        <v>10000</v>
+      </c>
+      <c r="AH47" s="9">
         <v>56</v>
       </c>
-      <c r="AI47" s="8">
+      <c r="AI47" s="9">
         <v>0</v>
       </c>
     </row>
@@ -6440,13 +6440,13 @@
         <v>0</v>
       </c>
       <c r="M48" s="3">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="N48" s="3">
         <v>1</v>
       </c>
       <c r="O48" s="3">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="P48" s="3">
         <v>-5500</v>
@@ -6545,7 +6545,7 @@
         <v>0</v>
       </c>
       <c r="M49" s="3">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="N49" s="3">
         <v>1</v>
@@ -6824,108 +6824,108 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:35" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="13">
+    <row r="52" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A52" s="3">
         <v>21103</v>
       </c>
-      <c r="B52" s="13">
-        <v>1</v>
-      </c>
-      <c r="C52" s="13"/>
-      <c r="D52" s="13">
+      <c r="B52" s="3">
+        <v>1</v>
+      </c>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3">
         <v>2</v>
       </c>
-      <c r="E52" s="13">
-        <v>1</v>
-      </c>
-      <c r="F52" s="13" t="s">
+      <c r="E52" s="3">
+        <v>1</v>
+      </c>
+      <c r="F52" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G52" s="13">
-        <v>0</v>
-      </c>
-      <c r="H52" s="13" t="s">
+      <c r="G52" s="3">
+        <v>0</v>
+      </c>
+      <c r="H52" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="I52" s="13">
+      <c r="I52" s="3">
         <v>800014011</v>
       </c>
-      <c r="J52" s="13">
+      <c r="J52" s="3">
         <v>2</v>
       </c>
-      <c r="K52" s="13">
+      <c r="K52" s="3">
         <v>158</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
       </c>
-      <c r="M52" s="13">
+      <c r="M52" s="3">
         <v>19</v>
       </c>
-      <c r="N52" s="13">
+      <c r="N52" s="3">
         <v>2</v>
       </c>
-      <c r="O52" s="13">
+      <c r="O52" s="3">
         <v>338</v>
       </c>
-      <c r="P52" s="13">
+      <c r="P52" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q52" s="13">
-        <v>1</v>
-      </c>
-      <c r="R52" s="13">
-        <v>0</v>
-      </c>
-      <c r="S52" s="13">
+      <c r="Q52" s="3">
+        <v>1</v>
+      </c>
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3">
         <v>2</v>
       </c>
-      <c r="T52" s="13">
-        <v>0</v>
-      </c>
-      <c r="U52" s="13">
+      <c r="T52" s="3">
+        <v>0</v>
+      </c>
+      <c r="U52" s="3">
         <v>98</v>
       </c>
-      <c r="V52" s="13">
+      <c r="V52" s="3">
         <v>174</v>
       </c>
-      <c r="W52" s="13">
+      <c r="W52" s="3">
         <v>136</v>
       </c>
-      <c r="X52" s="17">
+      <c r="X52" s="16">
         <v>214001011</v>
       </c>
-      <c r="Y52" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z52" s="13">
-        <v>1</v>
-      </c>
-      <c r="AA52" s="8" t="s">
+      <c r="Y52" s="16">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="3">
+        <v>1</v>
+      </c>
+      <c r="AA52" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="AB52" s="13">
+      <c r="AB52" s="3">
         <v>15000</v>
       </c>
-      <c r="AC52" s="13">
-        <v>10000</v>
-      </c>
-      <c r="AD52" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE52" s="8">
+      <c r="AC52" s="3">
+        <v>10000</v>
+      </c>
+      <c r="AD52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE52" s="9">
         <v>40</v>
       </c>
-      <c r="AF52" s="8">
-        <v>10000</v>
-      </c>
-      <c r="AG52" s="8">
-        <v>10000</v>
-      </c>
-      <c r="AH52" s="8">
+      <c r="AF52" s="9">
+        <v>10000</v>
+      </c>
+      <c r="AG52" s="9">
+        <v>10000</v>
+      </c>
+      <c r="AH52" s="9">
         <v>33</v>
       </c>
-      <c r="AI52" s="8">
+      <c r="AI52" s="9">
         <v>0</v>
       </c>
     </row>
@@ -7454,108 +7454,108 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:35" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="13">
+    <row r="58" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A58" s="3">
         <v>41103</v>
       </c>
-      <c r="B58" s="13">
-        <v>1</v>
-      </c>
-      <c r="C58" s="13"/>
-      <c r="D58" s="13">
+      <c r="B58" s="3">
+        <v>1</v>
+      </c>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3">
         <v>4</v>
       </c>
-      <c r="E58" s="13">
-        <v>1</v>
-      </c>
-      <c r="F58" s="13" t="s">
+      <c r="E58" s="3">
+        <v>1</v>
+      </c>
+      <c r="F58" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G58" s="13">
-        <v>0</v>
-      </c>
-      <c r="H58" s="13" t="s">
+      <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="I58" s="13">
+      <c r="I58" s="3">
         <v>800003021</v>
       </c>
-      <c r="J58" s="13">
+      <c r="J58" s="3">
         <v>4</v>
       </c>
-      <c r="K58" s="13">
+      <c r="K58" s="3">
         <v>647</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
-      <c r="M58" s="13">
+      <c r="M58" s="3">
         <v>90</v>
       </c>
-      <c r="N58" s="13">
+      <c r="N58" s="3">
         <v>8</v>
       </c>
-      <c r="O58" s="13">
+      <c r="O58" s="3">
         <v>1376</v>
       </c>
-      <c r="P58" s="13">
+      <c r="P58" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q58" s="13">
-        <v>1</v>
-      </c>
-      <c r="R58" s="13">
-        <v>0</v>
-      </c>
-      <c r="S58" s="13">
+      <c r="Q58" s="3">
+        <v>1</v>
+      </c>
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
         <v>2</v>
       </c>
-      <c r="T58" s="13">
-        <v>0</v>
-      </c>
-      <c r="U58" s="13">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
         <v>98</v>
       </c>
-      <c r="V58" s="13">
+      <c r="V58" s="3">
         <v>205</v>
       </c>
-      <c r="W58" s="13">
+      <c r="W58" s="3">
         <v>136</v>
       </c>
-      <c r="X58" s="17">
+      <c r="X58" s="16">
         <v>203002011</v>
       </c>
-      <c r="Y58" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z58" s="13">
-        <v>1</v>
-      </c>
-      <c r="AA58" s="8" t="s">
+      <c r="Y58" s="16">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="3">
+        <v>1</v>
+      </c>
+      <c r="AA58" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="AB58" s="13">
+      <c r="AB58" s="3">
         <v>15000</v>
       </c>
-      <c r="AC58" s="13">
-        <v>10000</v>
-      </c>
-      <c r="AD58" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE58" s="8">
+      <c r="AC58" s="3">
+        <v>10000</v>
+      </c>
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE58" s="9">
         <v>40</v>
       </c>
-      <c r="AF58" s="8">
-        <v>10000</v>
-      </c>
-      <c r="AG58" s="8">
-        <v>10000</v>
-      </c>
-      <c r="AH58" s="8">
+      <c r="AF58" s="9">
+        <v>10000</v>
+      </c>
+      <c r="AG58" s="9">
+        <v>10000</v>
+      </c>
+      <c r="AH58" s="9">
         <v>34</v>
       </c>
-      <c r="AI58" s="8">
+      <c r="AI58" s="9">
         <v>0</v>
       </c>
     </row>
@@ -7874,318 +7874,318 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:35" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="13">
+    <row r="62" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A62" s="3">
         <v>51104</v>
       </c>
-      <c r="B62" s="13">
+      <c r="B62" s="3">
         <v>2</v>
       </c>
-      <c r="C62" s="13"/>
-      <c r="D62" s="13">
+      <c r="C62" s="3"/>
+      <c r="D62" s="3">
         <v>5</v>
       </c>
-      <c r="E62" s="13">
-        <v>1</v>
-      </c>
-      <c r="F62" s="13" t="s">
+      <c r="E62" s="3">
+        <v>1</v>
+      </c>
+      <c r="F62" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G62" s="13">
-        <v>0</v>
-      </c>
-      <c r="H62" s="13" t="s">
+      <c r="G62" s="3">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="I62" s="13">
+      <c r="I62" s="3">
         <v>800001041</v>
       </c>
-      <c r="J62" s="13">
+      <c r="J62" s="3">
         <v>5</v>
       </c>
-      <c r="K62" s="13">
+      <c r="K62" s="3">
         <v>685</v>
       </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
-      <c r="M62" s="13">
+      <c r="M62" s="3">
         <v>147</v>
       </c>
-      <c r="N62" s="13">
+      <c r="N62" s="3">
         <v>4</v>
       </c>
-      <c r="O62" s="13">
+      <c r="O62" s="3">
         <v>229</v>
       </c>
-      <c r="P62" s="13">
+      <c r="P62" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q62" s="13">
-        <v>1</v>
-      </c>
-      <c r="R62" s="13">
-        <v>0</v>
-      </c>
-      <c r="S62" s="13">
-        <v>1</v>
-      </c>
-      <c r="T62" s="13">
-        <v>0</v>
-      </c>
-      <c r="U62" s="13">
+      <c r="Q62" s="3">
+        <v>1</v>
+      </c>
+      <c r="R62" s="3">
+        <v>0</v>
+      </c>
+      <c r="S62" s="3">
+        <v>1</v>
+      </c>
+      <c r="T62" s="3">
+        <v>0</v>
+      </c>
+      <c r="U62" s="3">
         <v>98</v>
       </c>
-      <c r="V62" s="13">
+      <c r="V62" s="3">
         <v>235</v>
       </c>
-      <c r="W62" s="13">
+      <c r="W62" s="3">
         <v>167</v>
       </c>
-      <c r="X62" s="17">
+      <c r="X62" s="16">
         <v>201004011</v>
       </c>
-      <c r="Y62" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z62" s="13">
-        <v>1</v>
-      </c>
-      <c r="AA62" s="8" t="s">
+      <c r="Y62" s="16">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="3">
+        <v>1</v>
+      </c>
+      <c r="AA62" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="AB62" s="13">
+      <c r="AB62" s="3">
         <v>15000</v>
       </c>
-      <c r="AC62" s="13">
-        <v>10000</v>
-      </c>
-      <c r="AD62" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE62" s="8">
+      <c r="AC62" s="3">
+        <v>10000</v>
+      </c>
+      <c r="AD62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE62" s="9">
         <v>40</v>
       </c>
-      <c r="AF62" s="8">
-        <v>10000</v>
-      </c>
-      <c r="AG62" s="8">
-        <v>10000</v>
-      </c>
-      <c r="AH62" s="8">
+      <c r="AF62" s="9">
+        <v>10000</v>
+      </c>
+      <c r="AG62" s="9">
+        <v>10000</v>
+      </c>
+      <c r="AH62" s="9">
         <v>65</v>
       </c>
-      <c r="AI62" s="8">
+      <c r="AI62" s="9">
         <v>10</v>
       </c>
     </row>
-    <row r="63" spans="1:35" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="13">
+    <row r="63" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A63" s="3">
         <v>61101</v>
       </c>
-      <c r="B63" s="13">
+      <c r="B63" s="3">
         <v>6</v>
       </c>
-      <c r="C63" s="13"/>
-      <c r="D63" s="13">
+      <c r="C63" s="3"/>
+      <c r="D63" s="3">
         <v>6</v>
       </c>
-      <c r="E63" s="13">
-        <v>1</v>
-      </c>
-      <c r="F63" s="13" t="s">
+      <c r="E63" s="3">
+        <v>1</v>
+      </c>
+      <c r="F63" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G63" s="13">
-        <v>0</v>
-      </c>
-      <c r="H63" s="13" t="s">
+      <c r="G63" s="3">
+        <v>0</v>
+      </c>
+      <c r="H63" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="I63" s="13">
+      <c r="I63" s="3">
         <v>800001021</v>
       </c>
-      <c r="J63" s="13">
+      <c r="J63" s="3">
         <v>6</v>
       </c>
-      <c r="K63" s="13">
+      <c r="K63" s="3">
         <v>1042</v>
       </c>
       <c r="L63" s="3">
         <v>0</v>
       </c>
-      <c r="M63" s="13">
+      <c r="M63" s="3">
         <v>157</v>
       </c>
-      <c r="N63" s="13">
+      <c r="N63" s="3">
         <v>13</v>
       </c>
-      <c r="O63" s="13">
+      <c r="O63" s="3">
         <v>341</v>
       </c>
-      <c r="P63" s="13">
+      <c r="P63" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q63" s="13">
-        <v>1</v>
-      </c>
-      <c r="R63" s="13">
-        <v>0</v>
-      </c>
-      <c r="S63" s="13">
-        <v>1</v>
-      </c>
-      <c r="T63" s="13">
-        <v>0</v>
-      </c>
-      <c r="U63" s="13">
+      <c r="Q63" s="3">
+        <v>1</v>
+      </c>
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3">
+        <v>1</v>
+      </c>
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+      <c r="U63" s="3">
         <v>48</v>
       </c>
-      <c r="V63" s="13">
+      <c r="V63" s="3">
         <v>97</v>
       </c>
-      <c r="W63" s="13">
+      <c r="W63" s="3">
         <v>72</v>
       </c>
-      <c r="X63" s="17">
+      <c r="X63" s="16">
         <v>201002011</v>
       </c>
-      <c r="Y63" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z63" s="13">
-        <v>1</v>
-      </c>
-      <c r="AA63" s="8" t="s">
+      <c r="Y63" s="16">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="3">
+        <v>1</v>
+      </c>
+      <c r="AA63" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="AB63" s="13">
+      <c r="AB63" s="3">
         <v>15000</v>
       </c>
-      <c r="AC63" s="13">
-        <v>10000</v>
-      </c>
-      <c r="AD63" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE63" s="8">
+      <c r="AC63" s="3">
+        <v>10000</v>
+      </c>
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="9">
         <v>40</v>
       </c>
-      <c r="AF63" s="8">
-        <v>10000</v>
-      </c>
-      <c r="AG63" s="8">
-        <v>10000</v>
-      </c>
-      <c r="AH63" s="8">
+      <c r="AF63" s="9">
+        <v>10000</v>
+      </c>
+      <c r="AG63" s="9">
+        <v>10000</v>
+      </c>
+      <c r="AH63" s="9">
         <v>55</v>
       </c>
-      <c r="AI63" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:35" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="13">
+      <c r="AI63" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A64" s="3">
         <v>61102</v>
       </c>
-      <c r="B64" s="13">
+      <c r="B64" s="3">
         <v>6</v>
       </c>
-      <c r="C64" s="13"/>
-      <c r="D64" s="13">
+      <c r="C64" s="3"/>
+      <c r="D64" s="3">
         <v>6</v>
       </c>
-      <c r="E64" s="13">
-        <v>1</v>
-      </c>
-      <c r="F64" s="13" t="s">
+      <c r="E64" s="3">
+        <v>1</v>
+      </c>
+      <c r="F64" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G64" s="13">
-        <v>0</v>
-      </c>
-      <c r="H64" s="13" t="s">
+      <c r="G64" s="3">
+        <v>0</v>
+      </c>
+      <c r="H64" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="I64" s="13">
+      <c r="I64" s="3">
         <v>800004021</v>
       </c>
-      <c r="J64" s="13">
+      <c r="J64" s="3">
         <v>6</v>
       </c>
-      <c r="K64" s="13">
+      <c r="K64" s="3">
         <v>1191</v>
       </c>
       <c r="L64" s="3">
         <v>0</v>
       </c>
-      <c r="M64" s="13">
+      <c r="M64" s="3">
         <v>210</v>
       </c>
-      <c r="N64" s="13">
+      <c r="N64" s="3">
         <v>14</v>
       </c>
-      <c r="O64" s="13">
+      <c r="O64" s="3">
         <v>857</v>
       </c>
-      <c r="P64" s="13">
+      <c r="P64" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q64" s="13">
-        <v>1</v>
-      </c>
-      <c r="R64" s="13">
-        <v>0</v>
-      </c>
-      <c r="S64" s="13">
-        <v>1</v>
-      </c>
-      <c r="T64" s="13">
-        <v>0</v>
-      </c>
-      <c r="U64" s="13">
+      <c r="Q64" s="3">
+        <v>1</v>
+      </c>
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3">
+        <v>1</v>
+      </c>
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+      <c r="U64" s="3">
         <v>48</v>
       </c>
-      <c r="V64" s="13">
+      <c r="V64" s="3">
         <v>97</v>
       </c>
-      <c r="W64" s="13">
+      <c r="W64" s="3">
         <v>72</v>
       </c>
-      <c r="X64" s="17">
+      <c r="X64" s="16">
         <v>204002001</v>
       </c>
-      <c r="Y64" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z64" s="13">
-        <v>1</v>
-      </c>
-      <c r="AA64" s="8" t="s">
+      <c r="Y64" s="16">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="3">
+        <v>1</v>
+      </c>
+      <c r="AA64" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="AB64" s="13">
+      <c r="AB64" s="3">
         <v>15000</v>
       </c>
-      <c r="AC64" s="13">
-        <v>10000</v>
-      </c>
-      <c r="AD64" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE64" s="8">
+      <c r="AC64" s="3">
+        <v>10000</v>
+      </c>
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="9">
         <v>40</v>
       </c>
-      <c r="AF64" s="8">
-        <v>10000</v>
-      </c>
-      <c r="AG64" s="8">
-        <v>10000</v>
-      </c>
-      <c r="AH64" s="8">
+      <c r="AF64" s="9">
+        <v>10000</v>
+      </c>
+      <c r="AG64" s="9">
+        <v>10000</v>
+      </c>
+      <c r="AH64" s="9">
         <v>54</v>
       </c>
-      <c r="AI64" s="8">
+      <c r="AI64" s="9">
         <v>0</v>
       </c>
     </row>
@@ -18027,7 +18027,7 @@
         <v>1</v>
       </c>
       <c r="K157" s="26">
-        <v>5</v>
+        <v>-4</v>
       </c>
       <c r="L157" s="3">
         <v>0</v>
@@ -18134,7 +18134,7 @@
         <v>1</v>
       </c>
       <c r="K158" s="26">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="L158" s="3">
         <v>0</v>
@@ -18241,7 +18241,7 @@
         <v>1</v>
       </c>
       <c r="K159" s="26">
-        <v>6</v>
+        <v>-4</v>
       </c>
       <c r="L159" s="3">
         <v>0</v>
@@ -18348,7 +18348,7 @@
         <v>1</v>
       </c>
       <c r="K160" s="26">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="L160" s="3">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8513ECB7-1EFA-46B4-AAE7-DF4F16CFE9DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55AB24EE-F142-41A4-9DAF-7570D8622EC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_foe_v8" sheetId="1" r:id="rId1"/>
@@ -1852,7 +1852,7 @@
         <v>25</v>
       </c>
       <c r="P5" s="3">
-        <v>-5000</v>
+        <v>-3500</v>
       </c>
       <c r="Q5" s="3">
         <v>1</v>
@@ -1959,7 +1959,7 @@
         <v>25</v>
       </c>
       <c r="P6" s="3">
-        <v>-5000</v>
+        <v>-3500</v>
       </c>
       <c r="Q6" s="3">
         <v>1</v>
@@ -2066,7 +2066,7 @@
         <v>25</v>
       </c>
       <c r="P7" s="3">
-        <v>-5000</v>
+        <v>-3500</v>
       </c>
       <c r="Q7" s="3">
         <v>1</v>
@@ -2173,7 +2173,7 @@
         <v>25</v>
       </c>
       <c r="P8" s="3">
-        <v>-5000</v>
+        <v>-3500</v>
       </c>
       <c r="Q8" s="3">
         <v>1</v>
@@ -2280,7 +2280,7 @@
         <v>25</v>
       </c>
       <c r="P9" s="3">
-        <v>-5000</v>
+        <v>-3500</v>
       </c>
       <c r="Q9" s="3">
         <v>1</v>
@@ -2387,7 +2387,7 @@
         <v>25</v>
       </c>
       <c r="P10" s="3">
-        <v>-5000</v>
+        <v>-3500</v>
       </c>
       <c r="Q10" s="3">
         <v>1</v>
@@ -2494,7 +2494,7 @@
         <v>25</v>
       </c>
       <c r="P11" s="3">
-        <v>-5000</v>
+        <v>-3500</v>
       </c>
       <c r="Q11" s="3">
         <v>1</v>
@@ -2601,7 +2601,7 @@
         <v>25</v>
       </c>
       <c r="P12" s="3">
-        <v>-5000</v>
+        <v>-3500</v>
       </c>
       <c r="Q12" s="3">
         <v>1</v>
@@ -2708,7 +2708,7 @@
         <v>25</v>
       </c>
       <c r="P13" s="3">
-        <v>-5000</v>
+        <v>-3500</v>
       </c>
       <c r="Q13" s="3">
         <v>1</v>
@@ -2815,7 +2815,7 @@
         <v>25</v>
       </c>
       <c r="P14" s="3">
-        <v>-5000</v>
+        <v>-3500</v>
       </c>
       <c r="Q14" s="3">
         <v>1</v>
@@ -2922,7 +2922,7 @@
         <v>25</v>
       </c>
       <c r="P15" s="3">
-        <v>-5000</v>
+        <v>-3500</v>
       </c>
       <c r="Q15" s="3">
         <v>1</v>
@@ -3029,7 +3029,7 @@
         <v>25</v>
       </c>
       <c r="P16" s="3">
-        <v>-5000</v>
+        <v>-3500</v>
       </c>
       <c r="Q16" s="3">
         <v>1</v>
@@ -3136,7 +3136,7 @@
         <v>25</v>
       </c>
       <c r="P17" s="3">
-        <v>-5000</v>
+        <v>-3500</v>
       </c>
       <c r="Q17" s="3">
         <v>1</v>
@@ -3243,7 +3243,7 @@
         <v>25</v>
       </c>
       <c r="P18" s="3">
-        <v>-5000</v>
+        <v>-3500</v>
       </c>
       <c r="Q18" s="3">
         <v>1</v>
@@ -3350,7 +3350,7 @@
         <v>36</v>
       </c>
       <c r="P19" s="3">
-        <v>-5000</v>
+        <v>-3500</v>
       </c>
       <c r="Q19" s="3">
         <v>1</v>
@@ -3457,13 +3457,13 @@
         <v>40</v>
       </c>
       <c r="P20" s="3">
-        <v>-5000</v>
+        <v>-3500</v>
       </c>
       <c r="Q20" s="3">
         <v>1</v>
       </c>
       <c r="R20" s="3">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="S20" s="3">
         <v>0</v>
@@ -3564,13 +3564,13 @@
         <v>44</v>
       </c>
       <c r="P21" s="3">
-        <v>-5000</v>
+        <v>-3500</v>
       </c>
       <c r="Q21" s="3">
         <v>1</v>
       </c>
       <c r="R21" s="3">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="S21" s="3">
         <v>0</v>
@@ -3671,13 +3671,13 @@
         <v>45</v>
       </c>
       <c r="P22" s="3">
-        <v>-5000</v>
+        <v>-3500</v>
       </c>
       <c r="Q22" s="3">
         <v>1</v>
       </c>
       <c r="R22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
@@ -3778,13 +3778,13 @@
         <v>50</v>
       </c>
       <c r="P23" s="3">
-        <v>-5000</v>
+        <v>-3500</v>
       </c>
       <c r="Q23" s="3">
         <v>1</v>
       </c>
       <c r="R23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S23" s="3">
         <v>0</v>
@@ -3885,13 +3885,13 @@
         <v>55</v>
       </c>
       <c r="P24" s="3">
-        <v>-5000</v>
+        <v>-3500</v>
       </c>
       <c r="Q24" s="3">
         <v>1</v>
       </c>
       <c r="R24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S24" s="3">
         <v>0</v>
@@ -3992,13 +3992,13 @@
         <v>160</v>
       </c>
       <c r="P25" s="3">
-        <v>-5000</v>
+        <v>-3500</v>
       </c>
       <c r="Q25" s="3">
         <v>1</v>
       </c>
       <c r="R25" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="S25" s="3">
         <v>0</v>
@@ -4099,13 +4099,13 @@
         <v>200</v>
       </c>
       <c r="P26" s="3">
-        <v>-5000</v>
+        <v>-3500</v>
       </c>
       <c r="Q26" s="3">
         <v>1</v>
       </c>
       <c r="R26" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="S26" s="3">
         <v>0</v>
@@ -4206,13 +4206,13 @@
         <v>240</v>
       </c>
       <c r="P27" s="3">
-        <v>-5000</v>
+        <v>-3500</v>
       </c>
       <c r="Q27" s="3">
         <v>1</v>
       </c>
       <c r="R27" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="S27" s="3">
         <v>0</v>
@@ -4313,13 +4313,13 @@
         <v>720</v>
       </c>
       <c r="P28" s="3">
-        <v>-5000</v>
+        <v>-3500</v>
       </c>
       <c r="Q28" s="3">
         <v>1</v>
       </c>
       <c r="R28" s="3">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="S28" s="3">
         <v>0</v>
@@ -4420,13 +4420,13 @@
         <v>800</v>
       </c>
       <c r="P29" s="3">
-        <v>-5000</v>
+        <v>-3500</v>
       </c>
       <c r="Q29" s="3">
         <v>1</v>
       </c>
       <c r="R29" s="3">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
@@ -4527,13 +4527,13 @@
         <v>880</v>
       </c>
       <c r="P30" s="3">
-        <v>-5000</v>
+        <v>-3500</v>
       </c>
       <c r="Q30" s="3">
         <v>1</v>
       </c>
       <c r="R30" s="3">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="S30" s="3">
         <v>0</v>
@@ -4634,7 +4634,7 @@
         <v>25</v>
       </c>
       <c r="P31" s="3">
-        <v>-5000</v>
+        <v>-3500</v>
       </c>
       <c r="Q31" s="3">
         <v>1</v>
@@ -4741,7 +4741,7 @@
         <v>25</v>
       </c>
       <c r="P32" s="3">
-        <v>-5000</v>
+        <v>-3500</v>
       </c>
       <c r="Q32" s="3">
         <v>1</v>
@@ -4848,7 +4848,7 @@
         <v>25</v>
       </c>
       <c r="P33" s="3">
-        <v>-5000</v>
+        <v>-3500</v>
       </c>
       <c r="Q33" s="3">
         <v>1</v>
@@ -4955,7 +4955,7 @@
         <v>25</v>
       </c>
       <c r="P34" s="3">
-        <v>-5000</v>
+        <v>-3500</v>
       </c>
       <c r="Q34" s="3">
         <v>1</v>
@@ -5062,7 +5062,7 @@
         <v>25</v>
       </c>
       <c r="P35" s="3">
-        <v>-5000</v>
+        <v>-3500</v>
       </c>
       <c r="Q35" s="3">
         <v>1</v>
@@ -5169,7 +5169,7 @@
         <v>25</v>
       </c>
       <c r="P36" s="3">
-        <v>-5000</v>
+        <v>-3500</v>
       </c>
       <c r="Q36" s="3">
         <v>1</v>
@@ -5276,7 +5276,7 @@
         <v>25</v>
       </c>
       <c r="P37" s="3">
-        <v>-5000</v>
+        <v>-3500</v>
       </c>
       <c r="Q37" s="3">
         <v>1</v>
@@ -5383,7 +5383,7 @@
         <v>25</v>
       </c>
       <c r="P38" s="3">
-        <v>-5000</v>
+        <v>-3500</v>
       </c>
       <c r="Q38" s="3">
         <v>1</v>
@@ -5490,7 +5490,7 @@
         <v>25</v>
       </c>
       <c r="P39" s="3">
-        <v>-5000</v>
+        <v>-3500</v>
       </c>
       <c r="Q39" s="3">
         <v>1</v>
@@ -5597,7 +5597,7 @@
         <v>25</v>
       </c>
       <c r="P40" s="3">
-        <v>-5000</v>
+        <v>-3500</v>
       </c>
       <c r="Q40" s="3">
         <v>1</v>
@@ -5704,7 +5704,7 @@
         <v>25</v>
       </c>
       <c r="P41" s="3">
-        <v>-5000</v>
+        <v>-3500</v>
       </c>
       <c r="Q41" s="3">
         <v>1</v>
@@ -5811,7 +5811,7 @@
         <v>25</v>
       </c>
       <c r="P42" s="3">
-        <v>-5000</v>
+        <v>-3500</v>
       </c>
       <c r="Q42" s="3">
         <v>1</v>
@@ -5918,7 +5918,7 @@
         <v>25</v>
       </c>
       <c r="P43" s="3">
-        <v>-5000</v>
+        <v>-3500</v>
       </c>
       <c r="Q43" s="3">
         <v>1</v>
@@ -6025,7 +6025,7 @@
         <v>25</v>
       </c>
       <c r="P44" s="3">
-        <v>-5000</v>
+        <v>-3500</v>
       </c>
       <c r="Q44" s="3">
         <v>1</v>
@@ -6132,7 +6132,7 @@
         <v>25</v>
       </c>
       <c r="P45" s="3">
-        <v>-5000</v>
+        <v>-3500</v>
       </c>
       <c r="Q45" s="3">
         <v>1</v>
@@ -6239,7 +6239,7 @@
         <v>25</v>
       </c>
       <c r="P46" s="3">
-        <v>-5000</v>
+        <v>-3500</v>
       </c>
       <c r="Q46" s="3">
         <v>1</v>
@@ -6335,22 +6335,22 @@
         <v>0</v>
       </c>
       <c r="M47" s="3">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="N47" s="3">
         <v>1</v>
       </c>
       <c r="O47" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P47" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q47" s="3">
         <v>1</v>
       </c>
       <c r="R47" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S47" s="3">
         <v>2</v>
@@ -6440,22 +6440,22 @@
         <v>0</v>
       </c>
       <c r="M48" s="3">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="N48" s="3">
         <v>1</v>
       </c>
       <c r="O48" s="3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="P48" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q48" s="3">
         <v>1</v>
       </c>
       <c r="R48" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S48" s="3">
         <v>2</v>
@@ -6545,7 +6545,7 @@
         <v>0</v>
       </c>
       <c r="M49" s="3">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="N49" s="3">
         <v>1</v>
@@ -6554,13 +6554,13 @@
         <v>201</v>
       </c>
       <c r="P49" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q49" s="3">
         <v>1</v>
       </c>
       <c r="R49" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S49" s="3">
         <v>2</v>
@@ -6659,13 +6659,13 @@
         <v>30</v>
       </c>
       <c r="P50" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q50" s="3">
         <v>1</v>
       </c>
       <c r="R50" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S50" s="3">
         <v>2</v>
@@ -6764,13 +6764,13 @@
         <v>79</v>
       </c>
       <c r="P51" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q51" s="3">
         <v>1</v>
       </c>
       <c r="R51" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S51" s="3">
         <v>2</v>
@@ -6869,13 +6869,13 @@
         <v>338</v>
       </c>
       <c r="P52" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q52" s="3">
         <v>1</v>
       </c>
       <c r="R52" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S52" s="3">
         <v>2</v>
@@ -6974,13 +6974,13 @@
         <v>59</v>
       </c>
       <c r="P53" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q53" s="3">
         <v>1</v>
       </c>
       <c r="R53" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S53" s="3">
         <v>2</v>
@@ -7079,13 +7079,13 @@
         <v>158</v>
       </c>
       <c r="P54" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q54" s="3">
         <v>1</v>
       </c>
       <c r="R54" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S54" s="3">
         <v>2</v>
@@ -7184,13 +7184,13 @@
         <v>572</v>
       </c>
       <c r="P55" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q55" s="3">
         <v>1</v>
       </c>
       <c r="R55" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S55" s="3">
         <v>2</v>
@@ -7289,13 +7289,13 @@
         <v>153</v>
       </c>
       <c r="P56" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q56" s="3">
         <v>1</v>
       </c>
       <c r="R56" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S56" s="3">
         <v>2</v>
@@ -7394,13 +7394,13 @@
         <v>334</v>
       </c>
       <c r="P57" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q57" s="3">
         <v>1</v>
       </c>
       <c r="R57" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S57" s="3">
         <v>2</v>
@@ -7499,13 +7499,13 @@
         <v>1376</v>
       </c>
       <c r="P58" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q58" s="3">
         <v>1</v>
       </c>
       <c r="R58" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S58" s="3">
         <v>2</v>
@@ -7604,13 +7604,13 @@
         <v>231</v>
       </c>
       <c r="P59" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q59" s="3">
         <v>1</v>
       </c>
       <c r="R59" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S59" s="3">
         <v>2</v>
@@ -7709,13 +7709,13 @@
         <v>580</v>
       </c>
       <c r="P60" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q60" s="3">
         <v>1</v>
       </c>
       <c r="R60" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S60" s="3">
         <v>2</v>
@@ -7814,13 +7814,13 @@
         <v>2297</v>
       </c>
       <c r="P61" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q61" s="3">
         <v>1</v>
       </c>
       <c r="R61" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S61" s="3">
         <v>2</v>
@@ -7919,13 +7919,13 @@
         <v>229</v>
       </c>
       <c r="P62" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q62" s="3">
         <v>1</v>
       </c>
       <c r="R62" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S62" s="3">
         <v>1</v>
@@ -8024,13 +8024,13 @@
         <v>341</v>
       </c>
       <c r="P63" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q63" s="3">
         <v>1</v>
       </c>
       <c r="R63" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S63" s="3">
         <v>1</v>
@@ -8129,13 +8129,13 @@
         <v>857</v>
       </c>
       <c r="P64" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q64" s="3">
         <v>1</v>
       </c>
       <c r="R64" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S64" s="3">
         <v>1</v>
@@ -8234,13 +8234,13 @@
         <v>3516</v>
       </c>
       <c r="P65" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q65" s="3">
         <v>1</v>
       </c>
       <c r="R65" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S65" s="3">
         <v>1</v>
@@ -8339,13 +8339,13 @@
         <v>339</v>
       </c>
       <c r="P66" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q66" s="3">
         <v>1</v>
       </c>
       <c r="R66" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S66" s="3">
         <v>1</v>
@@ -8444,13 +8444,13 @@
         <v>1866</v>
       </c>
       <c r="P67" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q67" s="3">
         <v>1</v>
       </c>
       <c r="R67" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S67" s="3">
         <v>1</v>
@@ -8549,13 +8549,13 @@
         <v>3368</v>
       </c>
       <c r="P68" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q68" s="3">
         <v>1</v>
       </c>
       <c r="R68" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S68" s="3">
         <v>1</v>
@@ -8654,13 +8654,13 @@
         <v>12884</v>
       </c>
       <c r="P69" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q69" s="3">
         <v>1</v>
       </c>
       <c r="R69" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S69" s="3">
         <v>1</v>
@@ -8759,13 +8759,13 @@
         <v>1424</v>
       </c>
       <c r="P70" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q70" s="3">
         <v>1</v>
       </c>
       <c r="R70" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S70" s="3">
         <v>1</v>
@@ -8864,13 +8864,13 @@
         <v>554</v>
       </c>
       <c r="P71" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q71" s="3">
         <v>1</v>
       </c>
       <c r="R71" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S71" s="3">
         <v>1</v>
@@ -8969,13 +8969,13 @@
         <v>1515</v>
       </c>
       <c r="P72" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q72" s="3">
         <v>1</v>
       </c>
       <c r="R72" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S72" s="3">
         <v>1</v>
@@ -9074,13 +9074,13 @@
         <v>5505</v>
       </c>
       <c r="P73" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q73" s="3">
         <v>1</v>
       </c>
       <c r="R73" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S73" s="3">
         <v>1</v>
@@ -9179,13 +9179,13 @@
         <v>622</v>
       </c>
       <c r="P74" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q74" s="3">
         <v>1</v>
       </c>
       <c r="R74" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S74" s="3">
         <v>1</v>
@@ -9284,13 +9284,13 @@
         <v>2829</v>
       </c>
       <c r="P75" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q75" s="3">
         <v>1</v>
       </c>
       <c r="R75" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S75" s="3">
         <v>1</v>
@@ -9389,13 +9389,13 @@
         <v>5561</v>
       </c>
       <c r="P76" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q76" s="3">
         <v>1</v>
       </c>
       <c r="R76" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S76" s="3">
         <v>1</v>
@@ -9494,13 +9494,13 @@
         <v>18790</v>
       </c>
       <c r="P77" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q77" s="3">
         <v>1</v>
       </c>
       <c r="R77" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S77" s="3">
         <v>1</v>
@@ -9599,13 +9599,13 @@
         <v>2441</v>
       </c>
       <c r="P78" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q78" s="3">
         <v>1</v>
       </c>
       <c r="R78" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S78" s="3">
         <v>1</v>
@@ -9704,13 +9704,13 @@
         <v>7946</v>
       </c>
       <c r="P79" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q79" s="3">
         <v>1</v>
       </c>
       <c r="R79" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S79" s="3">
         <v>1</v>
@@ -9809,13 +9809,13 @@
         <v>13594</v>
       </c>
       <c r="P80" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q80" s="3">
         <v>1</v>
       </c>
       <c r="R80" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S80" s="3">
         <v>1</v>
@@ -9914,13 +9914,13 @@
         <v>35946</v>
       </c>
       <c r="P81" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q81" s="3">
         <v>1</v>
       </c>
       <c r="R81" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S81" s="3">
         <v>1</v>
@@ -10019,13 +10019,13 @@
         <v>6855</v>
       </c>
       <c r="P82" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q82" s="3">
         <v>1</v>
       </c>
       <c r="R82" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S82" s="3">
         <v>1</v>
@@ -10124,13 +10124,13 @@
         <v>145411</v>
       </c>
       <c r="P83" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q83" s="3">
         <v>1</v>
       </c>
       <c r="R83" s="3">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="S83" s="3">
         <v>1</v>
@@ -10231,7 +10231,7 @@
         <v>25</v>
       </c>
       <c r="P84" s="3">
-        <v>-6500</v>
+        <v>-3500</v>
       </c>
       <c r="Q84" s="3">
         <v>1</v>
@@ -10338,7 +10338,7 @@
         <v>58</v>
       </c>
       <c r="P85" s="3">
-        <v>-4750</v>
+        <v>-3500</v>
       </c>
       <c r="Q85" s="3">
         <v>1</v>
@@ -10444,8 +10444,8 @@
       <c r="O86" s="2">
         <v>300</v>
       </c>
-      <c r="P86" s="2">
-        <v>-5000</v>
+      <c r="P86" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q86" s="2">
         <v>1</v>
@@ -10552,7 +10552,7 @@
         <v>25</v>
       </c>
       <c r="P87" s="3">
-        <v>-6500</v>
+        <v>-3500</v>
       </c>
       <c r="Q87" s="3">
         <v>1</v>
@@ -10659,7 +10659,7 @@
         <v>30</v>
       </c>
       <c r="P88" s="3">
-        <v>-6500</v>
+        <v>-3500</v>
       </c>
       <c r="Q88" s="3">
         <v>1</v>
@@ -10765,8 +10765,8 @@
       <c r="O89" s="2">
         <v>36</v>
       </c>
-      <c r="P89" s="2">
-        <v>-5000</v>
+      <c r="P89" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q89" s="2">
         <v>1</v>
@@ -10872,8 +10872,8 @@
       <c r="O90" s="2">
         <v>36</v>
       </c>
-      <c r="P90" s="2">
-        <v>-5000</v>
+      <c r="P90" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q90" s="2">
         <v>1</v>
@@ -10979,8 +10979,8 @@
       <c r="O91" s="2">
         <v>36</v>
       </c>
-      <c r="P91" s="2">
-        <v>-5000</v>
+      <c r="P91" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q91" s="2">
         <v>1</v>
@@ -11086,8 +11086,8 @@
       <c r="O92" s="2">
         <v>36</v>
       </c>
-      <c r="P92" s="2">
-        <v>-5000</v>
+      <c r="P92" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q92" s="2">
         <v>1</v>
@@ -11193,8 +11193,8 @@
       <c r="O93" s="2">
         <v>36</v>
       </c>
-      <c r="P93" s="2">
-        <v>-5000</v>
+      <c r="P93" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q93" s="2">
         <v>1</v>
@@ -11300,8 +11300,8 @@
       <c r="O94" s="2">
         <v>36</v>
       </c>
-      <c r="P94" s="2">
-        <v>-5000</v>
+      <c r="P94" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q94" s="2">
         <v>1</v>
@@ -11407,8 +11407,8 @@
       <c r="O95" s="2">
         <v>36</v>
       </c>
-      <c r="P95" s="2">
-        <v>-5000</v>
+      <c r="P95" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q95" s="2">
         <v>1</v>
@@ -11515,7 +11515,7 @@
         <v>712</v>
       </c>
       <c r="P96" s="3">
-        <v>-1600</v>
+        <v>-3500</v>
       </c>
       <c r="Q96" s="3">
         <v>1</v>
@@ -11621,8 +11621,8 @@
       <c r="O97" s="2">
         <v>36</v>
       </c>
-      <c r="P97" s="2">
-        <v>-5000</v>
+      <c r="P97" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q97" s="2">
         <v>1</v>
@@ -11728,8 +11728,8 @@
       <c r="O98" s="2">
         <v>36</v>
       </c>
-      <c r="P98" s="2">
-        <v>-5000</v>
+      <c r="P98" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q98" s="2">
         <v>1</v>
@@ -11835,8 +11835,8 @@
       <c r="O99" s="19">
         <v>10000</v>
       </c>
-      <c r="P99" s="19">
-        <v>-5000</v>
+      <c r="P99" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q99" s="19">
         <v>1</v>
@@ -11942,8 +11942,8 @@
       <c r="O100" s="19">
         <v>10000</v>
       </c>
-      <c r="P100" s="19">
-        <v>-5000</v>
+      <c r="P100" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q100" s="19">
         <v>1</v>
@@ -12049,8 +12049,8 @@
       <c r="O101" s="19">
         <v>10</v>
       </c>
-      <c r="P101" s="19">
-        <v>-5000</v>
+      <c r="P101" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q101" s="19">
         <v>1</v>
@@ -12156,8 +12156,8 @@
       <c r="O102" s="19">
         <v>10</v>
       </c>
-      <c r="P102" s="19">
-        <v>-5000</v>
+      <c r="P102" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q102" s="19">
         <v>1</v>
@@ -12263,8 +12263,8 @@
       <c r="O103" s="19">
         <v>300</v>
       </c>
-      <c r="P103" s="19">
-        <v>-5000</v>
+      <c r="P103" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q103" s="19">
         <v>1</v>
@@ -12370,8 +12370,8 @@
       <c r="O104" s="19">
         <v>300</v>
       </c>
-      <c r="P104" s="19">
-        <v>-5000</v>
+      <c r="P104" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q104" s="19">
         <v>1</v>
@@ -12477,8 +12477,8 @@
       <c r="O105" s="19">
         <v>300</v>
       </c>
-      <c r="P105" s="19">
-        <v>-5000</v>
+      <c r="P105" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q105" s="19">
         <v>1</v>
@@ -12584,8 +12584,8 @@
       <c r="O106" s="19">
         <v>300</v>
       </c>
-      <c r="P106" s="19">
-        <v>-5000</v>
+      <c r="P106" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q106" s="19">
         <v>1</v>
@@ -12691,8 +12691,8 @@
       <c r="O107" s="19">
         <v>1760</v>
       </c>
-      <c r="P107" s="19">
-        <v>-5000</v>
+      <c r="P107" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q107" s="19">
         <v>1</v>
@@ -12798,8 +12798,8 @@
       <c r="O108" s="13">
         <v>99999999</v>
       </c>
-      <c r="P108" s="13">
-        <v>-5500</v>
+      <c r="P108" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q108" s="13">
         <v>1</v>
@@ -12905,8 +12905,8 @@
       <c r="O109" s="13">
         <v>99999999</v>
       </c>
-      <c r="P109" s="13">
-        <v>-5500</v>
+      <c r="P109" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q109" s="13">
         <v>1</v>
@@ -13012,8 +13012,8 @@
       <c r="O110" s="13">
         <v>99999999</v>
       </c>
-      <c r="P110" s="13">
-        <v>-5500</v>
+      <c r="P110" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q110" s="13">
         <v>1</v>
@@ -13119,8 +13119,8 @@
       <c r="O111" s="13">
         <v>99999999</v>
       </c>
-      <c r="P111" s="13">
-        <v>-5500</v>
+      <c r="P111" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q111" s="13">
         <v>1</v>
@@ -13227,7 +13227,7 @@
         <v>20</v>
       </c>
       <c r="P112" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q112" s="3">
         <v>1</v>
@@ -13334,7 +13334,7 @@
         <v>105</v>
       </c>
       <c r="P113" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q113" s="3">
         <v>1</v>
@@ -13440,8 +13440,8 @@
       <c r="O114" s="2">
         <v>300</v>
       </c>
-      <c r="P114" s="2">
-        <v>-5500</v>
+      <c r="P114" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q114" s="2">
         <v>1</v>
@@ -13548,7 +13548,7 @@
         <v>17</v>
       </c>
       <c r="P115" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q115" s="3">
         <v>1</v>
@@ -13655,7 +13655,7 @@
         <v>43</v>
       </c>
       <c r="P116" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q116" s="3">
         <v>1</v>
@@ -13761,8 +13761,8 @@
       <c r="O117" s="2">
         <v>36</v>
       </c>
-      <c r="P117" s="2">
-        <v>-5500</v>
+      <c r="P117" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q117" s="2">
         <v>1</v>
@@ -13868,8 +13868,8 @@
       <c r="O118" s="2">
         <v>36</v>
       </c>
-      <c r="P118" s="2">
-        <v>-5500</v>
+      <c r="P118" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q118" s="2">
         <v>1</v>
@@ -13976,7 +13976,7 @@
         <v>36</v>
       </c>
       <c r="P119" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q119" s="3">
         <v>1</v>
@@ -14083,7 +14083,7 @@
         <v>36</v>
       </c>
       <c r="P120" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q120" s="3">
         <v>1</v>
@@ -14190,7 +14190,7 @@
         <v>36</v>
       </c>
       <c r="P121" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q121" s="3">
         <v>1</v>
@@ -14297,7 +14297,7 @@
         <v>36</v>
       </c>
       <c r="P122" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q122" s="3">
         <v>1</v>
@@ -14404,7 +14404,7 @@
         <v>36</v>
       </c>
       <c r="P123" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q123" s="3">
         <v>1</v>
@@ -14511,7 +14511,7 @@
         <v>1496</v>
       </c>
       <c r="P124" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q124" s="3">
         <v>1</v>
@@ -14618,7 +14618,7 @@
         <v>36</v>
       </c>
       <c r="P125" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q125" s="3">
         <v>1</v>
@@ -14724,8 +14724,8 @@
       <c r="O126" s="2">
         <v>36</v>
       </c>
-      <c r="P126" s="2">
-        <v>-5500</v>
+      <c r="P126" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q126" s="2">
         <v>1</v>
@@ -14832,7 +14832,7 @@
         <v>86</v>
       </c>
       <c r="P127" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q127" s="3">
         <v>1</v>
@@ -14939,7 +14939,7 @@
         <v>292</v>
       </c>
       <c r="P128" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q128" s="3">
         <v>1</v>
@@ -15045,8 +15045,8 @@
       <c r="O129" s="2">
         <v>300</v>
       </c>
-      <c r="P129" s="2">
-        <v>-5500</v>
+      <c r="P129" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q129" s="2">
         <v>1</v>
@@ -15153,7 +15153,7 @@
         <v>69</v>
       </c>
       <c r="P130" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q130" s="3">
         <v>1</v>
@@ -15260,7 +15260,7 @@
         <v>131</v>
       </c>
       <c r="P131" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q131" s="3">
         <v>1</v>
@@ -15366,8 +15366,8 @@
       <c r="O132" s="2">
         <v>36</v>
       </c>
-      <c r="P132" s="2">
-        <v>-5500</v>
+      <c r="P132" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q132" s="2">
         <v>1</v>
@@ -15473,8 +15473,8 @@
       <c r="O133" s="2">
         <v>36</v>
       </c>
-      <c r="P133" s="2">
-        <v>-5500</v>
+      <c r="P133" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q133" s="2">
         <v>1</v>
@@ -15580,8 +15580,8 @@
       <c r="O134" s="2">
         <v>36</v>
       </c>
-      <c r="P134" s="2">
-        <v>-5500</v>
+      <c r="P134" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q134" s="2">
         <v>1</v>
@@ -15687,8 +15687,8 @@
       <c r="O135" s="2">
         <v>36</v>
       </c>
-      <c r="P135" s="2">
-        <v>-5500</v>
+      <c r="P135" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q135" s="2">
         <v>1</v>
@@ -15794,8 +15794,8 @@
       <c r="O136" s="2">
         <v>36</v>
       </c>
-      <c r="P136" s="2">
-        <v>-5500</v>
+      <c r="P136" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q136" s="2">
         <v>1</v>
@@ -15901,8 +15901,8 @@
       <c r="O137" s="2">
         <v>36</v>
       </c>
-      <c r="P137" s="2">
-        <v>-5500</v>
+      <c r="P137" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q137" s="2">
         <v>1</v>
@@ -16008,8 +16008,8 @@
       <c r="O138" s="2">
         <v>36</v>
       </c>
-      <c r="P138" s="2">
-        <v>-5500</v>
+      <c r="P138" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q138" s="2">
         <v>1</v>
@@ -16116,7 +16116,7 @@
         <v>1496</v>
       </c>
       <c r="P139" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q139" s="3">
         <v>1</v>
@@ -16222,8 +16222,8 @@
       <c r="O140" s="2">
         <v>36</v>
       </c>
-      <c r="P140" s="2">
-        <v>-5500</v>
+      <c r="P140" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q140" s="2">
         <v>1</v>
@@ -16329,8 +16329,8 @@
       <c r="O141" s="2">
         <v>36</v>
       </c>
-      <c r="P141" s="2">
-        <v>-5500</v>
+      <c r="P141" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q141" s="2">
         <v>1</v>
@@ -16437,7 +16437,7 @@
         <v>211</v>
       </c>
       <c r="P142" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q142" s="3">
         <v>1</v>
@@ -16544,7 +16544,7 @@
         <v>570</v>
       </c>
       <c r="P143" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q143" s="3">
         <v>1</v>
@@ -16650,8 +16650,8 @@
       <c r="O144" s="2">
         <v>300</v>
       </c>
-      <c r="P144" s="2">
-        <v>-5500</v>
+      <c r="P144" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q144" s="2">
         <v>1</v>
@@ -16758,7 +16758,7 @@
         <v>169</v>
       </c>
       <c r="P145" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q145" s="3">
         <v>1</v>
@@ -16865,7 +16865,7 @@
         <v>301</v>
       </c>
       <c r="P146" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q146" s="3">
         <v>1</v>
@@ -16971,8 +16971,8 @@
       <c r="O147" s="2">
         <v>36</v>
       </c>
-      <c r="P147" s="2">
-        <v>-5500</v>
+      <c r="P147" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q147" s="2">
         <v>1</v>
@@ -17078,8 +17078,8 @@
       <c r="O148" s="2">
         <v>36</v>
       </c>
-      <c r="P148" s="2">
-        <v>-5500</v>
+      <c r="P148" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q148" s="2">
         <v>1</v>
@@ -17185,8 +17185,8 @@
       <c r="O149" s="2">
         <v>36</v>
       </c>
-      <c r="P149" s="2">
-        <v>-5500</v>
+      <c r="P149" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q149" s="2">
         <v>1</v>
@@ -17292,8 +17292,8 @@
       <c r="O150" s="2">
         <v>36</v>
       </c>
-      <c r="P150" s="2">
-        <v>-5500</v>
+      <c r="P150" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q150" s="2">
         <v>1</v>
@@ -17399,8 +17399,8 @@
       <c r="O151" s="2">
         <v>36</v>
       </c>
-      <c r="P151" s="2">
-        <v>-5500</v>
+      <c r="P151" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q151" s="2">
         <v>1</v>
@@ -17506,8 +17506,8 @@
       <c r="O152" s="2">
         <v>36</v>
       </c>
-      <c r="P152" s="2">
-        <v>-5500</v>
+      <c r="P152" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q152" s="2">
         <v>1</v>
@@ -17613,8 +17613,8 @@
       <c r="O153" s="2">
         <v>36</v>
       </c>
-      <c r="P153" s="2">
-        <v>-5500</v>
+      <c r="P153" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q153" s="2">
         <v>1</v>
@@ -17721,7 +17721,7 @@
         <v>570</v>
       </c>
       <c r="P154" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q154" s="3">
         <v>1</v>
@@ -17827,8 +17827,8 @@
       <c r="O155" s="2">
         <v>36</v>
       </c>
-      <c r="P155" s="2">
-        <v>-5500</v>
+      <c r="P155" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q155" s="2">
         <v>1</v>
@@ -17935,7 +17935,7 @@
         <v>3740</v>
       </c>
       <c r="P156" s="3">
-        <v>-5500</v>
+        <v>-3500</v>
       </c>
       <c r="Q156" s="3">
         <v>1</v>
@@ -18041,8 +18041,8 @@
       <c r="O157" s="24">
         <v>25</v>
       </c>
-      <c r="P157" s="24">
-        <v>-5000</v>
+      <c r="P157" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q157" s="24">
         <v>1</v>
@@ -18148,8 +18148,8 @@
       <c r="O158" s="24">
         <v>25</v>
       </c>
-      <c r="P158" s="24">
-        <v>-5000</v>
+      <c r="P158" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q158" s="24">
         <v>1</v>
@@ -18255,8 +18255,8 @@
       <c r="O159" s="24">
         <v>25</v>
       </c>
-      <c r="P159" s="24">
-        <v>-5000</v>
+      <c r="P159" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q159" s="24">
         <v>1</v>
@@ -18362,8 +18362,8 @@
       <c r="O160" s="24">
         <v>25</v>
       </c>
-      <c r="P160" s="24">
-        <v>-5000</v>
+      <c r="P160" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q160" s="24">
         <v>1</v>
@@ -18469,8 +18469,8 @@
       <c r="O161" s="24">
         <v>25</v>
       </c>
-      <c r="P161" s="24">
-        <v>-5000</v>
+      <c r="P161" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q161" s="24">
         <v>1</v>
@@ -18576,8 +18576,8 @@
       <c r="O162" s="24">
         <v>25</v>
       </c>
-      <c r="P162" s="24">
-        <v>-5000</v>
+      <c r="P162" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q162" s="24">
         <v>1</v>
@@ -18683,8 +18683,8 @@
       <c r="O163" s="24">
         <v>25</v>
       </c>
-      <c r="P163" s="24">
-        <v>-5000</v>
+      <c r="P163" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q163" s="24">
         <v>1</v>
@@ -18790,8 +18790,8 @@
       <c r="O164" s="24">
         <v>25</v>
       </c>
-      <c r="P164" s="24">
-        <v>-5000</v>
+      <c r="P164" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q164" s="24">
         <v>1</v>
@@ -18897,8 +18897,8 @@
       <c r="O165" s="24">
         <v>25</v>
       </c>
-      <c r="P165" s="24">
-        <v>-5000</v>
+      <c r="P165" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q165" s="24">
         <v>1</v>
@@ -19004,8 +19004,8 @@
       <c r="O166" s="32">
         <v>25</v>
       </c>
-      <c r="P166" s="32">
-        <v>-5000</v>
+      <c r="P166" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q166" s="32">
         <v>1</v>
@@ -19111,8 +19111,8 @@
       <c r="O167" s="24">
         <v>25</v>
       </c>
-      <c r="P167" s="24">
-        <v>-5000</v>
+      <c r="P167" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q167" s="24">
         <v>1</v>
@@ -19218,8 +19218,8 @@
       <c r="O168" s="24">
         <v>25</v>
       </c>
-      <c r="P168" s="24">
-        <v>-5000</v>
+      <c r="P168" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q168" s="24">
         <v>1</v>
@@ -19325,8 +19325,8 @@
       <c r="O169" s="24">
         <v>25</v>
       </c>
-      <c r="P169" s="24">
-        <v>-5000</v>
+      <c r="P169" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q169" s="24">
         <v>1</v>
@@ -19432,8 +19432,8 @@
       <c r="O170" s="24">
         <v>25</v>
       </c>
-      <c r="P170" s="24">
-        <v>-5000</v>
+      <c r="P170" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q170" s="24">
         <v>1</v>
@@ -19539,8 +19539,8 @@
       <c r="O171" s="24">
         <v>25</v>
       </c>
-      <c r="P171" s="24">
-        <v>-5000</v>
+      <c r="P171" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q171" s="24">
         <v>1</v>
@@ -19646,8 +19646,8 @@
       <c r="O172" s="24">
         <v>25</v>
       </c>
-      <c r="P172" s="24">
-        <v>-5000</v>
+      <c r="P172" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q172" s="24">
         <v>1</v>
@@ -19753,8 +19753,8 @@
       <c r="O173" s="24">
         <v>25</v>
       </c>
-      <c r="P173" s="24">
-        <v>-5000</v>
+      <c r="P173" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q173" s="24">
         <v>1</v>
@@ -19860,8 +19860,8 @@
       <c r="O174" s="24">
         <v>25</v>
       </c>
-      <c r="P174" s="24">
-        <v>-5000</v>
+      <c r="P174" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q174" s="24">
         <v>1</v>
@@ -19967,8 +19967,8 @@
       <c r="O175" s="24">
         <v>25</v>
       </c>
-      <c r="P175" s="24">
-        <v>-5000</v>
+      <c r="P175" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q175" s="24">
         <v>1</v>
@@ -20074,8 +20074,8 @@
       <c r="O176" s="24">
         <v>25</v>
       </c>
-      <c r="P176" s="24">
-        <v>-5000</v>
+      <c r="P176" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q176" s="24">
         <v>1</v>
@@ -20181,8 +20181,8 @@
       <c r="O177" s="24">
         <v>25</v>
       </c>
-      <c r="P177" s="24">
-        <v>-5000</v>
+      <c r="P177" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q177" s="24">
         <v>1</v>
@@ -20288,8 +20288,8 @@
       <c r="O178" s="24">
         <v>25</v>
       </c>
-      <c r="P178" s="24">
-        <v>-5000</v>
+      <c r="P178" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q178" s="24">
         <v>1</v>
@@ -20395,8 +20395,8 @@
       <c r="O179" s="24">
         <v>25</v>
       </c>
-      <c r="P179" s="24">
-        <v>-5000</v>
+      <c r="P179" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q179" s="24">
         <v>1</v>
@@ -20502,8 +20502,8 @@
       <c r="O180" s="24">
         <v>25</v>
       </c>
-      <c r="P180" s="24">
-        <v>-5000</v>
+      <c r="P180" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q180" s="24">
         <v>1</v>
@@ -20609,8 +20609,8 @@
       <c r="O181" s="24">
         <v>25</v>
       </c>
-      <c r="P181" s="24">
-        <v>-5000</v>
+      <c r="P181" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q181" s="24">
         <v>1</v>
@@ -20716,8 +20716,8 @@
       <c r="O182" s="24">
         <v>25</v>
       </c>
-      <c r="P182" s="24">
-        <v>-5000</v>
+      <c r="P182" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q182" s="24">
         <v>1</v>
@@ -20823,8 +20823,8 @@
       <c r="O183" s="24">
         <v>25</v>
       </c>
-      <c r="P183" s="24">
-        <v>-5000</v>
+      <c r="P183" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q183" s="24">
         <v>1</v>
@@ -20930,8 +20930,8 @@
       <c r="O184" s="24">
         <v>25</v>
       </c>
-      <c r="P184" s="24">
-        <v>-5000</v>
+      <c r="P184" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q184" s="24">
         <v>1</v>
@@ -21037,8 +21037,8 @@
       <c r="O185" s="24">
         <v>25</v>
       </c>
-      <c r="P185" s="24">
-        <v>-5000</v>
+      <c r="P185" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q185" s="24">
         <v>1</v>
@@ -21144,8 +21144,8 @@
       <c r="O186" s="24">
         <v>25</v>
       </c>
-      <c r="P186" s="24">
-        <v>-5000</v>
+      <c r="P186" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q186" s="24">
         <v>1</v>
@@ -21251,8 +21251,8 @@
       <c r="O187" s="24">
         <v>25</v>
       </c>
-      <c r="P187" s="24">
-        <v>-5000</v>
+      <c r="P187" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q187" s="24">
         <v>1</v>
@@ -21358,8 +21358,8 @@
       <c r="O188" s="24">
         <v>25</v>
       </c>
-      <c r="P188" s="24">
-        <v>-5000</v>
+      <c r="P188" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q188" s="24">
         <v>1</v>
@@ -21465,8 +21465,8 @@
       <c r="O189" s="24">
         <v>25</v>
       </c>
-      <c r="P189" s="24">
-        <v>-5000</v>
+      <c r="P189" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q189" s="24">
         <v>1</v>
@@ -21572,8 +21572,8 @@
       <c r="O190" s="24">
         <v>25</v>
       </c>
-      <c r="P190" s="24">
-        <v>-5000</v>
+      <c r="P190" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q190" s="24">
         <v>1</v>
@@ -21679,8 +21679,8 @@
       <c r="O191" s="24">
         <v>25</v>
       </c>
-      <c r="P191" s="24">
-        <v>-5000</v>
+      <c r="P191" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q191" s="24">
         <v>1</v>
@@ -21786,8 +21786,8 @@
       <c r="O192" s="24">
         <v>25</v>
       </c>
-      <c r="P192" s="24">
-        <v>-5000</v>
+      <c r="P192" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q192" s="24">
         <v>1</v>
@@ -21893,8 +21893,8 @@
       <c r="O193" s="24">
         <v>25</v>
       </c>
-      <c r="P193" s="24">
-        <v>-5000</v>
+      <c r="P193" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q193" s="24">
         <v>1</v>
@@ -22000,8 +22000,8 @@
       <c r="O194" s="24">
         <v>25</v>
       </c>
-      <c r="P194" s="24">
-        <v>-5000</v>
+      <c r="P194" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q194" s="24">
         <v>1</v>
@@ -22107,8 +22107,8 @@
       <c r="O195" s="24">
         <v>25</v>
       </c>
-      <c r="P195" s="24">
-        <v>-5000</v>
+      <c r="P195" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q195" s="24">
         <v>1</v>
@@ -22214,8 +22214,8 @@
       <c r="O196" s="24">
         <v>25</v>
       </c>
-      <c r="P196" s="24">
-        <v>-5000</v>
+      <c r="P196" s="3">
+        <v>-3500</v>
       </c>
       <c r="Q196" s="24">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55AB24EE-F142-41A4-9DAF-7570D8622EC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF64DEE3-B447-4833-BE39-96336BF7EA63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_foe_v8" sheetId="1" r:id="rId1"/>
@@ -6341,7 +6341,7 @@
         <v>1</v>
       </c>
       <c r="O47" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P47" s="3">
         <v>-3500</v>
@@ -6446,7 +6446,7 @@
         <v>1</v>
       </c>
       <c r="O48" s="3">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="P48" s="3">
         <v>-3500</v>
@@ -6551,7 +6551,7 @@
         <v>1</v>
       </c>
       <c r="O49" s="3">
-        <v>201</v>
+        <v>150</v>
       </c>
       <c r="P49" s="3">
         <v>-3500</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF64DEE3-B447-4833-BE39-96336BF7EA63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE2A4E91-D51C-47B7-9255-EEF984E00306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6335,7 +6335,7 @@
         <v>0</v>
       </c>
       <c r="M47" s="3">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="N47" s="3">
         <v>1</v>
@@ -6440,13 +6440,13 @@
         <v>0</v>
       </c>
       <c r="M48" s="3">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="N48" s="3">
         <v>1</v>
       </c>
       <c r="O48" s="3">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="P48" s="3">
         <v>-3500</v>
@@ -6545,7 +6545,7 @@
         <v>0</v>
       </c>
       <c r="M49" s="3">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="N49" s="3">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE2A4E91-D51C-47B7-9255-EEF984E00306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D095FBD5-7AE3-4868-BDBD-78046373F88C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6335,7 +6335,7 @@
         <v>0</v>
       </c>
       <c r="M47" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N47" s="3">
         <v>1</v>
@@ -6440,7 +6440,7 @@
         <v>0</v>
       </c>
       <c r="M48" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N48" s="3">
         <v>1</v>
@@ -6545,7 +6545,7 @@
         <v>0</v>
       </c>
       <c r="M49" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N49" s="3">
         <v>1</v>
@@ -18455,7 +18455,7 @@
         <v>1</v>
       </c>
       <c r="K161" s="26">
-        <v>6</v>
+        <v>-3</v>
       </c>
       <c r="L161" s="3">
         <v>0</v>
@@ -18562,7 +18562,7 @@
         <v>1</v>
       </c>
       <c r="K162" s="26">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="L162" s="3">
         <v>0</v>
@@ -18669,7 +18669,7 @@
         <v>1</v>
       </c>
       <c r="K163" s="26">
-        <v>8</v>
+        <v>-2</v>
       </c>
       <c r="L163" s="3">
         <v>0</v>
@@ -18776,7 +18776,7 @@
         <v>1</v>
       </c>
       <c r="K164" s="26">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="L164" s="3">
         <v>0</v>
@@ -18883,7 +18883,7 @@
         <v>1</v>
       </c>
       <c r="K165" s="26">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="L165" s="3">
         <v>0</v>
@@ -18990,7 +18990,7 @@
         <v>1</v>
       </c>
       <c r="K166" s="35">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L166" s="3">
         <v>0</v>
@@ -19097,7 +19097,7 @@
         <v>1</v>
       </c>
       <c r="K167" s="26">
-        <v>8</v>
+        <v>-3</v>
       </c>
       <c r="L167" s="3">
         <v>0</v>
@@ -19204,7 +19204,7 @@
         <v>1</v>
       </c>
       <c r="K168" s="26">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="L168" s="3">
         <v>0</v>
@@ -19311,7 +19311,7 @@
         <v>1</v>
       </c>
       <c r="K169" s="26">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="L169" s="3">
         <v>0</v>
@@ -19418,7 +19418,7 @@
         <v>1</v>
       </c>
       <c r="K170" s="26">
-        <v>8</v>
+        <v>-3</v>
       </c>
       <c r="L170" s="3">
         <v>0</v>
@@ -19525,7 +19525,7 @@
         <v>1</v>
       </c>
       <c r="K171" s="26">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="L171" s="3">
         <v>0</v>
@@ -19632,7 +19632,7 @@
         <v>1</v>
       </c>
       <c r="K172" s="26">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="L172" s="3">
         <v>0</v>
@@ -19739,7 +19739,7 @@
         <v>1</v>
       </c>
       <c r="K173" s="26">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="L173" s="3">
         <v>0</v>
@@ -19846,7 +19846,7 @@
         <v>1</v>
       </c>
       <c r="K174" s="26">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="L174" s="3">
         <v>0</v>
@@ -19953,7 +19953,7 @@
         <v>1</v>
       </c>
       <c r="K175" s="26">
-        <v>240</v>
+        <v>12</v>
       </c>
       <c r="L175" s="3">
         <v>0</v>
@@ -20060,7 +20060,7 @@
         <v>1</v>
       </c>
       <c r="K176" s="26">
-        <v>350</v>
+        <v>15</v>
       </c>
       <c r="L176" s="3">
         <v>0</v>
@@ -20167,7 +20167,7 @@
         <v>1</v>
       </c>
       <c r="K177" s="26">
-        <v>900</v>
+        <v>20</v>
       </c>
       <c r="L177" s="3">
         <v>0</v>
@@ -20274,7 +20274,7 @@
         <v>1</v>
       </c>
       <c r="K178" s="26">
-        <v>9</v>
+        <v>-3</v>
       </c>
       <c r="L178" s="3">
         <v>0</v>
@@ -20381,7 +20381,7 @@
         <v>1</v>
       </c>
       <c r="K179" s="26">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="L179" s="3">
         <v>0</v>
@@ -20488,7 +20488,7 @@
         <v>1</v>
       </c>
       <c r="K180" s="26">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="L180" s="3">
         <v>0</v>
@@ -20595,7 +20595,7 @@
         <v>1</v>
       </c>
       <c r="K181" s="26">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="L181" s="3">
         <v>0</v>
@@ -20702,7 +20702,7 @@
         <v>1</v>
       </c>
       <c r="K182" s="26">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="L182" s="3">
         <v>0</v>
@@ -20809,7 +20809,7 @@
         <v>1</v>
       </c>
       <c r="K183" s="26">
-        <v>135</v>
+        <v>9</v>
       </c>
       <c r="L183" s="3">
         <v>0</v>
@@ -20916,7 +20916,7 @@
         <v>1</v>
       </c>
       <c r="K184" s="26">
-        <v>250</v>
+        <v>13</v>
       </c>
       <c r="L184" s="3">
         <v>0</v>
@@ -21023,7 +21023,7 @@
         <v>1</v>
       </c>
       <c r="K185" s="26">
-        <v>450</v>
+        <v>17</v>
       </c>
       <c r="L185" s="3">
         <v>0</v>
@@ -21130,7 +21130,7 @@
         <v>1</v>
       </c>
       <c r="K186" s="26">
-        <v>500</v>
+        <v>19</v>
       </c>
       <c r="L186" s="3">
         <v>0</v>
@@ -21237,7 +21237,7 @@
         <v>1</v>
       </c>
       <c r="K187" s="26">
-        <v>1200</v>
+        <v>20</v>
       </c>
       <c r="L187" s="3">
         <v>0</v>
@@ -21344,7 +21344,7 @@
         <v>1</v>
       </c>
       <c r="K188" s="26">
-        <v>1500</v>
+        <v>24</v>
       </c>
       <c r="L188" s="3">
         <v>0</v>
@@ -21451,7 +21451,7 @@
         <v>1</v>
       </c>
       <c r="K189" s="26">
-        <v>3200</v>
+        <v>27</v>
       </c>
       <c r="L189" s="3">
         <v>0</v>
@@ -21558,7 +21558,7 @@
         <v>1</v>
       </c>
       <c r="K190" s="26">
-        <v>3500</v>
+        <v>30</v>
       </c>
       <c r="L190" s="3">
         <v>0</v>
@@ -21665,7 +21665,7 @@
         <v>1</v>
       </c>
       <c r="K191" s="26">
-        <v>11000</v>
+        <v>37</v>
       </c>
       <c r="L191" s="3">
         <v>0</v>
@@ -21772,7 +21772,7 @@
         <v>1</v>
       </c>
       <c r="K192" s="26">
-        <v>12000</v>
+        <v>39</v>
       </c>
       <c r="L192" s="3">
         <v>0</v>
@@ -21879,7 +21879,7 @@
         <v>1</v>
       </c>
       <c r="K193" s="26">
-        <v>22000</v>
+        <v>44</v>
       </c>
       <c r="L193" s="3">
         <v>0</v>
@@ -21986,7 +21986,7 @@
         <v>1</v>
       </c>
       <c r="K194" s="26">
-        <v>50000</v>
+        <v>46</v>
       </c>
       <c r="L194" s="3">
         <v>0</v>
@@ -22093,7 +22093,7 @@
         <v>1</v>
       </c>
       <c r="K195" s="26">
-        <v>70000</v>
+        <v>50</v>
       </c>
       <c r="L195" s="3">
         <v>0</v>
@@ -22200,7 +22200,7 @@
         <v>1</v>
       </c>
       <c r="K196" s="26">
-        <v>120000</v>
+        <v>52</v>
       </c>
       <c r="L196" s="3">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D095FBD5-7AE3-4868-BDBD-78046373F88C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B047921B-200A-4D1C-946C-F4CB0B2E7F3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_foe_v8" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="939" uniqueCount="247">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -790,6 +790,10 @@
   <si>
     <t>石像怪</t>
   </si>
+  <si>
+    <t>精英1</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -6306,7 +6310,9 @@
       <c r="B47" s="3">
         <v>1</v>
       </c>
-      <c r="C47" s="3"/>
+      <c r="C47" s="3" t="s">
+        <v>92</v>
+      </c>
       <c r="D47" s="3">
         <v>1</v>
       </c>
@@ -6329,28 +6335,28 @@
         <v>1</v>
       </c>
       <c r="K47" s="3">
-        <v>67</v>
+        <v>104</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
       <c r="M47" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N47" s="3">
         <v>1</v>
       </c>
       <c r="O47" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P47" s="3">
-        <v>-3500</v>
+        <v>-5500</v>
       </c>
       <c r="Q47" s="3">
         <v>1</v>
       </c>
       <c r="R47" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S47" s="3">
         <v>2</v>
@@ -6398,7 +6404,7 @@
         <v>10000</v>
       </c>
       <c r="AH47" s="9">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="AI47" s="9">
         <v>0</v>
@@ -6411,7 +6417,9 @@
       <c r="B48" s="3">
         <v>1</v>
       </c>
-      <c r="C48" s="3"/>
+      <c r="C48" s="3" t="s">
+        <v>95</v>
+      </c>
       <c r="D48" s="3">
         <v>1</v>
       </c>
@@ -6434,28 +6442,28 @@
         <v>1</v>
       </c>
       <c r="K48" s="3">
-        <v>76</v>
+        <v>119</v>
       </c>
       <c r="L48" s="3">
         <v>0</v>
       </c>
       <c r="M48" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N48" s="3">
         <v>1</v>
       </c>
       <c r="O48" s="3">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="P48" s="3">
-        <v>-3500</v>
+        <v>-5500</v>
       </c>
       <c r="Q48" s="3">
         <v>1</v>
       </c>
       <c r="R48" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S48" s="3">
         <v>2</v>
@@ -6503,7 +6511,7 @@
         <v>10000</v>
       </c>
       <c r="AH48" s="9">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AI48" s="9">
         <v>0</v>
@@ -6516,7 +6524,9 @@
       <c r="B49" s="3">
         <v>1</v>
       </c>
-      <c r="C49" s="3"/>
+      <c r="C49" s="3" t="s">
+        <v>98</v>
+      </c>
       <c r="D49" s="3">
         <v>1</v>
       </c>
@@ -6539,28 +6549,28 @@
         <v>1</v>
       </c>
       <c r="K49" s="3">
-        <v>105</v>
+        <v>164</v>
       </c>
       <c r="L49" s="3">
         <v>0</v>
       </c>
       <c r="M49" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N49" s="3">
         <v>1</v>
       </c>
       <c r="O49" s="3">
-        <v>150</v>
+        <v>241</v>
       </c>
       <c r="P49" s="3">
-        <v>-3500</v>
+        <v>-5500</v>
       </c>
       <c r="Q49" s="3">
         <v>1</v>
       </c>
       <c r="R49" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S49" s="3">
         <v>2</v>
@@ -6621,7 +6631,9 @@
       <c r="B50" s="3">
         <v>1</v>
       </c>
-      <c r="C50" s="3"/>
+      <c r="C50" s="3" t="s">
+        <v>92</v>
+      </c>
       <c r="D50" s="3">
         <v>2</v>
       </c>
@@ -6644,28 +6656,28 @@
         <v>2</v>
       </c>
       <c r="K50" s="3">
-        <v>101</v>
+        <v>154</v>
       </c>
       <c r="L50" s="3">
         <v>0</v>
       </c>
       <c r="M50" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="N50" s="3">
         <v>1</v>
       </c>
       <c r="O50" s="3">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="P50" s="3">
-        <v>-3500</v>
+        <v>-5500</v>
       </c>
       <c r="Q50" s="3">
         <v>1</v>
       </c>
       <c r="R50" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S50" s="3">
         <v>2</v>
@@ -6713,7 +6725,7 @@
         <v>10000</v>
       </c>
       <c r="AH50" s="9">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="AI50" s="9">
         <v>0</v>
@@ -6726,7 +6738,9 @@
       <c r="B51" s="3">
         <v>1</v>
       </c>
-      <c r="C51" s="3"/>
+      <c r="C51" s="3" t="s">
+        <v>95</v>
+      </c>
       <c r="D51" s="3">
         <v>2</v>
       </c>
@@ -6749,28 +6763,28 @@
         <v>2</v>
       </c>
       <c r="K51" s="3">
-        <v>115</v>
+        <v>176</v>
       </c>
       <c r="L51" s="3">
         <v>0</v>
       </c>
       <c r="M51" s="3">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="N51" s="3">
         <v>1</v>
       </c>
       <c r="O51" s="3">
-        <v>79</v>
+        <v>119</v>
       </c>
       <c r="P51" s="3">
-        <v>-3500</v>
+        <v>-5500</v>
       </c>
       <c r="Q51" s="3">
         <v>1</v>
       </c>
       <c r="R51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S51" s="3">
         <v>2</v>
@@ -6818,7 +6832,7 @@
         <v>10000</v>
       </c>
       <c r="AH51" s="9">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="AI51" s="9">
         <v>0</v>
@@ -6831,7 +6845,9 @@
       <c r="B52" s="3">
         <v>1</v>
       </c>
-      <c r="C52" s="3"/>
+      <c r="C52" s="3" t="s">
+        <v>98</v>
+      </c>
       <c r="D52" s="3">
         <v>2</v>
       </c>
@@ -6854,28 +6870,28 @@
         <v>2</v>
       </c>
       <c r="K52" s="3">
-        <v>158</v>
+        <v>242</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
       </c>
       <c r="M52" s="3">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="N52" s="3">
         <v>2</v>
       </c>
       <c r="O52" s="3">
-        <v>338</v>
+        <v>406</v>
       </c>
       <c r="P52" s="3">
-        <v>-3500</v>
+        <v>-5500</v>
       </c>
       <c r="Q52" s="3">
         <v>1</v>
       </c>
       <c r="R52" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S52" s="3">
         <v>2</v>
@@ -6936,7 +6952,9 @@
       <c r="B53" s="3">
         <v>1</v>
       </c>
-      <c r="C53" s="3"/>
+      <c r="C53" s="3" t="s">
+        <v>92</v>
+      </c>
       <c r="D53" s="3">
         <v>3</v>
       </c>
@@ -6959,28 +6977,28 @@
         <v>3</v>
       </c>
       <c r="K53" s="3">
-        <v>221</v>
+        <v>383</v>
       </c>
       <c r="L53" s="3">
         <v>0</v>
       </c>
       <c r="M53" s="3">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="N53" s="3">
         <v>3</v>
       </c>
       <c r="O53" s="3">
-        <v>59</v>
+        <v>133</v>
       </c>
       <c r="P53" s="3">
-        <v>-3500</v>
+        <v>-5500</v>
       </c>
       <c r="Q53" s="3">
         <v>1</v>
       </c>
       <c r="R53" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S53" s="3">
         <v>2</v>
@@ -7028,7 +7046,7 @@
         <v>10000</v>
       </c>
       <c r="AH53" s="9">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="AI53" s="9">
         <v>0</v>
@@ -7041,7 +7059,9 @@
       <c r="B54" s="3">
         <v>1</v>
       </c>
-      <c r="C54" s="3"/>
+      <c r="C54" s="3" t="s">
+        <v>95</v>
+      </c>
       <c r="D54" s="3">
         <v>3</v>
       </c>
@@ -7064,28 +7084,28 @@
         <v>3</v>
       </c>
       <c r="K54" s="3">
-        <v>252</v>
+        <v>438</v>
       </c>
       <c r="L54" s="3">
         <v>0</v>
       </c>
       <c r="M54" s="3">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="N54" s="3">
         <v>3</v>
       </c>
       <c r="O54" s="3">
-        <v>158</v>
+        <v>295</v>
       </c>
       <c r="P54" s="3">
-        <v>-3500</v>
+        <v>-5500</v>
       </c>
       <c r="Q54" s="3">
         <v>1</v>
       </c>
       <c r="R54" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S54" s="3">
         <v>2</v>
@@ -7133,7 +7153,7 @@
         <v>10000</v>
       </c>
       <c r="AH54" s="9">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="AI54" s="9">
         <v>0</v>
@@ -7146,7 +7166,9 @@
       <c r="B55" s="3">
         <v>1</v>
       </c>
-      <c r="C55" s="3"/>
+      <c r="C55" s="3" t="s">
+        <v>98</v>
+      </c>
       <c r="D55" s="3">
         <v>3</v>
       </c>
@@ -7169,28 +7191,28 @@
         <v>3</v>
       </c>
       <c r="K55" s="3">
-        <v>347</v>
+        <v>602</v>
       </c>
       <c r="L55" s="3">
         <v>0</v>
       </c>
       <c r="M55" s="3">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="N55" s="3">
         <v>4</v>
       </c>
       <c r="O55" s="3">
-        <v>572</v>
+        <v>855</v>
       </c>
       <c r="P55" s="3">
-        <v>-3500</v>
+        <v>-5500</v>
       </c>
       <c r="Q55" s="3">
         <v>1</v>
       </c>
       <c r="R55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S55" s="3">
         <v>2</v>
@@ -7251,7 +7273,9 @@
       <c r="B56" s="3">
         <v>1</v>
       </c>
-      <c r="C56" s="3"/>
+      <c r="C56" s="3" t="s">
+        <v>92</v>
+      </c>
       <c r="D56" s="3">
         <v>4</v>
       </c>
@@ -7274,28 +7298,28 @@
         <v>4</v>
       </c>
       <c r="K56" s="3">
-        <v>412</v>
+        <v>678</v>
       </c>
       <c r="L56" s="3">
         <v>0</v>
       </c>
       <c r="M56" s="3">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="N56" s="3">
         <v>5</v>
       </c>
       <c r="O56" s="3">
-        <v>153</v>
+        <v>275</v>
       </c>
       <c r="P56" s="3">
-        <v>-3500</v>
+        <v>-5500</v>
       </c>
       <c r="Q56" s="3">
         <v>1</v>
       </c>
       <c r="R56" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S56" s="3">
         <v>2</v>
@@ -7343,7 +7367,7 @@
         <v>10000</v>
       </c>
       <c r="AH56" s="9">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AI56" s="9">
         <v>0</v>
@@ -7356,7 +7380,9 @@
       <c r="B57" s="3">
         <v>1</v>
       </c>
-      <c r="C57" s="3"/>
+      <c r="C57" s="3" t="s">
+        <v>95</v>
+      </c>
       <c r="D57" s="3">
         <v>4</v>
       </c>
@@ -7379,28 +7405,28 @@
         <v>4</v>
       </c>
       <c r="K57" s="3">
-        <v>470</v>
+        <v>775</v>
       </c>
       <c r="L57" s="3">
         <v>0</v>
       </c>
       <c r="M57" s="3">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="N57" s="3">
         <v>5</v>
       </c>
       <c r="O57" s="3">
-        <v>334</v>
+        <v>500</v>
       </c>
       <c r="P57" s="3">
-        <v>-3500</v>
+        <v>-5500</v>
       </c>
       <c r="Q57" s="3">
         <v>1</v>
       </c>
       <c r="R57" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S57" s="3">
         <v>2</v>
@@ -7448,7 +7474,7 @@
         <v>10000</v>
       </c>
       <c r="AH57" s="9">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="AI57" s="9">
         <v>0</v>
@@ -7461,7 +7487,9 @@
       <c r="B58" s="3">
         <v>1</v>
       </c>
-      <c r="C58" s="3"/>
+      <c r="C58" s="3" t="s">
+        <v>98</v>
+      </c>
       <c r="D58" s="3">
         <v>4</v>
       </c>
@@ -7484,28 +7512,28 @@
         <v>4</v>
       </c>
       <c r="K58" s="3">
-        <v>647</v>
+        <v>1066</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
       <c r="M58" s="3">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="N58" s="3">
         <v>8</v>
       </c>
       <c r="O58" s="3">
-        <v>1376</v>
+        <v>1652</v>
       </c>
       <c r="P58" s="3">
-        <v>-3500</v>
+        <v>-5500</v>
       </c>
       <c r="Q58" s="3">
         <v>1</v>
       </c>
       <c r="R58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S58" s="3">
         <v>2</v>
@@ -7566,7 +7594,9 @@
       <c r="B59" s="3">
         <v>1</v>
       </c>
-      <c r="C59" s="3"/>
+      <c r="C59" s="3" t="s">
+        <v>92</v>
+      </c>
       <c r="D59" s="3">
         <v>5</v>
       </c>
@@ -7589,28 +7619,28 @@
         <v>5</v>
       </c>
       <c r="K59" s="3">
-        <v>685</v>
+        <v>1056</v>
       </c>
       <c r="L59" s="3">
         <v>0</v>
       </c>
       <c r="M59" s="3">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="N59" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O59" s="3">
-        <v>231</v>
+        <v>396</v>
       </c>
       <c r="P59" s="3">
-        <v>-3500</v>
+        <v>-5500</v>
       </c>
       <c r="Q59" s="3">
         <v>1</v>
       </c>
       <c r="R59" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S59" s="3">
         <v>2</v>
@@ -7658,7 +7688,7 @@
         <v>10000</v>
       </c>
       <c r="AH59" s="9">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="AI59" s="9">
         <v>0</v>
@@ -7671,7 +7701,9 @@
       <c r="B60" s="3">
         <v>1</v>
       </c>
-      <c r="C60" s="3"/>
+      <c r="C60" s="3" t="s">
+        <v>95</v>
+      </c>
       <c r="D60" s="3">
         <v>5</v>
       </c>
@@ -7694,28 +7726,28 @@
         <v>5</v>
       </c>
       <c r="K60" s="3">
-        <v>783</v>
+        <v>1207</v>
       </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
       <c r="M60" s="3">
-        <v>148</v>
+        <v>193</v>
       </c>
       <c r="N60" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O60" s="3">
-        <v>580</v>
+        <v>828</v>
       </c>
       <c r="P60" s="3">
-        <v>-3500</v>
+        <v>-5500</v>
       </c>
       <c r="Q60" s="3">
         <v>1</v>
       </c>
       <c r="R60" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S60" s="3">
         <v>2</v>
@@ -7763,7 +7795,7 @@
         <v>10000</v>
       </c>
       <c r="AH60" s="9">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="AI60" s="9">
         <v>0</v>
@@ -7776,7 +7808,9 @@
       <c r="B61" s="3">
         <v>1</v>
       </c>
-      <c r="C61" s="3"/>
+      <c r="C61" s="3" t="s">
+        <v>98</v>
+      </c>
       <c r="D61" s="3">
         <v>5</v>
       </c>
@@ -7799,28 +7833,28 @@
         <v>5</v>
       </c>
       <c r="K61" s="3">
-        <v>1077</v>
+        <v>1660</v>
       </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
       <c r="M61" s="3">
-        <v>134</v>
+        <v>201</v>
       </c>
       <c r="N61" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O61" s="3">
-        <v>2297</v>
+        <v>2623</v>
       </c>
       <c r="P61" s="3">
-        <v>-3500</v>
+        <v>-5500</v>
       </c>
       <c r="Q61" s="3">
         <v>1</v>
       </c>
       <c r="R61" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S61" s="3">
         <v>2</v>
@@ -7881,7 +7915,9 @@
       <c r="B62" s="3">
         <v>2</v>
       </c>
-      <c r="C62" s="3"/>
+      <c r="C62" s="3" t="s">
+        <v>99</v>
+      </c>
       <c r="D62" s="3">
         <v>5</v>
       </c>
@@ -7904,31 +7940,31 @@
         <v>5</v>
       </c>
       <c r="K62" s="3">
-        <v>685</v>
+        <v>1056</v>
       </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
       <c r="M62" s="3">
-        <v>147</v>
+        <v>173</v>
       </c>
       <c r="N62" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O62" s="3">
-        <v>229</v>
+        <v>544</v>
       </c>
       <c r="P62" s="3">
-        <v>-3500</v>
+        <v>-5500</v>
       </c>
       <c r="Q62" s="3">
         <v>1</v>
       </c>
       <c r="R62" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S62" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T62" s="3">
         <v>0</v>
@@ -7973,7 +8009,7 @@
         <v>10000</v>
       </c>
       <c r="AH62" s="9">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="AI62" s="9">
         <v>10</v>
@@ -7986,7 +8022,9 @@
       <c r="B63" s="3">
         <v>6</v>
       </c>
-      <c r="C63" s="3"/>
+      <c r="C63" s="3" t="s">
+        <v>92</v>
+      </c>
       <c r="D63" s="3">
         <v>6</v>
       </c>
@@ -8009,28 +8047,28 @@
         <v>6</v>
       </c>
       <c r="K63" s="3">
-        <v>1042</v>
+        <v>1600</v>
       </c>
       <c r="L63" s="3">
         <v>0</v>
       </c>
       <c r="M63" s="3">
-        <v>157</v>
+        <v>190</v>
       </c>
       <c r="N63" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O63" s="3">
-        <v>341</v>
+        <v>594</v>
       </c>
       <c r="P63" s="3">
-        <v>-3500</v>
+        <v>-5500</v>
       </c>
       <c r="Q63" s="3">
         <v>1</v>
       </c>
       <c r="R63" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S63" s="3">
         <v>1</v>
@@ -8078,7 +8116,7 @@
         <v>10000</v>
       </c>
       <c r="AH63" s="9">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="AI63" s="9">
         <v>0</v>
@@ -8091,7 +8129,9 @@
       <c r="B64" s="3">
         <v>6</v>
       </c>
-      <c r="C64" s="3"/>
+      <c r="C64" s="3" t="s">
+        <v>95</v>
+      </c>
       <c r="D64" s="3">
         <v>6</v>
       </c>
@@ -8114,28 +8154,28 @@
         <v>6</v>
       </c>
       <c r="K64" s="3">
-        <v>1191</v>
+        <v>1829</v>
       </c>
       <c r="L64" s="3">
         <v>0</v>
       </c>
       <c r="M64" s="3">
-        <v>210</v>
+        <v>293</v>
       </c>
       <c r="N64" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O64" s="3">
-        <v>857</v>
+        <v>1244</v>
       </c>
       <c r="P64" s="3">
-        <v>-3500</v>
+        <v>-5500</v>
       </c>
       <c r="Q64" s="3">
         <v>1</v>
       </c>
       <c r="R64" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S64" s="3">
         <v>1</v>
@@ -8183,7 +8223,7 @@
         <v>10000</v>
       </c>
       <c r="AH64" s="9">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="AI64" s="9">
         <v>0</v>
@@ -8196,7 +8236,9 @@
       <c r="B65" s="3">
         <v>6</v>
       </c>
-      <c r="C65" s="3"/>
+      <c r="C65" s="3" t="s">
+        <v>98</v>
+      </c>
       <c r="D65" s="3">
         <v>6</v>
       </c>
@@ -8219,28 +8261,28 @@
         <v>6</v>
       </c>
       <c r="K65" s="3">
-        <v>1638</v>
+        <v>2515</v>
       </c>
       <c r="L65" s="3">
         <v>0</v>
       </c>
       <c r="M65" s="3">
-        <v>185</v>
+        <v>295</v>
       </c>
       <c r="N65" s="3">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O65" s="3">
-        <v>3516</v>
+        <v>4093</v>
       </c>
       <c r="P65" s="3">
-        <v>-3500</v>
+        <v>-5500</v>
       </c>
       <c r="Q65" s="3">
         <v>1</v>
       </c>
       <c r="R65" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S65" s="3">
         <v>1</v>
@@ -8301,7 +8343,9 @@
       <c r="B66" s="3">
         <v>6</v>
       </c>
-      <c r="C66" s="3"/>
+      <c r="C66" s="3" t="s">
+        <v>99</v>
+      </c>
       <c r="D66" s="3">
         <v>6</v>
       </c>
@@ -8324,28 +8368,28 @@
         <v>6</v>
       </c>
       <c r="K66" s="3">
-        <v>1042</v>
+        <v>1600</v>
       </c>
       <c r="L66" s="3">
         <v>0</v>
       </c>
       <c r="M66" s="3">
-        <v>208</v>
+        <v>263</v>
       </c>
       <c r="N66" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O66" s="3">
-        <v>339</v>
+        <v>819</v>
       </c>
       <c r="P66" s="3">
-        <v>-3500</v>
+        <v>-5500</v>
       </c>
       <c r="Q66" s="3">
         <v>1</v>
       </c>
       <c r="R66" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S66" s="3">
         <v>1</v>
@@ -8393,7 +8437,7 @@
         <v>10000</v>
       </c>
       <c r="AH66" s="9">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="AI66" s="9">
         <v>10</v>
@@ -8406,7 +8450,9 @@
       <c r="B67" s="3">
         <v>6</v>
       </c>
-      <c r="C67" s="3"/>
+      <c r="C67" s="3" t="s">
+        <v>101</v>
+      </c>
       <c r="D67" s="3">
         <v>6</v>
       </c>
@@ -8429,28 +8475,28 @@
         <v>6</v>
       </c>
       <c r="K67" s="3">
-        <v>1194</v>
+        <v>1600</v>
       </c>
       <c r="L67" s="3">
         <v>0</v>
       </c>
       <c r="M67" s="3">
-        <v>163</v>
+        <v>190</v>
       </c>
       <c r="N67" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O67" s="3">
-        <v>1866</v>
+        <v>5168</v>
       </c>
       <c r="P67" s="3">
-        <v>-3500</v>
+        <v>-5500</v>
       </c>
       <c r="Q67" s="3">
         <v>1</v>
       </c>
       <c r="R67" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S67" s="3">
         <v>1</v>
@@ -8498,7 +8544,7 @@
         <v>10000</v>
       </c>
       <c r="AH67" s="9">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AI67" s="9">
         <v>0</v>
@@ -8511,7 +8557,9 @@
       <c r="B68" s="3">
         <v>6</v>
       </c>
-      <c r="C68" s="3"/>
+      <c r="C68" s="3" t="s">
+        <v>104</v>
+      </c>
       <c r="D68" s="3">
         <v>6</v>
       </c>
@@ -8534,28 +8582,28 @@
         <v>6</v>
       </c>
       <c r="K68" s="3">
-        <v>1365</v>
+        <v>1829</v>
       </c>
       <c r="L68" s="3">
         <v>0</v>
       </c>
       <c r="M68" s="3">
-        <v>219</v>
+        <v>293</v>
       </c>
       <c r="N68" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O68" s="3">
-        <v>3368</v>
+        <v>6702</v>
       </c>
       <c r="P68" s="3">
-        <v>-3500</v>
+        <v>-5500</v>
       </c>
       <c r="Q68" s="3">
         <v>1</v>
       </c>
       <c r="R68" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S68" s="3">
         <v>1</v>
@@ -8603,7 +8651,7 @@
         <v>10000</v>
       </c>
       <c r="AH68" s="9">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AI68" s="9">
         <v>0</v>
@@ -8616,7 +8664,9 @@
       <c r="B69" s="3">
         <v>6</v>
       </c>
-      <c r="C69" s="3"/>
+      <c r="C69" s="3" t="s">
+        <v>106</v>
+      </c>
       <c r="D69" s="3">
         <v>6</v>
       </c>
@@ -8639,28 +8689,28 @@
         <v>6</v>
       </c>
       <c r="K69" s="3">
-        <v>1877</v>
+        <v>2515</v>
       </c>
       <c r="L69" s="3">
         <v>0</v>
       </c>
       <c r="M69" s="3">
-        <v>192</v>
+        <v>295</v>
       </c>
       <c r="N69" s="3">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O69" s="3">
-        <v>12884</v>
+        <v>14512</v>
       </c>
       <c r="P69" s="3">
-        <v>-3500</v>
+        <v>-5500</v>
       </c>
       <c r="Q69" s="3">
         <v>1</v>
       </c>
       <c r="R69" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S69" s="3">
         <v>1</v>
@@ -8708,7 +8758,7 @@
         <v>10000</v>
       </c>
       <c r="AH69" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI69" s="9">
         <v>0</v>
@@ -8721,7 +8771,9 @@
       <c r="B70" s="3">
         <v>6</v>
       </c>
-      <c r="C70" s="3"/>
+      <c r="C70" s="3" t="s">
+        <v>107</v>
+      </c>
       <c r="D70" s="3">
         <v>6</v>
       </c>
@@ -8744,28 +8796,28 @@
         <v>6</v>
       </c>
       <c r="K70" s="3">
-        <v>1194</v>
+        <v>1600</v>
       </c>
       <c r="L70" s="3">
         <v>0</v>
       </c>
       <c r="M70" s="3">
-        <v>217</v>
+        <v>263</v>
       </c>
       <c r="N70" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O70" s="3">
-        <v>1424</v>
+        <v>3958</v>
       </c>
       <c r="P70" s="3">
-        <v>-3500</v>
+        <v>-5500</v>
       </c>
       <c r="Q70" s="3">
         <v>1</v>
       </c>
       <c r="R70" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S70" s="3">
         <v>1</v>
@@ -8813,7 +8865,7 @@
         <v>10000</v>
       </c>
       <c r="AH70" s="9">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AI70" s="9">
         <v>10</v>
@@ -8826,7 +8878,9 @@
       <c r="B71" s="3">
         <v>7</v>
       </c>
-      <c r="C71" s="3"/>
+      <c r="C71" s="3" t="s">
+        <v>92</v>
+      </c>
       <c r="D71" s="3">
         <v>7</v>
       </c>
@@ -8849,28 +8903,28 @@
         <v>7</v>
       </c>
       <c r="K71" s="3">
-        <v>1616</v>
+        <v>2363</v>
       </c>
       <c r="L71" s="3">
         <v>0</v>
       </c>
       <c r="M71" s="3">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="N71" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="O71" s="3">
-        <v>554</v>
+        <v>848</v>
       </c>
       <c r="P71" s="3">
-        <v>-3500</v>
+        <v>-5500</v>
       </c>
       <c r="Q71" s="3">
         <v>1</v>
       </c>
       <c r="R71" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S71" s="3">
         <v>1</v>
@@ -8918,7 +8972,7 @@
         <v>10000</v>
       </c>
       <c r="AH71" s="9">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="AI71" s="9">
         <v>0</v>
@@ -8931,7 +8985,9 @@
       <c r="B72" s="3">
         <v>7</v>
       </c>
-      <c r="C72" s="3"/>
+      <c r="C72" s="3" t="s">
+        <v>95</v>
+      </c>
       <c r="D72" s="3">
         <v>7</v>
       </c>
@@ -8954,28 +9010,28 @@
         <v>7</v>
       </c>
       <c r="K72" s="3">
-        <v>1846</v>
+        <v>2700</v>
       </c>
       <c r="L72" s="3">
         <v>0</v>
       </c>
       <c r="M72" s="3">
-        <v>314</v>
+        <v>368</v>
       </c>
       <c r="N72" s="3">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="O72" s="3">
-        <v>1515</v>
+        <v>1933</v>
       </c>
       <c r="P72" s="3">
-        <v>-3500</v>
+        <v>-5500</v>
       </c>
       <c r="Q72" s="3">
         <v>1</v>
       </c>
       <c r="R72" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S72" s="3">
         <v>1</v>
@@ -9023,7 +9079,7 @@
         <v>10000</v>
       </c>
       <c r="AH72" s="9">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AI72" s="9">
         <v>0</v>
@@ -9036,7 +9092,9 @@
       <c r="B73" s="3">
         <v>7</v>
       </c>
-      <c r="C73" s="3"/>
+      <c r="C73" s="3" t="s">
+        <v>98</v>
+      </c>
       <c r="D73" s="3">
         <v>7</v>
       </c>
@@ -9059,28 +9117,28 @@
         <v>7</v>
       </c>
       <c r="K73" s="3">
-        <v>2539</v>
+        <v>3713</v>
       </c>
       <c r="L73" s="3">
         <v>0</v>
       </c>
       <c r="M73" s="3">
-        <v>333</v>
+        <v>458</v>
       </c>
       <c r="N73" s="3">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="O73" s="3">
-        <v>5505</v>
+        <v>5611</v>
       </c>
       <c r="P73" s="3">
-        <v>-3500</v>
+        <v>-5500</v>
       </c>
       <c r="Q73" s="3">
         <v>1</v>
       </c>
       <c r="R73" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S73" s="3">
         <v>1</v>
@@ -9141,7 +9199,9 @@
       <c r="B74" s="3">
         <v>7</v>
       </c>
-      <c r="C74" s="3"/>
+      <c r="C74" s="3" t="s">
+        <v>99</v>
+      </c>
       <c r="D74" s="3">
         <v>7</v>
       </c>
@@ -9164,28 +9224,28 @@
         <v>7</v>
       </c>
       <c r="K74" s="3">
-        <v>1616</v>
+        <v>2363</v>
       </c>
       <c r="L74" s="3">
         <v>0</v>
       </c>
       <c r="M74" s="3">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="N74" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O74" s="3">
-        <v>622</v>
+        <v>1319</v>
       </c>
       <c r="P74" s="3">
-        <v>-3500</v>
+        <v>-5500</v>
       </c>
       <c r="Q74" s="3">
         <v>1</v>
       </c>
       <c r="R74" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S74" s="3">
         <v>1</v>
@@ -9233,7 +9293,7 @@
         <v>10000</v>
       </c>
       <c r="AH74" s="9">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="AI74" s="9">
         <v>10</v>
@@ -9246,7 +9306,9 @@
       <c r="B75" s="3">
         <v>7</v>
       </c>
-      <c r="C75" s="3"/>
+      <c r="C75" s="3" t="s">
+        <v>101</v>
+      </c>
       <c r="D75" s="3">
         <v>7</v>
       </c>
@@ -9269,28 +9331,28 @@
         <v>7</v>
       </c>
       <c r="K75" s="3">
-        <v>1753</v>
+        <v>2399</v>
       </c>
       <c r="L75" s="3">
         <v>0</v>
       </c>
       <c r="M75" s="3">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="N75" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="O75" s="3">
-        <v>2829</v>
+        <v>7783</v>
       </c>
       <c r="P75" s="3">
-        <v>-3500</v>
+        <v>-5500</v>
       </c>
       <c r="Q75" s="3">
         <v>1</v>
       </c>
       <c r="R75" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S75" s="3">
         <v>1</v>
@@ -9338,7 +9400,7 @@
         <v>10000</v>
       </c>
       <c r="AH75" s="9">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AI75" s="9">
         <v>0</v>
@@ -9351,7 +9413,9 @@
       <c r="B76" s="3">
         <v>7</v>
       </c>
-      <c r="C76" s="3"/>
+      <c r="C76" s="3" t="s">
+        <v>104</v>
+      </c>
       <c r="D76" s="3">
         <v>7</v>
       </c>
@@ -9374,28 +9438,28 @@
         <v>7</v>
       </c>
       <c r="K76" s="3">
-        <v>2003</v>
+        <v>2742</v>
       </c>
       <c r="L76" s="3">
         <v>0</v>
       </c>
       <c r="M76" s="3">
-        <v>321</v>
+        <v>368</v>
       </c>
       <c r="N76" s="3">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="O76" s="3">
-        <v>5561</v>
+        <v>10999</v>
       </c>
       <c r="P76" s="3">
-        <v>-3500</v>
+        <v>-5500</v>
       </c>
       <c r="Q76" s="3">
         <v>1</v>
       </c>
       <c r="R76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S76" s="3">
         <v>1</v>
@@ -9443,7 +9507,7 @@
         <v>10000</v>
       </c>
       <c r="AH76" s="9">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AI76" s="9">
         <v>0</v>
@@ -9456,7 +9520,9 @@
       <c r="B77" s="3">
         <v>7</v>
       </c>
-      <c r="C77" s="3"/>
+      <c r="C77" s="3" t="s">
+        <v>106</v>
+      </c>
       <c r="D77" s="3">
         <v>7</v>
       </c>
@@ -9479,28 +9545,28 @@
         <v>7</v>
       </c>
       <c r="K77" s="3">
-        <v>2754</v>
+        <v>3770</v>
       </c>
       <c r="L77" s="3">
         <v>0</v>
       </c>
       <c r="M77" s="3">
-        <v>340</v>
+        <v>458</v>
       </c>
       <c r="N77" s="3">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="O77" s="3">
-        <v>18790</v>
+        <v>21011</v>
       </c>
       <c r="P77" s="3">
-        <v>-3500</v>
+        <v>-5500</v>
       </c>
       <c r="Q77" s="3">
         <v>1</v>
       </c>
       <c r="R77" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S77" s="3">
         <v>1</v>
@@ -9548,7 +9614,7 @@
         <v>10000</v>
       </c>
       <c r="AH77" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI77" s="9">
         <v>0</v>
@@ -9561,7 +9627,9 @@
       <c r="B78" s="3">
         <v>7</v>
       </c>
-      <c r="C78" s="3"/>
+      <c r="C78" s="3" t="s">
+        <v>107</v>
+      </c>
       <c r="D78" s="3">
         <v>7</v>
       </c>
@@ -9584,28 +9652,28 @@
         <v>7</v>
       </c>
       <c r="K78" s="3">
-        <v>1753</v>
+        <v>2399</v>
       </c>
       <c r="L78" s="3">
         <v>0</v>
       </c>
       <c r="M78" s="3">
-        <v>387</v>
+        <v>413</v>
       </c>
       <c r="N78" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O78" s="3">
-        <v>2441</v>
+        <v>6722</v>
       </c>
       <c r="P78" s="3">
-        <v>-3500</v>
+        <v>-5500</v>
       </c>
       <c r="Q78" s="3">
         <v>1</v>
       </c>
       <c r="R78" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S78" s="3">
         <v>1</v>
@@ -9653,7 +9721,7 @@
         <v>10000</v>
       </c>
       <c r="AH78" s="9">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="AI78" s="9">
         <v>10</v>
@@ -9666,7 +9734,9 @@
       <c r="B79" s="3">
         <v>7</v>
       </c>
-      <c r="C79" s="3"/>
+      <c r="C79" s="3" t="s">
+        <v>109</v>
+      </c>
       <c r="D79" s="3">
         <v>7</v>
       </c>
@@ -9689,28 +9759,28 @@
         <v>7</v>
       </c>
       <c r="K79" s="3">
-        <v>1753</v>
+        <v>2528</v>
       </c>
       <c r="L79" s="3">
         <v>0</v>
       </c>
       <c r="M79" s="3">
-        <v>275</v>
+        <v>299</v>
       </c>
       <c r="N79" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O79" s="3">
-        <v>7946</v>
+        <v>17739</v>
       </c>
       <c r="P79" s="3">
-        <v>-3500</v>
+        <v>-5500</v>
       </c>
       <c r="Q79" s="3">
         <v>1</v>
       </c>
       <c r="R79" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S79" s="3">
         <v>1</v>
@@ -9758,7 +9828,7 @@
         <v>10000</v>
       </c>
       <c r="AH79" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI79" s="9">
         <v>0</v>
@@ -9771,7 +9841,9 @@
       <c r="B80" s="3">
         <v>7</v>
       </c>
-      <c r="C80" s="3"/>
+      <c r="C80" s="3" t="s">
+        <v>111</v>
+      </c>
       <c r="D80" s="3">
         <v>7</v>
       </c>
@@ -9794,28 +9866,28 @@
         <v>7</v>
       </c>
       <c r="K80" s="3">
-        <v>2003</v>
+        <v>2890</v>
       </c>
       <c r="L80" s="3">
         <v>0</v>
       </c>
       <c r="M80" s="3">
-        <v>321</v>
+        <v>387</v>
       </c>
       <c r="N80" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O80" s="3">
-        <v>13594</v>
+        <v>22451</v>
       </c>
       <c r="P80" s="3">
-        <v>-3500</v>
+        <v>-5500</v>
       </c>
       <c r="Q80" s="3">
         <v>1</v>
       </c>
       <c r="R80" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S80" s="3">
         <v>1</v>
@@ -9876,7 +9948,9 @@
       <c r="B81" s="3">
         <v>7</v>
       </c>
-      <c r="C81" s="3"/>
+      <c r="C81" s="3" t="s">
+        <v>113</v>
+      </c>
       <c r="D81" s="3">
         <v>7</v>
       </c>
@@ -9899,28 +9973,28 @@
         <v>7</v>
       </c>
       <c r="K81" s="3">
-        <v>2754</v>
+        <v>3973</v>
       </c>
       <c r="L81" s="3">
         <v>0</v>
       </c>
       <c r="M81" s="3">
-        <v>340</v>
+        <v>481</v>
       </c>
       <c r="N81" s="3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O81" s="3">
-        <v>35946</v>
+        <v>35578</v>
       </c>
       <c r="P81" s="3">
-        <v>-3500</v>
+        <v>-5500</v>
       </c>
       <c r="Q81" s="3">
         <v>1</v>
       </c>
       <c r="R81" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S81" s="3">
         <v>1</v>
@@ -9981,7 +10055,9 @@
       <c r="B82" s="3">
         <v>7</v>
       </c>
-      <c r="C82" s="3"/>
+      <c r="C82" s="3" t="s">
+        <v>115</v>
+      </c>
       <c r="D82" s="3">
         <v>7</v>
       </c>
@@ -10004,28 +10080,28 @@
         <v>7</v>
       </c>
       <c r="K82" s="3">
-        <v>1753</v>
+        <v>2528</v>
       </c>
       <c r="L82" s="3">
         <v>0</v>
       </c>
       <c r="M82" s="3">
-        <v>387</v>
+        <v>434</v>
       </c>
       <c r="N82" s="3">
         <v>10</v>
       </c>
       <c r="O82" s="3">
-        <v>6855</v>
+        <v>15307</v>
       </c>
       <c r="P82" s="3">
-        <v>-3500</v>
+        <v>-5500</v>
       </c>
       <c r="Q82" s="3">
         <v>1</v>
       </c>
       <c r="R82" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S82" s="3">
         <v>1</v>
@@ -10073,7 +10149,7 @@
         <v>10000</v>
       </c>
       <c r="AH82" s="9">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AI82" s="9">
         <v>10</v>
@@ -10086,7 +10162,9 @@
       <c r="B83" s="3">
         <v>7</v>
       </c>
-      <c r="C83" s="3"/>
+      <c r="C83" s="3" t="s">
+        <v>246</v>
+      </c>
       <c r="D83" s="3">
         <v>7</v>
       </c>
@@ -10109,28 +10187,28 @@
         <v>7</v>
       </c>
       <c r="K83" s="3">
-        <v>7512</v>
+        <v>10836</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
       </c>
       <c r="M83" s="3">
-        <v>985</v>
+        <v>1028</v>
       </c>
       <c r="N83" s="3">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="O83" s="3">
-        <v>145411</v>
+        <v>178356</v>
       </c>
       <c r="P83" s="3">
-        <v>-3500</v>
+        <v>-5500</v>
       </c>
       <c r="Q83" s="3">
         <v>1</v>
       </c>
       <c r="R83" s="3">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="S83" s="3">
         <v>1</v>
@@ -10178,7 +10256,7 @@
         <v>10000</v>
       </c>
       <c r="AH83" s="9">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AI83" s="9">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B047921B-200A-4D1C-946C-F4CB0B2E7F3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{568860E7-FFEB-4C9C-A353-3FD75B8AF19F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -792,7 +792,6 @@
   </si>
   <si>
     <t>精英1</t>
-    <phoneticPr fontId="13" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -6347,7 +6346,7 @@
         <v>1</v>
       </c>
       <c r="O47" s="3">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="P47" s="3">
         <v>-5500</v>
@@ -6404,7 +6403,7 @@
         <v>10000</v>
       </c>
       <c r="AH47" s="9">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="AI47" s="9">
         <v>0</v>
@@ -6448,13 +6447,13 @@
         <v>0</v>
       </c>
       <c r="M48" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N48" s="3">
         <v>1</v>
       </c>
       <c r="O48" s="3">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="P48" s="3">
         <v>-5500</v>
@@ -6511,7 +6510,7 @@
         <v>10000</v>
       </c>
       <c r="AH48" s="9">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AI48" s="9">
         <v>0</v>
@@ -6555,13 +6554,13 @@
         <v>0</v>
       </c>
       <c r="M49" s="3">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="N49" s="3">
         <v>1</v>
       </c>
       <c r="O49" s="3">
-        <v>241</v>
+        <v>194</v>
       </c>
       <c r="P49" s="3">
         <v>-5500</v>
@@ -6618,7 +6617,7 @@
         <v>10000</v>
       </c>
       <c r="AH49" s="9">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="AI49" s="9">
         <v>0</v>
@@ -6662,13 +6661,13 @@
         <v>0</v>
       </c>
       <c r="M50" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N50" s="3">
         <v>1</v>
       </c>
       <c r="O50" s="3">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="P50" s="3">
         <v>-5500</v>
@@ -6725,7 +6724,7 @@
         <v>10000</v>
       </c>
       <c r="AH50" s="9">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="AI50" s="9">
         <v>0</v>
@@ -6769,13 +6768,13 @@
         <v>0</v>
       </c>
       <c r="M51" s="3">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="N51" s="3">
         <v>1</v>
       </c>
       <c r="O51" s="3">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="P51" s="3">
         <v>-5500</v>
@@ -6832,7 +6831,7 @@
         <v>10000</v>
       </c>
       <c r="AH51" s="9">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="AI51" s="9">
         <v>0</v>
@@ -6876,13 +6875,13 @@
         <v>0</v>
       </c>
       <c r="M52" s="3">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="N52" s="3">
         <v>2</v>
       </c>
       <c r="O52" s="3">
-        <v>406</v>
+        <v>326</v>
       </c>
       <c r="P52" s="3">
         <v>-5500</v>
@@ -6939,7 +6938,7 @@
         <v>10000</v>
       </c>
       <c r="AH52" s="9">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="AI52" s="9">
         <v>0</v>
@@ -6983,13 +6982,13 @@
         <v>0</v>
       </c>
       <c r="M53" s="3">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N53" s="3">
         <v>3</v>
       </c>
       <c r="O53" s="3">
-        <v>133</v>
+        <v>111</v>
       </c>
       <c r="P53" s="3">
         <v>-5500</v>
@@ -7046,7 +7045,7 @@
         <v>10000</v>
       </c>
       <c r="AH53" s="9">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="AI53" s="9">
         <v>0</v>
@@ -7090,13 +7089,13 @@
         <v>0</v>
       </c>
       <c r="M54" s="3">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="N54" s="3">
         <v>3</v>
       </c>
       <c r="O54" s="3">
-        <v>295</v>
+        <v>226</v>
       </c>
       <c r="P54" s="3">
         <v>-5500</v>
@@ -7153,7 +7152,7 @@
         <v>10000</v>
       </c>
       <c r="AH54" s="9">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="AI54" s="9">
         <v>0</v>
@@ -7197,13 +7196,13 @@
         <v>0</v>
       </c>
       <c r="M55" s="3">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="N55" s="3">
         <v>4</v>
       </c>
       <c r="O55" s="3">
-        <v>855</v>
+        <v>826</v>
       </c>
       <c r="P55" s="3">
         <v>-5500</v>
@@ -7260,7 +7259,7 @@
         <v>10000</v>
       </c>
       <c r="AH55" s="9">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AI55" s="9">
         <v>0</v>
@@ -7304,13 +7303,13 @@
         <v>0</v>
       </c>
       <c r="M56" s="3">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="N56" s="3">
         <v>5</v>
       </c>
       <c r="O56" s="3">
-        <v>275</v>
+        <v>209</v>
       </c>
       <c r="P56" s="3">
         <v>-5500</v>
@@ -7367,7 +7366,7 @@
         <v>10000</v>
       </c>
       <c r="AH56" s="9">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="AI56" s="9">
         <v>0</v>
@@ -7411,13 +7410,13 @@
         <v>0</v>
       </c>
       <c r="M57" s="3">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="N57" s="3">
         <v>5</v>
       </c>
       <c r="O57" s="3">
-        <v>500</v>
+        <v>383</v>
       </c>
       <c r="P57" s="3">
         <v>-5500</v>
@@ -7474,7 +7473,7 @@
         <v>10000</v>
       </c>
       <c r="AH57" s="9">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="AI57" s="9">
         <v>0</v>
@@ -7518,13 +7517,13 @@
         <v>0</v>
       </c>
       <c r="M58" s="3">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="N58" s="3">
         <v>8</v>
       </c>
       <c r="O58" s="3">
-        <v>1652</v>
+        <v>1526</v>
       </c>
       <c r="P58" s="3">
         <v>-5500</v>
@@ -7581,7 +7580,7 @@
         <v>10000</v>
       </c>
       <c r="AH58" s="9">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="AI58" s="9">
         <v>0</v>
@@ -7625,13 +7624,13 @@
         <v>0</v>
       </c>
       <c r="M59" s="3">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="N59" s="3">
         <v>7</v>
       </c>
       <c r="O59" s="3">
-        <v>396</v>
+        <v>330</v>
       </c>
       <c r="P59" s="3">
         <v>-5500</v>
@@ -7688,7 +7687,7 @@
         <v>10000</v>
       </c>
       <c r="AH59" s="9">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="AI59" s="9">
         <v>0</v>
@@ -7732,13 +7731,13 @@
         <v>0</v>
       </c>
       <c r="M60" s="3">
-        <v>193</v>
+        <v>159</v>
       </c>
       <c r="N60" s="3">
         <v>8</v>
       </c>
       <c r="O60" s="3">
-        <v>828</v>
+        <v>674</v>
       </c>
       <c r="P60" s="3">
         <v>-5500</v>
@@ -7795,7 +7794,7 @@
         <v>10000</v>
       </c>
       <c r="AH60" s="9">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="AI60" s="9">
         <v>0</v>
@@ -7839,13 +7838,13 @@
         <v>0</v>
       </c>
       <c r="M61" s="3">
-        <v>201</v>
+        <v>173</v>
       </c>
       <c r="N61" s="3">
         <v>11</v>
       </c>
       <c r="O61" s="3">
-        <v>2623</v>
+        <v>2424</v>
       </c>
       <c r="P61" s="3">
         <v>-5500</v>
@@ -7902,7 +7901,7 @@
         <v>10000</v>
       </c>
       <c r="AH61" s="9">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AI61" s="9">
         <v>0</v>
@@ -7946,13 +7945,13 @@
         <v>0</v>
       </c>
       <c r="M62" s="3">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="N62" s="3">
         <v>3</v>
       </c>
       <c r="O62" s="3">
-        <v>544</v>
+        <v>454</v>
       </c>
       <c r="P62" s="3">
         <v>-5500</v>
@@ -8009,7 +8008,7 @@
         <v>10000</v>
       </c>
       <c r="AH62" s="9">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AI62" s="9">
         <v>10</v>
@@ -8053,13 +8052,13 @@
         <v>0</v>
       </c>
       <c r="M63" s="3">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="N63" s="3">
         <v>12</v>
       </c>
       <c r="O63" s="3">
-        <v>594</v>
+        <v>495</v>
       </c>
       <c r="P63" s="3">
         <v>-5500</v>
@@ -8116,7 +8115,7 @@
         <v>10000</v>
       </c>
       <c r="AH63" s="9">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="AI63" s="9">
         <v>0</v>
@@ -8160,13 +8159,13 @@
         <v>0</v>
       </c>
       <c r="M64" s="3">
-        <v>293</v>
+        <v>242</v>
       </c>
       <c r="N64" s="3">
         <v>13</v>
       </c>
       <c r="O64" s="3">
-        <v>1244</v>
+        <v>1013</v>
       </c>
       <c r="P64" s="3">
         <v>-5500</v>
@@ -8223,7 +8222,7 @@
         <v>10000</v>
       </c>
       <c r="AH64" s="9">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="AI64" s="9">
         <v>0</v>
@@ -8267,13 +8266,13 @@
         <v>0</v>
       </c>
       <c r="M65" s="3">
-        <v>295</v>
+        <v>242</v>
       </c>
       <c r="N65" s="3">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="O65" s="3">
-        <v>4093</v>
+        <v>3325</v>
       </c>
       <c r="P65" s="3">
         <v>-5500</v>
@@ -8330,7 +8329,7 @@
         <v>10000</v>
       </c>
       <c r="AH65" s="9">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="AI65" s="9">
         <v>0</v>
@@ -8374,13 +8373,13 @@
         <v>0</v>
       </c>
       <c r="M66" s="3">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="N66" s="3">
         <v>5</v>
       </c>
       <c r="O66" s="3">
-        <v>819</v>
+        <v>682</v>
       </c>
       <c r="P66" s="3">
         <v>-5500</v>
@@ -8437,7 +8436,7 @@
         <v>10000</v>
       </c>
       <c r="AH66" s="9">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AI66" s="9">
         <v>10</v>
@@ -8481,13 +8480,13 @@
         <v>0</v>
       </c>
       <c r="M67" s="3">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="N67" s="3">
         <v>12</v>
       </c>
       <c r="O67" s="3">
-        <v>5168</v>
+        <v>4257</v>
       </c>
       <c r="P67" s="3">
         <v>-5500</v>
@@ -8588,13 +8587,13 @@
         <v>0</v>
       </c>
       <c r="M68" s="3">
-        <v>293</v>
+        <v>242</v>
       </c>
       <c r="N68" s="3">
         <v>13</v>
       </c>
       <c r="O68" s="3">
-        <v>6702</v>
+        <v>5401</v>
       </c>
       <c r="P68" s="3">
         <v>-5500</v>
@@ -8651,7 +8650,7 @@
         <v>10000</v>
       </c>
       <c r="AH68" s="9">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AI68" s="9">
         <v>0</v>
@@ -8695,13 +8694,13 @@
         <v>0</v>
       </c>
       <c r="M69" s="3">
-        <v>295</v>
+        <v>242</v>
       </c>
       <c r="N69" s="3">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="O69" s="3">
-        <v>14512</v>
+        <v>11345</v>
       </c>
       <c r="P69" s="3">
         <v>-5500</v>
@@ -8758,7 +8757,7 @@
         <v>10000</v>
       </c>
       <c r="AH69" s="9">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AI69" s="9">
         <v>0</v>
@@ -8802,13 +8801,13 @@
         <v>0</v>
       </c>
       <c r="M70" s="3">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="N70" s="3">
         <v>5</v>
       </c>
       <c r="O70" s="3">
-        <v>3958</v>
+        <v>3260</v>
       </c>
       <c r="P70" s="3">
         <v>-5500</v>
@@ -8909,13 +8908,13 @@
         <v>0</v>
       </c>
       <c r="M71" s="3">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="N71" s="3">
         <v>17</v>
       </c>
       <c r="O71" s="3">
-        <v>848</v>
+        <v>707</v>
       </c>
       <c r="P71" s="3">
         <v>-5500</v>
@@ -8972,7 +8971,7 @@
         <v>10000</v>
       </c>
       <c r="AH71" s="9">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="AI71" s="9">
         <v>0</v>
@@ -9016,13 +9015,13 @@
         <v>0</v>
       </c>
       <c r="M72" s="3">
-        <v>368</v>
+        <v>323</v>
       </c>
       <c r="N72" s="3">
         <v>21</v>
       </c>
       <c r="O72" s="3">
-        <v>1933</v>
+        <v>1664</v>
       </c>
       <c r="P72" s="3">
         <v>-5500</v>
@@ -9079,7 +9078,7 @@
         <v>10000</v>
       </c>
       <c r="AH72" s="9">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AI72" s="9">
         <v>0</v>
@@ -9123,13 +9122,13 @@
         <v>0</v>
       </c>
       <c r="M73" s="3">
-        <v>458</v>
+        <v>393</v>
       </c>
       <c r="N73" s="3">
         <v>26</v>
       </c>
       <c r="O73" s="3">
-        <v>5611</v>
+        <v>5184</v>
       </c>
       <c r="P73" s="3">
         <v>-5500</v>
@@ -9186,7 +9185,7 @@
         <v>10000</v>
       </c>
       <c r="AH73" s="9">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AI73" s="9">
         <v>0</v>
@@ -9230,13 +9229,13 @@
         <v>0</v>
       </c>
       <c r="M74" s="3">
-        <v>413</v>
+        <v>395</v>
       </c>
       <c r="N74" s="3">
         <v>9</v>
       </c>
       <c r="O74" s="3">
-        <v>1319</v>
+        <v>1099</v>
       </c>
       <c r="P74" s="3">
         <v>-5500</v>
@@ -9293,7 +9292,7 @@
         <v>10000</v>
       </c>
       <c r="AH74" s="9">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="AI74" s="9">
         <v>10</v>
@@ -9337,13 +9336,13 @@
         <v>0</v>
       </c>
       <c r="M75" s="3">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="N75" s="3">
         <v>17</v>
       </c>
       <c r="O75" s="3">
-        <v>7783</v>
+        <v>6411</v>
       </c>
       <c r="P75" s="3">
         <v>-5500</v>
@@ -9444,13 +9443,13 @@
         <v>0</v>
       </c>
       <c r="M76" s="3">
-        <v>368</v>
+        <v>323</v>
       </c>
       <c r="N76" s="3">
         <v>21</v>
       </c>
       <c r="O76" s="3">
-        <v>10999</v>
+        <v>9371</v>
       </c>
       <c r="P76" s="3">
         <v>-5500</v>
@@ -9507,7 +9506,7 @@
         <v>10000</v>
       </c>
       <c r="AH76" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI76" s="9">
         <v>0</v>
@@ -9551,13 +9550,13 @@
         <v>0</v>
       </c>
       <c r="M77" s="3">
-        <v>458</v>
+        <v>393</v>
       </c>
       <c r="N77" s="3">
         <v>26</v>
       </c>
       <c r="O77" s="3">
-        <v>21011</v>
+        <v>18681</v>
       </c>
       <c r="P77" s="3">
         <v>-5500</v>
@@ -9614,7 +9613,7 @@
         <v>10000</v>
       </c>
       <c r="AH77" s="9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AI77" s="9">
         <v>0</v>
@@ -9658,13 +9657,13 @@
         <v>0</v>
       </c>
       <c r="M78" s="3">
-        <v>413</v>
+        <v>395</v>
       </c>
       <c r="N78" s="3">
         <v>9</v>
       </c>
       <c r="O78" s="3">
-        <v>6722</v>
+        <v>5537</v>
       </c>
       <c r="P78" s="3">
         <v>-5500</v>
@@ -9765,13 +9764,13 @@
         <v>0</v>
       </c>
       <c r="M79" s="3">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="N79" s="3">
         <v>18</v>
       </c>
       <c r="O79" s="3">
-        <v>17739</v>
+        <v>14703</v>
       </c>
       <c r="P79" s="3">
         <v>-5500</v>
@@ -9872,13 +9871,13 @@
         <v>0</v>
       </c>
       <c r="M80" s="3">
-        <v>387</v>
+        <v>340</v>
       </c>
       <c r="N80" s="3">
         <v>23</v>
       </c>
       <c r="O80" s="3">
-        <v>22451</v>
+        <v>19224</v>
       </c>
       <c r="P80" s="3">
         <v>-5500</v>
@@ -9935,7 +9934,7 @@
         <v>10000</v>
       </c>
       <c r="AH80" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI80" s="9">
         <v>0</v>
@@ -9979,13 +9978,13 @@
         <v>0</v>
       </c>
       <c r="M81" s="3">
-        <v>481</v>
+        <v>413</v>
       </c>
       <c r="N81" s="3">
         <v>28</v>
       </c>
       <c r="O81" s="3">
-        <v>35578</v>
+        <v>31733</v>
       </c>
       <c r="P81" s="3">
         <v>-5500</v>
@@ -10042,7 +10041,7 @@
         <v>10000</v>
       </c>
       <c r="AH81" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI81" s="9">
         <v>0</v>
@@ -10086,13 +10085,13 @@
         <v>0</v>
       </c>
       <c r="M82" s="3">
-        <v>434</v>
+        <v>416</v>
       </c>
       <c r="N82" s="3">
         <v>10</v>
       </c>
       <c r="O82" s="3">
-        <v>15307</v>
+        <v>12688</v>
       </c>
       <c r="P82" s="3">
         <v>-5500</v>
@@ -10199,7 +10198,7 @@
         <v>74</v>
       </c>
       <c r="O83" s="3">
-        <v>178356</v>
+        <v>164261</v>
       </c>
       <c r="P83" s="3">
         <v>-5500</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{568860E7-FFEB-4C9C-A353-3FD75B8AF19F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E7454C7-B044-4885-8C16-70EBB602C912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6340,7 +6340,7 @@
         <v>0</v>
       </c>
       <c r="M47" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N47" s="3">
         <v>1</v>
@@ -6447,13 +6447,13 @@
         <v>0</v>
       </c>
       <c r="M48" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N48" s="3">
         <v>1</v>
       </c>
       <c r="O48" s="3">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="P48" s="3">
         <v>-5500</v>
@@ -6554,13 +6554,13 @@
         <v>0</v>
       </c>
       <c r="M49" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N49" s="3">
         <v>1</v>
       </c>
       <c r="O49" s="3">
-        <v>194</v>
+        <v>145</v>
       </c>
       <c r="P49" s="3">
         <v>-5500</v>
@@ -6661,7 +6661,7 @@
         <v>0</v>
       </c>
       <c r="M50" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N50" s="3">
         <v>1</v>
@@ -6982,7 +6982,7 @@
         <v>0</v>
       </c>
       <c r="M53" s="3">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="N53" s="3">
         <v>3</v>
@@ -7303,7 +7303,7 @@
         <v>0</v>
       </c>
       <c r="M56" s="3">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="N56" s="3">
         <v>5</v>
@@ -7624,7 +7624,7 @@
         <v>0</v>
       </c>
       <c r="M59" s="3">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="N59" s="3">
         <v>7</v>
@@ -8052,7 +8052,7 @@
         <v>0</v>
       </c>
       <c r="M63" s="3">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="N63" s="3">
         <v>12</v>
@@ -8908,7 +8908,7 @@
         <v>0</v>
       </c>
       <c r="M71" s="3">
-        <v>293</v>
+        <v>261</v>
       </c>
       <c r="N71" s="3">
         <v>17</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E7454C7-B044-4885-8C16-70EBB602C912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{502B69BA-3CE1-470C-B604-46713AA27628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6774,7 +6774,7 @@
         <v>1</v>
       </c>
       <c r="O51" s="3">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="P51" s="3">
         <v>-5500</v>
@@ -6982,13 +6982,13 @@
         <v>0</v>
       </c>
       <c r="M53" s="3">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="N53" s="3">
         <v>3</v>
       </c>
       <c r="O53" s="3">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="P53" s="3">
         <v>-5500</v>
@@ -7089,13 +7089,13 @@
         <v>0</v>
       </c>
       <c r="M54" s="3">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="N54" s="3">
         <v>3</v>
       </c>
       <c r="O54" s="3">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="P54" s="3">
         <v>-5500</v>
@@ -7196,13 +7196,13 @@
         <v>0</v>
       </c>
       <c r="M55" s="3">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="N55" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O55" s="3">
-        <v>826</v>
+        <v>918</v>
       </c>
       <c r="P55" s="3">
         <v>-5500</v>
@@ -7303,13 +7303,13 @@
         <v>0</v>
       </c>
       <c r="M56" s="3">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="N56" s="3">
         <v>5</v>
       </c>
       <c r="O56" s="3">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="P56" s="3">
         <v>-5500</v>
@@ -7410,13 +7410,13 @@
         <v>0</v>
       </c>
       <c r="M57" s="3">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="N57" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O57" s="3">
-        <v>383</v>
+        <v>400</v>
       </c>
       <c r="P57" s="3">
         <v>-5500</v>
@@ -7517,13 +7517,13 @@
         <v>0</v>
       </c>
       <c r="M58" s="3">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="N58" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O58" s="3">
-        <v>1526</v>
+        <v>1795</v>
       </c>
       <c r="P58" s="3">
         <v>-5500</v>
@@ -7624,13 +7624,13 @@
         <v>0</v>
       </c>
       <c r="M59" s="3">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="N59" s="3">
         <v>7</v>
       </c>
       <c r="O59" s="3">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="P59" s="3">
         <v>-5500</v>
@@ -7731,13 +7731,13 @@
         <v>0</v>
       </c>
       <c r="M60" s="3">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="N60" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O60" s="3">
-        <v>674</v>
+        <v>714</v>
       </c>
       <c r="P60" s="3">
         <v>-5500</v>
@@ -7838,13 +7838,13 @@
         <v>0</v>
       </c>
       <c r="M61" s="3">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="N61" s="3">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="O61" s="3">
-        <v>2424</v>
+        <v>2889</v>
       </c>
       <c r="P61" s="3">
         <v>-5500</v>
@@ -7945,13 +7945,13 @@
         <v>0</v>
       </c>
       <c r="M62" s="3">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="N62" s="3">
         <v>3</v>
       </c>
       <c r="O62" s="3">
-        <v>454</v>
+        <v>439</v>
       </c>
       <c r="P62" s="3">
         <v>-5500</v>
@@ -8162,10 +8162,10 @@
         <v>242</v>
       </c>
       <c r="N64" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O64" s="3">
-        <v>1013</v>
+        <v>1111</v>
       </c>
       <c r="P64" s="3">
         <v>-5500</v>
@@ -8269,10 +8269,10 @@
         <v>242</v>
       </c>
       <c r="N65" s="3">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="O65" s="3">
-        <v>3325</v>
+        <v>4106</v>
       </c>
       <c r="P65" s="3">
         <v>-5500</v>
@@ -8483,10 +8483,10 @@
         <v>197</v>
       </c>
       <c r="N67" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O67" s="3">
-        <v>4257</v>
+        <v>4669</v>
       </c>
       <c r="P67" s="3">
         <v>-5500</v>
@@ -8590,10 +8590,10 @@
         <v>242</v>
       </c>
       <c r="N68" s="3">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O68" s="3">
-        <v>5401</v>
+        <v>6442</v>
       </c>
       <c r="P68" s="3">
         <v>-5500</v>
@@ -8697,10 +8697,10 @@
         <v>242</v>
       </c>
       <c r="N69" s="3">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="O69" s="3">
-        <v>11345</v>
+        <v>15034</v>
       </c>
       <c r="P69" s="3">
         <v>-5500</v>
@@ -9018,10 +9018,10 @@
         <v>323</v>
       </c>
       <c r="N72" s="3">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O72" s="3">
-        <v>1664</v>
+        <v>1823</v>
       </c>
       <c r="P72" s="3">
         <v>-5500</v>
@@ -9125,10 +9125,10 @@
         <v>393</v>
       </c>
       <c r="N73" s="3">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="O73" s="3">
-        <v>5184</v>
+        <v>6395</v>
       </c>
       <c r="P73" s="3">
         <v>-5500</v>
@@ -9339,10 +9339,10 @@
         <v>293</v>
       </c>
       <c r="N75" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O75" s="3">
-        <v>6411</v>
+        <v>7038</v>
       </c>
       <c r="P75" s="3">
         <v>-5500</v>
@@ -9446,10 +9446,10 @@
         <v>323</v>
       </c>
       <c r="N76" s="3">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="O76" s="3">
-        <v>9371</v>
+        <v>11154</v>
       </c>
       <c r="P76" s="3">
         <v>-5500</v>
@@ -9553,10 +9553,10 @@
         <v>393</v>
       </c>
       <c r="N77" s="3">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="O77" s="3">
-        <v>18681</v>
+        <v>24754</v>
       </c>
       <c r="P77" s="3">
         <v>-5500</v>
@@ -9767,10 +9767,10 @@
         <v>309</v>
       </c>
       <c r="N79" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="O79" s="3">
-        <v>14703</v>
+        <v>16112</v>
       </c>
       <c r="P79" s="3">
         <v>-5500</v>
@@ -9874,10 +9874,10 @@
         <v>340</v>
       </c>
       <c r="N80" s="3">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="O80" s="3">
-        <v>19224</v>
+        <v>22892</v>
       </c>
       <c r="P80" s="3">
         <v>-5500</v>
@@ -9981,10 +9981,10 @@
         <v>413</v>
       </c>
       <c r="N81" s="3">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="O81" s="3">
-        <v>31733</v>
+        <v>42094</v>
       </c>
       <c r="P81" s="3">
         <v>-5500</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{502B69BA-3CE1-470C-B604-46713AA27628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7614C785-5546-443E-8A5B-130D7AAB3F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6453,7 +6453,7 @@
         <v>1</v>
       </c>
       <c r="O48" s="3">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="P48" s="3">
         <v>-5500</v>
@@ -6560,7 +6560,7 @@
         <v>1</v>
       </c>
       <c r="O49" s="3">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="P49" s="3">
         <v>-5500</v>
@@ -6774,7 +6774,7 @@
         <v>1</v>
       </c>
       <c r="O51" s="3">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="P51" s="3">
         <v>-5500</v>
@@ -6881,7 +6881,7 @@
         <v>2</v>
       </c>
       <c r="O52" s="3">
-        <v>326</v>
+        <v>355</v>
       </c>
       <c r="P52" s="3">
         <v>-5500</v>
@@ -7095,7 +7095,7 @@
         <v>3</v>
       </c>
       <c r="O54" s="3">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="P54" s="3">
         <v>-5500</v>
@@ -7202,7 +7202,7 @@
         <v>5</v>
       </c>
       <c r="O55" s="3">
-        <v>918</v>
+        <v>999</v>
       </c>
       <c r="P55" s="3">
         <v>-5500</v>
@@ -7303,13 +7303,13 @@
         <v>0</v>
       </c>
       <c r="M56" s="3">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="N56" s="3">
         <v>5</v>
       </c>
       <c r="O56" s="3">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="P56" s="3">
         <v>-5500</v>
@@ -7410,13 +7410,13 @@
         <v>0</v>
       </c>
       <c r="M57" s="3">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N57" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O57" s="3">
-        <v>400</v>
+        <v>363</v>
       </c>
       <c r="P57" s="3">
         <v>-5500</v>
@@ -7517,13 +7517,13 @@
         <v>0</v>
       </c>
       <c r="M58" s="3">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N58" s="3">
         <v>10</v>
       </c>
       <c r="O58" s="3">
-        <v>1795</v>
+        <v>1862</v>
       </c>
       <c r="P58" s="3">
         <v>-5500</v>
@@ -7624,13 +7624,13 @@
         <v>0</v>
       </c>
       <c r="M59" s="3">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="N59" s="3">
         <v>7</v>
       </c>
       <c r="O59" s="3">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="P59" s="3">
         <v>-5500</v>
@@ -7731,13 +7731,13 @@
         <v>0</v>
       </c>
       <c r="M60" s="3">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="N60" s="3">
         <v>9</v>
       </c>
       <c r="O60" s="3">
-        <v>714</v>
+        <v>649</v>
       </c>
       <c r="P60" s="3">
         <v>-5500</v>
@@ -7838,13 +7838,13 @@
         <v>0</v>
       </c>
       <c r="M61" s="3">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="N61" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O61" s="3">
-        <v>2889</v>
+        <v>3037</v>
       </c>
       <c r="P61" s="3">
         <v>-5500</v>
@@ -7945,13 +7945,13 @@
         <v>0</v>
       </c>
       <c r="M62" s="3">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="N62" s="3">
         <v>3</v>
       </c>
       <c r="O62" s="3">
-        <v>439</v>
+        <v>400</v>
       </c>
       <c r="P62" s="3">
         <v>-5500</v>
@@ -8165,7 +8165,7 @@
         <v>14</v>
       </c>
       <c r="O64" s="3">
-        <v>1111</v>
+        <v>1049</v>
       </c>
       <c r="P64" s="3">
         <v>-5500</v>
@@ -8272,7 +8272,7 @@
         <v>20</v>
       </c>
       <c r="O65" s="3">
-        <v>4106</v>
+        <v>4468</v>
       </c>
       <c r="P65" s="3">
         <v>-5500</v>
@@ -8379,7 +8379,7 @@
         <v>5</v>
       </c>
       <c r="O66" s="3">
-        <v>682</v>
+        <v>645</v>
       </c>
       <c r="P66" s="3">
         <v>-5500</v>
@@ -8486,7 +8486,7 @@
         <v>13</v>
       </c>
       <c r="O67" s="3">
-        <v>4669</v>
+        <v>4940</v>
       </c>
       <c r="P67" s="3">
         <v>-5500</v>
@@ -8593,7 +8593,7 @@
         <v>15</v>
       </c>
       <c r="O68" s="3">
-        <v>6442</v>
+        <v>6710</v>
       </c>
       <c r="P68" s="3">
         <v>-5500</v>
@@ -8700,7 +8700,7 @@
         <v>22</v>
       </c>
       <c r="O69" s="3">
-        <v>15034</v>
+        <v>15552</v>
       </c>
       <c r="P69" s="3">
         <v>-5500</v>
@@ -8807,7 +8807,7 @@
         <v>5</v>
       </c>
       <c r="O70" s="3">
-        <v>3260</v>
+        <v>3450</v>
       </c>
       <c r="P70" s="3">
         <v>-5500</v>
@@ -9021,7 +9021,7 @@
         <v>23</v>
       </c>
       <c r="O72" s="3">
-        <v>1823</v>
+        <v>1722</v>
       </c>
       <c r="P72" s="3">
         <v>-5500</v>
@@ -9128,7 +9128,7 @@
         <v>32</v>
       </c>
       <c r="O73" s="3">
-        <v>6395</v>
+        <v>6960</v>
       </c>
       <c r="P73" s="3">
         <v>-5500</v>
@@ -9235,7 +9235,7 @@
         <v>9</v>
       </c>
       <c r="O74" s="3">
-        <v>1099</v>
+        <v>1038</v>
       </c>
       <c r="P74" s="3">
         <v>-5500</v>
@@ -9342,7 +9342,7 @@
         <v>18</v>
       </c>
       <c r="O75" s="3">
-        <v>7038</v>
+        <v>7447</v>
       </c>
       <c r="P75" s="3">
         <v>-5500</v>
@@ -9449,7 +9449,7 @@
         <v>25</v>
       </c>
       <c r="O76" s="3">
-        <v>11154</v>
+        <v>11619</v>
       </c>
       <c r="P76" s="3">
         <v>-5500</v>
@@ -9556,7 +9556,7 @@
         <v>35</v>
       </c>
       <c r="O77" s="3">
-        <v>24754</v>
+        <v>25607</v>
       </c>
       <c r="P77" s="3">
         <v>-5500</v>
@@ -9663,7 +9663,7 @@
         <v>9</v>
       </c>
       <c r="O78" s="3">
-        <v>5537</v>
+        <v>5859</v>
       </c>
       <c r="P78" s="3">
         <v>-5500</v>
@@ -9770,7 +9770,7 @@
         <v>20</v>
       </c>
       <c r="O79" s="3">
-        <v>16112</v>
+        <v>16459</v>
       </c>
       <c r="P79" s="3">
         <v>-5500</v>
@@ -9877,7 +9877,7 @@
         <v>27</v>
       </c>
       <c r="O80" s="3">
-        <v>22892</v>
+        <v>23385</v>
       </c>
       <c r="P80" s="3">
         <v>-5500</v>
@@ -9984,7 +9984,7 @@
         <v>37</v>
       </c>
       <c r="O81" s="3">
-        <v>42094</v>
+        <v>43000</v>
       </c>
       <c r="P81" s="3">
         <v>-5500</v>
@@ -10091,7 +10091,7 @@
         <v>10</v>
       </c>
       <c r="O82" s="3">
-        <v>12688</v>
+        <v>12960</v>
       </c>
       <c r="P82" s="3">
         <v>-5500</v>
@@ -10198,7 +10198,7 @@
         <v>74</v>
       </c>
       <c r="O83" s="3">
-        <v>164261</v>
+        <v>167794</v>
       </c>
       <c r="P83" s="3">
         <v>-5500</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7614C785-5546-443E-8A5B-130D7AAB3F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F5FA73E-1951-483B-A9E2-A205E60181B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11904,7 +11904,7 @@
         <v>0</v>
       </c>
       <c r="M99" s="19">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N99" s="19">
         <v>0</v>
@@ -12011,7 +12011,7 @@
         <v>0</v>
       </c>
       <c r="M100" s="19">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N100" s="19">
         <v>0</v>
@@ -12332,7 +12332,7 @@
         <v>0</v>
       </c>
       <c r="M103" s="19">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N103" s="19">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEE350E5-4280-48B0-A64A-498962F34B20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5ACA51D-BB61-4D84-9464-AF9CC3125104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6922,7 +6922,7 @@
         <v>1</v>
       </c>
       <c r="O47" s="3">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -7035,13 +7035,13 @@
         <v>0</v>
       </c>
       <c r="M48" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N48" s="3">
         <v>1</v>
       </c>
       <c r="O48" s="3">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="P48" s="3">
         <v>0</v>
@@ -7279,7 +7279,7 @@
         <v>1</v>
       </c>
       <c r="O50" s="3">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="P50" s="3">
         <v>0</v>
@@ -7392,13 +7392,13 @@
         <v>0</v>
       </c>
       <c r="M51" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N51" s="3">
         <v>2</v>
       </c>
       <c r="O51" s="3">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="P51" s="3">
         <v>0</v>
@@ -7630,13 +7630,13 @@
         <v>0</v>
       </c>
       <c r="M53" s="3">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N53" s="3">
         <v>2</v>
       </c>
       <c r="O53" s="3">
-        <v>101</v>
+        <v>135</v>
       </c>
       <c r="P53" s="3">
         <v>0</v>
@@ -7749,13 +7749,13 @@
         <v>0</v>
       </c>
       <c r="M54" s="3">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="N54" s="3">
         <v>3</v>
       </c>
       <c r="O54" s="3">
-        <v>212</v>
+        <v>342</v>
       </c>
       <c r="P54" s="3">
         <v>0</v>
@@ -7993,7 +7993,7 @@
         <v>5</v>
       </c>
       <c r="O56" s="3">
-        <v>191</v>
+        <v>254</v>
       </c>
       <c r="P56" s="3">
         <v>0</v>
@@ -8106,13 +8106,13 @@
         <v>0</v>
       </c>
       <c r="M57" s="3">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="N57" s="3">
         <v>6</v>
       </c>
       <c r="O57" s="3">
-        <v>360</v>
+        <v>583</v>
       </c>
       <c r="P57" s="3">
         <v>0</v>
@@ -8344,13 +8344,13 @@
         <v>0</v>
       </c>
       <c r="M59" s="3">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="N59" s="3">
         <v>8</v>
       </c>
       <c r="O59" s="3">
-        <v>306</v>
+        <v>408</v>
       </c>
       <c r="P59" s="3">
         <v>0</v>
@@ -8463,13 +8463,13 @@
         <v>0</v>
       </c>
       <c r="M60" s="3">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="N60" s="3">
         <v>9</v>
       </c>
       <c r="O60" s="3">
-        <v>649</v>
+        <v>1050</v>
       </c>
       <c r="P60" s="3">
         <v>0</v>
@@ -8707,7 +8707,7 @@
         <v>4</v>
       </c>
       <c r="O62" s="3">
-        <v>398</v>
+        <v>530</v>
       </c>
       <c r="P62" s="3">
         <v>0</v>
@@ -8820,13 +8820,13 @@
         <v>0</v>
       </c>
       <c r="M63" s="3">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="N63" s="3">
         <v>11</v>
       </c>
       <c r="O63" s="3">
-        <v>398</v>
+        <v>530</v>
       </c>
       <c r="P63" s="3">
         <v>0</v>
@@ -8939,13 +8939,13 @@
         <v>0</v>
       </c>
       <c r="M64" s="3">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="N64" s="3">
         <v>13</v>
       </c>
       <c r="O64" s="3">
-        <v>841</v>
+        <v>1360</v>
       </c>
       <c r="P64" s="3">
         <v>0</v>
@@ -9183,7 +9183,7 @@
         <v>5</v>
       </c>
       <c r="O66" s="3">
-        <v>518</v>
+        <v>691</v>
       </c>
       <c r="P66" s="3">
         <v>0</v>
@@ -9302,7 +9302,7 @@
         <v>15</v>
       </c>
       <c r="O67" s="3">
-        <v>5015</v>
+        <v>6687</v>
       </c>
       <c r="P67" s="3">
         <v>0</v>
@@ -9415,13 +9415,13 @@
         <v>0</v>
       </c>
       <c r="M68" s="3">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="N68" s="3">
         <v>18</v>
       </c>
       <c r="O68" s="3">
-        <v>6792</v>
+        <v>8301</v>
       </c>
       <c r="P68" s="3">
         <v>0</v>
@@ -9659,7 +9659,7 @@
         <v>6</v>
       </c>
       <c r="O70" s="3">
-        <v>3511</v>
+        <v>4682</v>
       </c>
       <c r="P70" s="3">
         <v>0</v>
@@ -9772,13 +9772,13 @@
         <v>0</v>
       </c>
       <c r="M71" s="3">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="N71" s="3">
         <v>17</v>
       </c>
       <c r="O71" s="3">
-        <v>591</v>
+        <v>788</v>
       </c>
       <c r="P71" s="3">
         <v>0</v>
@@ -9891,13 +9891,13 @@
         <v>0</v>
       </c>
       <c r="M72" s="3">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="N72" s="3">
         <v>23</v>
       </c>
       <c r="O72" s="3">
-        <v>1437</v>
+        <v>2324</v>
       </c>
       <c r="P72" s="3">
         <v>0</v>
@@ -10135,7 +10135,7 @@
         <v>9</v>
       </c>
       <c r="O74" s="3">
-        <v>871</v>
+        <v>1162</v>
       </c>
       <c r="P74" s="3">
         <v>0</v>
@@ -10254,7 +10254,7 @@
         <v>25</v>
       </c>
       <c r="O75" s="3">
-        <v>7402</v>
+        <v>9870</v>
       </c>
       <c r="P75" s="3">
         <v>0</v>
@@ -10367,13 +10367,13 @@
         <v>0</v>
       </c>
       <c r="M76" s="3">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="N76" s="3">
         <v>34</v>
       </c>
       <c r="O76" s="3">
-        <v>11500</v>
+        <v>14055</v>
       </c>
       <c r="P76" s="3">
         <v>0</v>
@@ -10611,7 +10611,7 @@
         <v>12</v>
       </c>
       <c r="O78" s="3">
-        <v>5871</v>
+        <v>7828</v>
       </c>
       <c r="P78" s="3">
         <v>0</v>
@@ -10730,7 +10730,7 @@
         <v>28</v>
       </c>
       <c r="O79" s="3">
-        <v>16333</v>
+        <v>21778</v>
       </c>
       <c r="P79" s="3">
         <v>0</v>
@@ -10843,13 +10843,13 @@
         <v>0</v>
       </c>
       <c r="M80" s="3">
-        <v>310</v>
+        <v>292</v>
       </c>
       <c r="N80" s="3">
         <v>38</v>
       </c>
       <c r="O80" s="3">
-        <v>23069</v>
+        <v>28195</v>
       </c>
       <c r="P80" s="3">
         <v>0</v>
@@ -11087,7 +11087,7 @@
         <v>14</v>
       </c>
       <c r="O82" s="3">
-        <v>12960</v>
+        <v>17281</v>
       </c>
       <c r="P82" s="3">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5ACA51D-BB61-4D84-9464-AF9CC3125104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{145D51A5-6DE1-486C-9F23-F3A8B818D22B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6922,7 +6922,7 @@
         <v>1</v>
       </c>
       <c r="O47" s="3">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -7041,7 +7041,7 @@
         <v>1</v>
       </c>
       <c r="O48" s="3">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="P48" s="3">
         <v>0</v>
@@ -7279,7 +7279,7 @@
         <v>1</v>
       </c>
       <c r="O50" s="3">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="P50" s="3">
         <v>0</v>
@@ -7636,7 +7636,7 @@
         <v>2</v>
       </c>
       <c r="O53" s="3">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="P53" s="3">
         <v>0</v>
@@ -7755,7 +7755,7 @@
         <v>3</v>
       </c>
       <c r="O54" s="3">
-        <v>342</v>
+        <v>311</v>
       </c>
       <c r="P54" s="3">
         <v>0</v>
@@ -7871,10 +7871,10 @@
         <v>56</v>
       </c>
       <c r="N55" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O55" s="3">
-        <v>999</v>
+        <v>972</v>
       </c>
       <c r="P55" s="3">
         <v>0</v>
@@ -7993,7 +7993,7 @@
         <v>5</v>
       </c>
       <c r="O56" s="3">
-        <v>254</v>
+        <v>229</v>
       </c>
       <c r="P56" s="3">
         <v>0</v>
@@ -8109,10 +8109,10 @@
         <v>89</v>
       </c>
       <c r="N57" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O57" s="3">
-        <v>583</v>
+        <v>534</v>
       </c>
       <c r="P57" s="3">
         <v>0</v>
@@ -8231,7 +8231,7 @@
         <v>10</v>
       </c>
       <c r="O58" s="3">
-        <v>1862</v>
+        <v>1788</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
@@ -8347,10 +8347,10 @@
         <v>106</v>
       </c>
       <c r="N59" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O59" s="3">
-        <v>408</v>
+        <v>369</v>
       </c>
       <c r="P59" s="3">
         <v>0</v>
@@ -8466,10 +8466,10 @@
         <v>136</v>
       </c>
       <c r="N60" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O60" s="3">
-        <v>1050</v>
+        <v>959</v>
       </c>
       <c r="P60" s="3">
         <v>0</v>
@@ -8585,10 +8585,10 @@
         <v>159</v>
       </c>
       <c r="N61" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O61" s="3">
-        <v>3007</v>
+        <v>2901</v>
       </c>
       <c r="P61" s="3">
         <v>0</v>
@@ -8823,10 +8823,10 @@
         <v>128</v>
       </c>
       <c r="N63" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O63" s="3">
-        <v>530</v>
+        <v>479</v>
       </c>
       <c r="P63" s="3">
         <v>0</v>
@@ -8942,10 +8942,10 @@
         <v>160</v>
       </c>
       <c r="N64" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O64" s="3">
-        <v>1360</v>
+        <v>1241</v>
       </c>
       <c r="P64" s="3">
         <v>0</v>
@@ -9064,7 +9064,7 @@
         <v>19</v>
       </c>
       <c r="O65" s="3">
-        <v>3566</v>
+        <v>3423</v>
       </c>
       <c r="P65" s="3">
         <v>0</v>
@@ -9775,10 +9775,10 @@
         <v>199</v>
       </c>
       <c r="N71" s="3">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O71" s="3">
-        <v>788</v>
+        <v>713</v>
       </c>
       <c r="P71" s="3">
         <v>0</v>
@@ -9894,10 +9894,10 @@
         <v>226</v>
       </c>
       <c r="N72" s="3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O72" s="3">
-        <v>2324</v>
+        <v>2124</v>
       </c>
       <c r="P72" s="3">
         <v>0</v>
@@ -10013,10 +10013,10 @@
         <v>287</v>
       </c>
       <c r="N73" s="3">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O73" s="3">
-        <v>5784</v>
+        <v>5568</v>
       </c>
       <c r="P73" s="3">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{145D51A5-6DE1-486C-9F23-F3A8B818D22B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23940CE0-ED5D-4E50-B784-EFAF3D140EA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6922,7 +6922,7 @@
         <v>1</v>
       </c>
       <c r="O47" s="3">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -7041,7 +7041,7 @@
         <v>1</v>
       </c>
       <c r="O48" s="3">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="P48" s="3">
         <v>0</v>
@@ -7276,10 +7276,10 @@
         <v>17</v>
       </c>
       <c r="N50" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O50" s="3">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="P50" s="3">
         <v>0</v>
@@ -7633,10 +7633,10 @@
         <v>37</v>
       </c>
       <c r="N53" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O53" s="3">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="P53" s="3">
         <v>0</v>
@@ -7990,10 +7990,10 @@
         <v>65</v>
       </c>
       <c r="N56" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O56" s="3">
-        <v>229</v>
+        <v>277</v>
       </c>
       <c r="P56" s="3">
         <v>0</v>
@@ -8347,10 +8347,10 @@
         <v>106</v>
       </c>
       <c r="N59" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O59" s="3">
-        <v>369</v>
+        <v>449</v>
       </c>
       <c r="P59" s="3">
         <v>0</v>
@@ -8823,10 +8823,10 @@
         <v>128</v>
       </c>
       <c r="N63" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O63" s="3">
-        <v>479</v>
+        <v>581</v>
       </c>
       <c r="P63" s="3">
         <v>0</v>
@@ -9775,10 +9775,10 @@
         <v>199</v>
       </c>
       <c r="N71" s="3">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="O71" s="3">
-        <v>713</v>
+        <v>862</v>
       </c>
       <c r="P71" s="3">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23940CE0-ED5D-4E50-B784-EFAF3D140EA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0DCACE2-7E36-4236-99F8-65E41EB3C764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6985,10 +6985,10 @@
         <v>40</v>
       </c>
       <c r="AJ47" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AK47" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AL47" s="9">
         <v>64</v>
@@ -7104,10 +7104,10 @@
         <v>40</v>
       </c>
       <c r="AJ48" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AK48" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AL48" s="9">
         <v>40</v>
@@ -7223,10 +7223,10 @@
         <v>40</v>
       </c>
       <c r="AJ49" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AK49" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AL49" s="9">
         <v>25</v>
@@ -7342,10 +7342,10 @@
         <v>40</v>
       </c>
       <c r="AJ50" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AK50" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AL50" s="9">
         <v>64</v>
@@ -7461,10 +7461,10 @@
         <v>40</v>
       </c>
       <c r="AJ51" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AK51" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AL51" s="9">
         <v>47</v>
@@ -7580,10 +7580,10 @@
         <v>40</v>
       </c>
       <c r="AJ52" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AK52" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AL52" s="9">
         <v>25</v>
@@ -7699,10 +7699,10 @@
         <v>40</v>
       </c>
       <c r="AJ53" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AK53" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AL53" s="9">
         <v>64</v>
@@ -7818,10 +7818,10 @@
         <v>40</v>
       </c>
       <c r="AJ54" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AK54" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AL54" s="9">
         <v>47</v>
@@ -7937,10 +7937,10 @@
         <v>40</v>
       </c>
       <c r="AJ55" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AK55" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AL55" s="9">
         <v>27</v>
@@ -8056,10 +8056,10 @@
         <v>40</v>
       </c>
       <c r="AJ56" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AK56" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AL56" s="9">
         <v>58</v>
@@ -8175,10 +8175,10 @@
         <v>40</v>
       </c>
       <c r="AJ57" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AK57" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AL57" s="9">
         <v>47</v>
@@ -8294,10 +8294,10 @@
         <v>40</v>
       </c>
       <c r="AJ58" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AK58" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AL58" s="9">
         <v>25</v>
@@ -8413,10 +8413,10 @@
         <v>40</v>
       </c>
       <c r="AJ59" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AK59" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AL59" s="9">
         <v>64</v>
@@ -8532,10 +8532,10 @@
         <v>40</v>
       </c>
       <c r="AJ60" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AK60" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AL60" s="9">
         <v>47</v>
@@ -8651,10 +8651,10 @@
         <v>40</v>
       </c>
       <c r="AJ61" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AK61" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AL61" s="9">
         <v>27</v>
@@ -8770,10 +8770,10 @@
         <v>40</v>
       </c>
       <c r="AJ62" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AK62" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AL62" s="9">
         <v>53</v>
@@ -8889,10 +8889,10 @@
         <v>40</v>
       </c>
       <c r="AJ63" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AK63" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AL63" s="9">
         <v>64</v>
@@ -9008,10 +9008,10 @@
         <v>40</v>
       </c>
       <c r="AJ64" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AK64" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AL64" s="9">
         <v>47</v>
@@ -9127,10 +9127,10 @@
         <v>40</v>
       </c>
       <c r="AJ65" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AK65" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AL65" s="9">
         <v>25</v>
@@ -9246,10 +9246,10 @@
         <v>40</v>
       </c>
       <c r="AJ66" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AK66" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AL66" s="9">
         <v>53</v>
@@ -9365,10 +9365,10 @@
         <v>40</v>
       </c>
       <c r="AJ67" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AK67" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AL67" s="9">
         <v>7</v>
@@ -9484,10 +9484,10 @@
         <v>40</v>
       </c>
       <c r="AJ68" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AK68" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AL68" s="9">
         <v>9</v>
@@ -9603,10 +9603,10 @@
         <v>40</v>
       </c>
       <c r="AJ69" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AK69" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AL69" s="9">
         <v>7</v>
@@ -9722,10 +9722,10 @@
         <v>40</v>
       </c>
       <c r="AJ70" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AK70" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AL70" s="9">
         <v>11</v>
@@ -9841,10 +9841,10 @@
         <v>40</v>
       </c>
       <c r="AJ71" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AK71" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AL71" s="9">
         <v>64</v>
@@ -9960,10 +9960,10 @@
         <v>40</v>
       </c>
       <c r="AJ72" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AK72" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AL72" s="9">
         <v>40</v>
@@ -10079,10 +10079,10 @@
         <v>40</v>
       </c>
       <c r="AJ73" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AK73" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AL73" s="9">
         <v>27</v>
@@ -10198,10 +10198,10 @@
         <v>40</v>
       </c>
       <c r="AJ74" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AK74" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AL74" s="9">
         <v>52</v>
@@ -10317,10 +10317,10 @@
         <v>40</v>
       </c>
       <c r="AJ75" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AK75" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AL75" s="9">
         <v>7</v>
@@ -10436,10 +10436,10 @@
         <v>40</v>
       </c>
       <c r="AJ76" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AK76" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AL76" s="9">
         <v>8</v>
@@ -10555,10 +10555,10 @@
         <v>40</v>
       </c>
       <c r="AJ77" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AK77" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AL77" s="9">
         <v>8</v>
@@ -10674,10 +10674,10 @@
         <v>40</v>
       </c>
       <c r="AJ78" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AK78" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AL78" s="9">
         <v>11</v>
@@ -10793,10 +10793,10 @@
         <v>40</v>
       </c>
       <c r="AJ79" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AK79" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AL79" s="9">
         <v>3</v>
@@ -10912,10 +10912,10 @@
         <v>40</v>
       </c>
       <c r="AJ80" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AK80" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AL80" s="9">
         <v>4</v>
@@ -11031,10 +11031,10 @@
         <v>40</v>
       </c>
       <c r="AJ81" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AK81" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AL81" s="9">
         <v>5</v>
@@ -11150,10 +11150,10 @@
         <v>40</v>
       </c>
       <c r="AJ82" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AK82" s="9">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="AL82" s="9">
         <v>5</v>
@@ -11269,10 +11269,10 @@
         <v>40</v>
       </c>
       <c r="AJ83" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AK83" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AL83" s="9">
         <v>14</v>
@@ -11382,7 +11382,7 @@
         <v>10000</v>
       </c>
       <c r="AH84" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AI84" s="9">
         <v>40</v>
@@ -11501,7 +11501,7 @@
         <v>10000</v>
       </c>
       <c r="AH85" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AI85" s="9">
         <v>40</v>
@@ -11619,8 +11619,8 @@
       <c r="AG86" s="2">
         <v>10000</v>
       </c>
-      <c r="AH86" s="2">
-        <v>25010001</v>
+      <c r="AH86" s="3">
+        <v>0</v>
       </c>
       <c r="AI86" s="9">
         <v>40</v>
@@ -11739,7 +11739,7 @@
         <v>10000</v>
       </c>
       <c r="AH87" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AI87" s="9">
         <v>40</v>
@@ -11858,7 +11858,7 @@
         <v>10000</v>
       </c>
       <c r="AH88" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AI88" s="9">
         <v>40</v>
@@ -11976,8 +11976,8 @@
       <c r="AG89" s="2">
         <v>10000</v>
       </c>
-      <c r="AH89" s="2">
-        <v>25010001</v>
+      <c r="AH89" s="3">
+        <v>0</v>
       </c>
       <c r="AI89" s="9">
         <v>40</v>
@@ -12095,8 +12095,8 @@
       <c r="AG90" s="2">
         <v>10000</v>
       </c>
-      <c r="AH90" s="2">
-        <v>25010001</v>
+      <c r="AH90" s="3">
+        <v>0</v>
       </c>
       <c r="AI90" s="9">
         <v>40</v>
@@ -12214,8 +12214,8 @@
       <c r="AG91" s="2">
         <v>10000</v>
       </c>
-      <c r="AH91" s="2">
-        <v>25010001</v>
+      <c r="AH91" s="3">
+        <v>0</v>
       </c>
       <c r="AI91" s="9">
         <v>40</v>
@@ -12333,8 +12333,8 @@
       <c r="AG92" s="2">
         <v>10000</v>
       </c>
-      <c r="AH92" s="2">
-        <v>25010001</v>
+      <c r="AH92" s="3">
+        <v>0</v>
       </c>
       <c r="AI92" s="9">
         <v>40</v>
@@ -12452,8 +12452,8 @@
       <c r="AG93" s="2">
         <v>10000</v>
       </c>
-      <c r="AH93" s="2">
-        <v>25010001</v>
+      <c r="AH93" s="3">
+        <v>0</v>
       </c>
       <c r="AI93" s="9">
         <v>40</v>
@@ -12571,8 +12571,8 @@
       <c r="AG94" s="2">
         <v>10000</v>
       </c>
-      <c r="AH94" s="2">
-        <v>25010001</v>
+      <c r="AH94" s="3">
+        <v>0</v>
       </c>
       <c r="AI94" s="9">
         <v>40</v>
@@ -12690,8 +12690,8 @@
       <c r="AG95" s="2">
         <v>10000</v>
       </c>
-      <c r="AH95" s="2">
-        <v>25010001</v>
+      <c r="AH95" s="3">
+        <v>0</v>
       </c>
       <c r="AI95" s="9">
         <v>40</v>
@@ -12810,7 +12810,7 @@
         <v>10000</v>
       </c>
       <c r="AH96" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AI96" s="9">
         <v>40</v>
@@ -12928,7 +12928,7 @@
       <c r="AG97" s="2">
         <v>10000</v>
       </c>
-      <c r="AH97" s="2">
+      <c r="AH97" s="3">
         <v>0</v>
       </c>
       <c r="AI97" s="9">
@@ -13047,7 +13047,7 @@
       <c r="AG98" s="2">
         <v>10000</v>
       </c>
-      <c r="AH98" s="2">
+      <c r="AH98" s="3">
         <v>0</v>
       </c>
       <c r="AI98" s="9">
@@ -13166,7 +13166,7 @@
       <c r="AG99" s="19">
         <v>10000</v>
       </c>
-      <c r="AH99" s="19">
+      <c r="AH99" s="3">
         <v>0</v>
       </c>
       <c r="AI99" s="19">
@@ -13285,7 +13285,7 @@
       <c r="AG100" s="19">
         <v>10000</v>
       </c>
-      <c r="AH100" s="19">
+      <c r="AH100" s="3">
         <v>0</v>
       </c>
       <c r="AI100" s="19">
@@ -13404,7 +13404,7 @@
       <c r="AG101" s="19">
         <v>10000</v>
       </c>
-      <c r="AH101" s="19">
+      <c r="AH101" s="3">
         <v>0</v>
       </c>
       <c r="AI101" s="19">
@@ -13523,7 +13523,7 @@
       <c r="AG102" s="19">
         <v>10000</v>
       </c>
-      <c r="AH102" s="19">
+      <c r="AH102" s="3">
         <v>0</v>
       </c>
       <c r="AI102" s="19">
@@ -13642,8 +13642,8 @@
       <c r="AG103" s="19">
         <v>10000</v>
       </c>
-      <c r="AH103" s="19">
-        <v>25010001</v>
+      <c r="AH103" s="3">
+        <v>0</v>
       </c>
       <c r="AI103" s="19">
         <v>40</v>
@@ -13761,8 +13761,8 @@
       <c r="AG104" s="19">
         <v>10000</v>
       </c>
-      <c r="AH104" s="19">
-        <v>25010001</v>
+      <c r="AH104" s="3">
+        <v>0</v>
       </c>
       <c r="AI104" s="19">
         <v>40</v>
@@ -13880,8 +13880,8 @@
       <c r="AG105" s="19">
         <v>10000</v>
       </c>
-      <c r="AH105" s="19">
-        <v>25010001</v>
+      <c r="AH105" s="3">
+        <v>0</v>
       </c>
       <c r="AI105" s="19">
         <v>40</v>
@@ -13999,8 +13999,8 @@
       <c r="AG106" s="19">
         <v>10000</v>
       </c>
-      <c r="AH106" s="19">
-        <v>25010001</v>
+      <c r="AH106" s="3">
+        <v>0</v>
       </c>
       <c r="AI106" s="19">
         <v>40</v>
@@ -14118,8 +14118,8 @@
       <c r="AG107" s="19">
         <v>10000</v>
       </c>
-      <c r="AH107" s="19">
-        <v>25010001</v>
+      <c r="AH107" s="3">
+        <v>0</v>
       </c>
       <c r="AI107" s="19">
         <v>40</v>
@@ -14237,7 +14237,7 @@
       <c r="AG108" s="13">
         <v>10000</v>
       </c>
-      <c r="AH108" s="13">
+      <c r="AH108" s="3">
         <v>0</v>
       </c>
       <c r="AI108" s="8">
@@ -14356,7 +14356,7 @@
       <c r="AG109" s="13">
         <v>10000</v>
       </c>
-      <c r="AH109" s="13">
+      <c r="AH109" s="3">
         <v>0</v>
       </c>
       <c r="AI109" s="8">
@@ -14475,7 +14475,7 @@
       <c r="AG110" s="13">
         <v>10000</v>
       </c>
-      <c r="AH110" s="13">
+      <c r="AH110" s="3">
         <v>0</v>
       </c>
       <c r="AI110" s="8">
@@ -14594,7 +14594,7 @@
       <c r="AG111" s="13">
         <v>10000</v>
       </c>
-      <c r="AH111" s="13">
+      <c r="AH111" s="3">
         <v>0</v>
       </c>
       <c r="AI111" s="8">
@@ -14714,7 +14714,7 @@
         <v>10000</v>
       </c>
       <c r="AH112" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AI112" s="9">
         <v>40</v>
@@ -14833,7 +14833,7 @@
         <v>10000</v>
       </c>
       <c r="AH113" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AI113" s="9">
         <v>40</v>
@@ -14951,8 +14951,8 @@
       <c r="AG114" s="2">
         <v>10000</v>
       </c>
-      <c r="AH114" s="2">
-        <v>25010001</v>
+      <c r="AH114" s="3">
+        <v>0</v>
       </c>
       <c r="AI114" s="9">
         <v>40</v>
@@ -15071,7 +15071,7 @@
         <v>10000</v>
       </c>
       <c r="AH115" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AI115" s="9">
         <v>40</v>
@@ -15190,7 +15190,7 @@
         <v>10000</v>
       </c>
       <c r="AH116" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AI116" s="9">
         <v>40</v>
@@ -15308,8 +15308,8 @@
       <c r="AG117" s="2">
         <v>10000</v>
       </c>
-      <c r="AH117" s="2">
-        <v>25010001</v>
+      <c r="AH117" s="3">
+        <v>0</v>
       </c>
       <c r="AI117" s="9">
         <v>40</v>
@@ -15427,8 +15427,8 @@
       <c r="AG118" s="2">
         <v>10000</v>
       </c>
-      <c r="AH118" s="2">
-        <v>25010001</v>
+      <c r="AH118" s="3">
+        <v>0</v>
       </c>
       <c r="AI118" s="9">
         <v>40</v>
@@ -15547,7 +15547,7 @@
         <v>10000</v>
       </c>
       <c r="AH119" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AI119" s="9">
         <v>40</v>
@@ -15666,7 +15666,7 @@
         <v>10000</v>
       </c>
       <c r="AH120" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AI120" s="9">
         <v>40</v>
@@ -15785,7 +15785,7 @@
         <v>10000</v>
       </c>
       <c r="AH121" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AI121" s="9">
         <v>40</v>
@@ -15904,7 +15904,7 @@
         <v>10000</v>
       </c>
       <c r="AH122" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AI122" s="9">
         <v>40</v>
@@ -16023,7 +16023,7 @@
         <v>10000</v>
       </c>
       <c r="AH123" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AI123" s="9">
         <v>40</v>
@@ -16142,7 +16142,7 @@
         <v>10000</v>
       </c>
       <c r="AH124" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AI124" s="9">
         <v>40</v>
@@ -16379,7 +16379,7 @@
       <c r="AG126" s="2">
         <v>10000</v>
       </c>
-      <c r="AH126" s="2">
+      <c r="AH126" s="3">
         <v>0</v>
       </c>
       <c r="AI126" s="9">
@@ -16499,7 +16499,7 @@
         <v>10000</v>
       </c>
       <c r="AH127" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AI127" s="9">
         <v>40</v>
@@ -16618,7 +16618,7 @@
         <v>10000</v>
       </c>
       <c r="AH128" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AI128" s="9">
         <v>40</v>
@@ -16736,8 +16736,8 @@
       <c r="AG129" s="2">
         <v>10000</v>
       </c>
-      <c r="AH129" s="2">
-        <v>25010001</v>
+      <c r="AH129" s="3">
+        <v>0</v>
       </c>
       <c r="AI129" s="9">
         <v>40</v>
@@ -16856,7 +16856,7 @@
         <v>10000</v>
       </c>
       <c r="AH130" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AI130" s="9">
         <v>40</v>
@@ -16975,7 +16975,7 @@
         <v>10000</v>
       </c>
       <c r="AH131" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AI131" s="9">
         <v>40</v>
@@ -17093,8 +17093,8 @@
       <c r="AG132" s="2">
         <v>10000</v>
       </c>
-      <c r="AH132" s="2">
-        <v>25010001</v>
+      <c r="AH132" s="3">
+        <v>0</v>
       </c>
       <c r="AI132" s="9">
         <v>40</v>
@@ -17212,8 +17212,8 @@
       <c r="AG133" s="2">
         <v>10000</v>
       </c>
-      <c r="AH133" s="2">
-        <v>25010001</v>
+      <c r="AH133" s="3">
+        <v>0</v>
       </c>
       <c r="AI133" s="9">
         <v>40</v>
@@ -17331,8 +17331,8 @@
       <c r="AG134" s="2">
         <v>10000</v>
       </c>
-      <c r="AH134" s="2">
-        <v>25010001</v>
+      <c r="AH134" s="3">
+        <v>0</v>
       </c>
       <c r="AI134" s="9">
         <v>40</v>
@@ -17450,8 +17450,8 @@
       <c r="AG135" s="2">
         <v>10000</v>
       </c>
-      <c r="AH135" s="2">
-        <v>25010001</v>
+      <c r="AH135" s="3">
+        <v>0</v>
       </c>
       <c r="AI135" s="9">
         <v>40</v>
@@ -17569,8 +17569,8 @@
       <c r="AG136" s="2">
         <v>10000</v>
       </c>
-      <c r="AH136" s="2">
-        <v>25010001</v>
+      <c r="AH136" s="3">
+        <v>0</v>
       </c>
       <c r="AI136" s="9">
         <v>40</v>
@@ -17688,8 +17688,8 @@
       <c r="AG137" s="2">
         <v>10000</v>
       </c>
-      <c r="AH137" s="2">
-        <v>25010001</v>
+      <c r="AH137" s="3">
+        <v>0</v>
       </c>
       <c r="AI137" s="9">
         <v>40</v>
@@ -17807,8 +17807,8 @@
       <c r="AG138" s="2">
         <v>10000</v>
       </c>
-      <c r="AH138" s="2">
-        <v>25010001</v>
+      <c r="AH138" s="3">
+        <v>0</v>
       </c>
       <c r="AI138" s="9">
         <v>40</v>
@@ -17927,7 +17927,7 @@
         <v>10000</v>
       </c>
       <c r="AH139" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AI139" s="9">
         <v>40</v>
@@ -18045,7 +18045,7 @@
       <c r="AG140" s="2">
         <v>10000</v>
       </c>
-      <c r="AH140" s="2">
+      <c r="AH140" s="3">
         <v>0</v>
       </c>
       <c r="AI140" s="9">
@@ -18164,7 +18164,7 @@
       <c r="AG141" s="2">
         <v>10000</v>
       </c>
-      <c r="AH141" s="2">
+      <c r="AH141" s="3">
         <v>0</v>
       </c>
       <c r="AI141" s="9">
@@ -18284,7 +18284,7 @@
         <v>10000</v>
       </c>
       <c r="AH142" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AI142" s="9">
         <v>40</v>
@@ -18403,7 +18403,7 @@
         <v>10000</v>
       </c>
       <c r="AH143" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AI143" s="9">
         <v>40</v>
@@ -18521,8 +18521,8 @@
       <c r="AG144" s="2">
         <v>10000</v>
       </c>
-      <c r="AH144" s="2">
-        <v>25010001</v>
+      <c r="AH144" s="3">
+        <v>0</v>
       </c>
       <c r="AI144" s="9">
         <v>40</v>
@@ -18641,7 +18641,7 @@
         <v>10000</v>
       </c>
       <c r="AH145" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AI145" s="9">
         <v>40</v>
@@ -18760,7 +18760,7 @@
         <v>10000</v>
       </c>
       <c r="AH146" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AI146" s="9">
         <v>40</v>
@@ -18878,8 +18878,8 @@
       <c r="AG147" s="2">
         <v>10000</v>
       </c>
-      <c r="AH147" s="2">
-        <v>25010001</v>
+      <c r="AH147" s="3">
+        <v>0</v>
       </c>
       <c r="AI147" s="9">
         <v>40</v>
@@ -18997,8 +18997,8 @@
       <c r="AG148" s="2">
         <v>10000</v>
       </c>
-      <c r="AH148" s="2">
-        <v>25010001</v>
+      <c r="AH148" s="3">
+        <v>0</v>
       </c>
       <c r="AI148" s="9">
         <v>40</v>
@@ -19116,8 +19116,8 @@
       <c r="AG149" s="2">
         <v>10000</v>
       </c>
-      <c r="AH149" s="2">
-        <v>25010001</v>
+      <c r="AH149" s="3">
+        <v>0</v>
       </c>
       <c r="AI149" s="9">
         <v>40</v>
@@ -19235,8 +19235,8 @@
       <c r="AG150" s="2">
         <v>10000</v>
       </c>
-      <c r="AH150" s="2">
-        <v>25010001</v>
+      <c r="AH150" s="3">
+        <v>0</v>
       </c>
       <c r="AI150" s="9">
         <v>40</v>
@@ -19354,8 +19354,8 @@
       <c r="AG151" s="2">
         <v>10000</v>
       </c>
-      <c r="AH151" s="2">
-        <v>25010001</v>
+      <c r="AH151" s="3">
+        <v>0</v>
       </c>
       <c r="AI151" s="9">
         <v>40</v>
@@ -19473,8 +19473,8 @@
       <c r="AG152" s="2">
         <v>10000</v>
       </c>
-      <c r="AH152" s="2">
-        <v>25010001</v>
+      <c r="AH152" s="3">
+        <v>0</v>
       </c>
       <c r="AI152" s="9">
         <v>40</v>
@@ -19592,8 +19592,8 @@
       <c r="AG153" s="2">
         <v>10000</v>
       </c>
-      <c r="AH153" s="2">
-        <v>25010001</v>
+      <c r="AH153" s="3">
+        <v>0</v>
       </c>
       <c r="AI153" s="9">
         <v>40</v>
@@ -19712,7 +19712,7 @@
         <v>10000</v>
       </c>
       <c r="AH154" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AI154" s="9">
         <v>40</v>
@@ -19830,7 +19830,7 @@
       <c r="AG155" s="2">
         <v>10000</v>
       </c>
-      <c r="AH155" s="2">
+      <c r="AH155" s="3">
         <v>0</v>
       </c>
       <c r="AI155" s="9">
@@ -19950,7 +19950,7 @@
         <v>10000</v>
       </c>
       <c r="AH156" s="3">
-        <v>25010001</v>
+        <v>0</v>
       </c>
       <c r="AI156" s="9">
         <v>40</v>
@@ -20068,7 +20068,7 @@
       <c r="AG157" s="24">
         <v>10000</v>
       </c>
-      <c r="AH157" s="24">
+      <c r="AH157" s="3">
         <v>0</v>
       </c>
       <c r="AI157" s="29">
@@ -20187,7 +20187,7 @@
       <c r="AG158" s="24">
         <v>10000</v>
       </c>
-      <c r="AH158" s="24">
+      <c r="AH158" s="3">
         <v>0</v>
       </c>
       <c r="AI158" s="29">
@@ -20306,7 +20306,7 @@
       <c r="AG159" s="24">
         <v>10000</v>
       </c>
-      <c r="AH159" s="24">
+      <c r="AH159" s="3">
         <v>0</v>
       </c>
       <c r="AI159" s="29">
@@ -20425,7 +20425,7 @@
       <c r="AG160" s="24">
         <v>10000</v>
       </c>
-      <c r="AH160" s="24">
+      <c r="AH160" s="3">
         <v>0</v>
       </c>
       <c r="AI160" s="29">
@@ -20544,7 +20544,7 @@
       <c r="AG161" s="24">
         <v>10000</v>
       </c>
-      <c r="AH161" s="24">
+      <c r="AH161" s="3">
         <v>0</v>
       </c>
       <c r="AI161" s="29">
@@ -20663,7 +20663,7 @@
       <c r="AG162" s="24">
         <v>10000</v>
       </c>
-      <c r="AH162" s="24">
+      <c r="AH162" s="3">
         <v>0</v>
       </c>
       <c r="AI162" s="29">
@@ -20782,7 +20782,7 @@
       <c r="AG163" s="24">
         <v>10000</v>
       </c>
-      <c r="AH163" s="24">
+      <c r="AH163" s="3">
         <v>0</v>
       </c>
       <c r="AI163" s="29">
@@ -20901,7 +20901,7 @@
       <c r="AG164" s="24">
         <v>10000</v>
       </c>
-      <c r="AH164" s="24">
+      <c r="AH164" s="3">
         <v>0</v>
       </c>
       <c r="AI164" s="29">
@@ -21020,7 +21020,7 @@
       <c r="AG165" s="24">
         <v>10000</v>
       </c>
-      <c r="AH165" s="24">
+      <c r="AH165" s="3">
         <v>0</v>
       </c>
       <c r="AI165" s="29">
@@ -21139,7 +21139,7 @@
       <c r="AG166" s="32">
         <v>10000</v>
       </c>
-      <c r="AH166" s="32">
+      <c r="AH166" s="3">
         <v>0</v>
       </c>
       <c r="AI166" s="37">
@@ -21258,7 +21258,7 @@
       <c r="AG167" s="24">
         <v>10000</v>
       </c>
-      <c r="AH167" s="24">
+      <c r="AH167" s="3">
         <v>0</v>
       </c>
       <c r="AI167" s="29">
@@ -21377,7 +21377,7 @@
       <c r="AG168" s="24">
         <v>10000</v>
       </c>
-      <c r="AH168" s="24">
+      <c r="AH168" s="3">
         <v>0</v>
       </c>
       <c r="AI168" s="29">
@@ -21496,7 +21496,7 @@
       <c r="AG169" s="24">
         <v>10000</v>
       </c>
-      <c r="AH169" s="24">
+      <c r="AH169" s="3">
         <v>0</v>
       </c>
       <c r="AI169" s="29">
@@ -21615,7 +21615,7 @@
       <c r="AG170" s="24">
         <v>10000</v>
       </c>
-      <c r="AH170" s="24">
+      <c r="AH170" s="3">
         <v>0</v>
       </c>
       <c r="AI170" s="29">
@@ -21734,7 +21734,7 @@
       <c r="AG171" s="24">
         <v>10000</v>
       </c>
-      <c r="AH171" s="24">
+      <c r="AH171" s="3">
         <v>0</v>
       </c>
       <c r="AI171" s="29">
@@ -21853,7 +21853,7 @@
       <c r="AG172" s="24">
         <v>10000</v>
       </c>
-      <c r="AH172" s="24">
+      <c r="AH172" s="3">
         <v>0</v>
       </c>
       <c r="AI172" s="29">
@@ -21972,7 +21972,7 @@
       <c r="AG173" s="24">
         <v>10000</v>
       </c>
-      <c r="AH173" s="24">
+      <c r="AH173" s="3">
         <v>0</v>
       </c>
       <c r="AI173" s="29">
@@ -22091,7 +22091,7 @@
       <c r="AG174" s="24">
         <v>10000</v>
       </c>
-      <c r="AH174" s="24">
+      <c r="AH174" s="3">
         <v>0</v>
       </c>
       <c r="AI174" s="29">
@@ -22210,7 +22210,7 @@
       <c r="AG175" s="24">
         <v>10000</v>
       </c>
-      <c r="AH175" s="24">
+      <c r="AH175" s="3">
         <v>0</v>
       </c>
       <c r="AI175" s="29">
@@ -22329,7 +22329,7 @@
       <c r="AG176" s="24">
         <v>10000</v>
       </c>
-      <c r="AH176" s="24">
+      <c r="AH176" s="3">
         <v>0</v>
       </c>
       <c r="AI176" s="29">
@@ -22448,7 +22448,7 @@
       <c r="AG177" s="24">
         <v>10000</v>
       </c>
-      <c r="AH177" s="24">
+      <c r="AH177" s="3">
         <v>0</v>
       </c>
       <c r="AI177" s="29">
@@ -22567,7 +22567,7 @@
       <c r="AG178" s="24">
         <v>10000</v>
       </c>
-      <c r="AH178" s="24">
+      <c r="AH178" s="3">
         <v>0</v>
       </c>
       <c r="AI178" s="29">
@@ -22686,7 +22686,7 @@
       <c r="AG179" s="24">
         <v>10000</v>
       </c>
-      <c r="AH179" s="24">
+      <c r="AH179" s="3">
         <v>0</v>
       </c>
       <c r="AI179" s="29">
@@ -22805,7 +22805,7 @@
       <c r="AG180" s="24">
         <v>10000</v>
       </c>
-      <c r="AH180" s="24">
+      <c r="AH180" s="3">
         <v>0</v>
       </c>
       <c r="AI180" s="29">
@@ -22924,7 +22924,7 @@
       <c r="AG181" s="24">
         <v>10000</v>
       </c>
-      <c r="AH181" s="24">
+      <c r="AH181" s="3">
         <v>0</v>
       </c>
       <c r="AI181" s="29">
@@ -23043,7 +23043,7 @@
       <c r="AG182" s="24">
         <v>10000</v>
       </c>
-      <c r="AH182" s="24">
+      <c r="AH182" s="3">
         <v>0</v>
       </c>
       <c r="AI182" s="29">
@@ -23162,7 +23162,7 @@
       <c r="AG183" s="24">
         <v>10000</v>
       </c>
-      <c r="AH183" s="24">
+      <c r="AH183" s="3">
         <v>0</v>
       </c>
       <c r="AI183" s="29">
@@ -23281,7 +23281,7 @@
       <c r="AG184" s="24">
         <v>10000</v>
       </c>
-      <c r="AH184" s="24">
+      <c r="AH184" s="3">
         <v>0</v>
       </c>
       <c r="AI184" s="29">
@@ -23400,7 +23400,7 @@
       <c r="AG185" s="24">
         <v>10000</v>
       </c>
-      <c r="AH185" s="24">
+      <c r="AH185" s="3">
         <v>0</v>
       </c>
       <c r="AI185" s="29">
@@ -23519,7 +23519,7 @@
       <c r="AG186" s="24">
         <v>10000</v>
       </c>
-      <c r="AH186" s="24">
+      <c r="AH186" s="3">
         <v>0</v>
       </c>
       <c r="AI186" s="29">
@@ -23638,7 +23638,7 @@
       <c r="AG187" s="24">
         <v>10000</v>
       </c>
-      <c r="AH187" s="24">
+      <c r="AH187" s="3">
         <v>0</v>
       </c>
       <c r="AI187" s="29">
@@ -23757,7 +23757,7 @@
       <c r="AG188" s="24">
         <v>10000</v>
       </c>
-      <c r="AH188" s="24">
+      <c r="AH188" s="3">
         <v>0</v>
       </c>
       <c r="AI188" s="29">
@@ -23876,7 +23876,7 @@
       <c r="AG189" s="24">
         <v>10000</v>
       </c>
-      <c r="AH189" s="24">
+      <c r="AH189" s="3">
         <v>0</v>
       </c>
       <c r="AI189" s="29">
@@ -23995,7 +23995,7 @@
       <c r="AG190" s="24">
         <v>10000</v>
       </c>
-      <c r="AH190" s="24">
+      <c r="AH190" s="3">
         <v>0</v>
       </c>
       <c r="AI190" s="29">
@@ -24114,7 +24114,7 @@
       <c r="AG191" s="24">
         <v>10000</v>
       </c>
-      <c r="AH191" s="24">
+      <c r="AH191" s="3">
         <v>0</v>
       </c>
       <c r="AI191" s="29">
@@ -24233,7 +24233,7 @@
       <c r="AG192" s="24">
         <v>10000</v>
       </c>
-      <c r="AH192" s="24">
+      <c r="AH192" s="3">
         <v>0</v>
       </c>
       <c r="AI192" s="29">
@@ -24352,7 +24352,7 @@
       <c r="AG193" s="24">
         <v>10000</v>
       </c>
-      <c r="AH193" s="24">
+      <c r="AH193" s="3">
         <v>0</v>
       </c>
       <c r="AI193" s="29">
@@ -24471,7 +24471,7 @@
       <c r="AG194" s="24">
         <v>10000</v>
       </c>
-      <c r="AH194" s="24">
+      <c r="AH194" s="3">
         <v>0</v>
       </c>
       <c r="AI194" s="29">
@@ -24590,7 +24590,7 @@
       <c r="AG195" s="24">
         <v>10000</v>
       </c>
-      <c r="AH195" s="24">
+      <c r="AH195" s="3">
         <v>0</v>
       </c>
       <c r="AI195" s="29">
@@ -24709,7 +24709,7 @@
       <c r="AG196" s="24">
         <v>10000</v>
       </c>
-      <c r="AH196" s="24">
+      <c r="AH196" s="3">
         <v>0</v>
       </c>
       <c r="AI196" s="29">

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0DCACE2-7E36-4236-99F8-65E41EB3C764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30105FA7-C679-46BF-A0FF-9BDF96044D66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6916,13 +6916,13 @@
         <v>0</v>
       </c>
       <c r="M47" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N47" s="3">
         <v>1</v>
       </c>
       <c r="O47" s="3">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -7035,13 +7035,13 @@
         <v>0</v>
       </c>
       <c r="M48" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N48" s="3">
         <v>1</v>
       </c>
       <c r="O48" s="3">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="P48" s="3">
         <v>0</v>
@@ -7154,13 +7154,13 @@
         <v>0</v>
       </c>
       <c r="M49" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N49" s="3">
         <v>1</v>
       </c>
       <c r="O49" s="3">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="P49" s="3">
         <v>0</v>
@@ -7276,10 +7276,10 @@
         <v>17</v>
       </c>
       <c r="N50" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O50" s="3">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="P50" s="3">
         <v>0</v>
@@ -7392,13 +7392,13 @@
         <v>0</v>
       </c>
       <c r="M51" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N51" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O51" s="3">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="P51" s="3">
         <v>0</v>
@@ -7517,7 +7517,7 @@
         <v>2</v>
       </c>
       <c r="O52" s="3">
-        <v>355</v>
+        <v>337</v>
       </c>
       <c r="P52" s="3">
         <v>0</v>
@@ -7633,10 +7633,10 @@
         <v>37</v>
       </c>
       <c r="N53" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O53" s="3">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="P53" s="3">
         <v>0</v>
@@ -7749,13 +7749,13 @@
         <v>0</v>
       </c>
       <c r="M54" s="3">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N54" s="3">
         <v>3</v>
       </c>
       <c r="O54" s="3">
-        <v>311</v>
+        <v>296</v>
       </c>
       <c r="P54" s="3">
         <v>0</v>
@@ -7874,7 +7874,7 @@
         <v>4</v>
       </c>
       <c r="O55" s="3">
-        <v>972</v>
+        <v>851</v>
       </c>
       <c r="P55" s="3">
         <v>0</v>
@@ -7990,10 +7990,10 @@
         <v>65</v>
       </c>
       <c r="N56" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O56" s="3">
-        <v>277</v>
+        <v>241</v>
       </c>
       <c r="P56" s="3">
         <v>0</v>
@@ -8106,7 +8106,7 @@
         <v>0</v>
       </c>
       <c r="M57" s="3">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="N57" s="3">
         <v>5</v>
@@ -8228,10 +8228,10 @@
         <v>96</v>
       </c>
       <c r="N58" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O58" s="3">
-        <v>1788</v>
+        <v>1652</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
@@ -8347,10 +8347,10 @@
         <v>106</v>
       </c>
       <c r="N59" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O59" s="3">
-        <v>449</v>
+        <v>390</v>
       </c>
       <c r="P59" s="3">
         <v>0</v>
@@ -8463,13 +8463,13 @@
         <v>0</v>
       </c>
       <c r="M60" s="3">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="N60" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O60" s="3">
-        <v>959</v>
+        <v>1002</v>
       </c>
       <c r="P60" s="3">
         <v>0</v>
@@ -8588,7 +8588,7 @@
         <v>14</v>
       </c>
       <c r="O61" s="3">
-        <v>2901</v>
+        <v>2780</v>
       </c>
       <c r="P61" s="3">
         <v>0</v>
@@ -8823,10 +8823,10 @@
         <v>128</v>
       </c>
       <c r="N63" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="O63" s="3">
-        <v>581</v>
+        <v>505</v>
       </c>
       <c r="P63" s="3">
         <v>0</v>
@@ -8939,13 +8939,13 @@
         <v>0</v>
       </c>
       <c r="M64" s="3">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="N64" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O64" s="3">
-        <v>1241</v>
+        <v>1299</v>
       </c>
       <c r="P64" s="3">
         <v>0</v>
@@ -9061,10 +9061,10 @@
         <v>171</v>
       </c>
       <c r="N65" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O65" s="3">
-        <v>3423</v>
+        <v>3293</v>
       </c>
       <c r="P65" s="3">
         <v>0</v>
@@ -9302,7 +9302,7 @@
         <v>15</v>
       </c>
       <c r="O67" s="3">
-        <v>6687</v>
+        <v>6383</v>
       </c>
       <c r="P67" s="3">
         <v>0</v>
@@ -9421,7 +9421,7 @@
         <v>18</v>
       </c>
       <c r="O68" s="3">
-        <v>8301</v>
+        <v>7956</v>
       </c>
       <c r="P68" s="3">
         <v>0</v>
@@ -9537,10 +9537,10 @@
         <v>232</v>
       </c>
       <c r="N69" s="3">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="O69" s="3">
-        <v>15698</v>
+        <v>14625</v>
       </c>
       <c r="P69" s="3">
         <v>0</v>
@@ -9775,10 +9775,10 @@
         <v>199</v>
       </c>
       <c r="N71" s="3">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="O71" s="3">
-        <v>862</v>
+        <v>751</v>
       </c>
       <c r="P71" s="3">
         <v>0</v>
@@ -9891,13 +9891,13 @@
         <v>0</v>
       </c>
       <c r="M72" s="3">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="N72" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O72" s="3">
-        <v>2124</v>
+        <v>2224</v>
       </c>
       <c r="P72" s="3">
         <v>0</v>
@@ -10013,10 +10013,10 @@
         <v>287</v>
       </c>
       <c r="N73" s="3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O73" s="3">
-        <v>5568</v>
+        <v>5350</v>
       </c>
       <c r="P73" s="3">
         <v>0</v>
@@ -10251,10 +10251,10 @@
         <v>273</v>
       </c>
       <c r="N75" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O75" s="3">
-        <v>9870</v>
+        <v>9440</v>
       </c>
       <c r="P75" s="3">
         <v>0</v>
@@ -10370,10 +10370,10 @@
         <v>279</v>
       </c>
       <c r="N76" s="3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="O76" s="3">
-        <v>14055</v>
+        <v>13525</v>
       </c>
       <c r="P76" s="3">
         <v>0</v>
@@ -10489,10 +10489,10 @@
         <v>352</v>
       </c>
       <c r="N77" s="3">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="O77" s="3">
-        <v>25233</v>
+        <v>23513</v>
       </c>
       <c r="P77" s="3">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1C4DF31-4181-4EF0-A7D8-5D05D343D0A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F97AA276-EDC3-465B-B6E7-1AA8852F8B7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1824,10 +1824,10 @@
         <v>50</v>
       </c>
       <c r="P4" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q4" s="12" t="s">
         <v>247</v>
-      </c>
-      <c r="Q4" s="12" t="s">
-        <v>248</v>
       </c>
       <c r="R4" s="12" t="s">
         <v>249</v>
@@ -11344,10 +11344,10 @@
         <v>56</v>
       </c>
       <c r="P84" s="3">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="Q84" s="3">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="R84" s="3">
         <v>0</v>
@@ -11463,10 +11463,10 @@
         <v>56</v>
       </c>
       <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
         <v>6000</v>
-      </c>
-      <c r="Q85" s="3">
-        <v>0</v>
       </c>
       <c r="R85" s="3">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F97AA276-EDC3-465B-B6E7-1AA8852F8B7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8B3D23C-091D-46E1-ACAC-F7233E0520CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_foe_v8" sheetId="1" r:id="rId1"/>
-    <sheet name="怪物难度" sheetId="5" r:id="rId2"/>
-    <sheet name="备注资源组与动作id" sheetId="2" r:id="rId3"/>
-    <sheet name="掉落" sheetId="3" r:id="rId4"/>
+    <sheet name="maze_foe_attr_v8" sheetId="6" r:id="rId2"/>
+    <sheet name="怪物难度" sheetId="5" r:id="rId3"/>
+    <sheet name="备注资源组与动作id" sheetId="2" r:id="rId4"/>
+    <sheet name="掉落" sheetId="3" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_foe_v8!$A$2:$AI$103</definedName>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="971" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1865" uniqueCount="270">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -841,6 +842,46 @@
   <si>
     <t>强盗抗电</t>
   </si>
+  <si>
+    <t>属性id</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>MAP&lt;INT:INT&gt;_S</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>extra_attr</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>额外属性列表</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>STRING</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>desc1</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>0:0</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>extra_attr_list</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>额外属性id列表</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1073,7 +1114,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1185,6 +1226,21 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1194,7 +1250,37 @@
     <cellStyle name="输入" xfId="1" builtinId="20"/>
     <cellStyle name="输入 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1477,7 +1563,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AM201"/>
+  <dimension ref="A1:AN201"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.125" style="9" customWidth="1"/>
@@ -1501,10 +1587,11 @@
     <col min="37" max="37" width="40.125" style="9" customWidth="1"/>
     <col min="38" max="38" width="13.875" style="9" customWidth="1"/>
     <col min="39" max="39" width="20.5" style="9" customWidth="1"/>
-    <col min="40" max="16384" width="9" style="9"/>
+    <col min="40" max="40" width="15" style="9" bestFit="1" customWidth="1"/>
+    <col min="41" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1539,7 +1626,7 @@
       <c r="AG1" s="3"/>
       <c r="AH1" s="3"/>
     </row>
-    <row r="2" spans="1:39" ht="14.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:40" ht="14.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
@@ -1657,8 +1744,11 @@
       <c r="AM2" s="10" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:39" ht="14.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="AN2" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:40" ht="14.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>9</v>
       </c>
@@ -1776,8 +1866,11 @@
       <c r="AM3" s="9" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="4" spans="1:39" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="AN3" s="9" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="4" spans="1:40" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>38</v>
       </c>
@@ -1895,8 +1988,11 @@
       <c r="AM4" s="9" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="AN4" s="9" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>10201</v>
       </c>
@@ -2015,7 +2111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>10301</v>
       </c>
@@ -2134,7 +2230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>10302</v>
       </c>
@@ -2253,7 +2349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>10303</v>
       </c>
@@ -2372,7 +2468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>10304</v>
       </c>
@@ -2491,7 +2587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>10305</v>
       </c>
@@ -2610,7 +2706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>10306</v>
       </c>
@@ -2729,7 +2825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>10307</v>
       </c>
@@ -2848,7 +2944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>10308</v>
       </c>
@@ -2967,7 +3063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>10309</v>
       </c>
@@ -3086,7 +3182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>10310</v>
       </c>
@@ -3205,7 +3301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>10401</v>
       </c>
@@ -25345,7 +25441,7 @@
   </sortState>
   <phoneticPr fontId="13" type="noConversion"/>
   <conditionalFormatting sqref="A117:A1048576 A1:A103">
-    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="34"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -25353,6 +25449,90 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEA96066-ADA1-4DBD-A542-A7B804C67E6E}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="20.5" style="39" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.25" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="41"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="40" t="s">
+        <v>262</v>
+      </c>
+      <c r="C3" s="42" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B4" s="40" t="s">
+        <v>263</v>
+      </c>
+      <c r="C4" s="42" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="39">
+        <v>1</v>
+      </c>
+      <c r="B5" s="43" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="39">
+        <v>2</v>
+      </c>
+      <c r="B6" s="43" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="39">
+        <v>3</v>
+      </c>
+      <c r="B7" s="43" t="s">
+        <v>267</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="13" type="noConversion"/>
+  <conditionalFormatting sqref="A1:A4">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:C2">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="I1:S28"/>
@@ -26073,7 +26253,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A6:O22"/>
@@ -26717,7 +26897,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="B2:K162"/>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,16 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8B3D23C-091D-46E1-ACAC-F7233E0520CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CE8050E-16A9-4CF3-A079-A2D86A6CBD34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_foe_v8" sheetId="1" r:id="rId1"/>
-    <sheet name="maze_foe_attr_v8" sheetId="6" r:id="rId2"/>
-    <sheet name="怪物难度" sheetId="5" r:id="rId3"/>
-    <sheet name="备注资源组与动作id" sheetId="2" r:id="rId4"/>
-    <sheet name="掉落" sheetId="3" r:id="rId5"/>
+    <sheet name="怪物难度" sheetId="5" r:id="rId2"/>
+    <sheet name="备注资源组与动作id" sheetId="2" r:id="rId3"/>
+    <sheet name="掉落" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_foe_v8!$A$2:$AI$103</definedName>
@@ -38,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1865" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="971" uniqueCount="260">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -842,46 +841,6 @@
   <si>
     <t>强盗抗电</t>
   </si>
-  <si>
-    <t>属性id</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>MAP&lt;INT:INT&gt;_S</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>extra_attr</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>额外属性列表</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>STRING</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>desc1</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>备注</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>0:0</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>extra_attr_list</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>额外属性id列表</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
 </sst>
 </file>
 
@@ -1114,7 +1073,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1226,21 +1185,6 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1250,37 +1194,7 @@
     <cellStyle name="输入" xfId="1" builtinId="20"/>
     <cellStyle name="输入 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1563,7 +1477,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AN201"/>
+  <dimension ref="A1:AM201"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.125" style="9" customWidth="1"/>
@@ -1587,11 +1501,10 @@
     <col min="37" max="37" width="40.125" style="9" customWidth="1"/>
     <col min="38" max="38" width="13.875" style="9" customWidth="1"/>
     <col min="39" max="39" width="20.5" style="9" customWidth="1"/>
-    <col min="40" max="40" width="15" style="9" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9" style="9"/>
+    <col min="40" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1626,7 +1539,7 @@
       <c r="AG1" s="3"/>
       <c r="AH1" s="3"/>
     </row>
-    <row r="2" spans="1:40" ht="14.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:39" ht="14.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
@@ -1744,11 +1657,8 @@
       <c r="AM2" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="AN2" s="10" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:40" ht="14.25" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:39" ht="14.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>9</v>
       </c>
@@ -1866,11 +1776,8 @@
       <c r="AM3" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="AN3" s="9" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="4" spans="1:40" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:39" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>38</v>
       </c>
@@ -1988,11 +1895,8 @@
       <c r="AM4" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="AN4" s="9" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>10201</v>
       </c>
@@ -2111,7 +2015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>10301</v>
       </c>
@@ -2230,7 +2134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>10302</v>
       </c>
@@ -2349,7 +2253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>10303</v>
       </c>
@@ -2468,7 +2372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>10304</v>
       </c>
@@ -2587,7 +2491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>10305</v>
       </c>
@@ -2706,7 +2610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>10306</v>
       </c>
@@ -2825,7 +2729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>10307</v>
       </c>
@@ -2944,7 +2848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>10308</v>
       </c>
@@ -3063,7 +2967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>10309</v>
       </c>
@@ -3182,7 +3086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>10310</v>
       </c>
@@ -3301,7 +3205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>10401</v>
       </c>
@@ -7097,10 +7001,10 @@
         <v>40</v>
       </c>
       <c r="AJ47" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AK47" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AL47" s="9">
         <v>64</v>
@@ -7216,10 +7120,10 @@
         <v>40</v>
       </c>
       <c r="AJ48" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AK48" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AL48" s="9">
         <v>40</v>
@@ -7335,10 +7239,10 @@
         <v>40</v>
       </c>
       <c r="AJ49" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AK49" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AL49" s="9">
         <v>25</v>
@@ -7454,10 +7358,10 @@
         <v>40</v>
       </c>
       <c r="AJ50" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AK50" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AL50" s="9">
         <v>64</v>
@@ -7573,10 +7477,10 @@
         <v>40</v>
       </c>
       <c r="AJ51" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AK51" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AL51" s="9">
         <v>47</v>
@@ -7692,10 +7596,10 @@
         <v>40</v>
       </c>
       <c r="AJ52" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AK52" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AL52" s="9">
         <v>25</v>
@@ -7811,10 +7715,10 @@
         <v>40</v>
       </c>
       <c r="AJ53" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AK53" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AL53" s="9">
         <v>64</v>
@@ -7930,10 +7834,10 @@
         <v>40</v>
       </c>
       <c r="AJ54" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AK54" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AL54" s="9">
         <v>47</v>
@@ -8049,10 +7953,10 @@
         <v>40</v>
       </c>
       <c r="AJ55" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AK55" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AL55" s="9">
         <v>27</v>
@@ -8168,10 +8072,10 @@
         <v>40</v>
       </c>
       <c r="AJ56" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AK56" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AL56" s="9">
         <v>58</v>
@@ -8287,10 +8191,10 @@
         <v>40</v>
       </c>
       <c r="AJ57" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AK57" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AL57" s="9">
         <v>47</v>
@@ -8406,10 +8310,10 @@
         <v>40</v>
       </c>
       <c r="AJ58" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AK58" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AL58" s="9">
         <v>25</v>
@@ -8525,10 +8429,10 @@
         <v>40</v>
       </c>
       <c r="AJ59" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AK59" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AL59" s="9">
         <v>64</v>
@@ -8644,10 +8548,10 @@
         <v>40</v>
       </c>
       <c r="AJ60" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AK60" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AL60" s="9">
         <v>47</v>
@@ -8763,10 +8667,10 @@
         <v>40</v>
       </c>
       <c r="AJ61" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AK61" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AL61" s="9">
         <v>27</v>
@@ -8882,10 +8786,10 @@
         <v>40</v>
       </c>
       <c r="AJ62" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AK62" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AL62" s="9">
         <v>53</v>
@@ -9001,10 +8905,10 @@
         <v>40</v>
       </c>
       <c r="AJ63" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AK63" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AL63" s="9">
         <v>64</v>
@@ -9120,10 +9024,10 @@
         <v>40</v>
       </c>
       <c r="AJ64" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AK64" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AL64" s="9">
         <v>47</v>
@@ -9239,10 +9143,10 @@
         <v>40</v>
       </c>
       <c r="AJ65" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AK65" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AL65" s="9">
         <v>25</v>
@@ -9358,10 +9262,10 @@
         <v>40</v>
       </c>
       <c r="AJ66" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AK66" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AL66" s="9">
         <v>53</v>
@@ -9477,10 +9381,10 @@
         <v>40</v>
       </c>
       <c r="AJ67" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AK67" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AL67" s="9">
         <v>7</v>
@@ -9596,10 +9500,10 @@
         <v>40</v>
       </c>
       <c r="AJ68" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AK68" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AL68" s="9">
         <v>9</v>
@@ -9715,10 +9619,10 @@
         <v>40</v>
       </c>
       <c r="AJ69" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AK69" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AL69" s="9">
         <v>7</v>
@@ -9834,10 +9738,10 @@
         <v>40</v>
       </c>
       <c r="AJ70" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AK70" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AL70" s="9">
         <v>11</v>
@@ -9953,10 +9857,10 @@
         <v>40</v>
       </c>
       <c r="AJ71" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AK71" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AL71" s="9">
         <v>64</v>
@@ -10072,10 +9976,10 @@
         <v>40</v>
       </c>
       <c r="AJ72" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AK72" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AL72" s="9">
         <v>40</v>
@@ -10191,10 +10095,10 @@
         <v>40</v>
       </c>
       <c r="AJ73" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AK73" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AL73" s="9">
         <v>27</v>
@@ -10310,10 +10214,10 @@
         <v>40</v>
       </c>
       <c r="AJ74" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AK74" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AL74" s="9">
         <v>52</v>
@@ -10429,10 +10333,10 @@
         <v>40</v>
       </c>
       <c r="AJ75" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AK75" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AL75" s="9">
         <v>7</v>
@@ -10548,10 +10452,10 @@
         <v>40</v>
       </c>
       <c r="AJ76" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AK76" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AL76" s="9">
         <v>8</v>
@@ -10667,10 +10571,10 @@
         <v>40</v>
       </c>
       <c r="AJ77" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AK77" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AL77" s="9">
         <v>8</v>
@@ -10786,10 +10690,10 @@
         <v>40</v>
       </c>
       <c r="AJ78" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AK78" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AL78" s="9">
         <v>11</v>
@@ -10905,10 +10809,10 @@
         <v>40</v>
       </c>
       <c r="AJ79" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AK79" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AL79" s="9">
         <v>3</v>
@@ -11024,10 +10928,10 @@
         <v>40</v>
       </c>
       <c r="AJ80" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AK80" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AL80" s="9">
         <v>4</v>
@@ -11143,10 +11047,10 @@
         <v>40</v>
       </c>
       <c r="AJ81" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AK81" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AL81" s="9">
         <v>5</v>
@@ -11262,10 +11166,10 @@
         <v>40</v>
       </c>
       <c r="AJ82" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AK82" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AL82" s="9">
         <v>5</v>
@@ -11500,10 +11404,10 @@
         <v>40</v>
       </c>
       <c r="AJ84" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AK84" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AL84" s="9">
         <v>64</v>
@@ -11619,7 +11523,7 @@
         <v>40</v>
       </c>
       <c r="AJ85" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AK85" s="9">
         <v>6000</v>
@@ -11738,7 +11642,7 @@
         <v>40</v>
       </c>
       <c r="AJ86" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AK86" s="9">
         <v>6000</v>
@@ -11857,7 +11761,7 @@
         <v>40</v>
       </c>
       <c r="AJ87" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AK87" s="9">
         <v>6000</v>
@@ -11976,7 +11880,7 @@
         <v>40</v>
       </c>
       <c r="AJ88" s="9">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="AK88" s="9">
         <v>6000</v>
@@ -25441,7 +25345,7 @@
   </sortState>
   <phoneticPr fontId="13" type="noConversion"/>
   <conditionalFormatting sqref="A117:A1048576 A1:A103">
-    <cfRule type="duplicateValues" dxfId="3" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -25449,90 +25353,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEA96066-ADA1-4DBD-A542-A7B804C67E6E}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="20.5" style="39" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.25" style="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9" style="41"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="40" t="s">
-        <v>262</v>
-      </c>
-      <c r="C3" s="42" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="B4" s="40" t="s">
-        <v>263</v>
-      </c>
-      <c r="C4" s="42" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="39">
-        <v>1</v>
-      </c>
-      <c r="B5" s="43" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="39">
-        <v>2</v>
-      </c>
-      <c r="B6" s="43" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="39">
-        <v>3</v>
-      </c>
-      <c r="B7" s="43" t="s">
-        <v>267</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="13" type="noConversion"/>
-  <conditionalFormatting sqref="A1:A4">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2:C2">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="I1:S28"/>
@@ -26253,7 +26073,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A6:O22"/>
@@ -26897,7 +26717,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="B2:K162"/>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CE8050E-16A9-4CF3-A079-A2D86A6CBD34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5D7B9FF-4AB0-40AC-B012-3FB149E84DC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7001,10 +7001,10 @@
         <v>40</v>
       </c>
       <c r="AJ47" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AK47" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AL47" s="9">
         <v>64</v>
@@ -7120,10 +7120,10 @@
         <v>40</v>
       </c>
       <c r="AJ48" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AK48" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AL48" s="9">
         <v>40</v>
@@ -7239,10 +7239,10 @@
         <v>40</v>
       </c>
       <c r="AJ49" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AK49" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AL49" s="9">
         <v>25</v>
@@ -7358,10 +7358,10 @@
         <v>40</v>
       </c>
       <c r="AJ50" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AK50" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AL50" s="9">
         <v>64</v>
@@ -7477,10 +7477,10 @@
         <v>40</v>
       </c>
       <c r="AJ51" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AK51" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AL51" s="9">
         <v>47</v>
@@ -7596,10 +7596,10 @@
         <v>40</v>
       </c>
       <c r="AJ52" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AK52" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AL52" s="9">
         <v>25</v>
@@ -7715,10 +7715,10 @@
         <v>40</v>
       </c>
       <c r="AJ53" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AK53" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AL53" s="9">
         <v>64</v>
@@ -7834,10 +7834,10 @@
         <v>40</v>
       </c>
       <c r="AJ54" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AK54" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AL54" s="9">
         <v>47</v>
@@ -7953,10 +7953,10 @@
         <v>40</v>
       </c>
       <c r="AJ55" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AK55" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AL55" s="9">
         <v>27</v>
@@ -8072,10 +8072,10 @@
         <v>40</v>
       </c>
       <c r="AJ56" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AK56" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AL56" s="9">
         <v>58</v>
@@ -8191,10 +8191,10 @@
         <v>40</v>
       </c>
       <c r="AJ57" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AK57" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AL57" s="9">
         <v>47</v>
@@ -8310,10 +8310,10 @@
         <v>40</v>
       </c>
       <c r="AJ58" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AK58" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AL58" s="9">
         <v>25</v>
@@ -8429,10 +8429,10 @@
         <v>40</v>
       </c>
       <c r="AJ59" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AK59" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AL59" s="9">
         <v>64</v>
@@ -8548,10 +8548,10 @@
         <v>40</v>
       </c>
       <c r="AJ60" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AK60" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AL60" s="9">
         <v>47</v>
@@ -8667,10 +8667,10 @@
         <v>40</v>
       </c>
       <c r="AJ61" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AK61" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AL61" s="9">
         <v>27</v>
@@ -8786,10 +8786,10 @@
         <v>40</v>
       </c>
       <c r="AJ62" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AK62" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AL62" s="9">
         <v>53</v>
@@ -8905,10 +8905,10 @@
         <v>40</v>
       </c>
       <c r="AJ63" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AK63" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AL63" s="9">
         <v>64</v>
@@ -9024,10 +9024,10 @@
         <v>40</v>
       </c>
       <c r="AJ64" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AK64" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AL64" s="9">
         <v>47</v>
@@ -9143,10 +9143,10 @@
         <v>40</v>
       </c>
       <c r="AJ65" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AK65" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AL65" s="9">
         <v>25</v>
@@ -9262,10 +9262,10 @@
         <v>40</v>
       </c>
       <c r="AJ66" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AK66" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AL66" s="9">
         <v>53</v>
@@ -9381,10 +9381,10 @@
         <v>40</v>
       </c>
       <c r="AJ67" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AK67" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AL67" s="9">
         <v>7</v>
@@ -9500,10 +9500,10 @@
         <v>40</v>
       </c>
       <c r="AJ68" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AK68" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AL68" s="9">
         <v>9</v>
@@ -9619,10 +9619,10 @@
         <v>40</v>
       </c>
       <c r="AJ69" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AK69" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AL69" s="9">
         <v>7</v>
@@ -9738,10 +9738,10 @@
         <v>40</v>
       </c>
       <c r="AJ70" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AK70" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AL70" s="9">
         <v>11</v>
@@ -9857,10 +9857,10 @@
         <v>40</v>
       </c>
       <c r="AJ71" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AK71" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AL71" s="9">
         <v>64</v>
@@ -9976,10 +9976,10 @@
         <v>40</v>
       </c>
       <c r="AJ72" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AK72" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AL72" s="9">
         <v>40</v>
@@ -10095,10 +10095,10 @@
         <v>40</v>
       </c>
       <c r="AJ73" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AK73" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AL73" s="9">
         <v>27</v>
@@ -10214,10 +10214,10 @@
         <v>40</v>
       </c>
       <c r="AJ74" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AK74" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AL74" s="9">
         <v>52</v>
@@ -10333,10 +10333,10 @@
         <v>40</v>
       </c>
       <c r="AJ75" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AK75" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AL75" s="9">
         <v>7</v>
@@ -10452,10 +10452,10 @@
         <v>40</v>
       </c>
       <c r="AJ76" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AK76" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AL76" s="9">
         <v>8</v>
@@ -10571,10 +10571,10 @@
         <v>40</v>
       </c>
       <c r="AJ77" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AK77" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AL77" s="9">
         <v>8</v>
@@ -10690,10 +10690,10 @@
         <v>40</v>
       </c>
       <c r="AJ78" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AK78" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AL78" s="9">
         <v>11</v>
@@ -10809,10 +10809,10 @@
         <v>40</v>
       </c>
       <c r="AJ79" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AK79" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AL79" s="9">
         <v>3</v>
@@ -10928,10 +10928,10 @@
         <v>40</v>
       </c>
       <c r="AJ80" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AK80" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AL80" s="9">
         <v>4</v>
@@ -11047,10 +11047,10 @@
         <v>40</v>
       </c>
       <c r="AJ81" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AK81" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AL81" s="9">
         <v>5</v>
@@ -11166,10 +11166,10 @@
         <v>40</v>
       </c>
       <c r="AJ82" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AK82" s="9">
-        <v>8000</v>
+        <v>6250</v>
       </c>
       <c r="AL82" s="9">
         <v>5</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8B78741-6F34-4745-9819-C006ACEE10A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D70EA58-3E90-404F-BA93-3501DB8B29E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="268">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -854,6 +854,18 @@
   <si>
     <t>强盗4</t>
   </si>
+  <si>
+    <t>强盗抗冰</t>
+  </si>
+  <si>
+    <t>强盗抗毒</t>
+  </si>
+  <si>
+    <t>强盗抗电</t>
+  </si>
+  <si>
+    <t>强盗1</t>
+  </si>
 </sst>
 </file>
 
@@ -12511,10 +12523,10 @@
         <v>92</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E94" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>67</v>
@@ -12522,29 +12534,29 @@
       <c r="G94" s="3">
         <v>0</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
+      <c r="H94" s="3" t="s">
+        <v>264</v>
       </c>
       <c r="I94" s="3">
-        <v>0</v>
+        <v>800002012</v>
       </c>
       <c r="J94" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K94" s="3">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="L94" s="3">
         <v>0</v>
       </c>
       <c r="M94" s="3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N94" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O94" s="3">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="P94" s="3">
         <v>0</v>
@@ -12568,22 +12580,22 @@
         <v>1</v>
       </c>
       <c r="W94" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X94" s="3">
         <v>0</v>
       </c>
       <c r="Y94" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z94" s="3">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="AA94" s="3">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="AB94" s="16">
-        <v>0</v>
+        <v>202001001</v>
       </c>
       <c r="AC94" s="16">
         <v>0</v>
@@ -12613,7 +12625,7 @@
         <v>6000</v>
       </c>
       <c r="AL94" s="9">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AM94" s="9">
         <v>0</v>
@@ -12630,10 +12642,10 @@
         <v>92</v>
       </c>
       <c r="D95" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E95" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>67</v>
@@ -12641,29 +12653,29 @@
       <c r="G95" s="3">
         <v>0</v>
       </c>
-      <c r="H95" s="3">
-        <v>0</v>
+      <c r="H95" s="3" t="s">
+        <v>265</v>
       </c>
       <c r="I95" s="3">
-        <v>0</v>
+        <v>800002015</v>
       </c>
       <c r="J95" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K95" s="3">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="L95" s="3">
         <v>0</v>
       </c>
       <c r="M95" s="3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N95" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O95" s="3">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="P95" s="3">
         <v>0</v>
@@ -12687,22 +12699,22 @@
         <v>1</v>
       </c>
       <c r="W95" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X95" s="3">
         <v>0</v>
       </c>
       <c r="Y95" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z95" s="3">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="AA95" s="3">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="AB95" s="16">
-        <v>0</v>
+        <v>202001001</v>
       </c>
       <c r="AC95" s="16">
         <v>0</v>
@@ -12732,7 +12744,7 @@
         <v>6000</v>
       </c>
       <c r="AL95" s="9">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AM95" s="9">
         <v>0</v>
@@ -12749,10 +12761,10 @@
         <v>92</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>67</v>
@@ -12760,29 +12772,29 @@
       <c r="G96" s="3">
         <v>0</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
+      <c r="H96" s="3" t="s">
+        <v>266</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>800002014</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K96" s="3">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
       <c r="M96" s="3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N96" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O96" s="3">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -12806,22 +12818,22 @@
         <v>1</v>
       </c>
       <c r="W96" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X96" s="3">
         <v>0</v>
       </c>
       <c r="Y96" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z96" s="3">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="AA96" s="3">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="AB96" s="16">
-        <v>0</v>
+        <v>202001001</v>
       </c>
       <c r="AC96" s="16">
         <v>0</v>
@@ -12851,7 +12863,7 @@
         <v>6000</v>
       </c>
       <c r="AL96" s="9">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AM96" s="9">
         <v>0</v>
@@ -12868,10 +12880,10 @@
         <v>92</v>
       </c>
       <c r="D97" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E97" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F97" s="3" t="s">
         <v>67</v>
@@ -12879,29 +12891,29 @@
       <c r="G97" s="3">
         <v>0</v>
       </c>
-      <c r="H97" s="3">
-        <v>0</v>
+      <c r="H97" s="3" t="s">
+        <v>267</v>
       </c>
       <c r="I97" s="3">
-        <v>0</v>
+        <v>800002011</v>
       </c>
       <c r="J97" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K97" s="3">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="L97" s="3">
         <v>0</v>
       </c>
       <c r="M97" s="3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N97" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O97" s="3">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="P97" s="3">
         <v>0</v>
@@ -12925,22 +12937,22 @@
         <v>1</v>
       </c>
       <c r="W97" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X97" s="3">
         <v>0</v>
       </c>
       <c r="Y97" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z97" s="3">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="AA97" s="3">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="AB97" s="16">
-        <v>0</v>
+        <v>202001001</v>
       </c>
       <c r="AC97" s="16">
         <v>0</v>
@@ -12970,7 +12982,7 @@
         <v>6000</v>
       </c>
       <c r="AL97" s="9">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AM97" s="9">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D70EA58-3E90-404F-BA93-3501DB8B29E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3251C50-64A6-4D34-A2B0-791B46DE9B97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="269">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -866,6 +866,9 @@
   <si>
     <t>强盗1</t>
   </si>
+  <si>
+    <t>强盗抗火</t>
+  </si>
 </sst>
 </file>
 
@@ -7775,28 +7778,28 @@
         <v>0</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="I54" s="3">
-        <v>800016011</v>
+        <v>800002041</v>
       </c>
       <c r="J54" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K54" s="3">
-        <v>10836</v>
+        <v>627</v>
       </c>
       <c r="L54" s="3">
         <v>0</v>
       </c>
       <c r="M54" s="3">
-        <v>829</v>
+        <v>44</v>
       </c>
       <c r="N54" s="3">
-        <v>104</v>
+        <v>4</v>
       </c>
       <c r="O54" s="3">
-        <v>158531</v>
+        <v>1993</v>
       </c>
       <c r="P54" s="3">
         <v>0</v>
@@ -12416,28 +12419,28 @@
         <v>0</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="I93" s="3">
-        <v>800002041</v>
+        <v>800002013</v>
       </c>
       <c r="J93" s="3">
         <v>2</v>
       </c>
       <c r="K93" s="3">
-        <v>627</v>
+        <v>146</v>
       </c>
       <c r="L93" s="3">
         <v>0</v>
       </c>
       <c r="M93" s="3">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="N93" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O93" s="3">
-        <v>1993</v>
+        <v>56</v>
       </c>
       <c r="P93" s="3">
         <v>6000</v>

--- a/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_foe_v8【迷宫-敌人信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3251C50-64A6-4D34-A2B0-791B46DE9B97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{113AD486-2A0D-4B7A-9266-3AD5CF1F4168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7838,7 +7838,7 @@
         <v>20001</v>
       </c>
       <c r="AB54" s="16">
-        <v>216001001</v>
+        <v>202004001</v>
       </c>
       <c r="AC54" s="16">
         <v>0</v>
@@ -12410,7 +12410,7 @@
         <v>2</v>
       </c>
       <c r="E93" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>67</v>
@@ -12470,16 +12470,16 @@
         <v>0</v>
       </c>
       <c r="Y93" s="3">
-        <v>30001</v>
+        <v>8</v>
       </c>
       <c r="Z93" s="3">
-        <v>1</v>
+        <v>174</v>
       </c>
       <c r="AA93" s="3">
-        <v>1</v>
+        <v>136</v>
       </c>
       <c r="AB93" s="16">
-        <v>202004001</v>
+        <v>202001001</v>
       </c>
       <c r="AC93" s="16">
         <v>0</v>
@@ -12509,7 +12509,7 @@
         <v>8000</v>
       </c>
       <c r="AL93" s="9">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="AM93" s="9">
         <v>0</v>
